--- a/plate3d/PLATE3D_COLUMN.xlsx
+++ b/plate3d/PLATE3D_COLUMN.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="333">
   <si>
     <t>COLUMN</t>
   </si>
@@ -53,6 +53,9 @@
     <t>r</t>
   </si>
   <si>
+    <t>Alpha</t>
+  </si>
+  <si>
     <t>kg/m</t>
   </si>
   <si>
@@ -98,6 +101,9 @@
     <t>splices</t>
   </si>
   <si>
+    <t>flanges face</t>
+  </si>
+  <si>
     <t xml:space="preserve">  2.  SPLICE PLATES</t>
   </si>
   <si>
@@ -122,18 +128,21 @@
     <t>Flange plate</t>
   </si>
   <si>
+    <t>Type H</t>
+  </si>
+  <si>
     <t>Flange inner plate</t>
   </si>
   <si>
-    <t>Type H</t>
-  </si>
-  <si>
     <t>Web plate</t>
   </si>
   <si>
     <t>End plate</t>
   </si>
   <si>
+    <t>Type R</t>
+  </si>
+  <si>
     <t>Width is across the flange or through the web; Length runs along the column. The end plate follows the section, plus 60 all round.</t>
   </si>
   <si>
@@ -369,6 +378,9 @@
   </si>
   <si>
     <t>upper, clear of the joint</t>
+  </si>
+  <si>
+    <t>the splice point goes round the axis with the rest of it</t>
   </si>
   <si>
     <t>END</t>
@@ -1590,15 +1602,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:J30"/>
+  <dimension ref="B1:K30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="3" customWidth="1"/>
+    <col min="5" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
@@ -1611,7 +1623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="4" ht="20" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1625,8 +1637,9 @@
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
-    </row>
-    <row r="5" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="4"/>
+    </row>
+    <row r="5" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C5" s="5" t="s">
         <v>4</v>
       </c>
@@ -1651,16 +1664,19 @@
       <c r="J5" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" s="8">
         <f>IF(PARAM!$C$6="H",IFERROR(VLOOKUP($D$6,SECT!$A:$G,2,FALSE),""),IFERROR(VLOOKUP($D$6,TUBE!$A:$G,2,FALSE),""))</f>
@@ -1682,53 +1698,57 @@
         <f>IF(PARAM!$C$6="H",IFERROR(VLOOKUP($D$6,SECT!$A:$G,6,FALSE),""),IFERROR(VLOOKUP($D$6,TUBE!$A:$G,6,FALSE),""))</f>
         <v>18</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="7">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9">
         <f>IF(PARAM!$C$6="H",IFERROR(VLOOKUP($D$6,SECT!$A:$G,7,FALSE),""),IFERROR(VLOOKUP($D$6,TUBE!$A:$G,7,FALSE),""))</f>
         <v>94</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7" s="7">
         <v>700</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7" s="7">
         <v>1400</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I7" s="7">
         <v>700</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
       <c r="J8" s="11"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K8" s="11"/>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="12"/>
       <c r="D9" s="12"/>
@@ -1738,39 +1758,40 @@
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10" s="11" t="str">
         <f>IF(PARAM!$E$6="","fill in the dimensions","ok")</f>
         <v>ok</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" s="11" t="str">
         <f>(IF(PARAM!$E$7&gt;0,1,0)+IF(PARAM!$I$7&gt;0,1,0))&amp;" of 2"</f>
         <v>2 of 2</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="H10" s="11" t="str">
-        <f>IF(PARAM!$G$7&gt;0,"ok","the middle piece has to be there")</f>
-        <v>ok</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+        <f>IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,"X","Y"),"all four alike")</f>
+        <v>X</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -1779,30 +1800,31 @@
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
     </row>
     <row r="13" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E13" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E14" s="7">
         <v>300</v>
@@ -1817,15 +1839,18 @@
         <v>2</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J14" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K14" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E15" s="7">
         <v>110</v>
@@ -1840,15 +1865,15 @@
         <v>4</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E16" s="7">
         <v>234</v>
@@ -1863,15 +1888,15 @@
         <v>2</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E17" s="17">
         <f>PARAM!$E$6+2*PARAM!$J$17</f>
@@ -1888,15 +1913,18 @@
         <v>2</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J17" s="7">
         <v>60</v>
       </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K17" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="12" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -1906,39 +1934,40 @@
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D19" s="11" t="str">
         <f>IF(PARAM!$C$6="H","cover plates","end plate")</f>
         <v>cover plates</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F19" s="11">
         <f>ROUND(IF(PARAM!$C$6="H",PARAM!$E$14*PARAM!$F$14*PARAM!$G$14*2+PARAM!$E$15*PARAM!$F$15*PARAM!$G$15*4+PARAM!$E$16*PARAM!$F$16*PARAM!$G$16*2,PARAM!$E$17*PARAM!$F$17*PARAM!$G$17*2)*7.85/1000000,1)</f>
         <v>42.2</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H19" s="11">
         <f>PARAM!$J$14</f>
         <v>10</v>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="21" ht="20" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -1947,30 +1976,31 @@
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
     </row>
     <row r="22" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E22" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E23" s="7">
         <v>16</v>
@@ -1980,7 +2010,7 @@
         <v>18</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H23" s="18">
         <f>IF(PARAM!$C$6="H",CEILING(PARAM!$G$14+PARAM!$H$6+PARAM!$G$15+1.1*PARAM!$E$23,5),"—")</f>
@@ -1997,30 +2027,30 @@
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="19" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E25" s="7">
         <v>4</v>
@@ -2043,7 +2073,7 @@
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E26" s="7">
         <v>4</v>
@@ -2066,21 +2096,21 @@
     </row>
     <row r="27" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E27" s="5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B28" s="16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E28" s="7">
         <v>3</v>
@@ -2095,9 +2125,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
@@ -2107,27 +2137,28 @@
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D30" s="11" t="str">
         <f>IF(PARAM!$C$6="H",ROUND((PARAM!$F$14/2-PARAM!$G$25-PARAM!$F$25/2)/(PARAM!$E$25/2-1),1)&amp;" / "&amp;ROUND((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1),1),"n/a")</f>
         <v>85 / 60</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F30" s="11" t="str">
         <f>IF(PARAM!$C$6="H",ROUND((PARAM!$F$16/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1),1)&amp;" / "&amp;ROUND((PARAM!$E$16-2*PARAM!$J$26-PARAM!$I$26)/(PARAM!$H$26-1),1),"n/a")</f>
         <v>90 / 77</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H30" s="11" t="str">
         <f>IF(PARAM!$C$6="H",2*PARAM!$E$25*PARAM!$H$25+PARAM!$E$26*PARAM!$H$26,2*PARAM!$E$28+2*MAX(0,PARAM!$H$28-2))&amp;" per splice"</f>
@@ -2136,15 +2167,15 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="C4:J4"/>
-    <mergeCell ref="E8:J8"/>
-    <mergeCell ref="B9:J9"/>
-    <mergeCell ref="C12:J12"/>
-    <mergeCell ref="B18:J18"/>
-    <mergeCell ref="C21:J21"/>
-    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="E8:K8"/>
+    <mergeCell ref="B9:K9"/>
+    <mergeCell ref="C12:K12"/>
+    <mergeCell ref="B18:K18"/>
+    <mergeCell ref="C21:K21"/>
+    <mergeCell ref="B29:K29"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" showErrorMessage="1" error="H for an I section, R for a square tube." sqref="C6">
       <formula1>"H,R"</formula1>
     </dataValidation>
@@ -2153,6 +2184,9 @@
     </dataValidation>
     <dataValidation type="list" sqref="G23">
       <formula1>"F8T,F10T,F13T"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" error="0, 90 or -90 degrees about the column axis." sqref="J6">
+      <formula1>"0,90,-90"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2174,41 +2208,41 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D6" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -2223,7 +2257,7 @@
         <v>H</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H6" s="21">
         <f>PARAM!$E$6</f>
@@ -2256,13 +2290,13 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D7" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -2277,7 +2311,7 @@
         <v>H</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H7" s="21">
         <f>PARAM!$E$6</f>
@@ -2310,13 +2344,13 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D8" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -2331,7 +2365,7 @@
         <v>H</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H8" s="21">
         <f>PARAM!$E$6</f>
@@ -2364,23 +2398,23 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D11" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -2391,10 +2425,10 @@
         <v>12</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H11" s="21">
         <f>IF(PARAM!$C$6="H",PARAM!$E$14,PARAM!$E$17)</f>
@@ -2407,13 +2441,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="B12" s="20" t="s">
-        <v>78</v>
-      </c>
       <c r="C12" s="21" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D12" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -2424,10 +2458,10 @@
         <v>10</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H12" s="21">
         <f>PARAM!$E$15</f>
@@ -2440,13 +2474,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D13" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -2457,10 +2491,10 @@
         <v>10</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H13" s="21">
         <f>PARAM!$E$16</f>
@@ -2473,13 +2507,13 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D14" s="21" t="str">
         <f>PARAM!$G$23</f>
@@ -2511,13 +2545,13 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D15" s="21" t="str">
         <f>PARAM!$G$23</f>
@@ -2549,28 +2583,28 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D19" s="21" t="str">
         <f>IF(PARAM!$E$7&gt;0,"sc.c1","")</f>
@@ -2587,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J19" s="21">
         <v>0</v>
@@ -2601,27 +2635,27 @@
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" s="21" t="str">
         <f>"sc.c2"</f>
@@ -2638,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="21" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J21" s="21">
         <v>0</v>
@@ -2652,27 +2686,27 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D23" s="21" t="str">
         <f>IF(PARAM!$I$7&gt;0,"sc.c3","")</f>
@@ -2689,7 +2723,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="21" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J23" s="21">
         <v>0</v>
@@ -2703,47 +2737,47 @@
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D27" s="21" t="str">
         <f>IF(PARAM!$E$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F27" s="21">
         <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$14/2)),0)</f>
@@ -2763,17 +2797,17 @@
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B28" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D28" s="21" t="str">
         <f>IF(PARAM!$E$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F28" s="21">
         <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$14/2)),0)</f>
@@ -2793,20 +2827,20 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D29" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F29" s="21">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15/2))</f>
@@ -2820,22 +2854,22 @@
         <v>0</v>
       </c>
       <c r="I29" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D30" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F30" s="21">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15/2))</f>
@@ -2849,22 +2883,22 @@
         <v>0</v>
       </c>
       <c r="I30" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D31" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F31" s="21">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15/2))</f>
@@ -2878,22 +2912,22 @@
         <v>0</v>
       </c>
       <c r="I31" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D32" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F32" s="21">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15/2))</f>
@@ -2907,25 +2941,25 @@
         <v>0</v>
       </c>
       <c r="I32" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" s="21" t="s">
         <v>104</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>101</v>
       </c>
       <c r="D33" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F33" s="21">
         <v>0</v>
@@ -2938,22 +2972,22 @@
         <v>0</v>
       </c>
       <c r="I33" s="21" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D34" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F34" s="21">
         <v>0</v>
@@ -2966,18 +3000,18 @@
         <v>0</v>
       </c>
       <c r="I34" s="21" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D35" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -2997,7 +3031,7 @@
         <v>35</v>
       </c>
       <c r="I35" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J35" s="21">
         <v>0</v>
@@ -3039,10 +3073,10 @@
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B36" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D36" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3062,7 +3096,7 @@
         <v>35</v>
       </c>
       <c r="I36" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J36" s="21">
         <v>0</v>
@@ -3104,10 +3138,10 @@
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B37" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D37" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3127,7 +3161,7 @@
         <v>-35</v>
       </c>
       <c r="I37" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J37" s="21">
         <v>0</v>
@@ -3169,10 +3203,10 @@
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B38" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D38" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3192,7 +3226,7 @@
         <v>-35</v>
       </c>
       <c r="I38" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J38" s="21">
         <v>0</v>
@@ -3234,10 +3268,10 @@
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B39" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D39" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3257,7 +3291,7 @@
         <v>35</v>
       </c>
       <c r="I39" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J39" s="21">
         <v>0</v>
@@ -3299,10 +3333,10 @@
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B40" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D40" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3322,7 +3356,7 @@
         <v>35</v>
       </c>
       <c r="I40" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J40" s="21">
         <v>0</v>
@@ -3364,10 +3398,10 @@
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B41" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D41" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3387,7 +3421,7 @@
         <v>-35</v>
       </c>
       <c r="I41" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J41" s="21">
         <v>0</v>
@@ -3429,10 +3463,10 @@
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B42" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D42" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3452,7 +3486,7 @@
         <v>-35</v>
       </c>
       <c r="I42" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J42" s="21">
         <v>0</v>
@@ -3494,13 +3528,13 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D43" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -3520,7 +3554,7 @@
         <v>-10</v>
       </c>
       <c r="I43" s="21" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J43" s="21">
         <v>0</v>
@@ -3548,10 +3582,10 @@
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B44" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D44" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -3571,7 +3605,7 @@
         <v>-10</v>
       </c>
       <c r="I44" s="21" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J44" s="21">
         <v>0</v>
@@ -3599,13 +3633,13 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D45" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$28&gt;2),"bo.f","")</f>
@@ -3625,7 +3659,7 @@
         <v>-10</v>
       </c>
       <c r="I45" s="21" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J45" s="21">
         <v>0</v>
@@ -3653,10 +3687,10 @@
     </row>
     <row r="46" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B46" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D46" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$28&gt;2),"bo.f","")</f>
@@ -3676,7 +3710,7 @@
         <v>-10</v>
       </c>
       <c r="I46" s="21" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J46" s="21">
         <v>0</v>
@@ -3704,13 +3738,13 @@
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D47" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -3730,7 +3764,7 @@
         <v>30</v>
       </c>
       <c r="I47" s="21" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J47" s="21">
         <v>0</v>
@@ -3772,10 +3806,10 @@
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B48" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D48" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -3795,7 +3829,7 @@
         <v>-30</v>
       </c>
       <c r="I48" s="21" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J48" s="21">
         <v>0</v>
@@ -3837,34 +3871,34 @@
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B49" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F49" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B50" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D50" s="21" t="str">
         <f>IF(PARAM!$I$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F50" s="21">
         <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$14/2)),0)</f>
@@ -3884,17 +3918,17 @@
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B51" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D51" s="21" t="str">
         <f>IF(PARAM!$I$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E51" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F51" s="21">
         <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$14/2)),0)</f>
@@ -3914,17 +3948,17 @@
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B52" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D52" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E52" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F52" s="21">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15/2))</f>
@@ -3938,22 +3972,22 @@
         <v>0</v>
       </c>
       <c r="I52" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B53" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D53" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E53" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F53" s="21">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15/2))</f>
@@ -3967,22 +4001,22 @@
         <v>0</v>
       </c>
       <c r="I53" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B54" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D54" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F54" s="21">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15/2))</f>
@@ -3996,22 +4030,22 @@
         <v>0</v>
       </c>
       <c r="I54" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B55" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D55" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E55" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F55" s="21">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15/2))</f>
@@ -4025,22 +4059,22 @@
         <v>0</v>
       </c>
       <c r="I55" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B56" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D56" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E56" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F56" s="21">
         <v>0</v>
@@ -4053,22 +4087,22 @@
         <v>0</v>
       </c>
       <c r="I56" s="21" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B57" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D57" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E57" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F57" s="21">
         <v>0</v>
@@ -4081,15 +4115,15 @@
         <v>0</v>
       </c>
       <c r="I57" s="21" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B58" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D58" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4109,7 +4143,7 @@
         <v>35</v>
       </c>
       <c r="I58" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J58" s="21">
         <v>0</v>
@@ -4151,10 +4185,10 @@
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B59" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D59" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4174,7 +4208,7 @@
         <v>35</v>
       </c>
       <c r="I59" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J59" s="21">
         <v>0</v>
@@ -4216,10 +4250,10 @@
     </row>
     <row r="60" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B60" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D60" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4239,7 +4273,7 @@
         <v>-35</v>
       </c>
       <c r="I60" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J60" s="21">
         <v>0</v>
@@ -4281,10 +4315,10 @@
     </row>
     <row r="61" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B61" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D61" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4304,7 +4338,7 @@
         <v>-35</v>
       </c>
       <c r="I61" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J61" s="21">
         <v>0</v>
@@ -4346,10 +4380,10 @@
     </row>
     <row r="62" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B62" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D62" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4369,7 +4403,7 @@
         <v>35</v>
       </c>
       <c r="I62" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J62" s="21">
         <v>0</v>
@@ -4411,10 +4445,10 @@
     </row>
     <row r="63" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B63" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D63" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4434,7 +4468,7 @@
         <v>35</v>
       </c>
       <c r="I63" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J63" s="21">
         <v>0</v>
@@ -4476,10 +4510,10 @@
     </row>
     <row r="64" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B64" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D64" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4499,7 +4533,7 @@
         <v>-35</v>
       </c>
       <c r="I64" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J64" s="21">
         <v>0</v>
@@ -4541,10 +4575,10 @@
     </row>
     <row r="65" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B65" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D65" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4564,7 +4598,7 @@
         <v>-35</v>
       </c>
       <c r="I65" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J65" s="21">
         <v>0</v>
@@ -4606,10 +4640,10 @@
     </row>
     <row r="66" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B66" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D66" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -4629,7 +4663,7 @@
         <v>-10</v>
       </c>
       <c r="I66" s="21" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J66" s="21">
         <v>0</v>
@@ -4657,10 +4691,10 @@
     </row>
     <row r="67" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B67" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D67" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -4680,7 +4714,7 @@
         <v>-10</v>
       </c>
       <c r="I67" s="21" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J67" s="21">
         <v>0</v>
@@ -4708,10 +4742,10 @@
     </row>
     <row r="68" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B68" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D68" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$28&gt;2),"bo.f","")</f>
@@ -4731,7 +4765,7 @@
         <v>-10</v>
       </c>
       <c r="I68" s="21" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J68" s="21">
         <v>0</v>
@@ -4759,10 +4793,10 @@
     </row>
     <row r="69" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B69" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D69" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$28&gt;2),"bo.f","")</f>
@@ -4782,7 +4816,7 @@
         <v>-10</v>
       </c>
       <c r="I69" s="21" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J69" s="21">
         <v>0</v>
@@ -4810,10 +4844,10 @@
     </row>
     <row r="70" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B70" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D70" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -4833,7 +4867,7 @@
         <v>30</v>
       </c>
       <c r="I70" s="21" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J70" s="21">
         <v>0</v>
@@ -4875,10 +4909,10 @@
     </row>
     <row r="71" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B71" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D71" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -4898,7 +4932,7 @@
         <v>-30</v>
       </c>
       <c r="I71" s="21" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J71" s="21">
         <v>0</v>
@@ -4940,46 +4974,46 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B72" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E72" s="21" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F72" s="21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B75" s="20" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C75" s="21" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E75" s="21" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F75" s="21">
         <v>0</v>
@@ -4991,22 +5025,32 @@
         <f>-PARAM!$G$7/2</f>
         <v>-700</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I75" s="21">
+        <v>0</v>
+      </c>
+      <c r="J75" s="21">
+        <v>0</v>
+      </c>
+      <c r="K75" s="21">
+        <f>PARAM!$J$6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B76" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="B76" s="20" t="s">
-        <v>113</v>
-      </c>
       <c r="C76" s="21" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D76" s="21" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E76" s="21" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F76" s="21">
         <v>0</v>
@@ -5018,22 +5062,32 @@
         <f>(PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$14,2*PARAM!$G$17))</f>
         <v>710</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I76" s="21">
+        <v>0</v>
+      </c>
+      <c r="J76" s="21">
+        <v>0</v>
+      </c>
+      <c r="K76" s="21">
+        <f>PARAM!$J$6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B77" s="20" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E77" s="21" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F77" s="21">
         <v>0</v>
@@ -5045,65 +5099,100 @@
         <f>-((PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$14,2*PARAM!$G$17))+MAX(1,PARAM!$I$7))</f>
         <v>-1410</v>
       </c>
-    </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I77" s="21">
+        <v>0</v>
+      </c>
+      <c r="J77" s="21">
+        <v>0</v>
+      </c>
+      <c r="K77" s="21">
+        <f>PARAM!$J$6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" s="12" t="s">
+        <v>120</v>
+      </c>
       <c r="B78" s="20" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E78" s="21" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F78" s="21">
-        <f>IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$14/2),0)</f>
+        <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$14/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
         <v>156</v>
       </c>
       <c r="G78" s="21">
+        <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$14/2),0))*SIN(RADIANS(PARAM!$J$6)),6)</f>
         <v>0</v>
       </c>
       <c r="H78" s="21">
         <f>(PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$14/2,PARAM!$G$17))+IF(PARAM!$C$6="H",0,-PARAM!$G$17/2)</f>
         <v>705</v>
       </c>
-    </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I78" s="21">
+        <v>0</v>
+      </c>
+      <c r="J78" s="21">
+        <v>0</v>
+      </c>
+      <c r="K78" s="21">
+        <f>PARAM!$J$6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79" s="20" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C79" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D79" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="D79" s="21" t="s">
-        <v>111</v>
-      </c>
       <c r="E79" s="21" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F79" s="21">
-        <f>IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$14/2),0)</f>
+        <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$14/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
         <v>156</v>
       </c>
       <c r="G79" s="21">
+        <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$14/2),0))*SIN(RADIANS(PARAM!$J$6)),6)</f>
         <v>0</v>
       </c>
       <c r="H79" s="21">
         <f>-(PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$14/2,PARAM!$G$17))+IF(PARAM!$C$6="H",0,PARAM!$G$17/2)</f>
         <v>-705</v>
       </c>
+      <c r="I79" s="21">
+        <v>0</v>
+      </c>
+      <c r="J79" s="21">
+        <v>0</v>
+      </c>
+      <c r="K79" s="21">
+        <f>PARAM!$J$6</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="81" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B81" s="20" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -5131,7 +5220,7 @@
         <v>7</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E1" s="23" t="s">
         <v>9</v>
@@ -5140,12 +5229,12 @@
         <v>10</v>
       </c>
       <c r="G1" s="23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
@@ -5156,7 +5245,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B3" s="27">
         <v>100</v>
@@ -5179,7 +5268,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B4" s="29">
         <v>125</v>
@@ -5202,7 +5291,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B5" s="27">
         <v>150</v>
@@ -5225,7 +5314,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B6" s="29">
         <v>148</v>
@@ -5248,7 +5337,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B7" s="27">
         <v>150</v>
@@ -5271,7 +5360,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B8" s="29">
         <v>198</v>
@@ -5294,7 +5383,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B9" s="27">
         <v>200</v>
@@ -5317,7 +5406,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B10" s="29">
         <v>194</v>
@@ -5340,7 +5429,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B11" s="27">
         <v>200</v>
@@ -5363,7 +5452,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B12" s="29">
         <v>200</v>
@@ -5386,7 +5475,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B13" s="27">
         <v>248</v>
@@ -5409,7 +5498,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B14" s="29">
         <v>250</v>
@@ -5432,7 +5521,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B15" s="27">
         <v>244</v>
@@ -5455,7 +5544,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B16" s="29">
         <v>250</v>
@@ -5478,7 +5567,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B17" s="27">
         <v>250</v>
@@ -5501,7 +5590,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B18" s="29">
         <v>298</v>
@@ -5524,7 +5613,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B19" s="27">
         <v>300</v>
@@ -5547,7 +5636,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B20" s="29">
         <v>294</v>
@@ -5570,7 +5659,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B21" s="27">
         <v>294</v>
@@ -5593,7 +5682,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B22" s="29">
         <v>300</v>
@@ -5616,7 +5705,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B23" s="27">
         <v>300</v>
@@ -5639,7 +5728,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B24" s="29">
         <v>346</v>
@@ -5662,7 +5751,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B25" s="27">
         <v>350</v>
@@ -5685,7 +5774,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B26" s="29">
         <v>340</v>
@@ -5708,7 +5797,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B27" s="27">
         <v>344</v>
@@ -5731,7 +5820,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B28" s="29">
         <v>350</v>
@@ -5754,7 +5843,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B29" s="27">
         <v>396</v>
@@ -5777,7 +5866,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B30" s="29">
         <v>400</v>
@@ -5800,7 +5889,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B31" s="27">
         <v>390</v>
@@ -5823,7 +5912,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="28" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B32" s="29">
         <v>388</v>
@@ -5846,7 +5935,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B33" s="27">
         <v>394</v>
@@ -5869,7 +5958,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="28" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B34" s="29">
         <v>400</v>
@@ -5892,7 +5981,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B35" s="27">
         <v>400</v>
@@ -5915,7 +6004,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B36" s="29">
         <v>414</v>
@@ -5938,7 +6027,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="26" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B37" s="27">
         <v>428</v>
@@ -5961,7 +6050,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="28" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B38" s="29">
         <v>458</v>
@@ -5984,7 +6073,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B39" s="27">
         <v>498</v>
@@ -6007,7 +6096,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="28" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B40" s="29">
         <v>446</v>
@@ -6030,7 +6119,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B41" s="27">
         <v>450</v>
@@ -6053,7 +6142,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="28" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B42" s="29">
         <v>440</v>
@@ -6076,7 +6165,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B43" s="27">
         <v>440</v>
@@ -6099,7 +6188,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="28" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B44" s="29">
         <v>496</v>
@@ -6122,7 +6211,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="26" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B45" s="27">
         <v>500</v>
@@ -6145,7 +6234,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="28" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B46" s="29">
         <v>482</v>
@@ -6168,7 +6257,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="26" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B47" s="27">
         <v>488</v>
@@ -6191,7 +6280,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="28" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B48" s="29">
         <v>596</v>
@@ -6214,7 +6303,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B49" s="27">
         <v>600</v>
@@ -6237,7 +6326,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="28" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B50" s="29">
         <v>582</v>
@@ -6260,7 +6349,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="26" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B51" s="27">
         <v>588</v>
@@ -6283,7 +6372,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="28" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B52" s="29">
         <v>594</v>
@@ -6306,7 +6395,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="26" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B53" s="27">
         <v>692</v>
@@ -6329,7 +6418,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="28" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B54" s="29">
         <v>700</v>
@@ -6352,7 +6441,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B55" s="27">
         <v>792</v>
@@ -6375,7 +6464,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="28" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B56" s="29">
         <v>800</v>
@@ -6398,7 +6487,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B57" s="27">
         <v>890</v>
@@ -6421,7 +6510,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="28" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B58" s="29">
         <v>900</v>
@@ -6444,7 +6533,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B59" s="27">
         <v>912</v>
@@ -6467,7 +6556,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="28" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B60" s="29">
         <v>918</v>
@@ -6513,7 +6602,7 @@
         <v>7</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E1" s="23" t="s">
         <v>9</v>
@@ -6522,12 +6611,12 @@
         <v>10</v>
       </c>
       <c r="G1" s="23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
@@ -6538,7 +6627,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B3" s="27">
         <v>20</v>
@@ -6561,7 +6650,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B4" s="29">
         <v>20</v>
@@ -6584,7 +6673,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B5" s="27">
         <v>25</v>
@@ -6607,7 +6696,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B6" s="29">
         <v>25</v>
@@ -6630,7 +6719,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B7" s="27">
         <v>30</v>
@@ -6653,7 +6742,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B8" s="29">
         <v>30</v>
@@ -6676,7 +6765,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B9" s="27">
         <v>40</v>
@@ -6699,7 +6788,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B10" s="29">
         <v>40</v>
@@ -6722,7 +6811,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B11" s="27">
         <v>50</v>
@@ -6745,7 +6834,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B12" s="29">
         <v>50</v>
@@ -6768,7 +6857,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B13" s="27">
         <v>50</v>
@@ -6791,7 +6880,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B14" s="29">
         <v>60</v>
@@ -6814,7 +6903,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B15" s="27">
         <v>60</v>
@@ -6837,7 +6926,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B16" s="29">
         <v>60</v>
@@ -6860,7 +6949,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B17" s="27">
         <v>75</v>
@@ -6883,7 +6972,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B18" s="29">
         <v>75</v>
@@ -6906,7 +6995,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B19" s="27">
         <v>75</v>
@@ -6929,7 +7018,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B20" s="29">
         <v>75</v>
@@ -6952,7 +7041,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B21" s="27">
         <v>80</v>
@@ -6975,7 +7064,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B22" s="29">
         <v>80</v>
@@ -6998,7 +7087,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B23" s="27">
         <v>80</v>
@@ -7021,7 +7110,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B24" s="29">
         <v>90</v>
@@ -7044,7 +7133,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B25" s="27">
         <v>90</v>
@@ -7067,7 +7156,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B26" s="29">
         <v>100</v>
@@ -7090,7 +7179,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B27" s="27">
         <v>100</v>
@@ -7113,7 +7202,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B28" s="29">
         <v>100</v>
@@ -7136,7 +7225,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B29" s="27">
         <v>100</v>
@@ -7159,7 +7248,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B30" s="29">
         <v>100</v>
@@ -7182,7 +7271,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B31" s="27">
         <v>100</v>
@@ -7205,7 +7294,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="28" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B32" s="29">
         <v>100</v>
@@ -7228,7 +7317,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B33" s="27">
         <v>125</v>
@@ -7251,7 +7340,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="28" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B34" s="29">
         <v>125</v>
@@ -7274,7 +7363,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B35" s="27">
         <v>125</v>
@@ -7297,7 +7386,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B36" s="29">
         <v>125</v>
@@ -7320,7 +7409,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="26" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B37" s="27">
         <v>125</v>
@@ -7343,7 +7432,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="28" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B38" s="29">
         <v>125</v>
@@ -7366,7 +7455,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B39" s="27">
         <v>150</v>
@@ -7389,7 +7478,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="28" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B40" s="29">
         <v>150</v>
@@ -7412,7 +7501,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B41" s="27">
         <v>150</v>
@@ -7435,7 +7524,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="28" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B42" s="29">
         <v>150</v>
@@ -7458,7 +7547,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B43" s="27">
         <v>175</v>
@@ -7481,7 +7570,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="28" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B44" s="29">
         <v>175</v>
@@ -7504,7 +7593,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="26" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B45" s="27">
         <v>175</v>
@@ -7527,7 +7616,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="28" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B46" s="29">
         <v>200</v>
@@ -7550,7 +7639,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="26" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B47" s="27">
         <v>200</v>
@@ -7573,7 +7662,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="28" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B48" s="29">
         <v>200</v>
@@ -7596,7 +7685,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B49" s="27">
         <v>200</v>
@@ -7619,7 +7708,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="28" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B50" s="29">
         <v>200</v>
@@ -7642,7 +7731,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="26" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B51" s="27">
         <v>250</v>
@@ -7665,7 +7754,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="28" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B52" s="29">
         <v>250</v>
@@ -7688,7 +7777,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="26" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B53" s="27">
         <v>250</v>
@@ -7711,7 +7800,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="28" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B54" s="29">
         <v>250</v>
@@ -7734,7 +7823,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B55" s="27">
         <v>250</v>
@@ -7757,7 +7846,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="28" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B56" s="29">
         <v>300</v>
@@ -7780,7 +7869,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B57" s="27">
         <v>300</v>
@@ -7803,7 +7892,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="28" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B58" s="29">
         <v>300</v>
@@ -7826,7 +7915,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B59" s="27">
         <v>300</v>
@@ -7849,7 +7938,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="28" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B60" s="29">
         <v>200</v>
@@ -7872,7 +7961,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B61" s="27">
         <v>200</v>
@@ -7895,7 +7984,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="28" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B62" s="29">
         <v>200</v>
@@ -7918,7 +8007,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="26" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B63" s="27">
         <v>200</v>
@@ -7941,7 +8030,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="28" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B64" s="29">
         <v>250</v>
@@ -7964,7 +8053,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="26" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B65" s="27">
         <v>250</v>
@@ -7987,7 +8076,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="28" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B66" s="29">
         <v>250</v>
@@ -8010,7 +8099,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="26" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B67" s="27">
         <v>250</v>
@@ -8033,7 +8122,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="28" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B68" s="29">
         <v>250</v>
@@ -8056,7 +8145,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="26" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B69" s="27">
         <v>250</v>
@@ -8079,7 +8168,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="28" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B70" s="29">
         <v>300</v>
@@ -8102,7 +8191,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="26" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B71" s="27">
         <v>300</v>
@@ -8125,7 +8214,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="28" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B72" s="29">
         <v>300</v>
@@ -8148,7 +8237,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="26" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B73" s="27">
         <v>300</v>
@@ -8171,7 +8260,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="28" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B74" s="29">
         <v>300</v>
@@ -8194,7 +8283,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="26" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B75" s="27">
         <v>300</v>
@@ -8217,7 +8306,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="28" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B76" s="29">
         <v>300</v>
@@ -8240,7 +8329,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="26" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B77" s="27">
         <v>350</v>
@@ -8263,7 +8352,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="28" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B78" s="29">
         <v>350</v>
@@ -8286,7 +8375,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="26" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B79" s="27">
         <v>350</v>
@@ -8309,7 +8398,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="28" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B80" s="29">
         <v>350</v>
@@ -8332,7 +8421,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="26" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B81" s="27">
         <v>350</v>
@@ -8355,7 +8444,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="28" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B82" s="29">
         <v>350</v>
@@ -8378,7 +8467,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="26" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B83" s="27">
         <v>400</v>
@@ -8401,7 +8490,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="28" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B84" s="29">
         <v>400</v>
@@ -8424,7 +8513,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="26" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B85" s="27">
         <v>400</v>
@@ -8447,7 +8536,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="28" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B86" s="29">
         <v>400</v>
@@ -8470,7 +8559,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="26" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B87" s="27">
         <v>400</v>
@@ -8493,7 +8582,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="28" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B88" s="29">
         <v>400</v>
@@ -8516,7 +8605,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="26" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B89" s="27">
         <v>450</v>
@@ -8539,7 +8628,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="28" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B90" s="29">
         <v>450</v>
@@ -8562,7 +8651,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="26" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B91" s="27">
         <v>450</v>
@@ -8585,7 +8674,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="28" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B92" s="29">
         <v>450</v>
@@ -8608,7 +8697,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="26" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B93" s="27">
         <v>450</v>
@@ -8631,7 +8720,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="28" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B94" s="29">
         <v>450</v>
@@ -8654,7 +8743,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="26" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B95" s="27">
         <v>500</v>
@@ -8677,7 +8766,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="28" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B96" s="29">
         <v>500</v>
@@ -8700,7 +8789,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="26" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B97" s="27">
         <v>500</v>
@@ -8723,7 +8812,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="28" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B98" s="29">
         <v>500</v>
@@ -8746,7 +8835,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="26" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B99" s="27">
         <v>500</v>
@@ -8769,7 +8858,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="28" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B100" s="29">
         <v>500</v>
@@ -8792,7 +8881,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="26" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B101" s="27">
         <v>550</v>
@@ -8815,7 +8904,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="28" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B102" s="29">
         <v>550</v>
@@ -8838,7 +8927,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="26" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B103" s="27">
         <v>550</v>
@@ -8861,7 +8950,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="28" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B104" s="29">
         <v>550</v>
@@ -8884,7 +8973,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="26" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B105" s="27">
         <v>550</v>
@@ -8907,7 +8996,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="28" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B106" s="29">
         <v>600</v>
@@ -8930,7 +9019,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="26" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B107" s="27">
         <v>600</v>
@@ -8953,7 +9042,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="28" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B108" s="29">
         <v>600</v>
@@ -8976,7 +9065,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="26" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B109" s="27">
         <v>600</v>
@@ -8999,7 +9088,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="28" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B110" s="29">
         <v>600</v>
@@ -9022,7 +9111,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="26" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B111" s="27">
         <v>600</v>
@@ -9045,7 +9134,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="28" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B112" s="29">
         <v>600</v>
@@ -9068,7 +9157,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="26" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B113" s="27">
         <v>600</v>
@@ -9091,7 +9180,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="28" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B114" s="29">
         <v>600</v>
@@ -9114,7 +9203,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="26" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B115" s="27">
         <v>600</v>
@@ -9137,7 +9226,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="28" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B116" s="29">
         <v>600</v>
@@ -9160,7 +9249,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="26" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B117" s="27">
         <v>650</v>
@@ -9183,7 +9272,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="28" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B118" s="29">
         <v>650</v>
@@ -9206,7 +9295,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="26" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B119" s="27">
         <v>650</v>
@@ -9229,7 +9318,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="28" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B120" s="29">
         <v>650</v>
@@ -9252,7 +9341,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="26" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B121" s="27">
         <v>650</v>
@@ -9275,7 +9364,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="28" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B122" s="29">
         <v>650</v>
@@ -9298,7 +9387,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="26" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B123" s="27">
         <v>650</v>
@@ -9321,7 +9410,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="28" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B124" s="29">
         <v>650</v>
@@ -9344,7 +9433,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="26" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B125" s="27">
         <v>650</v>
@@ -9367,7 +9456,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="28" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B126" s="29">
         <v>650</v>
@@ -9390,7 +9479,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="26" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B127" s="27">
         <v>700</v>
@@ -9413,7 +9502,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="28" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B128" s="29">
         <v>700</v>
@@ -9436,7 +9525,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="26" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B129" s="27">
         <v>700</v>
@@ -9459,7 +9548,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="28" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B130" s="29">
         <v>700</v>
@@ -9482,7 +9571,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="26" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B131" s="27">
         <v>700</v>
@@ -9505,7 +9594,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="28" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B132" s="29">
         <v>700</v>
@@ -9528,7 +9617,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="26" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B133" s="27">
         <v>700</v>
@@ -9551,7 +9640,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="28" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B134" s="29">
         <v>700</v>
@@ -9574,7 +9663,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="26" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B135" s="27">
         <v>700</v>
@@ -9597,7 +9686,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="28" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B136" s="29">
         <v>700</v>
@@ -9620,7 +9709,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="26" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B137" s="27">
         <v>750</v>
@@ -9643,7 +9732,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="28" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B138" s="29">
         <v>750</v>
@@ -9666,7 +9755,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="26" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B139" s="27">
         <v>750</v>
@@ -9689,7 +9778,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="28" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B140" s="29">
         <v>750</v>
@@ -9712,7 +9801,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="26" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B141" s="27">
         <v>750</v>
@@ -9735,7 +9824,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="28" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B142" s="29">
         <v>750</v>
@@ -9758,7 +9847,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="26" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B143" s="27">
         <v>750</v>
@@ -9781,7 +9870,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="28" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B144" s="29">
         <v>750</v>
@@ -9804,7 +9893,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="26" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B145" s="27">
         <v>750</v>
@@ -9827,7 +9916,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="28" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B146" s="29">
         <v>800</v>
@@ -9850,7 +9939,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="26" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B147" s="27">
         <v>800</v>
@@ -9873,7 +9962,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="28" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B148" s="29">
         <v>800</v>
@@ -9896,7 +9985,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="26" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B149" s="27">
         <v>800</v>
@@ -9919,7 +10008,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="28" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B150" s="29">
         <v>800</v>
@@ -9942,7 +10031,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="26" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B151" s="27">
         <v>800</v>
@@ -9965,7 +10054,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="28" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B152" s="29">
         <v>800</v>
@@ -9988,7 +10077,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="26" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B153" s="27">
         <v>800</v>
@@ -10011,7 +10100,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B154" s="29">
         <v>800</v>

--- a/plate3d/PLATE3D_COLUMN.xlsx
+++ b/plate3d/PLATE3D_COLUMN.xlsx
@@ -152,7 +152,7 @@
     <t>plate steel, kg</t>
   </si>
   <si>
-    <t>joint gap</t>
+    <t>plates fit</t>
   </si>
   <si>
     <t xml:space="preserve">  3.  BOLTS</t>
@@ -1957,9 +1957,9 @@
       <c r="G19" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H19" s="11">
-        <f>PARAM!$J$14</f>
-        <v>10</v>
+      <c r="H19" s="11" t="str">
+        <f>IF(PARAM!$C$6="H",IF(AND(PARAM!$E$14&lt;=PARAM!$F$6,PARAM!$E$16&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6),"ok",IF(PARAM!$E$14&gt;PARAM!$F$6,"flange plate too wide","web plate too deep")),"n/a")</f>
+        <v>ok</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">

--- a/plate3d/PLATE3D_COLUMN.xlsx
+++ b/plate3d/PLATE3D_COLUMN.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="334">
   <si>
     <t>COLUMN</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>Pick "user define" at the top of either list and the five cells go blank — type over them. A tube has no flange, so its wall goes in tw and tf alike.</t>
+  </si>
+  <si>
+    <t>Alpha turns the whole column about its axis, plates and bolts with it. 0 faces the flanges along X, ±90 along Y; a tube looks alike either way.</t>
   </si>
   <si>
     <t>checked for you</t>
@@ -1602,7 +1605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K30"/>
+  <dimension ref="B1:K31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -1760,115 +1763,106 @@
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="11" t="s">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="11" t="str">
+      <c r="C11" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="11" t="str">
         <f>IF(PARAM!$E$6="","fill in the dimensions","ok")</f>
         <v>ok</v>
       </c>
-      <c r="E10" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="11" t="str">
+      <c r="E11" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="11" t="str">
         <f>(IF(PARAM!$E$7&gt;0,1,0)+IF(PARAM!$I$7&gt;0,1,0))&amp;" of 2"</f>
         <v>2 of 2</v>
       </c>
-      <c r="G10" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="11" t="str">
+      <c r="G11" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="11" t="str">
         <f>IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,"X","Y"),"all four alike")</f>
         <v>X</v>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="4" t="s">
+    <row r="13" ht="20" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-    </row>
-    <row r="13" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E14" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="5" t="s">
+      <c r="G14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="H14" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="I14" s="5" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B14" s="6" t="s">
+      <c r="J14" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="E14" s="7">
-        <v>300</v>
-      </c>
-      <c r="F14" s="7">
-        <v>330</v>
-      </c>
-      <c r="G14" s="7">
-        <v>12</v>
-      </c>
-      <c r="H14" s="14">
-        <v>2</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J14" s="7">
-        <v>10</v>
-      </c>
-      <c r="K14" s="15" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15" s="7">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="F15" s="7">
         <v>330</v>
       </c>
       <c r="G15" s="7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H15" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>21</v>
       </c>
+      <c r="J15" s="7">
+        <v>10</v>
+      </c>
       <c r="K15" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
@@ -1876,7 +1870,7 @@
         <v>38</v>
       </c>
       <c r="E16" s="7">
-        <v>234</v>
+        <v>110</v>
       </c>
       <c r="F16" s="7">
         <v>330</v>
@@ -1885,29 +1879,27 @@
         <v>10</v>
       </c>
       <c r="H16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E17" s="17">
-        <f>PARAM!$E$6+2*PARAM!$J$17</f>
-        <v>420</v>
-      </c>
-      <c r="F17" s="17">
-        <f>PARAM!$F$6+2*PARAM!$J$17</f>
-        <v>420</v>
+      <c r="E17" s="7">
+        <v>234</v>
+      </c>
+      <c r="F17" s="7">
+        <v>330</v>
       </c>
       <c r="G17" s="7">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H17" s="14">
         <v>2</v>
@@ -1915,160 +1907,162 @@
       <c r="I17" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J17" s="7">
+      <c r="K17" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B18" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="17">
+        <f>PARAM!$E$6+2*PARAM!$J$18</f>
+        <v>420</v>
+      </c>
+      <c r="F18" s="17">
+        <f>PARAM!$F$6+2*PARAM!$J$18</f>
+        <v>420</v>
+      </c>
+      <c r="G18" s="7">
+        <v>20</v>
+      </c>
+      <c r="H18" s="14">
+        <v>2</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="7">
         <v>60</v>
       </c>
-      <c r="K17" s="15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="12" t="s">
+      <c r="K18" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="13" t="s">
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B19" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="11" t="str">
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="11" t="str">
         <f>IF(PARAM!$C$6="H","cover plates","end plate")</f>
         <v>cover plates</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F19" s="11">
-        <f>ROUND(IF(PARAM!$C$6="H",PARAM!$E$14*PARAM!$F$14*PARAM!$G$14*2+PARAM!$E$15*PARAM!$F$15*PARAM!$G$15*4+PARAM!$E$16*PARAM!$F$16*PARAM!$G$16*2,PARAM!$E$17*PARAM!$F$17*PARAM!$G$17*2)*7.85/1000000,1)</f>
+      <c r="E20" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="11">
+        <f>ROUND(IF(PARAM!$C$6="H",PARAM!$E$15*PARAM!$F$15*PARAM!$G$15*2+PARAM!$E$16*PARAM!$F$16*PARAM!$G$16*4+PARAM!$E$17*PARAM!$F$17*PARAM!$G$17*2,PARAM!$E$18*PARAM!$F$18*PARAM!$G$18*2)*7.85/1000000,1)</f>
         <v>42.2</v>
       </c>
-      <c r="G19" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="H19" s="11" t="str">
-        <f>IF(PARAM!$C$6="H",IF(AND(PARAM!$E$14&lt;=PARAM!$F$6,PARAM!$E$16&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6),"ok",IF(PARAM!$E$14&gt;PARAM!$F$6,"flange plate too wide","web plate too deep")),"n/a")</f>
+      <c r="G20" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="H20" s="11" t="str">
+        <f>IF(PARAM!$C$6="H",IF(AND(PARAM!$E$15&lt;=PARAM!$F$6,PARAM!$E$17&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6),"ok",IF(PARAM!$E$15&gt;PARAM!$F$6,"flange plate too wide","web plate too deep")),"n/a")</f>
         <v>ok</v>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="4" t="s">
+    <row r="22" ht="20" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-    </row>
-    <row r="22" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+    </row>
+    <row r="23" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E23" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="F23" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="G23" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="H23" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="I23" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
+      <c r="J23" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E23" s="7">
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E24" s="7">
         <v>16</v>
       </c>
-      <c r="F23" s="17">
-        <f>PARAM!$E$23+2</f>
+      <c r="F24" s="17">
+        <f>PARAM!$E$24+2</f>
         <v>18</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="H23" s="18">
-        <f>IF(PARAM!$C$6="H",CEILING(PARAM!$G$14+PARAM!$H$6+PARAM!$G$15+1.1*PARAM!$E$23,5),"—")</f>
+      <c r="G24" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="I23" s="18">
-        <f>IF(PARAM!$C$6="H",CEILING(PARAM!$G$6+2*PARAM!$G$16+1.1*PARAM!$E$23,5),"—")</f>
+      <c r="H24" s="18">
+        <f>IF(PARAM!$C$6="H",CEILING(PARAM!$G$15+PARAM!$H$6+PARAM!$G$16+1.1*PARAM!$E$24,5),"—")</f>
+        <v>55</v>
+      </c>
+      <c r="I24" s="18">
+        <f>IF(PARAM!$C$6="H",CEILING(PARAM!$G$6+2*PARAM!$G$17+1.1*PARAM!$E$24,5),"—")</f>
         <v>50</v>
       </c>
-      <c r="J23" s="18" t="str">
-        <f>IF(PARAM!$C$6="H","—",CEILING(2*PARAM!$G$17+1.1*PARAM!$E$23,5))</f>
+      <c r="J24" s="18" t="str">
+        <f>IF(PARAM!$C$6="H","—",CEILING(2*PARAM!$G$18+1.1*PARAM!$E$24,5))</f>
         <v>—</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="E24" s="5" t="s">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="F25" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="G25" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="I24" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J24" s="5" t="s">
+      <c r="H25" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25" s="5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" s="7">
-        <v>4</v>
-      </c>
-      <c r="F25" s="7">
-        <v>70</v>
-      </c>
-      <c r="G25" s="7">
-        <v>45</v>
-      </c>
-      <c r="H25" s="7">
-        <v>4</v>
-      </c>
-      <c r="I25" s="7">
-        <v>100</v>
-      </c>
-      <c r="J25" s="7">
-        <v>40</v>
+      <c r="J25" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
@@ -2079,101 +2073,125 @@
         <v>4</v>
       </c>
       <c r="F26" s="7">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G26" s="7">
         <v>45</v>
       </c>
       <c r="H26" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I26" s="7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J26" s="7">
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E27" s="5" t="s">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F27" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H27" s="5" t="s">
+      <c r="E27" s="7">
+        <v>4</v>
+      </c>
+      <c r="F27" s="7">
+        <v>60</v>
+      </c>
+      <c r="G27" s="7">
+        <v>45</v>
+      </c>
+      <c r="H27" s="7">
+        <v>3</v>
+      </c>
+      <c r="I27" s="7">
+        <v>0</v>
+      </c>
+      <c r="J27" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E28" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="I27" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" s="7">
+      <c r="F28" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B29" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29" s="7">
         <v>3</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F29" s="7">
         <v>30</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H29" s="7">
         <v>3</v>
       </c>
-      <c r="I28" s="7">
+      <c r="I29" s="7">
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B29" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="13" t="s">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B30" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D30" s="11" t="str">
-        <f>IF(PARAM!$C$6="H",ROUND((PARAM!$F$14/2-PARAM!$G$25-PARAM!$F$25/2)/(PARAM!$E$25/2-1),1)&amp;" / "&amp;ROUND((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1),1),"n/a")</f>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D31" s="11" t="str">
+        <f>IF(PARAM!$C$6="H",ROUND((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1),1)&amp;" / "&amp;ROUND((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1),1),"n/a")</f>
         <v>85 / 60</v>
       </c>
-      <c r="E30" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="F30" s="11" t="str">
-        <f>IF(PARAM!$C$6="H",ROUND((PARAM!$F$16/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1),1)&amp;" / "&amp;ROUND((PARAM!$E$16-2*PARAM!$J$26-PARAM!$I$26)/(PARAM!$H$26-1),1),"n/a")</f>
+      <c r="E31" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="F31" s="11" t="str">
+        <f>IF(PARAM!$C$6="H",ROUND((PARAM!$F$17/2-PARAM!$G$27-PARAM!$F$27/2)/(PARAM!$E$27/2-1),1)&amp;" / "&amp;ROUND((PARAM!$E$17-2*PARAM!$J$27-PARAM!$I$27)/(PARAM!$H$27-1),1),"n/a")</f>
         <v>90 / 77</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="H30" s="11" t="str">
-        <f>IF(PARAM!$C$6="H",2*PARAM!$E$25*PARAM!$H$25+PARAM!$E$26*PARAM!$H$26,2*PARAM!$E$28+2*MAX(0,PARAM!$H$28-2))&amp;" per splice"</f>
+      <c r="G31" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="H31" s="11" t="str">
+        <f>IF(PARAM!$C$6="H",2*PARAM!$E$26*PARAM!$H$26+PARAM!$E$27*PARAM!$H$27,2*PARAM!$E$29+2*MAX(0,PARAM!$H$29-2))&amp;" per splice"</f>
         <v>44 per splice</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="E8:K8"/>
     <mergeCell ref="B9:K9"/>
-    <mergeCell ref="C12:K12"/>
-    <mergeCell ref="B18:K18"/>
-    <mergeCell ref="C21:K21"/>
-    <mergeCell ref="B29:K29"/>
+    <mergeCell ref="B10:K10"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="B19:K19"/>
+    <mergeCell ref="C22:K22"/>
+    <mergeCell ref="B30:K30"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" showErrorMessage="1" error="H for an I section, R for a square tube." sqref="C6">
@@ -2182,7 +2200,7 @@
     <dataValidation type="list" showErrorMessage="1" error="Pick one from the list, or &quot;user define&quot; at the top of it." sqref="D6">
       <formula1>INDIRECT("SEC_"&amp;$C$6)</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="G23">
+    <dataValidation type="list" sqref="G24">
       <formula1>"F8T,F10T,F13T"</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="0, 90 or -90 degrees about the column axis." sqref="J6">
@@ -2208,30 +2226,30 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -2239,10 +2257,10 @@
         <v>17</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D6" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -2257,7 +2275,7 @@
         <v>H</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H6" s="21">
         <f>PARAM!$E$6</f>
@@ -2293,10 +2311,10 @@
         <v>18</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D7" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -2311,7 +2329,7 @@
         <v>H</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H7" s="21">
         <f>PARAM!$E$6</f>
@@ -2347,10 +2365,10 @@
         <v>19</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -2365,7 +2383,7 @@
         <v>H</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H8" s="21">
         <f>PARAM!$E$6</f>
@@ -2398,213 +2416,213 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D11" s="21" t="str">
         <f>PARAM!$C$8</f>
         <v>SS275</v>
       </c>
       <c r="E11" s="21">
-        <f>IF(PARAM!$C$6="H",PARAM!$G$14,PARAM!$G$17)</f>
+        <f>IF(PARAM!$C$6="H",PARAM!$G$15,PARAM!$G$18)</f>
         <v>12</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H11" s="21">
-        <f>IF(PARAM!$C$6="H",PARAM!$E$14,PARAM!$E$17)</f>
+        <f>IF(PARAM!$C$6="H",PARAM!$E$15,PARAM!$E$18)</f>
         <v>300</v>
       </c>
       <c r="I11" s="21">
-        <f>IF(PARAM!$C$6="H",PARAM!$F$14,PARAM!$F$17)</f>
+        <f>IF(PARAM!$C$6="H",PARAM!$F$15,PARAM!$F$18)</f>
         <v>330</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D12" s="21" t="str">
         <f>PARAM!$C$8</f>
         <v>SS275</v>
       </c>
       <c r="E12" s="21">
-        <f>PARAM!$G$15</f>
+        <f>PARAM!$G$16</f>
         <v>10</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H12" s="21">
-        <f>PARAM!$E$15</f>
+        <f>PARAM!$E$16</f>
         <v>110</v>
       </c>
       <c r="I12" s="21">
-        <f>PARAM!$F$15</f>
+        <f>PARAM!$F$16</f>
         <v>330</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D13" s="21" t="str">
         <f>PARAM!$C$8</f>
         <v>SS275</v>
       </c>
       <c r="E13" s="21">
-        <f>PARAM!$G$16</f>
+        <f>PARAM!$G$17</f>
         <v>10</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H13" s="21">
-        <f>PARAM!$E$16</f>
+        <f>PARAM!$E$17</f>
         <v>234</v>
       </c>
       <c r="I13" s="21">
-        <f>PARAM!$F$16</f>
+        <f>PARAM!$F$17</f>
         <v>330</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" s="21" t="str">
-        <f>PARAM!$G$23</f>
+        <f>PARAM!$G$24</f>
         <v>F10T</v>
       </c>
       <c r="E14" s="21">
-        <f>PARAM!$E$23</f>
+        <f>PARAM!$E$24</f>
         <v>16</v>
       </c>
       <c r="F14" s="21">
-        <f>IF(PARAM!$C$6="H",PARAM!$H$23,PARAM!$J$23)</f>
+        <f>IF(PARAM!$C$6="H",PARAM!$H$24,PARAM!$J$24)</f>
         <v>55</v>
       </c>
       <c r="G14" s="21">
-        <f>PARAM!$F$23</f>
+        <f>PARAM!$F$24</f>
         <v>18</v>
       </c>
       <c r="H14" s="21"/>
       <c r="I14" s="21"/>
       <c r="J14" s="21"/>
       <c r="K14" s="21">
-        <f>0.9*PARAM!$E$23</f>
+        <f>0.9*PARAM!$E$24</f>
         <v>14.4</v>
       </c>
       <c r="L14" s="21">
-        <f>IF(PARAM!$C$6="H",PARAM!$H$23-PARAM!$G$14-PARAM!$H$6-PARAM!$G$15,PARAM!$J$23-2*PARAM!$G$17)-0.9*PARAM!$E$23</f>
+        <f>IF(PARAM!$C$6="H",PARAM!$H$24-PARAM!$G$15-PARAM!$H$6-PARAM!$G$16,PARAM!$J$24-2*PARAM!$G$18)-0.9*PARAM!$E$24</f>
         <v>3.6</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D15" s="21" t="str">
-        <f>PARAM!$G$23</f>
+        <f>PARAM!$G$24</f>
         <v>F10T</v>
       </c>
       <c r="E15" s="21">
-        <f>PARAM!$E$23</f>
+        <f>PARAM!$E$24</f>
         <v>16</v>
       </c>
       <c r="F15" s="21">
-        <f>IF(PARAM!$C$6="H",PARAM!$I$23,1)</f>
+        <f>IF(PARAM!$C$6="H",PARAM!$I$24,1)</f>
         <v>50</v>
       </c>
       <c r="G15" s="21">
-        <f>PARAM!$F$23</f>
+        <f>PARAM!$F$24</f>
         <v>18</v>
       </c>
       <c r="H15" s="21"/>
       <c r="I15" s="21"/>
       <c r="J15" s="21"/>
       <c r="K15" s="21">
-        <f>0.9*PARAM!$E$23</f>
+        <f>0.9*PARAM!$E$24</f>
         <v>14.4</v>
       </c>
       <c r="L15" s="21">
-        <f>IF(PARAM!$C$6="H",PARAM!$I$23-PARAM!$G$6-2*PARAM!$G$16-0.9*PARAM!$E$23,0)</f>
+        <f>IF(PARAM!$C$6="H",PARAM!$I$24-PARAM!$G$6-2*PARAM!$G$17-0.9*PARAM!$E$24,0)</f>
         <v>5.6</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D19" s="21" t="str">
         <f>IF(PARAM!$E$7&gt;0,"sc.c1","")</f>
@@ -2621,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J19" s="21">
         <v>0</v>
@@ -2635,27 +2653,27 @@
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D21" s="21" t="str">
         <f>"sc.c2"</f>
@@ -2672,7 +2690,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J21" s="21">
         <v>0</v>
@@ -2686,27 +2704,27 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C22" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="21" t="s">
-        <v>99</v>
-      </c>
       <c r="E22" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" s="21" t="s">
         <v>77</v>
-      </c>
-      <c r="F22" s="21" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D23" s="21" t="str">
         <f>IF(PARAM!$I$7&gt;0,"sc.c3","")</f>
@@ -2723,7 +2741,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J23" s="21">
         <v>0</v>
@@ -2737,57 +2755,57 @@
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D27" s="21" t="str">
         <f>IF(PARAM!$E$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F27" s="21">
-        <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$14/2)),0)</f>
+        <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$15/2)),0)</f>
         <v>156</v>
       </c>
       <c r="G27" s="21">
         <v>0</v>
       </c>
       <c r="H27" s="21">
-        <f>IF(PARAM!$C$6="H",0,(PARAM!$G$17/2))</f>
+        <f>IF(PARAM!$C$6="H",0,(PARAM!$G$18/2))</f>
         <v>0</v>
       </c>
       <c r="I27" s="21" t="str">
@@ -2797,27 +2815,27 @@
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B28" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D28" s="21" t="str">
         <f>IF(PARAM!$E$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F28" s="21">
-        <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$14/2)),0)</f>
+        <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$15/2)),0)</f>
         <v>-156</v>
       </c>
       <c r="G28" s="21">
         <v>0</v>
       </c>
       <c r="H28" s="21">
-        <f>IF(PARAM!$C$6="H",0,-(PARAM!$G$17/2))</f>
+        <f>IF(PARAM!$C$6="H",0,-(PARAM!$G$18/2))</f>
         <v>0</v>
       </c>
       <c r="I28" s="21" t="str">
@@ -2827,191 +2845,191 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="21" t="s">
         <v>105</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>104</v>
       </c>
       <c r="D29" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F29" s="21">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15/2))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
         <v>130</v>
       </c>
       <c r="G29" s="21">
-        <f>((PARAM!$I$25/2+((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))/2))</f>
+        <f>((PARAM!$I$26/2+((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))/2))</f>
         <v>80</v>
       </c>
       <c r="H29" s="21">
         <v>0</v>
       </c>
       <c r="I29" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D30" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F30" s="21">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15/2))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
         <v>130</v>
       </c>
       <c r="G30" s="21">
-        <f>-((PARAM!$I$25/2+((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))/2))</f>
+        <f>-((PARAM!$I$26/2+((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))/2))</f>
         <v>-80</v>
       </c>
       <c r="H30" s="21">
         <v>0</v>
       </c>
       <c r="I30" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D31" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F31" s="21">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15/2))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
         <v>-130</v>
       </c>
       <c r="G31" s="21">
-        <f>((PARAM!$I$25/2+((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))/2))</f>
+        <f>((PARAM!$I$26/2+((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))/2))</f>
         <v>80</v>
       </c>
       <c r="H31" s="21">
         <v>0</v>
       </c>
       <c r="I31" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D32" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F32" s="21">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15/2))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
         <v>-130</v>
       </c>
       <c r="G32" s="21">
-        <f>-((PARAM!$I$25/2+((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))/2))</f>
+        <f>-((PARAM!$I$26/2+((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))/2))</f>
         <v>-80</v>
       </c>
       <c r="H32" s="21">
         <v>0</v>
       </c>
       <c r="I32" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D33" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F33" s="21">
         <v>0</v>
       </c>
       <c r="G33" s="21">
-        <f>((PARAM!$G$6/2+PARAM!$G$16/2))</f>
+        <f>((PARAM!$G$6/2+PARAM!$G$17/2))</f>
         <v>10</v>
       </c>
       <c r="H33" s="21">
         <v>0</v>
       </c>
       <c r="I33" s="21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D34" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F34" s="21">
         <v>0</v>
       </c>
       <c r="G34" s="21">
-        <f>-((PARAM!$G$6/2+PARAM!$G$16/2))</f>
+        <f>-((PARAM!$G$6/2+PARAM!$G$17/2))</f>
         <v>-10</v>
       </c>
       <c r="H34" s="21">
         <v>0</v>
       </c>
       <c r="I34" s="21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D35" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3019,19 +3037,19 @@
       </c>
       <c r="E35" s="21"/>
       <c r="F35" s="21">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
         <v>125</v>
       </c>
       <c r="G35" s="21">
-        <f>(PARAM!$I$25/2)</f>
+        <f>(PARAM!$I$26/2)</f>
         <v>50</v>
       </c>
       <c r="H35" s="21">
-        <f>(PARAM!$F$25/2)</f>
+        <f>(PARAM!$F$26/2)</f>
         <v>35</v>
       </c>
       <c r="I35" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J35" s="21">
         <v>0</v>
@@ -3046,14 +3064,14 @@
         <v>0</v>
       </c>
       <c r="N35" s="21">
-        <f>((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))</f>
+        <f>((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
         <v>60</v>
       </c>
       <c r="O35" s="21">
         <v>0</v>
       </c>
       <c r="P35" s="21">
-        <f>PARAM!$H$25/2-1</f>
+        <f>PARAM!$H$26/2-1</f>
         <v>1</v>
       </c>
       <c r="Q35" s="21">
@@ -3063,20 +3081,20 @@
         <v>0</v>
       </c>
       <c r="S35" s="21">
-        <f>((PARAM!$F$14/2-PARAM!$G$25-PARAM!$F$25/2)/(PARAM!$E$25/2-1))</f>
+        <f>((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
         <v>85</v>
       </c>
       <c r="T35" s="21">
-        <f>PARAM!$E$25/2-1</f>
+        <f>PARAM!$E$26/2-1</f>
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B36" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D36" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3084,19 +3102,19 @@
       </c>
       <c r="E36" s="21"/>
       <c r="F36" s="21">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
         <v>125</v>
       </c>
       <c r="G36" s="21">
-        <f>-(PARAM!$I$25/2)</f>
+        <f>-(PARAM!$I$26/2)</f>
         <v>-50</v>
       </c>
       <c r="H36" s="21">
-        <f>(PARAM!$F$25/2)</f>
+        <f>(PARAM!$F$26/2)</f>
         <v>35</v>
       </c>
       <c r="I36" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J36" s="21">
         <v>0</v>
@@ -3111,14 +3129,14 @@
         <v>0</v>
       </c>
       <c r="N36" s="21">
-        <f>-((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))</f>
+        <f>-((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
         <v>-60</v>
       </c>
       <c r="O36" s="21">
         <v>0</v>
       </c>
       <c r="P36" s="21">
-        <f>PARAM!$H$25/2-1</f>
+        <f>PARAM!$H$26/2-1</f>
         <v>1</v>
       </c>
       <c r="Q36" s="21">
@@ -3128,20 +3146,20 @@
         <v>0</v>
       </c>
       <c r="S36" s="21">
-        <f>((PARAM!$F$14/2-PARAM!$G$25-PARAM!$F$25/2)/(PARAM!$E$25/2-1))</f>
+        <f>((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
         <v>85</v>
       </c>
       <c r="T36" s="21">
-        <f>PARAM!$E$25/2-1</f>
+        <f>PARAM!$E$26/2-1</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B37" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D37" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3149,19 +3167,19 @@
       </c>
       <c r="E37" s="21"/>
       <c r="F37" s="21">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
         <v>125</v>
       </c>
       <c r="G37" s="21">
-        <f>(PARAM!$I$25/2)</f>
+        <f>(PARAM!$I$26/2)</f>
         <v>50</v>
       </c>
       <c r="H37" s="21">
-        <f>-(PARAM!$F$25/2)</f>
+        <f>-(PARAM!$F$26/2)</f>
         <v>-35</v>
       </c>
       <c r="I37" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J37" s="21">
         <v>0</v>
@@ -3176,14 +3194,14 @@
         <v>0</v>
       </c>
       <c r="N37" s="21">
-        <f>((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))</f>
+        <f>((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
         <v>60</v>
       </c>
       <c r="O37" s="21">
         <v>0</v>
       </c>
       <c r="P37" s="21">
-        <f>PARAM!$H$25/2-1</f>
+        <f>PARAM!$H$26/2-1</f>
         <v>1</v>
       </c>
       <c r="Q37" s="21">
@@ -3193,20 +3211,20 @@
         <v>0</v>
       </c>
       <c r="S37" s="21">
-        <f>-((PARAM!$F$14/2-PARAM!$G$25-PARAM!$F$25/2)/(PARAM!$E$25/2-1))</f>
+        <f>-((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
         <v>-85</v>
       </c>
       <c r="T37" s="21">
-        <f>PARAM!$E$25/2-1</f>
+        <f>PARAM!$E$26/2-1</f>
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B38" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D38" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3214,19 +3232,19 @@
       </c>
       <c r="E38" s="21"/>
       <c r="F38" s="21">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
         <v>125</v>
       </c>
       <c r="G38" s="21">
-        <f>-(PARAM!$I$25/2)</f>
+        <f>-(PARAM!$I$26/2)</f>
         <v>-50</v>
       </c>
       <c r="H38" s="21">
-        <f>-(PARAM!$F$25/2)</f>
+        <f>-(PARAM!$F$26/2)</f>
         <v>-35</v>
       </c>
       <c r="I38" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J38" s="21">
         <v>0</v>
@@ -3241,14 +3259,14 @@
         <v>0</v>
       </c>
       <c r="N38" s="21">
-        <f>-((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))</f>
+        <f>-((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
         <v>-60</v>
       </c>
       <c r="O38" s="21">
         <v>0</v>
       </c>
       <c r="P38" s="21">
-        <f>PARAM!$H$25/2-1</f>
+        <f>PARAM!$H$26/2-1</f>
         <v>1</v>
       </c>
       <c r="Q38" s="21">
@@ -3258,20 +3276,20 @@
         <v>0</v>
       </c>
       <c r="S38" s="21">
-        <f>-((PARAM!$F$14/2-PARAM!$G$25-PARAM!$F$25/2)/(PARAM!$E$25/2-1))</f>
+        <f>-((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
         <v>-85</v>
       </c>
       <c r="T38" s="21">
-        <f>PARAM!$E$25/2-1</f>
+        <f>PARAM!$E$26/2-1</f>
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B39" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D39" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3279,19 +3297,19 @@
       </c>
       <c r="E39" s="21"/>
       <c r="F39" s="21">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
         <v>-125</v>
       </c>
       <c r="G39" s="21">
-        <f>(PARAM!$I$25/2)</f>
+        <f>(PARAM!$I$26/2)</f>
         <v>50</v>
       </c>
       <c r="H39" s="21">
-        <f>(PARAM!$F$25/2)</f>
+        <f>(PARAM!$F$26/2)</f>
         <v>35</v>
       </c>
       <c r="I39" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J39" s="21">
         <v>0</v>
@@ -3306,14 +3324,14 @@
         <v>0</v>
       </c>
       <c r="N39" s="21">
-        <f>((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))</f>
+        <f>((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
         <v>60</v>
       </c>
       <c r="O39" s="21">
         <v>0</v>
       </c>
       <c r="P39" s="21">
-        <f>PARAM!$H$25/2-1</f>
+        <f>PARAM!$H$26/2-1</f>
         <v>1</v>
       </c>
       <c r="Q39" s="21">
@@ -3323,20 +3341,20 @@
         <v>0</v>
       </c>
       <c r="S39" s="21">
-        <f>((PARAM!$F$14/2-PARAM!$G$25-PARAM!$F$25/2)/(PARAM!$E$25/2-1))</f>
+        <f>((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
         <v>85</v>
       </c>
       <c r="T39" s="21">
-        <f>PARAM!$E$25/2-1</f>
+        <f>PARAM!$E$26/2-1</f>
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B40" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D40" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3344,19 +3362,19 @@
       </c>
       <c r="E40" s="21"/>
       <c r="F40" s="21">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
         <v>-125</v>
       </c>
       <c r="G40" s="21">
-        <f>-(PARAM!$I$25/2)</f>
+        <f>-(PARAM!$I$26/2)</f>
         <v>-50</v>
       </c>
       <c r="H40" s="21">
-        <f>(PARAM!$F$25/2)</f>
+        <f>(PARAM!$F$26/2)</f>
         <v>35</v>
       </c>
       <c r="I40" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J40" s="21">
         <v>0</v>
@@ -3371,14 +3389,14 @@
         <v>0</v>
       </c>
       <c r="N40" s="21">
-        <f>-((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))</f>
+        <f>-((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
         <v>-60</v>
       </c>
       <c r="O40" s="21">
         <v>0</v>
       </c>
       <c r="P40" s="21">
-        <f>PARAM!$H$25/2-1</f>
+        <f>PARAM!$H$26/2-1</f>
         <v>1</v>
       </c>
       <c r="Q40" s="21">
@@ -3388,20 +3406,20 @@
         <v>0</v>
       </c>
       <c r="S40" s="21">
-        <f>((PARAM!$F$14/2-PARAM!$G$25-PARAM!$F$25/2)/(PARAM!$E$25/2-1))</f>
+        <f>((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
         <v>85</v>
       </c>
       <c r="T40" s="21">
-        <f>PARAM!$E$25/2-1</f>
+        <f>PARAM!$E$26/2-1</f>
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B41" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D41" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3409,19 +3427,19 @@
       </c>
       <c r="E41" s="21"/>
       <c r="F41" s="21">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
         <v>-125</v>
       </c>
       <c r="G41" s="21">
-        <f>(PARAM!$I$25/2)</f>
+        <f>(PARAM!$I$26/2)</f>
         <v>50</v>
       </c>
       <c r="H41" s="21">
-        <f>-(PARAM!$F$25/2)</f>
+        <f>-(PARAM!$F$26/2)</f>
         <v>-35</v>
       </c>
       <c r="I41" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J41" s="21">
         <v>0</v>
@@ -3436,14 +3454,14 @@
         <v>0</v>
       </c>
       <c r="N41" s="21">
-        <f>((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))</f>
+        <f>((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
         <v>60</v>
       </c>
       <c r="O41" s="21">
         <v>0</v>
       </c>
       <c r="P41" s="21">
-        <f>PARAM!$H$25/2-1</f>
+        <f>PARAM!$H$26/2-1</f>
         <v>1</v>
       </c>
       <c r="Q41" s="21">
@@ -3453,20 +3471,20 @@
         <v>0</v>
       </c>
       <c r="S41" s="21">
-        <f>-((PARAM!$F$14/2-PARAM!$G$25-PARAM!$F$25/2)/(PARAM!$E$25/2-1))</f>
+        <f>-((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
         <v>-85</v>
       </c>
       <c r="T41" s="21">
-        <f>PARAM!$E$25/2-1</f>
+        <f>PARAM!$E$26/2-1</f>
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B42" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D42" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3474,19 +3492,19 @@
       </c>
       <c r="E42" s="21"/>
       <c r="F42" s="21">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
         <v>-125</v>
       </c>
       <c r="G42" s="21">
-        <f>-(PARAM!$I$25/2)</f>
+        <f>-(PARAM!$I$26/2)</f>
         <v>-50</v>
       </c>
       <c r="H42" s="21">
-        <f>-(PARAM!$F$25/2)</f>
+        <f>-(PARAM!$F$26/2)</f>
         <v>-35</v>
       </c>
       <c r="I42" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J42" s="21">
         <v>0</v>
@@ -3501,14 +3519,14 @@
         <v>0</v>
       </c>
       <c r="N42" s="21">
-        <f>-((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))</f>
+        <f>-((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
         <v>-60</v>
       </c>
       <c r="O42" s="21">
         <v>0</v>
       </c>
       <c r="P42" s="21">
-        <f>PARAM!$H$25/2-1</f>
+        <f>PARAM!$H$26/2-1</f>
         <v>1</v>
       </c>
       <c r="Q42" s="21">
@@ -3518,23 +3536,23 @@
         <v>0</v>
       </c>
       <c r="S42" s="21">
-        <f>-((PARAM!$F$14/2-PARAM!$G$25-PARAM!$F$25/2)/(PARAM!$E$25/2-1))</f>
+        <f>-((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
         <v>-85</v>
       </c>
       <c r="T42" s="21">
-        <f>PARAM!$E$25/2-1</f>
+        <f>PARAM!$E$26/2-1</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D43" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -3542,19 +3560,19 @@
       </c>
       <c r="E43" s="21"/>
       <c r="F43" s="21">
-        <f>-(PARAM!$E$17/2-PARAM!$F$28)</f>
+        <f>-(PARAM!$E$18/2-PARAM!$F$29)</f>
         <v>-180</v>
       </c>
       <c r="G43" s="21">
-        <f>((PARAM!$F$17/2-PARAM!$I$28))</f>
+        <f>((PARAM!$F$18/2-PARAM!$I$29))</f>
         <v>180</v>
       </c>
       <c r="H43" s="21">
-        <f>-PARAM!$G$17/2</f>
+        <f>-PARAM!$G$18/2</f>
         <v>-10</v>
       </c>
       <c r="I43" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J43" s="21">
         <v>0</v>
@@ -3566,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="M43" s="21">
-        <f>((PARAM!$E$17-2*PARAM!$F$28)/(PARAM!$E$28-1))</f>
+        <f>((PARAM!$E$18-2*PARAM!$F$29)/(PARAM!$E$29-1))</f>
         <v>180</v>
       </c>
       <c r="N43" s="21">
@@ -3576,16 +3594,16 @@
         <v>0</v>
       </c>
       <c r="P43" s="21">
-        <f>PARAM!$E$28-1</f>
+        <f>PARAM!$E$29-1</f>
         <v>2</v>
       </c>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B44" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D44" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -3593,19 +3611,19 @@
       </c>
       <c r="E44" s="21"/>
       <c r="F44" s="21">
-        <f>-(PARAM!$E$17/2-PARAM!$F$28)</f>
+        <f>-(PARAM!$E$18/2-PARAM!$F$29)</f>
         <v>-180</v>
       </c>
       <c r="G44" s="21">
-        <f>-((PARAM!$F$17/2-PARAM!$I$28))</f>
+        <f>-((PARAM!$F$18/2-PARAM!$I$29))</f>
         <v>-180</v>
       </c>
       <c r="H44" s="21">
-        <f>-PARAM!$G$17/2</f>
+        <f>-PARAM!$G$18/2</f>
         <v>-10</v>
       </c>
       <c r="I44" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J44" s="21">
         <v>0</v>
@@ -3617,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="M44" s="21">
-        <f>((PARAM!$E$17-2*PARAM!$F$28)/(PARAM!$E$28-1))</f>
+        <f>((PARAM!$E$18-2*PARAM!$F$29)/(PARAM!$E$29-1))</f>
         <v>180</v>
       </c>
       <c r="N44" s="21">
@@ -3627,39 +3645,39 @@
         <v>0</v>
       </c>
       <c r="P44" s="21">
-        <f>PARAM!$E$28-1</f>
+        <f>PARAM!$E$29-1</f>
         <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D45" s="21" t="str">
-        <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$28&gt;2),"bo.f","")</f>
+        <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$29&gt;2),"bo.f","")</f>
         <v/>
       </c>
       <c r="E45" s="21"/>
       <c r="F45" s="21">
-        <f>((PARAM!$E$17/2-PARAM!$F$28))</f>
+        <f>((PARAM!$E$18/2-PARAM!$F$29))</f>
         <v>180</v>
       </c>
       <c r="G45" s="21">
-        <f>-(PARAM!$F$17/2-PARAM!$I$28)+((PARAM!$F$17-2*PARAM!$I$28)/(PARAM!$H$28-1))</f>
+        <f>-(PARAM!$F$18/2-PARAM!$I$29)+((PARAM!$F$18-2*PARAM!$I$29)/(PARAM!$H$29-1))</f>
         <v>0</v>
       </c>
       <c r="H45" s="21">
-        <f>-PARAM!$G$17/2</f>
+        <f>-PARAM!$G$18/2</f>
         <v>-10</v>
       </c>
       <c r="I45" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J45" s="21">
         <v>0</v>
@@ -3674,43 +3692,43 @@
         <v>0</v>
       </c>
       <c r="N45" s="21">
-        <f>IF(PARAM!$H$28&gt;3,((PARAM!$F$17-2*PARAM!$I$28)/(PARAM!$H$28-1)),0)</f>
+        <f>IF(PARAM!$H$29&gt;3,((PARAM!$F$18-2*PARAM!$I$29)/(PARAM!$H$29-1)),0)</f>
         <v>0</v>
       </c>
       <c r="O45" s="21">
         <v>0</v>
       </c>
       <c r="P45" s="21">
-        <f>MAX(0,PARAM!$H$28-3)</f>
+        <f>MAX(0,PARAM!$H$29-3)</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B46" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D46" s="21" t="str">
-        <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$28&gt;2),"bo.f","")</f>
+        <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$29&gt;2),"bo.f","")</f>
         <v/>
       </c>
       <c r="E46" s="21"/>
       <c r="F46" s="21">
-        <f>-((PARAM!$E$17/2-PARAM!$F$28))</f>
+        <f>-((PARAM!$E$18/2-PARAM!$F$29))</f>
         <v>-180</v>
       </c>
       <c r="G46" s="21">
-        <f>-(PARAM!$F$17/2-PARAM!$I$28)+((PARAM!$F$17-2*PARAM!$I$28)/(PARAM!$H$28-1))</f>
+        <f>-(PARAM!$F$18/2-PARAM!$I$29)+((PARAM!$F$18-2*PARAM!$I$29)/(PARAM!$H$29-1))</f>
         <v>0</v>
       </c>
       <c r="H46" s="21">
-        <f>-PARAM!$G$17/2</f>
+        <f>-PARAM!$G$18/2</f>
         <v>-10</v>
       </c>
       <c r="I46" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J46" s="21">
         <v>0</v>
@@ -3725,26 +3743,26 @@
         <v>0</v>
       </c>
       <c r="N46" s="21">
-        <f>IF(PARAM!$H$28&gt;3,((PARAM!$F$17-2*PARAM!$I$28)/(PARAM!$H$28-1)),0)</f>
+        <f>IF(PARAM!$H$29&gt;3,((PARAM!$F$18-2*PARAM!$I$29)/(PARAM!$H$29-1)),0)</f>
         <v>0</v>
       </c>
       <c r="O46" s="21">
         <v>0</v>
       </c>
       <c r="P46" s="21">
-        <f>MAX(0,PARAM!$H$28-3)</f>
+        <f>MAX(0,PARAM!$H$29-3)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D47" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -3752,19 +3770,19 @@
       </c>
       <c r="E47" s="21"/>
       <c r="F47" s="21">
-        <f>-(PARAM!$E$16/2-PARAM!$J$26)</f>
+        <f>-(PARAM!$E$17/2-PARAM!$J$27)</f>
         <v>-77</v>
       </c>
       <c r="G47" s="21">
-        <f>(PARAM!$G$6/2+PARAM!$G$16)</f>
+        <f>(PARAM!$G$6/2+PARAM!$G$17)</f>
         <v>15</v>
       </c>
       <c r="H47" s="21">
-        <f>(PARAM!$F$26/2)</f>
+        <f>(PARAM!$F$27/2)</f>
         <v>30</v>
       </c>
       <c r="I47" s="21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J47" s="21">
         <v>0</v>
@@ -3776,7 +3794,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="21">
-        <f>(PARAM!$E$16-2*PARAM!$J$26-PARAM!$I$26)/(PARAM!$H$26-1)</f>
+        <f>(PARAM!$E$17-2*PARAM!$J$27-PARAM!$I$27)/(PARAM!$H$27-1)</f>
         <v>77</v>
       </c>
       <c r="N47" s="21">
@@ -3786,7 +3804,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="21">
-        <f>PARAM!$H$26-1</f>
+        <f>PARAM!$H$27-1</f>
         <v>2</v>
       </c>
       <c r="Q47" s="21">
@@ -3796,20 +3814,20 @@
         <v>0</v>
       </c>
       <c r="S47" s="21">
-        <f>((PARAM!$F$16/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
+        <f>((PARAM!$F$17/2-PARAM!$G$27-PARAM!$F$27/2)/(PARAM!$E$27/2-1))</f>
         <v>90</v>
       </c>
       <c r="T47" s="21">
-        <f>PARAM!$E$26/2-1</f>
+        <f>PARAM!$E$27/2-1</f>
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B48" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D48" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -3817,19 +3835,19 @@
       </c>
       <c r="E48" s="21"/>
       <c r="F48" s="21">
-        <f>-(PARAM!$E$16/2-PARAM!$J$26)</f>
+        <f>-(PARAM!$E$17/2-PARAM!$J$27)</f>
         <v>-77</v>
       </c>
       <c r="G48" s="21">
-        <f>(PARAM!$G$6/2+PARAM!$G$16)</f>
+        <f>(PARAM!$G$6/2+PARAM!$G$17)</f>
         <v>15</v>
       </c>
       <c r="H48" s="21">
-        <f>-(PARAM!$F$26/2)</f>
+        <f>-(PARAM!$F$27/2)</f>
         <v>-30</v>
       </c>
       <c r="I48" s="21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J48" s="21">
         <v>0</v>
@@ -3841,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="21">
-        <f>(PARAM!$E$16-2*PARAM!$J$26-PARAM!$I$26)/(PARAM!$H$26-1)</f>
+        <f>(PARAM!$E$17-2*PARAM!$J$27-PARAM!$I$27)/(PARAM!$H$27-1)</f>
         <v>77</v>
       </c>
       <c r="N48" s="21">
@@ -3851,7 +3869,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="21">
-        <f>PARAM!$H$26-1</f>
+        <f>PARAM!$H$27-1</f>
         <v>2</v>
       </c>
       <c r="Q48" s="21">
@@ -3861,54 +3879,54 @@
         <v>0</v>
       </c>
       <c r="S48" s="21">
-        <f>-((PARAM!$F$16/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
+        <f>-((PARAM!$F$17/2-PARAM!$G$27-PARAM!$F$27/2)/(PARAM!$E$27/2-1))</f>
         <v>-90</v>
       </c>
       <c r="T48" s="21">
-        <f>PARAM!$E$26/2-1</f>
+        <f>PARAM!$E$27/2-1</f>
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B49" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F49" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B50" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D50" s="21" t="str">
         <f>IF(PARAM!$I$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F50" s="21">
-        <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$14/2)),0)</f>
+        <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$15/2)),0)</f>
         <v>156</v>
       </c>
       <c r="G50" s="21">
         <v>0</v>
       </c>
       <c r="H50" s="21">
-        <f>IF(PARAM!$C$6="H",0,(PARAM!$G$17/2))</f>
+        <f>IF(PARAM!$C$6="H",0,(PARAM!$G$18/2))</f>
         <v>0</v>
       </c>
       <c r="I50" s="21" t="str">
@@ -3918,27 +3936,27 @@
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B51" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D51" s="21" t="str">
         <f>IF(PARAM!$I$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E51" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F51" s="21">
-        <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$14/2)),0)</f>
+        <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$15/2)),0)</f>
         <v>-156</v>
       </c>
       <c r="G51" s="21">
         <v>0</v>
       </c>
       <c r="H51" s="21">
-        <f>IF(PARAM!$C$6="H",0,-(PARAM!$G$17/2))</f>
+        <f>IF(PARAM!$C$6="H",0,-(PARAM!$G$18/2))</f>
         <v>0</v>
       </c>
       <c r="I51" s="21" t="str">
@@ -3948,182 +3966,182 @@
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B52" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D52" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E52" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F52" s="21">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15/2))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
         <v>130</v>
       </c>
       <c r="G52" s="21">
-        <f>((PARAM!$I$25/2+((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))/2))</f>
+        <f>((PARAM!$I$26/2+((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))/2))</f>
         <v>80</v>
       </c>
       <c r="H52" s="21">
         <v>0</v>
       </c>
       <c r="I52" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B53" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D53" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E53" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F53" s="21">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15/2))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
         <v>130</v>
       </c>
       <c r="G53" s="21">
-        <f>-((PARAM!$I$25/2+((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))/2))</f>
+        <f>-((PARAM!$I$26/2+((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))/2))</f>
         <v>-80</v>
       </c>
       <c r="H53" s="21">
         <v>0</v>
       </c>
       <c r="I53" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B54" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D54" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F54" s="21">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15/2))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
         <v>-130</v>
       </c>
       <c r="G54" s="21">
-        <f>((PARAM!$I$25/2+((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))/2))</f>
+        <f>((PARAM!$I$26/2+((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))/2))</f>
         <v>80</v>
       </c>
       <c r="H54" s="21">
         <v>0</v>
       </c>
       <c r="I54" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B55" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D55" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E55" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F55" s="21">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15/2))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
         <v>-130</v>
       </c>
       <c r="G55" s="21">
-        <f>-((PARAM!$I$25/2+((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))/2))</f>
+        <f>-((PARAM!$I$26/2+((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))/2))</f>
         <v>-80</v>
       </c>
       <c r="H55" s="21">
         <v>0</v>
       </c>
       <c r="I55" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B56" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D56" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E56" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F56" s="21">
         <v>0</v>
       </c>
       <c r="G56" s="21">
-        <f>((PARAM!$G$6/2+PARAM!$G$16/2))</f>
+        <f>((PARAM!$G$6/2+PARAM!$G$17/2))</f>
         <v>10</v>
       </c>
       <c r="H56" s="21">
         <v>0</v>
       </c>
       <c r="I56" s="21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B57" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D57" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E57" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F57" s="21">
         <v>0</v>
       </c>
       <c r="G57" s="21">
-        <f>-((PARAM!$G$6/2+PARAM!$G$16/2))</f>
+        <f>-((PARAM!$G$6/2+PARAM!$G$17/2))</f>
         <v>-10</v>
       </c>
       <c r="H57" s="21">
         <v>0</v>
       </c>
       <c r="I57" s="21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B58" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D58" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4131,19 +4149,19 @@
       </c>
       <c r="E58" s="21"/>
       <c r="F58" s="21">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
         <v>125</v>
       </c>
       <c r="G58" s="21">
-        <f>(PARAM!$I$25/2)</f>
+        <f>(PARAM!$I$26/2)</f>
         <v>50</v>
       </c>
       <c r="H58" s="21">
-        <f>(PARAM!$F$25/2)</f>
+        <f>(PARAM!$F$26/2)</f>
         <v>35</v>
       </c>
       <c r="I58" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J58" s="21">
         <v>0</v>
@@ -4158,14 +4176,14 @@
         <v>0</v>
       </c>
       <c r="N58" s="21">
-        <f>((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))</f>
+        <f>((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
         <v>60</v>
       </c>
       <c r="O58" s="21">
         <v>0</v>
       </c>
       <c r="P58" s="21">
-        <f>PARAM!$H$25/2-1</f>
+        <f>PARAM!$H$26/2-1</f>
         <v>1</v>
       </c>
       <c r="Q58" s="21">
@@ -4175,20 +4193,20 @@
         <v>0</v>
       </c>
       <c r="S58" s="21">
-        <f>((PARAM!$F$14/2-PARAM!$G$25-PARAM!$F$25/2)/(PARAM!$E$25/2-1))</f>
+        <f>((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
         <v>85</v>
       </c>
       <c r="T58" s="21">
-        <f>PARAM!$E$25/2-1</f>
+        <f>PARAM!$E$26/2-1</f>
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B59" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D59" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4196,19 +4214,19 @@
       </c>
       <c r="E59" s="21"/>
       <c r="F59" s="21">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
         <v>125</v>
       </c>
       <c r="G59" s="21">
-        <f>-(PARAM!$I$25/2)</f>
+        <f>-(PARAM!$I$26/2)</f>
         <v>-50</v>
       </c>
       <c r="H59" s="21">
-        <f>(PARAM!$F$25/2)</f>
+        <f>(PARAM!$F$26/2)</f>
         <v>35</v>
       </c>
       <c r="I59" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J59" s="21">
         <v>0</v>
@@ -4223,14 +4241,14 @@
         <v>0</v>
       </c>
       <c r="N59" s="21">
-        <f>-((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))</f>
+        <f>-((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
         <v>-60</v>
       </c>
       <c r="O59" s="21">
         <v>0</v>
       </c>
       <c r="P59" s="21">
-        <f>PARAM!$H$25/2-1</f>
+        <f>PARAM!$H$26/2-1</f>
         <v>1</v>
       </c>
       <c r="Q59" s="21">
@@ -4240,20 +4258,20 @@
         <v>0</v>
       </c>
       <c r="S59" s="21">
-        <f>((PARAM!$F$14/2-PARAM!$G$25-PARAM!$F$25/2)/(PARAM!$E$25/2-1))</f>
+        <f>((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
         <v>85</v>
       </c>
       <c r="T59" s="21">
-        <f>PARAM!$E$25/2-1</f>
+        <f>PARAM!$E$26/2-1</f>
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B60" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D60" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4261,19 +4279,19 @@
       </c>
       <c r="E60" s="21"/>
       <c r="F60" s="21">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
         <v>125</v>
       </c>
       <c r="G60" s="21">
-        <f>(PARAM!$I$25/2)</f>
+        <f>(PARAM!$I$26/2)</f>
         <v>50</v>
       </c>
       <c r="H60" s="21">
-        <f>-(PARAM!$F$25/2)</f>
+        <f>-(PARAM!$F$26/2)</f>
         <v>-35</v>
       </c>
       <c r="I60" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J60" s="21">
         <v>0</v>
@@ -4288,14 +4306,14 @@
         <v>0</v>
       </c>
       <c r="N60" s="21">
-        <f>((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))</f>
+        <f>((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
         <v>60</v>
       </c>
       <c r="O60" s="21">
         <v>0</v>
       </c>
       <c r="P60" s="21">
-        <f>PARAM!$H$25/2-1</f>
+        <f>PARAM!$H$26/2-1</f>
         <v>1</v>
       </c>
       <c r="Q60" s="21">
@@ -4305,20 +4323,20 @@
         <v>0</v>
       </c>
       <c r="S60" s="21">
-        <f>-((PARAM!$F$14/2-PARAM!$G$25-PARAM!$F$25/2)/(PARAM!$E$25/2-1))</f>
+        <f>-((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
         <v>-85</v>
       </c>
       <c r="T60" s="21">
-        <f>PARAM!$E$25/2-1</f>
+        <f>PARAM!$E$26/2-1</f>
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B61" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D61" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4326,19 +4344,19 @@
       </c>
       <c r="E61" s="21"/>
       <c r="F61" s="21">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
         <v>125</v>
       </c>
       <c r="G61" s="21">
-        <f>-(PARAM!$I$25/2)</f>
+        <f>-(PARAM!$I$26/2)</f>
         <v>-50</v>
       </c>
       <c r="H61" s="21">
-        <f>-(PARAM!$F$25/2)</f>
+        <f>-(PARAM!$F$26/2)</f>
         <v>-35</v>
       </c>
       <c r="I61" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J61" s="21">
         <v>0</v>
@@ -4353,14 +4371,14 @@
         <v>0</v>
       </c>
       <c r="N61" s="21">
-        <f>-((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))</f>
+        <f>-((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
         <v>-60</v>
       </c>
       <c r="O61" s="21">
         <v>0</v>
       </c>
       <c r="P61" s="21">
-        <f>PARAM!$H$25/2-1</f>
+        <f>PARAM!$H$26/2-1</f>
         <v>1</v>
       </c>
       <c r="Q61" s="21">
@@ -4370,20 +4388,20 @@
         <v>0</v>
       </c>
       <c r="S61" s="21">
-        <f>-((PARAM!$F$14/2-PARAM!$G$25-PARAM!$F$25/2)/(PARAM!$E$25/2-1))</f>
+        <f>-((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
         <v>-85</v>
       </c>
       <c r="T61" s="21">
-        <f>PARAM!$E$25/2-1</f>
+        <f>PARAM!$E$26/2-1</f>
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B62" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D62" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4391,19 +4409,19 @@
       </c>
       <c r="E62" s="21"/>
       <c r="F62" s="21">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
         <v>-125</v>
       </c>
       <c r="G62" s="21">
-        <f>(PARAM!$I$25/2)</f>
+        <f>(PARAM!$I$26/2)</f>
         <v>50</v>
       </c>
       <c r="H62" s="21">
-        <f>(PARAM!$F$25/2)</f>
+        <f>(PARAM!$F$26/2)</f>
         <v>35</v>
       </c>
       <c r="I62" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J62" s="21">
         <v>0</v>
@@ -4418,14 +4436,14 @@
         <v>0</v>
       </c>
       <c r="N62" s="21">
-        <f>((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))</f>
+        <f>((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
         <v>60</v>
       </c>
       <c r="O62" s="21">
         <v>0</v>
       </c>
       <c r="P62" s="21">
-        <f>PARAM!$H$25/2-1</f>
+        <f>PARAM!$H$26/2-1</f>
         <v>1</v>
       </c>
       <c r="Q62" s="21">
@@ -4435,20 +4453,20 @@
         <v>0</v>
       </c>
       <c r="S62" s="21">
-        <f>((PARAM!$F$14/2-PARAM!$G$25-PARAM!$F$25/2)/(PARAM!$E$25/2-1))</f>
+        <f>((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
         <v>85</v>
       </c>
       <c r="T62" s="21">
-        <f>PARAM!$E$25/2-1</f>
+        <f>PARAM!$E$26/2-1</f>
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B63" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D63" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4456,19 +4474,19 @@
       </c>
       <c r="E63" s="21"/>
       <c r="F63" s="21">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
         <v>-125</v>
       </c>
       <c r="G63" s="21">
-        <f>-(PARAM!$I$25/2)</f>
+        <f>-(PARAM!$I$26/2)</f>
         <v>-50</v>
       </c>
       <c r="H63" s="21">
-        <f>(PARAM!$F$25/2)</f>
+        <f>(PARAM!$F$26/2)</f>
         <v>35</v>
       </c>
       <c r="I63" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J63" s="21">
         <v>0</v>
@@ -4483,14 +4501,14 @@
         <v>0</v>
       </c>
       <c r="N63" s="21">
-        <f>-((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))</f>
+        <f>-((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
         <v>-60</v>
       </c>
       <c r="O63" s="21">
         <v>0</v>
       </c>
       <c r="P63" s="21">
-        <f>PARAM!$H$25/2-1</f>
+        <f>PARAM!$H$26/2-1</f>
         <v>1</v>
       </c>
       <c r="Q63" s="21">
@@ -4500,20 +4518,20 @@
         <v>0</v>
       </c>
       <c r="S63" s="21">
-        <f>((PARAM!$F$14/2-PARAM!$G$25-PARAM!$F$25/2)/(PARAM!$E$25/2-1))</f>
+        <f>((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
         <v>85</v>
       </c>
       <c r="T63" s="21">
-        <f>PARAM!$E$25/2-1</f>
+        <f>PARAM!$E$26/2-1</f>
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B64" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D64" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4521,19 +4539,19 @@
       </c>
       <c r="E64" s="21"/>
       <c r="F64" s="21">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
         <v>-125</v>
       </c>
       <c r="G64" s="21">
-        <f>(PARAM!$I$25/2)</f>
+        <f>(PARAM!$I$26/2)</f>
         <v>50</v>
       </c>
       <c r="H64" s="21">
-        <f>-(PARAM!$F$25/2)</f>
+        <f>-(PARAM!$F$26/2)</f>
         <v>-35</v>
       </c>
       <c r="I64" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J64" s="21">
         <v>0</v>
@@ -4548,14 +4566,14 @@
         <v>0</v>
       </c>
       <c r="N64" s="21">
-        <f>((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))</f>
+        <f>((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
         <v>60</v>
       </c>
       <c r="O64" s="21">
         <v>0</v>
       </c>
       <c r="P64" s="21">
-        <f>PARAM!$H$25/2-1</f>
+        <f>PARAM!$H$26/2-1</f>
         <v>1</v>
       </c>
       <c r="Q64" s="21">
@@ -4565,20 +4583,20 @@
         <v>0</v>
       </c>
       <c r="S64" s="21">
-        <f>-((PARAM!$F$14/2-PARAM!$G$25-PARAM!$F$25/2)/(PARAM!$E$25/2-1))</f>
+        <f>-((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
         <v>-85</v>
       </c>
       <c r="T64" s="21">
-        <f>PARAM!$E$25/2-1</f>
+        <f>PARAM!$E$26/2-1</f>
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B65" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D65" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4586,19 +4604,19 @@
       </c>
       <c r="E65" s="21"/>
       <c r="F65" s="21">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$15))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
         <v>-125</v>
       </c>
       <c r="G65" s="21">
-        <f>-(PARAM!$I$25/2)</f>
+        <f>-(PARAM!$I$26/2)</f>
         <v>-50</v>
       </c>
       <c r="H65" s="21">
-        <f>-(PARAM!$F$25/2)</f>
+        <f>-(PARAM!$F$26/2)</f>
         <v>-35</v>
       </c>
       <c r="I65" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J65" s="21">
         <v>0</v>
@@ -4613,14 +4631,14 @@
         <v>0</v>
       </c>
       <c r="N65" s="21">
-        <f>-((PARAM!$E$14/2-PARAM!$J$25-PARAM!$I$25/2)/(PARAM!$H$25/2-1))</f>
+        <f>-((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
         <v>-60</v>
       </c>
       <c r="O65" s="21">
         <v>0</v>
       </c>
       <c r="P65" s="21">
-        <f>PARAM!$H$25/2-1</f>
+        <f>PARAM!$H$26/2-1</f>
         <v>1</v>
       </c>
       <c r="Q65" s="21">
@@ -4630,20 +4648,20 @@
         <v>0</v>
       </c>
       <c r="S65" s="21">
-        <f>-((PARAM!$F$14/2-PARAM!$G$25-PARAM!$F$25/2)/(PARAM!$E$25/2-1))</f>
+        <f>-((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
         <v>-85</v>
       </c>
       <c r="T65" s="21">
-        <f>PARAM!$E$25/2-1</f>
+        <f>PARAM!$E$26/2-1</f>
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B66" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D66" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -4651,19 +4669,19 @@
       </c>
       <c r="E66" s="21"/>
       <c r="F66" s="21">
-        <f>-(PARAM!$E$17/2-PARAM!$F$28)</f>
+        <f>-(PARAM!$E$18/2-PARAM!$F$29)</f>
         <v>-180</v>
       </c>
       <c r="G66" s="21">
-        <f>((PARAM!$F$17/2-PARAM!$I$28))</f>
+        <f>((PARAM!$F$18/2-PARAM!$I$29))</f>
         <v>180</v>
       </c>
       <c r="H66" s="21">
-        <f>-PARAM!$G$17/2</f>
+        <f>-PARAM!$G$18/2</f>
         <v>-10</v>
       </c>
       <c r="I66" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J66" s="21">
         <v>0</v>
@@ -4675,7 +4693,7 @@
         <v>0</v>
       </c>
       <c r="M66" s="21">
-        <f>((PARAM!$E$17-2*PARAM!$F$28)/(PARAM!$E$28-1))</f>
+        <f>((PARAM!$E$18-2*PARAM!$F$29)/(PARAM!$E$29-1))</f>
         <v>180</v>
       </c>
       <c r="N66" s="21">
@@ -4685,16 +4703,16 @@
         <v>0</v>
       </c>
       <c r="P66" s="21">
-        <f>PARAM!$E$28-1</f>
+        <f>PARAM!$E$29-1</f>
         <v>2</v>
       </c>
     </row>
     <row r="67" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B67" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D67" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -4702,19 +4720,19 @@
       </c>
       <c r="E67" s="21"/>
       <c r="F67" s="21">
-        <f>-(PARAM!$E$17/2-PARAM!$F$28)</f>
+        <f>-(PARAM!$E$18/2-PARAM!$F$29)</f>
         <v>-180</v>
       </c>
       <c r="G67" s="21">
-        <f>-((PARAM!$F$17/2-PARAM!$I$28))</f>
+        <f>-((PARAM!$F$18/2-PARAM!$I$29))</f>
         <v>-180</v>
       </c>
       <c r="H67" s="21">
-        <f>-PARAM!$G$17/2</f>
+        <f>-PARAM!$G$18/2</f>
         <v>-10</v>
       </c>
       <c r="I67" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J67" s="21">
         <v>0</v>
@@ -4726,7 +4744,7 @@
         <v>0</v>
       </c>
       <c r="M67" s="21">
-        <f>((PARAM!$E$17-2*PARAM!$F$28)/(PARAM!$E$28-1))</f>
+        <f>((PARAM!$E$18-2*PARAM!$F$29)/(PARAM!$E$29-1))</f>
         <v>180</v>
       </c>
       <c r="N67" s="21">
@@ -4736,36 +4754,36 @@
         <v>0</v>
       </c>
       <c r="P67" s="21">
-        <f>PARAM!$E$28-1</f>
+        <f>PARAM!$E$29-1</f>
         <v>2</v>
       </c>
     </row>
     <row r="68" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B68" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D68" s="21" t="str">
-        <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$28&gt;2),"bo.f","")</f>
+        <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$29&gt;2),"bo.f","")</f>
         <v/>
       </c>
       <c r="E68" s="21"/>
       <c r="F68" s="21">
-        <f>((PARAM!$E$17/2-PARAM!$F$28))</f>
+        <f>((PARAM!$E$18/2-PARAM!$F$29))</f>
         <v>180</v>
       </c>
       <c r="G68" s="21">
-        <f>-(PARAM!$F$17/2-PARAM!$I$28)+((PARAM!$F$17-2*PARAM!$I$28)/(PARAM!$H$28-1))</f>
+        <f>-(PARAM!$F$18/2-PARAM!$I$29)+((PARAM!$F$18-2*PARAM!$I$29)/(PARAM!$H$29-1))</f>
         <v>0</v>
       </c>
       <c r="H68" s="21">
-        <f>-PARAM!$G$17/2</f>
+        <f>-PARAM!$G$18/2</f>
         <v>-10</v>
       </c>
       <c r="I68" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J68" s="21">
         <v>0</v>
@@ -4780,43 +4798,43 @@
         <v>0</v>
       </c>
       <c r="N68" s="21">
-        <f>IF(PARAM!$H$28&gt;3,((PARAM!$F$17-2*PARAM!$I$28)/(PARAM!$H$28-1)),0)</f>
+        <f>IF(PARAM!$H$29&gt;3,((PARAM!$F$18-2*PARAM!$I$29)/(PARAM!$H$29-1)),0)</f>
         <v>0</v>
       </c>
       <c r="O68" s="21">
         <v>0</v>
       </c>
       <c r="P68" s="21">
-        <f>MAX(0,PARAM!$H$28-3)</f>
+        <f>MAX(0,PARAM!$H$29-3)</f>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B69" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D69" s="21" t="str">
-        <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$28&gt;2),"bo.f","")</f>
+        <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$29&gt;2),"bo.f","")</f>
         <v/>
       </c>
       <c r="E69" s="21"/>
       <c r="F69" s="21">
-        <f>-((PARAM!$E$17/2-PARAM!$F$28))</f>
+        <f>-((PARAM!$E$18/2-PARAM!$F$29))</f>
         <v>-180</v>
       </c>
       <c r="G69" s="21">
-        <f>-(PARAM!$F$17/2-PARAM!$I$28)+((PARAM!$F$17-2*PARAM!$I$28)/(PARAM!$H$28-1))</f>
+        <f>-(PARAM!$F$18/2-PARAM!$I$29)+((PARAM!$F$18-2*PARAM!$I$29)/(PARAM!$H$29-1))</f>
         <v>0</v>
       </c>
       <c r="H69" s="21">
-        <f>-PARAM!$G$17/2</f>
+        <f>-PARAM!$G$18/2</f>
         <v>-10</v>
       </c>
       <c r="I69" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J69" s="21">
         <v>0</v>
@@ -4831,23 +4849,23 @@
         <v>0</v>
       </c>
       <c r="N69" s="21">
-        <f>IF(PARAM!$H$28&gt;3,((PARAM!$F$17-2*PARAM!$I$28)/(PARAM!$H$28-1)),0)</f>
+        <f>IF(PARAM!$H$29&gt;3,((PARAM!$F$18-2*PARAM!$I$29)/(PARAM!$H$29-1)),0)</f>
         <v>0</v>
       </c>
       <c r="O69" s="21">
         <v>0</v>
       </c>
       <c r="P69" s="21">
-        <f>MAX(0,PARAM!$H$28-3)</f>
+        <f>MAX(0,PARAM!$H$29-3)</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B70" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D70" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -4855,19 +4873,19 @@
       </c>
       <c r="E70" s="21"/>
       <c r="F70" s="21">
-        <f>-(PARAM!$E$16/2-PARAM!$J$26)</f>
+        <f>-(PARAM!$E$17/2-PARAM!$J$27)</f>
         <v>-77</v>
       </c>
       <c r="G70" s="21">
-        <f>(PARAM!$G$6/2+PARAM!$G$16)</f>
+        <f>(PARAM!$G$6/2+PARAM!$G$17)</f>
         <v>15</v>
       </c>
       <c r="H70" s="21">
-        <f>(PARAM!$F$26/2)</f>
+        <f>(PARAM!$F$27/2)</f>
         <v>30</v>
       </c>
       <c r="I70" s="21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J70" s="21">
         <v>0</v>
@@ -4879,7 +4897,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="21">
-        <f>(PARAM!$E$16-2*PARAM!$J$26-PARAM!$I$26)/(PARAM!$H$26-1)</f>
+        <f>(PARAM!$E$17-2*PARAM!$J$27-PARAM!$I$27)/(PARAM!$H$27-1)</f>
         <v>77</v>
       </c>
       <c r="N70" s="21">
@@ -4889,7 +4907,7 @@
         <v>0</v>
       </c>
       <c r="P70" s="21">
-        <f>PARAM!$H$26-1</f>
+        <f>PARAM!$H$27-1</f>
         <v>2</v>
       </c>
       <c r="Q70" s="21">
@@ -4899,20 +4917,20 @@
         <v>0</v>
       </c>
       <c r="S70" s="21">
-        <f>((PARAM!$F$16/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
+        <f>((PARAM!$F$17/2-PARAM!$G$27-PARAM!$F$27/2)/(PARAM!$E$27/2-1))</f>
         <v>90</v>
       </c>
       <c r="T70" s="21">
-        <f>PARAM!$E$26/2-1</f>
+        <f>PARAM!$E$27/2-1</f>
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B71" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D71" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -4920,19 +4938,19 @@
       </c>
       <c r="E71" s="21"/>
       <c r="F71" s="21">
-        <f>-(PARAM!$E$16/2-PARAM!$J$26)</f>
+        <f>-(PARAM!$E$17/2-PARAM!$J$27)</f>
         <v>-77</v>
       </c>
       <c r="G71" s="21">
-        <f>(PARAM!$G$6/2+PARAM!$G$16)</f>
+        <f>(PARAM!$G$6/2+PARAM!$G$17)</f>
         <v>15</v>
       </c>
       <c r="H71" s="21">
-        <f>-(PARAM!$F$26/2)</f>
+        <f>-(PARAM!$F$27/2)</f>
         <v>-30</v>
       </c>
       <c r="I71" s="21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J71" s="21">
         <v>0</v>
@@ -4944,7 +4962,7 @@
         <v>0</v>
       </c>
       <c r="M71" s="21">
-        <f>(PARAM!$E$16-2*PARAM!$J$26-PARAM!$I$26)/(PARAM!$H$26-1)</f>
+        <f>(PARAM!$E$17-2*PARAM!$J$27-PARAM!$I$27)/(PARAM!$H$27-1)</f>
         <v>77</v>
       </c>
       <c r="N71" s="21">
@@ -4954,7 +4972,7 @@
         <v>0</v>
       </c>
       <c r="P71" s="21">
-        <f>PARAM!$H$26-1</f>
+        <f>PARAM!$H$27-1</f>
         <v>2</v>
       </c>
       <c r="Q71" s="21">
@@ -4964,39 +4982,39 @@
         <v>0</v>
       </c>
       <c r="S71" s="21">
-        <f>-((PARAM!$F$16/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
+        <f>-((PARAM!$F$17/2-PARAM!$G$27-PARAM!$F$27/2)/(PARAM!$E$27/2-1))</f>
         <v>-90</v>
       </c>
       <c r="T71" s="21">
-        <f>PARAM!$E$26/2-1</f>
+        <f>PARAM!$E$27/2-1</f>
         <v>1</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B72" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C72" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="D72" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="E72" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="D72" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="E72" s="21" t="s">
-        <v>113</v>
-      </c>
       <c r="F72" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -5004,16 +5022,16 @@
         <v>18</v>
       </c>
       <c r="B75" s="20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C75" s="21" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E75" s="21" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F75" s="21">
         <v>0</v>
@@ -5038,20 +5056,20 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B76" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C76" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="D76" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="E76" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="B76" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="C76" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="D76" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="E76" s="21" t="s">
-        <v>118</v>
-      </c>
       <c r="F76" s="21">
         <v>0</v>
       </c>
@@ -5059,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="H76" s="21">
-        <f>(PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$14,2*PARAM!$G$17))</f>
+        <f>(PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$15,2*PARAM!$G$18))</f>
         <v>710</v>
       </c>
       <c r="I76" s="21">
@@ -5078,16 +5096,16 @@
         <v>19</v>
       </c>
       <c r="B77" s="20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E77" s="21" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F77" s="21">
         <v>0</v>
@@ -5096,7 +5114,7 @@
         <v>0</v>
       </c>
       <c r="H77" s="21">
-        <f>-((PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$14,2*PARAM!$G$17))+MAX(1,PARAM!$I$7))</f>
+        <f>-((PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$15,2*PARAM!$G$18))+MAX(1,PARAM!$I$7))</f>
         <v>-1410</v>
       </c>
       <c r="I77" s="21">
@@ -5112,30 +5130,30 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B78" s="20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E78" s="21" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F78" s="21">
-        <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$14/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
+        <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$15/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
         <v>156</v>
       </c>
       <c r="G78" s="21">
-        <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$14/2),0))*SIN(RADIANS(PARAM!$J$6)),6)</f>
+        <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$15/2),0))*SIN(RADIANS(PARAM!$J$6)),6)</f>
         <v>0</v>
       </c>
       <c r="H78" s="21">
-        <f>(PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$14/2,PARAM!$G$17))+IF(PARAM!$C$6="H",0,-PARAM!$G$17/2)</f>
+        <f>(PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$15/2,PARAM!$G$18))+IF(PARAM!$C$6="H",0,-PARAM!$G$18/2)</f>
         <v>705</v>
       </c>
       <c r="I78" s="21">
@@ -5151,27 +5169,27 @@
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79" s="20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D79" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E79" s="21" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F79" s="21">
-        <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$14/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
+        <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$15/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
         <v>156</v>
       </c>
       <c r="G79" s="21">
-        <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$14/2),0))*SIN(RADIANS(PARAM!$J$6)),6)</f>
+        <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$15/2),0))*SIN(RADIANS(PARAM!$J$6)),6)</f>
         <v>0</v>
       </c>
       <c r="H79" s="21">
-        <f>-(PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$14/2,PARAM!$G$17))+IF(PARAM!$C$6="H",0,PARAM!$G$17/2)</f>
+        <f>-(PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$15/2,PARAM!$G$18))+IF(PARAM!$C$6="H",0,PARAM!$G$18/2)</f>
         <v>-705</v>
       </c>
       <c r="I79" s="21">
@@ -5187,12 +5205,12 @@
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="81" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B81" s="20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -5220,7 +5238,7 @@
         <v>7</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E1" s="23" t="s">
         <v>9</v>
@@ -5234,7 +5252,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
@@ -5245,7 +5263,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B3" s="27">
         <v>100</v>
@@ -5268,7 +5286,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B4" s="29">
         <v>125</v>
@@ -5291,7 +5309,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B5" s="27">
         <v>150</v>
@@ -5314,7 +5332,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B6" s="29">
         <v>148</v>
@@ -5337,7 +5355,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B7" s="27">
         <v>150</v>
@@ -5360,7 +5378,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B8" s="29">
         <v>198</v>
@@ -5383,7 +5401,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B9" s="27">
         <v>200</v>
@@ -5406,7 +5424,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B10" s="29">
         <v>194</v>
@@ -5429,7 +5447,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B11" s="27">
         <v>200</v>
@@ -5452,7 +5470,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B12" s="29">
         <v>200</v>
@@ -5475,7 +5493,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B13" s="27">
         <v>248</v>
@@ -5498,7 +5516,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B14" s="29">
         <v>250</v>
@@ -5521,7 +5539,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B15" s="27">
         <v>244</v>
@@ -5544,7 +5562,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B16" s="29">
         <v>250</v>
@@ -5567,7 +5585,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B17" s="27">
         <v>250</v>
@@ -5590,7 +5608,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B18" s="29">
         <v>298</v>
@@ -5613,7 +5631,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B19" s="27">
         <v>300</v>
@@ -5636,7 +5654,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B20" s="29">
         <v>294</v>
@@ -5659,7 +5677,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B21" s="27">
         <v>294</v>
@@ -5705,7 +5723,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B23" s="27">
         <v>300</v>
@@ -5728,7 +5746,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B24" s="29">
         <v>346</v>
@@ -5751,7 +5769,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B25" s="27">
         <v>350</v>
@@ -5774,7 +5792,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B26" s="29">
         <v>340</v>
@@ -5797,7 +5815,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B27" s="27">
         <v>344</v>
@@ -5820,7 +5838,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B28" s="29">
         <v>350</v>
@@ -5843,7 +5861,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B29" s="27">
         <v>396</v>
@@ -5866,7 +5884,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B30" s="29">
         <v>400</v>
@@ -5889,7 +5907,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B31" s="27">
         <v>390</v>
@@ -5912,7 +5930,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="28" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B32" s="29">
         <v>388</v>
@@ -5935,7 +5953,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B33" s="27">
         <v>394</v>
@@ -5958,7 +5976,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="28" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B34" s="29">
         <v>400</v>
@@ -5981,7 +5999,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B35" s="27">
         <v>400</v>
@@ -6004,7 +6022,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B36" s="29">
         <v>414</v>
@@ -6027,7 +6045,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B37" s="27">
         <v>428</v>
@@ -6050,7 +6068,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B38" s="29">
         <v>458</v>
@@ -6073,7 +6091,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B39" s="27">
         <v>498</v>
@@ -6096,7 +6114,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B40" s="29">
         <v>446</v>
@@ -6119,7 +6137,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B41" s="27">
         <v>450</v>
@@ -6142,7 +6160,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="28" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B42" s="29">
         <v>440</v>
@@ -6165,7 +6183,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B43" s="27">
         <v>440</v>
@@ -6188,7 +6206,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="28" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B44" s="29">
         <v>496</v>
@@ -6211,7 +6229,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="26" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B45" s="27">
         <v>500</v>
@@ -6234,7 +6252,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="28" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B46" s="29">
         <v>482</v>
@@ -6257,7 +6275,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="26" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B47" s="27">
         <v>488</v>
@@ -6280,7 +6298,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="28" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B48" s="29">
         <v>596</v>
@@ -6303,7 +6321,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B49" s="27">
         <v>600</v>
@@ -6326,7 +6344,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="28" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B50" s="29">
         <v>582</v>
@@ -6349,7 +6367,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B51" s="27">
         <v>588</v>
@@ -6372,7 +6390,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B52" s="29">
         <v>594</v>
@@ -6395,7 +6413,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="26" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B53" s="27">
         <v>692</v>
@@ -6418,7 +6436,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="28" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B54" s="29">
         <v>700</v>
@@ -6441,7 +6459,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B55" s="27">
         <v>792</v>
@@ -6464,7 +6482,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B56" s="29">
         <v>800</v>
@@ -6487,7 +6505,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B57" s="27">
         <v>890</v>
@@ -6510,7 +6528,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="28" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B58" s="29">
         <v>900</v>
@@ -6533,7 +6551,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B59" s="27">
         <v>912</v>
@@ -6556,7 +6574,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="28" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B60" s="29">
         <v>918</v>
@@ -6602,7 +6620,7 @@
         <v>7</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E1" s="23" t="s">
         <v>9</v>
@@ -6616,7 +6634,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
@@ -6627,7 +6645,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B3" s="27">
         <v>20</v>
@@ -6650,7 +6668,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B4" s="29">
         <v>20</v>
@@ -6673,7 +6691,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B5" s="27">
         <v>25</v>
@@ -6696,7 +6714,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B6" s="29">
         <v>25</v>
@@ -6719,7 +6737,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B7" s="27">
         <v>30</v>
@@ -6742,7 +6760,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B8" s="29">
         <v>30</v>
@@ -6765,7 +6783,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B9" s="27">
         <v>40</v>
@@ -6788,7 +6806,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B10" s="29">
         <v>40</v>
@@ -6811,7 +6829,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B11" s="27">
         <v>50</v>
@@ -6834,7 +6852,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B12" s="29">
         <v>50</v>
@@ -6857,7 +6875,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B13" s="27">
         <v>50</v>
@@ -6880,7 +6898,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B14" s="29">
         <v>60</v>
@@ -6903,7 +6921,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B15" s="27">
         <v>60</v>
@@ -6926,7 +6944,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B16" s="29">
         <v>60</v>
@@ -6949,7 +6967,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B17" s="27">
         <v>75</v>
@@ -6972,7 +6990,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" s="29">
         <v>75</v>
@@ -6995,7 +7013,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B19" s="27">
         <v>75</v>
@@ -7018,7 +7036,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B20" s="29">
         <v>75</v>
@@ -7041,7 +7059,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B21" s="27">
         <v>80</v>
@@ -7064,7 +7082,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B22" s="29">
         <v>80</v>
@@ -7087,7 +7105,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B23" s="27">
         <v>80</v>
@@ -7110,7 +7128,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B24" s="29">
         <v>90</v>
@@ -7133,7 +7151,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B25" s="27">
         <v>90</v>
@@ -7156,7 +7174,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B26" s="29">
         <v>100</v>
@@ -7179,7 +7197,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B27" s="27">
         <v>100</v>
@@ -7202,7 +7220,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B28" s="29">
         <v>100</v>
@@ -7225,7 +7243,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B29" s="27">
         <v>100</v>
@@ -7248,7 +7266,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B30" s="29">
         <v>100</v>
@@ -7271,7 +7289,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B31" s="27">
         <v>100</v>
@@ -7294,7 +7312,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="28" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B32" s="29">
         <v>100</v>
@@ -7317,7 +7335,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B33" s="27">
         <v>125</v>
@@ -7340,7 +7358,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="28" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B34" s="29">
         <v>125</v>
@@ -7363,7 +7381,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B35" s="27">
         <v>125</v>
@@ -7386,7 +7404,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B36" s="29">
         <v>125</v>
@@ -7409,7 +7427,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="26" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B37" s="27">
         <v>125</v>
@@ -7432,7 +7450,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="28" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B38" s="29">
         <v>125</v>
@@ -7455,7 +7473,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B39" s="27">
         <v>150</v>
@@ -7478,7 +7496,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="28" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B40" s="29">
         <v>150</v>
@@ -7501,7 +7519,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B41" s="27">
         <v>150</v>
@@ -7524,7 +7542,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="28" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B42" s="29">
         <v>150</v>
@@ -7547,7 +7565,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B43" s="27">
         <v>175</v>
@@ -7570,7 +7588,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="28" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B44" s="29">
         <v>175</v>
@@ -7593,7 +7611,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="26" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B45" s="27">
         <v>175</v>
@@ -7616,7 +7634,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="28" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B46" s="29">
         <v>200</v>
@@ -7639,7 +7657,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="26" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B47" s="27">
         <v>200</v>
@@ -7662,7 +7680,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="28" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B48" s="29">
         <v>200</v>
@@ -7685,7 +7703,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B49" s="27">
         <v>200</v>
@@ -7708,7 +7726,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="28" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B50" s="29">
         <v>200</v>
@@ -7731,7 +7749,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="26" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B51" s="27">
         <v>250</v>
@@ -7754,7 +7772,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="28" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B52" s="29">
         <v>250</v>
@@ -7777,7 +7795,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="26" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B53" s="27">
         <v>250</v>
@@ -7800,7 +7818,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="28" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B54" s="29">
         <v>250</v>
@@ -7823,7 +7841,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B55" s="27">
         <v>250</v>
@@ -7846,7 +7864,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="28" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B56" s="29">
         <v>300</v>
@@ -7869,7 +7887,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B57" s="27">
         <v>300</v>
@@ -7892,7 +7910,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="28" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B58" s="29">
         <v>300</v>
@@ -7915,7 +7933,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B59" s="27">
         <v>300</v>
@@ -7938,7 +7956,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="28" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B60" s="29">
         <v>200</v>
@@ -7961,7 +7979,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B61" s="27">
         <v>200</v>
@@ -7984,7 +8002,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="28" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B62" s="29">
         <v>200</v>
@@ -8007,7 +8025,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="26" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B63" s="27">
         <v>200</v>
@@ -8030,7 +8048,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="28" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B64" s="29">
         <v>250</v>
@@ -8053,7 +8071,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="26" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B65" s="27">
         <v>250</v>
@@ -8076,7 +8094,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="28" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B66" s="29">
         <v>250</v>
@@ -8099,7 +8117,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="26" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B67" s="27">
         <v>250</v>
@@ -8122,7 +8140,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="28" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B68" s="29">
         <v>250</v>
@@ -8145,7 +8163,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="26" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B69" s="27">
         <v>250</v>
@@ -8168,7 +8186,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="28" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B70" s="29">
         <v>300</v>
@@ -8191,7 +8209,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="26" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B71" s="27">
         <v>300</v>
@@ -8214,7 +8232,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="28" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B72" s="29">
         <v>300</v>
@@ -8237,7 +8255,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="26" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B73" s="27">
         <v>300</v>
@@ -8260,7 +8278,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="28" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B74" s="29">
         <v>300</v>
@@ -8283,7 +8301,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B75" s="27">
         <v>300</v>
@@ -8306,7 +8324,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="28" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B76" s="29">
         <v>300</v>
@@ -8329,7 +8347,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="26" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B77" s="27">
         <v>350</v>
@@ -8352,7 +8370,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="28" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B78" s="29">
         <v>350</v>
@@ -8375,7 +8393,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B79" s="27">
         <v>350</v>
@@ -8398,7 +8416,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="28" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B80" s="29">
         <v>350</v>
@@ -8421,7 +8439,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="26" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B81" s="27">
         <v>350</v>
@@ -8444,7 +8462,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="28" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B82" s="29">
         <v>350</v>
@@ -8467,7 +8485,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B83" s="27">
         <v>400</v>
@@ -8490,7 +8508,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B84" s="29">
         <v>400</v>
@@ -8513,7 +8531,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="26" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B85" s="27">
         <v>400</v>
@@ -8536,7 +8554,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="28" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B86" s="29">
         <v>400</v>
@@ -8559,7 +8577,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="26" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B87" s="27">
         <v>400</v>
@@ -8582,7 +8600,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="28" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B88" s="29">
         <v>400</v>
@@ -8605,7 +8623,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="26" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B89" s="27">
         <v>450</v>
@@ -8628,7 +8646,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="28" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B90" s="29">
         <v>450</v>
@@ -8651,7 +8669,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="26" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B91" s="27">
         <v>450</v>
@@ -8674,7 +8692,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="28" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B92" s="29">
         <v>450</v>
@@ -8697,7 +8715,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="26" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B93" s="27">
         <v>450</v>
@@ -8720,7 +8738,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="28" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B94" s="29">
         <v>450</v>
@@ -8743,7 +8761,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="26" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B95" s="27">
         <v>500</v>
@@ -8766,7 +8784,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="28" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B96" s="29">
         <v>500</v>
@@ -8789,7 +8807,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="26" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B97" s="27">
         <v>500</v>
@@ -8812,7 +8830,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="28" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B98" s="29">
         <v>500</v>
@@ -8835,7 +8853,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="26" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B99" s="27">
         <v>500</v>
@@ -8858,7 +8876,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="28" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B100" s="29">
         <v>500</v>
@@ -8881,7 +8899,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="26" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B101" s="27">
         <v>550</v>
@@ -8904,7 +8922,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B102" s="29">
         <v>550</v>
@@ -8927,7 +8945,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="26" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B103" s="27">
         <v>550</v>
@@ -8950,7 +8968,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="28" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B104" s="29">
         <v>550</v>
@@ -8973,7 +8991,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="26" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B105" s="27">
         <v>550</v>
@@ -8996,7 +9014,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="28" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B106" s="29">
         <v>600</v>
@@ -9019,7 +9037,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="26" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B107" s="27">
         <v>600</v>
@@ -9042,7 +9060,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="28" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B108" s="29">
         <v>600</v>
@@ -9065,7 +9083,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="26" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B109" s="27">
         <v>600</v>
@@ -9088,7 +9106,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="28" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B110" s="29">
         <v>600</v>
@@ -9111,7 +9129,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B111" s="27">
         <v>600</v>
@@ -9134,7 +9152,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B112" s="29">
         <v>600</v>
@@ -9157,7 +9175,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="26" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B113" s="27">
         <v>600</v>
@@ -9180,7 +9198,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="28" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B114" s="29">
         <v>600</v>
@@ -9203,7 +9221,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="26" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B115" s="27">
         <v>600</v>
@@ -9226,7 +9244,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="28" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B116" s="29">
         <v>600</v>
@@ -9249,7 +9267,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="26" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B117" s="27">
         <v>650</v>
@@ -9272,7 +9290,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="28" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B118" s="29">
         <v>650</v>
@@ -9295,7 +9313,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="26" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B119" s="27">
         <v>650</v>
@@ -9318,7 +9336,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="28" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B120" s="29">
         <v>650</v>
@@ -9341,7 +9359,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="26" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B121" s="27">
         <v>650</v>
@@ -9364,7 +9382,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="28" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B122" s="29">
         <v>650</v>
@@ -9387,7 +9405,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="26" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B123" s="27">
         <v>650</v>
@@ -9410,7 +9428,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="28" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B124" s="29">
         <v>650</v>
@@ -9433,7 +9451,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="26" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B125" s="27">
         <v>650</v>
@@ -9456,7 +9474,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="28" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B126" s="29">
         <v>650</v>
@@ -9479,7 +9497,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="26" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B127" s="27">
         <v>700</v>
@@ -9502,7 +9520,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="28" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B128" s="29">
         <v>700</v>
@@ -9525,7 +9543,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="26" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B129" s="27">
         <v>700</v>
@@ -9548,7 +9566,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="28" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B130" s="29">
         <v>700</v>
@@ -9571,7 +9589,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="26" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B131" s="27">
         <v>700</v>
@@ -9594,7 +9612,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="28" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B132" s="29">
         <v>700</v>
@@ -9617,7 +9635,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="26" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B133" s="27">
         <v>700</v>
@@ -9640,7 +9658,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="28" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B134" s="29">
         <v>700</v>
@@ -9663,7 +9681,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="26" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B135" s="27">
         <v>700</v>
@@ -9686,7 +9704,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="28" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B136" s="29">
         <v>700</v>
@@ -9709,7 +9727,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="26" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B137" s="27">
         <v>750</v>
@@ -9732,7 +9750,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="28" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B138" s="29">
         <v>750</v>
@@ -9755,7 +9773,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="26" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B139" s="27">
         <v>750</v>
@@ -9778,7 +9796,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="28" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B140" s="29">
         <v>750</v>
@@ -9801,7 +9819,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="26" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B141" s="27">
         <v>750</v>
@@ -9824,7 +9842,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="28" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B142" s="29">
         <v>750</v>
@@ -9847,7 +9865,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="26" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B143" s="27">
         <v>750</v>
@@ -9870,7 +9888,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="28" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B144" s="29">
         <v>750</v>
@@ -9893,7 +9911,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="26" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B145" s="27">
         <v>750</v>
@@ -9916,7 +9934,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="28" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B146" s="29">
         <v>800</v>
@@ -9939,7 +9957,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="26" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B147" s="27">
         <v>800</v>
@@ -9962,7 +9980,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="28" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B148" s="29">
         <v>800</v>
@@ -9985,7 +10003,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="26" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B149" s="27">
         <v>800</v>
@@ -10008,7 +10026,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="28" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B150" s="29">
         <v>800</v>
@@ -10031,7 +10049,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="26" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B151" s="27">
         <v>800</v>
@@ -10054,7 +10072,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="28" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B152" s="29">
         <v>800</v>
@@ -10077,7 +10095,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="26" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B153" s="27">
         <v>800</v>
@@ -10100,7 +10118,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="28" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B154" s="29">
         <v>800</v>

--- a/plate3d/PLATE3D_COLUMN.xlsx
+++ b/plate3d/PLATE3D_COLUMN.xlsx
@@ -1270,7 +1270,68 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FFB9C2CE"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF9FAFB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFB9C2CE"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF9FAFB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFB9C2CE"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF9FAFB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFB9C2CE"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF9FAFB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFB9C2CE"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF9FAFB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFB9C2CE"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF9FAFB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2193,6 +2254,36 @@
     <mergeCell ref="C22:K22"/>
     <mergeCell ref="B30:K30"/>
   </mergeCells>
+  <conditionalFormatting sqref="B15:K17">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$C$6&lt;&gt;"H"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26:K27">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$C$6&lt;&gt;"H"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H24:I24">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>$C$6&lt;&gt;"H"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18:K18">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>$C$6="H"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28:K29">
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>$C$6="H"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J24:J24">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>$C$6="H"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation type="list" showErrorMessage="1" error="H for an I section, R for a square tube." sqref="C6">
       <formula1>"H,R"</formula1>

--- a/plate3d/PLATE3D_COLUMN.xlsx
+++ b/plate3d/PLATE3D_COLUMN.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="393">
   <si>
     <t>COLUMN</t>
   </si>
@@ -227,6 +227,96 @@
     <t>bolts</t>
   </si>
   <si>
+    <t xml:space="preserve">  4.  BEAMS</t>
+  </si>
+  <si>
+    <t>four world directions - X+ X- Y+ Y-. Length 0 and that beam is not there</t>
+  </si>
+  <si>
+    <t>Detail</t>
+  </si>
+  <si>
+    <t>tw</t>
+  </si>
+  <si>
+    <t>X+</t>
+  </si>
+  <si>
+    <t>end plate</t>
+  </si>
+  <si>
+    <t>H-300x150x6.5x9 r13</t>
+  </si>
+  <si>
+    <t>X-</t>
+  </si>
+  <si>
+    <t>fin plate</t>
+  </si>
+  <si>
+    <t>Y+</t>
+  </si>
+  <si>
+    <t>Y-</t>
+  </si>
+  <si>
+    <t>Beams are H only: a tube has no web to bolt through. The direction is the world's, so Alpha decides whether a beam lands on a flange or on the web.</t>
+  </si>
+  <si>
+    <t>X faces</t>
+  </si>
+  <si>
+    <t>Y faces</t>
+  </si>
+  <si>
+    <t>beams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  5.  BEAM CONNECTION</t>
+  </si>
+  <si>
+    <t>end plate bolts through the column; fin plate is welded to it and bolts through the beam web — the one a tube can take</t>
+  </si>
+  <si>
+    <t>setback</t>
+  </si>
+  <si>
+    <t>width</t>
+  </si>
+  <si>
+    <t>height</t>
+  </si>
+  <si>
+    <t>thick</t>
+  </si>
+  <si>
+    <t>gauge</t>
+  </si>
+  <si>
+    <t>edge</t>
+  </si>
+  <si>
+    <t>pitch</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>Fin plate</t>
+  </si>
+  <si>
+    <t>Each height follows its own bolts. End plate gauge is across the beam web; fin plate gauge is out from the column face, setback the beam end short.</t>
+  </si>
+  <si>
+    <t>between flanges</t>
+  </si>
+  <si>
+    <t>bolt</t>
+  </si>
+  <si>
+    <t>flange passes</t>
+  </si>
+  <si>
     <t>Written from PARAM. Nothing here needs editing — change the front sheet instead.</t>
   </si>
   <si>
@@ -386,12 +476,102 @@
     <t>the splice point goes round the axis with the rest of it</t>
   </si>
   <si>
+    <t>SECT / PLATE / BOLT for the beams. One end plate serves all four; the bolt comes in two lengths because an X face and a Y face are not the same thickness of steel once Alpha has turned the column.</t>
+  </si>
+  <si>
+    <t>one per direction, so each can be its own section</t>
+  </si>
+  <si>
+    <t>sc.bma</t>
+  </si>
+  <si>
+    <t>sc.bmb</t>
+  </si>
+  <si>
+    <t>sc.bmc</t>
+  </si>
+  <si>
+    <t>sc.bmd</t>
+  </si>
+  <si>
+    <t>the beam end plate</t>
+  </si>
+  <si>
+    <t>pl.bep</t>
+  </si>
+  <si>
+    <t>the fin plate — welded to the column, not the beam</t>
+  </si>
+  <si>
+    <t>pl.fin</t>
+  </si>
+  <si>
+    <t>the fin plate bolt: through plate and web, and never through the column</t>
+  </si>
+  <si>
+    <t>bo.fin</t>
+  </si>
+  <si>
+    <t>through the flange on an H column, or through two plates on a tube</t>
+  </si>
+  <si>
+    <t>bo.bx</t>
+  </si>
+  <si>
+    <t>bo.by</t>
+  </si>
+  <si>
+    <t>Each beam is one module, written for BOTH details at once. Its origin is the START FACE OF THE BEAM, which is the point BASE holds, so every other row is a distance measured back from there.</t>
+  </si>
+  <si>
+    <t>beam X+  —  end plate</t>
+  </si>
+  <si>
+    <t>end plate, on the beam end</t>
+  </si>
+  <si>
+    <t>md.bma</t>
+  </si>
+  <si>
+    <t>on a tube column, a second one welded to the wall</t>
+  </si>
+  <si>
+    <t>fin plate, reaching out from the column beside the web</t>
+  </si>
+  <si>
+    <t>the beam, at the module origin</t>
+  </si>
+  <si>
+    <t>two across the web on an end plate, one line on a fin</t>
+  </si>
+  <si>
+    <t>beam X-  —  fin plate</t>
+  </si>
+  <si>
+    <t>md.bmb</t>
+  </si>
+  <si>
+    <t>beam Y+  —  fin plate</t>
+  </si>
+  <si>
+    <t>md.bmc</t>
+  </si>
+  <si>
+    <t>beam Y-  —  off, its Length being 0</t>
+  </si>
+  <si>
+    <t>md.bmd</t>
+  </si>
+  <si>
+    <t>The beams go on last. No spin: they belong to the grid, not to the column.</t>
+  </si>
+  <si>
+    <t>the beam start: the column face, plus the plate or plates in front of it</t>
+  </si>
+  <si>
     <t>END</t>
   </si>
   <si>
-    <t>tw</t>
-  </si>
-  <si>
     <t>user define</t>
   </si>
   <si>
@@ -441,9 +621,6 @@
   </si>
   <si>
     <t>H-298x149x5.5x8 r13</t>
-  </si>
-  <si>
-    <t>H-300x150x6.5x9 r13</t>
   </si>
   <si>
     <t>H-294x200x8x12 r18</t>
@@ -1666,7 +1843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K31"/>
+  <dimension ref="B1:L47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -2243,8 +2420,401 @@
         <v>44 per splice</v>
       </c>
     </row>
+    <row r="33" ht="20" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B33" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+    </row>
+    <row r="34" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C34" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B35" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E35" s="8">
+        <f>IFERROR(VLOOKUP($D$35,SECT!$A:$G,2,FALSE),"")</f>
+        <v>300</v>
+      </c>
+      <c r="F35" s="8">
+        <f>IFERROR(VLOOKUP($D$35,SECT!$A:$G,3,FALSE),"")</f>
+        <v>150</v>
+      </c>
+      <c r="G35" s="8">
+        <f>IFERROR(VLOOKUP($D$35,SECT!$A:$G,4,FALSE),"")</f>
+        <v>6.5</v>
+      </c>
+      <c r="H35" s="8">
+        <f>IFERROR(VLOOKUP($D$35,SECT!$A:$G,5,FALSE),"")</f>
+        <v>9</v>
+      </c>
+      <c r="I35" s="8">
+        <f>IFERROR(VLOOKUP($D$35,SECT!$A:$G,6,FALSE),"")</f>
+        <v>13</v>
+      </c>
+      <c r="J35" s="7">
+        <v>900</v>
+      </c>
+      <c r="K35" s="9">
+        <f>IFERROR(VLOOKUP($D$35,SECT!$A:$G,7,FALSE),"")</f>
+        <v>36.7</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B36" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E36" s="8">
+        <f>IFERROR(VLOOKUP($D$36,SECT!$A:$G,2,FALSE),"")</f>
+        <v>300</v>
+      </c>
+      <c r="F36" s="8">
+        <f>IFERROR(VLOOKUP($D$36,SECT!$A:$G,3,FALSE),"")</f>
+        <v>150</v>
+      </c>
+      <c r="G36" s="8">
+        <f>IFERROR(VLOOKUP($D$36,SECT!$A:$G,4,FALSE),"")</f>
+        <v>6.5</v>
+      </c>
+      <c r="H36" s="8">
+        <f>IFERROR(VLOOKUP($D$36,SECT!$A:$G,5,FALSE),"")</f>
+        <v>9</v>
+      </c>
+      <c r="I36" s="8">
+        <f>IFERROR(VLOOKUP($D$36,SECT!$A:$G,6,FALSE),"")</f>
+        <v>13</v>
+      </c>
+      <c r="J36" s="7">
+        <v>900</v>
+      </c>
+      <c r="K36" s="9">
+        <f>IFERROR(VLOOKUP($D$36,SECT!$A:$G,7,FALSE),"")</f>
+        <v>36.7</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B37" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E37" s="8">
+        <f>IFERROR(VLOOKUP($D$37,SECT!$A:$G,2,FALSE),"")</f>
+        <v>300</v>
+      </c>
+      <c r="F37" s="8">
+        <f>IFERROR(VLOOKUP($D$37,SECT!$A:$G,3,FALSE),"")</f>
+        <v>150</v>
+      </c>
+      <c r="G37" s="8">
+        <f>IFERROR(VLOOKUP($D$37,SECT!$A:$G,4,FALSE),"")</f>
+        <v>6.5</v>
+      </c>
+      <c r="H37" s="8">
+        <f>IFERROR(VLOOKUP($D$37,SECT!$A:$G,5,FALSE),"")</f>
+        <v>9</v>
+      </c>
+      <c r="I37" s="8">
+        <f>IFERROR(VLOOKUP($D$37,SECT!$A:$G,6,FALSE),"")</f>
+        <v>13</v>
+      </c>
+      <c r="J37" s="7">
+        <v>900</v>
+      </c>
+      <c r="K37" s="9">
+        <f>IFERROR(VLOOKUP($D$37,SECT!$A:$G,7,FALSE),"")</f>
+        <v>36.7</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B38" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38" s="8">
+        <f>IFERROR(VLOOKUP($D$38,SECT!$A:$G,2,FALSE),"")</f>
+        <v>300</v>
+      </c>
+      <c r="F38" s="8">
+        <f>IFERROR(VLOOKUP($D$38,SECT!$A:$G,3,FALSE),"")</f>
+        <v>150</v>
+      </c>
+      <c r="G38" s="8">
+        <f>IFERROR(VLOOKUP($D$38,SECT!$A:$G,4,FALSE),"")</f>
+        <v>6.5</v>
+      </c>
+      <c r="H38" s="8">
+        <f>IFERROR(VLOOKUP($D$38,SECT!$A:$G,5,FALSE),"")</f>
+        <v>9</v>
+      </c>
+      <c r="I38" s="8">
+        <f>IFERROR(VLOOKUP($D$38,SECT!$A:$G,6,FALSE),"")</f>
+        <v>13</v>
+      </c>
+      <c r="J38" s="7">
+        <v>0</v>
+      </c>
+      <c r="K38" s="9">
+        <f>IFERROR(VLOOKUP($D$38,SECT!$A:$G,7,FALSE),"")</f>
+        <v>36.7</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B39" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="12"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40" s="11" t="str">
+        <f>IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,"flange","web"),"tube wall")</f>
+        <v>flange</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="F40" s="11" t="str">
+        <f>IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,"web","flange"),"tube wall")</f>
+        <v>web</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H40" s="11" t="str">
+        <f>(IF(PARAM!$J$35&gt;0,1,0)+IF(PARAM!$J$36&gt;0,1,0)+IF(PARAM!$J$37&gt;0,1,0)+IF(PARAM!$J$38&gt;0,1,0))&amp;" of 4"</f>
+        <v>3 of 4</v>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B42" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+    </row>
+    <row r="43" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D43" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B44" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D44" s="14">
+        <v>0</v>
+      </c>
+      <c r="E44" s="7">
+        <v>230</v>
+      </c>
+      <c r="F44" s="17">
+        <f>PARAM!$J$44*(PARAM!$K$44-1)+2*PARAM!$I$44</f>
+        <v>230</v>
+      </c>
+      <c r="G44" s="7">
+        <v>20</v>
+      </c>
+      <c r="H44" s="7">
+        <v>140</v>
+      </c>
+      <c r="I44" s="7">
+        <v>45</v>
+      </c>
+      <c r="J44" s="7">
+        <v>70</v>
+      </c>
+      <c r="K44" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B45" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D45" s="7">
+        <v>10</v>
+      </c>
+      <c r="E45" s="7">
+        <v>140</v>
+      </c>
+      <c r="F45" s="17">
+        <f>PARAM!$J$45*(PARAM!$K$45-1)+2*PARAM!$I$45</f>
+        <v>230</v>
+      </c>
+      <c r="G45" s="7">
+        <v>10</v>
+      </c>
+      <c r="H45" s="7">
+        <v>60</v>
+      </c>
+      <c r="I45" s="7">
+        <v>45</v>
+      </c>
+      <c r="J45" s="7">
+        <v>70</v>
+      </c>
+      <c r="K45" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B46" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B47" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D47" s="11" t="str">
+        <f>IF(PARAM!$C$6="H",IF(PARAM!$H$44&gt;=PARAM!$G$35+3*PARAM!$E$24,"ok","too tight for the web"),IF(PARAM!$H$44&gt;=PARAM!$F$35+3*PARAM!$E$24,"ok","must clear the beam on a tube"))</f>
+        <v>ok</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F47" s="11" t="str">
+        <f>IF(PARAM!$E$44/2-PARAM!$H$44/2&gt;=1.5*PARAM!$E$24,"ok","plate too narrow")</f>
+        <v>ok</v>
+      </c>
+      <c r="G47" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="H47" s="11" t="str">
+        <f>IF(PARAM!$C$6="H",IF(PARAM!$E$44&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,PARAM!$E$44&amp;" ≤ "&amp;(PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6),"hits the flanges on a web face"),"n/a")</f>
+        <v>230 ≤ 234</v>
+      </c>
+      <c r="I47" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="J47" s="11" t="str">
+        <f>"M"&amp;PARAM!$E$24&amp;" L"&amp;IF(PARAM!$C$6="H",CEILING(MAX(IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6),IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6))+PARAM!$G$44+1.1*PARAM!$E$24,5),CEILING(2*PARAM!$G$44+1.1*PARAM!$E$24,5))</f>
+        <v>M16 L55</v>
+      </c>
+      <c r="K47" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="L47" s="11" t="str">
+        <f>IF(NOT(PARAM!$C$6="H"),"n/a",IF(MOD(PARAM!$J$6,180)=0,IF(MAX(PARAM!$F$37,PARAM!$F$38)&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"ok","strip the beam flange"),IF(MAX(PARAM!$F$35,PARAM!$F$36)&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"ok","strip the beam flange")))</f>
+        <v>ok</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="12">
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="E8:K8"/>
     <mergeCell ref="B9:K9"/>
@@ -2253,6 +2823,10 @@
     <mergeCell ref="B19:K19"/>
     <mergeCell ref="C22:K22"/>
     <mergeCell ref="B30:K30"/>
+    <mergeCell ref="C33:K33"/>
+    <mergeCell ref="B39:K39"/>
+    <mergeCell ref="C42:K42"/>
+    <mergeCell ref="B46:K46"/>
   </mergeCells>
   <conditionalFormatting sqref="B15:K17">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2284,9 +2858,15 @@
       <formula>$C$6="H"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="6">
+    <dataValidation type="list" showErrorMessage="1" error="end plate bolts through the column; fin plate bolts through the beam web." sqref="C35:C38">
+      <formula1>"end plate,fin plate"</formula1>
+    </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="H for an I section, R for a square tube." sqref="C6">
       <formula1>"H,R"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" error="Pick an H section — a beam has to have a web to bolt through." sqref="D35:D38">
+      <formula1>SECT!$A$2:$A$60</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="Pick one from the list, or &quot;user define&quot; at the top of it." sqref="D6">
       <formula1>INDIRECT("SEC_"&amp;$C$6)</formula1>
@@ -2305,7 +2885,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T81"/>
+  <dimension ref="A1:T132"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -2317,30 +2897,30 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -2348,10 +2928,10 @@
         <v>17</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="D6" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -2366,7 +2946,7 @@
         <v>H</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="H6" s="21">
         <f>PARAM!$E$6</f>
@@ -2402,10 +2982,10 @@
         <v>18</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="D7" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -2420,7 +3000,7 @@
         <v>H</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="H7" s="21">
         <f>PARAM!$E$6</f>
@@ -2456,10 +3036,10 @@
         <v>19</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="D8" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -2474,7 +3054,7 @@
         <v>H</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="H8" s="21">
         <f>PARAM!$E$6</f>
@@ -2507,23 +3087,23 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="D11" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -2534,10 +3114,10 @@
         <v>12</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="H11" s="21">
         <f>IF(PARAM!$C$6="H",PARAM!$E$15,PARAM!$E$18)</f>
@@ -2550,13 +3130,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="D12" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -2567,10 +3147,10 @@
         <v>10</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="H12" s="21">
         <f>PARAM!$E$16</f>
@@ -2583,13 +3163,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="D13" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -2600,10 +3180,10 @@
         <v>10</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="H13" s="21">
         <f>PARAM!$E$17</f>
@@ -2616,13 +3196,13 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="D14" s="21" t="str">
         <f>PARAM!$G$24</f>
@@ -2654,13 +3234,13 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="D15" s="21" t="str">
         <f>PARAM!$G$24</f>
@@ -2692,28 +3272,28 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="D19" s="21" t="str">
         <f>IF(PARAM!$E$7&gt;0,"sc.c1","")</f>
@@ -2730,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="J19" s="21">
         <v>0</v>
@@ -2744,27 +3324,27 @@
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="D21" s="21" t="str">
         <f>"sc.c2"</f>
@@ -2781,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="21" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="J21" s="21">
         <v>0</v>
@@ -2795,27 +3375,27 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="D23" s="21" t="str">
         <f>IF(PARAM!$I$7&gt;0,"sc.c3","")</f>
@@ -2832,7 +3412,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="21" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="J23" s="21">
         <v>0</v>
@@ -2846,47 +3426,47 @@
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D27" s="21" t="str">
         <f>IF(PARAM!$E$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F27" s="21">
         <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$15/2)),0)</f>
@@ -2906,17 +3486,17 @@
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B28" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D28" s="21" t="str">
         <f>IF(PARAM!$E$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F28" s="21">
         <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$15/2)),0)</f>
@@ -2936,20 +3516,20 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D29" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F29" s="21">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -2963,22 +3543,22 @@
         <v>0</v>
       </c>
       <c r="I29" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D30" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F30" s="21">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -2992,22 +3572,22 @@
         <v>0</v>
       </c>
       <c r="I30" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D31" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F31" s="21">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -3021,22 +3601,22 @@
         <v>0</v>
       </c>
       <c r="I31" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D32" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F32" s="21">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -3050,25 +3630,25 @@
         <v>0</v>
       </c>
       <c r="I32" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D33" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F33" s="21">
         <v>0</v>
@@ -3081,22 +3661,22 @@
         <v>0</v>
       </c>
       <c r="I33" s="21" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D34" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F34" s="21">
         <v>0</v>
@@ -3109,18 +3689,18 @@
         <v>0</v>
       </c>
       <c r="I34" s="21" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D35" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3140,7 +3720,7 @@
         <v>35</v>
       </c>
       <c r="I35" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="J35" s="21">
         <v>0</v>
@@ -3182,10 +3762,10 @@
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B36" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D36" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3205,7 +3785,7 @@
         <v>35</v>
       </c>
       <c r="I36" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="J36" s="21">
         <v>0</v>
@@ -3247,10 +3827,10 @@
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B37" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D37" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3270,7 +3850,7 @@
         <v>-35</v>
       </c>
       <c r="I37" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="J37" s="21">
         <v>0</v>
@@ -3312,10 +3892,10 @@
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B38" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D38" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3335,7 +3915,7 @@
         <v>-35</v>
       </c>
       <c r="I38" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="J38" s="21">
         <v>0</v>
@@ -3377,10 +3957,10 @@
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B39" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D39" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3400,7 +3980,7 @@
         <v>35</v>
       </c>
       <c r="I39" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="J39" s="21">
         <v>0</v>
@@ -3442,10 +4022,10 @@
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B40" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D40" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3465,7 +4045,7 @@
         <v>35</v>
       </c>
       <c r="I40" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="J40" s="21">
         <v>0</v>
@@ -3507,10 +4087,10 @@
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B41" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D41" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3530,7 +4110,7 @@
         <v>-35</v>
       </c>
       <c r="I41" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="J41" s="21">
         <v>0</v>
@@ -3572,10 +4152,10 @@
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B42" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D42" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -3595,7 +4175,7 @@
         <v>-35</v>
       </c>
       <c r="I42" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="J42" s="21">
         <v>0</v>
@@ -3637,13 +4217,13 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D43" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -3663,7 +4243,7 @@
         <v>-10</v>
       </c>
       <c r="I43" s="21" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="J43" s="21">
         <v>0</v>
@@ -3691,10 +4271,10 @@
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B44" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D44" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -3714,7 +4294,7 @@
         <v>-10</v>
       </c>
       <c r="I44" s="21" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="J44" s="21">
         <v>0</v>
@@ -3742,13 +4322,13 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D45" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$29&gt;2),"bo.f","")</f>
@@ -3768,7 +4348,7 @@
         <v>-10</v>
       </c>
       <c r="I45" s="21" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="J45" s="21">
         <v>0</v>
@@ -3796,10 +4376,10 @@
     </row>
     <row r="46" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B46" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D46" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$29&gt;2),"bo.f","")</f>
@@ -3819,7 +4399,7 @@
         <v>-10</v>
       </c>
       <c r="I46" s="21" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="J46" s="21">
         <v>0</v>
@@ -3847,13 +4427,13 @@
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D47" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -3873,7 +4453,7 @@
         <v>30</v>
       </c>
       <c r="I47" s="21" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="J47" s="21">
         <v>0</v>
@@ -3915,10 +4495,10 @@
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B48" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D48" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -3938,7 +4518,7 @@
         <v>-30</v>
       </c>
       <c r="I48" s="21" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="J48" s="21">
         <v>0</v>
@@ -3980,34 +4560,34 @@
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B49" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="F49" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B50" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D50" s="21" t="str">
         <f>IF(PARAM!$I$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F50" s="21">
         <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$15/2)),0)</f>
@@ -4027,17 +4607,17 @@
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B51" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D51" s="21" t="str">
         <f>IF(PARAM!$I$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E51" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F51" s="21">
         <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$15/2)),0)</f>
@@ -4057,17 +4637,17 @@
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B52" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D52" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E52" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F52" s="21">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -4081,22 +4661,22 @@
         <v>0</v>
       </c>
       <c r="I52" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B53" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D53" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E53" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F53" s="21">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -4110,22 +4690,22 @@
         <v>0</v>
       </c>
       <c r="I53" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B54" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D54" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F54" s="21">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -4139,22 +4719,22 @@
         <v>0</v>
       </c>
       <c r="I54" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B55" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D55" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E55" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F55" s="21">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -4168,22 +4748,22 @@
         <v>0</v>
       </c>
       <c r="I55" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B56" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D56" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E56" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F56" s="21">
         <v>0</v>
@@ -4196,22 +4776,22 @@
         <v>0</v>
       </c>
       <c r="I56" s="21" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B57" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D57" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E57" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F57" s="21">
         <v>0</v>
@@ -4224,15 +4804,15 @@
         <v>0</v>
       </c>
       <c r="I57" s="21" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B58" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D58" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4252,7 +4832,7 @@
         <v>35</v>
       </c>
       <c r="I58" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="J58" s="21">
         <v>0</v>
@@ -4294,10 +4874,10 @@
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B59" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D59" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4317,7 +4897,7 @@
         <v>35</v>
       </c>
       <c r="I59" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="J59" s="21">
         <v>0</v>
@@ -4359,10 +4939,10 @@
     </row>
     <row r="60" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B60" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D60" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4382,7 +4962,7 @@
         <v>-35</v>
       </c>
       <c r="I60" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="J60" s="21">
         <v>0</v>
@@ -4424,10 +5004,10 @@
     </row>
     <row r="61" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B61" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D61" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4447,7 +5027,7 @@
         <v>-35</v>
       </c>
       <c r="I61" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="J61" s="21">
         <v>0</v>
@@ -4489,10 +5069,10 @@
     </row>
     <row r="62" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B62" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D62" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4512,7 +5092,7 @@
         <v>35</v>
       </c>
       <c r="I62" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="J62" s="21">
         <v>0</v>
@@ -4554,10 +5134,10 @@
     </row>
     <row r="63" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B63" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D63" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4577,7 +5157,7 @@
         <v>35</v>
       </c>
       <c r="I63" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="J63" s="21">
         <v>0</v>
@@ -4619,10 +5199,10 @@
     </row>
     <row r="64" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B64" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D64" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4642,7 +5222,7 @@
         <v>-35</v>
       </c>
       <c r="I64" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="J64" s="21">
         <v>0</v>
@@ -4684,10 +5264,10 @@
     </row>
     <row r="65" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B65" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D65" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4707,7 +5287,7 @@
         <v>-35</v>
       </c>
       <c r="I65" s="21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="J65" s="21">
         <v>0</v>
@@ -4749,10 +5329,10 @@
     </row>
     <row r="66" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B66" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D66" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -4772,7 +5352,7 @@
         <v>-10</v>
       </c>
       <c r="I66" s="21" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="J66" s="21">
         <v>0</v>
@@ -4800,10 +5380,10 @@
     </row>
     <row r="67" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B67" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D67" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -4823,7 +5403,7 @@
         <v>-10</v>
       </c>
       <c r="I67" s="21" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="J67" s="21">
         <v>0</v>
@@ -4851,10 +5431,10 @@
     </row>
     <row r="68" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B68" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D68" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$29&gt;2),"bo.f","")</f>
@@ -4874,7 +5454,7 @@
         <v>-10</v>
       </c>
       <c r="I68" s="21" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="J68" s="21">
         <v>0</v>
@@ -4902,10 +5482,10 @@
     </row>
     <row r="69" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B69" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D69" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$29&gt;2),"bo.f","")</f>
@@ -4925,7 +5505,7 @@
         <v>-10</v>
       </c>
       <c r="I69" s="21" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="J69" s="21">
         <v>0</v>
@@ -4953,10 +5533,10 @@
     </row>
     <row r="70" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B70" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D70" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -4976,7 +5556,7 @@
         <v>30</v>
       </c>
       <c r="I70" s="21" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="J70" s="21">
         <v>0</v>
@@ -5018,10 +5598,10 @@
     </row>
     <row r="71" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B71" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D71" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -5041,7 +5621,7 @@
         <v>-30</v>
       </c>
       <c r="I71" s="21" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="J71" s="21">
         <v>0</v>
@@ -5083,29 +5663,29 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B72" s="20" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="E72" s="21" t="s">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="F72" s="21" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -5113,16 +5693,16 @@
         <v>18</v>
       </c>
       <c r="B75" s="20" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="C75" s="21" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="E75" s="21" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="F75" s="21">
         <v>0</v>
@@ -5147,19 +5727,19 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="B76" s="20" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="D76" s="21" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="E76" s="21" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="F76" s="21">
         <v>0</v>
@@ -5187,16 +5767,16 @@
         <v>19</v>
       </c>
       <c r="B77" s="20" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="E77" s="21" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="F77" s="21">
         <v>0</v>
@@ -5221,19 +5801,19 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="B78" s="20" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="E78" s="21" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="F78" s="21">
         <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$15/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
@@ -5260,16 +5840,16 @@
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79" s="20" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="D79" s="21" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="E79" s="21" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="F79" s="21">
         <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$15/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
@@ -5296,12 +5876,1504 @@
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B81" s="20" t="s">
-        <v>122</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="12" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A82" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="B82" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="C82" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="D82" s="21" t="str">
+        <f>PARAM!$C$8</f>
+        <v>SS275</v>
+      </c>
+      <c r="E82" s="21">
+        <f>MAX(1,PARAM!$J$35)</f>
+        <v>900</v>
+      </c>
+      <c r="F82" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G82" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="H82" s="21">
+        <f>PARAM!$E$35</f>
+        <v>300</v>
+      </c>
+      <c r="I82" s="21">
+        <f>PARAM!$F$35</f>
+        <v>150</v>
+      </c>
+      <c r="J82" s="21">
+        <f>PARAM!$F$35</f>
+        <v>150</v>
+      </c>
+      <c r="K82" s="21">
+        <f>PARAM!$G$35</f>
+        <v>6.5</v>
+      </c>
+      <c r="L82" s="21">
+        <f>PARAM!$H$35</f>
+        <v>9</v>
+      </c>
+      <c r="M82" s="21">
+        <f>PARAM!$H$35</f>
+        <v>9</v>
+      </c>
+      <c r="N82" s="21">
+        <f>PARAM!$I$35</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B83" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="C83" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="D83" s="21" t="str">
+        <f>PARAM!$C$8</f>
+        <v>SS275</v>
+      </c>
+      <c r="E83" s="21">
+        <f>MAX(1,PARAM!$J$36)</f>
+        <v>900</v>
+      </c>
+      <c r="F83" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G83" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="H83" s="21">
+        <f>PARAM!$E$36</f>
+        <v>300</v>
+      </c>
+      <c r="I83" s="21">
+        <f>PARAM!$F$36</f>
+        <v>150</v>
+      </c>
+      <c r="J83" s="21">
+        <f>PARAM!$F$36</f>
+        <v>150</v>
+      </c>
+      <c r="K83" s="21">
+        <f>PARAM!$G$36</f>
+        <v>6.5</v>
+      </c>
+      <c r="L83" s="21">
+        <f>PARAM!$H$36</f>
+        <v>9</v>
+      </c>
+      <c r="M83" s="21">
+        <f>PARAM!$H$36</f>
+        <v>9</v>
+      </c>
+      <c r="N83" s="21">
+        <f>PARAM!$I$36</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B84" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="C84" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D84" s="21" t="str">
+        <f>PARAM!$C$8</f>
+        <v>SS275</v>
+      </c>
+      <c r="E84" s="21">
+        <f>MAX(1,PARAM!$J$37)</f>
+        <v>900</v>
+      </c>
+      <c r="F84" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G84" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="H84" s="21">
+        <f>PARAM!$E$37</f>
+        <v>300</v>
+      </c>
+      <c r="I84" s="21">
+        <f>PARAM!$F$37</f>
+        <v>150</v>
+      </c>
+      <c r="J84" s="21">
+        <f>PARAM!$F$37</f>
+        <v>150</v>
+      </c>
+      <c r="K84" s="21">
+        <f>PARAM!$G$37</f>
+        <v>6.5</v>
+      </c>
+      <c r="L84" s="21">
+        <f>PARAM!$H$37</f>
+        <v>9</v>
+      </c>
+      <c r="M84" s="21">
+        <f>PARAM!$H$37</f>
+        <v>9</v>
+      </c>
+      <c r="N84" s="21">
+        <f>PARAM!$I$37</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B85" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="C85" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="D85" s="21" t="str">
+        <f>PARAM!$C$8</f>
+        <v>SS275</v>
+      </c>
+      <c r="E85" s="21">
+        <f>MAX(1,PARAM!$J$38)</f>
+        <v>1</v>
+      </c>
+      <c r="F85" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G85" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="H85" s="21">
+        <f>PARAM!$E$38</f>
+        <v>300</v>
+      </c>
+      <c r="I85" s="21">
+        <f>PARAM!$F$38</f>
+        <v>150</v>
+      </c>
+      <c r="J85" s="21">
+        <f>PARAM!$F$38</f>
+        <v>150</v>
+      </c>
+      <c r="K85" s="21">
+        <f>PARAM!$G$38</f>
+        <v>6.5</v>
+      </c>
+      <c r="L85" s="21">
+        <f>PARAM!$H$38</f>
+        <v>9</v>
+      </c>
+      <c r="M85" s="21">
+        <f>PARAM!$H$38</f>
+        <v>9</v>
+      </c>
+      <c r="N85" s="21">
+        <f>PARAM!$I$38</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B86" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C86" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="D86" s="21" t="str">
+        <f>PARAM!$C$8</f>
+        <v>SS275</v>
+      </c>
+      <c r="E86" s="21">
+        <f>PARAM!$G$44</f>
+        <v>20</v>
+      </c>
+      <c r="F86" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="G86" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="H86" s="21">
+        <f>PARAM!$E$44</f>
+        <v>230</v>
+      </c>
+      <c r="I86" s="21">
+        <f>PARAM!$F$44</f>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="B87" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C87" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="D87" s="21" t="str">
+        <f>PARAM!$C$8</f>
+        <v>SS275</v>
+      </c>
+      <c r="E87" s="21">
+        <f>PARAM!$G$45</f>
+        <v>10</v>
+      </c>
+      <c r="F87" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="G87" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="H87" s="21">
+        <f>PARAM!$E$45</f>
+        <v>140</v>
+      </c>
+      <c r="I87" s="21">
+        <f>PARAM!$F$45</f>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="B88" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C88" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="D88" s="21" t="str">
+        <f>PARAM!$G$24</f>
+        <v>F10T</v>
+      </c>
+      <c r="E88" s="21">
+        <f>PARAM!$E$24</f>
+        <v>16</v>
+      </c>
+      <c r="F88" s="21">
+        <f>CEILING(PARAM!$G$45+PARAM!$G$35+1.1*PARAM!$E$24,5)</f>
+        <v>35</v>
+      </c>
+      <c r="G88" s="21">
+        <f>PARAM!$F$24</f>
+        <v>18</v>
+      </c>
+      <c r="H88" s="21"/>
+      <c r="I88" s="21"/>
+      <c r="J88" s="21"/>
+      <c r="K88" s="21">
+        <f>0.9*PARAM!$E$24</f>
+        <v>14.4</v>
+      </c>
+      <c r="L88" s="21">
+        <f>CEILING(PARAM!$G$45+PARAM!$G$35+1.1*PARAM!$E$24,5)-PARAM!$G$45-PARAM!$G$35-0.9*PARAM!$E$24</f>
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B89" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C89" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="D89" s="21" t="str">
+        <f>PARAM!$G$24</f>
+        <v>F10T</v>
+      </c>
+      <c r="E89" s="21">
+        <f>PARAM!$E$24</f>
+        <v>16</v>
+      </c>
+      <c r="F89" s="21">
+        <f>IF(PARAM!$C$6="H",CEILING(IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+PARAM!$G$44+1.1*PARAM!$E$24,5),CEILING(2*PARAM!$G$44+1.1*PARAM!$E$24,5))</f>
+        <v>55</v>
+      </c>
+      <c r="G89" s="21">
+        <f>PARAM!$F$24</f>
+        <v>18</v>
+      </c>
+      <c r="H89" s="21"/>
+      <c r="I89" s="21"/>
+      <c r="J89" s="21"/>
+      <c r="K89" s="21">
+        <f>0.9*PARAM!$E$24</f>
+        <v>14.4</v>
+      </c>
+      <c r="L89" s="21">
+        <f>(IF(PARAM!$C$6="H",CEILING(IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+PARAM!$G$44+1.1*PARAM!$E$24,5),CEILING(2*PARAM!$G$44+1.1*PARAM!$E$24,5)))-(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+PARAM!$G$44,2*PARAM!$G$44))-0.9*PARAM!$E$24</f>
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="90" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B90" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C90" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="D90" s="21" t="str">
+        <f>PARAM!$G$24</f>
+        <v>F10T</v>
+      </c>
+      <c r="E90" s="21">
+        <f>PARAM!$E$24</f>
+        <v>16</v>
+      </c>
+      <c r="F90" s="21">
+        <f>IF(PARAM!$C$6="H",CEILING(IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+PARAM!$G$44+1.1*PARAM!$E$24,5),CEILING(2*PARAM!$G$44+1.1*PARAM!$E$24,5))</f>
+        <v>50</v>
+      </c>
+      <c r="G90" s="21">
+        <f>PARAM!$F$24</f>
+        <v>18</v>
+      </c>
+      <c r="H90" s="21"/>
+      <c r="I90" s="21"/>
+      <c r="J90" s="21"/>
+      <c r="K90" s="21">
+        <f>0.9*PARAM!$E$24</f>
+        <v>14.4</v>
+      </c>
+      <c r="L90" s="21">
+        <f>(IF(PARAM!$C$6="H",CEILING(IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+PARAM!$G$44+1.1*PARAM!$E$24,5),CEILING(2*PARAM!$G$44+1.1*PARAM!$E$24,5)))-(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+PARAM!$G$44,2*PARAM!$G$44))-0.9*PARAM!$E$24</f>
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="12" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="12" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A95" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="B95" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C95" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D95" s="21" t="str">
+        <f>IF(AND(PARAM!$J$35&gt;0,PARAM!$C$35="end plate"),"pl.bep","")</f>
+        <v>pl.bep</v>
+      </c>
+      <c r="E95" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="F95" s="21">
+        <f>-PARAM!$G$44/2</f>
+        <v>-10</v>
+      </c>
+      <c r="G95" s="21">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="H95" s="21">
+        <v>0</v>
+      </c>
+      <c r="I95" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="J95" s="21">
+        <v>0</v>
+      </c>
+      <c r="K95" s="21">
+        <v>0</v>
+      </c>
+      <c r="L95" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A96" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="B96" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C96" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D96" s="21" t="str">
+        <f>IF(AND(PARAM!$J$35&gt;0,PARAM!$C$35="end plate",NOT(PARAM!$C$6="H")),"pl.bep","")</f>
+        <v/>
+      </c>
+      <c r="E96" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="F96" s="21">
+        <f>-1.5*PARAM!$G$44</f>
+        <v>-30</v>
+      </c>
+      <c r="G96" s="21">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="H96" s="21">
+        <v>0</v>
+      </c>
+      <c r="I96" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="J96" s="21">
+        <v>0</v>
+      </c>
+      <c r="K96" s="21">
+        <v>0</v>
+      </c>
+      <c r="L96" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="B97" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C97" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D97" s="21" t="str">
+        <f>IF(AND(PARAM!$J$35&gt;0,PARAM!$C$35="fin plate"),"pl.fin","")</f>
+        <v/>
+      </c>
+      <c r="E97" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="F97" s="21">
+        <f>PARAM!$E$45/2-PARAM!$D$45</f>
+        <v>60</v>
+      </c>
+      <c r="G97" s="21">
+        <f>PARAM!$G$35/2+PARAM!$G$45/2</f>
+        <v>8.25</v>
+      </c>
+      <c r="H97" s="21">
+        <v>0</v>
+      </c>
+      <c r="I97" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="J97" s="21">
+        <v>0</v>
+      </c>
+      <c r="K97" s="21">
+        <v>0</v>
+      </c>
+      <c r="L97" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A98" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B98" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C98" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D98" s="21" t="str">
+        <f>IF(PARAM!$J$35&gt;0,"sc.bma","")</f>
+        <v>sc.bma</v>
+      </c>
+      <c r="E98" s="21"/>
+      <c r="F98" s="21">
+        <v>0</v>
+      </c>
+      <c r="G98" s="21">
+        <v>0</v>
+      </c>
+      <c r="H98" s="21">
+        <v>0</v>
+      </c>
+      <c r="I98" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="J98" s="21">
+        <v>0</v>
+      </c>
+      <c r="K98" s="21">
+        <v>0</v>
+      </c>
+      <c r="L98" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A99" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="B99" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C99" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D99" s="21" t="str">
+        <f>IF(PARAM!$J$35&lt;=0,"",IF(PARAM!$C$35="end plate","bo.bx","bo.fin"))</f>
+        <v>bo.bx</v>
+      </c>
+      <c r="E99" s="21"/>
+      <c r="F99" s="21">
+        <f>IF(PARAM!$C$35="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6))+PARAM!$G$44),-2*PARAM!$G$44),PARAM!$H$45-PARAM!$D$45)</f>
+        <v>-35</v>
+      </c>
+      <c r="G99" s="21">
+        <f>IF(PARAM!$C$35="end plate",-PARAM!$H$44/2,PARAM!$G$35/2+PARAM!$G$45)</f>
+        <v>-70</v>
+      </c>
+      <c r="H99" s="21">
+        <f>IF(PARAM!$C$35="end plate",-PARAM!$J$44*(PARAM!$K$44-1)/2,-PARAM!$J$45*(PARAM!$K$45-1)/2)</f>
+        <v>-70</v>
+      </c>
+      <c r="I99" s="21" t="str">
+        <f>IF(PARAM!$C$35="end plate","YZ","XZ")</f>
+        <v>YZ</v>
+      </c>
+      <c r="J99" s="21">
+        <v>0</v>
+      </c>
+      <c r="K99" s="21">
+        <v>0</v>
+      </c>
+      <c r="L99" s="21">
+        <v>0</v>
+      </c>
+      <c r="M99" s="21">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="N99" s="21">
+        <f>IF(PARAM!$C$35="end plate",PARAM!$H$44,0)</f>
+        <v>140</v>
+      </c>
+      <c r="O99" s="21">
+        <v>0</v>
+      </c>
+      <c r="P99" s="21">
+        <f>IF(PARAM!$C$35="end plate",1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q99" s="21">
+        <v>0</v>
+      </c>
+      <c r="R99" s="21">
+        <v>0</v>
+      </c>
+      <c r="S99" s="21">
+        <f>IF(PARAM!$C$35="end plate",PARAM!$J$44,PARAM!$J$45)</f>
+        <v>70</v>
+      </c>
+      <c r="T99" s="21">
+        <f>IF(PARAM!$C$35="end plate",PARAM!$K$44-1,PARAM!$K$45-1)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B100" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C100" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D100" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E100" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="F100" s="21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="103" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B103" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C103" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D103" s="21" t="str">
+        <f>IF(AND(PARAM!$J$36&gt;0,PARAM!$C$36="end plate"),"pl.bep","")</f>
+        <v/>
+      </c>
+      <c r="E103" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="F103" s="21">
+        <f>-(-PARAM!$G$44/2)</f>
+        <v>10</v>
+      </c>
+      <c r="G103" s="21">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="H103" s="21">
+        <v>0</v>
+      </c>
+      <c r="I103" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="J103" s="21">
+        <v>0</v>
+      </c>
+      <c r="K103" s="21">
+        <v>0</v>
+      </c>
+      <c r="L103" s="21">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="104" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B104" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C104" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D104" s="21" t="str">
+        <f>IF(AND(PARAM!$J$36&gt;0,PARAM!$C$36="end plate",NOT(PARAM!$C$6="H")),"pl.bep","")</f>
+        <v/>
+      </c>
+      <c r="E104" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="F104" s="21">
+        <f>-(-1.5*PARAM!$G$44)</f>
+        <v>30</v>
+      </c>
+      <c r="G104" s="21">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="H104" s="21">
+        <v>0</v>
+      </c>
+      <c r="I104" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="J104" s="21">
+        <v>0</v>
+      </c>
+      <c r="K104" s="21">
+        <v>0</v>
+      </c>
+      <c r="L104" s="21">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="105" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B105" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C105" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D105" s="21" t="str">
+        <f>IF(AND(PARAM!$J$36&gt;0,PARAM!$C$36="fin plate"),"pl.fin","")</f>
+        <v>pl.fin</v>
+      </c>
+      <c r="E105" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="F105" s="21">
+        <f>-(PARAM!$E$45/2-PARAM!$D$45)</f>
+        <v>-60</v>
+      </c>
+      <c r="G105" s="21">
+        <f>-(PARAM!$G$36/2+PARAM!$G$45/2)</f>
+        <v>-8.25</v>
+      </c>
+      <c r="H105" s="21">
+        <v>0</v>
+      </c>
+      <c r="I105" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="J105" s="21">
+        <v>0</v>
+      </c>
+      <c r="K105" s="21">
+        <v>0</v>
+      </c>
+      <c r="L105" s="21">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="106" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B106" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C106" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D106" s="21" t="str">
+        <f>IF(PARAM!$J$36&gt;0,"sc.bmb","")</f>
+        <v>sc.bmb</v>
+      </c>
+      <c r="E106" s="21"/>
+      <c r="F106" s="21">
+        <v>0</v>
+      </c>
+      <c r="G106" s="21">
+        <v>0</v>
+      </c>
+      <c r="H106" s="21">
+        <v>0</v>
+      </c>
+      <c r="I106" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="J106" s="21">
+        <v>0</v>
+      </c>
+      <c r="K106" s="21">
+        <v>0</v>
+      </c>
+      <c r="L106" s="21">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="107" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B107" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C107" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D107" s="21" t="str">
+        <f>IF(PARAM!$J$36&lt;=0,"",IF(PARAM!$C$36="end plate","bo.bx","bo.fin"))</f>
+        <v>bo.fin</v>
+      </c>
+      <c r="E107" s="21"/>
+      <c r="F107" s="21">
+        <f>-(IF(PARAM!$C$36="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6))+PARAM!$G$44),-2*PARAM!$G$44),PARAM!$H$45-PARAM!$D$45))</f>
+        <v>-50</v>
+      </c>
+      <c r="G107" s="21">
+        <f>-(IF(PARAM!$C$36="end plate",-PARAM!$H$44/2,PARAM!$G$36/2+PARAM!$G$45))</f>
+        <v>-13.25</v>
+      </c>
+      <c r="H107" s="21">
+        <f>IF(PARAM!$C$36="end plate",-PARAM!$J$44*(PARAM!$K$44-1)/2,-PARAM!$J$45*(PARAM!$K$45-1)/2)</f>
+        <v>-70</v>
+      </c>
+      <c r="I107" s="21" t="str">
+        <f>IF(PARAM!$C$36="end plate","YZ","XZ")</f>
+        <v>XZ</v>
+      </c>
+      <c r="J107" s="21">
+        <v>0</v>
+      </c>
+      <c r="K107" s="21">
+        <v>0</v>
+      </c>
+      <c r="L107" s="21">
+        <v>180</v>
+      </c>
+      <c r="M107" s="21">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="N107" s="21">
+        <f>-(IF(PARAM!$C$36="end plate",PARAM!$H$44,0))</f>
+        <v>0</v>
+      </c>
+      <c r="O107" s="21">
+        <v>0</v>
+      </c>
+      <c r="P107" s="21">
+        <f>IF(PARAM!$C$36="end plate",1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q107" s="21">
+        <v>0</v>
+      </c>
+      <c r="R107" s="21">
+        <v>0</v>
+      </c>
+      <c r="S107" s="21">
+        <f>IF(PARAM!$C$36="end plate",PARAM!$J$44,PARAM!$J$45)</f>
+        <v>70</v>
+      </c>
+      <c r="T107" s="21">
+        <f>IF(PARAM!$C$36="end plate",PARAM!$K$44-1,PARAM!$K$45-1)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B108" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C108" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D108" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E108" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="F108" s="21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="111" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B111" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C111" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="D111" s="21" t="str">
+        <f>IF(AND(PARAM!$J$37&gt;0,PARAM!$C$37="end plate"),"pl.bep","")</f>
+        <v/>
+      </c>
+      <c r="E111" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="F111" s="21">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G111" s="21">
+        <f>-PARAM!$G$44/2</f>
+        <v>-10</v>
+      </c>
+      <c r="H111" s="21">
+        <v>0</v>
+      </c>
+      <c r="I111" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="J111" s="21">
+        <v>0</v>
+      </c>
+      <c r="K111" s="21">
+        <v>0</v>
+      </c>
+      <c r="L111" s="21">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="112" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B112" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C112" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="D112" s="21" t="str">
+        <f>IF(AND(PARAM!$J$37&gt;0,PARAM!$C$37="end plate",NOT(PARAM!$C$6="H")),"pl.bep","")</f>
+        <v/>
+      </c>
+      <c r="E112" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="F112" s="21">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G112" s="21">
+        <f>-1.5*PARAM!$G$44</f>
+        <v>-30</v>
+      </c>
+      <c r="H112" s="21">
+        <v>0</v>
+      </c>
+      <c r="I112" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="J112" s="21">
+        <v>0</v>
+      </c>
+      <c r="K112" s="21">
+        <v>0</v>
+      </c>
+      <c r="L112" s="21">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="113" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B113" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C113" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="D113" s="21" t="str">
+        <f>IF(AND(PARAM!$J$37&gt;0,PARAM!$C$37="fin plate"),"pl.fin","")</f>
+        <v>pl.fin</v>
+      </c>
+      <c r="E113" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="F113" s="21">
+        <f>PARAM!$G$37/2+PARAM!$G$45/2</f>
+        <v>8.25</v>
+      </c>
+      <c r="G113" s="21">
+        <f>PARAM!$E$45/2-PARAM!$D$45</f>
+        <v>60</v>
+      </c>
+      <c r="H113" s="21">
+        <v>0</v>
+      </c>
+      <c r="I113" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="J113" s="21">
+        <v>0</v>
+      </c>
+      <c r="K113" s="21">
+        <v>0</v>
+      </c>
+      <c r="L113" s="21">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="114" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B114" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C114" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="D114" s="21" t="str">
+        <f>IF(PARAM!$J$37&gt;0,"sc.bmc","")</f>
+        <v>sc.bmc</v>
+      </c>
+      <c r="E114" s="21"/>
+      <c r="F114" s="21">
+        <v>0</v>
+      </c>
+      <c r="G114" s="21">
+        <v>0</v>
+      </c>
+      <c r="H114" s="21">
+        <v>0</v>
+      </c>
+      <c r="I114" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="J114" s="21">
+        <v>0</v>
+      </c>
+      <c r="K114" s="21">
+        <v>0</v>
+      </c>
+      <c r="L114" s="21">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="115" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B115" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C115" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="D115" s="21" t="str">
+        <f>IF(PARAM!$J$37&lt;=0,"",IF(PARAM!$C$37="end plate","bo.by","bo.fin"))</f>
+        <v>bo.fin</v>
+      </c>
+      <c r="E115" s="21"/>
+      <c r="F115" s="21">
+        <f>IF(PARAM!$C$37="end plate",-PARAM!$H$44/2,PARAM!$G$37/2+PARAM!$G$45)</f>
+        <v>13.25</v>
+      </c>
+      <c r="G115" s="21">
+        <f>IF(PARAM!$C$37="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6))+PARAM!$G$44),-2*PARAM!$G$44),PARAM!$H$45-PARAM!$D$45)</f>
+        <v>50</v>
+      </c>
+      <c r="H115" s="21">
+        <f>IF(PARAM!$C$37="end plate",-PARAM!$J$44*(PARAM!$K$44-1)/2,-PARAM!$J$45*(PARAM!$K$45-1)/2)</f>
+        <v>-70</v>
+      </c>
+      <c r="I115" s="21" t="str">
+        <f>IF(PARAM!$C$37="end plate","XZ","YZ")</f>
+        <v>YZ</v>
+      </c>
+      <c r="J115" s="21">
+        <v>0</v>
+      </c>
+      <c r="K115" s="21">
+        <v>0</v>
+      </c>
+      <c r="L115" s="21">
+        <v>180</v>
+      </c>
+      <c r="M115" s="21">
+        <f>IF(PARAM!$C$37="end plate",PARAM!$H$44,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N115" s="21">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="O115" s="21">
+        <v>0</v>
+      </c>
+      <c r="P115" s="21">
+        <f>IF(PARAM!$C$37="end plate",1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q115" s="21">
+        <v>0</v>
+      </c>
+      <c r="R115" s="21">
+        <v>0</v>
+      </c>
+      <c r="S115" s="21">
+        <f>IF(PARAM!$C$37="end plate",PARAM!$J$44,PARAM!$J$45)</f>
+        <v>70</v>
+      </c>
+      <c r="T115" s="21">
+        <f>IF(PARAM!$C$37="end plate",PARAM!$K$44-1,PARAM!$K$45-1)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B116" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C116" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="D116" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E116" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="F116" s="21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="12" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="119" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B119" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C119" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="D119" s="21" t="str">
+        <f>IF(AND(PARAM!$J$38&gt;0,PARAM!$C$38="end plate"),"pl.bep","")</f>
+        <v/>
+      </c>
+      <c r="E119" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="F119" s="21">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G119" s="21">
+        <f>-(-PARAM!$G$44/2)</f>
+        <v>10</v>
+      </c>
+      <c r="H119" s="21">
+        <v>0</v>
+      </c>
+      <c r="I119" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="J119" s="21">
+        <v>0</v>
+      </c>
+      <c r="K119" s="21">
+        <v>0</v>
+      </c>
+      <c r="L119" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B120" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C120" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="D120" s="21" t="str">
+        <f>IF(AND(PARAM!$J$38&gt;0,PARAM!$C$38="end plate",NOT(PARAM!$C$6="H")),"pl.bep","")</f>
+        <v/>
+      </c>
+      <c r="E120" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="F120" s="21">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G120" s="21">
+        <f>-(-1.5*PARAM!$G$44)</f>
+        <v>30</v>
+      </c>
+      <c r="H120" s="21">
+        <v>0</v>
+      </c>
+      <c r="I120" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="J120" s="21">
+        <v>0</v>
+      </c>
+      <c r="K120" s="21">
+        <v>0</v>
+      </c>
+      <c r="L120" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B121" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C121" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="D121" s="21" t="str">
+        <f>IF(AND(PARAM!$J$38&gt;0,PARAM!$C$38="fin plate"),"pl.fin","")</f>
+        <v/>
+      </c>
+      <c r="E121" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="F121" s="21">
+        <f>-(PARAM!$G$38/2+PARAM!$G$45/2)</f>
+        <v>-8.25</v>
+      </c>
+      <c r="G121" s="21">
+        <f>-(PARAM!$E$45/2-PARAM!$D$45)</f>
+        <v>-60</v>
+      </c>
+      <c r="H121" s="21">
+        <v>0</v>
+      </c>
+      <c r="I121" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="J121" s="21">
+        <v>0</v>
+      </c>
+      <c r="K121" s="21">
+        <v>0</v>
+      </c>
+      <c r="L121" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B122" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C122" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="D122" s="21" t="str">
+        <f>IF(PARAM!$J$38&gt;0,"sc.bmd","")</f>
+        <v/>
+      </c>
+      <c r="E122" s="21"/>
+      <c r="F122" s="21">
+        <v>0</v>
+      </c>
+      <c r="G122" s="21">
+        <v>0</v>
+      </c>
+      <c r="H122" s="21">
+        <v>0</v>
+      </c>
+      <c r="I122" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="J122" s="21">
+        <v>0</v>
+      </c>
+      <c r="K122" s="21">
+        <v>0</v>
+      </c>
+      <c r="L122" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B123" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C123" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="D123" s="21" t="str">
+        <f>IF(PARAM!$J$38&lt;=0,"",IF(PARAM!$C$38="end plate","bo.by","bo.fin"))</f>
+        <v/>
+      </c>
+      <c r="E123" s="21"/>
+      <c r="F123" s="21">
+        <f>-(IF(PARAM!$C$38="end plate",-PARAM!$H$44/2,PARAM!$G$38/2+PARAM!$G$45))</f>
+        <v>-13.25</v>
+      </c>
+      <c r="G123" s="21">
+        <f>-(IF(PARAM!$C$38="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6))+PARAM!$G$44),-2*PARAM!$G$44),PARAM!$H$45-PARAM!$D$45))</f>
+        <v>-50</v>
+      </c>
+      <c r="H123" s="21">
+        <f>IF(PARAM!$C$38="end plate",-PARAM!$J$44*(PARAM!$K$44-1)/2,-PARAM!$J$45*(PARAM!$K$45-1)/2)</f>
+        <v>-70</v>
+      </c>
+      <c r="I123" s="21" t="str">
+        <f>IF(PARAM!$C$38="end plate","XZ","YZ")</f>
+        <v>YZ</v>
+      </c>
+      <c r="J123" s="21">
+        <v>0</v>
+      </c>
+      <c r="K123" s="21">
+        <v>0</v>
+      </c>
+      <c r="L123" s="21">
+        <v>0</v>
+      </c>
+      <c r="M123" s="21">
+        <f>-(IF(PARAM!$C$38="end plate",PARAM!$H$44,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N123" s="21">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="O123" s="21">
+        <v>0</v>
+      </c>
+      <c r="P123" s="21">
+        <f>IF(PARAM!$C$38="end plate",1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q123" s="21">
+        <v>0</v>
+      </c>
+      <c r="R123" s="21">
+        <v>0</v>
+      </c>
+      <c r="S123" s="21">
+        <f>IF(PARAM!$C$38="end plate",PARAM!$J$44,PARAM!$J$45)</f>
+        <v>70</v>
+      </c>
+      <c r="T123" s="21">
+        <f>IF(PARAM!$C$38="end plate",PARAM!$K$44-1,PARAM!$K$45-1)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B124" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C124" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="D124" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E124" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="F124" s="21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="B127" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="C127" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="D127" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="E127" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="F127" s="21">
+        <f>(IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(PARAM!$C$35="end plate",IF(PARAM!$C$6="H",PARAM!$G$44,2*PARAM!$G$44),PARAM!$D$45)</f>
+        <v>170</v>
+      </c>
+      <c r="G127" s="21">
+        <v>0</v>
+      </c>
+      <c r="H127" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B128" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="C128" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="D128" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="E128" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="F128" s="21">
+        <f>-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(PARAM!$C$36="end plate",IF(PARAM!$C$6="H",PARAM!$G$44,2*PARAM!$G$44),PARAM!$D$45))</f>
+        <v>-160</v>
+      </c>
+      <c r="G128" s="21">
+        <v>0</v>
+      </c>
+      <c r="H128" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B129" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="C129" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="D129" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="E129" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="F129" s="21">
+        <v>0</v>
+      </c>
+      <c r="G129" s="21">
+        <f>(IF(MOD(PARAM!$J$6,180)=0,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2),PARAM!$E$6/2))+IF(PARAM!$C$37="end plate",IF(PARAM!$C$6="H",PARAM!$G$44,2*PARAM!$G$44),PARAM!$D$45)</f>
+        <v>15</v>
+      </c>
+      <c r="H129" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B130" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="C130" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="D130" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="E130" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="F130" s="21">
+        <v>0</v>
+      </c>
+      <c r="G130" s="21">
+        <f>-((IF(MOD(PARAM!$J$6,180)=0,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2),PARAM!$E$6/2))+IF(PARAM!$C$38="end plate",IF(PARAM!$C$6="H",PARAM!$G$44,2*PARAM!$G$44),PARAM!$D$45))</f>
+        <v>-15</v>
+      </c>
+      <c r="H130" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B132" s="20" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -5329,7 +7401,7 @@
         <v>7</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="E1" s="23" t="s">
         <v>9</v>
@@ -5343,7 +7415,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>124</v>
+        <v>184</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
@@ -5354,7 +7426,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>125</v>
+        <v>185</v>
       </c>
       <c r="B3" s="27">
         <v>100</v>
@@ -5377,7 +7449,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>126</v>
+        <v>186</v>
       </c>
       <c r="B4" s="29">
         <v>125</v>
@@ -5400,7 +7472,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
-        <v>127</v>
+        <v>187</v>
       </c>
       <c r="B5" s="27">
         <v>150</v>
@@ -5423,7 +7495,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
-        <v>128</v>
+        <v>188</v>
       </c>
       <c r="B6" s="29">
         <v>148</v>
@@ -5446,7 +7518,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>129</v>
+        <v>189</v>
       </c>
       <c r="B7" s="27">
         <v>150</v>
@@ -5469,7 +7541,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="B8" s="29">
         <v>198</v>
@@ -5492,7 +7564,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="B9" s="27">
         <v>200</v>
@@ -5515,7 +7587,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>132</v>
+        <v>192</v>
       </c>
       <c r="B10" s="29">
         <v>194</v>
@@ -5538,7 +7610,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
-        <v>133</v>
+        <v>193</v>
       </c>
       <c r="B11" s="27">
         <v>200</v>
@@ -5561,7 +7633,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>134</v>
+        <v>194</v>
       </c>
       <c r="B12" s="29">
         <v>200</v>
@@ -5584,7 +7656,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="B13" s="27">
         <v>248</v>
@@ -5607,7 +7679,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="B14" s="29">
         <v>250</v>
@@ -5630,7 +7702,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>137</v>
+        <v>197</v>
       </c>
       <c r="B15" s="27">
         <v>244</v>
@@ -5653,7 +7725,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>138</v>
+        <v>198</v>
       </c>
       <c r="B16" s="29">
         <v>250</v>
@@ -5676,7 +7748,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="B17" s="27">
         <v>250</v>
@@ -5699,7 +7771,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="B18" s="29">
         <v>298</v>
@@ -5722,7 +7794,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="B19" s="27">
         <v>300</v>
@@ -5745,7 +7817,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>142</v>
+        <v>201</v>
       </c>
       <c r="B20" s="29">
         <v>294</v>
@@ -5768,7 +7840,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
-        <v>143</v>
+        <v>202</v>
       </c>
       <c r="B21" s="27">
         <v>294</v>
@@ -5814,7 +7886,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
-        <v>144</v>
+        <v>203</v>
       </c>
       <c r="B23" s="27">
         <v>300</v>
@@ -5837,7 +7909,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
-        <v>145</v>
+        <v>204</v>
       </c>
       <c r="B24" s="29">
         <v>346</v>
@@ -5860,7 +7932,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
-        <v>146</v>
+        <v>205</v>
       </c>
       <c r="B25" s="27">
         <v>350</v>
@@ -5883,7 +7955,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>147</v>
+        <v>206</v>
       </c>
       <c r="B26" s="29">
         <v>340</v>
@@ -5906,7 +7978,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
-        <v>148</v>
+        <v>207</v>
       </c>
       <c r="B27" s="27">
         <v>344</v>
@@ -5929,7 +8001,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
-        <v>149</v>
+        <v>208</v>
       </c>
       <c r="B28" s="29">
         <v>350</v>
@@ -5952,7 +8024,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
-        <v>150</v>
+        <v>209</v>
       </c>
       <c r="B29" s="27">
         <v>396</v>
@@ -5975,7 +8047,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
-        <v>151</v>
+        <v>210</v>
       </c>
       <c r="B30" s="29">
         <v>400</v>
@@ -5998,7 +8070,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
-        <v>152</v>
+        <v>211</v>
       </c>
       <c r="B31" s="27">
         <v>390</v>
@@ -6021,7 +8093,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="28" t="s">
-        <v>153</v>
+        <v>212</v>
       </c>
       <c r="B32" s="29">
         <v>388</v>
@@ -6044,7 +8116,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="B33" s="27">
         <v>394</v>
@@ -6067,7 +8139,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="28" t="s">
-        <v>155</v>
+        <v>214</v>
       </c>
       <c r="B34" s="29">
         <v>400</v>
@@ -6090,7 +8162,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
-        <v>156</v>
+        <v>215</v>
       </c>
       <c r="B35" s="27">
         <v>400</v>
@@ -6113,7 +8185,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
-        <v>157</v>
+        <v>216</v>
       </c>
       <c r="B36" s="29">
         <v>414</v>
@@ -6136,7 +8208,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="26" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="B37" s="27">
         <v>428</v>
@@ -6159,7 +8231,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="28" t="s">
-        <v>159</v>
+        <v>218</v>
       </c>
       <c r="B38" s="29">
         <v>458</v>
@@ -6182,7 +8254,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
-        <v>160</v>
+        <v>219</v>
       </c>
       <c r="B39" s="27">
         <v>498</v>
@@ -6205,7 +8277,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="28" t="s">
-        <v>161</v>
+        <v>220</v>
       </c>
       <c r="B40" s="29">
         <v>446</v>
@@ -6228,7 +8300,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
-        <v>162</v>
+        <v>221</v>
       </c>
       <c r="B41" s="27">
         <v>450</v>
@@ -6251,7 +8323,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="28" t="s">
-        <v>163</v>
+        <v>222</v>
       </c>
       <c r="B42" s="29">
         <v>440</v>
@@ -6274,7 +8346,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
-        <v>164</v>
+        <v>223</v>
       </c>
       <c r="B43" s="27">
         <v>440</v>
@@ -6297,7 +8369,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="28" t="s">
-        <v>165</v>
+        <v>224</v>
       </c>
       <c r="B44" s="29">
         <v>496</v>
@@ -6320,7 +8392,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="26" t="s">
-        <v>166</v>
+        <v>225</v>
       </c>
       <c r="B45" s="27">
         <v>500</v>
@@ -6343,7 +8415,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="28" t="s">
-        <v>167</v>
+        <v>226</v>
       </c>
       <c r="B46" s="29">
         <v>482</v>
@@ -6366,7 +8438,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="26" t="s">
-        <v>168</v>
+        <v>227</v>
       </c>
       <c r="B47" s="27">
         <v>488</v>
@@ -6389,7 +8461,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="28" t="s">
-        <v>169</v>
+        <v>228</v>
       </c>
       <c r="B48" s="29">
         <v>596</v>
@@ -6412,7 +8484,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
-        <v>170</v>
+        <v>229</v>
       </c>
       <c r="B49" s="27">
         <v>600</v>
@@ -6435,7 +8507,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="28" t="s">
-        <v>171</v>
+        <v>230</v>
       </c>
       <c r="B50" s="29">
         <v>582</v>
@@ -6458,7 +8530,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="26" t="s">
-        <v>172</v>
+        <v>231</v>
       </c>
       <c r="B51" s="27">
         <v>588</v>
@@ -6481,7 +8553,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="28" t="s">
-        <v>173</v>
+        <v>232</v>
       </c>
       <c r="B52" s="29">
         <v>594</v>
@@ -6504,7 +8576,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="26" t="s">
-        <v>174</v>
+        <v>233</v>
       </c>
       <c r="B53" s="27">
         <v>692</v>
@@ -6527,7 +8599,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="28" t="s">
-        <v>175</v>
+        <v>234</v>
       </c>
       <c r="B54" s="29">
         <v>700</v>
@@ -6550,7 +8622,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
-        <v>176</v>
+        <v>235</v>
       </c>
       <c r="B55" s="27">
         <v>792</v>
@@ -6573,7 +8645,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="28" t="s">
-        <v>177</v>
+        <v>236</v>
       </c>
       <c r="B56" s="29">
         <v>800</v>
@@ -6596,7 +8668,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
-        <v>178</v>
+        <v>237</v>
       </c>
       <c r="B57" s="27">
         <v>890</v>
@@ -6619,7 +8691,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="28" t="s">
-        <v>179</v>
+        <v>238</v>
       </c>
       <c r="B58" s="29">
         <v>900</v>
@@ -6642,7 +8714,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>180</v>
+        <v>239</v>
       </c>
       <c r="B59" s="27">
         <v>912</v>
@@ -6665,7 +8737,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="28" t="s">
-        <v>181</v>
+        <v>240</v>
       </c>
       <c r="B60" s="29">
         <v>918</v>
@@ -6711,7 +8783,7 @@
         <v>7</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="E1" s="23" t="s">
         <v>9</v>
@@ -6725,7 +8797,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>124</v>
+        <v>184</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
@@ -6736,7 +8808,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>182</v>
+        <v>241</v>
       </c>
       <c r="B3" s="27">
         <v>20</v>
@@ -6759,7 +8831,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>183</v>
+        <v>242</v>
       </c>
       <c r="B4" s="29">
         <v>20</v>
@@ -6782,7 +8854,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
-        <v>184</v>
+        <v>243</v>
       </c>
       <c r="B5" s="27">
         <v>25</v>
@@ -6805,7 +8877,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
-        <v>185</v>
+        <v>244</v>
       </c>
       <c r="B6" s="29">
         <v>25</v>
@@ -6828,7 +8900,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>186</v>
+        <v>245</v>
       </c>
       <c r="B7" s="27">
         <v>30</v>
@@ -6851,7 +8923,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
-        <v>187</v>
+        <v>246</v>
       </c>
       <c r="B8" s="29">
         <v>30</v>
@@ -6874,7 +8946,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>188</v>
+        <v>247</v>
       </c>
       <c r="B9" s="27">
         <v>40</v>
@@ -6897,7 +8969,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>189</v>
+        <v>248</v>
       </c>
       <c r="B10" s="29">
         <v>40</v>
@@ -6920,7 +8992,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
-        <v>190</v>
+        <v>249</v>
       </c>
       <c r="B11" s="27">
         <v>50</v>
@@ -6943,7 +9015,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>191</v>
+        <v>250</v>
       </c>
       <c r="B12" s="29">
         <v>50</v>
@@ -6966,7 +9038,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
-        <v>192</v>
+        <v>251</v>
       </c>
       <c r="B13" s="27">
         <v>50</v>
@@ -6989,7 +9061,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>193</v>
+        <v>252</v>
       </c>
       <c r="B14" s="29">
         <v>60</v>
@@ -7012,7 +9084,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="B15" s="27">
         <v>60</v>
@@ -7035,7 +9107,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>195</v>
+        <v>254</v>
       </c>
       <c r="B16" s="29">
         <v>60</v>
@@ -7058,7 +9130,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>196</v>
+        <v>255</v>
       </c>
       <c r="B17" s="27">
         <v>75</v>
@@ -7081,7 +9153,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>197</v>
+        <v>256</v>
       </c>
       <c r="B18" s="29">
         <v>75</v>
@@ -7104,7 +9176,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
-        <v>198</v>
+        <v>257</v>
       </c>
       <c r="B19" s="27">
         <v>75</v>
@@ -7127,7 +9199,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>199</v>
+        <v>258</v>
       </c>
       <c r="B20" s="29">
         <v>75</v>
@@ -7150,7 +9222,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
-        <v>200</v>
+        <v>259</v>
       </c>
       <c r="B21" s="27">
         <v>80</v>
@@ -7173,7 +9245,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
-        <v>201</v>
+        <v>260</v>
       </c>
       <c r="B22" s="29">
         <v>80</v>
@@ -7196,7 +9268,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
-        <v>202</v>
+        <v>261</v>
       </c>
       <c r="B23" s="27">
         <v>80</v>
@@ -7219,7 +9291,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
-        <v>203</v>
+        <v>262</v>
       </c>
       <c r="B24" s="29">
         <v>90</v>
@@ -7242,7 +9314,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
-        <v>204</v>
+        <v>263</v>
       </c>
       <c r="B25" s="27">
         <v>90</v>
@@ -7265,7 +9337,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>205</v>
+        <v>264</v>
       </c>
       <c r="B26" s="29">
         <v>100</v>
@@ -7288,7 +9360,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
-        <v>206</v>
+        <v>265</v>
       </c>
       <c r="B27" s="27">
         <v>100</v>
@@ -7311,7 +9383,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
-        <v>207</v>
+        <v>266</v>
       </c>
       <c r="B28" s="29">
         <v>100</v>
@@ -7334,7 +9406,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
-        <v>208</v>
+        <v>267</v>
       </c>
       <c r="B29" s="27">
         <v>100</v>
@@ -7357,7 +9429,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
-        <v>209</v>
+        <v>268</v>
       </c>
       <c r="B30" s="29">
         <v>100</v>
@@ -7380,7 +9452,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
-        <v>210</v>
+        <v>269</v>
       </c>
       <c r="B31" s="27">
         <v>100</v>
@@ -7403,7 +9475,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="28" t="s">
-        <v>211</v>
+        <v>270</v>
       </c>
       <c r="B32" s="29">
         <v>100</v>
@@ -7426,7 +9498,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
-        <v>212</v>
+        <v>271</v>
       </c>
       <c r="B33" s="27">
         <v>125</v>
@@ -7449,7 +9521,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="28" t="s">
-        <v>213</v>
+        <v>272</v>
       </c>
       <c r="B34" s="29">
         <v>125</v>
@@ -7472,7 +9544,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
-        <v>214</v>
+        <v>273</v>
       </c>
       <c r="B35" s="27">
         <v>125</v>
@@ -7495,7 +9567,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
-        <v>215</v>
+        <v>274</v>
       </c>
       <c r="B36" s="29">
         <v>125</v>
@@ -7518,7 +9590,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="26" t="s">
-        <v>216</v>
+        <v>275</v>
       </c>
       <c r="B37" s="27">
         <v>125</v>
@@ -7541,7 +9613,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="28" t="s">
-        <v>217</v>
+        <v>276</v>
       </c>
       <c r="B38" s="29">
         <v>125</v>
@@ -7564,7 +9636,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
-        <v>218</v>
+        <v>277</v>
       </c>
       <c r="B39" s="27">
         <v>150</v>
@@ -7587,7 +9659,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="28" t="s">
-        <v>219</v>
+        <v>278</v>
       </c>
       <c r="B40" s="29">
         <v>150</v>
@@ -7610,7 +9682,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
-        <v>220</v>
+        <v>279</v>
       </c>
       <c r="B41" s="27">
         <v>150</v>
@@ -7633,7 +9705,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="28" t="s">
-        <v>221</v>
+        <v>280</v>
       </c>
       <c r="B42" s="29">
         <v>150</v>
@@ -7656,7 +9728,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
-        <v>222</v>
+        <v>281</v>
       </c>
       <c r="B43" s="27">
         <v>175</v>
@@ -7679,7 +9751,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="28" t="s">
-        <v>223</v>
+        <v>282</v>
       </c>
       <c r="B44" s="29">
         <v>175</v>
@@ -7702,7 +9774,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="26" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="B45" s="27">
         <v>175</v>
@@ -7725,7 +9797,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="28" t="s">
-        <v>225</v>
+        <v>284</v>
       </c>
       <c r="B46" s="29">
         <v>200</v>
@@ -7748,7 +9820,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="26" t="s">
-        <v>226</v>
+        <v>285</v>
       </c>
       <c r="B47" s="27">
         <v>200</v>
@@ -7771,7 +9843,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="28" t="s">
-        <v>227</v>
+        <v>286</v>
       </c>
       <c r="B48" s="29">
         <v>200</v>
@@ -7794,7 +9866,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
-        <v>228</v>
+        <v>287</v>
       </c>
       <c r="B49" s="27">
         <v>200</v>
@@ -7817,7 +9889,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="28" t="s">
-        <v>229</v>
+        <v>288</v>
       </c>
       <c r="B50" s="29">
         <v>200</v>
@@ -7840,7 +9912,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="26" t="s">
-        <v>230</v>
+        <v>289</v>
       </c>
       <c r="B51" s="27">
         <v>250</v>
@@ -7863,7 +9935,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="28" t="s">
-        <v>231</v>
+        <v>290</v>
       </c>
       <c r="B52" s="29">
         <v>250</v>
@@ -7886,7 +9958,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="26" t="s">
-        <v>232</v>
+        <v>291</v>
       </c>
       <c r="B53" s="27">
         <v>250</v>
@@ -7909,7 +9981,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="28" t="s">
-        <v>233</v>
+        <v>292</v>
       </c>
       <c r="B54" s="29">
         <v>250</v>
@@ -7932,7 +10004,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
-        <v>234</v>
+        <v>293</v>
       </c>
       <c r="B55" s="27">
         <v>250</v>
@@ -7955,7 +10027,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="28" t="s">
-        <v>235</v>
+        <v>294</v>
       </c>
       <c r="B56" s="29">
         <v>300</v>
@@ -7978,7 +10050,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
-        <v>236</v>
+        <v>295</v>
       </c>
       <c r="B57" s="27">
         <v>300</v>
@@ -8001,7 +10073,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="28" t="s">
-        <v>237</v>
+        <v>296</v>
       </c>
       <c r="B58" s="29">
         <v>300</v>
@@ -8024,7 +10096,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>238</v>
+        <v>297</v>
       </c>
       <c r="B59" s="27">
         <v>300</v>
@@ -8047,7 +10119,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="28" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="B60" s="29">
         <v>200</v>
@@ -8070,7 +10142,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
-        <v>240</v>
+        <v>299</v>
       </c>
       <c r="B61" s="27">
         <v>200</v>
@@ -8093,7 +10165,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="28" t="s">
-        <v>241</v>
+        <v>300</v>
       </c>
       <c r="B62" s="29">
         <v>200</v>
@@ -8116,7 +10188,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="26" t="s">
-        <v>242</v>
+        <v>301</v>
       </c>
       <c r="B63" s="27">
         <v>200</v>
@@ -8139,7 +10211,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="28" t="s">
-        <v>243</v>
+        <v>302</v>
       </c>
       <c r="B64" s="29">
         <v>250</v>
@@ -8162,7 +10234,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="26" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="B65" s="27">
         <v>250</v>
@@ -8185,7 +10257,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="28" t="s">
-        <v>245</v>
+        <v>304</v>
       </c>
       <c r="B66" s="29">
         <v>250</v>
@@ -8208,7 +10280,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="26" t="s">
-        <v>246</v>
+        <v>305</v>
       </c>
       <c r="B67" s="27">
         <v>250</v>
@@ -8231,7 +10303,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="28" t="s">
-        <v>247</v>
+        <v>306</v>
       </c>
       <c r="B68" s="29">
         <v>250</v>
@@ -8254,7 +10326,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="26" t="s">
-        <v>248</v>
+        <v>307</v>
       </c>
       <c r="B69" s="27">
         <v>250</v>
@@ -8277,7 +10349,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="28" t="s">
-        <v>249</v>
+        <v>308</v>
       </c>
       <c r="B70" s="29">
         <v>300</v>
@@ -8300,7 +10372,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="26" t="s">
-        <v>250</v>
+        <v>309</v>
       </c>
       <c r="B71" s="27">
         <v>300</v>
@@ -8323,7 +10395,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="28" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="B72" s="29">
         <v>300</v>
@@ -8346,7 +10418,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="26" t="s">
-        <v>252</v>
+        <v>311</v>
       </c>
       <c r="B73" s="27">
         <v>300</v>
@@ -8369,7 +10441,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="28" t="s">
-        <v>253</v>
+        <v>312</v>
       </c>
       <c r="B74" s="29">
         <v>300</v>
@@ -8392,7 +10464,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="26" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="B75" s="27">
         <v>300</v>
@@ -8415,7 +10487,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="28" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="B76" s="29">
         <v>300</v>
@@ -8438,7 +10510,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="26" t="s">
-        <v>256</v>
+        <v>315</v>
       </c>
       <c r="B77" s="27">
         <v>350</v>
@@ -8461,7 +10533,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="28" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="B78" s="29">
         <v>350</v>
@@ -8484,7 +10556,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="26" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="B79" s="27">
         <v>350</v>
@@ -8507,7 +10579,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="28" t="s">
-        <v>259</v>
+        <v>318</v>
       </c>
       <c r="B80" s="29">
         <v>350</v>
@@ -8530,7 +10602,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="26" t="s">
-        <v>260</v>
+        <v>319</v>
       </c>
       <c r="B81" s="27">
         <v>350</v>
@@ -8553,7 +10625,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="28" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="B82" s="29">
         <v>350</v>
@@ -8576,7 +10648,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="26" t="s">
-        <v>262</v>
+        <v>321</v>
       </c>
       <c r="B83" s="27">
         <v>400</v>
@@ -8599,7 +10671,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="28" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="B84" s="29">
         <v>400</v>
@@ -8622,7 +10694,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="26" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="B85" s="27">
         <v>400</v>
@@ -8645,7 +10717,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="28" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="B86" s="29">
         <v>400</v>
@@ -8668,7 +10740,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="26" t="s">
-        <v>266</v>
+        <v>325</v>
       </c>
       <c r="B87" s="27">
         <v>400</v>
@@ -8691,7 +10763,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="28" t="s">
-        <v>267</v>
+        <v>326</v>
       </c>
       <c r="B88" s="29">
         <v>400</v>
@@ -8714,7 +10786,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="26" t="s">
-        <v>268</v>
+        <v>327</v>
       </c>
       <c r="B89" s="27">
         <v>450</v>
@@ -8737,7 +10809,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="28" t="s">
-        <v>269</v>
+        <v>328</v>
       </c>
       <c r="B90" s="29">
         <v>450</v>
@@ -8760,7 +10832,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="26" t="s">
-        <v>270</v>
+        <v>329</v>
       </c>
       <c r="B91" s="27">
         <v>450</v>
@@ -8783,7 +10855,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="28" t="s">
-        <v>271</v>
+        <v>330</v>
       </c>
       <c r="B92" s="29">
         <v>450</v>
@@ -8806,7 +10878,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="26" t="s">
-        <v>272</v>
+        <v>331</v>
       </c>
       <c r="B93" s="27">
         <v>450</v>
@@ -8829,7 +10901,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="28" t="s">
-        <v>273</v>
+        <v>332</v>
       </c>
       <c r="B94" s="29">
         <v>450</v>
@@ -8852,7 +10924,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="26" t="s">
-        <v>274</v>
+        <v>333</v>
       </c>
       <c r="B95" s="27">
         <v>500</v>
@@ -8875,7 +10947,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="28" t="s">
-        <v>275</v>
+        <v>334</v>
       </c>
       <c r="B96" s="29">
         <v>500</v>
@@ -8898,7 +10970,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="26" t="s">
-        <v>276</v>
+        <v>335</v>
       </c>
       <c r="B97" s="27">
         <v>500</v>
@@ -8921,7 +10993,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="28" t="s">
-        <v>277</v>
+        <v>336</v>
       </c>
       <c r="B98" s="29">
         <v>500</v>
@@ -8944,7 +11016,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="26" t="s">
-        <v>278</v>
+        <v>337</v>
       </c>
       <c r="B99" s="27">
         <v>500</v>
@@ -8967,7 +11039,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="28" t="s">
-        <v>279</v>
+        <v>338</v>
       </c>
       <c r="B100" s="29">
         <v>500</v>
@@ -8990,7 +11062,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="26" t="s">
-        <v>280</v>
+        <v>339</v>
       </c>
       <c r="B101" s="27">
         <v>550</v>
@@ -9013,7 +11085,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="28" t="s">
-        <v>281</v>
+        <v>340</v>
       </c>
       <c r="B102" s="29">
         <v>550</v>
@@ -9036,7 +11108,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="26" t="s">
-        <v>282</v>
+        <v>341</v>
       </c>
       <c r="B103" s="27">
         <v>550</v>
@@ -9059,7 +11131,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="28" t="s">
-        <v>283</v>
+        <v>342</v>
       </c>
       <c r="B104" s="29">
         <v>550</v>
@@ -9082,7 +11154,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="26" t="s">
-        <v>284</v>
+        <v>343</v>
       </c>
       <c r="B105" s="27">
         <v>550</v>
@@ -9105,7 +11177,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="28" t="s">
-        <v>285</v>
+        <v>344</v>
       </c>
       <c r="B106" s="29">
         <v>600</v>
@@ -9128,7 +11200,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="26" t="s">
-        <v>286</v>
+        <v>345</v>
       </c>
       <c r="B107" s="27">
         <v>600</v>
@@ -9151,7 +11223,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="28" t="s">
-        <v>287</v>
+        <v>346</v>
       </c>
       <c r="B108" s="29">
         <v>600</v>
@@ -9174,7 +11246,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="26" t="s">
-        <v>288</v>
+        <v>347</v>
       </c>
       <c r="B109" s="27">
         <v>600</v>
@@ -9197,7 +11269,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="28" t="s">
-        <v>289</v>
+        <v>348</v>
       </c>
       <c r="B110" s="29">
         <v>600</v>
@@ -9220,7 +11292,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="26" t="s">
-        <v>290</v>
+        <v>349</v>
       </c>
       <c r="B111" s="27">
         <v>600</v>
@@ -9243,7 +11315,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="28" t="s">
-        <v>291</v>
+        <v>350</v>
       </c>
       <c r="B112" s="29">
         <v>600</v>
@@ -9266,7 +11338,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="26" t="s">
-        <v>292</v>
+        <v>351</v>
       </c>
       <c r="B113" s="27">
         <v>600</v>
@@ -9289,7 +11361,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="28" t="s">
-        <v>293</v>
+        <v>352</v>
       </c>
       <c r="B114" s="29">
         <v>600</v>
@@ -9312,7 +11384,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="26" t="s">
-        <v>294</v>
+        <v>353</v>
       </c>
       <c r="B115" s="27">
         <v>600</v>
@@ -9335,7 +11407,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="28" t="s">
-        <v>295</v>
+        <v>354</v>
       </c>
       <c r="B116" s="29">
         <v>600</v>
@@ -9358,7 +11430,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="26" t="s">
-        <v>296</v>
+        <v>355</v>
       </c>
       <c r="B117" s="27">
         <v>650</v>
@@ -9381,7 +11453,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="28" t="s">
-        <v>297</v>
+        <v>356</v>
       </c>
       <c r="B118" s="29">
         <v>650</v>
@@ -9404,7 +11476,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="26" t="s">
-        <v>298</v>
+        <v>357</v>
       </c>
       <c r="B119" s="27">
         <v>650</v>
@@ -9427,7 +11499,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="28" t="s">
-        <v>299</v>
+        <v>358</v>
       </c>
       <c r="B120" s="29">
         <v>650</v>
@@ -9450,7 +11522,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="26" t="s">
-        <v>300</v>
+        <v>359</v>
       </c>
       <c r="B121" s="27">
         <v>650</v>
@@ -9473,7 +11545,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="28" t="s">
-        <v>301</v>
+        <v>360</v>
       </c>
       <c r="B122" s="29">
         <v>650</v>
@@ -9496,7 +11568,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="26" t="s">
-        <v>302</v>
+        <v>361</v>
       </c>
       <c r="B123" s="27">
         <v>650</v>
@@ -9519,7 +11591,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="28" t="s">
-        <v>303</v>
+        <v>362</v>
       </c>
       <c r="B124" s="29">
         <v>650</v>
@@ -9542,7 +11614,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="26" t="s">
-        <v>304</v>
+        <v>363</v>
       </c>
       <c r="B125" s="27">
         <v>650</v>
@@ -9565,7 +11637,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="28" t="s">
-        <v>305</v>
+        <v>364</v>
       </c>
       <c r="B126" s="29">
         <v>650</v>
@@ -9588,7 +11660,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="26" t="s">
-        <v>306</v>
+        <v>365</v>
       </c>
       <c r="B127" s="27">
         <v>700</v>
@@ -9611,7 +11683,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="28" t="s">
-        <v>307</v>
+        <v>366</v>
       </c>
       <c r="B128" s="29">
         <v>700</v>
@@ -9634,7 +11706,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="26" t="s">
-        <v>308</v>
+        <v>367</v>
       </c>
       <c r="B129" s="27">
         <v>700</v>
@@ -9657,7 +11729,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="28" t="s">
-        <v>309</v>
+        <v>368</v>
       </c>
       <c r="B130" s="29">
         <v>700</v>
@@ -9680,7 +11752,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="26" t="s">
-        <v>310</v>
+        <v>369</v>
       </c>
       <c r="B131" s="27">
         <v>700</v>
@@ -9703,7 +11775,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="28" t="s">
-        <v>311</v>
+        <v>370</v>
       </c>
       <c r="B132" s="29">
         <v>700</v>
@@ -9726,7 +11798,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="26" t="s">
-        <v>312</v>
+        <v>371</v>
       </c>
       <c r="B133" s="27">
         <v>700</v>
@@ -9749,7 +11821,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="28" t="s">
-        <v>313</v>
+        <v>372</v>
       </c>
       <c r="B134" s="29">
         <v>700</v>
@@ -9772,7 +11844,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="26" t="s">
-        <v>314</v>
+        <v>373</v>
       </c>
       <c r="B135" s="27">
         <v>700</v>
@@ -9795,7 +11867,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="28" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="B136" s="29">
         <v>700</v>
@@ -9818,7 +11890,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="26" t="s">
-        <v>316</v>
+        <v>375</v>
       </c>
       <c r="B137" s="27">
         <v>750</v>
@@ -9841,7 +11913,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="28" t="s">
-        <v>317</v>
+        <v>376</v>
       </c>
       <c r="B138" s="29">
         <v>750</v>
@@ -9864,7 +11936,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="26" t="s">
-        <v>318</v>
+        <v>377</v>
       </c>
       <c r="B139" s="27">
         <v>750</v>
@@ -9887,7 +11959,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="28" t="s">
-        <v>319</v>
+        <v>378</v>
       </c>
       <c r="B140" s="29">
         <v>750</v>
@@ -9910,7 +11982,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="26" t="s">
-        <v>320</v>
+        <v>379</v>
       </c>
       <c r="B141" s="27">
         <v>750</v>
@@ -9933,7 +12005,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="28" t="s">
-        <v>321</v>
+        <v>380</v>
       </c>
       <c r="B142" s="29">
         <v>750</v>
@@ -9956,7 +12028,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="26" t="s">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="B143" s="27">
         <v>750</v>
@@ -9979,7 +12051,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="28" t="s">
-        <v>323</v>
+        <v>382</v>
       </c>
       <c r="B144" s="29">
         <v>750</v>
@@ -10002,7 +12074,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="26" t="s">
-        <v>324</v>
+        <v>383</v>
       </c>
       <c r="B145" s="27">
         <v>750</v>
@@ -10025,7 +12097,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="28" t="s">
-        <v>325</v>
+        <v>384</v>
       </c>
       <c r="B146" s="29">
         <v>800</v>
@@ -10048,7 +12120,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="26" t="s">
-        <v>326</v>
+        <v>385</v>
       </c>
       <c r="B147" s="27">
         <v>800</v>
@@ -10071,7 +12143,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="28" t="s">
-        <v>327</v>
+        <v>386</v>
       </c>
       <c r="B148" s="29">
         <v>800</v>
@@ -10094,7 +12166,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="26" t="s">
-        <v>328</v>
+        <v>387</v>
       </c>
       <c r="B149" s="27">
         <v>800</v>
@@ -10117,7 +12189,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="28" t="s">
-        <v>329</v>
+        <v>388</v>
       </c>
       <c r="B150" s="29">
         <v>800</v>
@@ -10140,7 +12212,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="26" t="s">
-        <v>330</v>
+        <v>389</v>
       </c>
       <c r="B151" s="27">
         <v>800</v>
@@ -10163,7 +12235,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="28" t="s">
-        <v>331</v>
+        <v>390</v>
       </c>
       <c r="B152" s="29">
         <v>800</v>
@@ -10186,7 +12258,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="26" t="s">
-        <v>332</v>
+        <v>391</v>
       </c>
       <c r="B153" s="27">
         <v>800</v>
@@ -10209,7 +12281,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="28" t="s">
-        <v>333</v>
+        <v>392</v>
       </c>
       <c r="B154" s="29">
         <v>800</v>

--- a/plate3d/PLATE3D_COLUMN.xlsx
+++ b/plate3d/PLATE3D_COLUMN.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="440">
   <si>
     <t>COLUMN</t>
   </si>
@@ -242,76 +242,112 @@
     <t>X+</t>
   </si>
   <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>H-300x150x6.5x9 r13</t>
+  </si>
+  <si>
+    <t>X-</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>Y+</t>
+  </si>
+  <si>
+    <t>Y-</t>
+  </si>
+  <si>
+    <t>Beams are H only: a tube has no web to bolt through. The direction is the world's, so Alpha decides whether a beam lands on a flange or on the web.</t>
+  </si>
+  <si>
+    <t>X faces</t>
+  </si>
+  <si>
+    <t>Y faces</t>
+  </si>
+  <si>
+    <t>beams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  5.  CONNECTION</t>
+  </si>
+  <si>
+    <t>declare them here, then name one against each beam above — end plate bolts through the column, fin plate through the beam web</t>
+  </si>
+  <si>
+    <t>what it is</t>
+  </si>
+  <si>
+    <t>setback</t>
+  </si>
+  <si>
+    <t>width</t>
+  </si>
+  <si>
+    <t>thick</t>
+  </si>
+  <si>
+    <t>gauge</t>
+  </si>
+  <si>
+    <t>edge</t>
+  </si>
+  <si>
+    <t>pitch</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
     <t>end plate</t>
   </si>
   <si>
-    <t>H-300x150x6.5x9 r13</t>
-  </si>
-  <si>
-    <t>X-</t>
+    <t>3 rows, through the col</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>4 rows, for a deep beam</t>
   </si>
   <si>
     <t>fin plate</t>
   </si>
   <si>
-    <t>Y+</t>
-  </si>
-  <si>
-    <t>Y-</t>
-  </si>
-  <si>
-    <t>Beams are H only: a tube has no web to bolt through. The direction is the world's, so Alpha decides whether a beam lands on a flange or on the web.</t>
-  </si>
-  <si>
-    <t>X faces</t>
-  </si>
-  <si>
-    <t>Y faces</t>
-  </si>
-  <si>
-    <t>beams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  5.  BEAM CONNECTION</t>
-  </si>
-  <si>
-    <t>end plate bolts through the column; fin plate is welded to it and bolts through the beam web — the one a tube can take</t>
-  </si>
-  <si>
-    <t>setback</t>
-  </si>
-  <si>
-    <t>width</t>
-  </si>
-  <si>
-    <t>height</t>
-  </si>
-  <si>
-    <t>thick</t>
-  </si>
-  <si>
-    <t>gauge</t>
-  </si>
-  <si>
-    <t>edge</t>
-  </si>
-  <si>
-    <t>pitch</t>
-  </si>
-  <si>
-    <t>count</t>
-  </si>
-  <si>
-    <t>Fin plate</t>
-  </si>
-  <si>
-    <t>Each height follows its own bolts. End plate gauge is across the beam web; fin plate gauge is out from the column face, setback the beam end short.</t>
-  </si>
-  <si>
-    <t>between flanges</t>
-  </si>
-  <si>
-    <t>bolt</t>
+    <t>3 bolts through the web</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>4 bolts through the web</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>2 bolts, a thinner fin</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>spare — set a Type</t>
+  </si>
+  <si>
+    <t>The mark is just a mark — Type says what it is. End plate gauge is across the beam web, fin plate gauge out from the column face.</t>
+  </si>
+  <si>
+    <t>marks</t>
+  </si>
+  <si>
+    <t>widest end plate</t>
+  </si>
+  <si>
+    <t>longest bolt</t>
   </si>
   <si>
     <t>flange passes</t>
@@ -593,37 +629,43 @@
     <t>sc.bmd</t>
   </si>
   <si>
-    <t>the beam end plate</t>
-  </si>
-  <si>
-    <t>pl.bep</t>
-  </si>
-  <si>
-    <t>the fin plate — welded to the column, not the beam</t>
-  </si>
-  <si>
-    <t>pl.fin</t>
-  </si>
-  <si>
-    <t>the fin plate bolt: through plate and web, and never through the column</t>
-  </si>
-  <si>
-    <t>bo.fin</t>
-  </si>
-  <si>
-    <t>through the flange on an H column, or through two plates on a tube</t>
-  </si>
-  <si>
-    <t>bo.bx</t>
-  </si>
-  <si>
-    <t>bo.by</t>
+    <t>One plate and one bolt for each beam, since each beam names its own connection. The plate is the end plate or the fin depending on that mark; MAX(1,..) keeps it defined when the mark is blank.</t>
+  </si>
+  <si>
+    <t>the end plate or the fin, whichever this beam's mark names</t>
+  </si>
+  <si>
+    <t>pl.cna</t>
+  </si>
+  <si>
+    <t>pl.cnb</t>
+  </si>
+  <si>
+    <t>pl.cnc</t>
+  </si>
+  <si>
+    <t>pl.cnd</t>
+  </si>
+  <si>
+    <t>its length follows the grip, and the grip follows the mark</t>
+  </si>
+  <si>
+    <t>bo.cna</t>
+  </si>
+  <si>
+    <t>bo.cnb</t>
+  </si>
+  <si>
+    <t>bo.cnc</t>
+  </si>
+  <si>
+    <t>bo.cnd</t>
   </si>
   <si>
     <t>Each beam is one module, written for BOTH details at once. Its origin is the START FACE OF THE BEAM, which is the point BASE holds, so every other row is a distance measured back from there.</t>
   </si>
   <si>
-    <t>beam X+  —  end plate</t>
+    <t>beam X+  —  C1, end plate</t>
   </si>
   <si>
     <t>end plate, on the beam end</t>
@@ -644,13 +686,13 @@
     <t>two across the web on an end plate, one line on a fin</t>
   </si>
   <si>
-    <t>beam X-  —  fin plate</t>
+    <t>beam X-  —  C3, fin plate</t>
   </si>
   <si>
     <t>md.bmb</t>
   </si>
   <si>
-    <t>beam Y+  —  fin plate</t>
+    <t>beam Y+  —  C3, fin plate</t>
   </si>
   <si>
     <t>md.bmc</t>
@@ -1955,7 +1997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:L60"/>
+  <dimension ref="B1:K64"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -2785,7 +2827,10 @@
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
     </row>
-    <row r="43" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C43" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="D43" s="5" t="s">
         <v>86</v>
       </c>
@@ -2813,266 +2858,317 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D44" s="14">
-        <v>0</v>
-      </c>
-      <c r="E44" s="7">
+        <v>74</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0</v>
+      </c>
+      <c r="F44" s="8">
         <v>230</v>
       </c>
-      <c r="F44" s="17">
-        <f>PARAM!$J$44*(PARAM!$K$44-1)+2*PARAM!$I$44</f>
-        <v>230</v>
-      </c>
-      <c r="G44" s="7">
+      <c r="G44" s="8">
         <v>20</v>
       </c>
-      <c r="H44" s="7">
+      <c r="H44" s="8">
         <v>140</v>
       </c>
-      <c r="I44" s="7">
+      <c r="I44" s="8">
         <v>45</v>
       </c>
-      <c r="J44" s="7">
+      <c r="J44" s="8">
         <v>70</v>
       </c>
-      <c r="K44" s="7">
+      <c r="K44" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="D45" s="7">
+      <c r="D45" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0</v>
+      </c>
+      <c r="F45" s="8">
+        <v>230</v>
+      </c>
+      <c r="G45" s="8">
+        <v>20</v>
+      </c>
+      <c r="H45" s="8">
+        <v>140</v>
+      </c>
+      <c r="I45" s="8">
+        <v>45</v>
+      </c>
+      <c r="J45" s="8">
+        <v>70</v>
+      </c>
+      <c r="K45" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B46" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E46" s="8">
         <v>10</v>
       </c>
-      <c r="E45" s="7">
+      <c r="F46" s="8">
         <v>140</v>
       </c>
-      <c r="F45" s="17">
-        <f>PARAM!$J$45*(PARAM!$K$45-1)+2*PARAM!$I$45</f>
-        <v>230</v>
-      </c>
-      <c r="G45" s="7">
+      <c r="G46" s="8">
         <v>10</v>
       </c>
-      <c r="H45" s="7">
+      <c r="H46" s="8">
         <v>60</v>
       </c>
-      <c r="I45" s="7">
+      <c r="I46" s="8">
         <v>45</v>
       </c>
-      <c r="J45" s="7">
+      <c r="J46" s="8">
         <v>70</v>
       </c>
-      <c r="K45" s="7">
+      <c r="K46" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B46" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="12"/>
-      <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B47" s="11" t="s">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B47" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D47" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="E47" s="8">
+        <v>10</v>
+      </c>
+      <c r="F47" s="8">
+        <v>140</v>
+      </c>
+      <c r="G47" s="8">
+        <v>10</v>
+      </c>
+      <c r="H47" s="8">
+        <v>60</v>
+      </c>
+      <c r="I47" s="8">
+        <v>45</v>
+      </c>
+      <c r="J47" s="8">
+        <v>70</v>
+      </c>
+      <c r="K47" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B48" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="E48" s="8">
+        <v>10</v>
+      </c>
+      <c r="F48" s="8">
+        <v>120</v>
+      </c>
+      <c r="G48" s="8">
+        <v>9</v>
+      </c>
+      <c r="H48" s="8">
+        <v>55</v>
+      </c>
+      <c r="I48" s="8">
+        <v>40</v>
+      </c>
+      <c r="J48" s="8">
+        <v>60</v>
+      </c>
+      <c r="K48" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B49" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C49" s="7"/>
+      <c r="D49" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0</v>
+      </c>
+      <c r="F49" s="8">
+        <v>0</v>
+      </c>
+      <c r="G49" s="8">
+        <v>0</v>
+      </c>
+      <c r="H49" s="8">
+        <v>0</v>
+      </c>
+      <c r="I49" s="8">
+        <v>0</v>
+      </c>
+      <c r="J49" s="8">
+        <v>0</v>
+      </c>
+      <c r="K49" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B50" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="12"/>
+      <c r="J50" s="12"/>
+      <c r="K50" s="12"/>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B51" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D47" s="11" t="str">
-        <f>IF(PARAM!$C$6="H",IF(PARAM!$H$44&gt;=PARAM!$G$35+3*PARAM!$E$24,"ok","too tight for the web"),IF(PARAM!$H$44&gt;=PARAM!$F$35+3*PARAM!$E$24,"ok","must clear the beam on a tube"))</f>
-        <v>ok</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="F47" s="11" t="str">
-        <f>IF(PARAM!$E$44/2-PARAM!$H$44/2&gt;=1.5*PARAM!$E$24,"ok","plate too narrow")</f>
-        <v>ok</v>
-      </c>
-      <c r="G47" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="H47" s="11" t="str">
-        <f>IF(PARAM!$C$6="H",IF(PARAM!$E$44&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,PARAM!$E$44&amp;" ≤ "&amp;(PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6),"hits the flanges on a web face"),"n/a")</f>
-        <v>230 ≤ 234</v>
-      </c>
-      <c r="I47" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="J47" s="11" t="str">
-        <f>"M"&amp;PARAM!$E$24&amp;" L"&amp;IF(PARAM!$C$6="H",CEILING(MAX(IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6),IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6))+PARAM!$G$44+1.1*PARAM!$E$24,5),CEILING(2*PARAM!$G$44+1.1*PARAM!$E$24,5))</f>
+      <c r="C51" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D51" s="11" t="str">
+        <f>IF(COUNTIF(PARAM!$B$44:$B$49,PARAM!$C$35)+COUNTIF(PARAM!$B$44:$B$49,PARAM!$C$36)+COUNTIF(PARAM!$B$44:$B$49,PARAM!$C$37)+COUNTIF(PARAM!$B$44:$B$49,PARAM!$C$38)=4,"all 4 beams found theirs","a beam names a mark that is not in the list")</f>
+        <v>all 4 beams found theirs</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="F51" s="11" t="str">
+        <f>IF(NOT(PARAM!$C$6="H"),"n/a",IF(SUMPRODUCT(MAX((PARAM!$C$44:$C$49="end plate")*(PARAM!$F$44:$F$49)))&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"fits between the flanges","hits the flanges on a web face"))</f>
+        <v>fits between the flanges</v>
+      </c>
+      <c r="G51" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H51" s="11" t="str">
+        <f>"M"&amp;PARAM!$E$24&amp;" L"&amp;MAX(IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0))+1.1*PARAM!$E$24,5),IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$35+1.1*PARAM!$E$24,5),0)),IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0))+1.1*PARAM!$E$24,5),IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$36+1.1*PARAM!$E$24,5),0)),IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0))+1.1*PARAM!$E$24,5),IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$37+1.1*PARAM!$E$24,5),0)),IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0))+1.1*PARAM!$E$24,5),IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$38+1.1*PARAM!$E$24,5),0)))</f>
         <v>M16 L55</v>
       </c>
-      <c r="K47" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="L47" s="11" t="str">
+      <c r="I51" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="J51" s="11" t="str">
         <f>IF(NOT(PARAM!$C$6="H"),"n/a",IF(MOD(PARAM!$J$6,180)=0,IF(MAX(PARAM!$F$37,PARAM!$F$38)&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"ok","strip the beam flange"),IF(MAX(PARAM!$F$35,PARAM!$F$36)&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"ok","strip the beam flange")))</f>
         <v>ok</v>
       </c>
     </row>
-    <row r="49" ht="20" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B49" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-    </row>
-    <row r="50" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D50" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="H50" s="5" t="s">
+    <row r="53" ht="20" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B53" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+    </row>
+    <row r="54" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D54" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="H54" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B51" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D51" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="E51" s="8">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B55" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D55" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="E55" s="8">
         <v>145.5</v>
       </c>
-      <c r="F51" s="8">
+      <c r="F55" s="8">
         <v>145</v>
       </c>
-      <c r="G51" s="8">
+      <c r="G55" s="8">
         <v>270</v>
       </c>
-      <c r="H51" s="8">
+      <c r="H55" s="8">
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B52" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D52" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="E52" s="8">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B56" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D56" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="E56" s="8">
         <v>-145.5</v>
       </c>
-      <c r="F52" s="8">
+      <c r="F56" s="8">
         <v>145</v>
       </c>
-      <c r="G52" s="8">
+      <c r="G56" s="8">
         <v>270</v>
       </c>
-      <c r="H52" s="8">
+      <c r="H56" s="8">
         <v>12</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B53" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="D53" s="20"/>
-      <c r="E53" s="8">
-        <v>0</v>
-      </c>
-      <c r="F53" s="8">
-        <v>0</v>
-      </c>
-      <c r="G53" s="8">
-        <v>0</v>
-      </c>
-      <c r="H53" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B54" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D54" s="20"/>
-      <c r="E54" s="8">
-        <v>0</v>
-      </c>
-      <c r="F54" s="8">
-        <v>0</v>
-      </c>
-      <c r="G54" s="8">
-        <v>0</v>
-      </c>
-      <c r="H54" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B55" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="D55" s="20"/>
-      <c r="E55" s="8">
-        <v>0</v>
-      </c>
-      <c r="F55" s="8">
-        <v>0</v>
-      </c>
-      <c r="G55" s="8">
-        <v>0</v>
-      </c>
-      <c r="H55" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B56" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="D56" s="20"/>
-      <c r="E56" s="8">
-        <v>0</v>
-      </c>
-      <c r="F56" s="8">
-        <v>0</v>
-      </c>
-      <c r="G56" s="8">
-        <v>0</v>
-      </c>
-      <c r="H56" s="8">
-        <v>0</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B57" s="16" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D57" s="20"/>
       <c r="E57" s="8">
@@ -3090,7 +3186,7 @@
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B58" s="16" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D58" s="20"/>
       <c r="E58" s="8">
@@ -3106,42 +3202,114 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B59" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="12"/>
-      <c r="H59" s="12"/>
-      <c r="I59" s="12"/>
-      <c r="J59" s="12"/>
-      <c r="K59" s="12"/>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B59" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D59" s="20"/>
+      <c r="E59" s="8">
+        <v>0</v>
+      </c>
+      <c r="F59" s="8">
+        <v>0</v>
+      </c>
+      <c r="G59" s="8">
+        <v>0</v>
+      </c>
+      <c r="H59" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B60" s="11" t="s">
+      <c r="B60" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D60" s="20"/>
+      <c r="E60" s="8">
+        <v>0</v>
+      </c>
+      <c r="F60" s="8">
+        <v>0</v>
+      </c>
+      <c r="G60" s="8">
+        <v>0</v>
+      </c>
+      <c r="H60" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B61" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="D61" s="20"/>
+      <c r="E61" s="8">
+        <v>0</v>
+      </c>
+      <c r="F61" s="8">
+        <v>0</v>
+      </c>
+      <c r="G61" s="8">
+        <v>0</v>
+      </c>
+      <c r="H61" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B62" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D62" s="20"/>
+      <c r="E62" s="8">
+        <v>0</v>
+      </c>
+      <c r="F62" s="8">
+        <v>0</v>
+      </c>
+      <c r="G62" s="8">
+        <v>0</v>
+      </c>
+      <c r="H62" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B63" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
+      <c r="I63" s="12"/>
+      <c r="J63" s="12"/>
+      <c r="K63" s="12"/>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B64" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C60" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="D60" s="11" t="str">
-        <f>IF(PARAM!$C$6="H",IF($H$51&gt;0,2,0)+IF($H$52&gt;0,2,0)+IF($H$53&gt;0,2,0)+IF($H$54&gt;0,2,0)+IF($H$55&gt;0,2,0)+IF($H$56&gt;0,2,0)+IF($H$57&gt;0,2,0)+IF($H$58&gt;0,2,0),0)&amp;" of 16"</f>
+      <c r="C64" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D64" s="11" t="str">
+        <f>IF(PARAM!$C$6="H",IF($H$55&gt;0,2,0)+IF($H$56&gt;0,2,0)+IF($H$57&gt;0,2,0)+IF($H$58&gt;0,2,0)+IF($H$59&gt;0,2,0)+IF($H$60&gt;0,2,0)+IF($H$61&gt;0,2,0)+IF($H$62&gt;0,2,0),0)&amp;" of 16"</f>
         <v>4 of 16</v>
       </c>
-      <c r="E60" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="F60" s="11" t="str">
-        <f>IF(NOT(PARAM!$C$6="H"),"n/a",IF(MAX($F$51:$F$58)&gt;(PARAM!$F$6-PARAM!$G$6)/2,"too wide",IF(MAX($G$51:$G$58)&gt;PARAM!$E$6-2*PARAM!$H$6,"too deep","ok")))</f>
+      <c r="E64" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F64" s="11" t="str">
+        <f>IF(NOT(PARAM!$C$6="H"),"n/a",IF(MAX($F$55:$F$62)&gt;(PARAM!$F$6-PARAM!$G$6)/2,"too wide",IF(MAX($G$55:$G$62)&gt;PARAM!$E$6-2*PARAM!$H$6,"too deep","ok")))</f>
         <v>ok</v>
       </c>
-      <c r="G60" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="H60" s="11" t="str">
+      <c r="G64" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="H64" s="11" t="str">
         <f>ROUND((PARAM!$E$35-PARAM!$H$35)/2,1)&amp;" / "&amp;ROUND((PARAM!$E$36-PARAM!$H$36)/2,1)&amp;" / "&amp;ROUND((PARAM!$E$37-PARAM!$H$37)/2,1)&amp;" / "&amp;ROUND((PARAM!$E$38-PARAM!$H$38)/2,1)</f>
         <v>145.5 / 145.5 / 145.5 / 145.5</v>
       </c>
@@ -3159,9 +3327,9 @@
     <mergeCell ref="C33:K33"/>
     <mergeCell ref="B39:K39"/>
     <mergeCell ref="C42:K42"/>
-    <mergeCell ref="B46:K46"/>
-    <mergeCell ref="C49:K49"/>
-    <mergeCell ref="B59:K59"/>
+    <mergeCell ref="B50:K50"/>
+    <mergeCell ref="C53:K53"/>
+    <mergeCell ref="B63:K63"/>
   </mergeCells>
   <conditionalFormatting sqref="B15:K17">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -3193,13 +3361,16 @@
       <formula>$C$6="H"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B51:K58">
+  <conditionalFormatting sqref="B55:K62">
     <cfRule type="expression" dxfId="6" priority="1">
       <formula>$C$6&lt;&gt;"H"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
-    <dataValidation type="list" showErrorMessage="1" error="end plate bolts through the column; fin plate bolts through the beam web." sqref="C35:C38">
+  <dataValidations count="7">
+    <dataValidation type="list" showErrorMessage="1" error="Name one of the connections declared in chapter 5." sqref="C35:C38">
+      <formula1>PARAM!$B$44:$B$49</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="end plate bolts through the column; fin plate bolts through the beam web." sqref="C44:C49">
       <formula1>"end plate,fin plate"</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="H for an I section, R for a square tube." sqref="C6">
@@ -3225,7 +3396,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T154"/>
+  <dimension ref="A1:T159"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -3237,30 +3408,30 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="21" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -3268,10 +3439,10 @@
         <v>17</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D6" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3286,7 +3457,7 @@
         <v>H</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H6" s="22">
         <f>PARAM!$E$6</f>
@@ -3322,10 +3493,10 @@
         <v>18</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="D7" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3340,7 +3511,7 @@
         <v>H</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H7" s="22">
         <f>PARAM!$E$6</f>
@@ -3376,10 +3547,10 @@
         <v>19</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="D8" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3394,7 +3565,7 @@
         <v>H</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H8" s="22">
         <f>PARAM!$E$6</f>
@@ -3427,23 +3598,23 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D11" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3454,10 +3625,10 @@
         <v>12</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H11" s="22">
         <f>IF(PARAM!$C$6="H",PARAM!$E$15,PARAM!$E$18)</f>
@@ -3470,13 +3641,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="D12" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3487,10 +3658,10 @@
         <v>10</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H12" s="22">
         <f>PARAM!$E$16</f>
@@ -3503,13 +3674,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D13" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3520,10 +3691,10 @@
         <v>10</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H13" s="22">
         <f>PARAM!$E$17</f>
@@ -3536,13 +3707,13 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="D14" s="22" t="str">
         <f>PARAM!$G$24</f>
@@ -3574,13 +3745,13 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="D15" s="22" t="str">
         <f>PARAM!$G$24</f>
@@ -3612,286 +3783,286 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="D19" s="22" t="str">
         <f>PARAM!$C$8</f>
         <v>SS275</v>
       </c>
       <c r="E19" s="22">
-        <f>MAX(1,PARAM!$H$51)</f>
+        <f>MAX(1,PARAM!$H$55)</f>
         <v>12</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H19" s="22">
-        <f>MAX(1,PARAM!$G$51)</f>
+        <f>MAX(1,PARAM!$G$55)</f>
         <v>270</v>
       </c>
       <c r="I19" s="22">
-        <f>MAX(1,PARAM!$F$51)</f>
+        <f>MAX(1,PARAM!$F$55)</f>
         <v>145</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="21" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D20" s="22" t="str">
         <f>PARAM!$C$8</f>
         <v>SS275</v>
       </c>
       <c r="E20" s="22">
-        <f>MAX(1,PARAM!$H$52)</f>
+        <f>MAX(1,PARAM!$H$56)</f>
         <v>12</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H20" s="22">
-        <f>MAX(1,PARAM!$G$52)</f>
+        <f>MAX(1,PARAM!$G$56)</f>
         <v>270</v>
       </c>
       <c r="I20" s="22">
-        <f>MAX(1,PARAM!$F$52)</f>
+        <f>MAX(1,PARAM!$F$56)</f>
         <v>145</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="21" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="D21" s="22" t="str">
         <f>PARAM!$C$8</f>
         <v>SS275</v>
       </c>
       <c r="E21" s="22">
-        <f>MAX(1,PARAM!$H$53)</f>
+        <f>MAX(1,PARAM!$H$57)</f>
         <v>1</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H21" s="22">
-        <f>MAX(1,PARAM!$G$53)</f>
+        <f>MAX(1,PARAM!$G$57)</f>
         <v>1</v>
       </c>
       <c r="I21" s="22">
-        <f>MAX(1,PARAM!$F$53)</f>
+        <f>MAX(1,PARAM!$F$57)</f>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="21" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="D22" s="22" t="str">
         <f>PARAM!$C$8</f>
         <v>SS275</v>
       </c>
       <c r="E22" s="22">
-        <f>MAX(1,PARAM!$H$54)</f>
+        <f>MAX(1,PARAM!$H$58)</f>
         <v>1</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H22" s="22">
-        <f>MAX(1,PARAM!$G$54)</f>
+        <f>MAX(1,PARAM!$G$58)</f>
         <v>1</v>
       </c>
       <c r="I22" s="22">
-        <f>MAX(1,PARAM!$F$54)</f>
+        <f>MAX(1,PARAM!$F$58)</f>
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="21" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="D23" s="22" t="str">
         <f>PARAM!$C$8</f>
         <v>SS275</v>
       </c>
       <c r="E23" s="22">
-        <f>MAX(1,PARAM!$H$55)</f>
+        <f>MAX(1,PARAM!$H$59)</f>
         <v>1</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H23" s="22">
-        <f>MAX(1,PARAM!$G$55)</f>
+        <f>MAX(1,PARAM!$G$59)</f>
         <v>1</v>
       </c>
       <c r="I23" s="22">
-        <f>MAX(1,PARAM!$F$55)</f>
+        <f>MAX(1,PARAM!$F$59)</f>
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="21" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="D24" s="22" t="str">
         <f>PARAM!$C$8</f>
         <v>SS275</v>
       </c>
       <c r="E24" s="22">
-        <f>MAX(1,PARAM!$H$56)</f>
+        <f>MAX(1,PARAM!$H$60)</f>
         <v>1</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H24" s="22">
-        <f>MAX(1,PARAM!$G$56)</f>
+        <f>MAX(1,PARAM!$G$60)</f>
         <v>1</v>
       </c>
       <c r="I24" s="22">
-        <f>MAX(1,PARAM!$F$56)</f>
+        <f>MAX(1,PARAM!$F$60)</f>
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="21" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="D25" s="22" t="str">
         <f>PARAM!$C$8</f>
         <v>SS275</v>
       </c>
       <c r="E25" s="22">
-        <f>MAX(1,PARAM!$H$57)</f>
+        <f>MAX(1,PARAM!$H$61)</f>
         <v>1</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="G25" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H25" s="22">
-        <f>MAX(1,PARAM!$G$57)</f>
+        <f>MAX(1,PARAM!$G$61)</f>
         <v>1</v>
       </c>
       <c r="I25" s="22">
-        <f>MAX(1,PARAM!$F$57)</f>
+        <f>MAX(1,PARAM!$F$61)</f>
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="21" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D26" s="22" t="str">
         <f>PARAM!$C$8</f>
         <v>SS275</v>
       </c>
       <c r="E26" s="22">
-        <f>MAX(1,PARAM!$H$58)</f>
+        <f>MAX(1,PARAM!$H$62)</f>
         <v>1</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H26" s="22">
-        <f>MAX(1,PARAM!$G$58)</f>
+        <f>MAX(1,PARAM!$G$62)</f>
         <v>1</v>
       </c>
       <c r="I26" s="22">
-        <f>MAX(1,PARAM!$F$58)</f>
+        <f>MAX(1,PARAM!$F$62)</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="D30" s="22" t="str">
         <f>IF(PARAM!$E$7&gt;0,"sc.c1","")</f>
@@ -3908,7 +4079,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J30" s="22">
         <v>0</v>
@@ -3922,27 +4093,27 @@
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D32" s="22" t="str">
         <f>"sc.c2"</f>
@@ -3959,7 +4130,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J32" s="22">
         <v>0</v>
@@ -3973,27 +4144,27 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="D34" s="22" t="str">
         <f>IF(PARAM!$I$7&gt;0,"sc.c3","")</f>
@@ -4010,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J34" s="22">
         <v>0</v>
@@ -4024,47 +4195,47 @@
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D38" s="22" t="str">
         <f>IF(PARAM!$E$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F38" s="22">
         <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$15/2)),0)</f>
@@ -4084,17 +4255,17 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D39" s="22" t="str">
         <f>IF(PARAM!$E$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F39" s="22">
         <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$15/2)),0)</f>
@@ -4114,20 +4285,20 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D40" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F40" s="22">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -4141,22 +4312,22 @@
         <v>0</v>
       </c>
       <c r="I40" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B41" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D41" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F41" s="22">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -4170,22 +4341,22 @@
         <v>0</v>
       </c>
       <c r="I41" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D42" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F42" s="22">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -4199,22 +4370,22 @@
         <v>0</v>
       </c>
       <c r="I42" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D43" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F43" s="22">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -4228,25 +4399,25 @@
         <v>0</v>
       </c>
       <c r="I43" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D44" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F44" s="22">
         <v>0</v>
@@ -4259,22 +4430,22 @@
         <v>0</v>
       </c>
       <c r="I44" s="22" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B45" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D45" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F45" s="22">
         <v>0</v>
@@ -4287,18 +4458,18 @@
         <v>0</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D46" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4318,7 +4489,7 @@
         <v>35</v>
       </c>
       <c r="I46" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J46" s="22">
         <v>0</v>
@@ -4360,10 +4531,10 @@
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B47" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D47" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4383,7 +4554,7 @@
         <v>35</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J47" s="22">
         <v>0</v>
@@ -4425,10 +4596,10 @@
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B48" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D48" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4448,7 +4619,7 @@
         <v>-35</v>
       </c>
       <c r="I48" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J48" s="22">
         <v>0</v>
@@ -4490,10 +4661,10 @@
     </row>
     <row r="49" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B49" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D49" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4513,7 +4684,7 @@
         <v>-35</v>
       </c>
       <c r="I49" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J49" s="22">
         <v>0</v>
@@ -4555,10 +4726,10 @@
     </row>
     <row r="50" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B50" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D50" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4578,7 +4749,7 @@
         <v>35</v>
       </c>
       <c r="I50" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J50" s="22">
         <v>0</v>
@@ -4620,10 +4791,10 @@
     </row>
     <row r="51" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B51" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D51" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4643,7 +4814,7 @@
         <v>35</v>
       </c>
       <c r="I51" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J51" s="22">
         <v>0</v>
@@ -4685,10 +4856,10 @@
     </row>
     <row r="52" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B52" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D52" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4708,7 +4879,7 @@
         <v>-35</v>
       </c>
       <c r="I52" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J52" s="22">
         <v>0</v>
@@ -4750,10 +4921,10 @@
     </row>
     <row r="53" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B53" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D53" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4773,7 +4944,7 @@
         <v>-35</v>
       </c>
       <c r="I53" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J53" s="22">
         <v>0</v>
@@ -4815,13 +4986,13 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D54" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -4841,7 +5012,7 @@
         <v>-10</v>
       </c>
       <c r="I54" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J54" s="22">
         <v>0</v>
@@ -4869,10 +5040,10 @@
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B55" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D55" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -4892,7 +5063,7 @@
         <v>-10</v>
       </c>
       <c r="I55" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J55" s="22">
         <v>0</v>
@@ -4920,13 +5091,13 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D56" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$29&gt;2),"bo.f","")</f>
@@ -4946,7 +5117,7 @@
         <v>-10</v>
       </c>
       <c r="I56" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J56" s="22">
         <v>0</v>
@@ -4974,10 +5145,10 @@
     </row>
     <row r="57" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B57" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D57" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$29&gt;2),"bo.f","")</f>
@@ -4997,7 +5168,7 @@
         <v>-10</v>
       </c>
       <c r="I57" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J57" s="22">
         <v>0</v>
@@ -5025,13 +5196,13 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D58" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -5051,7 +5222,7 @@
         <v>30</v>
       </c>
       <c r="I58" s="22" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="J58" s="22">
         <v>0</v>
@@ -5093,10 +5264,10 @@
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B59" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D59" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -5116,7 +5287,7 @@
         <v>-30</v>
       </c>
       <c r="I59" s="22" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="J59" s="22">
         <v>0</v>
@@ -5158,34 +5329,34 @@
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B60" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D60" s="22" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="E60" s="22" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="F60" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B61" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D61" s="22" t="str">
         <f>IF(PARAM!$I$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E61" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F61" s="22">
         <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$15/2)),0)</f>
@@ -5205,17 +5376,17 @@
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B62" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D62" s="22" t="str">
         <f>IF(PARAM!$I$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F62" s="22">
         <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$15/2)),0)</f>
@@ -5235,17 +5406,17 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B63" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D63" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E63" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F63" s="22">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -5259,22 +5430,22 @@
         <v>0</v>
       </c>
       <c r="I63" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B64" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D64" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E64" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F64" s="22">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -5288,22 +5459,22 @@
         <v>0</v>
       </c>
       <c r="I64" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B65" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D65" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E65" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F65" s="22">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -5317,22 +5488,22 @@
         <v>0</v>
       </c>
       <c r="I65" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B66" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C66" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D66" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E66" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F66" s="22">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -5346,22 +5517,22 @@
         <v>0</v>
       </c>
       <c r="I66" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B67" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C67" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D67" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E67" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F67" s="22">
         <v>0</v>
@@ -5374,22 +5545,22 @@
         <v>0</v>
       </c>
       <c r="I67" s="22" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B68" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D68" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F68" s="22">
         <v>0</v>
@@ -5402,15 +5573,15 @@
         <v>0</v>
       </c>
       <c r="I68" s="22" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B69" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D69" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5430,7 +5601,7 @@
         <v>35</v>
       </c>
       <c r="I69" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J69" s="22">
         <v>0</v>
@@ -5472,10 +5643,10 @@
     </row>
     <row r="70" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B70" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D70" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5495,7 +5666,7 @@
         <v>35</v>
       </c>
       <c r="I70" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J70" s="22">
         <v>0</v>
@@ -5537,10 +5708,10 @@
     </row>
     <row r="71" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B71" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D71" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5560,7 +5731,7 @@
         <v>-35</v>
       </c>
       <c r="I71" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J71" s="22">
         <v>0</v>
@@ -5602,10 +5773,10 @@
     </row>
     <row r="72" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B72" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D72" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5625,7 +5796,7 @@
         <v>-35</v>
       </c>
       <c r="I72" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J72" s="22">
         <v>0</v>
@@ -5667,10 +5838,10 @@
     </row>
     <row r="73" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B73" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D73" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5690,7 +5861,7 @@
         <v>35</v>
       </c>
       <c r="I73" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J73" s="22">
         <v>0</v>
@@ -5732,10 +5903,10 @@
     </row>
     <row r="74" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B74" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C74" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D74" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5755,7 +5926,7 @@
         <v>35</v>
       </c>
       <c r="I74" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J74" s="22">
         <v>0</v>
@@ -5797,10 +5968,10 @@
     </row>
     <row r="75" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B75" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C75" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D75" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5820,7 +5991,7 @@
         <v>-35</v>
       </c>
       <c r="I75" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J75" s="22">
         <v>0</v>
@@ -5862,10 +6033,10 @@
     </row>
     <row r="76" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B76" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C76" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D76" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5885,7 +6056,7 @@
         <v>-35</v>
       </c>
       <c r="I76" s="22" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J76" s="22">
         <v>0</v>
@@ -5927,10 +6098,10 @@
     </row>
     <row r="77" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B77" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D77" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -5950,7 +6121,7 @@
         <v>-10</v>
       </c>
       <c r="I77" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J77" s="22">
         <v>0</v>
@@ -5978,10 +6149,10 @@
     </row>
     <row r="78" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B78" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C78" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D78" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -6001,7 +6172,7 @@
         <v>-10</v>
       </c>
       <c r="I78" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J78" s="22">
         <v>0</v>
@@ -6029,10 +6200,10 @@
     </row>
     <row r="79" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B79" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C79" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D79" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$29&gt;2),"bo.f","")</f>
@@ -6052,7 +6223,7 @@
         <v>-10</v>
       </c>
       <c r="I79" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J79" s="22">
         <v>0</v>
@@ -6080,10 +6251,10 @@
     </row>
     <row r="80" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B80" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C80" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D80" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$29&gt;2),"bo.f","")</f>
@@ -6103,7 +6274,7 @@
         <v>-10</v>
       </c>
       <c r="I80" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J80" s="22">
         <v>0</v>
@@ -6131,10 +6302,10 @@
     </row>
     <row r="81" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B81" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C81" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D81" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -6154,7 +6325,7 @@
         <v>30</v>
       </c>
       <c r="I81" s="22" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="J81" s="22">
         <v>0</v>
@@ -6196,10 +6367,10 @@
     </row>
     <row r="82" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B82" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C82" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D82" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -6219,7 +6390,7 @@
         <v>-30</v>
       </c>
       <c r="I82" s="22" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="J82" s="22">
         <v>0</v>
@@ -6261,52 +6432,52 @@
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B83" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C83" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D83" s="22" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="E83" s="22" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="F83" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="B87" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C87" s="22" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D87" s="22" t="str">
-        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$51&gt;0),"pl.stf1","")</f>
+        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$55&gt;0),"pl.stf1","")</f>
         <v>pl.stf1</v>
       </c>
       <c r="E87" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F87" s="22">
         <v>0</v>
@@ -6316,11 +6487,11 @@
         <v>-77.5</v>
       </c>
       <c r="H87" s="22">
-        <f>PARAM!$G$7/2+PARAM!$E$51</f>
+        <f>PARAM!$G$7/2+PARAM!$E$55</f>
         <v>845.5</v>
       </c>
       <c r="I87" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J87" s="22">
         <v>0</v>
@@ -6347,17 +6518,17 @@
     </row>
     <row r="88" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B88" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C88" s="22" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D88" s="22" t="str">
-        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$52&gt;0),"pl.stf2","")</f>
+        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$56&gt;0),"pl.stf2","")</f>
         <v>pl.stf2</v>
       </c>
       <c r="E88" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F88" s="22">
         <v>0</v>
@@ -6367,11 +6538,11 @@
         <v>-77.5</v>
       </c>
       <c r="H88" s="22">
-        <f>PARAM!$G$7/2+PARAM!$E$52</f>
+        <f>PARAM!$G$7/2+PARAM!$E$56</f>
         <v>554.5</v>
       </c>
       <c r="I88" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J88" s="22">
         <v>0</v>
@@ -6398,17 +6569,17 @@
     </row>
     <row r="89" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B89" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C89" s="22" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D89" s="22" t="str">
-        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$53&gt;0),"pl.stf3","")</f>
+        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$57&gt;0),"pl.stf3","")</f>
         <v/>
       </c>
       <c r="E89" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F89" s="22">
         <v>0</v>
@@ -6418,11 +6589,11 @@
         <v>-77.5</v>
       </c>
       <c r="H89" s="22">
-        <f>PARAM!$G$7/2+PARAM!$E$53</f>
+        <f>PARAM!$G$7/2+PARAM!$E$57</f>
         <v>700</v>
       </c>
       <c r="I89" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J89" s="22">
         <v>0</v>
@@ -6449,17 +6620,17 @@
     </row>
     <row r="90" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B90" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C90" s="22" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D90" s="22" t="str">
-        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$54&gt;0),"pl.stf4","")</f>
+        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$58&gt;0),"pl.stf4","")</f>
         <v/>
       </c>
       <c r="E90" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F90" s="22">
         <v>0</v>
@@ -6469,11 +6640,11 @@
         <v>-77.5</v>
       </c>
       <c r="H90" s="22">
-        <f>PARAM!$G$7/2+PARAM!$E$54</f>
+        <f>PARAM!$G$7/2+PARAM!$E$58</f>
         <v>700</v>
       </c>
       <c r="I90" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J90" s="22">
         <v>0</v>
@@ -6500,17 +6671,17 @@
     </row>
     <row r="91" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B91" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C91" s="22" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D91" s="22" t="str">
-        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$55&gt;0),"pl.stf5","")</f>
+        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$59&gt;0),"pl.stf5","")</f>
         <v/>
       </c>
       <c r="E91" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F91" s="22">
         <v>0</v>
@@ -6520,11 +6691,11 @@
         <v>-77.5</v>
       </c>
       <c r="H91" s="22">
-        <f>PARAM!$G$7/2+PARAM!$E$55</f>
+        <f>PARAM!$G$7/2+PARAM!$E$59</f>
         <v>700</v>
       </c>
       <c r="I91" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J91" s="22">
         <v>0</v>
@@ -6551,17 +6722,17 @@
     </row>
     <row r="92" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B92" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C92" s="22" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D92" s="22" t="str">
-        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$56&gt;0),"pl.stf6","")</f>
+        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$60&gt;0),"pl.stf6","")</f>
         <v/>
       </c>
       <c r="E92" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F92" s="22">
         <v>0</v>
@@ -6571,11 +6742,11 @@
         <v>-77.5</v>
       </c>
       <c r="H92" s="22">
-        <f>PARAM!$G$7/2+PARAM!$E$56</f>
+        <f>PARAM!$G$7/2+PARAM!$E$60</f>
         <v>700</v>
       </c>
       <c r="I92" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J92" s="22">
         <v>0</v>
@@ -6602,17 +6773,17 @@
     </row>
     <row r="93" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B93" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C93" s="22" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D93" s="22" t="str">
-        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$57&gt;0),"pl.stf7","")</f>
+        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$61&gt;0),"pl.stf7","")</f>
         <v/>
       </c>
       <c r="E93" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F93" s="22">
         <v>0</v>
@@ -6622,11 +6793,11 @@
         <v>-77.5</v>
       </c>
       <c r="H93" s="22">
-        <f>PARAM!$G$7/2+PARAM!$E$57</f>
+        <f>PARAM!$G$7/2+PARAM!$E$61</f>
         <v>700</v>
       </c>
       <c r="I93" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J93" s="22">
         <v>0</v>
@@ -6653,17 +6824,17 @@
     </row>
     <row r="94" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B94" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C94" s="22" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D94" s="22" t="str">
-        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$58&gt;0),"pl.stf8","")</f>
+        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$62&gt;0),"pl.stf8","")</f>
         <v/>
       </c>
       <c r="E94" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F94" s="22">
         <v>0</v>
@@ -6673,11 +6844,11 @@
         <v>-77.5</v>
       </c>
       <c r="H94" s="22">
-        <f>PARAM!$G$7/2+PARAM!$E$58</f>
+        <f>PARAM!$G$7/2+PARAM!$E$62</f>
         <v>700</v>
       </c>
       <c r="I94" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J94" s="22">
         <v>0</v>
@@ -6704,12 +6875,12 @@
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -6717,16 +6888,16 @@
         <v>18</v>
       </c>
       <c r="B97" s="21" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="C97" s="22" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D97" s="22" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="E97" s="22" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="F97" s="22">
         <v>0</v>
@@ -6751,19 +6922,19 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="B98" s="21" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="C98" s="22" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D98" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="E98" s="22" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="F98" s="22">
         <v>0</v>
@@ -6791,16 +6962,16 @@
         <v>19</v>
       </c>
       <c r="B99" s="21" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="C99" s="22" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D99" s="22" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="E99" s="22" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="F99" s="22">
         <v>0</v>
@@ -6825,19 +6996,19 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="B100" s="21" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="C100" s="22" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D100" s="22" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="E100" s="22" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="F100" s="22">
         <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$15/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
@@ -6864,16 +7035,16 @@
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" s="21" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="C101" s="22" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D101" s="22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="E101" s="22" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="F101" s="22">
         <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$15/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
@@ -6900,23 +7071,23 @@
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="B104" s="21" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C104" s="22" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="D104" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -6930,7 +7101,7 @@
         <v>14</v>
       </c>
       <c r="G104" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H104" s="22">
         <f>PARAM!$E$35</f>
@@ -6963,10 +7134,10 @@
     </row>
     <row r="105" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B105" s="21" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C105" s="22" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="D105" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -6980,7 +7151,7 @@
         <v>14</v>
       </c>
       <c r="G105" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H105" s="22">
         <f>PARAM!$E$36</f>
@@ -7013,10 +7184,10 @@
     </row>
     <row r="106" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B106" s="21" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C106" s="22" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="D106" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7030,7 +7201,7 @@
         <v>14</v>
       </c>
       <c r="G106" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H106" s="22">
         <f>PARAM!$E$37</f>
@@ -7063,10 +7234,10 @@
     </row>
     <row r="107" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B107" s="21" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C107" s="22" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="D107" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7080,7 +7251,7 @@
         <v>14</v>
       </c>
       <c r="G107" s="22" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H107" s="22">
         <f>PARAM!$E$38</f>
@@ -7111,729 +7282,696 @@
         <v>13</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="B108" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="C108" s="22" t="s">
-        <v>192</v>
-      </c>
-      <c r="D108" s="22" t="str">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="12" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B110" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="C110" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="D110" s="22" t="str">
         <f>PARAM!$C$8</f>
         <v>SS275</v>
       </c>
-      <c r="E108" s="22">
-        <f>PARAM!$G$44</f>
+      <c r="E110" s="22">
+        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0))</f>
         <v>20</v>
       </c>
-      <c r="F108" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="G108" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H108" s="22">
-        <f>PARAM!$E$44</f>
+      <c r="F110" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="G110" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="H110" s="22">
+        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,5,FALSE),0))</f>
         <v>230</v>
       </c>
-      <c r="I108" s="22">
-        <f>PARAM!$F$44</f>
+      <c r="I110" s="22">
+        <f>MAX(1,(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,9,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,10,FALSE),0)-1)+2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,8,FALSE),0)))</f>
         <v>230</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="B109" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="C109" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="D109" s="22" t="str">
+    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B111" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="C111" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="D111" s="22" t="str">
         <f>PARAM!$C$8</f>
         <v>SS275</v>
       </c>
-      <c r="E109" s="22">
-        <f>PARAM!$G$45</f>
+      <c r="E111" s="22">
+        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0))</f>
         <v>10</v>
       </c>
-      <c r="F109" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="G109" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H109" s="22">
-        <f>PARAM!$E$45</f>
+      <c r="F111" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="G111" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="H111" s="22">
+        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,5,FALSE),0))</f>
         <v>140</v>
       </c>
-      <c r="I109" s="22">
-        <f>PARAM!$F$45</f>
+      <c r="I111" s="22">
+        <f>MAX(1,(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,9,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,10,FALSE),0)-1)+2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,8,FALSE),0)))</f>
         <v>230</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A110" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="B110" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="C110" s="22" t="s">
-        <v>196</v>
-      </c>
-      <c r="D110" s="22" t="str">
+    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B112" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="C112" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="D112" s="22" t="str">
+        <f>PARAM!$C$8</f>
+        <v>SS275</v>
+      </c>
+      <c r="E112" s="22">
+        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0))</f>
+        <v>10</v>
+      </c>
+      <c r="F112" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="G112" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="H112" s="22">
+        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,5,FALSE),0))</f>
+        <v>140</v>
+      </c>
+      <c r="I112" s="22">
+        <f>MAX(1,(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,9,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,10,FALSE),0)-1)+2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,8,FALSE),0)))</f>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B113" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="C113" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="D113" s="22" t="str">
+        <f>PARAM!$C$8</f>
+        <v>SS275</v>
+      </c>
+      <c r="E113" s="22">
+        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0))</f>
+        <v>10</v>
+      </c>
+      <c r="F113" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="G113" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="H113" s="22">
+        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,5,FALSE),0))</f>
+        <v>140</v>
+      </c>
+      <c r="I113" s="22">
+        <f>MAX(1,(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,9,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,10,FALSE),0)-1)+2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,8,FALSE),0)))</f>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A114" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="B114" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="C114" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="D114" s="22" t="str">
         <f>PARAM!$G$24</f>
         <v>F10T</v>
       </c>
-      <c r="E110" s="22">
+      <c r="E114" s="22">
         <f>PARAM!$E$24</f>
         <v>16</v>
       </c>
-      <c r="F110" s="22">
-        <f>CEILING(PARAM!$G$45+PARAM!$G$35+1.1*PARAM!$E$24,5)</f>
-        <v>35</v>
-      </c>
-      <c r="G110" s="22">
+      <c r="F114" s="22">
+        <f>MAX(1,CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$35)+1.1*PARAM!$E$24,5))</f>
+        <v>55</v>
+      </c>
+      <c r="G114" s="22">
         <f>PARAM!$F$24</f>
         <v>18</v>
       </c>
-      <c r="H110" s="22"/>
-      <c r="I110" s="22"/>
-      <c r="J110" s="22"/>
-      <c r="K110" s="22">
+      <c r="H114" s="22"/>
+      <c r="I114" s="22"/>
+      <c r="J114" s="22"/>
+      <c r="K114" s="22">
         <f>0.9*PARAM!$E$24</f>
         <v>14.4</v>
       </c>
-      <c r="L110" s="22">
-        <f>CEILING(PARAM!$G$45+PARAM!$G$35+1.1*PARAM!$E$24,5)-PARAM!$G$45-PARAM!$G$35-0.9*PARAM!$E$24</f>
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A111" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="B111" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="C111" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="D111" s="22" t="str">
+      <c r="L114" s="22">
+        <f>MAX(0,(CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$35)+1.1*PARAM!$E$24,5))-(IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$35))-0.9*PARAM!$E$24)</f>
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="115" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B115" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="C115" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="D115" s="22" t="str">
         <f>PARAM!$G$24</f>
         <v>F10T</v>
       </c>
-      <c r="E111" s="22">
+      <c r="E115" s="22">
         <f>PARAM!$E$24</f>
         <v>16</v>
       </c>
-      <c r="F111" s="22">
-        <f>IF(PARAM!$C$6="H",CEILING(IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+PARAM!$G$44+1.1*PARAM!$E$24,5),CEILING(2*PARAM!$G$44+1.1*PARAM!$E$24,5))</f>
-        <v>55</v>
-      </c>
-      <c r="G111" s="22">
+      <c r="F115" s="22">
+        <f>MAX(1,CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$36)+1.1*PARAM!$E$24,5))</f>
+        <v>35</v>
+      </c>
+      <c r="G115" s="22">
         <f>PARAM!$F$24</f>
         <v>18</v>
       </c>
-      <c r="H111" s="22"/>
-      <c r="I111" s="22"/>
-      <c r="J111" s="22"/>
-      <c r="K111" s="22">
+      <c r="H115" s="22"/>
+      <c r="I115" s="22"/>
+      <c r="J115" s="22"/>
+      <c r="K115" s="22">
         <f>0.9*PARAM!$E$24</f>
         <v>14.4</v>
       </c>
-      <c r="L111" s="22">
-        <f>(IF(PARAM!$C$6="H",CEILING(IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+PARAM!$G$44+1.1*PARAM!$E$24,5),CEILING(2*PARAM!$G$44+1.1*PARAM!$E$24,5)))-(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+PARAM!$G$44,2*PARAM!$G$44))-0.9*PARAM!$E$24</f>
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="112" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B112" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="C112" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="D112" s="22" t="str">
+      <c r="L115" s="22">
+        <f>MAX(0,(CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$36)+1.1*PARAM!$E$24,5))-(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$36))-0.9*PARAM!$E$24)</f>
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="116" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B116" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="C116" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="D116" s="22" t="str">
         <f>PARAM!$G$24</f>
         <v>F10T</v>
       </c>
-      <c r="E112" s="22">
+      <c r="E116" s="22">
         <f>PARAM!$E$24</f>
         <v>16</v>
       </c>
-      <c r="F112" s="22">
-        <f>IF(PARAM!$C$6="H",CEILING(IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+PARAM!$G$44+1.1*PARAM!$E$24,5),CEILING(2*PARAM!$G$44+1.1*PARAM!$E$24,5))</f>
-        <v>50</v>
-      </c>
-      <c r="G112" s="22">
+      <c r="F116" s="22">
+        <f>MAX(1,CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$37)+1.1*PARAM!$E$24,5))</f>
+        <v>35</v>
+      </c>
+      <c r="G116" s="22">
         <f>PARAM!$F$24</f>
         <v>18</v>
       </c>
-      <c r="H112" s="22"/>
-      <c r="I112" s="22"/>
-      <c r="J112" s="22"/>
-      <c r="K112" s="22">
+      <c r="H116" s="22"/>
+      <c r="I116" s="22"/>
+      <c r="J116" s="22"/>
+      <c r="K116" s="22">
         <f>0.9*PARAM!$E$24</f>
         <v>14.4</v>
       </c>
-      <c r="L112" s="22">
-        <f>(IF(PARAM!$C$6="H",CEILING(IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+PARAM!$G$44+1.1*PARAM!$E$24,5),CEILING(2*PARAM!$G$44+1.1*PARAM!$E$24,5)))-(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+PARAM!$G$44,2*PARAM!$G$44))-0.9*PARAM!$E$24</f>
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="12" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" s="12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="12" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A117" s="12" t="s">
-        <v>202</v>
-      </c>
+      <c r="L116" s="22">
+        <f>MAX(0,(CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$37)+1.1*PARAM!$E$24,5))-(IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$37))-0.9*PARAM!$E$24)</f>
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="117" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B117" s="21" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C117" s="22" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="D117" s="22" t="str">
-        <f>IF(AND(PARAM!$J$35&gt;0,PARAM!$C$35="end plate"),"pl.bep","")</f>
-        <v>pl.bep</v>
-      </c>
-      <c r="E117" s="22" t="s">
-        <v>126</v>
+        <f>PARAM!$G$24</f>
+        <v>F10T</v>
+      </c>
+      <c r="E117" s="22">
+        <f>PARAM!$E$24</f>
+        <v>16</v>
       </c>
       <c r="F117" s="22">
-        <f>-PARAM!$G$44/2</f>
+        <f>MAX(1,CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$38)+1.1*PARAM!$E$24,5))</f>
+        <v>35</v>
+      </c>
+      <c r="G117" s="22">
+        <f>PARAM!$F$24</f>
+        <v>18</v>
+      </c>
+      <c r="H117" s="22"/>
+      <c r="I117" s="22"/>
+      <c r="J117" s="22"/>
+      <c r="K117" s="22">
+        <f>0.9*PARAM!$E$24</f>
+        <v>14.4</v>
+      </c>
+      <c r="L117" s="22">
+        <f>MAX(0,(CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$38)+1.1*PARAM!$E$24,5))-(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$38))-0.9*PARAM!$E$24)</f>
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="12" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="12" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A122" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="B122" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C122" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="D122" s="22" t="str">
+        <f>IF(AND(PARAM!$J$35&gt;0,IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),"pl.cna","")</f>
+        <v>pl.cna</v>
+      </c>
+      <c r="E122" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F122" s="22">
+        <f>-IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)/2</f>
         <v>-10</v>
       </c>
-      <c r="G117" s="22">
+      <c r="G122" s="22">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H117" s="22">
-        <v>0</v>
-      </c>
-      <c r="I117" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="J117" s="22">
-        <v>0</v>
-      </c>
-      <c r="K117" s="22">
-        <v>0</v>
-      </c>
-      <c r="L117" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A118" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="B118" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C118" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="D118" s="22" t="str">
-        <f>IF(AND(PARAM!$J$35&gt;0,PARAM!$C$35="end plate",NOT(PARAM!$C$6="H")),"pl.bep","")</f>
+      <c r="H122" s="22">
+        <v>0</v>
+      </c>
+      <c r="I122" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="J122" s="22">
+        <v>0</v>
+      </c>
+      <c r="K122" s="22">
+        <v>0</v>
+      </c>
+      <c r="L122" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A123" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="B123" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C123" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="D123" s="22" t="str">
+        <f>IF(AND(PARAM!$J$35&gt;0,IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cna","")</f>
         <v/>
       </c>
-      <c r="E118" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="F118" s="22">
-        <f>-1.5*PARAM!$G$44</f>
+      <c r="E123" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F123" s="22">
+        <f>-1.5*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)</f>
         <v>-30</v>
       </c>
-      <c r="G118" s="22">
+      <c r="G123" s="22">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H118" s="22">
-        <v>0</v>
-      </c>
-      <c r="I118" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="J118" s="22">
-        <v>0</v>
-      </c>
-      <c r="K118" s="22">
-        <v>0</v>
-      </c>
-      <c r="L118" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A119" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="B119" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C119" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="D119" s="22" t="str">
-        <f>IF(AND(PARAM!$J$35&gt;0,PARAM!$C$35="fin plate"),"pl.fin","")</f>
+      <c r="H123" s="22">
+        <v>0</v>
+      </c>
+      <c r="I123" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="J123" s="22">
+        <v>0</v>
+      </c>
+      <c r="K123" s="22">
+        <v>0</v>
+      </c>
+      <c r="L123" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="B124" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C124" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="D124" s="22" t="str">
+        <f>IF(AND(PARAM!$J$35&gt;0,IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"),"pl.cna","")</f>
         <v/>
       </c>
-      <c r="E119" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="F119" s="22">
-        <f>PARAM!$E$45/2-PARAM!$D$45</f>
-        <v>60</v>
-      </c>
-      <c r="G119" s="22">
-        <f>PARAM!$G$35/2+PARAM!$G$45/2</f>
-        <v>8.25</v>
-      </c>
-      <c r="H119" s="22">
-        <v>0</v>
-      </c>
-      <c r="I119" s="22" t="s">
+      <c r="E124" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F124" s="22">
+        <f>IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,4,FALSE),0)</f>
+        <v>115</v>
+      </c>
+      <c r="G124" s="22">
+        <f>PARAM!$G$35/2+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)/2</f>
+        <v>13.25</v>
+      </c>
+      <c r="H124" s="22">
+        <v>0</v>
+      </c>
+      <c r="I124" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="J124" s="22">
+        <v>0</v>
+      </c>
+      <c r="K124" s="22">
+        <v>0</v>
+      </c>
+      <c r="L124" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="B125" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="J119" s="22">
-        <v>0</v>
-      </c>
-      <c r="K119" s="22">
-        <v>0</v>
-      </c>
-      <c r="L119" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A120" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="B120" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C120" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="D120" s="22" t="str">
+      <c r="C125" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="D125" s="22" t="str">
         <f>IF(PARAM!$J$35&gt;0,"sc.bma","")</f>
         <v>sc.bma</v>
       </c>
-      <c r="E120" s="22"/>
-      <c r="F120" s="22">
-        <v>0</v>
-      </c>
-      <c r="G120" s="22">
-        <v>0</v>
-      </c>
-      <c r="H120" s="22">
-        <v>0</v>
-      </c>
-      <c r="I120" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="J120" s="22">
-        <v>0</v>
-      </c>
-      <c r="K120" s="22">
-        <v>0</v>
-      </c>
-      <c r="L120" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A121" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="B121" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C121" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="D121" s="22" t="str">
-        <f>IF(PARAM!$J$35&lt;=0,"",IF(PARAM!$C$35="end plate","bo.bx","bo.fin"))</f>
-        <v>bo.bx</v>
-      </c>
-      <c r="E121" s="22"/>
-      <c r="F121" s="22">
-        <f>IF(PARAM!$C$35="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6))+PARAM!$G$44),-2*PARAM!$G$44),PARAM!$H$45-PARAM!$D$45)</f>
+      <c r="E125" s="22"/>
+      <c r="F125" s="22">
+        <v>0</v>
+      </c>
+      <c r="G125" s="22">
+        <v>0</v>
+      </c>
+      <c r="H125" s="22">
+        <v>0</v>
+      </c>
+      <c r="I125" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="J125" s="22">
+        <v>0</v>
+      </c>
+      <c r="K125" s="22">
+        <v>0</v>
+      </c>
+      <c r="L125" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A126" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="B126" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C126" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="D126" s="22" t="str">
+        <f>IF(OR(PARAM!$J$35&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"))),"","bo.cna")</f>
+        <v>bo.cna</v>
+      </c>
+      <c r="E126" s="22"/>
+      <c r="F126" s="22">
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6))+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)),-2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)-IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,4,FALSE),0))</f>
         <v>-35</v>
       </c>
-      <c r="G121" s="22">
-        <f>IF(PARAM!$C$35="end plate",-PARAM!$H$44/2,PARAM!$G$35/2+PARAM!$G$45)</f>
+      <c r="G126" s="22">
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",-IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)/2,PARAM!$G$35/2+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0))</f>
         <v>-70</v>
       </c>
-      <c r="H121" s="22">
-        <f>IF(PARAM!$C$35="end plate",-PARAM!$J$44*(PARAM!$K$44-1)/2,-PARAM!$J$45*(PARAM!$K$45-1)/2)</f>
+      <c r="H126" s="22">
+        <f>-IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,9,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,10,FALSE),0)-1)/2</f>
         <v>-70</v>
       </c>
-      <c r="I121" s="22" t="str">
-        <f>IF(PARAM!$C$35="end plate","YZ","XZ")</f>
+      <c r="I126" s="22" t="str">
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate","YZ","XZ")</f>
         <v>YZ</v>
       </c>
-      <c r="J121" s="22">
-        <v>0</v>
-      </c>
-      <c r="K121" s="22">
-        <v>0</v>
-      </c>
-      <c r="L121" s="22">
-        <v>0</v>
-      </c>
-      <c r="M121" s="22">
+      <c r="J126" s="22">
+        <v>0</v>
+      </c>
+      <c r="K126" s="22">
+        <v>0</v>
+      </c>
+      <c r="L126" s="22">
+        <v>0</v>
+      </c>
+      <c r="M126" s="22">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="N121" s="22">
-        <f>IF(PARAM!$C$35="end plate",PARAM!$H$44,0)</f>
+      <c r="N126" s="22">
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0),0)</f>
         <v>140</v>
       </c>
-      <c r="O121" s="22">
-        <v>0</v>
-      </c>
-      <c r="P121" s="22">
-        <f>IF(PARAM!$C$35="end plate",1,0)</f>
+      <c r="O126" s="22">
+        <v>0</v>
+      </c>
+      <c r="P126" s="22">
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",1,0)</f>
         <v>1</v>
       </c>
-      <c r="Q121" s="22">
-        <v>0</v>
-      </c>
-      <c r="R121" s="22">
-        <v>0</v>
-      </c>
-      <c r="S121" s="22">
-        <f>IF(PARAM!$C$35="end plate",PARAM!$J$44,PARAM!$J$45)</f>
+      <c r="Q126" s="22">
+        <v>0</v>
+      </c>
+      <c r="R126" s="22">
+        <v>0</v>
+      </c>
+      <c r="S126" s="22">
+        <f>IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,9,FALSE),0)</f>
         <v>70</v>
       </c>
-      <c r="T121" s="22">
-        <f>IF(PARAM!$C$35="end plate",PARAM!$K$44-1,PARAM!$K$45-1)</f>
+      <c r="T126" s="22">
+        <f>IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,10,FALSE),0)-1</f>
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B122" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C122" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="D122" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="E122" s="22" t="s">
-        <v>187</v>
-      </c>
-      <c r="F122" s="22" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" s="12" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="125" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B125" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C125" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="D125" s="22" t="str">
-        <f>IF(AND(PARAM!$J$36&gt;0,PARAM!$C$36="end plate"),"pl.bep","")</f>
+    <row r="127" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B127" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C127" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="D127" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="E127" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="F127" s="22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="12" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="130" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B130" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C130" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="D130" s="22" t="str">
+        <f>IF(AND(PARAM!$J$36&gt;0,IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),"pl.cnb","")</f>
         <v/>
       </c>
-      <c r="E125" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="F125" s="22">
-        <f>-(-PARAM!$G$44/2)</f>
-        <v>10</v>
-      </c>
-      <c r="G125" s="22">
+      <c r="E130" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F130" s="22">
+        <f>-(-IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)/2)</f>
+        <v>5</v>
+      </c>
+      <c r="G130" s="22">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H125" s="22">
-        <v>0</v>
-      </c>
-      <c r="I125" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="J125" s="22">
-        <v>0</v>
-      </c>
-      <c r="K125" s="22">
-        <v>0</v>
-      </c>
-      <c r="L125" s="22">
+      <c r="H130" s="22">
+        <v>0</v>
+      </c>
+      <c r="I130" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="J130" s="22">
+        <v>0</v>
+      </c>
+      <c r="K130" s="22">
+        <v>0</v>
+      </c>
+      <c r="L130" s="22">
         <v>180</v>
       </c>
     </row>
-    <row r="126" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B126" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C126" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="D126" s="22" t="str">
-        <f>IF(AND(PARAM!$J$36&gt;0,PARAM!$C$36="end plate",NOT(PARAM!$C$6="H")),"pl.bep","")</f>
+    <row r="131" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B131" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C131" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="D131" s="22" t="str">
+        <f>IF(AND(PARAM!$J$36&gt;0,IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnb","")</f>
         <v/>
       </c>
-      <c r="E126" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="F126" s="22">
-        <f>-(-1.5*PARAM!$G$44)</f>
-        <v>30</v>
-      </c>
-      <c r="G126" s="22">
+      <c r="E131" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F131" s="22">
+        <f>-(-1.5*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0))</f>
+        <v>15</v>
+      </c>
+      <c r="G131" s="22">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H126" s="22">
-        <v>0</v>
-      </c>
-      <c r="I126" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="J126" s="22">
-        <v>0</v>
-      </c>
-      <c r="K126" s="22">
-        <v>0</v>
-      </c>
-      <c r="L126" s="22">
+      <c r="H131" s="22">
+        <v>0</v>
+      </c>
+      <c r="I131" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="J131" s="22">
+        <v>0</v>
+      </c>
+      <c r="K131" s="22">
+        <v>0</v>
+      </c>
+      <c r="L131" s="22">
         <v>180</v>
       </c>
     </row>
-    <row r="127" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B127" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C127" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="D127" s="22" t="str">
-        <f>IF(AND(PARAM!$J$36&gt;0,PARAM!$C$36="fin plate"),"pl.fin","")</f>
-        <v>pl.fin</v>
-      </c>
-      <c r="E127" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="F127" s="22">
-        <f>-(PARAM!$E$45/2-PARAM!$D$45)</f>
+    <row r="132" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B132" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C132" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="D132" s="22" t="str">
+        <f>IF(AND(PARAM!$J$36&gt;0,IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"),"pl.cnb","")</f>
+        <v>pl.cnb</v>
+      </c>
+      <c r="E132" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F132" s="22">
+        <f>-(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,4,FALSE),0))</f>
         <v>-60</v>
       </c>
-      <c r="G127" s="22">
-        <f>-(PARAM!$G$36/2+PARAM!$G$45/2)</f>
+      <c r="G132" s="22">
+        <f>-(PARAM!$G$36/2+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)/2)</f>
         <v>-8.25</v>
       </c>
-      <c r="H127" s="22">
-        <v>0</v>
-      </c>
-      <c r="I127" s="22" t="s">
+      <c r="H132" s="22">
+        <v>0</v>
+      </c>
+      <c r="I132" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="J132" s="22">
+        <v>0</v>
+      </c>
+      <c r="K132" s="22">
+        <v>0</v>
+      </c>
+      <c r="L132" s="22">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="133" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B133" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="J127" s="22">
-        <v>0</v>
-      </c>
-      <c r="K127" s="22">
-        <v>0</v>
-      </c>
-      <c r="L127" s="22">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="128" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B128" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C128" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="D128" s="22" t="str">
+      <c r="C133" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="D133" s="22" t="str">
         <f>IF(PARAM!$J$36&gt;0,"sc.bmb","")</f>
         <v>sc.bmb</v>
       </c>
-      <c r="E128" s="22"/>
-      <c r="F128" s="22">
-        <v>0</v>
-      </c>
-      <c r="G128" s="22">
-        <v>0</v>
-      </c>
-      <c r="H128" s="22">
-        <v>0</v>
-      </c>
-      <c r="I128" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="J128" s="22">
-        <v>0</v>
-      </c>
-      <c r="K128" s="22">
-        <v>0</v>
-      </c>
-      <c r="L128" s="22">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="129" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B129" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C129" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="D129" s="22" t="str">
-        <f>IF(PARAM!$J$36&lt;=0,"",IF(PARAM!$C$36="end plate","bo.bx","bo.fin"))</f>
-        <v>bo.fin</v>
-      </c>
-      <c r="E129" s="22"/>
-      <c r="F129" s="22">
-        <f>-(IF(PARAM!$C$36="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6))+PARAM!$G$44),-2*PARAM!$G$44),PARAM!$H$45-PARAM!$D$45))</f>
-        <v>-50</v>
-      </c>
-      <c r="G129" s="22">
-        <f>-(IF(PARAM!$C$36="end plate",-PARAM!$H$44/2,PARAM!$G$36/2+PARAM!$G$45))</f>
-        <v>-13.25</v>
-      </c>
-      <c r="H129" s="22">
-        <f>IF(PARAM!$C$36="end plate",-PARAM!$J$44*(PARAM!$K$44-1)/2,-PARAM!$J$45*(PARAM!$K$45-1)/2)</f>
-        <v>-70</v>
-      </c>
-      <c r="I129" s="22" t="str">
-        <f>IF(PARAM!$C$36="end plate","YZ","XZ")</f>
-        <v>XZ</v>
-      </c>
-      <c r="J129" s="22">
-        <v>0</v>
-      </c>
-      <c r="K129" s="22">
-        <v>0</v>
-      </c>
-      <c r="L129" s="22">
-        <v>180</v>
-      </c>
-      <c r="M129" s="22">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="N129" s="22">
-        <f>-(IF(PARAM!$C$36="end plate",PARAM!$H$44,0))</f>
-        <v>0</v>
-      </c>
-      <c r="O129" s="22">
-        <v>0</v>
-      </c>
-      <c r="P129" s="22">
-        <f>IF(PARAM!$C$36="end plate",1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q129" s="22">
-        <v>0</v>
-      </c>
-      <c r="R129" s="22">
-        <v>0</v>
-      </c>
-      <c r="S129" s="22">
-        <f>IF(PARAM!$C$36="end plate",PARAM!$J$44,PARAM!$J$45)</f>
-        <v>70</v>
-      </c>
-      <c r="T129" s="22">
-        <f>IF(PARAM!$C$36="end plate",PARAM!$K$44-1,PARAM!$K$45-1)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="130" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B130" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C130" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="D130" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="E130" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="F130" s="22" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" s="12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" s="12" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="133" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B133" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C133" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="D133" s="22" t="str">
-        <f>IF(AND(PARAM!$J$37&gt;0,PARAM!$C$37="end plate"),"pl.bep","")</f>
-        <v/>
-      </c>
-      <c r="E133" s="22" t="s">
-        <v>126</v>
-      </c>
+      <c r="E133" s="22"/>
       <c r="F133" s="22">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="G133" s="22">
-        <f>-PARAM!$G$44/2</f>
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="H133" s="22">
         <v>0</v>
       </c>
       <c r="I133" s="22" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="J133" s="22">
         <v>0</v>
@@ -7845,33 +7983,33 @@
         <v>180</v>
       </c>
     </row>
-    <row r="134" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B134" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C134" s="22" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="D134" s="22" t="str">
-        <f>IF(AND(PARAM!$J$37&gt;0,PARAM!$C$37="end plate",NOT(PARAM!$C$6="H")),"pl.bep","")</f>
-        <v/>
-      </c>
-      <c r="E134" s="22" t="s">
-        <v>126</v>
-      </c>
+        <f>IF(OR(PARAM!$J$36&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"))),"","bo.cnb")</f>
+        <v>bo.cnb</v>
+      </c>
+      <c r="E134" s="22"/>
       <c r="F134" s="22">
-        <f>0</f>
-        <v>0</v>
+        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6))+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)),-2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)-IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,4,FALSE),0)))</f>
+        <v>-50</v>
       </c>
       <c r="G134" s="22">
-        <f>-1.5*PARAM!$G$44</f>
-        <v>-30</v>
+        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",-IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)/2,PARAM!$G$36/2+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)))</f>
+        <v>-13.25</v>
       </c>
       <c r="H134" s="22">
-        <v>0</v>
-      </c>
-      <c r="I134" s="22" t="s">
-        <v>169</v>
+        <f>-IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,9,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,10,FALSE),0)-1)/2</f>
+        <v>-70</v>
+      </c>
+      <c r="I134" s="22" t="str">
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate","YZ","XZ")</f>
+        <v>XZ</v>
       </c>
       <c r="J134" s="22">
         <v>0</v>
@@ -7882,522 +8020,654 @@
       <c r="L134" s="22">
         <v>180</v>
       </c>
-    </row>
-    <row r="135" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M134" s="22">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="N134" s="22">
+        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="O134" s="22">
+        <v>0</v>
+      </c>
+      <c r="P134" s="22">
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q134" s="22">
+        <v>0</v>
+      </c>
+      <c r="R134" s="22">
+        <v>0</v>
+      </c>
+      <c r="S134" s="22">
+        <f>IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,9,FALSE),0)</f>
+        <v>70</v>
+      </c>
+      <c r="T134" s="22">
+        <f>IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,10,FALSE),0)-1</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B135" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C135" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="D135" s="22" t="str">
-        <f>IF(AND(PARAM!$J$37&gt;0,PARAM!$C$37="fin plate"),"pl.fin","")</f>
-        <v>pl.fin</v>
+        <v>223</v>
+      </c>
+      <c r="D135" s="22" t="s">
+        <v>172</v>
       </c>
       <c r="E135" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="F135" s="22">
-        <f>PARAM!$G$37/2+PARAM!$G$45/2</f>
+        <v>200</v>
+      </c>
+      <c r="F135" s="22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="12" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="138" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B138" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C138" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="D138" s="22" t="str">
+        <f>IF(AND(PARAM!$J$37&gt;0,IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),"pl.cnc","")</f>
+        <v/>
+      </c>
+      <c r="E138" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F138" s="22">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G138" s="22">
+        <f>-IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)/2</f>
+        <v>-5</v>
+      </c>
+      <c r="H138" s="22">
+        <v>0</v>
+      </c>
+      <c r="I138" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="J138" s="22">
+        <v>0</v>
+      </c>
+      <c r="K138" s="22">
+        <v>0</v>
+      </c>
+      <c r="L138" s="22">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="139" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B139" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C139" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="D139" s="22" t="str">
+        <f>IF(AND(PARAM!$J$37&gt;0,IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnc","")</f>
+        <v/>
+      </c>
+      <c r="E139" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F139" s="22">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="G139" s="22">
+        <f>-1.5*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)</f>
+        <v>-15</v>
+      </c>
+      <c r="H139" s="22">
+        <v>0</v>
+      </c>
+      <c r="I139" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="J139" s="22">
+        <v>0</v>
+      </c>
+      <c r="K139" s="22">
+        <v>0</v>
+      </c>
+      <c r="L139" s="22">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="140" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B140" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C140" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="D140" s="22" t="str">
+        <f>IF(AND(PARAM!$J$37&gt;0,IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"),"pl.cnc","")</f>
+        <v>pl.cnc</v>
+      </c>
+      <c r="E140" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F140" s="22">
+        <f>PARAM!$G$37/2+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)/2</f>
         <v>8.25</v>
       </c>
-      <c r="G135" s="22">
-        <f>PARAM!$E$45/2-PARAM!$D$45</f>
+      <c r="G140" s="22">
+        <f>IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,4,FALSE),0)</f>
         <v>60</v>
       </c>
-      <c r="H135" s="22">
-        <v>0</v>
-      </c>
-      <c r="I135" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="J135" s="22">
-        <v>0</v>
-      </c>
-      <c r="K135" s="22">
-        <v>0</v>
-      </c>
-      <c r="L135" s="22">
+      <c r="H140" s="22">
+        <v>0</v>
+      </c>
+      <c r="I140" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="J140" s="22">
+        <v>0</v>
+      </c>
+      <c r="K140" s="22">
+        <v>0</v>
+      </c>
+      <c r="L140" s="22">
         <v>180</v>
       </c>
     </row>
-    <row r="136" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B136" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C136" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="D136" s="22" t="str">
+    <row r="141" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B141" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C141" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="D141" s="22" t="str">
         <f>IF(PARAM!$J$37&gt;0,"sc.bmc","")</f>
         <v>sc.bmc</v>
       </c>
-      <c r="E136" s="22"/>
-      <c r="F136" s="22">
-        <v>0</v>
-      </c>
-      <c r="G136" s="22">
-        <v>0</v>
-      </c>
-      <c r="H136" s="22">
-        <v>0</v>
-      </c>
-      <c r="I136" s="22" t="s">
+      <c r="E141" s="22"/>
+      <c r="F141" s="22">
+        <v>0</v>
+      </c>
+      <c r="G141" s="22">
+        <v>0</v>
+      </c>
+      <c r="H141" s="22">
+        <v>0</v>
+      </c>
+      <c r="I141" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="J141" s="22">
+        <v>0</v>
+      </c>
+      <c r="K141" s="22">
+        <v>0</v>
+      </c>
+      <c r="L141" s="22">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="142" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B142" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="J136" s="22">
-        <v>0</v>
-      </c>
-      <c r="K136" s="22">
-        <v>0</v>
-      </c>
-      <c r="L136" s="22">
+      <c r="C142" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="D142" s="22" t="str">
+        <f>IF(OR(PARAM!$J$37&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"))),"","bo.cnc")</f>
+        <v>bo.cnc</v>
+      </c>
+      <c r="E142" s="22"/>
+      <c r="F142" s="22">
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",-IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)/2,PARAM!$G$37/2+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0))</f>
+        <v>13.25</v>
+      </c>
+      <c r="G142" s="22">
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6))+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)),-2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)-IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,4,FALSE),0))</f>
+        <v>50</v>
+      </c>
+      <c r="H142" s="22">
+        <f>-IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,9,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,10,FALSE),0)-1)/2</f>
+        <v>-70</v>
+      </c>
+      <c r="I142" s="22" t="str">
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate","XZ","YZ")</f>
+        <v>YZ</v>
+      </c>
+      <c r="J142" s="22">
+        <v>0</v>
+      </c>
+      <c r="K142" s="22">
+        <v>0</v>
+      </c>
+      <c r="L142" s="22">
         <v>180</v>
       </c>
-    </row>
-    <row r="137" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B137" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C137" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="D137" s="22" t="str">
-        <f>IF(PARAM!$J$37&lt;=0,"",IF(PARAM!$C$37="end plate","bo.by","bo.fin"))</f>
-        <v>bo.fin</v>
-      </c>
-      <c r="E137" s="22"/>
-      <c r="F137" s="22">
-        <f>IF(PARAM!$C$37="end plate",-PARAM!$H$44/2,PARAM!$G$37/2+PARAM!$G$45)</f>
-        <v>13.25</v>
-      </c>
-      <c r="G137" s="22">
-        <f>IF(PARAM!$C$37="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6))+PARAM!$G$44),-2*PARAM!$G$44),PARAM!$H$45-PARAM!$D$45)</f>
-        <v>50</v>
-      </c>
-      <c r="H137" s="22">
-        <f>IF(PARAM!$C$37="end plate",-PARAM!$J$44*(PARAM!$K$44-1)/2,-PARAM!$J$45*(PARAM!$K$45-1)/2)</f>
-        <v>-70</v>
-      </c>
-      <c r="I137" s="22" t="str">
-        <f>IF(PARAM!$C$37="end plate","XZ","YZ")</f>
-        <v>YZ</v>
-      </c>
-      <c r="J137" s="22">
-        <v>0</v>
-      </c>
-      <c r="K137" s="22">
-        <v>0</v>
-      </c>
-      <c r="L137" s="22">
-        <v>180</v>
-      </c>
-      <c r="M137" s="22">
-        <f>IF(PARAM!$C$37="end plate",PARAM!$H$44,0)</f>
-        <v>0</v>
-      </c>
-      <c r="N137" s="22">
+      <c r="M142" s="22">
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N142" s="22">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="O137" s="22">
-        <v>0</v>
-      </c>
-      <c r="P137" s="22">
-        <f>IF(PARAM!$C$37="end plate",1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q137" s="22">
-        <v>0</v>
-      </c>
-      <c r="R137" s="22">
-        <v>0</v>
-      </c>
-      <c r="S137" s="22">
-        <f>IF(PARAM!$C$37="end plate",PARAM!$J$44,PARAM!$J$45)</f>
+      <c r="O142" s="22">
+        <v>0</v>
+      </c>
+      <c r="P142" s="22">
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q142" s="22">
+        <v>0</v>
+      </c>
+      <c r="R142" s="22">
+        <v>0</v>
+      </c>
+      <c r="S142" s="22">
+        <f>IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,9,FALSE),0)</f>
         <v>70</v>
       </c>
-      <c r="T137" s="22">
-        <f>IF(PARAM!$C$37="end plate",PARAM!$K$44-1,PARAM!$K$45-1)</f>
+      <c r="T142" s="22">
+        <f>IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,10,FALSE),0)-1</f>
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B138" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C138" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="D138" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="E138" s="22" t="s">
-        <v>189</v>
-      </c>
-      <c r="F138" s="22" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" s="12" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="141" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B141" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C141" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="D141" s="22" t="str">
-        <f>IF(AND(PARAM!$J$38&gt;0,PARAM!$C$38="end plate"),"pl.bep","")</f>
+    <row r="143" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B143" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C143" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="D143" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="E143" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="F143" s="22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="12" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="146" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B146" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C146" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="D146" s="22" t="str">
+        <f>IF(AND(PARAM!$J$38&gt;0,IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),"pl.cnd","")</f>
         <v/>
       </c>
-      <c r="E141" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="F141" s="22">
+      <c r="E146" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F146" s="22">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="G141" s="22">
-        <f>-(-PARAM!$G$44/2)</f>
-        <v>10</v>
-      </c>
-      <c r="H141" s="22">
-        <v>0</v>
-      </c>
-      <c r="I141" s="22" t="s">
+      <c r="G146" s="22">
+        <f>-(-IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)/2)</f>
+        <v>5</v>
+      </c>
+      <c r="H146" s="22">
+        <v>0</v>
+      </c>
+      <c r="I146" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="J146" s="22">
+        <v>0</v>
+      </c>
+      <c r="K146" s="22">
+        <v>0</v>
+      </c>
+      <c r="L146" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B147" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="J141" s="22">
-        <v>0</v>
-      </c>
-      <c r="K141" s="22">
-        <v>0</v>
-      </c>
-      <c r="L141" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B142" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C142" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="D142" s="22" t="str">
-        <f>IF(AND(PARAM!$J$38&gt;0,PARAM!$C$38="end plate",NOT(PARAM!$C$6="H")),"pl.bep","")</f>
+      <c r="C147" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="D147" s="22" t="str">
+        <f>IF(AND(PARAM!$J$38&gt;0,IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnd","")</f>
         <v/>
       </c>
-      <c r="E142" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="F142" s="22">
+      <c r="E147" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F147" s="22">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="G142" s="22">
-        <f>-(-1.5*PARAM!$G$44)</f>
-        <v>30</v>
-      </c>
-      <c r="H142" s="22">
-        <v>0</v>
-      </c>
-      <c r="I142" s="22" t="s">
+      <c r="G147" s="22">
+        <f>-(-1.5*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0))</f>
+        <v>15</v>
+      </c>
+      <c r="H147" s="22">
+        <v>0</v>
+      </c>
+      <c r="I147" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="J147" s="22">
+        <v>0</v>
+      </c>
+      <c r="K147" s="22">
+        <v>0</v>
+      </c>
+      <c r="L147" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B148" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="J142" s="22">
-        <v>0</v>
-      </c>
-      <c r="K142" s="22">
-        <v>0</v>
-      </c>
-      <c r="L142" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B143" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C143" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="D143" s="22" t="str">
-        <f>IF(AND(PARAM!$J$38&gt;0,PARAM!$C$38="fin plate"),"pl.fin","")</f>
+      <c r="C148" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="D148" s="22" t="str">
+        <f>IF(AND(PARAM!$J$38&gt;0,IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"),"pl.cnd","")</f>
         <v/>
       </c>
-      <c r="E143" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="F143" s="22">
-        <f>-(PARAM!$G$38/2+PARAM!$G$45/2)</f>
+      <c r="E148" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F148" s="22">
+        <f>-(PARAM!$G$38/2+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)/2)</f>
         <v>-8.25</v>
       </c>
-      <c r="G143" s="22">
-        <f>-(PARAM!$E$45/2-PARAM!$D$45)</f>
+      <c r="G148" s="22">
+        <f>-(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,4,FALSE),0))</f>
         <v>-60</v>
       </c>
-      <c r="H143" s="22">
-        <v>0</v>
-      </c>
-      <c r="I143" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="J143" s="22">
-        <v>0</v>
-      </c>
-      <c r="K143" s="22">
-        <v>0</v>
-      </c>
-      <c r="L143" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B144" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C144" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="D144" s="22" t="str">
+      <c r="H148" s="22">
+        <v>0</v>
+      </c>
+      <c r="I148" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="J148" s="22">
+        <v>0</v>
+      </c>
+      <c r="K148" s="22">
+        <v>0</v>
+      </c>
+      <c r="L148" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B149" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C149" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="D149" s="22" t="str">
         <f>IF(PARAM!$J$38&gt;0,"sc.bmd","")</f>
         <v/>
       </c>
-      <c r="E144" s="22"/>
-      <c r="F144" s="22">
-        <v>0</v>
-      </c>
-      <c r="G144" s="22">
-        <v>0</v>
-      </c>
-      <c r="H144" s="22">
-        <v>0</v>
-      </c>
-      <c r="I144" s="22" t="s">
+      <c r="E149" s="22"/>
+      <c r="F149" s="22">
+        <v>0</v>
+      </c>
+      <c r="G149" s="22">
+        <v>0</v>
+      </c>
+      <c r="H149" s="22">
+        <v>0</v>
+      </c>
+      <c r="I149" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="J149" s="22">
+        <v>0</v>
+      </c>
+      <c r="K149" s="22">
+        <v>0</v>
+      </c>
+      <c r="L149" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B150" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="J144" s="22">
-        <v>0</v>
-      </c>
-      <c r="K144" s="22">
-        <v>0</v>
-      </c>
-      <c r="L144" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B145" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C145" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="D145" s="22" t="str">
-        <f>IF(PARAM!$J$38&lt;=0,"",IF(PARAM!$C$38="end plate","bo.by","bo.fin"))</f>
+      <c r="C150" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="D150" s="22" t="str">
+        <f>IF(OR(PARAM!$J$38&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"))),"","bo.cnd")</f>
         <v/>
       </c>
-      <c r="E145" s="22"/>
-      <c r="F145" s="22">
-        <f>-(IF(PARAM!$C$38="end plate",-PARAM!$H$44/2,PARAM!$G$38/2+PARAM!$G$45))</f>
+      <c r="E150" s="22"/>
+      <c r="F150" s="22">
+        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",-IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)/2,PARAM!$G$38/2+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)))</f>
         <v>-13.25</v>
       </c>
-      <c r="G145" s="22">
-        <f>-(IF(PARAM!$C$38="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6))+PARAM!$G$44),-2*PARAM!$G$44),PARAM!$H$45-PARAM!$D$45))</f>
+      <c r="G150" s="22">
+        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6))+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)),-2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)-IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,4,FALSE),0)))</f>
         <v>-50</v>
       </c>
-      <c r="H145" s="22">
-        <f>IF(PARAM!$C$38="end plate",-PARAM!$J$44*(PARAM!$K$44-1)/2,-PARAM!$J$45*(PARAM!$K$45-1)/2)</f>
+      <c r="H150" s="22">
+        <f>-IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,9,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,10,FALSE),0)-1)/2</f>
         <v>-70</v>
       </c>
-      <c r="I145" s="22" t="str">
-        <f>IF(PARAM!$C$38="end plate","XZ","YZ")</f>
+      <c r="I150" s="22" t="str">
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate","XZ","YZ")</f>
         <v>YZ</v>
       </c>
-      <c r="J145" s="22">
-        <v>0</v>
-      </c>
-      <c r="K145" s="22">
-        <v>0</v>
-      </c>
-      <c r="L145" s="22">
-        <v>0</v>
-      </c>
-      <c r="M145" s="22">
-        <f>-(IF(PARAM!$C$38="end plate",PARAM!$H$44,0))</f>
-        <v>0</v>
-      </c>
-      <c r="N145" s="22">
+      <c r="J150" s="22">
+        <v>0</v>
+      </c>
+      <c r="K150" s="22">
+        <v>0</v>
+      </c>
+      <c r="L150" s="22">
+        <v>0</v>
+      </c>
+      <c r="M150" s="22">
+        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="N150" s="22">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="O145" s="22">
-        <v>0</v>
-      </c>
-      <c r="P145" s="22">
-        <f>IF(PARAM!$C$38="end plate",1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q145" s="22">
-        <v>0</v>
-      </c>
-      <c r="R145" s="22">
-        <v>0</v>
-      </c>
-      <c r="S145" s="22">
-        <f>IF(PARAM!$C$38="end plate",PARAM!$J$44,PARAM!$J$45)</f>
+      <c r="O150" s="22">
+        <v>0</v>
+      </c>
+      <c r="P150" s="22">
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q150" s="22">
+        <v>0</v>
+      </c>
+      <c r="R150" s="22">
+        <v>0</v>
+      </c>
+      <c r="S150" s="22">
+        <f>IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,9,FALSE),0)</f>
         <v>70</v>
       </c>
-      <c r="T145" s="22">
-        <f>IF(PARAM!$C$38="end plate",PARAM!$K$44-1,PARAM!$K$45-1)</f>
+      <c r="T150" s="22">
+        <f>IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,10,FALSE),0)-1</f>
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B146" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C146" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="D146" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="E146" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="F146" s="22" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" s="12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" s="12" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A149" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="B149" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="C149" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="D149" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="E149" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="F149" s="22">
-        <f>(IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(PARAM!$C$35="end plate",IF(PARAM!$C$6="H",PARAM!$G$44,2*PARAM!$G$44),PARAM!$D$45)</f>
-        <v>170</v>
-      </c>
-      <c r="G149" s="22">
-        <v>0</v>
-      </c>
-      <c r="H149" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B150" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="C150" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="D150" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E150" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="F150" s="22">
-        <f>-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(PARAM!$C$36="end plate",IF(PARAM!$C$6="H",PARAM!$G$44,2*PARAM!$G$44),PARAM!$D$45))</f>
-        <v>-160</v>
-      </c>
-      <c r="G150" s="22">
-        <v>0</v>
-      </c>
-      <c r="H150" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B151" s="21" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="C151" s="22" t="s">
-        <v>181</v>
+        <v>227</v>
       </c>
       <c r="D151" s="22" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="E151" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="F151" s="22">
-        <v>0</v>
-      </c>
-      <c r="G151" s="22">
-        <f>(IF(MOD(PARAM!$J$6,180)=0,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2),PARAM!$E$6/2))+IF(PARAM!$C$37="end plate",IF(PARAM!$C$6="H",PARAM!$G$44,2*PARAM!$G$44),PARAM!$D$45)</f>
-        <v>15</v>
-      </c>
-      <c r="H151" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B152" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="C152" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="D152" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="E152" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="F152" s="22">
-        <v>0</v>
-      </c>
-      <c r="G152" s="22">
-        <f>-((IF(MOD(PARAM!$J$6,180)=0,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2),PARAM!$E$6/2))+IF(PARAM!$C$38="end plate",IF(PARAM!$C$6="H",PARAM!$G$44,2*PARAM!$G$44),PARAM!$D$45))</f>
-        <v>-15</v>
-      </c>
-      <c r="H152" s="22">
-        <v>0</v>
+        <v>202</v>
+      </c>
+      <c r="F151" s="22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="12" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" s="12" t="s">
+        <v>229</v>
+      </c>
       <c r="B154" s="21" t="s">
-        <v>216</v>
+        <v>192</v>
+      </c>
+      <c r="C154" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="D154" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="E154" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="F154" s="22">
+        <f>(IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,4,FALSE),0))</f>
+        <v>170</v>
+      </c>
+      <c r="G154" s="22">
+        <v>0</v>
+      </c>
+      <c r="H154" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B155" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="C155" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="D155" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="E155" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="F155" s="22">
+        <f>-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,4,FALSE),0)))</f>
+        <v>-160</v>
+      </c>
+      <c r="G155" s="22">
+        <v>0</v>
+      </c>
+      <c r="H155" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B156" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="C156" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="D156" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="E156" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="F156" s="22">
+        <v>0</v>
+      </c>
+      <c r="G156" s="22">
+        <f>(IF(MOD(PARAM!$J$6,180)=0,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2),PARAM!$E$6/2))+IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,4,FALSE),0))</f>
+        <v>15</v>
+      </c>
+      <c r="H156" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B157" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="C157" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="D157" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="E157" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="F157" s="22">
+        <v>0</v>
+      </c>
+      <c r="G157" s="22">
+        <f>-((IF(MOD(PARAM!$J$6,180)=0,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2),PARAM!$E$6/2))+IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,4,FALSE),0)))</f>
+        <v>-15</v>
+      </c>
+      <c r="H157" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B159" s="21" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -8439,7 +8709,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -8450,7 +8720,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B3" s="28">
         <v>100</v>
@@ -8473,7 +8743,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="B4" s="30">
         <v>125</v>
@@ -8496,7 +8766,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="B5" s="28">
         <v>150</v>
@@ -8519,7 +8789,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="B6" s="30">
         <v>148</v>
@@ -8542,7 +8812,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="B7" s="28">
         <v>150</v>
@@ -8565,7 +8835,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="B8" s="30">
         <v>198</v>
@@ -8588,7 +8858,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="B9" s="28">
         <v>200</v>
@@ -8611,7 +8881,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="B10" s="30">
         <v>194</v>
@@ -8634,7 +8904,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="B11" s="28">
         <v>200</v>
@@ -8657,7 +8927,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="B12" s="30">
         <v>200</v>
@@ -8680,7 +8950,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="B13" s="28">
         <v>248</v>
@@ -8703,7 +8973,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="B14" s="30">
         <v>250</v>
@@ -8726,7 +8996,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="B15" s="28">
         <v>244</v>
@@ -8749,7 +9019,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="B16" s="30">
         <v>250</v>
@@ -8772,7 +9042,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="B17" s="28">
         <v>250</v>
@@ -8795,7 +9065,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="B18" s="30">
         <v>298</v>
@@ -8841,7 +9111,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="B20" s="30">
         <v>294</v>
@@ -8864,7 +9134,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="B21" s="28">
         <v>294</v>
@@ -8910,7 +9180,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="B23" s="28">
         <v>300</v>
@@ -8933,7 +9203,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B24" s="30">
         <v>346</v>
@@ -8956,7 +9226,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="B25" s="28">
         <v>350</v>
@@ -8979,7 +9249,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="B26" s="30">
         <v>340</v>
@@ -9002,7 +9272,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="B27" s="28">
         <v>344</v>
@@ -9025,7 +9295,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="B28" s="30">
         <v>350</v>
@@ -9048,7 +9318,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="B29" s="28">
         <v>396</v>
@@ -9071,7 +9341,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="B30" s="30">
         <v>400</v>
@@ -9094,7 +9364,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="B31" s="28">
         <v>390</v>
@@ -9117,7 +9387,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="B32" s="30">
         <v>388</v>
@@ -9140,7 +9410,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="27" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="B33" s="28">
         <v>394</v>
@@ -9163,7 +9433,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="B34" s="30">
         <v>400</v>
@@ -9186,7 +9456,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="B35" s="28">
         <v>400</v>
@@ -9209,7 +9479,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="B36" s="30">
         <v>414</v>
@@ -9232,7 +9502,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="B37" s="28">
         <v>428</v>
@@ -9255,7 +9525,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="B38" s="30">
         <v>458</v>
@@ -9278,7 +9548,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="B39" s="28">
         <v>498</v>
@@ -9301,7 +9571,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="B40" s="30">
         <v>446</v>
@@ -9324,7 +9594,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="B41" s="28">
         <v>450</v>
@@ -9347,7 +9617,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="B42" s="30">
         <v>440</v>
@@ -9370,7 +9640,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="27" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="B43" s="28">
         <v>440</v>
@@ -9393,7 +9663,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="B44" s="30">
         <v>496</v>
@@ -9416,7 +9686,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B45" s="28">
         <v>500</v>
@@ -9439,7 +9709,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="B46" s="30">
         <v>482</v>
@@ -9462,7 +9732,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="27" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="B47" s="28">
         <v>488</v>
@@ -9485,7 +9755,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="B48" s="30">
         <v>596</v>
@@ -9508,7 +9778,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="B49" s="28">
         <v>600</v>
@@ -9531,7 +9801,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="B50" s="30">
         <v>582</v>
@@ -9554,7 +9824,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="B51" s="28">
         <v>588</v>
@@ -9577,7 +9847,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="B52" s="30">
         <v>594</v>
@@ -9600,7 +9870,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="27" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="B53" s="28">
         <v>692</v>
@@ -9623,7 +9893,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="B54" s="30">
         <v>700</v>
@@ -9646,7 +9916,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="B55" s="28">
         <v>792</v>
@@ -9669,7 +9939,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="B56" s="30">
         <v>800</v>
@@ -9692,7 +9962,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="27" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="B57" s="28">
         <v>890</v>
@@ -9715,7 +9985,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="B58" s="30">
         <v>900</v>
@@ -9738,7 +10008,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="B59" s="28">
         <v>912</v>
@@ -9761,7 +10031,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="B60" s="30">
         <v>918</v>
@@ -9821,7 +10091,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -9832,7 +10102,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="B3" s="28">
         <v>20</v>
@@ -9855,7 +10125,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="B4" s="30">
         <v>20</v>
@@ -9878,7 +10148,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="B5" s="28">
         <v>25</v>
@@ -9901,7 +10171,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="B6" s="30">
         <v>25</v>
@@ -9924,7 +10194,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="B7" s="28">
         <v>30</v>
@@ -9947,7 +10217,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="B8" s="30">
         <v>30</v>
@@ -9970,7 +10240,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="B9" s="28">
         <v>40</v>
@@ -9993,7 +10263,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="B10" s="30">
         <v>40</v>
@@ -10016,7 +10286,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="B11" s="28">
         <v>50</v>
@@ -10039,7 +10309,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="B12" s="30">
         <v>50</v>
@@ -10062,7 +10332,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="B13" s="28">
         <v>50</v>
@@ -10085,7 +10355,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="B14" s="30">
         <v>60</v>
@@ -10108,7 +10378,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="B15" s="28">
         <v>60</v>
@@ -10131,7 +10401,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="B16" s="30">
         <v>60</v>
@@ -10154,7 +10424,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="B17" s="28">
         <v>75</v>
@@ -10177,7 +10447,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="B18" s="30">
         <v>75</v>
@@ -10200,7 +10470,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="B19" s="28">
         <v>75</v>
@@ -10223,7 +10493,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B20" s="30">
         <v>75</v>
@@ -10246,7 +10516,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="B21" s="28">
         <v>80</v>
@@ -10269,7 +10539,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="B22" s="30">
         <v>80</v>
@@ -10292,7 +10562,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="B23" s="28">
         <v>80</v>
@@ -10315,7 +10585,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B24" s="30">
         <v>90</v>
@@ -10338,7 +10608,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="B25" s="28">
         <v>90</v>
@@ -10361,7 +10631,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="B26" s="30">
         <v>100</v>
@@ -10384,7 +10654,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="B27" s="28">
         <v>100</v>
@@ -10407,7 +10677,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="B28" s="30">
         <v>100</v>
@@ -10430,7 +10700,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="B29" s="28">
         <v>100</v>
@@ -10453,7 +10723,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="B30" s="30">
         <v>100</v>
@@ -10476,7 +10746,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="B31" s="28">
         <v>100</v>
@@ -10499,7 +10769,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="B32" s="30">
         <v>100</v>
@@ -10522,7 +10792,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="27" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="B33" s="28">
         <v>125</v>
@@ -10545,7 +10815,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="B34" s="30">
         <v>125</v>
@@ -10568,7 +10838,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="B35" s="28">
         <v>125</v>
@@ -10591,7 +10861,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="B36" s="30">
         <v>125</v>
@@ -10614,7 +10884,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="B37" s="28">
         <v>125</v>
@@ -10637,7 +10907,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="B38" s="30">
         <v>125</v>
@@ -10660,7 +10930,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="B39" s="28">
         <v>150</v>
@@ -10683,7 +10953,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="B40" s="30">
         <v>150</v>
@@ -10706,7 +10976,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="B41" s="28">
         <v>150</v>
@@ -10729,7 +10999,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="B42" s="30">
         <v>150</v>
@@ -10752,7 +11022,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="27" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="B43" s="28">
         <v>175</v>
@@ -10775,7 +11045,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="B44" s="30">
         <v>175</v>
@@ -10798,7 +11068,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="B45" s="28">
         <v>175</v>
@@ -10821,7 +11091,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="B46" s="30">
         <v>200</v>
@@ -10844,7 +11114,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="27" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="B47" s="28">
         <v>200</v>
@@ -10867,7 +11137,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="B48" s="30">
         <v>200</v>
@@ -10890,7 +11160,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="B49" s="28">
         <v>200</v>
@@ -10913,7 +11183,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="B50" s="30">
         <v>200</v>
@@ -10936,7 +11206,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="B51" s="28">
         <v>250</v>
@@ -10959,7 +11229,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="B52" s="30">
         <v>250</v>
@@ -10982,7 +11252,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="27" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="B53" s="28">
         <v>250</v>
@@ -11005,7 +11275,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="B54" s="30">
         <v>250</v>
@@ -11028,7 +11298,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="B55" s="28">
         <v>250</v>
@@ -11051,7 +11321,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="B56" s="30">
         <v>300</v>
@@ -11074,7 +11344,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="27" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="B57" s="28">
         <v>300</v>
@@ -11097,7 +11367,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="B58" s="30">
         <v>300</v>
@@ -11120,7 +11390,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="B59" s="28">
         <v>300</v>
@@ -11143,7 +11413,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="B60" s="30">
         <v>200</v>
@@ -11166,7 +11436,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="27" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="B61" s="28">
         <v>200</v>
@@ -11189,7 +11459,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="29" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="B62" s="30">
         <v>200</v>
@@ -11212,7 +11482,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="27" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="B63" s="28">
         <v>200</v>
@@ -11235,7 +11505,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="29" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="B64" s="30">
         <v>250</v>
@@ -11258,7 +11528,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="27" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="B65" s="28">
         <v>250</v>
@@ -11281,7 +11551,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="29" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="B66" s="30">
         <v>250</v>
@@ -11304,7 +11574,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="27" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="B67" s="28">
         <v>250</v>
@@ -11327,7 +11597,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="29" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="B68" s="30">
         <v>250</v>
@@ -11350,7 +11620,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="27" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="B69" s="28">
         <v>250</v>
@@ -11373,7 +11643,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="29" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B70" s="30">
         <v>300</v>
@@ -11396,7 +11666,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="27" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="B71" s="28">
         <v>300</v>
@@ -11419,7 +11689,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="29" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="B72" s="30">
         <v>300</v>
@@ -11442,7 +11712,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="27" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="B73" s="28">
         <v>300</v>
@@ -11465,7 +11735,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="29" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="B74" s="30">
         <v>300</v>
@@ -11488,7 +11758,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="27" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="B75" s="28">
         <v>300</v>
@@ -11511,7 +11781,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="29" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="B76" s="30">
         <v>300</v>
@@ -11534,7 +11804,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="27" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="B77" s="28">
         <v>350</v>
@@ -11557,7 +11827,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="29" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="B78" s="30">
         <v>350</v>
@@ -11580,7 +11850,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="27" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="B79" s="28">
         <v>350</v>
@@ -11603,7 +11873,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="29" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B80" s="30">
         <v>350</v>
@@ -11626,7 +11896,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="27" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="B81" s="28">
         <v>350</v>
@@ -11649,7 +11919,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="29" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="B82" s="30">
         <v>350</v>
@@ -11672,7 +11942,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="27" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B83" s="28">
         <v>400</v>
@@ -11695,7 +11965,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="29" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="B84" s="30">
         <v>400</v>
@@ -11718,7 +11988,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="27" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="B85" s="28">
         <v>400</v>
@@ -11741,7 +12011,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="29" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="B86" s="30">
         <v>400</v>
@@ -11764,7 +12034,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="27" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="B87" s="28">
         <v>400</v>
@@ -11787,7 +12057,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="29" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B88" s="30">
         <v>400</v>
@@ -11810,7 +12080,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="27" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="B89" s="28">
         <v>450</v>
@@ -11833,7 +12103,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="29" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B90" s="30">
         <v>450</v>
@@ -11856,7 +12126,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="27" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="B91" s="28">
         <v>450</v>
@@ -11879,7 +12149,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="29" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="B92" s="30">
         <v>450</v>
@@ -11902,7 +12172,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="27" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="B93" s="28">
         <v>450</v>
@@ -11925,7 +12195,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="29" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="B94" s="30">
         <v>450</v>
@@ -11948,7 +12218,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="27" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="B95" s="28">
         <v>500</v>
@@ -11971,7 +12241,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="29" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="B96" s="30">
         <v>500</v>
@@ -11994,7 +12264,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="27" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="B97" s="28">
         <v>500</v>
@@ -12017,7 +12287,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="29" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="B98" s="30">
         <v>500</v>
@@ -12040,7 +12310,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="27" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="B99" s="28">
         <v>500</v>
@@ -12063,7 +12333,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="29" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="B100" s="30">
         <v>500</v>
@@ -12086,7 +12356,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="27" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="B101" s="28">
         <v>550</v>
@@ -12109,7 +12379,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="29" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="B102" s="30">
         <v>550</v>
@@ -12132,7 +12402,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="27" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="B103" s="28">
         <v>550</v>
@@ -12155,7 +12425,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="29" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="B104" s="30">
         <v>550</v>
@@ -12178,7 +12448,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="27" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="B105" s="28">
         <v>550</v>
@@ -12201,7 +12471,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="29" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B106" s="30">
         <v>600</v>
@@ -12224,7 +12494,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="27" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="B107" s="28">
         <v>600</v>
@@ -12247,7 +12517,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="29" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="B108" s="30">
         <v>600</v>
@@ -12270,7 +12540,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="27" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="B109" s="28">
         <v>600</v>
@@ -12293,7 +12563,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="29" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="B110" s="30">
         <v>600</v>
@@ -12316,7 +12586,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="27" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="B111" s="28">
         <v>600</v>
@@ -12339,7 +12609,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="29" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="B112" s="30">
         <v>600</v>
@@ -12362,7 +12632,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="27" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="B113" s="28">
         <v>600</v>
@@ -12385,7 +12655,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="29" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="B114" s="30">
         <v>600</v>
@@ -12408,7 +12678,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="27" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="B115" s="28">
         <v>600</v>
@@ -12431,7 +12701,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="29" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="B116" s="30">
         <v>600</v>
@@ -12454,7 +12724,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="27" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="B117" s="28">
         <v>650</v>
@@ -12477,7 +12747,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="29" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="B118" s="30">
         <v>650</v>
@@ -12500,7 +12770,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="27" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="B119" s="28">
         <v>650</v>
@@ -12523,7 +12793,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="29" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="B120" s="30">
         <v>650</v>
@@ -12546,7 +12816,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="27" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="B121" s="28">
         <v>650</v>
@@ -12569,7 +12839,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="29" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B122" s="30">
         <v>650</v>
@@ -12592,7 +12862,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="27" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="B123" s="28">
         <v>650</v>
@@ -12615,7 +12885,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="29" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="B124" s="30">
         <v>650</v>
@@ -12638,7 +12908,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="27" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="B125" s="28">
         <v>650</v>
@@ -12661,7 +12931,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="29" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="B126" s="30">
         <v>650</v>
@@ -12684,7 +12954,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="27" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="B127" s="28">
         <v>700</v>
@@ -12707,7 +12977,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="29" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="B128" s="30">
         <v>700</v>
@@ -12730,7 +13000,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="27" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="B129" s="28">
         <v>700</v>
@@ -12753,7 +13023,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="29" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="B130" s="30">
         <v>700</v>
@@ -12776,7 +13046,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="27" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="B131" s="28">
         <v>700</v>
@@ -12799,7 +13069,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="29" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="B132" s="30">
         <v>700</v>
@@ -12822,7 +13092,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="27" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="B133" s="28">
         <v>700</v>
@@ -12845,7 +13115,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="29" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="B134" s="30">
         <v>700</v>
@@ -12868,7 +13138,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="27" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="B135" s="28">
         <v>700</v>
@@ -12891,7 +13161,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="29" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="B136" s="30">
         <v>700</v>
@@ -12914,7 +13184,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="27" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="B137" s="28">
         <v>750</v>
@@ -12937,7 +13207,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="29" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="B138" s="30">
         <v>750</v>
@@ -12960,7 +13230,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="27" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="B139" s="28">
         <v>750</v>
@@ -12983,7 +13253,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="29" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="B140" s="30">
         <v>750</v>
@@ -13006,7 +13276,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="27" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="B141" s="28">
         <v>750</v>
@@ -13029,7 +13299,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="29" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="B142" s="30">
         <v>750</v>
@@ -13052,7 +13322,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="27" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="B143" s="28">
         <v>750</v>
@@ -13075,7 +13345,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="29" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="B144" s="30">
         <v>750</v>
@@ -13098,7 +13368,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="27" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="B145" s="28">
         <v>750</v>
@@ -13121,7 +13391,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="29" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="B146" s="30">
         <v>800</v>
@@ -13144,7 +13414,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="27" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="B147" s="28">
         <v>800</v>
@@ -13167,7 +13437,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="29" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="B148" s="30">
         <v>800</v>
@@ -13190,7 +13460,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="27" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="B149" s="28">
         <v>800</v>
@@ -13213,7 +13483,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="29" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="B150" s="30">
         <v>800</v>
@@ -13236,7 +13506,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="27" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="B151" s="28">
         <v>800</v>
@@ -13259,7 +13529,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="29" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="B152" s="30">
         <v>800</v>
@@ -13282,7 +13552,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="27" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="B153" s="28">
         <v>800</v>
@@ -13305,7 +13575,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="29" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="B154" s="30">
         <v>800</v>

--- a/plate3d/PLATE3D_COLUMN.xlsx
+++ b/plate3d/PLATE3D_COLUMN.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="441">
   <si>
     <t>COLUMN</t>
   </si>
@@ -285,6 +285,9 @@
   </si>
   <si>
     <t>width</t>
+  </si>
+  <si>
+    <t>height</t>
   </si>
   <si>
     <t>thick</t>
@@ -1997,15 +2000,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K64"/>
+  <dimension ref="B1:L64"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="10" width="10" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="3" customWidth="1"/>
+    <col min="5" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
@@ -2018,7 +2021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" ht="20" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
@@ -2033,6 +2036,7 @@
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
     </row>
     <row r="5" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C5" s="5" t="s">
@@ -2124,7 +2128,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>20</v>
       </c>
@@ -2140,8 +2144,9 @@
       <c r="I8" s="11"/>
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L8" s="11"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
         <v>23</v>
       </c>
@@ -2154,8 +2159,9 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L9" s="12"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="12" t="s">
         <v>24</v>
       </c>
@@ -2168,6 +2174,7 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
@@ -2195,7 +2202,7 @@
         <v>X</v>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" ht="20" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>29</v>
       </c>
@@ -2210,6 +2217,7 @@
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
     </row>
     <row r="14" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E14" s="5" t="s">
@@ -2331,7 +2339,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="12" t="s">
         <v>42</v>
       </c>
@@ -2344,6 +2352,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="11" t="s">
@@ -2371,7 +2380,7 @@
         <v>ok</v>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="22" ht="20" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
         <v>46</v>
       </c>
@@ -2386,6 +2395,7 @@
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
     </row>
     <row r="23" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E23" s="5" t="s">
@@ -2534,7 +2544,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B30" s="12" t="s">
         <v>65</v>
       </c>
@@ -2547,6 +2557,7 @@
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="11" t="s">
@@ -2574,7 +2585,7 @@
         <v>44 per splice</v>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="33" ht="20" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
         <v>69</v>
       </c>
@@ -2589,6 +2600,7 @@
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
     </row>
     <row r="34" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C34" s="5" t="s">
@@ -2771,7 +2783,7 @@
         <v>36.7</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B39" s="12" t="s">
         <v>80</v>
       </c>
@@ -2784,6 +2796,7 @@
       <c r="I39" s="12"/>
       <c r="J39" s="12"/>
       <c r="K39" s="12"/>
+      <c r="L39" s="12"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="11" t="s">
@@ -2811,7 +2824,7 @@
         <v>3 of 4</v>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" ht="20" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B42" s="3" t="s">
         <v>84</v>
       </c>
@@ -2826,8 +2839,9 @@
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
-    </row>
-    <row r="43" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="L42" s="4"/>
+    </row>
+    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C43" s="5" t="s">
         <v>4</v>
       </c>
@@ -2855,16 +2869,19 @@
       <c r="K43" s="5" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L43" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B44" s="6" t="s">
         <v>74</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D44" s="20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E44" s="8">
         <v>0</v>
@@ -2872,31 +2889,35 @@
       <c r="F44" s="8">
         <v>230</v>
       </c>
-      <c r="G44" s="8">
+      <c r="G44" s="17">
+        <f>K44*(L44-1)+2*J44</f>
+        <v>230</v>
+      </c>
+      <c r="H44" s="8">
         <v>20</v>
       </c>
-      <c r="H44" s="8">
+      <c r="I44" s="8">
         <v>140</v>
       </c>
-      <c r="I44" s="8">
+      <c r="J44" s="8">
         <v>45</v>
       </c>
-      <c r="J44" s="8">
+      <c r="K44" s="8">
         <v>70</v>
       </c>
-      <c r="K44" s="8">
+      <c r="L44" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B45" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E45" s="8">
         <v>0</v>
@@ -2904,31 +2925,35 @@
       <c r="F45" s="8">
         <v>230</v>
       </c>
-      <c r="G45" s="8">
+      <c r="G45" s="17">
+        <f>K45*(L45-1)+2*J45</f>
+        <v>300</v>
+      </c>
+      <c r="H45" s="8">
         <v>20</v>
       </c>
-      <c r="H45" s="8">
+      <c r="I45" s="8">
         <v>140</v>
       </c>
-      <c r="I45" s="8">
+      <c r="J45" s="8">
         <v>45</v>
       </c>
-      <c r="J45" s="8">
+      <c r="K45" s="8">
         <v>70</v>
       </c>
-      <c r="K45" s="8">
+      <c r="L45" s="8">
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B46" s="6" t="s">
         <v>77</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E46" s="8">
         <v>10</v>
@@ -2936,31 +2961,35 @@
       <c r="F46" s="8">
         <v>140</v>
       </c>
-      <c r="G46" s="8">
+      <c r="G46" s="17">
+        <f>K46*(L46-1)+2*J46</f>
+        <v>230</v>
+      </c>
+      <c r="H46" s="8">
         <v>10</v>
       </c>
-      <c r="H46" s="8">
+      <c r="I46" s="8">
         <v>60</v>
       </c>
-      <c r="I46" s="8">
+      <c r="J46" s="8">
         <v>45</v>
       </c>
-      <c r="J46" s="8">
+      <c r="K46" s="8">
         <v>70</v>
       </c>
-      <c r="K46" s="8">
+      <c r="L46" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B47" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E47" s="8">
         <v>10</v>
@@ -2968,31 +2997,35 @@
       <c r="F47" s="8">
         <v>140</v>
       </c>
-      <c r="G47" s="8">
+      <c r="G47" s="17">
+        <f>K47*(L47-1)+2*J47</f>
+        <v>300</v>
+      </c>
+      <c r="H47" s="8">
         <v>10</v>
       </c>
-      <c r="H47" s="8">
+      <c r="I47" s="8">
         <v>60</v>
       </c>
-      <c r="I47" s="8">
+      <c r="J47" s="8">
         <v>45</v>
       </c>
-      <c r="J47" s="8">
+      <c r="K47" s="8">
         <v>70</v>
       </c>
-      <c r="K47" s="8">
+      <c r="L47" s="8">
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B48" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E48" s="8">
         <v>10</v>
@@ -3000,29 +3033,33 @@
       <c r="F48" s="8">
         <v>120</v>
       </c>
-      <c r="G48" s="8">
+      <c r="G48" s="17">
+        <f>K48*(L48-1)+2*J48</f>
+        <v>140</v>
+      </c>
+      <c r="H48" s="8">
         <v>9</v>
       </c>
-      <c r="H48" s="8">
+      <c r="I48" s="8">
         <v>55</v>
       </c>
-      <c r="I48" s="8">
+      <c r="J48" s="8">
         <v>40</v>
       </c>
-      <c r="J48" s="8">
+      <c r="K48" s="8">
         <v>60</v>
       </c>
-      <c r="K48" s="8">
+      <c r="L48" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B49" s="16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E49" s="8">
         <v>0</v>
@@ -3030,7 +3067,8 @@
       <c r="F49" s="8">
         <v>0</v>
       </c>
-      <c r="G49" s="8">
+      <c r="G49" s="17">
+        <f>K49*(L49-1)+2*J49</f>
         <v>0</v>
       </c>
       <c r="H49" s="8">
@@ -3045,10 +3083,13 @@
       <c r="K49" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L49" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
@@ -3059,46 +3100,47 @@
       <c r="I50" s="12"/>
       <c r="J50" s="12"/>
       <c r="K50" s="12"/>
+      <c r="L50" s="12"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D51" s="11" t="str">
         <f>IF(COUNTIF(PARAM!$B$44:$B$49,PARAM!$C$35)+COUNTIF(PARAM!$B$44:$B$49,PARAM!$C$36)+COUNTIF(PARAM!$B$44:$B$49,PARAM!$C$37)+COUNTIF(PARAM!$B$44:$B$49,PARAM!$C$38)=4,"all 4 beams found theirs","a beam names a mark that is not in the list")</f>
         <v>all 4 beams found theirs</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F51" s="11" t="str">
         <f>IF(NOT(PARAM!$C$6="H"),"n/a",IF(SUMPRODUCT(MAX((PARAM!$C$44:$C$49="end plate")*(PARAM!$F$44:$F$49)))&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"fits between the flanges","hits the flanges on a web face"))</f>
         <v>fits between the flanges</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H51" s="11" t="str">
-        <f>"M"&amp;PARAM!$E$24&amp;" L"&amp;MAX(IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0))+1.1*PARAM!$E$24,5),IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$35+1.1*PARAM!$E$24,5),0)),IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0))+1.1*PARAM!$E$24,5),IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$36+1.1*PARAM!$E$24,5),0)),IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0))+1.1*PARAM!$E$24,5),IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$37+1.1*PARAM!$E$24,5),0)),IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0))+1.1*PARAM!$E$24,5),IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$38+1.1*PARAM!$E$24,5),0)))</f>
+        <f>"M"&amp;PARAM!$E$24&amp;" L"&amp;MAX(IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0))+1.1*PARAM!$E$24,5),IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$35+1.1*PARAM!$E$24,5),0)),IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0))+1.1*PARAM!$E$24,5),IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$36+1.1*PARAM!$E$24,5),0)),IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0))+1.1*PARAM!$E$24,5),IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$37+1.1*PARAM!$E$24,5),0)),IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0))+1.1*PARAM!$E$24,5),IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$38+1.1*PARAM!$E$24,5),0)))</f>
         <v>M16 L55</v>
       </c>
       <c r="I51" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J51" s="11" t="str">
         <f>IF(NOT(PARAM!$C$6="H"),"n/a",IF(MOD(PARAM!$J$6,180)=0,IF(MAX(PARAM!$F$37,PARAM!$F$38)&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"ok","strip the beam flange"),IF(MAX(PARAM!$F$35,PARAM!$F$36)&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"ok","strip the beam flange")))</f>
         <v>ok</v>
       </c>
     </row>
-    <row r="53" ht="20" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="53" ht="20" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B53" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -3108,30 +3150,31 @@
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
       <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
     </row>
     <row r="54" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D54" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>88</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B55" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D55" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E55" s="8">
         <v>145.5</v>
@@ -3148,10 +3191,10 @@
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B56" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D56" s="20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E56" s="8">
         <v>-145.5</v>
@@ -3168,7 +3211,7 @@
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B57" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D57" s="20"/>
       <c r="E57" s="8">
@@ -3186,7 +3229,7 @@
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B58" s="16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D58" s="20"/>
       <c r="E58" s="8">
@@ -3204,7 +3247,7 @@
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B59" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D59" s="20"/>
       <c r="E59" s="8">
@@ -3222,7 +3265,7 @@
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B60" s="16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D60" s="20"/>
       <c r="E60" s="8">
@@ -3240,7 +3283,7 @@
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B61" s="16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D61" s="20"/>
       <c r="E61" s="8">
@@ -3258,7 +3301,7 @@
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B62" s="16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D62" s="20"/>
       <c r="E62" s="8">
@@ -3274,9 +3317,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B63" s="12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C63" s="12"/>
       <c r="D63" s="12"/>
@@ -3287,27 +3330,28 @@
       <c r="I63" s="12"/>
       <c r="J63" s="12"/>
       <c r="K63" s="12"/>
+      <c r="L63" s="12"/>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B64" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D64" s="11" t="str">
         <f>IF(PARAM!$C$6="H",IF($H$55&gt;0,2,0)+IF($H$56&gt;0,2,0)+IF($H$57&gt;0,2,0)+IF($H$58&gt;0,2,0)+IF($H$59&gt;0,2,0)+IF($H$60&gt;0,2,0)+IF($H$61&gt;0,2,0)+IF($H$62&gt;0,2,0),0)&amp;" of 16"</f>
         <v>4 of 16</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F64" s="11" t="str">
         <f>IF(NOT(PARAM!$C$6="H"),"n/a",IF(MAX($F$55:$F$62)&gt;(PARAM!$F$6-PARAM!$G$6)/2,"too wide",IF(MAX($G$55:$G$62)&gt;PARAM!$E$6-2*PARAM!$H$6,"too deep","ok")))</f>
         <v>ok</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H64" s="11" t="str">
         <f>ROUND((PARAM!$E$35-PARAM!$H$35)/2,1)&amp;" / "&amp;ROUND((PARAM!$E$36-PARAM!$H$36)/2,1)&amp;" / "&amp;ROUND((PARAM!$E$37-PARAM!$H$37)/2,1)&amp;" / "&amp;ROUND((PARAM!$E$38-PARAM!$H$38)/2,1)</f>
@@ -3316,20 +3360,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="C4:K4"/>
-    <mergeCell ref="E8:K8"/>
-    <mergeCell ref="B9:K9"/>
-    <mergeCell ref="B10:K10"/>
-    <mergeCell ref="C13:K13"/>
-    <mergeCell ref="B19:K19"/>
-    <mergeCell ref="C22:K22"/>
-    <mergeCell ref="B30:K30"/>
-    <mergeCell ref="C33:K33"/>
-    <mergeCell ref="B39:K39"/>
-    <mergeCell ref="C42:K42"/>
-    <mergeCell ref="B50:K50"/>
-    <mergeCell ref="C53:K53"/>
-    <mergeCell ref="B63:K63"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="E8:L8"/>
+    <mergeCell ref="B9:L9"/>
+    <mergeCell ref="B10:L10"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="B19:L19"/>
+    <mergeCell ref="C22:L22"/>
+    <mergeCell ref="B30:L30"/>
+    <mergeCell ref="C33:L33"/>
+    <mergeCell ref="B39:L39"/>
+    <mergeCell ref="C42:L42"/>
+    <mergeCell ref="B50:L50"/>
+    <mergeCell ref="C53:L53"/>
+    <mergeCell ref="B63:L63"/>
   </mergeCells>
   <conditionalFormatting sqref="B15:K17">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -3408,30 +3452,30 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="21" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -3439,10 +3483,10 @@
         <v>17</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D6" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3457,7 +3501,7 @@
         <v>H</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H6" s="22">
         <f>PARAM!$E$6</f>
@@ -3493,10 +3537,10 @@
         <v>18</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D7" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3511,7 +3555,7 @@
         <v>H</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H7" s="22">
         <f>PARAM!$E$6</f>
@@ -3547,10 +3591,10 @@
         <v>19</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D8" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3565,7 +3609,7 @@
         <v>H</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H8" s="22">
         <f>PARAM!$E$6</f>
@@ -3598,23 +3642,23 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D11" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3625,10 +3669,10 @@
         <v>12</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H11" s="22">
         <f>IF(PARAM!$C$6="H",PARAM!$E$15,PARAM!$E$18)</f>
@@ -3641,13 +3685,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3658,10 +3702,10 @@
         <v>10</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H12" s="22">
         <f>PARAM!$E$16</f>
@@ -3674,13 +3718,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D13" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3691,10 +3735,10 @@
         <v>10</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H13" s="22">
         <f>PARAM!$E$17</f>
@@ -3707,13 +3751,13 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D14" s="22" t="str">
         <f>PARAM!$G$24</f>
@@ -3745,13 +3789,13 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D15" s="22" t="str">
         <f>PARAM!$G$24</f>
@@ -3783,28 +3827,28 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D19" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3815,10 +3859,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H19" s="22">
         <f>MAX(1,PARAM!$G$55)</f>
@@ -3831,10 +3875,10 @@
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D20" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3845,10 +3889,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H20" s="22">
         <f>MAX(1,PARAM!$G$56)</f>
@@ -3861,10 +3905,10 @@
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D21" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3875,10 +3919,10 @@
         <v>1</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H21" s="22">
         <f>MAX(1,PARAM!$G$57)</f>
@@ -3891,10 +3935,10 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D22" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3905,10 +3949,10 @@
         <v>1</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H22" s="22">
         <f>MAX(1,PARAM!$G$58)</f>
@@ -3921,10 +3965,10 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D23" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3935,10 +3979,10 @@
         <v>1</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H23" s="22">
         <f>MAX(1,PARAM!$G$59)</f>
@@ -3951,10 +3995,10 @@
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D24" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3965,10 +4009,10 @@
         <v>1</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H24" s="22">
         <f>MAX(1,PARAM!$G$60)</f>
@@ -3981,10 +4025,10 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D25" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3995,10 +4039,10 @@
         <v>1</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G25" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H25" s="22">
         <f>MAX(1,PARAM!$G$61)</f>
@@ -4011,10 +4055,10 @@
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D26" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -4025,10 +4069,10 @@
         <v>1</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H26" s="22">
         <f>MAX(1,PARAM!$G$62)</f>
@@ -4041,28 +4085,28 @@
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D30" s="22" t="str">
         <f>IF(PARAM!$E$7&gt;0,"sc.c1","")</f>
@@ -4079,7 +4123,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J30" s="22">
         <v>0</v>
@@ -4093,27 +4137,27 @@
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D32" s="22" t="str">
         <f>"sc.c2"</f>
@@ -4130,7 +4174,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J32" s="22">
         <v>0</v>
@@ -4144,27 +4188,27 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C33" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="D33" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="D33" s="22" t="s">
-        <v>172</v>
-      </c>
       <c r="E33" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F33" s="22" t="s">
         <v>139</v>
-      </c>
-      <c r="F33" s="22" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D34" s="22" t="str">
         <f>IF(PARAM!$I$7&gt;0,"sc.c3","")</f>
@@ -4181,7 +4225,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J34" s="22">
         <v>0</v>
@@ -4195,47 +4239,47 @@
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D38" s="22" t="str">
         <f>IF(PARAM!$E$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F38" s="22">
         <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$15/2)),0)</f>
@@ -4255,17 +4299,17 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D39" s="22" t="str">
         <f>IF(PARAM!$E$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F39" s="22">
         <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$15/2)),0)</f>
@@ -4285,20 +4329,20 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="C40" s="22" t="s">
         <v>178</v>
-      </c>
-      <c r="B40" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="C40" s="22" t="s">
-        <v>177</v>
       </c>
       <c r="D40" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F40" s="22">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -4312,22 +4356,22 @@
         <v>0</v>
       </c>
       <c r="I40" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B41" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D41" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F41" s="22">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -4341,22 +4385,22 @@
         <v>0</v>
       </c>
       <c r="I41" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D42" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F42" s="22">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -4370,22 +4414,22 @@
         <v>0</v>
       </c>
       <c r="I42" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D43" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F43" s="22">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -4399,25 +4443,25 @@
         <v>0</v>
       </c>
       <c r="I43" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D44" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F44" s="22">
         <v>0</v>
@@ -4430,22 +4474,22 @@
         <v>0</v>
       </c>
       <c r="I44" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B45" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D45" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F45" s="22">
         <v>0</v>
@@ -4458,18 +4502,18 @@
         <v>0</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D46" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4489,7 +4533,7 @@
         <v>35</v>
       </c>
       <c r="I46" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J46" s="22">
         <v>0</v>
@@ -4531,10 +4575,10 @@
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B47" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D47" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4554,7 +4598,7 @@
         <v>35</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J47" s="22">
         <v>0</v>
@@ -4596,10 +4640,10 @@
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B48" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D48" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4619,7 +4663,7 @@
         <v>-35</v>
       </c>
       <c r="I48" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J48" s="22">
         <v>0</v>
@@ -4661,10 +4705,10 @@
     </row>
     <row r="49" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B49" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D49" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4684,7 +4728,7 @@
         <v>-35</v>
       </c>
       <c r="I49" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J49" s="22">
         <v>0</v>
@@ -4726,10 +4770,10 @@
     </row>
     <row r="50" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B50" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D50" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4749,7 +4793,7 @@
         <v>35</v>
       </c>
       <c r="I50" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J50" s="22">
         <v>0</v>
@@ -4791,10 +4835,10 @@
     </row>
     <row r="51" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B51" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D51" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4814,7 +4858,7 @@
         <v>35</v>
       </c>
       <c r="I51" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J51" s="22">
         <v>0</v>
@@ -4856,10 +4900,10 @@
     </row>
     <row r="52" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B52" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D52" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4879,7 +4923,7 @@
         <v>-35</v>
       </c>
       <c r="I52" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J52" s="22">
         <v>0</v>
@@ -4921,10 +4965,10 @@
     </row>
     <row r="53" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B53" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D53" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4944,7 +4988,7 @@
         <v>-35</v>
       </c>
       <c r="I53" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J53" s="22">
         <v>0</v>
@@ -4986,13 +5030,13 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D54" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -5012,7 +5056,7 @@
         <v>-10</v>
       </c>
       <c r="I54" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J54" s="22">
         <v>0</v>
@@ -5040,10 +5084,10 @@
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B55" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D55" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -5063,7 +5107,7 @@
         <v>-10</v>
       </c>
       <c r="I55" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J55" s="22">
         <v>0</v>
@@ -5091,13 +5135,13 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D56" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$29&gt;2),"bo.f","")</f>
@@ -5117,7 +5161,7 @@
         <v>-10</v>
       </c>
       <c r="I56" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J56" s="22">
         <v>0</v>
@@ -5145,10 +5189,10 @@
     </row>
     <row r="57" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B57" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D57" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$29&gt;2),"bo.f","")</f>
@@ -5168,7 +5212,7 @@
         <v>-10</v>
       </c>
       <c r="I57" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J57" s="22">
         <v>0</v>
@@ -5196,13 +5240,13 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D58" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -5222,7 +5266,7 @@
         <v>30</v>
       </c>
       <c r="I58" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J58" s="22">
         <v>0</v>
@@ -5264,10 +5308,10 @@
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B59" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D59" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -5287,7 +5331,7 @@
         <v>-30</v>
       </c>
       <c r="I59" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J59" s="22">
         <v>0</v>
@@ -5329,34 +5373,34 @@
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B60" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D60" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E60" s="22" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F60" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B61" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D61" s="22" t="str">
         <f>IF(PARAM!$I$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E61" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F61" s="22">
         <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$15/2)),0)</f>
@@ -5376,17 +5420,17 @@
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B62" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D62" s="22" t="str">
         <f>IF(PARAM!$I$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F62" s="22">
         <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$15/2)),0)</f>
@@ -5406,17 +5450,17 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B63" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D63" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E63" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F63" s="22">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -5430,22 +5474,22 @@
         <v>0</v>
       </c>
       <c r="I63" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B64" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D64" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E64" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F64" s="22">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -5459,22 +5503,22 @@
         <v>0</v>
       </c>
       <c r="I64" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B65" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D65" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E65" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F65" s="22">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -5488,22 +5532,22 @@
         <v>0</v>
       </c>
       <c r="I65" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B66" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C66" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D66" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E66" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F66" s="22">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
@@ -5517,22 +5561,22 @@
         <v>0</v>
       </c>
       <c r="I66" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B67" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C67" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D67" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E67" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F67" s="22">
         <v>0</v>
@@ -5545,22 +5589,22 @@
         <v>0</v>
       </c>
       <c r="I67" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B68" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D68" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F68" s="22">
         <v>0</v>
@@ -5573,15 +5617,15 @@
         <v>0</v>
       </c>
       <c r="I68" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B69" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D69" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5601,7 +5645,7 @@
         <v>35</v>
       </c>
       <c r="I69" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J69" s="22">
         <v>0</v>
@@ -5643,10 +5687,10 @@
     </row>
     <row r="70" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B70" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D70" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5666,7 +5710,7 @@
         <v>35</v>
       </c>
       <c r="I70" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J70" s="22">
         <v>0</v>
@@ -5708,10 +5752,10 @@
     </row>
     <row r="71" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B71" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D71" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5731,7 +5775,7 @@
         <v>-35</v>
       </c>
       <c r="I71" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J71" s="22">
         <v>0</v>
@@ -5773,10 +5817,10 @@
     </row>
     <row r="72" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B72" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D72" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5796,7 +5840,7 @@
         <v>-35</v>
       </c>
       <c r="I72" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J72" s="22">
         <v>0</v>
@@ -5838,10 +5882,10 @@
     </row>
     <row r="73" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B73" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D73" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5861,7 +5905,7 @@
         <v>35</v>
       </c>
       <c r="I73" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J73" s="22">
         <v>0</v>
@@ -5903,10 +5947,10 @@
     </row>
     <row r="74" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B74" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C74" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D74" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5926,7 +5970,7 @@
         <v>35</v>
       </c>
       <c r="I74" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J74" s="22">
         <v>0</v>
@@ -5968,10 +6012,10 @@
     </row>
     <row r="75" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B75" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C75" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D75" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5991,7 +6035,7 @@
         <v>-35</v>
       </c>
       <c r="I75" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J75" s="22">
         <v>0</v>
@@ -6033,10 +6077,10 @@
     </row>
     <row r="76" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B76" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C76" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D76" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -6056,7 +6100,7 @@
         <v>-35</v>
       </c>
       <c r="I76" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J76" s="22">
         <v>0</v>
@@ -6098,10 +6142,10 @@
     </row>
     <row r="77" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B77" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D77" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -6121,7 +6165,7 @@
         <v>-10</v>
       </c>
       <c r="I77" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J77" s="22">
         <v>0</v>
@@ -6149,10 +6193,10 @@
     </row>
     <row r="78" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B78" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C78" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D78" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -6172,7 +6216,7 @@
         <v>-10</v>
       </c>
       <c r="I78" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J78" s="22">
         <v>0</v>
@@ -6200,10 +6244,10 @@
     </row>
     <row r="79" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B79" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C79" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D79" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$29&gt;2),"bo.f","")</f>
@@ -6223,7 +6267,7 @@
         <v>-10</v>
       </c>
       <c r="I79" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J79" s="22">
         <v>0</v>
@@ -6251,10 +6295,10 @@
     </row>
     <row r="80" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B80" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C80" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D80" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$29&gt;2),"bo.f","")</f>
@@ -6274,7 +6318,7 @@
         <v>-10</v>
       </c>
       <c r="I80" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J80" s="22">
         <v>0</v>
@@ -6302,10 +6346,10 @@
     </row>
     <row r="81" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B81" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C81" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D81" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -6325,7 +6369,7 @@
         <v>30</v>
       </c>
       <c r="I81" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J81" s="22">
         <v>0</v>
@@ -6367,10 +6411,10 @@
     </row>
     <row r="82" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B82" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C82" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D82" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -6390,7 +6434,7 @@
         <v>-30</v>
       </c>
       <c r="I82" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J82" s="22">
         <v>0</v>
@@ -6432,52 +6476,52 @@
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B83" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C83" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="D83" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="E83" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="D83" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="E83" s="22" t="s">
-        <v>186</v>
-      </c>
       <c r="F83" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B87" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C87" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D87" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$55&gt;0),"pl.stf1","")</f>
         <v>pl.stf1</v>
       </c>
       <c r="E87" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F87" s="22">
         <v>0</v>
@@ -6491,7 +6535,7 @@
         <v>845.5</v>
       </c>
       <c r="I87" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J87" s="22">
         <v>0</v>
@@ -6518,17 +6562,17 @@
     </row>
     <row r="88" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B88" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C88" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D88" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$56&gt;0),"pl.stf2","")</f>
         <v>pl.stf2</v>
       </c>
       <c r="E88" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F88" s="22">
         <v>0</v>
@@ -6542,7 +6586,7 @@
         <v>554.5</v>
       </c>
       <c r="I88" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J88" s="22">
         <v>0</v>
@@ -6569,17 +6613,17 @@
     </row>
     <row r="89" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B89" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C89" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D89" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$57&gt;0),"pl.stf3","")</f>
         <v/>
       </c>
       <c r="E89" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F89" s="22">
         <v>0</v>
@@ -6593,7 +6637,7 @@
         <v>700</v>
       </c>
       <c r="I89" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J89" s="22">
         <v>0</v>
@@ -6620,17 +6664,17 @@
     </row>
     <row r="90" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B90" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C90" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D90" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$58&gt;0),"pl.stf4","")</f>
         <v/>
       </c>
       <c r="E90" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F90" s="22">
         <v>0</v>
@@ -6644,7 +6688,7 @@
         <v>700</v>
       </c>
       <c r="I90" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J90" s="22">
         <v>0</v>
@@ -6671,17 +6715,17 @@
     </row>
     <row r="91" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B91" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C91" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D91" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$59&gt;0),"pl.stf5","")</f>
         <v/>
       </c>
       <c r="E91" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F91" s="22">
         <v>0</v>
@@ -6695,7 +6739,7 @@
         <v>700</v>
       </c>
       <c r="I91" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J91" s="22">
         <v>0</v>
@@ -6722,17 +6766,17 @@
     </row>
     <row r="92" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B92" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C92" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D92" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$60&gt;0),"pl.stf6","")</f>
         <v/>
       </c>
       <c r="E92" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F92" s="22">
         <v>0</v>
@@ -6746,7 +6790,7 @@
         <v>700</v>
       </c>
       <c r="I92" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J92" s="22">
         <v>0</v>
@@ -6773,17 +6817,17 @@
     </row>
     <row r="93" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B93" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C93" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D93" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$61&gt;0),"pl.stf7","")</f>
         <v/>
       </c>
       <c r="E93" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F93" s="22">
         <v>0</v>
@@ -6797,7 +6841,7 @@
         <v>700</v>
       </c>
       <c r="I93" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J93" s="22">
         <v>0</v>
@@ -6824,17 +6868,17 @@
     </row>
     <row r="94" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B94" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C94" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D94" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$62&gt;0),"pl.stf8","")</f>
         <v/>
       </c>
       <c r="E94" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F94" s="22">
         <v>0</v>
@@ -6848,7 +6892,7 @@
         <v>700</v>
       </c>
       <c r="I94" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J94" s="22">
         <v>0</v>
@@ -6875,12 +6919,12 @@
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -6888,16 +6932,16 @@
         <v>18</v>
       </c>
       <c r="B97" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C97" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D97" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E97" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F97" s="22">
         <v>0</v>
@@ -6922,19 +6966,19 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="B98" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="C98" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="D98" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="E98" s="22" t="s">
         <v>195</v>
-      </c>
-      <c r="B98" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="C98" s="22" t="s">
-        <v>193</v>
-      </c>
-      <c r="D98" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="E98" s="22" t="s">
-        <v>194</v>
       </c>
       <c r="F98" s="22">
         <v>0</v>
@@ -6962,16 +7006,16 @@
         <v>19</v>
       </c>
       <c r="B99" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C99" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D99" s="22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E99" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F99" s="22">
         <v>0</v>
@@ -6996,19 +7040,19 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B100" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C100" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D100" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E100" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F100" s="22">
         <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$15/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
@@ -7035,16 +7079,16 @@
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C101" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D101" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E101" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F101" s="22">
         <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$15/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
@@ -7071,23 +7115,23 @@
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B104" s="21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C104" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D104" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7101,7 +7145,7 @@
         <v>14</v>
       </c>
       <c r="G104" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H104" s="22">
         <f>PARAM!$E$35</f>
@@ -7134,10 +7178,10 @@
     </row>
     <row r="105" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B105" s="21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C105" s="22" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D105" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7151,7 +7195,7 @@
         <v>14</v>
       </c>
       <c r="G105" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H105" s="22">
         <f>PARAM!$E$36</f>
@@ -7184,10 +7228,10 @@
     </row>
     <row r="106" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B106" s="21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C106" s="22" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D106" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7201,7 +7245,7 @@
         <v>14</v>
       </c>
       <c r="G106" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H106" s="22">
         <f>PARAM!$E$37</f>
@@ -7234,10 +7278,10 @@
     </row>
     <row r="107" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B107" s="21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C107" s="22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D107" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7251,7 +7295,7 @@
         <v>14</v>
       </c>
       <c r="G107" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H107" s="22">
         <f>PARAM!$E$38</f>
@@ -7284,146 +7328,146 @@
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B110" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C110" s="22" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D110" s="22" t="str">
         <f>PARAM!$C$8</f>
         <v>SS275</v>
       </c>
       <c r="E110" s="22">
-        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0))</f>
+        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0))</f>
         <v>20</v>
       </c>
       <c r="F110" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G110" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H110" s="22">
         <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,5,FALSE),0))</f>
         <v>230</v>
       </c>
       <c r="I110" s="22">
-        <f>MAX(1,(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,9,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,10,FALSE),0)-1)+2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,8,FALSE),0)))</f>
+        <f>MAX(1,(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,11,FALSE),0)-1)+2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,9,FALSE),0)))</f>
         <v>230</v>
       </c>
     </row>
     <row r="111" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B111" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C111" s="22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D111" s="22" t="str">
         <f>PARAM!$C$8</f>
         <v>SS275</v>
       </c>
       <c r="E111" s="22">
-        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0))</f>
+        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0))</f>
         <v>10</v>
       </c>
       <c r="F111" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G111" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H111" s="22">
         <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,5,FALSE),0))</f>
         <v>140</v>
       </c>
       <c r="I111" s="22">
-        <f>MAX(1,(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,9,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,10,FALSE),0)-1)+2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,8,FALSE),0)))</f>
+        <f>MAX(1,(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,11,FALSE),0)-1)+2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,9,FALSE),0)))</f>
         <v>230</v>
       </c>
     </row>
     <row r="112" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B112" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C112" s="22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D112" s="22" t="str">
         <f>PARAM!$C$8</f>
         <v>SS275</v>
       </c>
       <c r="E112" s="22">
-        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0))</f>
+        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0))</f>
         <v>10</v>
       </c>
       <c r="F112" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G112" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H112" s="22">
         <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,5,FALSE),0))</f>
         <v>140</v>
       </c>
       <c r="I112" s="22">
-        <f>MAX(1,(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,9,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,10,FALSE),0)-1)+2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,8,FALSE),0)))</f>
+        <f>MAX(1,(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,11,FALSE),0)-1)+2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,9,FALSE),0)))</f>
         <v>230</v>
       </c>
     </row>
     <row r="113" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B113" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C113" s="22" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D113" s="22" t="str">
         <f>PARAM!$C$8</f>
         <v>SS275</v>
       </c>
       <c r="E113" s="22">
-        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0))</f>
+        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0))</f>
         <v>10</v>
       </c>
       <c r="F113" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G113" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H113" s="22">
         <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,5,FALSE),0))</f>
         <v>140</v>
       </c>
       <c r="I113" s="22">
-        <f>MAX(1,(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,9,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,10,FALSE),0)-1)+2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,8,FALSE),0)))</f>
+        <f>MAX(1,(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,11,FALSE),0)-1)+2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,9,FALSE),0)))</f>
         <v>230</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B114" s="21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C114" s="22" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D114" s="22" t="str">
         <f>PARAM!$G$24</f>
@@ -7434,7 +7478,7 @@
         <v>16</v>
       </c>
       <c r="F114" s="22">
-        <f>MAX(1,CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$35)+1.1*PARAM!$E$24,5))</f>
+        <f>MAX(1,CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$35)+1.1*PARAM!$E$24,5))</f>
         <v>55</v>
       </c>
       <c r="G114" s="22">
@@ -7449,16 +7493,16 @@
         <v>14.4</v>
       </c>
       <c r="L114" s="22">
-        <f>MAX(0,(CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$35)+1.1*PARAM!$E$24,5))-(IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$35))-0.9*PARAM!$E$24)</f>
+        <f>MAX(0,(CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$35)+1.1*PARAM!$E$24,5))-(IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$35))-0.9*PARAM!$E$24)</f>
         <v>5.6</v>
       </c>
     </row>
     <row r="115" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B115" s="21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C115" s="22" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D115" s="22" t="str">
         <f>PARAM!$G$24</f>
@@ -7469,7 +7513,7 @@
         <v>16</v>
       </c>
       <c r="F115" s="22">
-        <f>MAX(1,CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$36)+1.1*PARAM!$E$24,5))</f>
+        <f>MAX(1,CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$36)+1.1*PARAM!$E$24,5))</f>
         <v>35</v>
       </c>
       <c r="G115" s="22">
@@ -7484,16 +7528,16 @@
         <v>14.4</v>
       </c>
       <c r="L115" s="22">
-        <f>MAX(0,(CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$36)+1.1*PARAM!$E$24,5))-(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$36))-0.9*PARAM!$E$24)</f>
+        <f>MAX(0,(CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$36)+1.1*PARAM!$E$24,5))-(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$36))-0.9*PARAM!$E$24)</f>
         <v>4.1</v>
       </c>
     </row>
     <row r="116" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B116" s="21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C116" s="22" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D116" s="22" t="str">
         <f>PARAM!$G$24</f>
@@ -7504,7 +7548,7 @@
         <v>16</v>
       </c>
       <c r="F116" s="22">
-        <f>MAX(1,CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$37)+1.1*PARAM!$E$24,5))</f>
+        <f>MAX(1,CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$37)+1.1*PARAM!$E$24,5))</f>
         <v>35</v>
       </c>
       <c r="G116" s="22">
@@ -7519,16 +7563,16 @@
         <v>14.4</v>
       </c>
       <c r="L116" s="22">
-        <f>MAX(0,(CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$37)+1.1*PARAM!$E$24,5))-(IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$37))-0.9*PARAM!$E$24)</f>
+        <f>MAX(0,(CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$37)+1.1*PARAM!$E$24,5))-(IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$37))-0.9*PARAM!$E$24)</f>
         <v>4.1</v>
       </c>
     </row>
     <row r="117" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B117" s="21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C117" s="22" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D117" s="22" t="str">
         <f>PARAM!$G$24</f>
@@ -7539,7 +7583,7 @@
         <v>16</v>
       </c>
       <c r="F117" s="22">
-        <f>MAX(1,CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$38)+1.1*PARAM!$E$24,5))</f>
+        <f>MAX(1,CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$38)+1.1*PARAM!$E$24,5))</f>
         <v>35</v>
       </c>
       <c r="G117" s="22">
@@ -7554,49 +7598,49 @@
         <v>14.4</v>
       </c>
       <c r="L117" s="22">
-        <f>MAX(0,(CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$38)+1.1*PARAM!$E$24,5))-(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)+PARAM!$G$38))-0.9*PARAM!$E$24)</f>
+        <f>MAX(0,(CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$38)+1.1*PARAM!$E$24,5))-(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$38))-0.9*PARAM!$E$24)</f>
         <v>4.1</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B122" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C122" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D122" s="22" t="str">
         <f>IF(AND(PARAM!$J$35&gt;0,IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),"pl.cna","")</f>
         <v>pl.cna</v>
       </c>
       <c r="E122" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F122" s="22">
-        <f>-IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)/2</f>
+        <f>-IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)/2</f>
         <v>-10</v>
       </c>
       <c r="G122" s="22">
@@ -7607,7 +7651,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J122" s="22">
         <v>0</v>
@@ -7621,23 +7665,23 @@
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="B123" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="C123" s="22" t="s">
         <v>218</v>
-      </c>
-      <c r="B123" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="C123" s="22" t="s">
-        <v>217</v>
       </c>
       <c r="D123" s="22" t="str">
         <f>IF(AND(PARAM!$J$35&gt;0,IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cna","")</f>
         <v/>
       </c>
       <c r="E123" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F123" s="22">
-        <f>-1.5*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)</f>
+        <f>-1.5*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)</f>
         <v>-30</v>
       </c>
       <c r="G123" s="22">
@@ -7648,7 +7692,7 @@
         <v>0</v>
       </c>
       <c r="I123" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J123" s="22">
         <v>0</v>
@@ -7662,34 +7706,34 @@
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B124" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C124" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D124" s="22" t="str">
         <f>IF(AND(PARAM!$J$35&gt;0,IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"),"pl.cna","")</f>
         <v/>
       </c>
       <c r="E124" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F124" s="22">
         <f>IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,4,FALSE),0)</f>
         <v>115</v>
       </c>
       <c r="G124" s="22">
-        <f>PARAM!$G$35/2+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)/2</f>
+        <f>PARAM!$G$35/2+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)/2</f>
         <v>13.25</v>
       </c>
       <c r="H124" s="22">
         <v>0</v>
       </c>
       <c r="I124" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J124" s="22">
         <v>0</v>
@@ -7703,13 +7747,13 @@
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B125" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C125" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D125" s="22" t="str">
         <f>IF(PARAM!$J$35&gt;0,"sc.bma","")</f>
@@ -7726,7 +7770,7 @@
         <v>0</v>
       </c>
       <c r="I125" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J125" s="22">
         <v>0</v>
@@ -7740,13 +7784,13 @@
     </row>
     <row r="126" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B126" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C126" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D126" s="22" t="str">
         <f>IF(OR(PARAM!$J$35&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"))),"","bo.cna")</f>
@@ -7754,15 +7798,15 @@
       </c>
       <c r="E126" s="22"/>
       <c r="F126" s="22">
-        <f>IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6))+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)),-2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)-IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,4,FALSE),0))</f>
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6))+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)),-2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,8,FALSE),0)-IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,4,FALSE),0))</f>
         <v>-35</v>
       </c>
       <c r="G126" s="22">
-        <f>IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",-IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)/2,PARAM!$G$35/2+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0))</f>
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",-IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,8,FALSE),0)/2,PARAM!$G$35/2+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0))</f>
         <v>-70</v>
       </c>
       <c r="H126" s="22">
-        <f>-IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,9,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,10,FALSE),0)-1)/2</f>
+        <f>-IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,11,FALSE),0)-1)/2</f>
         <v>-70</v>
       </c>
       <c r="I126" s="22" t="str">
@@ -7783,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="N126" s="22">
-        <f>IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0),0)</f>
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,8,FALSE),0),0)</f>
         <v>140</v>
       </c>
       <c r="O126" s="22">
@@ -7800,57 +7844,57 @@
         <v>0</v>
       </c>
       <c r="S126" s="22">
-        <f>IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,9,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,10,FALSE),0)</f>
         <v>70</v>
       </c>
       <c r="T126" s="22">
-        <f>IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,10,FALSE),0)-1</f>
+        <f>IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,11,FALSE),0)-1</f>
         <v>2</v>
       </c>
     </row>
     <row r="127" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B127" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C127" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D127" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E127" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F127" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="130" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B130" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C130" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D130" s="22" t="str">
         <f>IF(AND(PARAM!$J$36&gt;0,IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),"pl.cnb","")</f>
         <v/>
       </c>
       <c r="E130" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F130" s="22">
-        <f>-(-IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)/2)</f>
+        <f>-(-IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)/2)</f>
         <v>5</v>
       </c>
       <c r="G130" s="22">
@@ -7861,7 +7905,7 @@
         <v>0</v>
       </c>
       <c r="I130" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J130" s="22">
         <v>0</v>
@@ -7875,20 +7919,20 @@
     </row>
     <row r="131" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B131" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C131" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D131" s="22" t="str">
         <f>IF(AND(PARAM!$J$36&gt;0,IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnb","")</f>
         <v/>
       </c>
       <c r="E131" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F131" s="22">
-        <f>-(-1.5*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0))</f>
+        <f>-(-1.5*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0))</f>
         <v>15</v>
       </c>
       <c r="G131" s="22">
@@ -7899,7 +7943,7 @@
         <v>0</v>
       </c>
       <c r="I131" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J131" s="22">
         <v>0</v>
@@ -7913,31 +7957,31 @@
     </row>
     <row r="132" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B132" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C132" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D132" s="22" t="str">
         <f>IF(AND(PARAM!$J$36&gt;0,IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"),"pl.cnb","")</f>
         <v>pl.cnb</v>
       </c>
       <c r="E132" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F132" s="22">
         <f>-(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,4,FALSE),0))</f>
         <v>-60</v>
       </c>
       <c r="G132" s="22">
-        <f>-(PARAM!$G$36/2+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)/2)</f>
+        <f>-(PARAM!$G$36/2+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)/2)</f>
         <v>-8.25</v>
       </c>
       <c r="H132" s="22">
         <v>0</v>
       </c>
       <c r="I132" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J132" s="22">
         <v>0</v>
@@ -7951,10 +7995,10 @@
     </row>
     <row r="133" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B133" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C133" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D133" s="22" t="str">
         <f>IF(PARAM!$J$36&gt;0,"sc.bmb","")</f>
@@ -7971,7 +8015,7 @@
         <v>0</v>
       </c>
       <c r="I133" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J133" s="22">
         <v>0</v>
@@ -7985,10 +8029,10 @@
     </row>
     <row r="134" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B134" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C134" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D134" s="22" t="str">
         <f>IF(OR(PARAM!$J$36&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"))),"","bo.cnb")</f>
@@ -7996,15 +8040,15 @@
       </c>
       <c r="E134" s="22"/>
       <c r="F134" s="22">
-        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6))+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)),-2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)-IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,4,FALSE),0)))</f>
+        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6))+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)),-2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,8,FALSE),0)-IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,4,FALSE),0)))</f>
         <v>-50</v>
       </c>
       <c r="G134" s="22">
-        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",-IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)/2,PARAM!$G$36/2+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)))</f>
+        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",-IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,8,FALSE),0)/2,PARAM!$G$36/2+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)))</f>
         <v>-13.25</v>
       </c>
       <c r="H134" s="22">
-        <f>-IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,9,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,10,FALSE),0)-1)/2</f>
+        <f>-IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,11,FALSE),0)-1)/2</f>
         <v>-70</v>
       </c>
       <c r="I134" s="22" t="str">
@@ -8025,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="N134" s="22">
-        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0),0))</f>
+        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,8,FALSE),0),0))</f>
         <v>0</v>
       </c>
       <c r="O134" s="22">
@@ -8042,68 +8086,68 @@
         <v>0</v>
       </c>
       <c r="S134" s="22">
-        <f>IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,9,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,10,FALSE),0)</f>
         <v>70</v>
       </c>
       <c r="T134" s="22">
-        <f>IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,10,FALSE),0)-1</f>
+        <f>IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,11,FALSE),0)-1</f>
         <v>2</v>
       </c>
     </row>
     <row r="135" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B135" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C135" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D135" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E135" s="22" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F135" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="138" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B138" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C138" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D138" s="22" t="str">
         <f>IF(AND(PARAM!$J$37&gt;0,IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),"pl.cnc","")</f>
         <v/>
       </c>
       <c r="E138" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F138" s="22">
         <f>0</f>
         <v>0</v>
       </c>
       <c r="G138" s="22">
-        <f>-IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)/2</f>
+        <f>-IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)/2</f>
         <v>-5</v>
       </c>
       <c r="H138" s="22">
         <v>0</v>
       </c>
       <c r="I138" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J138" s="22">
         <v>0</v>
@@ -8117,31 +8161,31 @@
     </row>
     <row r="139" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B139" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C139" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D139" s="22" t="str">
         <f>IF(AND(PARAM!$J$37&gt;0,IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnc","")</f>
         <v/>
       </c>
       <c r="E139" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F139" s="22">
         <f>0</f>
         <v>0</v>
       </c>
       <c r="G139" s="22">
-        <f>-1.5*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)</f>
+        <f>-1.5*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)</f>
         <v>-15</v>
       </c>
       <c r="H139" s="22">
         <v>0</v>
       </c>
       <c r="I139" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J139" s="22">
         <v>0</v>
@@ -8155,20 +8199,20 @@
     </row>
     <row r="140" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B140" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C140" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D140" s="22" t="str">
         <f>IF(AND(PARAM!$J$37&gt;0,IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"),"pl.cnc","")</f>
         <v>pl.cnc</v>
       </c>
       <c r="E140" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F140" s="22">
-        <f>PARAM!$G$37/2+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)/2</f>
+        <f>PARAM!$G$37/2+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)/2</f>
         <v>8.25</v>
       </c>
       <c r="G140" s="22">
@@ -8179,7 +8223,7 @@
         <v>0</v>
       </c>
       <c r="I140" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J140" s="22">
         <v>0</v>
@@ -8193,10 +8237,10 @@
     </row>
     <row r="141" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B141" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C141" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D141" s="22" t="str">
         <f>IF(PARAM!$J$37&gt;0,"sc.bmc","")</f>
@@ -8213,7 +8257,7 @@
         <v>0</v>
       </c>
       <c r="I141" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J141" s="22">
         <v>0</v>
@@ -8227,10 +8271,10 @@
     </row>
     <row r="142" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B142" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C142" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D142" s="22" t="str">
         <f>IF(OR(PARAM!$J$37&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"))),"","bo.cnc")</f>
@@ -8238,15 +8282,15 @@
       </c>
       <c r="E142" s="22"/>
       <c r="F142" s="22">
-        <f>IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",-IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)/2,PARAM!$G$37/2+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0))</f>
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",-IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,8,FALSE),0)/2,PARAM!$G$37/2+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0))</f>
         <v>13.25</v>
       </c>
       <c r="G142" s="22">
-        <f>IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6))+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)),-2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)-IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,4,FALSE),0))</f>
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6))+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)),-2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,8,FALSE),0)-IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,4,FALSE),0))</f>
         <v>50</v>
       </c>
       <c r="H142" s="22">
-        <f>-IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,9,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,10,FALSE),0)-1)/2</f>
+        <f>-IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,11,FALSE),0)-1)/2</f>
         <v>-70</v>
       </c>
       <c r="I142" s="22" t="str">
@@ -8263,7 +8307,7 @@
         <v>180</v>
       </c>
       <c r="M142" s="22">
-        <f>IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0),0)</f>
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,8,FALSE),0),0)</f>
         <v>0</v>
       </c>
       <c r="N142" s="22">
@@ -8284,68 +8328,68 @@
         <v>0</v>
       </c>
       <c r="S142" s="22">
-        <f>IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,9,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,10,FALSE),0)</f>
         <v>70</v>
       </c>
       <c r="T142" s="22">
-        <f>IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,10,FALSE),0)-1</f>
+        <f>IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,11,FALSE),0)-1</f>
         <v>2</v>
       </c>
     </row>
     <row r="143" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B143" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C143" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D143" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E143" s="22" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F143" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="146" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B146" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C146" s="22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D146" s="22" t="str">
         <f>IF(AND(PARAM!$J$38&gt;0,IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),"pl.cnd","")</f>
         <v/>
       </c>
       <c r="E146" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F146" s="22">
         <f>0</f>
         <v>0</v>
       </c>
       <c r="G146" s="22">
-        <f>-(-IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)/2)</f>
+        <f>-(-IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)/2)</f>
         <v>5</v>
       </c>
       <c r="H146" s="22">
         <v>0</v>
       </c>
       <c r="I146" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J146" s="22">
         <v>0</v>
@@ -8359,31 +8403,31 @@
     </row>
     <row r="147" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B147" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C147" s="22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D147" s="22" t="str">
         <f>IF(AND(PARAM!$J$38&gt;0,IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnd","")</f>
         <v/>
       </c>
       <c r="E147" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F147" s="22">
         <f>0</f>
         <v>0</v>
       </c>
       <c r="G147" s="22">
-        <f>-(-1.5*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0))</f>
+        <f>-(-1.5*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0))</f>
         <v>15</v>
       </c>
       <c r="H147" s="22">
         <v>0</v>
       </c>
       <c r="I147" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J147" s="22">
         <v>0</v>
@@ -8397,20 +8441,20 @@
     </row>
     <row r="148" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B148" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C148" s="22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D148" s="22" t="str">
         <f>IF(AND(PARAM!$J$38&gt;0,IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"),"pl.cnd","")</f>
         <v/>
       </c>
       <c r="E148" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F148" s="22">
-        <f>-(PARAM!$G$38/2+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)/2)</f>
+        <f>-(PARAM!$G$38/2+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)/2)</f>
         <v>-8.25</v>
       </c>
       <c r="G148" s="22">
@@ -8421,7 +8465,7 @@
         <v>0</v>
       </c>
       <c r="I148" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J148" s="22">
         <v>0</v>
@@ -8435,10 +8479,10 @@
     </row>
     <row r="149" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B149" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C149" s="22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D149" s="22" t="str">
         <f>IF(PARAM!$J$38&gt;0,"sc.bmd","")</f>
@@ -8455,7 +8499,7 @@
         <v>0</v>
       </c>
       <c r="I149" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J149" s="22">
         <v>0</v>
@@ -8469,10 +8513,10 @@
     </row>
     <row r="150" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B150" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C150" s="22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D150" s="22" t="str">
         <f>IF(OR(PARAM!$J$38&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"))),"","bo.cnd")</f>
@@ -8480,15 +8524,15 @@
       </c>
       <c r="E150" s="22"/>
       <c r="F150" s="22">
-        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",-IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)/2,PARAM!$G$38/2+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)))</f>
+        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",-IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,8,FALSE),0)/2,PARAM!$G$38/2+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)))</f>
         <v>-13.25</v>
       </c>
       <c r="G150" s="22">
-        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6))+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)),-2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)-IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,4,FALSE),0)))</f>
+        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6))+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)),-2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,8,FALSE),0)-IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,4,FALSE),0)))</f>
         <v>-50</v>
       </c>
       <c r="H150" s="22">
-        <f>-IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,9,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,10,FALSE),0)-1)/2</f>
+        <f>-IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,11,FALSE),0)-1)/2</f>
         <v>-70</v>
       </c>
       <c r="I150" s="22" t="str">
@@ -8505,7 +8549,7 @@
         <v>0</v>
       </c>
       <c r="M150" s="22">
-        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0),0))</f>
+        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,8,FALSE),0),0))</f>
         <v>0</v>
       </c>
       <c r="N150" s="22">
@@ -8526,59 +8570,59 @@
         <v>0</v>
       </c>
       <c r="S150" s="22">
-        <f>IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,9,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,10,FALSE),0)</f>
         <v>70</v>
       </c>
       <c r="T150" s="22">
-        <f>IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,10,FALSE),0)-1</f>
+        <f>IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,11,FALSE),0)-1</f>
         <v>2</v>
       </c>
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B151" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C151" s="22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D151" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E151" s="22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F151" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B154" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C154" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D154" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E154" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F154" s="22">
-        <f>(IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,4,FALSE),0))</f>
+        <f>(IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,4,FALSE),0))</f>
         <v>170</v>
       </c>
       <c r="G154" s="22">
@@ -8590,19 +8634,19 @@
     </row>
     <row r="155" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B155" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C155" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D155" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E155" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F155" s="22">
-        <f>-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,4,FALSE),0)))</f>
+        <f>-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,4,FALSE),0)))</f>
         <v>-160</v>
       </c>
       <c r="G155" s="22">
@@ -8614,22 +8658,22 @@
     </row>
     <row r="156" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B156" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C156" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D156" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E156" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F156" s="22">
         <v>0</v>
       </c>
       <c r="G156" s="22">
-        <f>(IF(MOD(PARAM!$J$6,180)=0,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2),PARAM!$E$6/2))+IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,4,FALSE),0))</f>
+        <f>(IF(MOD(PARAM!$J$6,180)=0,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2),PARAM!$E$6/2))+IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,4,FALSE),0))</f>
         <v>15</v>
       </c>
       <c r="H156" s="22">
@@ -8638,22 +8682,22 @@
     </row>
     <row r="157" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B157" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C157" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D157" s="22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E157" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F157" s="22">
         <v>0</v>
       </c>
       <c r="G157" s="22">
-        <f>-((IF(MOD(PARAM!$J$6,180)=0,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2),PARAM!$E$6/2))+IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,6,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,4,FALSE),0)))</f>
+        <f>-((IF(MOD(PARAM!$J$6,180)=0,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2),PARAM!$E$6/2))+IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,4,FALSE),0)))</f>
         <v>-15</v>
       </c>
       <c r="H157" s="22">
@@ -8662,12 +8706,12 @@
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="159" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B159" s="21" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -8709,7 +8753,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -8720,7 +8764,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B3" s="28">
         <v>100</v>
@@ -8743,7 +8787,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B4" s="30">
         <v>125</v>
@@ -8766,7 +8810,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B5" s="28">
         <v>150</v>
@@ -8789,7 +8833,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B6" s="30">
         <v>148</v>
@@ -8812,7 +8856,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B7" s="28">
         <v>150</v>
@@ -8835,7 +8879,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B8" s="30">
         <v>198</v>
@@ -8858,7 +8902,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B9" s="28">
         <v>200</v>
@@ -8881,7 +8925,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B10" s="30">
         <v>194</v>
@@ -8904,7 +8948,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B11" s="28">
         <v>200</v>
@@ -8927,7 +8971,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B12" s="30">
         <v>200</v>
@@ -8950,7 +8994,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B13" s="28">
         <v>248</v>
@@ -8973,7 +9017,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B14" s="30">
         <v>250</v>
@@ -8996,7 +9040,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B15" s="28">
         <v>244</v>
@@ -9019,7 +9063,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B16" s="30">
         <v>250</v>
@@ -9042,7 +9086,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B17" s="28">
         <v>250</v>
@@ -9065,7 +9109,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B18" s="30">
         <v>298</v>
@@ -9111,7 +9155,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B20" s="30">
         <v>294</v>
@@ -9134,7 +9178,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B21" s="28">
         <v>294</v>
@@ -9180,7 +9224,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B23" s="28">
         <v>300</v>
@@ -9203,7 +9247,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B24" s="30">
         <v>346</v>
@@ -9226,7 +9270,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B25" s="28">
         <v>350</v>
@@ -9249,7 +9293,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B26" s="30">
         <v>340</v>
@@ -9272,7 +9316,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B27" s="28">
         <v>344</v>
@@ -9295,7 +9339,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B28" s="30">
         <v>350</v>
@@ -9318,7 +9362,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B29" s="28">
         <v>396</v>
@@ -9341,7 +9385,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B30" s="30">
         <v>400</v>
@@ -9364,7 +9408,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B31" s="28">
         <v>390</v>
@@ -9387,7 +9431,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B32" s="30">
         <v>388</v>
@@ -9410,7 +9454,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="27" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B33" s="28">
         <v>394</v>
@@ -9433,7 +9477,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B34" s="30">
         <v>400</v>
@@ -9456,7 +9500,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B35" s="28">
         <v>400</v>
@@ -9479,7 +9523,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B36" s="30">
         <v>414</v>
@@ -9502,7 +9546,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B37" s="28">
         <v>428</v>
@@ -9525,7 +9569,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B38" s="30">
         <v>458</v>
@@ -9548,7 +9592,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B39" s="28">
         <v>498</v>
@@ -9571,7 +9615,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B40" s="30">
         <v>446</v>
@@ -9594,7 +9638,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B41" s="28">
         <v>450</v>
@@ -9617,7 +9661,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B42" s="30">
         <v>440</v>
@@ -9640,7 +9684,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="27" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B43" s="28">
         <v>440</v>
@@ -9663,7 +9707,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B44" s="30">
         <v>496</v>
@@ -9686,7 +9730,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B45" s="28">
         <v>500</v>
@@ -9709,7 +9753,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B46" s="30">
         <v>482</v>
@@ -9732,7 +9776,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="27" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B47" s="28">
         <v>488</v>
@@ -9755,7 +9799,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B48" s="30">
         <v>596</v>
@@ -9778,7 +9822,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B49" s="28">
         <v>600</v>
@@ -9801,7 +9845,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B50" s="30">
         <v>582</v>
@@ -9824,7 +9868,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B51" s="28">
         <v>588</v>
@@ -9847,7 +9891,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B52" s="30">
         <v>594</v>
@@ -9870,7 +9914,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="27" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B53" s="28">
         <v>692</v>
@@ -9893,7 +9937,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B54" s="30">
         <v>700</v>
@@ -9916,7 +9960,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B55" s="28">
         <v>792</v>
@@ -9939,7 +9983,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B56" s="30">
         <v>800</v>
@@ -9962,7 +10006,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="27" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B57" s="28">
         <v>890</v>
@@ -9985,7 +10029,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B58" s="30">
         <v>900</v>
@@ -10008,7 +10052,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B59" s="28">
         <v>912</v>
@@ -10031,7 +10075,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B60" s="30">
         <v>918</v>
@@ -10091,7 +10135,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -10102,7 +10146,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B3" s="28">
         <v>20</v>
@@ -10125,7 +10169,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B4" s="30">
         <v>20</v>
@@ -10148,7 +10192,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B5" s="28">
         <v>25</v>
@@ -10171,7 +10215,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B6" s="30">
         <v>25</v>
@@ -10194,7 +10238,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B7" s="28">
         <v>30</v>
@@ -10217,7 +10261,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B8" s="30">
         <v>30</v>
@@ -10240,7 +10284,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B9" s="28">
         <v>40</v>
@@ -10263,7 +10307,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B10" s="30">
         <v>40</v>
@@ -10286,7 +10330,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B11" s="28">
         <v>50</v>
@@ -10309,7 +10353,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B12" s="30">
         <v>50</v>
@@ -10332,7 +10376,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B13" s="28">
         <v>50</v>
@@ -10355,7 +10399,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B14" s="30">
         <v>60</v>
@@ -10378,7 +10422,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B15" s="28">
         <v>60</v>
@@ -10401,7 +10445,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B16" s="30">
         <v>60</v>
@@ -10424,7 +10468,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B17" s="28">
         <v>75</v>
@@ -10447,7 +10491,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B18" s="30">
         <v>75</v>
@@ -10470,7 +10514,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B19" s="28">
         <v>75</v>
@@ -10493,7 +10537,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B20" s="30">
         <v>75</v>
@@ -10516,7 +10560,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B21" s="28">
         <v>80</v>
@@ -10539,7 +10583,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B22" s="30">
         <v>80</v>
@@ -10562,7 +10606,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B23" s="28">
         <v>80</v>
@@ -10585,7 +10629,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B24" s="30">
         <v>90</v>
@@ -10608,7 +10652,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B25" s="28">
         <v>90</v>
@@ -10631,7 +10675,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B26" s="30">
         <v>100</v>
@@ -10654,7 +10698,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B27" s="28">
         <v>100</v>
@@ -10677,7 +10721,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B28" s="30">
         <v>100</v>
@@ -10700,7 +10744,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B29" s="28">
         <v>100</v>
@@ -10723,7 +10767,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B30" s="30">
         <v>100</v>
@@ -10746,7 +10790,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B31" s="28">
         <v>100</v>
@@ -10769,7 +10813,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B32" s="30">
         <v>100</v>
@@ -10792,7 +10836,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="27" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B33" s="28">
         <v>125</v>
@@ -10815,7 +10859,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B34" s="30">
         <v>125</v>
@@ -10838,7 +10882,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B35" s="28">
         <v>125</v>
@@ -10861,7 +10905,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B36" s="30">
         <v>125</v>
@@ -10884,7 +10928,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B37" s="28">
         <v>125</v>
@@ -10907,7 +10951,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B38" s="30">
         <v>125</v>
@@ -10930,7 +10974,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B39" s="28">
         <v>150</v>
@@ -10953,7 +10997,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B40" s="30">
         <v>150</v>
@@ -10976,7 +11020,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B41" s="28">
         <v>150</v>
@@ -10999,7 +11043,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B42" s="30">
         <v>150</v>
@@ -11022,7 +11066,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="27" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B43" s="28">
         <v>175</v>
@@ -11045,7 +11089,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B44" s="30">
         <v>175</v>
@@ -11068,7 +11112,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B45" s="28">
         <v>175</v>
@@ -11091,7 +11135,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B46" s="30">
         <v>200</v>
@@ -11114,7 +11158,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="27" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B47" s="28">
         <v>200</v>
@@ -11137,7 +11181,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B48" s="30">
         <v>200</v>
@@ -11160,7 +11204,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B49" s="28">
         <v>200</v>
@@ -11183,7 +11227,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B50" s="30">
         <v>200</v>
@@ -11206,7 +11250,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B51" s="28">
         <v>250</v>
@@ -11229,7 +11273,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B52" s="30">
         <v>250</v>
@@ -11252,7 +11296,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="27" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B53" s="28">
         <v>250</v>
@@ -11275,7 +11319,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B54" s="30">
         <v>250</v>
@@ -11298,7 +11342,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B55" s="28">
         <v>250</v>
@@ -11321,7 +11365,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B56" s="30">
         <v>300</v>
@@ -11344,7 +11388,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="27" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B57" s="28">
         <v>300</v>
@@ -11367,7 +11411,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B58" s="30">
         <v>300</v>
@@ -11390,7 +11434,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B59" s="28">
         <v>300</v>
@@ -11413,7 +11457,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B60" s="30">
         <v>200</v>
@@ -11436,7 +11480,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="27" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B61" s="28">
         <v>200</v>
@@ -11459,7 +11503,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="29" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B62" s="30">
         <v>200</v>
@@ -11482,7 +11526,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="27" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B63" s="28">
         <v>200</v>
@@ -11505,7 +11549,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="29" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B64" s="30">
         <v>250</v>
@@ -11528,7 +11572,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="27" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B65" s="28">
         <v>250</v>
@@ -11551,7 +11595,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="29" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B66" s="30">
         <v>250</v>
@@ -11574,7 +11618,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="27" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B67" s="28">
         <v>250</v>
@@ -11597,7 +11641,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="29" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B68" s="30">
         <v>250</v>
@@ -11620,7 +11664,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="27" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B69" s="28">
         <v>250</v>
@@ -11643,7 +11687,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="29" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B70" s="30">
         <v>300</v>
@@ -11666,7 +11710,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="27" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B71" s="28">
         <v>300</v>
@@ -11689,7 +11733,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="29" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B72" s="30">
         <v>300</v>
@@ -11712,7 +11756,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="27" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B73" s="28">
         <v>300</v>
@@ -11735,7 +11779,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="29" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B74" s="30">
         <v>300</v>
@@ -11758,7 +11802,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="27" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B75" s="28">
         <v>300</v>
@@ -11781,7 +11825,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="29" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B76" s="30">
         <v>300</v>
@@ -11804,7 +11848,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="27" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B77" s="28">
         <v>350</v>
@@ -11827,7 +11871,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="29" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B78" s="30">
         <v>350</v>
@@ -11850,7 +11894,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="27" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B79" s="28">
         <v>350</v>
@@ -11873,7 +11917,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="29" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B80" s="30">
         <v>350</v>
@@ -11896,7 +11940,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="27" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B81" s="28">
         <v>350</v>
@@ -11919,7 +11963,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="29" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B82" s="30">
         <v>350</v>
@@ -11942,7 +11986,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="27" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B83" s="28">
         <v>400</v>
@@ -11965,7 +12009,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="29" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B84" s="30">
         <v>400</v>
@@ -11988,7 +12032,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="27" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B85" s="28">
         <v>400</v>
@@ -12011,7 +12055,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="29" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B86" s="30">
         <v>400</v>
@@ -12034,7 +12078,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="27" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B87" s="28">
         <v>400</v>
@@ -12057,7 +12101,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="29" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B88" s="30">
         <v>400</v>
@@ -12080,7 +12124,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="27" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B89" s="28">
         <v>450</v>
@@ -12103,7 +12147,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="29" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B90" s="30">
         <v>450</v>
@@ -12126,7 +12170,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="27" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B91" s="28">
         <v>450</v>
@@ -12149,7 +12193,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="29" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B92" s="30">
         <v>450</v>
@@ -12172,7 +12216,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="27" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B93" s="28">
         <v>450</v>
@@ -12195,7 +12239,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="29" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B94" s="30">
         <v>450</v>
@@ -12218,7 +12262,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="27" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B95" s="28">
         <v>500</v>
@@ -12241,7 +12285,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="29" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B96" s="30">
         <v>500</v>
@@ -12264,7 +12308,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="27" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B97" s="28">
         <v>500</v>
@@ -12287,7 +12331,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="29" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B98" s="30">
         <v>500</v>
@@ -12310,7 +12354,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="27" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B99" s="28">
         <v>500</v>
@@ -12333,7 +12377,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="29" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B100" s="30">
         <v>500</v>
@@ -12356,7 +12400,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="27" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B101" s="28">
         <v>550</v>
@@ -12379,7 +12423,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="29" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B102" s="30">
         <v>550</v>
@@ -12402,7 +12446,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="27" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B103" s="28">
         <v>550</v>
@@ -12425,7 +12469,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="29" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B104" s="30">
         <v>550</v>
@@ -12448,7 +12492,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="27" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B105" s="28">
         <v>550</v>
@@ -12471,7 +12515,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="29" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B106" s="30">
         <v>600</v>
@@ -12494,7 +12538,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="27" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B107" s="28">
         <v>600</v>
@@ -12517,7 +12561,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="29" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B108" s="30">
         <v>600</v>
@@ -12540,7 +12584,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="27" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B109" s="28">
         <v>600</v>
@@ -12563,7 +12607,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="29" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B110" s="30">
         <v>600</v>
@@ -12586,7 +12630,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="27" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B111" s="28">
         <v>600</v>
@@ -12609,7 +12653,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="29" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B112" s="30">
         <v>600</v>
@@ -12632,7 +12676,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="27" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B113" s="28">
         <v>600</v>
@@ -12655,7 +12699,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="29" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B114" s="30">
         <v>600</v>
@@ -12678,7 +12722,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="27" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B115" s="28">
         <v>600</v>
@@ -12701,7 +12745,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="29" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B116" s="30">
         <v>600</v>
@@ -12724,7 +12768,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="27" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B117" s="28">
         <v>650</v>
@@ -12747,7 +12791,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="29" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B118" s="30">
         <v>650</v>
@@ -12770,7 +12814,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="27" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B119" s="28">
         <v>650</v>
@@ -12793,7 +12837,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="29" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B120" s="30">
         <v>650</v>
@@ -12816,7 +12860,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="27" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B121" s="28">
         <v>650</v>
@@ -12839,7 +12883,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="29" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B122" s="30">
         <v>650</v>
@@ -12862,7 +12906,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="27" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B123" s="28">
         <v>650</v>
@@ -12885,7 +12929,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="29" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B124" s="30">
         <v>650</v>
@@ -12908,7 +12952,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="27" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B125" s="28">
         <v>650</v>
@@ -12931,7 +12975,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="29" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B126" s="30">
         <v>650</v>
@@ -12954,7 +12998,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="27" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B127" s="28">
         <v>700</v>
@@ -12977,7 +13021,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="29" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B128" s="30">
         <v>700</v>
@@ -13000,7 +13044,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="27" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B129" s="28">
         <v>700</v>
@@ -13023,7 +13067,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="29" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B130" s="30">
         <v>700</v>
@@ -13046,7 +13090,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="27" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B131" s="28">
         <v>700</v>
@@ -13069,7 +13113,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="29" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B132" s="30">
         <v>700</v>
@@ -13092,7 +13136,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="27" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B133" s="28">
         <v>700</v>
@@ -13115,7 +13159,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="29" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B134" s="30">
         <v>700</v>
@@ -13138,7 +13182,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="27" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B135" s="28">
         <v>700</v>
@@ -13161,7 +13205,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="29" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B136" s="30">
         <v>700</v>
@@ -13184,7 +13228,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="27" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B137" s="28">
         <v>750</v>
@@ -13207,7 +13251,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="29" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B138" s="30">
         <v>750</v>
@@ -13230,7 +13274,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="27" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B139" s="28">
         <v>750</v>
@@ -13253,7 +13297,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="29" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B140" s="30">
         <v>750</v>
@@ -13276,7 +13320,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="27" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B141" s="28">
         <v>750</v>
@@ -13299,7 +13343,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="29" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B142" s="30">
         <v>750</v>
@@ -13322,7 +13366,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="27" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B143" s="28">
         <v>750</v>
@@ -13345,7 +13389,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="29" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B144" s="30">
         <v>750</v>
@@ -13368,7 +13412,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="27" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B145" s="28">
         <v>750</v>
@@ -13391,7 +13435,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="29" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B146" s="30">
         <v>800</v>
@@ -13414,7 +13458,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="27" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B147" s="28">
         <v>800</v>
@@ -13437,7 +13481,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="29" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B148" s="30">
         <v>800</v>
@@ -13460,7 +13504,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="27" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B149" s="28">
         <v>800</v>
@@ -13483,7 +13527,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B150" s="30">
         <v>800</v>
@@ -13506,7 +13550,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="27" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B151" s="28">
         <v>800</v>
@@ -13529,7 +13573,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="29" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B152" s="30">
         <v>800</v>
@@ -13552,7 +13596,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="27" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B153" s="28">
         <v>800</v>
@@ -13575,7 +13619,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="29" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B154" s="30">
         <v>800</v>

--- a/plate3d/PLATE3D_COLUMN.xlsx
+++ b/plate3d/PLATE3D_COLUMN.xlsx
@@ -107,7 +107,70 @@
     <t>flanges face</t>
   </si>
   <si>
-    <t xml:space="preserve">  2.  SPLICE PLATES</t>
+    <t xml:space="preserve">  2.  COLUMN STIFFENER</t>
+  </si>
+  <si>
+    <t>horizontal plates inside an H — a tube cannot take one, nothing reaches inside the wall</t>
+  </si>
+  <si>
+    <t>for</t>
+  </si>
+  <si>
+    <t>offset</t>
+  </si>
+  <si>
+    <t>width</t>
+  </si>
+  <si>
+    <t>depth</t>
+  </si>
+  <si>
+    <t>thick</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>beam top flange</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>beam bottom flange</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Offset is signed, from the middle column's centre — where the beams sit. Width runs out from the web, depth between the flanges. Thick 0 = off.</t>
+  </si>
+  <si>
+    <t>plates</t>
+  </si>
+  <si>
+    <t>fits</t>
+  </si>
+  <si>
+    <t>beam flange at ±</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3.  SPLICE PLATES</t>
   </si>
   <si>
     <t>cover plates on an H, an end plate on a tube — Type keeps whichever the section calls for</t>
@@ -158,7 +221,7 @@
     <t>plates fit</t>
   </si>
   <si>
-    <t xml:space="preserve">  3.  BOLTS</t>
+    <t xml:space="preserve">  4.  BOLTS</t>
   </si>
   <si>
     <t>the shank and the hole are different sizes, and each grip gets its own length</t>
@@ -227,7 +290,91 @@
     <t>bolts</t>
   </si>
   <si>
-    <t xml:space="preserve">  4.  BEAMS</t>
+    <t xml:space="preserve">  5.  CONNECTION</t>
+  </si>
+  <si>
+    <t>declare them here, then name one against each beam below — end plate bolts through the column, fin plate through the beam web</t>
+  </si>
+  <si>
+    <t>what it is</t>
+  </si>
+  <si>
+    <t>setback</t>
+  </si>
+  <si>
+    <t>height</t>
+  </si>
+  <si>
+    <t>gauge</t>
+  </si>
+  <si>
+    <t>edge</t>
+  </si>
+  <si>
+    <t>pitch</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>end plate</t>
+  </si>
+  <si>
+    <t>3 rows, through the col</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>4 rows, for a deep beam</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>fin plate</t>
+  </si>
+  <si>
+    <t>3 bolts through the web</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>4 bolts through the web</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>2 bolts, a thinner fin</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>spare — set a Type</t>
+  </si>
+  <si>
+    <t>The mark is just a mark — Type says what it is. End plate gauge is across the beam web, fin plate gauge out from the column face.</t>
+  </si>
+  <si>
+    <t>marks</t>
+  </si>
+  <si>
+    <t>widest end plate</t>
+  </si>
+  <si>
+    <t>longest bolt</t>
+  </si>
+  <si>
+    <t>flange passes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  6.  BEAMS</t>
   </si>
   <si>
     <t>four world directions - X+ X- Y+ Y-. Length 0 and that beam is not there</t>
@@ -242,18 +389,12 @@
     <t>X+</t>
   </si>
   <si>
-    <t>C1</t>
-  </si>
-  <si>
     <t>H-300x150x6.5x9 r13</t>
   </si>
   <si>
     <t>X-</t>
   </si>
   <si>
-    <t>C3</t>
-  </si>
-  <si>
     <t>Y+</t>
   </si>
   <si>
@@ -270,147 +411,6 @@
   </si>
   <si>
     <t>beams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  5.  CONNECTION</t>
-  </si>
-  <si>
-    <t>declare them here, then name one against each beam above — end plate bolts through the column, fin plate through the beam web</t>
-  </si>
-  <si>
-    <t>what it is</t>
-  </si>
-  <si>
-    <t>setback</t>
-  </si>
-  <si>
-    <t>width</t>
-  </si>
-  <si>
-    <t>height</t>
-  </si>
-  <si>
-    <t>thick</t>
-  </si>
-  <si>
-    <t>gauge</t>
-  </si>
-  <si>
-    <t>edge</t>
-  </si>
-  <si>
-    <t>pitch</t>
-  </si>
-  <si>
-    <t>count</t>
-  </si>
-  <si>
-    <t>end plate</t>
-  </si>
-  <si>
-    <t>3 rows, through the col</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>4 rows, for a deep beam</t>
-  </si>
-  <si>
-    <t>fin plate</t>
-  </si>
-  <si>
-    <t>3 bolts through the web</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>4 bolts through the web</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>2 bolts, a thinner fin</t>
-  </si>
-  <si>
-    <t>C6</t>
-  </si>
-  <si>
-    <t>spare — set a Type</t>
-  </si>
-  <si>
-    <t>The mark is just a mark — Type says what it is. End plate gauge is across the beam web, fin plate gauge out from the column face.</t>
-  </si>
-  <si>
-    <t>marks</t>
-  </si>
-  <si>
-    <t>widest end plate</t>
-  </si>
-  <si>
-    <t>longest bolt</t>
-  </si>
-  <si>
-    <t>flange passes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  6.  COLUMN STIFFENER</t>
-  </si>
-  <si>
-    <t>horizontal plates inside an H — a tube cannot take one, nothing reaches inside the wall</t>
-  </si>
-  <si>
-    <t>for</t>
-  </si>
-  <si>
-    <t>offset</t>
-  </si>
-  <si>
-    <t>depth</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>beam top flange</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>beam bottom flange</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Offset is signed, from the middle column's centre — where the beams sit. Width runs out from the web, depth between the flanges. Thick 0 = off.</t>
-  </si>
-  <si>
-    <t>plates</t>
-  </si>
-  <si>
-    <t>fits</t>
-  </si>
-  <si>
-    <t>beam flange at ±</t>
   </si>
   <si>
     <t>Written from PARAM. Nothing here needs editing — change the front sheet instead.</t>
@@ -1539,14 +1539,17 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1555,9 +1558,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2219,1102 +2219,1102 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D14" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="E14" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J14" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E15" s="7">
-        <v>300</v>
-      </c>
-      <c r="F15" s="7">
-        <v>330</v>
-      </c>
-      <c r="G15" s="7">
+      <c r="D15" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="8">
+        <v>145.5</v>
+      </c>
+      <c r="F15" s="8">
+        <v>145</v>
+      </c>
+      <c r="G15" s="8">
+        <v>270</v>
+      </c>
+      <c r="H15" s="8">
         <v>12</v>
       </c>
-      <c r="H15" s="14">
-        <v>2</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J15" s="7">
-        <v>10</v>
-      </c>
-      <c r="K15" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E16" s="7">
+      <c r="D16" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-145.5</v>
+      </c>
+      <c r="F16" s="8">
+        <v>145</v>
+      </c>
+      <c r="G16" s="8">
+        <v>270</v>
+      </c>
+      <c r="H16" s="8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="14"/>
+      <c r="E17" s="8">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="14"/>
+      <c r="E18" s="8">
+        <v>0</v>
+      </c>
+      <c r="F18" s="8">
+        <v>0</v>
+      </c>
+      <c r="G18" s="8">
+        <v>0</v>
+      </c>
+      <c r="H18" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="14"/>
+      <c r="E19" s="8">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="14"/>
+      <c r="E20" s="8">
+        <v>0</v>
+      </c>
+      <c r="F20" s="8">
+        <v>0</v>
+      </c>
+      <c r="G20" s="8">
+        <v>0</v>
+      </c>
+      <c r="H20" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="14"/>
+      <c r="E21" s="8">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="14"/>
+      <c r="E22" s="8">
+        <v>0</v>
+      </c>
+      <c r="F22" s="8">
+        <v>0</v>
+      </c>
+      <c r="G22" s="8">
+        <v>0</v>
+      </c>
+      <c r="H22" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B23" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="11" t="str">
+        <f>IF(PARAM!$C$6="H",IF($H$15&gt;0,2,0)+IF($H$16&gt;0,2,0)+IF($H$17&gt;0,2,0)+IF($H$18&gt;0,2,0)+IF($H$19&gt;0,2,0)+IF($H$20&gt;0,2,0)+IF($H$21&gt;0,2,0)+IF($H$22&gt;0,2,0),0)&amp;" of 16"</f>
+        <v>4 of 16</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" s="11" t="str">
+        <f>IF(NOT(PARAM!$C$6="H"),"n/a",IF(MAX($F$15:$F$22)&gt;(PARAM!$F$6-PARAM!$G$6)/2,"too wide",IF(MAX($G$15:$G$22)&gt;PARAM!$E$6-2*PARAM!$H$6,"too deep","ok")))</f>
+        <v>ok</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H24" s="11" t="str">
+        <f>ROUND((PARAM!$E$59-PARAM!$H$59)/2,1)&amp;" / "&amp;ROUND((PARAM!$E$60-PARAM!$H$60)/2,1)&amp;" / "&amp;ROUND((PARAM!$E$61-PARAM!$H$61)/2,1)&amp;" / "&amp;ROUND((PARAM!$E$62-PARAM!$H$62)/2,1)</f>
+        <v>145.5 / 145.5 / 145.5 / 145.5</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B26" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+    </row>
+    <row r="27" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E27" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" s="7">
+        <v>300</v>
+      </c>
+      <c r="F28" s="7">
+        <v>330</v>
+      </c>
+      <c r="G28" s="7">
+        <v>12</v>
+      </c>
+      <c r="H28" s="16">
+        <v>2</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" s="7">
+        <v>10</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B29" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="7">
         <v>110</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F29" s="7">
         <v>330</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G29" s="7">
         <v>10</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H29" s="16">
         <v>4</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I29" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="K16" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" s="7">
+      <c r="K29" s="17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E30" s="7">
         <v>234</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F30" s="7">
         <v>330</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G30" s="7">
         <v>10</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H30" s="16">
         <v>2</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I30" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="K17" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" s="17">
-        <f>PARAM!$E$6+2*PARAM!$J$18</f>
+      <c r="K30" s="17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B31" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" s="18">
+        <f>PARAM!$E$6+2*PARAM!$J$31</f>
         <v>420</v>
       </c>
-      <c r="F18" s="17">
-        <f>PARAM!$F$6+2*PARAM!$J$18</f>
+      <c r="F31" s="18">
+        <f>PARAM!$F$6+2*PARAM!$J$31</f>
         <v>420</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G31" s="7">
         <v>20</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H31" s="16">
         <v>2</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I31" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J18" s="7">
+      <c r="J31" s="7">
         <v>60</v>
       </c>
-      <c r="K18" s="15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B19" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="11" t="s">
+      <c r="K31" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B32" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="11" t="str">
+      <c r="C33" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="11" t="str">
         <f>IF(PARAM!$C$6="H","cover plates","end plate")</f>
         <v>cover plates</v>
       </c>
-      <c r="E20" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="11">
-        <f>ROUND(IF(PARAM!$C$6="H",PARAM!$E$15*PARAM!$F$15*PARAM!$G$15*2+PARAM!$E$16*PARAM!$F$16*PARAM!$G$16*4+PARAM!$E$17*PARAM!$F$17*PARAM!$G$17*2,PARAM!$E$18*PARAM!$F$18*PARAM!$G$18*2)*7.85/1000000,1)</f>
+      <c r="E33" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F33" s="11">
+        <f>ROUND(IF(PARAM!$C$6="H",PARAM!$E$28*PARAM!$F$28*PARAM!$G$28*2+PARAM!$E$29*PARAM!$F$29*PARAM!$G$29*4+PARAM!$E$30*PARAM!$F$30*PARAM!$G$30*2,PARAM!$E$31*PARAM!$F$31*PARAM!$G$31*2)*7.85/1000000,1)</f>
         <v>42.2</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G33" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H33" s="11" t="str">
+        <f>IF(PARAM!$C$6="H",IF(AND(PARAM!$E$28&lt;=PARAM!$F$6,PARAM!$E$30&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6),"ok",IF(PARAM!$E$28&gt;PARAM!$F$6,"flange plate too wide","web plate too deep")),"n/a")</f>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B35" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+    </row>
+    <row r="36" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E36" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B37" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E37" s="7">
+        <v>16</v>
+      </c>
+      <c r="F37" s="18">
+        <f>PARAM!$E$37+2</f>
+        <v>18</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H37" s="19">
+        <f>IF(PARAM!$C$6="H",CEILING(PARAM!$G$28+PARAM!$H$6+PARAM!$G$29+1.1*PARAM!$E$37,5),"—")</f>
+        <v>55</v>
+      </c>
+      <c r="I37" s="19">
+        <f>IF(PARAM!$C$6="H",CEILING(PARAM!$G$6+2*PARAM!$G$30+1.1*PARAM!$E$37,5),"—")</f>
+        <v>50</v>
+      </c>
+      <c r="J37" s="19" t="str">
+        <f>IF(PARAM!$C$6="H","—",CEILING(2*PARAM!$G$31+1.1*PARAM!$E$37,5))</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B38" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B39" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E39" s="7">
+        <v>4</v>
+      </c>
+      <c r="F39" s="7">
+        <v>70</v>
+      </c>
+      <c r="G39" s="7">
         <v>45</v>
       </c>
-      <c r="H20" s="11" t="str">
-        <f>IF(PARAM!$C$6="H",IF(AND(PARAM!$E$15&lt;=PARAM!$F$6,PARAM!$E$17&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6),"ok",IF(PARAM!$E$15&gt;PARAM!$F$6,"flange plate too wide","web plate too deep")),"n/a")</f>
-        <v>ok</v>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B22" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-    </row>
-    <row r="23" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E23" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E24" s="7">
-        <v>16</v>
-      </c>
-      <c r="F24" s="17">
-        <f>PARAM!$E$24+2</f>
-        <v>18</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H24" s="18">
-        <f>IF(PARAM!$C$6="H",CEILING(PARAM!$G$15+PARAM!$H$6+PARAM!$G$16+1.1*PARAM!$E$24,5),"—")</f>
-        <v>55</v>
-      </c>
-      <c r="I24" s="18">
-        <f>IF(PARAM!$C$6="H",CEILING(PARAM!$G$6+2*PARAM!$G$17+1.1*PARAM!$E$24,5),"—")</f>
-        <v>50</v>
-      </c>
-      <c r="J24" s="18" t="str">
-        <f>IF(PARAM!$C$6="H","—",CEILING(2*PARAM!$G$18+1.1*PARAM!$E$24,5))</f>
-        <v>—</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H25" s="5" t="s">
+      <c r="H39" s="7">
+        <v>4</v>
+      </c>
+      <c r="I39" s="7">
+        <v>100</v>
+      </c>
+      <c r="J39" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" s="7">
+        <v>4</v>
+      </c>
+      <c r="F40" s="7">
         <v>60</v>
       </c>
-      <c r="I25" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="6" t="s">
+      <c r="G40" s="7">
+        <v>45</v>
+      </c>
+      <c r="H40" s="7">
+        <v>3</v>
+      </c>
+      <c r="I40" s="7">
+        <v>0</v>
+      </c>
+      <c r="J40" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E41" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B42" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E42" s="7">
+        <v>3</v>
+      </c>
+      <c r="F42" s="7">
+        <v>30</v>
+      </c>
+      <c r="H42" s="7">
+        <v>3</v>
+      </c>
+      <c r="I42" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B43" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12"/>
+      <c r="L43" s="12"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B44" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D44" s="11" t="str">
+        <f>IF(PARAM!$C$6="H",ROUND((PARAM!$F$28/2-PARAM!$G$39-PARAM!$F$39/2)/(PARAM!$E$39/2-1),1)&amp;" / "&amp;ROUND((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1),1),"n/a")</f>
+        <v>85 / 60</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F44" s="11" t="str">
+        <f>IF(PARAM!$C$6="H",ROUND((PARAM!$F$30/2-PARAM!$G$40-PARAM!$F$40/2)/(PARAM!$E$40/2-1),1)&amp;" / "&amp;ROUND((PARAM!$E$30-2*PARAM!$J$40-PARAM!$I$40)/(PARAM!$H$40-1),1),"n/a")</f>
+        <v>90 / 77</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="H44" s="11" t="str">
+        <f>IF(PARAM!$C$6="H",2*PARAM!$E$39*PARAM!$H$39+PARAM!$E$40*PARAM!$H$40,2*PARAM!$E$42+2*MAX(0,PARAM!$H$42-2))&amp;" per splice"</f>
+        <v>44 per splice</v>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B46" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+    </row>
+    <row r="47" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C47" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F26" s="7">
-        <v>70</v>
-      </c>
-      <c r="G26" s="7">
-        <v>45</v>
-      </c>
-      <c r="H26" s="7">
-        <v>4</v>
-      </c>
-      <c r="I26" s="7">
-        <v>100</v>
-      </c>
-      <c r="J26" s="7">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E27" s="7">
-        <v>4</v>
-      </c>
-      <c r="F27" s="7">
-        <v>60</v>
-      </c>
-      <c r="G27" s="7">
-        <v>45</v>
-      </c>
-      <c r="H27" s="7">
-        <v>3</v>
-      </c>
-      <c r="I27" s="7">
-        <v>0</v>
-      </c>
-      <c r="J27" s="7">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E28" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="E29" s="7">
-        <v>3</v>
-      </c>
-      <c r="F29" s="7">
-        <v>30</v>
-      </c>
-      <c r="H29" s="7">
-        <v>3</v>
-      </c>
-      <c r="I29" s="7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B30" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D31" s="11" t="str">
-        <f>IF(PARAM!$C$6="H",ROUND((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1),1)&amp;" / "&amp;ROUND((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1),1),"n/a")</f>
-        <v>85 / 60</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="F31" s="11" t="str">
-        <f>IF(PARAM!$C$6="H",ROUND((PARAM!$F$17/2-PARAM!$G$27-PARAM!$F$27/2)/(PARAM!$E$27/2-1),1)&amp;" / "&amp;ROUND((PARAM!$E$17-2*PARAM!$J$27-PARAM!$I$27)/(PARAM!$H$27-1),1),"n/a")</f>
-        <v>90 / 77</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="H31" s="11" t="str">
-        <f>IF(PARAM!$C$6="H",2*PARAM!$E$26*PARAM!$H$26+PARAM!$E$27*PARAM!$H$27,2*PARAM!$E$29+2*MAX(0,PARAM!$H$29-2))&amp;" per splice"</f>
-        <v>44 per splice</v>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B33" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-    </row>
-    <row r="34" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C34" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J34" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K34" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B35" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E35" s="8">
-        <f>IFERROR(VLOOKUP($D$35,SECT!$A:$G,2,FALSE),"")</f>
-        <v>300</v>
-      </c>
-      <c r="F35" s="8">
-        <f>IFERROR(VLOOKUP($D$35,SECT!$A:$G,3,FALSE),"")</f>
-        <v>150</v>
-      </c>
-      <c r="G35" s="8">
-        <f>IFERROR(VLOOKUP($D$35,SECT!$A:$G,4,FALSE),"")</f>
-        <v>6.5</v>
-      </c>
-      <c r="H35" s="8">
-        <f>IFERROR(VLOOKUP($D$35,SECT!$A:$G,5,FALSE),"")</f>
-        <v>9</v>
-      </c>
-      <c r="I35" s="8">
-        <f>IFERROR(VLOOKUP($D$35,SECT!$A:$G,6,FALSE),"")</f>
-        <v>13</v>
-      </c>
-      <c r="J35" s="7">
-        <v>900</v>
-      </c>
-      <c r="K35" s="9">
-        <f>IFERROR(VLOOKUP($D$35,SECT!$A:$G,7,FALSE),"")</f>
-        <v>36.7</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B36" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E36" s="8">
-        <f>IFERROR(VLOOKUP($D$36,SECT!$A:$G,2,FALSE),"")</f>
-        <v>300</v>
-      </c>
-      <c r="F36" s="8">
-        <f>IFERROR(VLOOKUP($D$36,SECT!$A:$G,3,FALSE),"")</f>
-        <v>150</v>
-      </c>
-      <c r="G36" s="8">
-        <f>IFERROR(VLOOKUP($D$36,SECT!$A:$G,4,FALSE),"")</f>
-        <v>6.5</v>
-      </c>
-      <c r="H36" s="8">
-        <f>IFERROR(VLOOKUP($D$36,SECT!$A:$G,5,FALSE),"")</f>
-        <v>9</v>
-      </c>
-      <c r="I36" s="8">
-        <f>IFERROR(VLOOKUP($D$36,SECT!$A:$G,6,FALSE),"")</f>
-        <v>13</v>
-      </c>
-      <c r="J36" s="7">
-        <v>900</v>
-      </c>
-      <c r="K36" s="9">
-        <f>IFERROR(VLOOKUP($D$36,SECT!$A:$G,7,FALSE),"")</f>
-        <v>36.7</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B37" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E37" s="8">
-        <f>IFERROR(VLOOKUP($D$37,SECT!$A:$G,2,FALSE),"")</f>
-        <v>300</v>
-      </c>
-      <c r="F37" s="8">
-        <f>IFERROR(VLOOKUP($D$37,SECT!$A:$G,3,FALSE),"")</f>
-        <v>150</v>
-      </c>
-      <c r="G37" s="8">
-        <f>IFERROR(VLOOKUP($D$37,SECT!$A:$G,4,FALSE),"")</f>
-        <v>6.5</v>
-      </c>
-      <c r="H37" s="8">
-        <f>IFERROR(VLOOKUP($D$37,SECT!$A:$G,5,FALSE),"")</f>
-        <v>9</v>
-      </c>
-      <c r="I37" s="8">
-        <f>IFERROR(VLOOKUP($D$37,SECT!$A:$G,6,FALSE),"")</f>
-        <v>13</v>
-      </c>
-      <c r="J37" s="7">
-        <v>900</v>
-      </c>
-      <c r="K37" s="9">
-        <f>IFERROR(VLOOKUP($D$37,SECT!$A:$G,7,FALSE),"")</f>
-        <v>36.7</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B38" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E38" s="8">
-        <f>IFERROR(VLOOKUP($D$38,SECT!$A:$G,2,FALSE),"")</f>
-        <v>300</v>
-      </c>
-      <c r="F38" s="8">
-        <f>IFERROR(VLOOKUP($D$38,SECT!$A:$G,3,FALSE),"")</f>
-        <v>150</v>
-      </c>
-      <c r="G38" s="8">
-        <f>IFERROR(VLOOKUP($D$38,SECT!$A:$G,4,FALSE),"")</f>
-        <v>6.5</v>
-      </c>
-      <c r="H38" s="8">
-        <f>IFERROR(VLOOKUP($D$38,SECT!$A:$G,5,FALSE),"")</f>
-        <v>9</v>
-      </c>
-      <c r="I38" s="8">
-        <f>IFERROR(VLOOKUP($D$38,SECT!$A:$G,6,FALSE),"")</f>
-        <v>13</v>
-      </c>
-      <c r="J38" s="7">
-        <v>0</v>
-      </c>
-      <c r="K38" s="9">
-        <f>IFERROR(VLOOKUP($D$38,SECT!$A:$G,7,FALSE),"")</f>
-        <v>36.7</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B39" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="12"/>
-      <c r="L39" s="12"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D40" s="11" t="str">
-        <f>IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,"flange","web"),"tube wall")</f>
-        <v>flange</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="F40" s="11" t="str">
-        <f>IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,"web","flange"),"tube wall")</f>
-        <v>web</v>
-      </c>
-      <c r="G40" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="H40" s="11" t="str">
-        <f>(IF(PARAM!$J$35&gt;0,1,0)+IF(PARAM!$J$36&gt;0,1,0)+IF(PARAM!$J$37&gt;0,1,0)+IF(PARAM!$J$38&gt;0,1,0))&amp;" of 4"</f>
-        <v>3 of 4</v>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B42" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-    </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C43" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="I43" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="J43" s="5" t="s">
+      <c r="D47" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="K43" s="5" t="s">
+      <c r="E47" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="L43" s="5" t="s">
+      <c r="F47" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G47" s="5" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B44" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C44" s="7" t="s">
+      <c r="H47" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I47" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D44" s="20" t="s">
+      <c r="J47" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E44" s="8">
-        <v>0</v>
-      </c>
-      <c r="F44" s="8">
-        <v>230</v>
-      </c>
-      <c r="G44" s="17">
-        <f>K44*(L44-1)+2*J44</f>
-        <v>230</v>
-      </c>
-      <c r="H44" s="8">
-        <v>20</v>
-      </c>
-      <c r="I44" s="8">
-        <v>140</v>
-      </c>
-      <c r="J44" s="8">
-        <v>45</v>
-      </c>
-      <c r="K44" s="8">
-        <v>70</v>
-      </c>
-      <c r="L44" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B45" s="6" t="s">
+      <c r="K47" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D45" s="20" t="s">
+      <c r="L47" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="E45" s="8">
-        <v>0</v>
-      </c>
-      <c r="F45" s="8">
-        <v>230</v>
-      </c>
-      <c r="G45" s="17">
-        <f>K45*(L45-1)+2*J45</f>
-        <v>300</v>
-      </c>
-      <c r="H45" s="8">
-        <v>20</v>
-      </c>
-      <c r="I45" s="8">
-        <v>140</v>
-      </c>
-      <c r="J45" s="8">
-        <v>45</v>
-      </c>
-      <c r="K45" s="8">
-        <v>70</v>
-      </c>
-      <c r="L45" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B46" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D46" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="E46" s="8">
-        <v>10</v>
-      </c>
-      <c r="F46" s="8">
-        <v>140</v>
-      </c>
-      <c r="G46" s="17">
-        <f>K46*(L46-1)+2*J46</f>
-        <v>230</v>
-      </c>
-      <c r="H46" s="8">
-        <v>10</v>
-      </c>
-      <c r="I46" s="8">
-        <v>60</v>
-      </c>
-      <c r="J46" s="8">
-        <v>45</v>
-      </c>
-      <c r="K46" s="8">
-        <v>70</v>
-      </c>
-      <c r="L46" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B47" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="E47" s="8">
-        <v>10</v>
-      </c>
-      <c r="F47" s="8">
-        <v>140</v>
-      </c>
-      <c r="G47" s="17">
-        <f>K47*(L47-1)+2*J47</f>
-        <v>300</v>
-      </c>
-      <c r="H47" s="8">
-        <v>10</v>
-      </c>
-      <c r="I47" s="8">
-        <v>60</v>
-      </c>
-      <c r="J47" s="8">
-        <v>45</v>
-      </c>
-      <c r="K47" s="8">
-        <v>70</v>
-      </c>
-      <c r="L47" s="8">
-        <v>4</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B48" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0</v>
+      </c>
+      <c r="F48" s="8">
+        <v>230</v>
+      </c>
+      <c r="G48" s="18">
+        <f>K48*(L48-1)+2*J48</f>
+        <v>230</v>
+      </c>
+      <c r="H48" s="8">
+        <v>20</v>
+      </c>
+      <c r="I48" s="8">
+        <v>140</v>
+      </c>
+      <c r="J48" s="8">
+        <v>45</v>
+      </c>
+      <c r="K48" s="8">
+        <v>70</v>
+      </c>
+      <c r="L48" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B49" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D49" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="E49" s="8">
+        <v>0</v>
+      </c>
+      <c r="F49" s="8">
+        <v>230</v>
+      </c>
+      <c r="G49" s="18">
+        <f>K49*(L49-1)+2*J49</f>
+        <v>300</v>
+      </c>
+      <c r="H49" s="8">
+        <v>20</v>
+      </c>
+      <c r="I49" s="8">
+        <v>140</v>
+      </c>
+      <c r="J49" s="8">
+        <v>45</v>
+      </c>
+      <c r="K49" s="8">
+        <v>70</v>
+      </c>
+      <c r="L49" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B50" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="E50" s="8">
+        <v>10</v>
+      </c>
+      <c r="F50" s="8">
+        <v>140</v>
+      </c>
+      <c r="G50" s="18">
+        <f>K50*(L50-1)+2*J50</f>
+        <v>230</v>
+      </c>
+      <c r="H50" s="8">
+        <v>10</v>
+      </c>
+      <c r="I50" s="8">
+        <v>60</v>
+      </c>
+      <c r="J50" s="8">
+        <v>45</v>
+      </c>
+      <c r="K50" s="8">
+        <v>70</v>
+      </c>
+      <c r="L50" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B51" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E51" s="8">
+        <v>10</v>
+      </c>
+      <c r="F51" s="8">
+        <v>140</v>
+      </c>
+      <c r="G51" s="18">
+        <f>K51*(L51-1)+2*J51</f>
+        <v>300</v>
+      </c>
+      <c r="H51" s="8">
+        <v>10</v>
+      </c>
+      <c r="I51" s="8">
+        <v>60</v>
+      </c>
+      <c r="J51" s="8">
+        <v>45</v>
+      </c>
+      <c r="K51" s="8">
+        <v>70</v>
+      </c>
+      <c r="L51" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B52" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="E52" s="8">
+        <v>10</v>
+      </c>
+      <c r="F52" s="8">
+        <v>120</v>
+      </c>
+      <c r="G52" s="18">
+        <f>K52*(L52-1)+2*J52</f>
+        <v>140</v>
+      </c>
+      <c r="H52" s="8">
+        <v>9</v>
+      </c>
+      <c r="I52" s="8">
+        <v>55</v>
+      </c>
+      <c r="J52" s="8">
+        <v>40</v>
+      </c>
+      <c r="K52" s="8">
+        <v>60</v>
+      </c>
+      <c r="L52" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B53" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C53" s="7"/>
+      <c r="D53" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E53" s="8">
+        <v>0</v>
+      </c>
+      <c r="F53" s="8">
+        <v>0</v>
+      </c>
+      <c r="G53" s="18">
+        <f>K53*(L53-1)+2*J53</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="8">
+        <v>0</v>
+      </c>
+      <c r="I53" s="8">
+        <v>0</v>
+      </c>
+      <c r="J53" s="8">
+        <v>0</v>
+      </c>
+      <c r="K53" s="8">
+        <v>0</v>
+      </c>
+      <c r="L53" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B54" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="12"/>
+      <c r="K54" s="12"/>
+      <c r="L54" s="12"/>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B55" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D55" s="11" t="str">
+        <f>IF(COUNTIF(PARAM!$B$48:$B$53,PARAM!$C$59)+COUNTIF(PARAM!$B$48:$B$53,PARAM!$C$60)+COUNTIF(PARAM!$B$48:$B$53,PARAM!$C$61)+COUNTIF(PARAM!$B$48:$B$53,PARAM!$C$62)=4,"all 4 beams found theirs","a beam names a mark that is not in the list")</f>
+        <v>all 4 beams found theirs</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="F55" s="11" t="str">
+        <f>IF(NOT(PARAM!$C$6="H"),"n/a",IF(SUMPRODUCT(MAX((PARAM!$C$48:$C$53="end plate")*(PARAM!$F$48:$F$53)))&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"fits between the flanges","hits the flanges on a web face"))</f>
+        <v>fits between the flanges</v>
+      </c>
+      <c r="G55" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H55" s="11" t="str">
+        <f>"M"&amp;PARAM!$E$37&amp;" L"&amp;MAX(IF(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0))+1.1*PARAM!$E$37,5),IF(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$59+1.1*PARAM!$E$37,5),0)),IF(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0))+1.1*PARAM!$E$37,5),IF(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$60+1.1*PARAM!$E$37,5),0)),IF(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0))+1.1*PARAM!$E$37,5),IF(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$61+1.1*PARAM!$E$37,5),0)),IF(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0))+1.1*PARAM!$E$37,5),IF(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$62+1.1*PARAM!$E$37,5),0)))</f>
+        <v>M16 L55</v>
+      </c>
+      <c r="I55" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="J55" s="11" t="str">
+        <f>IF(NOT(PARAM!$C$6="H"),"n/a",IF(MOD(PARAM!$J$6,180)=0,IF(MAX(PARAM!$F$61,PARAM!$F$62)&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"ok","strip the beam flange"),IF(MAX(PARAM!$F$59,PARAM!$F$60)&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"ok","strip the beam flange")))</f>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B57" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+    </row>
+    <row r="58" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C58" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K58" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B59" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C59" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D48" s="20" t="s">
+      <c r="D59" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E59" s="8">
+        <f>IFERROR(VLOOKUP($D$59,SECT!$A:$G,2,FALSE),"")</f>
+        <v>300</v>
+      </c>
+      <c r="F59" s="8">
+        <f>IFERROR(VLOOKUP($D$59,SECT!$A:$G,3,FALSE),"")</f>
+        <v>150</v>
+      </c>
+      <c r="G59" s="8">
+        <f>IFERROR(VLOOKUP($D$59,SECT!$A:$G,4,FALSE),"")</f>
+        <v>6.5</v>
+      </c>
+      <c r="H59" s="8">
+        <f>IFERROR(VLOOKUP($D$59,SECT!$A:$G,5,FALSE),"")</f>
+        <v>9</v>
+      </c>
+      <c r="I59" s="8">
+        <f>IFERROR(VLOOKUP($D$59,SECT!$A:$G,6,FALSE),"")</f>
+        <v>13</v>
+      </c>
+      <c r="J59" s="7">
+        <v>900</v>
+      </c>
+      <c r="K59" s="9">
+        <f>IFERROR(VLOOKUP($D$59,SECT!$A:$G,7,FALSE),"")</f>
+        <v>36.7</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B60" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C60" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E48" s="8">
-        <v>10</v>
-      </c>
-      <c r="F48" s="8">
-        <v>120</v>
-      </c>
-      <c r="G48" s="17">
-        <f>K48*(L48-1)+2*J48</f>
-        <v>140</v>
-      </c>
-      <c r="H48" s="8">
+      <c r="D60" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E60" s="8">
+        <f>IFERROR(VLOOKUP($D$60,SECT!$A:$G,2,FALSE),"")</f>
+        <v>300</v>
+      </c>
+      <c r="F60" s="8">
+        <f>IFERROR(VLOOKUP($D$60,SECT!$A:$G,3,FALSE),"")</f>
+        <v>150</v>
+      </c>
+      <c r="G60" s="8">
+        <f>IFERROR(VLOOKUP($D$60,SECT!$A:$G,4,FALSE),"")</f>
+        <v>6.5</v>
+      </c>
+      <c r="H60" s="8">
+        <f>IFERROR(VLOOKUP($D$60,SECT!$A:$G,5,FALSE),"")</f>
         <v>9</v>
       </c>
-      <c r="I48" s="8">
-        <v>55</v>
-      </c>
-      <c r="J48" s="8">
-        <v>40</v>
-      </c>
-      <c r="K48" s="8">
-        <v>60</v>
-      </c>
-      <c r="L48" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B49" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="C49" s="7"/>
-      <c r="D49" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0</v>
-      </c>
-      <c r="F49" s="8">
-        <v>0</v>
-      </c>
-      <c r="G49" s="17">
-        <f>K49*(L49-1)+2*J49</f>
-        <v>0</v>
-      </c>
-      <c r="H49" s="8">
-        <v>0</v>
-      </c>
-      <c r="I49" s="8">
-        <v>0</v>
-      </c>
-      <c r="J49" s="8">
-        <v>0</v>
-      </c>
-      <c r="K49" s="8">
-        <v>0</v>
-      </c>
-      <c r="L49" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B50" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="12"/>
-      <c r="H50" s="12"/>
-      <c r="I50" s="12"/>
-      <c r="J50" s="12"/>
-      <c r="K50" s="12"/>
-      <c r="L50" s="12"/>
-    </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B51" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="D51" s="11" t="str">
-        <f>IF(COUNTIF(PARAM!$B$44:$B$49,PARAM!$C$35)+COUNTIF(PARAM!$B$44:$B$49,PARAM!$C$36)+COUNTIF(PARAM!$B$44:$B$49,PARAM!$C$37)+COUNTIF(PARAM!$B$44:$B$49,PARAM!$C$38)=4,"all 4 beams found theirs","a beam names a mark that is not in the list")</f>
-        <v>all 4 beams found theirs</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="F51" s="11" t="str">
-        <f>IF(NOT(PARAM!$C$6="H"),"n/a",IF(SUMPRODUCT(MAX((PARAM!$C$44:$C$49="end plate")*(PARAM!$F$44:$F$49)))&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"fits between the flanges","hits the flanges on a web face"))</f>
-        <v>fits between the flanges</v>
-      </c>
-      <c r="G51" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="H51" s="11" t="str">
-        <f>"M"&amp;PARAM!$E$24&amp;" L"&amp;MAX(IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0))+1.1*PARAM!$E$24,5),IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$35+1.1*PARAM!$E$24,5),0)),IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0))+1.1*PARAM!$E$24,5),IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$36+1.1*PARAM!$E$24,5),0)),IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0))+1.1*PARAM!$E$24,5),IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$37+1.1*PARAM!$E$24,5),0)),IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0))+1.1*PARAM!$E$24,5),IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$38+1.1*PARAM!$E$24,5),0)))</f>
-        <v>M16 L55</v>
-      </c>
-      <c r="I51" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="J51" s="11" t="str">
-        <f>IF(NOT(PARAM!$C$6="H"),"n/a",IF(MOD(PARAM!$J$6,180)=0,IF(MAX(PARAM!$F$37,PARAM!$F$38)&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"ok","strip the beam flange"),IF(MAX(PARAM!$F$35,PARAM!$F$36)&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"ok","strip the beam flange")))</f>
-        <v>ok</v>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B53" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-    </row>
-    <row r="54" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D54" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B55" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D55" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="E55" s="8">
-        <v>145.5</v>
-      </c>
-      <c r="F55" s="8">
-        <v>145</v>
-      </c>
-      <c r="G55" s="8">
-        <v>270</v>
-      </c>
-      <c r="H55" s="8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B56" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D56" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-145.5</v>
-      </c>
-      <c r="F56" s="8">
-        <v>145</v>
-      </c>
-      <c r="G56" s="8">
-        <v>270</v>
-      </c>
-      <c r="H56" s="8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B57" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="D57" s="20"/>
-      <c r="E57" s="8">
-        <v>0</v>
-      </c>
-      <c r="F57" s="8">
-        <v>0</v>
-      </c>
-      <c r="G57" s="8">
-        <v>0</v>
-      </c>
-      <c r="H57" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B58" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="D58" s="20"/>
-      <c r="E58" s="8">
-        <v>0</v>
-      </c>
-      <c r="F58" s="8">
-        <v>0</v>
-      </c>
-      <c r="G58" s="8">
-        <v>0</v>
-      </c>
-      <c r="H58" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B59" s="16" t="s">
+      <c r="I60" s="8">
+        <f>IFERROR(VLOOKUP($D$60,SECT!$A:$G,6,FALSE),"")</f>
+        <v>13</v>
+      </c>
+      <c r="J60" s="7">
+        <v>900</v>
+      </c>
+      <c r="K60" s="9">
+        <f>IFERROR(VLOOKUP($D$60,SECT!$A:$G,7,FALSE),"")</f>
+        <v>36.7</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B61" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D61" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D59" s="20"/>
-      <c r="E59" s="8">
-        <v>0</v>
-      </c>
-      <c r="F59" s="8">
-        <v>0</v>
-      </c>
-      <c r="G59" s="8">
-        <v>0</v>
-      </c>
-      <c r="H59" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B60" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="D60" s="20"/>
-      <c r="E60" s="8">
-        <v>0</v>
-      </c>
-      <c r="F60" s="8">
-        <v>0</v>
-      </c>
-      <c r="G60" s="8">
-        <v>0</v>
-      </c>
-      <c r="H60" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B61" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="D61" s="20"/>
       <c r="E61" s="8">
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($D$61,SECT!$A:$G,2,FALSE),"")</f>
+        <v>300</v>
       </c>
       <c r="F61" s="8">
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($D$61,SECT!$A:$G,3,FALSE),"")</f>
+        <v>150</v>
       </c>
       <c r="G61" s="8">
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($D$61,SECT!$A:$G,4,FALSE),"")</f>
+        <v>6.5</v>
       </c>
       <c r="H61" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B62" s="16" t="s">
+        <f>IFERROR(VLOOKUP($D$61,SECT!$A:$G,5,FALSE),"")</f>
+        <v>9</v>
+      </c>
+      <c r="I61" s="8">
+        <f>IFERROR(VLOOKUP($D$61,SECT!$A:$G,6,FALSE),"")</f>
+        <v>13</v>
+      </c>
+      <c r="J61" s="7">
+        <v>900</v>
+      </c>
+      <c r="K61" s="9">
+        <f>IFERROR(VLOOKUP($D$61,SECT!$A:$G,7,FALSE),"")</f>
+        <v>36.7</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B62" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="D62" s="20"/>
+      <c r="C62" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>123</v>
+      </c>
       <c r="E62" s="8">
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($D$62,SECT!$A:$G,2,FALSE),"")</f>
+        <v>300</v>
       </c>
       <c r="F62" s="8">
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($D$62,SECT!$A:$G,3,FALSE),"")</f>
+        <v>150</v>
       </c>
       <c r="G62" s="8">
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($D$62,SECT!$A:$G,4,FALSE),"")</f>
+        <v>6.5</v>
       </c>
       <c r="H62" s="8">
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($D$62,SECT!$A:$G,5,FALSE),"")</f>
+        <v>9</v>
+      </c>
+      <c r="I62" s="8">
+        <f>IFERROR(VLOOKUP($D$62,SECT!$A:$G,6,FALSE),"")</f>
+        <v>13</v>
+      </c>
+      <c r="J62" s="7">
+        <v>0</v>
+      </c>
+      <c r="K62" s="9">
+        <f>IFERROR(VLOOKUP($D$62,SECT!$A:$G,7,FALSE),"")</f>
+        <v>36.7</v>
       </c>
     </row>
     <row r="63" spans="2:12" x14ac:dyDescent="0.25">
@@ -3340,22 +3340,22 @@
         <v>128</v>
       </c>
       <c r="D64" s="11" t="str">
-        <f>IF(PARAM!$C$6="H",IF($H$55&gt;0,2,0)+IF($H$56&gt;0,2,0)+IF($H$57&gt;0,2,0)+IF($H$58&gt;0,2,0)+IF($H$59&gt;0,2,0)+IF($H$60&gt;0,2,0)+IF($H$61&gt;0,2,0)+IF($H$62&gt;0,2,0),0)&amp;" of 16"</f>
-        <v>4 of 16</v>
+        <f>IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,"flange","web"),"tube wall")</f>
+        <v>flange</v>
       </c>
       <c r="E64" s="13" t="s">
         <v>129</v>
       </c>
       <c r="F64" s="11" t="str">
-        <f>IF(NOT(PARAM!$C$6="H"),"n/a",IF(MAX($F$55:$F$62)&gt;(PARAM!$F$6-PARAM!$G$6)/2,"too wide",IF(MAX($G$55:$G$62)&gt;PARAM!$E$6-2*PARAM!$H$6,"too deep","ok")))</f>
-        <v>ok</v>
+        <f>IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,"web","flange"),"tube wall")</f>
+        <v>web</v>
       </c>
       <c r="G64" s="13" t="s">
         <v>130</v>
       </c>
       <c r="H64" s="11" t="str">
-        <f>ROUND((PARAM!$E$35-PARAM!$H$35)/2,1)&amp;" / "&amp;ROUND((PARAM!$E$36-PARAM!$H$36)/2,1)&amp;" / "&amp;ROUND((PARAM!$E$37-PARAM!$H$37)/2,1)&amp;" / "&amp;ROUND((PARAM!$E$38-PARAM!$H$38)/2,1)</f>
-        <v>145.5 / 145.5 / 145.5 / 145.5</v>
+        <f>(IF(PARAM!$J$59&gt;0,1,0)+IF(PARAM!$J$60&gt;0,1,0)+IF(PARAM!$J$61&gt;0,1,0)+IF(PARAM!$J$62&gt;0,1,0))&amp;" of 4"</f>
+        <v>3 of 4</v>
       </c>
     </row>
   </sheetData>
@@ -3365,68 +3365,68 @@
     <mergeCell ref="B9:L9"/>
     <mergeCell ref="B10:L10"/>
     <mergeCell ref="C13:L13"/>
-    <mergeCell ref="B19:L19"/>
-    <mergeCell ref="C22:L22"/>
-    <mergeCell ref="B30:L30"/>
-    <mergeCell ref="C33:L33"/>
-    <mergeCell ref="B39:L39"/>
-    <mergeCell ref="C42:L42"/>
-    <mergeCell ref="B50:L50"/>
-    <mergeCell ref="C53:L53"/>
+    <mergeCell ref="B23:L23"/>
+    <mergeCell ref="C26:L26"/>
+    <mergeCell ref="B32:L32"/>
+    <mergeCell ref="C35:L35"/>
+    <mergeCell ref="B43:L43"/>
+    <mergeCell ref="C46:L46"/>
+    <mergeCell ref="B54:L54"/>
+    <mergeCell ref="C57:L57"/>
     <mergeCell ref="B63:L63"/>
   </mergeCells>
-  <conditionalFormatting sqref="B15:K17">
+  <conditionalFormatting sqref="B28:L30">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$C$6&lt;&gt;"H"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B26:K27">
+  <conditionalFormatting sqref="B39:L40">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$C$6&lt;&gt;"H"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H24:I24">
+  <conditionalFormatting sqref="H37:I37">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>$C$6&lt;&gt;"H"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B18:K18">
+  <conditionalFormatting sqref="B31:L31">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$C$6="H"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:K29">
+  <conditionalFormatting sqref="B41:L42">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>$C$6="H"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J24:J24">
+  <conditionalFormatting sqref="J37:J37">
     <cfRule type="expression" dxfId="5" priority="1">
       <formula>$C$6="H"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B55:K62">
+  <conditionalFormatting sqref="B15:L22">
     <cfRule type="expression" dxfId="6" priority="1">
       <formula>$C$6&lt;&gt;"H"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
-    <dataValidation type="list" showErrorMessage="1" error="Name one of the connections declared in chapter 5." sqref="C35:C38">
-      <formula1>PARAM!$B$44:$B$49</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="end plate bolts through the column; fin plate bolts through the beam web." sqref="C48:C53">
+      <formula1>"end plate,fin plate"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="end plate bolts through the column; fin plate bolts through the beam web." sqref="C44:C49">
-      <formula1>"end plate,fin plate"</formula1>
+    <dataValidation type="list" showErrorMessage="1" error="Name one of the connections declared in chapter 5." sqref="C59:C62">
+      <formula1>PARAM!$B$48:$B$53</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="H for an I section, R for a square tube." sqref="C6">
       <formula1>"H,R"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" error="Pick an H section — a beam has to have a web to bolt through." sqref="D35:D38">
+    <dataValidation type="list" showErrorMessage="1" error="Pick an H section — a beam has to have a web to bolt through." sqref="D59:D62">
       <formula1>SECT!$A$2:$A$60</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="Pick one from the list, or &quot;user define&quot; at the top of it." sqref="D6">
       <formula1>INDIRECT("SEC_"&amp;$C$6)</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="G24">
+    <dataValidation type="list" sqref="G37">
       <formula1>"F8T,F10T,F13T"</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="0, 90 or -90 degrees about the column axis." sqref="J6">
@@ -3665,7 +3665,7 @@
         <v>SS275</v>
       </c>
       <c r="E11" s="22">
-        <f>IF(PARAM!$C$6="H",PARAM!$G$15,PARAM!$G$18)</f>
+        <f>IF(PARAM!$C$6="H",PARAM!$G$28,PARAM!$G$31)</f>
         <v>12</v>
       </c>
       <c r="F11" s="22" t="s">
@@ -3675,11 +3675,11 @@
         <v>139</v>
       </c>
       <c r="H11" s="22">
-        <f>IF(PARAM!$C$6="H",PARAM!$E$15,PARAM!$E$18)</f>
+        <f>IF(PARAM!$C$6="H",PARAM!$E$28,PARAM!$E$31)</f>
         <v>300</v>
       </c>
       <c r="I11" s="22">
-        <f>IF(PARAM!$C$6="H",PARAM!$F$15,PARAM!$F$18)</f>
+        <f>IF(PARAM!$C$6="H",PARAM!$F$28,PARAM!$F$31)</f>
         <v>330</v>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
         <v>SS275</v>
       </c>
       <c r="E12" s="22">
-        <f>PARAM!$G$16</f>
+        <f>PARAM!$G$29</f>
         <v>10</v>
       </c>
       <c r="F12" s="22" t="s">
@@ -3708,11 +3708,11 @@
         <v>139</v>
       </c>
       <c r="H12" s="22">
-        <f>PARAM!$E$16</f>
+        <f>PARAM!$E$29</f>
         <v>110</v>
       </c>
       <c r="I12" s="22">
-        <f>PARAM!$F$16</f>
+        <f>PARAM!$F$29</f>
         <v>330</v>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
         <v>SS275</v>
       </c>
       <c r="E13" s="22">
-        <f>PARAM!$G$17</f>
+        <f>PARAM!$G$30</f>
         <v>10</v>
       </c>
       <c r="F13" s="22" t="s">
@@ -3741,11 +3741,11 @@
         <v>139</v>
       </c>
       <c r="H13" s="22">
-        <f>PARAM!$E$17</f>
+        <f>PARAM!$E$30</f>
         <v>234</v>
       </c>
       <c r="I13" s="22">
-        <f>PARAM!$F$17</f>
+        <f>PARAM!$F$30</f>
         <v>330</v>
       </c>
     </row>
@@ -3760,30 +3760,30 @@
         <v>153</v>
       </c>
       <c r="D14" s="22" t="str">
-        <f>PARAM!$G$24</f>
+        <f>PARAM!$G$37</f>
         <v>F10T</v>
       </c>
       <c r="E14" s="22">
-        <f>PARAM!$E$24</f>
+        <f>PARAM!$E$37</f>
         <v>16</v>
       </c>
       <c r="F14" s="22">
-        <f>IF(PARAM!$C$6="H",PARAM!$H$24,PARAM!$J$24)</f>
+        <f>IF(PARAM!$C$6="H",PARAM!$H$37,PARAM!$J$37)</f>
         <v>55</v>
       </c>
       <c r="G14" s="22">
-        <f>PARAM!$F$24</f>
+        <f>PARAM!$F$37</f>
         <v>18</v>
       </c>
       <c r="H14" s="22"/>
       <c r="I14" s="22"/>
       <c r="J14" s="22"/>
       <c r="K14" s="22">
-        <f>0.9*PARAM!$E$24</f>
+        <f>0.9*PARAM!$E$37</f>
         <v>14.4</v>
       </c>
       <c r="L14" s="22">
-        <f>IF(PARAM!$C$6="H",PARAM!$H$24-PARAM!$G$15-PARAM!$H$6-PARAM!$G$16,PARAM!$J$24-2*PARAM!$G$18)-0.9*PARAM!$E$24</f>
+        <f>IF(PARAM!$C$6="H",PARAM!$H$37-PARAM!$G$28-PARAM!$H$6-PARAM!$G$29,PARAM!$J$37-2*PARAM!$G$31)-0.9*PARAM!$E$37</f>
         <v>3.6</v>
       </c>
     </row>
@@ -3798,30 +3798,30 @@
         <v>155</v>
       </c>
       <c r="D15" s="22" t="str">
-        <f>PARAM!$G$24</f>
+        <f>PARAM!$G$37</f>
         <v>F10T</v>
       </c>
       <c r="E15" s="22">
-        <f>PARAM!$E$24</f>
+        <f>PARAM!$E$37</f>
         <v>16</v>
       </c>
       <c r="F15" s="22">
-        <f>IF(PARAM!$C$6="H",PARAM!$I$24,1)</f>
+        <f>IF(PARAM!$C$6="H",PARAM!$I$37,1)</f>
         <v>50</v>
       </c>
       <c r="G15" s="22">
-        <f>PARAM!$F$24</f>
+        <f>PARAM!$F$37</f>
         <v>18</v>
       </c>
       <c r="H15" s="22"/>
       <c r="I15" s="22"/>
       <c r="J15" s="22"/>
       <c r="K15" s="22">
-        <f>0.9*PARAM!$E$24</f>
+        <f>0.9*PARAM!$E$37</f>
         <v>14.4</v>
       </c>
       <c r="L15" s="22">
-        <f>IF(PARAM!$C$6="H",PARAM!$I$24-PARAM!$G$6-2*PARAM!$G$17-0.9*PARAM!$E$24,0)</f>
+        <f>IF(PARAM!$C$6="H",PARAM!$I$37-PARAM!$G$6-2*PARAM!$G$30-0.9*PARAM!$E$37,0)</f>
         <v>5.6</v>
       </c>
     </row>
@@ -3855,7 +3855,7 @@
         <v>SS275</v>
       </c>
       <c r="E19" s="22">
-        <f>MAX(1,PARAM!$H$55)</f>
+        <f>MAX(1,PARAM!$H$15)</f>
         <v>12</v>
       </c>
       <c r="F19" s="22" t="s">
@@ -3865,11 +3865,11 @@
         <v>139</v>
       </c>
       <c r="H19" s="22">
-        <f>MAX(1,PARAM!$G$55)</f>
+        <f>MAX(1,PARAM!$G$15)</f>
         <v>270</v>
       </c>
       <c r="I19" s="22">
-        <f>MAX(1,PARAM!$F$55)</f>
+        <f>MAX(1,PARAM!$F$15)</f>
         <v>145</v>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
         <v>SS275</v>
       </c>
       <c r="E20" s="22">
-        <f>MAX(1,PARAM!$H$56)</f>
+        <f>MAX(1,PARAM!$H$16)</f>
         <v>12</v>
       </c>
       <c r="F20" s="22" t="s">
@@ -3895,11 +3895,11 @@
         <v>139</v>
       </c>
       <c r="H20" s="22">
-        <f>MAX(1,PARAM!$G$56)</f>
+        <f>MAX(1,PARAM!$G$16)</f>
         <v>270</v>
       </c>
       <c r="I20" s="22">
-        <f>MAX(1,PARAM!$F$56)</f>
+        <f>MAX(1,PARAM!$F$16)</f>
         <v>145</v>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
         <v>SS275</v>
       </c>
       <c r="E21" s="22">
-        <f>MAX(1,PARAM!$H$57)</f>
+        <f>MAX(1,PARAM!$H$17)</f>
         <v>1</v>
       </c>
       <c r="F21" s="22" t="s">
@@ -3925,11 +3925,11 @@
         <v>139</v>
       </c>
       <c r="H21" s="22">
-        <f>MAX(1,PARAM!$G$57)</f>
+        <f>MAX(1,PARAM!$G$17)</f>
         <v>1</v>
       </c>
       <c r="I21" s="22">
-        <f>MAX(1,PARAM!$F$57)</f>
+        <f>MAX(1,PARAM!$F$17)</f>
         <v>1</v>
       </c>
     </row>
@@ -3945,7 +3945,7 @@
         <v>SS275</v>
       </c>
       <c r="E22" s="22">
-        <f>MAX(1,PARAM!$H$58)</f>
+        <f>MAX(1,PARAM!$H$18)</f>
         <v>1</v>
       </c>
       <c r="F22" s="22" t="s">
@@ -3955,11 +3955,11 @@
         <v>139</v>
       </c>
       <c r="H22" s="22">
-        <f>MAX(1,PARAM!$G$58)</f>
+        <f>MAX(1,PARAM!$G$18)</f>
         <v>1</v>
       </c>
       <c r="I22" s="22">
-        <f>MAX(1,PARAM!$F$58)</f>
+        <f>MAX(1,PARAM!$F$18)</f>
         <v>1</v>
       </c>
     </row>
@@ -3975,7 +3975,7 @@
         <v>SS275</v>
       </c>
       <c r="E23" s="22">
-        <f>MAX(1,PARAM!$H$59)</f>
+        <f>MAX(1,PARAM!$H$19)</f>
         <v>1</v>
       </c>
       <c r="F23" s="22" t="s">
@@ -3985,11 +3985,11 @@
         <v>139</v>
       </c>
       <c r="H23" s="22">
-        <f>MAX(1,PARAM!$G$59)</f>
+        <f>MAX(1,PARAM!$G$19)</f>
         <v>1</v>
       </c>
       <c r="I23" s="22">
-        <f>MAX(1,PARAM!$F$59)</f>
+        <f>MAX(1,PARAM!$F$19)</f>
         <v>1</v>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
         <v>SS275</v>
       </c>
       <c r="E24" s="22">
-        <f>MAX(1,PARAM!$H$60)</f>
+        <f>MAX(1,PARAM!$H$20)</f>
         <v>1</v>
       </c>
       <c r="F24" s="22" t="s">
@@ -4015,11 +4015,11 @@
         <v>139</v>
       </c>
       <c r="H24" s="22">
-        <f>MAX(1,PARAM!$G$60)</f>
+        <f>MAX(1,PARAM!$G$20)</f>
         <v>1</v>
       </c>
       <c r="I24" s="22">
-        <f>MAX(1,PARAM!$F$60)</f>
+        <f>MAX(1,PARAM!$F$20)</f>
         <v>1</v>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
         <v>SS275</v>
       </c>
       <c r="E25" s="22">
-        <f>MAX(1,PARAM!$H$61)</f>
+        <f>MAX(1,PARAM!$H$21)</f>
         <v>1</v>
       </c>
       <c r="F25" s="22" t="s">
@@ -4045,11 +4045,11 @@
         <v>139</v>
       </c>
       <c r="H25" s="22">
-        <f>MAX(1,PARAM!$G$61)</f>
+        <f>MAX(1,PARAM!$G$21)</f>
         <v>1</v>
       </c>
       <c r="I25" s="22">
-        <f>MAX(1,PARAM!$F$61)</f>
+        <f>MAX(1,PARAM!$F$21)</f>
         <v>1</v>
       </c>
     </row>
@@ -4065,7 +4065,7 @@
         <v>SS275</v>
       </c>
       <c r="E26" s="22">
-        <f>MAX(1,PARAM!$H$62)</f>
+        <f>MAX(1,PARAM!$H$22)</f>
         <v>1</v>
       </c>
       <c r="F26" s="22" t="s">
@@ -4075,11 +4075,11 @@
         <v>139</v>
       </c>
       <c r="H26" s="22">
-        <f>MAX(1,PARAM!$G$62)</f>
+        <f>MAX(1,PARAM!$G$22)</f>
         <v>1</v>
       </c>
       <c r="I26" s="22">
-        <f>MAX(1,PARAM!$F$62)</f>
+        <f>MAX(1,PARAM!$F$22)</f>
         <v>1</v>
       </c>
     </row>
@@ -4282,14 +4282,14 @@
         <v>139</v>
       </c>
       <c r="F38" s="22">
-        <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$15/2)),0)</f>
+        <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$28/2)),0)</f>
         <v>156</v>
       </c>
       <c r="G38" s="22">
         <v>0</v>
       </c>
       <c r="H38" s="22">
-        <f>IF(PARAM!$C$6="H",0,(PARAM!$G$18/2))</f>
+        <f>IF(PARAM!$C$6="H",0,(PARAM!$G$31/2))</f>
         <v>0</v>
       </c>
       <c r="I38" s="22" t="str">
@@ -4312,14 +4312,14 @@
         <v>139</v>
       </c>
       <c r="F39" s="22">
-        <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$15/2)),0)</f>
+        <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$28/2)),0)</f>
         <v>-156</v>
       </c>
       <c r="G39" s="22">
         <v>0</v>
       </c>
       <c r="H39" s="22">
-        <f>IF(PARAM!$C$6="H",0,-(PARAM!$G$18/2))</f>
+        <f>IF(PARAM!$C$6="H",0,-(PARAM!$G$31/2))</f>
         <v>0</v>
       </c>
       <c r="I39" s="22" t="str">
@@ -4345,11 +4345,11 @@
         <v>139</v>
       </c>
       <c r="F40" s="22">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
         <v>130</v>
       </c>
       <c r="G40" s="22">
-        <f>((PARAM!$I$26/2+((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))/2))</f>
+        <f>((PARAM!$I$39/2+((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))/2))</f>
         <v>80</v>
       </c>
       <c r="H40" s="22">
@@ -4374,11 +4374,11 @@
         <v>139</v>
       </c>
       <c r="F41" s="22">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
         <v>130</v>
       </c>
       <c r="G41" s="22">
-        <f>-((PARAM!$I$26/2+((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))/2))</f>
+        <f>-((PARAM!$I$39/2+((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))/2))</f>
         <v>-80</v>
       </c>
       <c r="H41" s="22">
@@ -4403,11 +4403,11 @@
         <v>139</v>
       </c>
       <c r="F42" s="22">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
         <v>-130</v>
       </c>
       <c r="G42" s="22">
-        <f>((PARAM!$I$26/2+((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))/2))</f>
+        <f>((PARAM!$I$39/2+((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))/2))</f>
         <v>80</v>
       </c>
       <c r="H42" s="22">
@@ -4432,11 +4432,11 @@
         <v>139</v>
       </c>
       <c r="F43" s="22">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
         <v>-130</v>
       </c>
       <c r="G43" s="22">
-        <f>-((PARAM!$I$26/2+((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))/2))</f>
+        <f>-((PARAM!$I$39/2+((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))/2))</f>
         <v>-80</v>
       </c>
       <c r="H43" s="22">
@@ -4467,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="22">
-        <f>((PARAM!$G$6/2+PARAM!$G$17/2))</f>
+        <f>((PARAM!$G$6/2+PARAM!$G$30/2))</f>
         <v>10</v>
       </c>
       <c r="H44" s="22">
@@ -4495,7 +4495,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="22">
-        <f>-((PARAM!$G$6/2+PARAM!$G$17/2))</f>
+        <f>-((PARAM!$G$6/2+PARAM!$G$30/2))</f>
         <v>-10</v>
       </c>
       <c r="H45" s="22">
@@ -4521,15 +4521,15 @@
       </c>
       <c r="E46" s="22"/>
       <c r="F46" s="22">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29))</f>
         <v>125</v>
       </c>
       <c r="G46" s="22">
-        <f>(PARAM!$I$26/2)</f>
+        <f>(PARAM!$I$39/2)</f>
         <v>50</v>
       </c>
       <c r="H46" s="22">
-        <f>(PARAM!$F$26/2)</f>
+        <f>(PARAM!$F$39/2)</f>
         <v>35</v>
       </c>
       <c r="I46" s="22" t="s">
@@ -4548,14 +4548,14 @@
         <v>0</v>
       </c>
       <c r="N46" s="22">
-        <f>((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
+        <f>((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))</f>
         <v>60</v>
       </c>
       <c r="O46" s="22">
         <v>0</v>
       </c>
       <c r="P46" s="22">
-        <f>PARAM!$H$26/2-1</f>
+        <f>PARAM!$H$39/2-1</f>
         <v>1</v>
       </c>
       <c r="Q46" s="22">
@@ -4565,11 +4565,11 @@
         <v>0</v>
       </c>
       <c r="S46" s="22">
-        <f>((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
+        <f>((PARAM!$F$28/2-PARAM!$G$39-PARAM!$F$39/2)/(PARAM!$E$39/2-1))</f>
         <v>85</v>
       </c>
       <c r="T46" s="22">
-        <f>PARAM!$E$26/2-1</f>
+        <f>PARAM!$E$39/2-1</f>
         <v>1</v>
       </c>
     </row>
@@ -4586,15 +4586,15 @@
       </c>
       <c r="E47" s="22"/>
       <c r="F47" s="22">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29))</f>
         <v>125</v>
       </c>
       <c r="G47" s="22">
-        <f>-(PARAM!$I$26/2)</f>
+        <f>-(PARAM!$I$39/2)</f>
         <v>-50</v>
       </c>
       <c r="H47" s="22">
-        <f>(PARAM!$F$26/2)</f>
+        <f>(PARAM!$F$39/2)</f>
         <v>35</v>
       </c>
       <c r="I47" s="22" t="s">
@@ -4613,14 +4613,14 @@
         <v>0</v>
       </c>
       <c r="N47" s="22">
-        <f>-((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
+        <f>-((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))</f>
         <v>-60</v>
       </c>
       <c r="O47" s="22">
         <v>0</v>
       </c>
       <c r="P47" s="22">
-        <f>PARAM!$H$26/2-1</f>
+        <f>PARAM!$H$39/2-1</f>
         <v>1</v>
       </c>
       <c r="Q47" s="22">
@@ -4630,11 +4630,11 @@
         <v>0</v>
       </c>
       <c r="S47" s="22">
-        <f>((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
+        <f>((PARAM!$F$28/2-PARAM!$G$39-PARAM!$F$39/2)/(PARAM!$E$39/2-1))</f>
         <v>85</v>
       </c>
       <c r="T47" s="22">
-        <f>PARAM!$E$26/2-1</f>
+        <f>PARAM!$E$39/2-1</f>
         <v>1</v>
       </c>
     </row>
@@ -4651,15 +4651,15 @@
       </c>
       <c r="E48" s="22"/>
       <c r="F48" s="22">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29))</f>
         <v>125</v>
       </c>
       <c r="G48" s="22">
-        <f>(PARAM!$I$26/2)</f>
+        <f>(PARAM!$I$39/2)</f>
         <v>50</v>
       </c>
       <c r="H48" s="22">
-        <f>-(PARAM!$F$26/2)</f>
+        <f>-(PARAM!$F$39/2)</f>
         <v>-35</v>
       </c>
       <c r="I48" s="22" t="s">
@@ -4678,14 +4678,14 @@
         <v>0</v>
       </c>
       <c r="N48" s="22">
-        <f>((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
+        <f>((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))</f>
         <v>60</v>
       </c>
       <c r="O48" s="22">
         <v>0</v>
       </c>
       <c r="P48" s="22">
-        <f>PARAM!$H$26/2-1</f>
+        <f>PARAM!$H$39/2-1</f>
         <v>1</v>
       </c>
       <c r="Q48" s="22">
@@ -4695,11 +4695,11 @@
         <v>0</v>
       </c>
       <c r="S48" s="22">
-        <f>-((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
+        <f>-((PARAM!$F$28/2-PARAM!$G$39-PARAM!$F$39/2)/(PARAM!$E$39/2-1))</f>
         <v>-85</v>
       </c>
       <c r="T48" s="22">
-        <f>PARAM!$E$26/2-1</f>
+        <f>PARAM!$E$39/2-1</f>
         <v>1</v>
       </c>
     </row>
@@ -4716,15 +4716,15 @@
       </c>
       <c r="E49" s="22"/>
       <c r="F49" s="22">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29))</f>
         <v>125</v>
       </c>
       <c r="G49" s="22">
-        <f>-(PARAM!$I$26/2)</f>
+        <f>-(PARAM!$I$39/2)</f>
         <v>-50</v>
       </c>
       <c r="H49" s="22">
-        <f>-(PARAM!$F$26/2)</f>
+        <f>-(PARAM!$F$39/2)</f>
         <v>-35</v>
       </c>
       <c r="I49" s="22" t="s">
@@ -4743,14 +4743,14 @@
         <v>0</v>
       </c>
       <c r="N49" s="22">
-        <f>-((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
+        <f>-((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))</f>
         <v>-60</v>
       </c>
       <c r="O49" s="22">
         <v>0</v>
       </c>
       <c r="P49" s="22">
-        <f>PARAM!$H$26/2-1</f>
+        <f>PARAM!$H$39/2-1</f>
         <v>1</v>
       </c>
       <c r="Q49" s="22">
@@ -4760,11 +4760,11 @@
         <v>0</v>
       </c>
       <c r="S49" s="22">
-        <f>-((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
+        <f>-((PARAM!$F$28/2-PARAM!$G$39-PARAM!$F$39/2)/(PARAM!$E$39/2-1))</f>
         <v>-85</v>
       </c>
       <c r="T49" s="22">
-        <f>PARAM!$E$26/2-1</f>
+        <f>PARAM!$E$39/2-1</f>
         <v>1</v>
       </c>
     </row>
@@ -4781,15 +4781,15 @@
       </c>
       <c r="E50" s="22"/>
       <c r="F50" s="22">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29))</f>
         <v>-125</v>
       </c>
       <c r="G50" s="22">
-        <f>(PARAM!$I$26/2)</f>
+        <f>(PARAM!$I$39/2)</f>
         <v>50</v>
       </c>
       <c r="H50" s="22">
-        <f>(PARAM!$F$26/2)</f>
+        <f>(PARAM!$F$39/2)</f>
         <v>35</v>
       </c>
       <c r="I50" s="22" t="s">
@@ -4808,14 +4808,14 @@
         <v>0</v>
       </c>
       <c r="N50" s="22">
-        <f>((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
+        <f>((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))</f>
         <v>60</v>
       </c>
       <c r="O50" s="22">
         <v>0</v>
       </c>
       <c r="P50" s="22">
-        <f>PARAM!$H$26/2-1</f>
+        <f>PARAM!$H$39/2-1</f>
         <v>1</v>
       </c>
       <c r="Q50" s="22">
@@ -4825,11 +4825,11 @@
         <v>0</v>
       </c>
       <c r="S50" s="22">
-        <f>((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
+        <f>((PARAM!$F$28/2-PARAM!$G$39-PARAM!$F$39/2)/(PARAM!$E$39/2-1))</f>
         <v>85</v>
       </c>
       <c r="T50" s="22">
-        <f>PARAM!$E$26/2-1</f>
+        <f>PARAM!$E$39/2-1</f>
         <v>1</v>
       </c>
     </row>
@@ -4846,15 +4846,15 @@
       </c>
       <c r="E51" s="22"/>
       <c r="F51" s="22">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29))</f>
         <v>-125</v>
       </c>
       <c r="G51" s="22">
-        <f>-(PARAM!$I$26/2)</f>
+        <f>-(PARAM!$I$39/2)</f>
         <v>-50</v>
       </c>
       <c r="H51" s="22">
-        <f>(PARAM!$F$26/2)</f>
+        <f>(PARAM!$F$39/2)</f>
         <v>35</v>
       </c>
       <c r="I51" s="22" t="s">
@@ -4873,14 +4873,14 @@
         <v>0</v>
       </c>
       <c r="N51" s="22">
-        <f>-((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
+        <f>-((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))</f>
         <v>-60</v>
       </c>
       <c r="O51" s="22">
         <v>0</v>
       </c>
       <c r="P51" s="22">
-        <f>PARAM!$H$26/2-1</f>
+        <f>PARAM!$H$39/2-1</f>
         <v>1</v>
       </c>
       <c r="Q51" s="22">
@@ -4890,11 +4890,11 @@
         <v>0</v>
       </c>
       <c r="S51" s="22">
-        <f>((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
+        <f>((PARAM!$F$28/2-PARAM!$G$39-PARAM!$F$39/2)/(PARAM!$E$39/2-1))</f>
         <v>85</v>
       </c>
       <c r="T51" s="22">
-        <f>PARAM!$E$26/2-1</f>
+        <f>PARAM!$E$39/2-1</f>
         <v>1</v>
       </c>
     </row>
@@ -4911,15 +4911,15 @@
       </c>
       <c r="E52" s="22"/>
       <c r="F52" s="22">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29))</f>
         <v>-125</v>
       </c>
       <c r="G52" s="22">
-        <f>(PARAM!$I$26/2)</f>
+        <f>(PARAM!$I$39/2)</f>
         <v>50</v>
       </c>
       <c r="H52" s="22">
-        <f>-(PARAM!$F$26/2)</f>
+        <f>-(PARAM!$F$39/2)</f>
         <v>-35</v>
       </c>
       <c r="I52" s="22" t="s">
@@ -4938,14 +4938,14 @@
         <v>0</v>
       </c>
       <c r="N52" s="22">
-        <f>((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
+        <f>((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))</f>
         <v>60</v>
       </c>
       <c r="O52" s="22">
         <v>0</v>
       </c>
       <c r="P52" s="22">
-        <f>PARAM!$H$26/2-1</f>
+        <f>PARAM!$H$39/2-1</f>
         <v>1</v>
       </c>
       <c r="Q52" s="22">
@@ -4955,11 +4955,11 @@
         <v>0</v>
       </c>
       <c r="S52" s="22">
-        <f>-((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
+        <f>-((PARAM!$F$28/2-PARAM!$G$39-PARAM!$F$39/2)/(PARAM!$E$39/2-1))</f>
         <v>-85</v>
       </c>
       <c r="T52" s="22">
-        <f>PARAM!$E$26/2-1</f>
+        <f>PARAM!$E$39/2-1</f>
         <v>1</v>
       </c>
     </row>
@@ -4976,15 +4976,15 @@
       </c>
       <c r="E53" s="22"/>
       <c r="F53" s="22">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29))</f>
         <v>-125</v>
       </c>
       <c r="G53" s="22">
-        <f>-(PARAM!$I$26/2)</f>
+        <f>-(PARAM!$I$39/2)</f>
         <v>-50</v>
       </c>
       <c r="H53" s="22">
-        <f>-(PARAM!$F$26/2)</f>
+        <f>-(PARAM!$F$39/2)</f>
         <v>-35</v>
       </c>
       <c r="I53" s="22" t="s">
@@ -5003,14 +5003,14 @@
         <v>0</v>
       </c>
       <c r="N53" s="22">
-        <f>-((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
+        <f>-((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))</f>
         <v>-60</v>
       </c>
       <c r="O53" s="22">
         <v>0</v>
       </c>
       <c r="P53" s="22">
-        <f>PARAM!$H$26/2-1</f>
+        <f>PARAM!$H$39/2-1</f>
         <v>1</v>
       </c>
       <c r="Q53" s="22">
@@ -5020,11 +5020,11 @@
         <v>0</v>
       </c>
       <c r="S53" s="22">
-        <f>-((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
+        <f>-((PARAM!$F$28/2-PARAM!$G$39-PARAM!$F$39/2)/(PARAM!$E$39/2-1))</f>
         <v>-85</v>
       </c>
       <c r="T53" s="22">
-        <f>PARAM!$E$26/2-1</f>
+        <f>PARAM!$E$39/2-1</f>
         <v>1</v>
       </c>
     </row>
@@ -5044,15 +5044,15 @@
       </c>
       <c r="E54" s="22"/>
       <c r="F54" s="22">
-        <f>-(PARAM!$E$18/2-PARAM!$F$29)</f>
+        <f>-(PARAM!$E$31/2-PARAM!$F$42)</f>
         <v>-180</v>
       </c>
       <c r="G54" s="22">
-        <f>((PARAM!$F$18/2-PARAM!$I$29))</f>
+        <f>((PARAM!$F$31/2-PARAM!$I$42))</f>
         <v>180</v>
       </c>
       <c r="H54" s="22">
-        <f>-PARAM!$G$18/2</f>
+        <f>-PARAM!$G$31/2</f>
         <v>-10</v>
       </c>
       <c r="I54" s="22" t="s">
@@ -5068,7 +5068,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="22">
-        <f>((PARAM!$E$18-2*PARAM!$F$29)/(PARAM!$E$29-1))</f>
+        <f>((PARAM!$E$31-2*PARAM!$F$42)/(PARAM!$E$42-1))</f>
         <v>180</v>
       </c>
       <c r="N54" s="22">
@@ -5078,7 +5078,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="22">
-        <f>PARAM!$E$29-1</f>
+        <f>PARAM!$E$42-1</f>
         <v>2</v>
       </c>
     </row>
@@ -5095,15 +5095,15 @@
       </c>
       <c r="E55" s="22"/>
       <c r="F55" s="22">
-        <f>-(PARAM!$E$18/2-PARAM!$F$29)</f>
+        <f>-(PARAM!$E$31/2-PARAM!$F$42)</f>
         <v>-180</v>
       </c>
       <c r="G55" s="22">
-        <f>-((PARAM!$F$18/2-PARAM!$I$29))</f>
+        <f>-((PARAM!$F$31/2-PARAM!$I$42))</f>
         <v>-180</v>
       </c>
       <c r="H55" s="22">
-        <f>-PARAM!$G$18/2</f>
+        <f>-PARAM!$G$31/2</f>
         <v>-10</v>
       </c>
       <c r="I55" s="22" t="s">
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="M55" s="22">
-        <f>((PARAM!$E$18-2*PARAM!$F$29)/(PARAM!$E$29-1))</f>
+        <f>((PARAM!$E$31-2*PARAM!$F$42)/(PARAM!$E$42-1))</f>
         <v>180</v>
       </c>
       <c r="N55" s="22">
@@ -5129,7 +5129,7 @@
         <v>0</v>
       </c>
       <c r="P55" s="22">
-        <f>PARAM!$E$29-1</f>
+        <f>PARAM!$E$42-1</f>
         <v>2</v>
       </c>
     </row>
@@ -5144,20 +5144,20 @@
         <v>178</v>
       </c>
       <c r="D56" s="22" t="str">
-        <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$29&gt;2),"bo.f","")</f>
+        <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
         <v/>
       </c>
       <c r="E56" s="22"/>
       <c r="F56" s="22">
-        <f>((PARAM!$E$18/2-PARAM!$F$29))</f>
+        <f>((PARAM!$E$31/2-PARAM!$F$42))</f>
         <v>180</v>
       </c>
       <c r="G56" s="22">
-        <f>-(PARAM!$F$18/2-PARAM!$I$29)+((PARAM!$F$18-2*PARAM!$I$29)/(PARAM!$H$29-1))</f>
+        <f>-(PARAM!$F$31/2-PARAM!$I$42)+((PARAM!$F$31-2*PARAM!$I$42)/(PARAM!$H$42-1))</f>
         <v>0</v>
       </c>
       <c r="H56" s="22">
-        <f>-PARAM!$G$18/2</f>
+        <f>-PARAM!$G$31/2</f>
         <v>-10</v>
       </c>
       <c r="I56" s="22" t="s">
@@ -5176,14 +5176,14 @@
         <v>0</v>
       </c>
       <c r="N56" s="22">
-        <f>IF(PARAM!$H$29&gt;3,((PARAM!$F$18-2*PARAM!$I$29)/(PARAM!$H$29-1)),0)</f>
+        <f>IF(PARAM!$H$42&gt;3,((PARAM!$F$31-2*PARAM!$I$42)/(PARAM!$H$42-1)),0)</f>
         <v>0</v>
       </c>
       <c r="O56" s="22">
         <v>0</v>
       </c>
       <c r="P56" s="22">
-        <f>MAX(0,PARAM!$H$29-3)</f>
+        <f>MAX(0,PARAM!$H$42-3)</f>
         <v>0</v>
       </c>
     </row>
@@ -5195,20 +5195,20 @@
         <v>178</v>
       </c>
       <c r="D57" s="22" t="str">
-        <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$29&gt;2),"bo.f","")</f>
+        <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
         <v/>
       </c>
       <c r="E57" s="22"/>
       <c r="F57" s="22">
-        <f>-((PARAM!$E$18/2-PARAM!$F$29))</f>
+        <f>-((PARAM!$E$31/2-PARAM!$F$42))</f>
         <v>-180</v>
       </c>
       <c r="G57" s="22">
-        <f>-(PARAM!$F$18/2-PARAM!$I$29)+((PARAM!$F$18-2*PARAM!$I$29)/(PARAM!$H$29-1))</f>
+        <f>-(PARAM!$F$31/2-PARAM!$I$42)+((PARAM!$F$31-2*PARAM!$I$42)/(PARAM!$H$42-1))</f>
         <v>0</v>
       </c>
       <c r="H57" s="22">
-        <f>-PARAM!$G$18/2</f>
+        <f>-PARAM!$G$31/2</f>
         <v>-10</v>
       </c>
       <c r="I57" s="22" t="s">
@@ -5227,14 +5227,14 @@
         <v>0</v>
       </c>
       <c r="N57" s="22">
-        <f>IF(PARAM!$H$29&gt;3,((PARAM!$F$18-2*PARAM!$I$29)/(PARAM!$H$29-1)),0)</f>
+        <f>IF(PARAM!$H$42&gt;3,((PARAM!$F$31-2*PARAM!$I$42)/(PARAM!$H$42-1)),0)</f>
         <v>0</v>
       </c>
       <c r="O57" s="22">
         <v>0</v>
       </c>
       <c r="P57" s="22">
-        <f>MAX(0,PARAM!$H$29-3)</f>
+        <f>MAX(0,PARAM!$H$42-3)</f>
         <v>0</v>
       </c>
     </row>
@@ -5254,15 +5254,15 @@
       </c>
       <c r="E58" s="22"/>
       <c r="F58" s="22">
-        <f>-(PARAM!$E$17/2-PARAM!$J$27)</f>
+        <f>-(PARAM!$E$30/2-PARAM!$J$40)</f>
         <v>-77</v>
       </c>
       <c r="G58" s="22">
-        <f>(PARAM!$G$6/2+PARAM!$G$17)</f>
+        <f>(PARAM!$G$6/2+PARAM!$G$30)</f>
         <v>15</v>
       </c>
       <c r="H58" s="22">
-        <f>(PARAM!$F$27/2)</f>
+        <f>(PARAM!$F$40/2)</f>
         <v>30</v>
       </c>
       <c r="I58" s="22" t="s">
@@ -5278,7 +5278,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="22">
-        <f>(PARAM!$E$17-2*PARAM!$J$27-PARAM!$I$27)/(PARAM!$H$27-1)</f>
+        <f>(PARAM!$E$30-2*PARAM!$J$40-PARAM!$I$40)/(PARAM!$H$40-1)</f>
         <v>77</v>
       </c>
       <c r="N58" s="22">
@@ -5288,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="P58" s="22">
-        <f>PARAM!$H$27-1</f>
+        <f>PARAM!$H$40-1</f>
         <v>2</v>
       </c>
       <c r="Q58" s="22">
@@ -5298,11 +5298,11 @@
         <v>0</v>
       </c>
       <c r="S58" s="22">
-        <f>((PARAM!$F$17/2-PARAM!$G$27-PARAM!$F$27/2)/(PARAM!$E$27/2-1))</f>
+        <f>((PARAM!$F$30/2-PARAM!$G$40-PARAM!$F$40/2)/(PARAM!$E$40/2-1))</f>
         <v>90</v>
       </c>
       <c r="T58" s="22">
-        <f>PARAM!$E$27/2-1</f>
+        <f>PARAM!$E$40/2-1</f>
         <v>1</v>
       </c>
     </row>
@@ -5319,15 +5319,15 @@
       </c>
       <c r="E59" s="22"/>
       <c r="F59" s="22">
-        <f>-(PARAM!$E$17/2-PARAM!$J$27)</f>
+        <f>-(PARAM!$E$30/2-PARAM!$J$40)</f>
         <v>-77</v>
       </c>
       <c r="G59" s="22">
-        <f>(PARAM!$G$6/2+PARAM!$G$17)</f>
+        <f>(PARAM!$G$6/2+PARAM!$G$30)</f>
         <v>15</v>
       </c>
       <c r="H59" s="22">
-        <f>-(PARAM!$F$27/2)</f>
+        <f>-(PARAM!$F$40/2)</f>
         <v>-30</v>
       </c>
       <c r="I59" s="22" t="s">
@@ -5343,7 +5343,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="22">
-        <f>(PARAM!$E$17-2*PARAM!$J$27-PARAM!$I$27)/(PARAM!$H$27-1)</f>
+        <f>(PARAM!$E$30-2*PARAM!$J$40-PARAM!$I$40)/(PARAM!$H$40-1)</f>
         <v>77</v>
       </c>
       <c r="N59" s="22">
@@ -5353,7 +5353,7 @@
         <v>0</v>
       </c>
       <c r="P59" s="22">
-        <f>PARAM!$H$27-1</f>
+        <f>PARAM!$H$40-1</f>
         <v>2</v>
       </c>
       <c r="Q59" s="22">
@@ -5363,11 +5363,11 @@
         <v>0</v>
       </c>
       <c r="S59" s="22">
-        <f>-((PARAM!$F$17/2-PARAM!$G$27-PARAM!$F$27/2)/(PARAM!$E$27/2-1))</f>
+        <f>-((PARAM!$F$30/2-PARAM!$G$40-PARAM!$F$40/2)/(PARAM!$E$40/2-1))</f>
         <v>-90</v>
       </c>
       <c r="T59" s="22">
-        <f>PARAM!$E$27/2-1</f>
+        <f>PARAM!$E$40/2-1</f>
         <v>1</v>
       </c>
     </row>
@@ -5403,14 +5403,14 @@
         <v>139</v>
       </c>
       <c r="F61" s="22">
-        <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$15/2)),0)</f>
+        <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$28/2)),0)</f>
         <v>156</v>
       </c>
       <c r="G61" s="22">
         <v>0</v>
       </c>
       <c r="H61" s="22">
-        <f>IF(PARAM!$C$6="H",0,(PARAM!$G$18/2))</f>
+        <f>IF(PARAM!$C$6="H",0,(PARAM!$G$31/2))</f>
         <v>0</v>
       </c>
       <c r="I61" s="22" t="str">
@@ -5433,14 +5433,14 @@
         <v>139</v>
       </c>
       <c r="F62" s="22">
-        <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$15/2)),0)</f>
+        <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$28/2)),0)</f>
         <v>-156</v>
       </c>
       <c r="G62" s="22">
         <v>0</v>
       </c>
       <c r="H62" s="22">
-        <f>IF(PARAM!$C$6="H",0,-(PARAM!$G$18/2))</f>
+        <f>IF(PARAM!$C$6="H",0,-(PARAM!$G$31/2))</f>
         <v>0</v>
       </c>
       <c r="I62" s="22" t="str">
@@ -5463,11 +5463,11 @@
         <v>139</v>
       </c>
       <c r="F63" s="22">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
         <v>130</v>
       </c>
       <c r="G63" s="22">
-        <f>((PARAM!$I$26/2+((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))/2))</f>
+        <f>((PARAM!$I$39/2+((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))/2))</f>
         <v>80</v>
       </c>
       <c r="H63" s="22">
@@ -5492,11 +5492,11 @@
         <v>139</v>
       </c>
       <c r="F64" s="22">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
         <v>130</v>
       </c>
       <c r="G64" s="22">
-        <f>-((PARAM!$I$26/2+((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))/2))</f>
+        <f>-((PARAM!$I$39/2+((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))/2))</f>
         <v>-80</v>
       </c>
       <c r="H64" s="22">
@@ -5521,11 +5521,11 @@
         <v>139</v>
       </c>
       <c r="F65" s="22">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
         <v>-130</v>
       </c>
       <c r="G65" s="22">
-        <f>((PARAM!$I$26/2+((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))/2))</f>
+        <f>((PARAM!$I$39/2+((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))/2))</f>
         <v>80</v>
       </c>
       <c r="H65" s="22">
@@ -5550,11 +5550,11 @@
         <v>139</v>
       </c>
       <c r="F66" s="22">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16/2))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
         <v>-130</v>
       </c>
       <c r="G66" s="22">
-        <f>-((PARAM!$I$26/2+((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))/2))</f>
+        <f>-((PARAM!$I$39/2+((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))/2))</f>
         <v>-80</v>
       </c>
       <c r="H66" s="22">
@@ -5582,7 +5582,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="22">
-        <f>((PARAM!$G$6/2+PARAM!$G$17/2))</f>
+        <f>((PARAM!$G$6/2+PARAM!$G$30/2))</f>
         <v>10</v>
       </c>
       <c r="H67" s="22">
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="22">
-        <f>-((PARAM!$G$6/2+PARAM!$G$17/2))</f>
+        <f>-((PARAM!$G$6/2+PARAM!$G$30/2))</f>
         <v>-10</v>
       </c>
       <c r="H68" s="22">
@@ -5633,15 +5633,15 @@
       </c>
       <c r="E69" s="22"/>
       <c r="F69" s="22">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29))</f>
         <v>125</v>
       </c>
       <c r="G69" s="22">
-        <f>(PARAM!$I$26/2)</f>
+        <f>(PARAM!$I$39/2)</f>
         <v>50</v>
       </c>
       <c r="H69" s="22">
-        <f>(PARAM!$F$26/2)</f>
+        <f>(PARAM!$F$39/2)</f>
         <v>35</v>
       </c>
       <c r="I69" s="22" t="s">
@@ -5660,14 +5660,14 @@
         <v>0</v>
       </c>
       <c r="N69" s="22">
-        <f>((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
+        <f>((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))</f>
         <v>60</v>
       </c>
       <c r="O69" s="22">
         <v>0</v>
       </c>
       <c r="P69" s="22">
-        <f>PARAM!$H$26/2-1</f>
+        <f>PARAM!$H$39/2-1</f>
         <v>1</v>
       </c>
       <c r="Q69" s="22">
@@ -5677,11 +5677,11 @@
         <v>0</v>
       </c>
       <c r="S69" s="22">
-        <f>((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
+        <f>((PARAM!$F$28/2-PARAM!$G$39-PARAM!$F$39/2)/(PARAM!$E$39/2-1))</f>
         <v>85</v>
       </c>
       <c r="T69" s="22">
-        <f>PARAM!$E$26/2-1</f>
+        <f>PARAM!$E$39/2-1</f>
         <v>1</v>
       </c>
     </row>
@@ -5698,15 +5698,15 @@
       </c>
       <c r="E70" s="22"/>
       <c r="F70" s="22">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29))</f>
         <v>125</v>
       </c>
       <c r="G70" s="22">
-        <f>-(PARAM!$I$26/2)</f>
+        <f>-(PARAM!$I$39/2)</f>
         <v>-50</v>
       </c>
       <c r="H70" s="22">
-        <f>(PARAM!$F$26/2)</f>
+        <f>(PARAM!$F$39/2)</f>
         <v>35</v>
       </c>
       <c r="I70" s="22" t="s">
@@ -5725,14 +5725,14 @@
         <v>0</v>
       </c>
       <c r="N70" s="22">
-        <f>-((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
+        <f>-((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))</f>
         <v>-60</v>
       </c>
       <c r="O70" s="22">
         <v>0</v>
       </c>
       <c r="P70" s="22">
-        <f>PARAM!$H$26/2-1</f>
+        <f>PARAM!$H$39/2-1</f>
         <v>1</v>
       </c>
       <c r="Q70" s="22">
@@ -5742,11 +5742,11 @@
         <v>0</v>
       </c>
       <c r="S70" s="22">
-        <f>((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
+        <f>((PARAM!$F$28/2-PARAM!$G$39-PARAM!$F$39/2)/(PARAM!$E$39/2-1))</f>
         <v>85</v>
       </c>
       <c r="T70" s="22">
-        <f>PARAM!$E$26/2-1</f>
+        <f>PARAM!$E$39/2-1</f>
         <v>1</v>
       </c>
     </row>
@@ -5763,15 +5763,15 @@
       </c>
       <c r="E71" s="22"/>
       <c r="F71" s="22">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29))</f>
         <v>125</v>
       </c>
       <c r="G71" s="22">
-        <f>(PARAM!$I$26/2)</f>
+        <f>(PARAM!$I$39/2)</f>
         <v>50</v>
       </c>
       <c r="H71" s="22">
-        <f>-(PARAM!$F$26/2)</f>
+        <f>-(PARAM!$F$39/2)</f>
         <v>-35</v>
       </c>
       <c r="I71" s="22" t="s">
@@ -5790,14 +5790,14 @@
         <v>0</v>
       </c>
       <c r="N71" s="22">
-        <f>((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
+        <f>((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))</f>
         <v>60</v>
       </c>
       <c r="O71" s="22">
         <v>0</v>
       </c>
       <c r="P71" s="22">
-        <f>PARAM!$H$26/2-1</f>
+        <f>PARAM!$H$39/2-1</f>
         <v>1</v>
       </c>
       <c r="Q71" s="22">
@@ -5807,11 +5807,11 @@
         <v>0</v>
       </c>
       <c r="S71" s="22">
-        <f>-((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
+        <f>-((PARAM!$F$28/2-PARAM!$G$39-PARAM!$F$39/2)/(PARAM!$E$39/2-1))</f>
         <v>-85</v>
       </c>
       <c r="T71" s="22">
-        <f>PARAM!$E$26/2-1</f>
+        <f>PARAM!$E$39/2-1</f>
         <v>1</v>
       </c>
     </row>
@@ -5828,15 +5828,15 @@
       </c>
       <c r="E72" s="22"/>
       <c r="F72" s="22">
-        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
+        <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29))</f>
         <v>125</v>
       </c>
       <c r="G72" s="22">
-        <f>-(PARAM!$I$26/2)</f>
+        <f>-(PARAM!$I$39/2)</f>
         <v>-50</v>
       </c>
       <c r="H72" s="22">
-        <f>-(PARAM!$F$26/2)</f>
+        <f>-(PARAM!$F$39/2)</f>
         <v>-35</v>
       </c>
       <c r="I72" s="22" t="s">
@@ -5855,14 +5855,14 @@
         <v>0</v>
       </c>
       <c r="N72" s="22">
-        <f>-((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
+        <f>-((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))</f>
         <v>-60</v>
       </c>
       <c r="O72" s="22">
         <v>0</v>
       </c>
       <c r="P72" s="22">
-        <f>PARAM!$H$26/2-1</f>
+        <f>PARAM!$H$39/2-1</f>
         <v>1</v>
       </c>
       <c r="Q72" s="22">
@@ -5872,11 +5872,11 @@
         <v>0</v>
       </c>
       <c r="S72" s="22">
-        <f>-((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
+        <f>-((PARAM!$F$28/2-PARAM!$G$39-PARAM!$F$39/2)/(PARAM!$E$39/2-1))</f>
         <v>-85</v>
       </c>
       <c r="T72" s="22">
-        <f>PARAM!$E$26/2-1</f>
+        <f>PARAM!$E$39/2-1</f>
         <v>1</v>
       </c>
     </row>
@@ -5893,15 +5893,15 @@
       </c>
       <c r="E73" s="22"/>
       <c r="F73" s="22">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29))</f>
         <v>-125</v>
       </c>
       <c r="G73" s="22">
-        <f>(PARAM!$I$26/2)</f>
+        <f>(PARAM!$I$39/2)</f>
         <v>50</v>
       </c>
       <c r="H73" s="22">
-        <f>(PARAM!$F$26/2)</f>
+        <f>(PARAM!$F$39/2)</f>
         <v>35</v>
       </c>
       <c r="I73" s="22" t="s">
@@ -5920,14 +5920,14 @@
         <v>0</v>
       </c>
       <c r="N73" s="22">
-        <f>((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
+        <f>((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))</f>
         <v>60</v>
       </c>
       <c r="O73" s="22">
         <v>0</v>
       </c>
       <c r="P73" s="22">
-        <f>PARAM!$H$26/2-1</f>
+        <f>PARAM!$H$39/2-1</f>
         <v>1</v>
       </c>
       <c r="Q73" s="22">
@@ -5937,11 +5937,11 @@
         <v>0</v>
       </c>
       <c r="S73" s="22">
-        <f>((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
+        <f>((PARAM!$F$28/2-PARAM!$G$39-PARAM!$F$39/2)/(PARAM!$E$39/2-1))</f>
         <v>85</v>
       </c>
       <c r="T73" s="22">
-        <f>PARAM!$E$26/2-1</f>
+        <f>PARAM!$E$39/2-1</f>
         <v>1</v>
       </c>
     </row>
@@ -5958,15 +5958,15 @@
       </c>
       <c r="E74" s="22"/>
       <c r="F74" s="22">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29))</f>
         <v>-125</v>
       </c>
       <c r="G74" s="22">
-        <f>-(PARAM!$I$26/2)</f>
+        <f>-(PARAM!$I$39/2)</f>
         <v>-50</v>
       </c>
       <c r="H74" s="22">
-        <f>(PARAM!$F$26/2)</f>
+        <f>(PARAM!$F$39/2)</f>
         <v>35</v>
       </c>
       <c r="I74" s="22" t="s">
@@ -5985,14 +5985,14 @@
         <v>0</v>
       </c>
       <c r="N74" s="22">
-        <f>-((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
+        <f>-((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))</f>
         <v>-60</v>
       </c>
       <c r="O74" s="22">
         <v>0</v>
       </c>
       <c r="P74" s="22">
-        <f>PARAM!$H$26/2-1</f>
+        <f>PARAM!$H$39/2-1</f>
         <v>1</v>
       </c>
       <c r="Q74" s="22">
@@ -6002,11 +6002,11 @@
         <v>0</v>
       </c>
       <c r="S74" s="22">
-        <f>((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
+        <f>((PARAM!$F$28/2-PARAM!$G$39-PARAM!$F$39/2)/(PARAM!$E$39/2-1))</f>
         <v>85</v>
       </c>
       <c r="T74" s="22">
-        <f>PARAM!$E$26/2-1</f>
+        <f>PARAM!$E$39/2-1</f>
         <v>1</v>
       </c>
     </row>
@@ -6023,15 +6023,15 @@
       </c>
       <c r="E75" s="22"/>
       <c r="F75" s="22">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29))</f>
         <v>-125</v>
       </c>
       <c r="G75" s="22">
-        <f>(PARAM!$I$26/2)</f>
+        <f>(PARAM!$I$39/2)</f>
         <v>50</v>
       </c>
       <c r="H75" s="22">
-        <f>-(PARAM!$F$26/2)</f>
+        <f>-(PARAM!$F$39/2)</f>
         <v>-35</v>
       </c>
       <c r="I75" s="22" t="s">
@@ -6050,14 +6050,14 @@
         <v>0</v>
       </c>
       <c r="N75" s="22">
-        <f>((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
+        <f>((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))</f>
         <v>60</v>
       </c>
       <c r="O75" s="22">
         <v>0</v>
       </c>
       <c r="P75" s="22">
-        <f>PARAM!$H$26/2-1</f>
+        <f>PARAM!$H$39/2-1</f>
         <v>1</v>
       </c>
       <c r="Q75" s="22">
@@ -6067,11 +6067,11 @@
         <v>0</v>
       </c>
       <c r="S75" s="22">
-        <f>-((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
+        <f>-((PARAM!$F$28/2-PARAM!$G$39-PARAM!$F$39/2)/(PARAM!$E$39/2-1))</f>
         <v>-85</v>
       </c>
       <c r="T75" s="22">
-        <f>PARAM!$E$26/2-1</f>
+        <f>PARAM!$E$39/2-1</f>
         <v>1</v>
       </c>
     </row>
@@ -6088,15 +6088,15 @@
       </c>
       <c r="E76" s="22"/>
       <c r="F76" s="22">
-        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$16))</f>
+        <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29))</f>
         <v>-125</v>
       </c>
       <c r="G76" s="22">
-        <f>-(PARAM!$I$26/2)</f>
+        <f>-(PARAM!$I$39/2)</f>
         <v>-50</v>
       </c>
       <c r="H76" s="22">
-        <f>-(PARAM!$F$26/2)</f>
+        <f>-(PARAM!$F$39/2)</f>
         <v>-35</v>
       </c>
       <c r="I76" s="22" t="s">
@@ -6115,14 +6115,14 @@
         <v>0</v>
       </c>
       <c r="N76" s="22">
-        <f>-((PARAM!$E$15/2-PARAM!$J$26-PARAM!$I$26/2)/(PARAM!$H$26/2-1))</f>
+        <f>-((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))</f>
         <v>-60</v>
       </c>
       <c r="O76" s="22">
         <v>0</v>
       </c>
       <c r="P76" s="22">
-        <f>PARAM!$H$26/2-1</f>
+        <f>PARAM!$H$39/2-1</f>
         <v>1</v>
       </c>
       <c r="Q76" s="22">
@@ -6132,11 +6132,11 @@
         <v>0</v>
       </c>
       <c r="S76" s="22">
-        <f>-((PARAM!$F$15/2-PARAM!$G$26-PARAM!$F$26/2)/(PARAM!$E$26/2-1))</f>
+        <f>-((PARAM!$F$28/2-PARAM!$G$39-PARAM!$F$39/2)/(PARAM!$E$39/2-1))</f>
         <v>-85</v>
       </c>
       <c r="T76" s="22">
-        <f>PARAM!$E$26/2-1</f>
+        <f>PARAM!$E$39/2-1</f>
         <v>1</v>
       </c>
     </row>
@@ -6153,15 +6153,15 @@
       </c>
       <c r="E77" s="22"/>
       <c r="F77" s="22">
-        <f>-(PARAM!$E$18/2-PARAM!$F$29)</f>
+        <f>-(PARAM!$E$31/2-PARAM!$F$42)</f>
         <v>-180</v>
       </c>
       <c r="G77" s="22">
-        <f>((PARAM!$F$18/2-PARAM!$I$29))</f>
+        <f>((PARAM!$F$31/2-PARAM!$I$42))</f>
         <v>180</v>
       </c>
       <c r="H77" s="22">
-        <f>-PARAM!$G$18/2</f>
+        <f>-PARAM!$G$31/2</f>
         <v>-10</v>
       </c>
       <c r="I77" s="22" t="s">
@@ -6177,7 +6177,7 @@
         <v>0</v>
       </c>
       <c r="M77" s="22">
-        <f>((PARAM!$E$18-2*PARAM!$F$29)/(PARAM!$E$29-1))</f>
+        <f>((PARAM!$E$31-2*PARAM!$F$42)/(PARAM!$E$42-1))</f>
         <v>180</v>
       </c>
       <c r="N77" s="22">
@@ -6187,7 +6187,7 @@
         <v>0</v>
       </c>
       <c r="P77" s="22">
-        <f>PARAM!$E$29-1</f>
+        <f>PARAM!$E$42-1</f>
         <v>2</v>
       </c>
     </row>
@@ -6204,15 +6204,15 @@
       </c>
       <c r="E78" s="22"/>
       <c r="F78" s="22">
-        <f>-(PARAM!$E$18/2-PARAM!$F$29)</f>
+        <f>-(PARAM!$E$31/2-PARAM!$F$42)</f>
         <v>-180</v>
       </c>
       <c r="G78" s="22">
-        <f>-((PARAM!$F$18/2-PARAM!$I$29))</f>
+        <f>-((PARAM!$F$31/2-PARAM!$I$42))</f>
         <v>-180</v>
       </c>
       <c r="H78" s="22">
-        <f>-PARAM!$G$18/2</f>
+        <f>-PARAM!$G$31/2</f>
         <v>-10</v>
       </c>
       <c r="I78" s="22" t="s">
@@ -6228,7 +6228,7 @@
         <v>0</v>
       </c>
       <c r="M78" s="22">
-        <f>((PARAM!$E$18-2*PARAM!$F$29)/(PARAM!$E$29-1))</f>
+        <f>((PARAM!$E$31-2*PARAM!$F$42)/(PARAM!$E$42-1))</f>
         <v>180</v>
       </c>
       <c r="N78" s="22">
@@ -6238,7 +6238,7 @@
         <v>0</v>
       </c>
       <c r="P78" s="22">
-        <f>PARAM!$E$29-1</f>
+        <f>PARAM!$E$42-1</f>
         <v>2</v>
       </c>
     </row>
@@ -6250,20 +6250,20 @@
         <v>188</v>
       </c>
       <c r="D79" s="22" t="str">
-        <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$29&gt;2),"bo.f","")</f>
+        <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
         <v/>
       </c>
       <c r="E79" s="22"/>
       <c r="F79" s="22">
-        <f>((PARAM!$E$18/2-PARAM!$F$29))</f>
+        <f>((PARAM!$E$31/2-PARAM!$F$42))</f>
         <v>180</v>
       </c>
       <c r="G79" s="22">
-        <f>-(PARAM!$F$18/2-PARAM!$I$29)+((PARAM!$F$18-2*PARAM!$I$29)/(PARAM!$H$29-1))</f>
+        <f>-(PARAM!$F$31/2-PARAM!$I$42)+((PARAM!$F$31-2*PARAM!$I$42)/(PARAM!$H$42-1))</f>
         <v>0</v>
       </c>
       <c r="H79" s="22">
-        <f>-PARAM!$G$18/2</f>
+        <f>-PARAM!$G$31/2</f>
         <v>-10</v>
       </c>
       <c r="I79" s="22" t="s">
@@ -6282,14 +6282,14 @@
         <v>0</v>
       </c>
       <c r="N79" s="22">
-        <f>IF(PARAM!$H$29&gt;3,((PARAM!$F$18-2*PARAM!$I$29)/(PARAM!$H$29-1)),0)</f>
+        <f>IF(PARAM!$H$42&gt;3,((PARAM!$F$31-2*PARAM!$I$42)/(PARAM!$H$42-1)),0)</f>
         <v>0</v>
       </c>
       <c r="O79" s="22">
         <v>0</v>
       </c>
       <c r="P79" s="22">
-        <f>MAX(0,PARAM!$H$29-3)</f>
+        <f>MAX(0,PARAM!$H$42-3)</f>
         <v>0</v>
       </c>
     </row>
@@ -6301,20 +6301,20 @@
         <v>188</v>
       </c>
       <c r="D80" s="22" t="str">
-        <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$29&gt;2),"bo.f","")</f>
+        <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
         <v/>
       </c>
       <c r="E80" s="22"/>
       <c r="F80" s="22">
-        <f>-((PARAM!$E$18/2-PARAM!$F$29))</f>
+        <f>-((PARAM!$E$31/2-PARAM!$F$42))</f>
         <v>-180</v>
       </c>
       <c r="G80" s="22">
-        <f>-(PARAM!$F$18/2-PARAM!$I$29)+((PARAM!$F$18-2*PARAM!$I$29)/(PARAM!$H$29-1))</f>
+        <f>-(PARAM!$F$31/2-PARAM!$I$42)+((PARAM!$F$31-2*PARAM!$I$42)/(PARAM!$H$42-1))</f>
         <v>0</v>
       </c>
       <c r="H80" s="22">
-        <f>-PARAM!$G$18/2</f>
+        <f>-PARAM!$G$31/2</f>
         <v>-10</v>
       </c>
       <c r="I80" s="22" t="s">
@@ -6333,14 +6333,14 @@
         <v>0</v>
       </c>
       <c r="N80" s="22">
-        <f>IF(PARAM!$H$29&gt;3,((PARAM!$F$18-2*PARAM!$I$29)/(PARAM!$H$29-1)),0)</f>
+        <f>IF(PARAM!$H$42&gt;3,((PARAM!$F$31-2*PARAM!$I$42)/(PARAM!$H$42-1)),0)</f>
         <v>0</v>
       </c>
       <c r="O80" s="22">
         <v>0</v>
       </c>
       <c r="P80" s="22">
-        <f>MAX(0,PARAM!$H$29-3)</f>
+        <f>MAX(0,PARAM!$H$42-3)</f>
         <v>0</v>
       </c>
     </row>
@@ -6357,15 +6357,15 @@
       </c>
       <c r="E81" s="22"/>
       <c r="F81" s="22">
-        <f>-(PARAM!$E$17/2-PARAM!$J$27)</f>
+        <f>-(PARAM!$E$30/2-PARAM!$J$40)</f>
         <v>-77</v>
       </c>
       <c r="G81" s="22">
-        <f>(PARAM!$G$6/2+PARAM!$G$17)</f>
+        <f>(PARAM!$G$6/2+PARAM!$G$30)</f>
         <v>15</v>
       </c>
       <c r="H81" s="22">
-        <f>(PARAM!$F$27/2)</f>
+        <f>(PARAM!$F$40/2)</f>
         <v>30</v>
       </c>
       <c r="I81" s="22" t="s">
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="22">
-        <f>(PARAM!$E$17-2*PARAM!$J$27-PARAM!$I$27)/(PARAM!$H$27-1)</f>
+        <f>(PARAM!$E$30-2*PARAM!$J$40-PARAM!$I$40)/(PARAM!$H$40-1)</f>
         <v>77</v>
       </c>
       <c r="N81" s="22">
@@ -6391,7 +6391,7 @@
         <v>0</v>
       </c>
       <c r="P81" s="22">
-        <f>PARAM!$H$27-1</f>
+        <f>PARAM!$H$40-1</f>
         <v>2</v>
       </c>
       <c r="Q81" s="22">
@@ -6401,11 +6401,11 @@
         <v>0</v>
       </c>
       <c r="S81" s="22">
-        <f>((PARAM!$F$17/2-PARAM!$G$27-PARAM!$F$27/2)/(PARAM!$E$27/2-1))</f>
+        <f>((PARAM!$F$30/2-PARAM!$G$40-PARAM!$F$40/2)/(PARAM!$E$40/2-1))</f>
         <v>90</v>
       </c>
       <c r="T81" s="22">
-        <f>PARAM!$E$27/2-1</f>
+        <f>PARAM!$E$40/2-1</f>
         <v>1</v>
       </c>
     </row>
@@ -6422,15 +6422,15 @@
       </c>
       <c r="E82" s="22"/>
       <c r="F82" s="22">
-        <f>-(PARAM!$E$17/2-PARAM!$J$27)</f>
+        <f>-(PARAM!$E$30/2-PARAM!$J$40)</f>
         <v>-77</v>
       </c>
       <c r="G82" s="22">
-        <f>(PARAM!$G$6/2+PARAM!$G$17)</f>
+        <f>(PARAM!$G$6/2+PARAM!$G$30)</f>
         <v>15</v>
       </c>
       <c r="H82" s="22">
-        <f>-(PARAM!$F$27/2)</f>
+        <f>-(PARAM!$F$40/2)</f>
         <v>-30</v>
       </c>
       <c r="I82" s="22" t="s">
@@ -6446,7 +6446,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="22">
-        <f>(PARAM!$E$17-2*PARAM!$J$27-PARAM!$I$27)/(PARAM!$H$27-1)</f>
+        <f>(PARAM!$E$30-2*PARAM!$J$40-PARAM!$I$40)/(PARAM!$H$40-1)</f>
         <v>77</v>
       </c>
       <c r="N82" s="22">
@@ -6456,7 +6456,7 @@
         <v>0</v>
       </c>
       <c r="P82" s="22">
-        <f>PARAM!$H$27-1</f>
+        <f>PARAM!$H$40-1</f>
         <v>2</v>
       </c>
       <c r="Q82" s="22">
@@ -6466,11 +6466,11 @@
         <v>0</v>
       </c>
       <c r="S82" s="22">
-        <f>-((PARAM!$F$17/2-PARAM!$G$27-PARAM!$F$27/2)/(PARAM!$E$27/2-1))</f>
+        <f>-((PARAM!$F$30/2-PARAM!$G$40-PARAM!$F$40/2)/(PARAM!$E$40/2-1))</f>
         <v>-90</v>
       </c>
       <c r="T82" s="22">
-        <f>PARAM!$E$27/2-1</f>
+        <f>PARAM!$E$40/2-1</f>
         <v>1</v>
       </c>
     </row>
@@ -6517,7 +6517,7 @@
         <v>174</v>
       </c>
       <c r="D87" s="22" t="str">
-        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$55&gt;0),"pl.stf1","")</f>
+        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$15&gt;0),"pl.stf1","")</f>
         <v>pl.stf1</v>
       </c>
       <c r="E87" s="22" t="s">
@@ -6531,7 +6531,7 @@
         <v>-77.5</v>
       </c>
       <c r="H87" s="22">
-        <f>PARAM!$G$7/2+PARAM!$E$55</f>
+        <f>PARAM!$G$7/2+PARAM!$E$15</f>
         <v>845.5</v>
       </c>
       <c r="I87" s="22" t="s">
@@ -6568,7 +6568,7 @@
         <v>174</v>
       </c>
       <c r="D88" s="22" t="str">
-        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$56&gt;0),"pl.stf2","")</f>
+        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$16&gt;0),"pl.stf2","")</f>
         <v>pl.stf2</v>
       </c>
       <c r="E88" s="22" t="s">
@@ -6582,7 +6582,7 @@
         <v>-77.5</v>
       </c>
       <c r="H88" s="22">
-        <f>PARAM!$G$7/2+PARAM!$E$56</f>
+        <f>PARAM!$G$7/2+PARAM!$E$16</f>
         <v>554.5</v>
       </c>
       <c r="I88" s="22" t="s">
@@ -6619,7 +6619,7 @@
         <v>174</v>
       </c>
       <c r="D89" s="22" t="str">
-        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$57&gt;0),"pl.stf3","")</f>
+        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$17&gt;0),"pl.stf3","")</f>
         <v/>
       </c>
       <c r="E89" s="22" t="s">
@@ -6633,7 +6633,7 @@
         <v>-77.5</v>
       </c>
       <c r="H89" s="22">
-        <f>PARAM!$G$7/2+PARAM!$E$57</f>
+        <f>PARAM!$G$7/2+PARAM!$E$17</f>
         <v>700</v>
       </c>
       <c r="I89" s="22" t="s">
@@ -6670,7 +6670,7 @@
         <v>174</v>
       </c>
       <c r="D90" s="22" t="str">
-        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$58&gt;0),"pl.stf4","")</f>
+        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$18&gt;0),"pl.stf4","")</f>
         <v/>
       </c>
       <c r="E90" s="22" t="s">
@@ -6684,7 +6684,7 @@
         <v>-77.5</v>
       </c>
       <c r="H90" s="22">
-        <f>PARAM!$G$7/2+PARAM!$E$58</f>
+        <f>PARAM!$G$7/2+PARAM!$E$18</f>
         <v>700</v>
       </c>
       <c r="I90" s="22" t="s">
@@ -6721,7 +6721,7 @@
         <v>174</v>
       </c>
       <c r="D91" s="22" t="str">
-        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$59&gt;0),"pl.stf5","")</f>
+        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$19&gt;0),"pl.stf5","")</f>
         <v/>
       </c>
       <c r="E91" s="22" t="s">
@@ -6735,7 +6735,7 @@
         <v>-77.5</v>
       </c>
       <c r="H91" s="22">
-        <f>PARAM!$G$7/2+PARAM!$E$59</f>
+        <f>PARAM!$G$7/2+PARAM!$E$19</f>
         <v>700</v>
       </c>
       <c r="I91" s="22" t="s">
@@ -6772,7 +6772,7 @@
         <v>174</v>
       </c>
       <c r="D92" s="22" t="str">
-        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$60&gt;0),"pl.stf6","")</f>
+        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$20&gt;0),"pl.stf6","")</f>
         <v/>
       </c>
       <c r="E92" s="22" t="s">
@@ -6786,7 +6786,7 @@
         <v>-77.5</v>
       </c>
       <c r="H92" s="22">
-        <f>PARAM!$G$7/2+PARAM!$E$60</f>
+        <f>PARAM!$G$7/2+PARAM!$E$20</f>
         <v>700</v>
       </c>
       <c r="I92" s="22" t="s">
@@ -6823,7 +6823,7 @@
         <v>174</v>
       </c>
       <c r="D93" s="22" t="str">
-        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$61&gt;0),"pl.stf7","")</f>
+        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$21&gt;0),"pl.stf7","")</f>
         <v/>
       </c>
       <c r="E93" s="22" t="s">
@@ -6837,7 +6837,7 @@
         <v>-77.5</v>
       </c>
       <c r="H93" s="22">
-        <f>PARAM!$G$7/2+PARAM!$E$61</f>
+        <f>PARAM!$G$7/2+PARAM!$E$21</f>
         <v>700</v>
       </c>
       <c r="I93" s="22" t="s">
@@ -6874,7 +6874,7 @@
         <v>174</v>
       </c>
       <c r="D94" s="22" t="str">
-        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$62&gt;0),"pl.stf8","")</f>
+        <f>IF(AND(PARAM!$C$6="H",PARAM!$H$22&gt;0),"pl.stf8","")</f>
         <v/>
       </c>
       <c r="E94" s="22" t="s">
@@ -6888,7 +6888,7 @@
         <v>-77.5</v>
       </c>
       <c r="H94" s="22">
-        <f>PARAM!$G$7/2+PARAM!$E$62</f>
+        <f>PARAM!$G$7/2+PARAM!$E$22</f>
         <v>700</v>
       </c>
       <c r="I94" s="22" t="s">
@@ -6987,7 +6987,7 @@
         <v>0</v>
       </c>
       <c r="H98" s="22">
-        <f>(PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$15,2*PARAM!$G$18))</f>
+        <f>(PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$28,2*PARAM!$G$31))</f>
         <v>710</v>
       </c>
       <c r="I98" s="22">
@@ -7024,7 +7024,7 @@
         <v>0</v>
       </c>
       <c r="H99" s="22">
-        <f>-((PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$15,2*PARAM!$G$18))+MAX(1,PARAM!$I$7))</f>
+        <f>-((PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$28,2*PARAM!$G$31))+MAX(1,PARAM!$I$7))</f>
         <v>-1410</v>
       </c>
       <c r="I99" s="22">
@@ -7055,15 +7055,15 @@
         <v>195</v>
       </c>
       <c r="F100" s="22">
-        <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$15/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
+        <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$28/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
         <v>156</v>
       </c>
       <c r="G100" s="22">
-        <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$15/2),0))*SIN(RADIANS(PARAM!$J$6)),6)</f>
+        <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$28/2),0))*SIN(RADIANS(PARAM!$J$6)),6)</f>
         <v>0</v>
       </c>
       <c r="H100" s="22">
-        <f>(PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$15/2,PARAM!$G$18))+IF(PARAM!$C$6="H",0,-PARAM!$G$18/2)</f>
+        <f>(PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$28/2,PARAM!$G$31))+IF(PARAM!$C$6="H",0,-PARAM!$G$31/2)</f>
         <v>705</v>
       </c>
       <c r="I100" s="22">
@@ -7091,15 +7091,15 @@
         <v>195</v>
       </c>
       <c r="F101" s="22">
-        <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$15/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
+        <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$28/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
         <v>156</v>
       </c>
       <c r="G101" s="22">
-        <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$15/2),0))*SIN(RADIANS(PARAM!$J$6)),6)</f>
+        <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$28/2),0))*SIN(RADIANS(PARAM!$J$6)),6)</f>
         <v>0</v>
       </c>
       <c r="H101" s="22">
-        <f>-(PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$15/2,PARAM!$G$18))+IF(PARAM!$C$6="H",0,PARAM!$G$18/2)</f>
+        <f>-(PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$28/2,PARAM!$G$31))+IF(PARAM!$C$6="H",0,PARAM!$G$31/2)</f>
         <v>-705</v>
       </c>
       <c r="I101" s="22">
@@ -7138,7 +7138,7 @@
         <v>SS275</v>
       </c>
       <c r="E104" s="22">
-        <f>MAX(1,PARAM!$J$35)</f>
+        <f>MAX(1,PARAM!$J$59)</f>
         <v>900</v>
       </c>
       <c r="F104" s="22" t="s">
@@ -7148,31 +7148,31 @@
         <v>139</v>
       </c>
       <c r="H104" s="22">
-        <f>PARAM!$E$35</f>
+        <f>PARAM!$E$59</f>
         <v>300</v>
       </c>
       <c r="I104" s="22">
-        <f>PARAM!$F$35</f>
+        <f>PARAM!$F$59</f>
         <v>150</v>
       </c>
       <c r="J104" s="22">
-        <f>PARAM!$F$35</f>
+        <f>PARAM!$F$59</f>
         <v>150</v>
       </c>
       <c r="K104" s="22">
-        <f>PARAM!$G$35</f>
+        <f>PARAM!$G$59</f>
         <v>6.5</v>
       </c>
       <c r="L104" s="22">
-        <f>PARAM!$H$35</f>
+        <f>PARAM!$H$59</f>
         <v>9</v>
       </c>
       <c r="M104" s="22">
-        <f>PARAM!$H$35</f>
+        <f>PARAM!$H$59</f>
         <v>9</v>
       </c>
       <c r="N104" s="22">
-        <f>PARAM!$I$35</f>
+        <f>PARAM!$I$59</f>
         <v>13</v>
       </c>
     </row>
@@ -7188,7 +7188,7 @@
         <v>SS275</v>
       </c>
       <c r="E105" s="22">
-        <f>MAX(1,PARAM!$J$36)</f>
+        <f>MAX(1,PARAM!$J$60)</f>
         <v>900</v>
       </c>
       <c r="F105" s="22" t="s">
@@ -7198,31 +7198,31 @@
         <v>139</v>
       </c>
       <c r="H105" s="22">
-        <f>PARAM!$E$36</f>
+        <f>PARAM!$E$60</f>
         <v>300</v>
       </c>
       <c r="I105" s="22">
-        <f>PARAM!$F$36</f>
+        <f>PARAM!$F$60</f>
         <v>150</v>
       </c>
       <c r="J105" s="22">
-        <f>PARAM!$F$36</f>
+        <f>PARAM!$F$60</f>
         <v>150</v>
       </c>
       <c r="K105" s="22">
-        <f>PARAM!$G$36</f>
+        <f>PARAM!$G$60</f>
         <v>6.5</v>
       </c>
       <c r="L105" s="22">
-        <f>PARAM!$H$36</f>
+        <f>PARAM!$H$60</f>
         <v>9</v>
       </c>
       <c r="M105" s="22">
-        <f>PARAM!$H$36</f>
+        <f>PARAM!$H$60</f>
         <v>9</v>
       </c>
       <c r="N105" s="22">
-        <f>PARAM!$I$36</f>
+        <f>PARAM!$I$60</f>
         <v>13</v>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
         <v>SS275</v>
       </c>
       <c r="E106" s="22">
-        <f>MAX(1,PARAM!$J$37)</f>
+        <f>MAX(1,PARAM!$J$61)</f>
         <v>900</v>
       </c>
       <c r="F106" s="22" t="s">
@@ -7248,31 +7248,31 @@
         <v>139</v>
       </c>
       <c r="H106" s="22">
-        <f>PARAM!$E$37</f>
+        <f>PARAM!$E$61</f>
         <v>300</v>
       </c>
       <c r="I106" s="22">
-        <f>PARAM!$F$37</f>
+        <f>PARAM!$F$61</f>
         <v>150</v>
       </c>
       <c r="J106" s="22">
-        <f>PARAM!$F$37</f>
+        <f>PARAM!$F$61</f>
         <v>150</v>
       </c>
       <c r="K106" s="22">
-        <f>PARAM!$G$37</f>
+        <f>PARAM!$G$61</f>
         <v>6.5</v>
       </c>
       <c r="L106" s="22">
-        <f>PARAM!$H$37</f>
+        <f>PARAM!$H$61</f>
         <v>9</v>
       </c>
       <c r="M106" s="22">
-        <f>PARAM!$H$37</f>
+        <f>PARAM!$H$61</f>
         <v>9</v>
       </c>
       <c r="N106" s="22">
-        <f>PARAM!$I$37</f>
+        <f>PARAM!$I$61</f>
         <v>13</v>
       </c>
     </row>
@@ -7288,7 +7288,7 @@
         <v>SS275</v>
       </c>
       <c r="E107" s="22">
-        <f>MAX(1,PARAM!$J$38)</f>
+        <f>MAX(1,PARAM!$J$62)</f>
         <v>1</v>
       </c>
       <c r="F107" s="22" t="s">
@@ -7298,31 +7298,31 @@
         <v>139</v>
       </c>
       <c r="H107" s="22">
-        <f>PARAM!$E$38</f>
+        <f>PARAM!$E$62</f>
         <v>300</v>
       </c>
       <c r="I107" s="22">
-        <f>PARAM!$F$38</f>
+        <f>PARAM!$F$62</f>
         <v>150</v>
       </c>
       <c r="J107" s="22">
-        <f>PARAM!$F$38</f>
+        <f>PARAM!$F$62</f>
         <v>150</v>
       </c>
       <c r="K107" s="22">
-        <f>PARAM!$G$38</f>
+        <f>PARAM!$G$62</f>
         <v>6.5</v>
       </c>
       <c r="L107" s="22">
-        <f>PARAM!$H$38</f>
+        <f>PARAM!$H$62</f>
         <v>9</v>
       </c>
       <c r="M107" s="22">
-        <f>PARAM!$H$38</f>
+        <f>PARAM!$H$62</f>
         <v>9</v>
       </c>
       <c r="N107" s="22">
-        <f>PARAM!$I$38</f>
+        <f>PARAM!$I$62</f>
         <v>13</v>
       </c>
     </row>
@@ -7351,7 +7351,7 @@
         <v>SS275</v>
       </c>
       <c r="E110" s="22">
-        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0))</f>
+        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0))</f>
         <v>20</v>
       </c>
       <c r="F110" s="22" t="s">
@@ -7361,11 +7361,11 @@
         <v>139</v>
       </c>
       <c r="H110" s="22">
-        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,5,FALSE),0))</f>
+        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,5,FALSE),0))</f>
         <v>230</v>
       </c>
       <c r="I110" s="22">
-        <f>MAX(1,(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,11,FALSE),0)-1)+2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,9,FALSE),0)))</f>
+        <f>MAX(1,(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,11,FALSE),0)-1)+2*IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,9,FALSE),0)))</f>
         <v>230</v>
       </c>
     </row>
@@ -7381,7 +7381,7 @@
         <v>SS275</v>
       </c>
       <c r="E111" s="22">
-        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0))</f>
+        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0))</f>
         <v>10</v>
       </c>
       <c r="F111" s="22" t="s">
@@ -7391,11 +7391,11 @@
         <v>139</v>
       </c>
       <c r="H111" s="22">
-        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,5,FALSE),0))</f>
+        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,5,FALSE),0))</f>
         <v>140</v>
       </c>
       <c r="I111" s="22">
-        <f>MAX(1,(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,11,FALSE),0)-1)+2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,9,FALSE),0)))</f>
+        <f>MAX(1,(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,11,FALSE),0)-1)+2*IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,9,FALSE),0)))</f>
         <v>230</v>
       </c>
     </row>
@@ -7411,7 +7411,7 @@
         <v>SS275</v>
       </c>
       <c r="E112" s="22">
-        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0))</f>
+        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0))</f>
         <v>10</v>
       </c>
       <c r="F112" s="22" t="s">
@@ -7421,11 +7421,11 @@
         <v>139</v>
       </c>
       <c r="H112" s="22">
-        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,5,FALSE),0))</f>
+        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,5,FALSE),0))</f>
         <v>140</v>
       </c>
       <c r="I112" s="22">
-        <f>MAX(1,(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,11,FALSE),0)-1)+2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,9,FALSE),0)))</f>
+        <f>MAX(1,(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,11,FALSE),0)-1)+2*IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,9,FALSE),0)))</f>
         <v>230</v>
       </c>
     </row>
@@ -7441,7 +7441,7 @@
         <v>SS275</v>
       </c>
       <c r="E113" s="22">
-        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0))</f>
+        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0))</f>
         <v>10</v>
       </c>
       <c r="F113" s="22" t="s">
@@ -7451,11 +7451,11 @@
         <v>139</v>
       </c>
       <c r="H113" s="22">
-        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,5,FALSE),0))</f>
+        <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,5,FALSE),0))</f>
         <v>140</v>
       </c>
       <c r="I113" s="22">
-        <f>MAX(1,(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,11,FALSE),0)-1)+2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,9,FALSE),0)))</f>
+        <f>MAX(1,(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,11,FALSE),0)-1)+2*IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,9,FALSE),0)))</f>
         <v>230</v>
       </c>
     </row>
@@ -7470,30 +7470,30 @@
         <v>211</v>
       </c>
       <c r="D114" s="22" t="str">
-        <f>PARAM!$G$24</f>
+        <f>PARAM!$G$37</f>
         <v>F10T</v>
       </c>
       <c r="E114" s="22">
-        <f>PARAM!$E$24</f>
+        <f>PARAM!$E$37</f>
         <v>16</v>
       </c>
       <c r="F114" s="22">
-        <f>MAX(1,CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$35)+1.1*PARAM!$E$24,5))</f>
+        <f>MAX(1,CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$59)+1.1*PARAM!$E$37,5))</f>
         <v>55</v>
       </c>
       <c r="G114" s="22">
-        <f>PARAM!$F$24</f>
+        <f>PARAM!$F$37</f>
         <v>18</v>
       </c>
       <c r="H114" s="22"/>
       <c r="I114" s="22"/>
       <c r="J114" s="22"/>
       <c r="K114" s="22">
-        <f>0.9*PARAM!$E$24</f>
+        <f>0.9*PARAM!$E$37</f>
         <v>14.4</v>
       </c>
       <c r="L114" s="22">
-        <f>MAX(0,(CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$35)+1.1*PARAM!$E$24,5))-(IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$35))-0.9*PARAM!$E$24)</f>
+        <f>MAX(0,(CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$59)+1.1*PARAM!$E$37,5))-(IF(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$59))-0.9*PARAM!$E$37)</f>
         <v>5.6</v>
       </c>
     </row>
@@ -7505,30 +7505,30 @@
         <v>212</v>
       </c>
       <c r="D115" s="22" t="str">
-        <f>PARAM!$G$24</f>
+        <f>PARAM!$G$37</f>
         <v>F10T</v>
       </c>
       <c r="E115" s="22">
-        <f>PARAM!$E$24</f>
+        <f>PARAM!$E$37</f>
         <v>16</v>
       </c>
       <c r="F115" s="22">
-        <f>MAX(1,CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$36)+1.1*PARAM!$E$24,5))</f>
+        <f>MAX(1,CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$60)+1.1*PARAM!$E$37,5))</f>
         <v>35</v>
       </c>
       <c r="G115" s="22">
-        <f>PARAM!$F$24</f>
+        <f>PARAM!$F$37</f>
         <v>18</v>
       </c>
       <c r="H115" s="22"/>
       <c r="I115" s="22"/>
       <c r="J115" s="22"/>
       <c r="K115" s="22">
-        <f>0.9*PARAM!$E$24</f>
+        <f>0.9*PARAM!$E$37</f>
         <v>14.4</v>
       </c>
       <c r="L115" s="22">
-        <f>MAX(0,(CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$36)+1.1*PARAM!$E$24,5))-(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$36))-0.9*PARAM!$E$24)</f>
+        <f>MAX(0,(CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$60)+1.1*PARAM!$E$37,5))-(IF(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$60))-0.9*PARAM!$E$37)</f>
         <v>4.1</v>
       </c>
     </row>
@@ -7540,30 +7540,30 @@
         <v>213</v>
       </c>
       <c r="D116" s="22" t="str">
-        <f>PARAM!$G$24</f>
+        <f>PARAM!$G$37</f>
         <v>F10T</v>
       </c>
       <c r="E116" s="22">
-        <f>PARAM!$E$24</f>
+        <f>PARAM!$E$37</f>
         <v>16</v>
       </c>
       <c r="F116" s="22">
-        <f>MAX(1,CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$37)+1.1*PARAM!$E$24,5))</f>
+        <f>MAX(1,CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$61)+1.1*PARAM!$E$37,5))</f>
         <v>35</v>
       </c>
       <c r="G116" s="22">
-        <f>PARAM!$F$24</f>
+        <f>PARAM!$F$37</f>
         <v>18</v>
       </c>
       <c r="H116" s="22"/>
       <c r="I116" s="22"/>
       <c r="J116" s="22"/>
       <c r="K116" s="22">
-        <f>0.9*PARAM!$E$24</f>
+        <f>0.9*PARAM!$E$37</f>
         <v>14.4</v>
       </c>
       <c r="L116" s="22">
-        <f>MAX(0,(CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$37)+1.1*PARAM!$E$24,5))-(IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$37))-0.9*PARAM!$E$24)</f>
+        <f>MAX(0,(CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$61)+1.1*PARAM!$E$37,5))-(IF(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$61))-0.9*PARAM!$E$37)</f>
         <v>4.1</v>
       </c>
     </row>
@@ -7575,30 +7575,30 @@
         <v>214</v>
       </c>
       <c r="D117" s="22" t="str">
-        <f>PARAM!$G$24</f>
+        <f>PARAM!$G$37</f>
         <v>F10T</v>
       </c>
       <c r="E117" s="22">
-        <f>PARAM!$E$24</f>
+        <f>PARAM!$E$37</f>
         <v>16</v>
       </c>
       <c r="F117" s="22">
-        <f>MAX(1,CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$38)+1.1*PARAM!$E$24,5))</f>
+        <f>MAX(1,CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$62)+1.1*PARAM!$E$37,5))</f>
         <v>35</v>
       </c>
       <c r="G117" s="22">
-        <f>PARAM!$F$24</f>
+        <f>PARAM!$F$37</f>
         <v>18</v>
       </c>
       <c r="H117" s="22"/>
       <c r="I117" s="22"/>
       <c r="J117" s="22"/>
       <c r="K117" s="22">
-        <f>0.9*PARAM!$E$24</f>
+        <f>0.9*PARAM!$E$37</f>
         <v>14.4</v>
       </c>
       <c r="L117" s="22">
-        <f>MAX(0,(CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$38)+1.1*PARAM!$E$24,5))-(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)+PARAM!$G$38))-0.9*PARAM!$E$24)</f>
+        <f>MAX(0,(CEILING(IF(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$62)+1.1*PARAM!$E$37,5))-(IF(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$62))-0.9*PARAM!$E$37)</f>
         <v>4.1</v>
       </c>
     </row>
@@ -7633,14 +7633,14 @@
         <v>218</v>
       </c>
       <c r="D122" s="22" t="str">
-        <f>IF(AND(PARAM!$J$35&gt;0,IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),"pl.cna","")</f>
+        <f>IF(AND(PARAM!$J$59&gt;0,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cna","")</f>
         <v>pl.cna</v>
       </c>
       <c r="E122" s="22" t="s">
         <v>139</v>
       </c>
       <c r="F122" s="22">
-        <f>-IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)/2</f>
+        <f>-IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)/2</f>
         <v>-10</v>
       </c>
       <c r="G122" s="22">
@@ -7674,14 +7674,14 @@
         <v>218</v>
       </c>
       <c r="D123" s="22" t="str">
-        <f>IF(AND(PARAM!$J$35&gt;0,IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cna","")</f>
+        <f>IF(AND(PARAM!$J$59&gt;0,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cna","")</f>
         <v/>
       </c>
       <c r="E123" s="22" t="s">
         <v>139</v>
       </c>
       <c r="F123" s="22">
-        <f>-1.5*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)</f>
+        <f>-1.5*IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)</f>
         <v>-30</v>
       </c>
       <c r="G123" s="22">
@@ -7715,18 +7715,18 @@
         <v>218</v>
       </c>
       <c r="D124" s="22" t="str">
-        <f>IF(AND(PARAM!$J$35&gt;0,IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"),"pl.cna","")</f>
+        <f>IF(AND(PARAM!$J$59&gt;0,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cna","")</f>
         <v/>
       </c>
       <c r="E124" s="22" t="s">
         <v>139</v>
       </c>
       <c r="F124" s="22">
-        <f>IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,4,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,4,FALSE),0)</f>
         <v>115</v>
       </c>
       <c r="G124" s="22">
-        <f>PARAM!$G$35/2+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)/2</f>
+        <f>PARAM!$G$59/2+IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)/2</f>
         <v>13.25</v>
       </c>
       <c r="H124" s="22">
@@ -7756,7 +7756,7 @@
         <v>218</v>
       </c>
       <c r="D125" s="22" t="str">
-        <f>IF(PARAM!$J$35&gt;0,"sc.bma","")</f>
+        <f>IF(PARAM!$J$59&gt;0,"sc.bma","")</f>
         <v>sc.bma</v>
       </c>
       <c r="E125" s="22"/>
@@ -7793,24 +7793,24 @@
         <v>218</v>
       </c>
       <c r="D126" s="22" t="str">
-        <f>IF(OR(PARAM!$J$35&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"))),"","bo.cna")</f>
+        <f>IF(OR(PARAM!$J$59&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cna")</f>
         <v>bo.cna</v>
       </c>
       <c r="E126" s="22"/>
       <c r="F126" s="22">
-        <f>IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6))+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)),-2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,8,FALSE),0)-IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,4,FALSE),0))</f>
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6))+IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)),-2*IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,8,FALSE),0)-IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,4,FALSE),0))</f>
         <v>-35</v>
       </c>
       <c r="G126" s="22">
-        <f>IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",-IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,8,FALSE),0)/2,PARAM!$G$35/2+IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0))</f>
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",-IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,8,FALSE),0)/2,PARAM!$G$59/2+IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0))</f>
         <v>-70</v>
       </c>
       <c r="H126" s="22">
-        <f>-IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,11,FALSE),0)-1)/2</f>
+        <f>-IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,11,FALSE),0)-1)/2</f>
         <v>-70</v>
       </c>
       <c r="I126" s="22" t="str">
-        <f>IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate","YZ","XZ")</f>
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate","YZ","XZ")</f>
         <v>YZ</v>
       </c>
       <c r="J126" s="22">
@@ -7827,14 +7827,14 @@
         <v>0</v>
       </c>
       <c r="N126" s="22">
-        <f>IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,8,FALSE),0),0)</f>
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,8,FALSE),0),0)</f>
         <v>140</v>
       </c>
       <c r="O126" s="22">
         <v>0</v>
       </c>
       <c r="P126" s="22">
-        <f>IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",1,0)</f>
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",1,0)</f>
         <v>1</v>
       </c>
       <c r="Q126" s="22">
@@ -7844,11 +7844,11 @@
         <v>0</v>
       </c>
       <c r="S126" s="22">
-        <f>IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,10,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,10,FALSE),0)</f>
         <v>70</v>
       </c>
       <c r="T126" s="22">
-        <f>IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,11,FALSE),0)-1</f>
+        <f>IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,11,FALSE),0)-1</f>
         <v>2</v>
       </c>
     </row>
@@ -7887,14 +7887,14 @@
         <v>224</v>
       </c>
       <c r="D130" s="22" t="str">
-        <f>IF(AND(PARAM!$J$36&gt;0,IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),"pl.cnb","")</f>
+        <f>IF(AND(PARAM!$J$60&gt;0,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cnb","")</f>
         <v/>
       </c>
       <c r="E130" s="22" t="s">
         <v>139</v>
       </c>
       <c r="F130" s="22">
-        <f>-(-IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)/2)</f>
+        <f>-(-IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)/2)</f>
         <v>5</v>
       </c>
       <c r="G130" s="22">
@@ -7925,14 +7925,14 @@
         <v>224</v>
       </c>
       <c r="D131" s="22" t="str">
-        <f>IF(AND(PARAM!$J$36&gt;0,IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnb","")</f>
+        <f>IF(AND(PARAM!$J$60&gt;0,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnb","")</f>
         <v/>
       </c>
       <c r="E131" s="22" t="s">
         <v>139</v>
       </c>
       <c r="F131" s="22">
-        <f>-(-1.5*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0))</f>
+        <f>-(-1.5*IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0))</f>
         <v>15</v>
       </c>
       <c r="G131" s="22">
@@ -7963,18 +7963,18 @@
         <v>224</v>
       </c>
       <c r="D132" s="22" t="str">
-        <f>IF(AND(PARAM!$J$36&gt;0,IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"),"pl.cnb","")</f>
+        <f>IF(AND(PARAM!$J$60&gt;0,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cnb","")</f>
         <v>pl.cnb</v>
       </c>
       <c r="E132" s="22" t="s">
         <v>139</v>
       </c>
       <c r="F132" s="22">
-        <f>-(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,4,FALSE),0))</f>
+        <f>-(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,4,FALSE),0))</f>
         <v>-60</v>
       </c>
       <c r="G132" s="22">
-        <f>-(PARAM!$G$36/2+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)/2)</f>
+        <f>-(PARAM!$G$60/2+IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)/2)</f>
         <v>-8.25</v>
       </c>
       <c r="H132" s="22">
@@ -8001,7 +8001,7 @@
         <v>224</v>
       </c>
       <c r="D133" s="22" t="str">
-        <f>IF(PARAM!$J$36&gt;0,"sc.bmb","")</f>
+        <f>IF(PARAM!$J$60&gt;0,"sc.bmb","")</f>
         <v>sc.bmb</v>
       </c>
       <c r="E133" s="22"/>
@@ -8035,24 +8035,24 @@
         <v>224</v>
       </c>
       <c r="D134" s="22" t="str">
-        <f>IF(OR(PARAM!$J$36&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"))),"","bo.cnb")</f>
+        <f>IF(OR(PARAM!$J$60&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cnb")</f>
         <v>bo.cnb</v>
       </c>
       <c r="E134" s="22"/>
       <c r="F134" s="22">
-        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6))+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)),-2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,8,FALSE),0)-IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,4,FALSE),0)))</f>
+        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6))+IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)),-2*IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,8,FALSE),0)-IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,4,FALSE),0)))</f>
         <v>-50</v>
       </c>
       <c r="G134" s="22">
-        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",-IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,8,FALSE),0)/2,PARAM!$G$36/2+IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)))</f>
+        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",-IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,8,FALSE),0)/2,PARAM!$G$60/2+IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)))</f>
         <v>-13.25</v>
       </c>
       <c r="H134" s="22">
-        <f>-IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,11,FALSE),0)-1)/2</f>
+        <f>-IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,11,FALSE),0)-1)/2</f>
         <v>-70</v>
       </c>
       <c r="I134" s="22" t="str">
-        <f>IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate","YZ","XZ")</f>
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate","YZ","XZ")</f>
         <v>XZ</v>
       </c>
       <c r="J134" s="22">
@@ -8069,14 +8069,14 @@
         <v>0</v>
       </c>
       <c r="N134" s="22">
-        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,8,FALSE),0),0))</f>
+        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,8,FALSE),0),0))</f>
         <v>0</v>
       </c>
       <c r="O134" s="22">
         <v>0</v>
       </c>
       <c r="P134" s="22">
-        <f>IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",1,0)</f>
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",1,0)</f>
         <v>0</v>
       </c>
       <c r="Q134" s="22">
@@ -8086,11 +8086,11 @@
         <v>0</v>
       </c>
       <c r="S134" s="22">
-        <f>IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,10,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,10,FALSE),0)</f>
         <v>70</v>
       </c>
       <c r="T134" s="22">
-        <f>IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,11,FALSE),0)-1</f>
+        <f>IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,11,FALSE),0)-1</f>
         <v>2</v>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
         <v>226</v>
       </c>
       <c r="D138" s="22" t="str">
-        <f>IF(AND(PARAM!$J$37&gt;0,IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),"pl.cnc","")</f>
+        <f>IF(AND(PARAM!$J$61&gt;0,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cnc","")</f>
         <v/>
       </c>
       <c r="E138" s="22" t="s">
@@ -8140,7 +8140,7 @@
         <v>0</v>
       </c>
       <c r="G138" s="22">
-        <f>-IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)/2</f>
+        <f>-IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0)/2</f>
         <v>-5</v>
       </c>
       <c r="H138" s="22">
@@ -8167,7 +8167,7 @@
         <v>226</v>
       </c>
       <c r="D139" s="22" t="str">
-        <f>IF(AND(PARAM!$J$37&gt;0,IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnc","")</f>
+        <f>IF(AND(PARAM!$J$61&gt;0,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnc","")</f>
         <v/>
       </c>
       <c r="E139" s="22" t="s">
@@ -8178,7 +8178,7 @@
         <v>0</v>
       </c>
       <c r="G139" s="22">
-        <f>-1.5*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)</f>
+        <f>-1.5*IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0)</f>
         <v>-15</v>
       </c>
       <c r="H139" s="22">
@@ -8205,18 +8205,18 @@
         <v>226</v>
       </c>
       <c r="D140" s="22" t="str">
-        <f>IF(AND(PARAM!$J$37&gt;0,IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"),"pl.cnc","")</f>
+        <f>IF(AND(PARAM!$J$61&gt;0,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cnc","")</f>
         <v>pl.cnc</v>
       </c>
       <c r="E140" s="22" t="s">
         <v>139</v>
       </c>
       <c r="F140" s="22">
-        <f>PARAM!$G$37/2+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)/2</f>
+        <f>PARAM!$G$61/2+IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0)/2</f>
         <v>8.25</v>
       </c>
       <c r="G140" s="22">
-        <f>IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,4,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,4,FALSE),0)</f>
         <v>60</v>
       </c>
       <c r="H140" s="22">
@@ -8243,7 +8243,7 @@
         <v>226</v>
       </c>
       <c r="D141" s="22" t="str">
-        <f>IF(PARAM!$J$37&gt;0,"sc.bmc","")</f>
+        <f>IF(PARAM!$J$61&gt;0,"sc.bmc","")</f>
         <v>sc.bmc</v>
       </c>
       <c r="E141" s="22"/>
@@ -8277,24 +8277,24 @@
         <v>226</v>
       </c>
       <c r="D142" s="22" t="str">
-        <f>IF(OR(PARAM!$J$37&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"))),"","bo.cnc")</f>
+        <f>IF(OR(PARAM!$J$61&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cnc")</f>
         <v>bo.cnc</v>
       </c>
       <c r="E142" s="22"/>
       <c r="F142" s="22">
-        <f>IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",-IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,8,FALSE),0)/2,PARAM!$G$37/2+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0))</f>
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",-IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,8,FALSE),0)/2,PARAM!$G$61/2+IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0))</f>
         <v>13.25</v>
       </c>
       <c r="G142" s="22">
-        <f>IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6))+IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)),-2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,8,FALSE),0)-IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,4,FALSE),0))</f>
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6))+IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0)),-2*IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,8,FALSE),0)-IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,4,FALSE),0))</f>
         <v>50</v>
       </c>
       <c r="H142" s="22">
-        <f>-IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,11,FALSE),0)-1)/2</f>
+        <f>-IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,11,FALSE),0)-1)/2</f>
         <v>-70</v>
       </c>
       <c r="I142" s="22" t="str">
-        <f>IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate","XZ","YZ")</f>
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate","XZ","YZ")</f>
         <v>YZ</v>
       </c>
       <c r="J142" s="22">
@@ -8307,7 +8307,7 @@
         <v>180</v>
       </c>
       <c r="M142" s="22">
-        <f>IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,8,FALSE),0),0)</f>
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,8,FALSE),0),0)</f>
         <v>0</v>
       </c>
       <c r="N142" s="22">
@@ -8318,7 +8318,7 @@
         <v>0</v>
       </c>
       <c r="P142" s="22">
-        <f>IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",1,0)</f>
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",1,0)</f>
         <v>0</v>
       </c>
       <c r="Q142" s="22">
@@ -8328,11 +8328,11 @@
         <v>0</v>
       </c>
       <c r="S142" s="22">
-        <f>IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,10,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,10,FALSE),0)</f>
         <v>70</v>
       </c>
       <c r="T142" s="22">
-        <f>IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,11,FALSE),0)-1</f>
+        <f>IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,11,FALSE),0)-1</f>
         <v>2</v>
       </c>
     </row>
@@ -8371,7 +8371,7 @@
         <v>228</v>
       </c>
       <c r="D146" s="22" t="str">
-        <f>IF(AND(PARAM!$J$38&gt;0,IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),"pl.cnd","")</f>
+        <f>IF(AND(PARAM!$J$62&gt;0,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cnd","")</f>
         <v/>
       </c>
       <c r="E146" s="22" t="s">
@@ -8382,7 +8382,7 @@
         <v>0</v>
       </c>
       <c r="G146" s="22">
-        <f>-(-IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)/2)</f>
+        <f>-(-IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0)/2)</f>
         <v>5</v>
       </c>
       <c r="H146" s="22">
@@ -8409,7 +8409,7 @@
         <v>228</v>
       </c>
       <c r="D147" s="22" t="str">
-        <f>IF(AND(PARAM!$J$38&gt;0,IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnd","")</f>
+        <f>IF(AND(PARAM!$J$62&gt;0,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnd","")</f>
         <v/>
       </c>
       <c r="E147" s="22" t="s">
@@ -8420,7 +8420,7 @@
         <v>0</v>
       </c>
       <c r="G147" s="22">
-        <f>-(-1.5*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0))</f>
+        <f>-(-1.5*IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0))</f>
         <v>15</v>
       </c>
       <c r="H147" s="22">
@@ -8447,18 +8447,18 @@
         <v>228</v>
       </c>
       <c r="D148" s="22" t="str">
-        <f>IF(AND(PARAM!$J$38&gt;0,IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"),"pl.cnd","")</f>
+        <f>IF(AND(PARAM!$J$62&gt;0,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cnd","")</f>
         <v/>
       </c>
       <c r="E148" s="22" t="s">
         <v>139</v>
       </c>
       <c r="F148" s="22">
-        <f>-(PARAM!$G$38/2+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)/2)</f>
+        <f>-(PARAM!$G$62/2+IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0)/2)</f>
         <v>-8.25</v>
       </c>
       <c r="G148" s="22">
-        <f>-(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,4,FALSE),0))</f>
+        <f>-(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,4,FALSE),0))</f>
         <v>-60</v>
       </c>
       <c r="H148" s="22">
@@ -8485,7 +8485,7 @@
         <v>228</v>
       </c>
       <c r="D149" s="22" t="str">
-        <f>IF(PARAM!$J$38&gt;0,"sc.bmd","")</f>
+        <f>IF(PARAM!$J$62&gt;0,"sc.bmd","")</f>
         <v/>
       </c>
       <c r="E149" s="22"/>
@@ -8519,24 +8519,24 @@
         <v>228</v>
       </c>
       <c r="D150" s="22" t="str">
-        <f>IF(OR(PARAM!$J$38&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="fin plate"))),"","bo.cnd")</f>
+        <f>IF(OR(PARAM!$J$62&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cnd")</f>
         <v/>
       </c>
       <c r="E150" s="22"/>
       <c r="F150" s="22">
-        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",-IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,8,FALSE),0)/2,PARAM!$G$38/2+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)))</f>
+        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",-IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,8,FALSE),0)/2,PARAM!$G$62/2+IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0)))</f>
         <v>-13.25</v>
       </c>
       <c r="G150" s="22">
-        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6))+IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)),-2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,8,FALSE),0)-IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,4,FALSE),0)))</f>
+        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6))+IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0)),-2*IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,8,FALSE),0)-IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,4,FALSE),0)))</f>
         <v>-50</v>
       </c>
       <c r="H150" s="22">
-        <f>-IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,11,FALSE),0)-1)/2</f>
+        <f>-IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,10,FALSE),0)*(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,11,FALSE),0)-1)/2</f>
         <v>-70</v>
       </c>
       <c r="I150" s="22" t="str">
-        <f>IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate","XZ","YZ")</f>
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate","XZ","YZ")</f>
         <v>YZ</v>
       </c>
       <c r="J150" s="22">
@@ -8549,7 +8549,7 @@
         <v>0</v>
       </c>
       <c r="M150" s="22">
-        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,8,FALSE),0),0))</f>
+        <f>-(IF(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,8,FALSE),0),0))</f>
         <v>0</v>
       </c>
       <c r="N150" s="22">
@@ -8560,7 +8560,7 @@
         <v>0</v>
       </c>
       <c r="P150" s="22">
-        <f>IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",1,0)</f>
+        <f>IF(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",1,0)</f>
         <v>0</v>
       </c>
       <c r="Q150" s="22">
@@ -8570,11 +8570,11 @@
         <v>0</v>
       </c>
       <c r="S150" s="22">
-        <f>IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,10,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,10,FALSE),0)</f>
         <v>70</v>
       </c>
       <c r="T150" s="22">
-        <f>IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,11,FALSE),0)-1</f>
+        <f>IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,11,FALSE),0)-1</f>
         <v>2</v>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
         <v>195</v>
       </c>
       <c r="F154" s="22">
-        <f>(IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$35,PARAM!$B$44:$K$49,4,FALSE),0))</f>
+        <f>(IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,4,FALSE),0))</f>
         <v>170</v>
       </c>
       <c r="G154" s="22">
@@ -8646,7 +8646,7 @@
         <v>195</v>
       </c>
       <c r="F155" s="22">
-        <f>-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$36,PARAM!$B$44:$K$49,4,FALSE),0)))</f>
+        <f>-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,4,FALSE),0)))</f>
         <v>-160</v>
       </c>
       <c r="G155" s="22">
@@ -8673,7 +8673,7 @@
         <v>0</v>
       </c>
       <c r="G156" s="22">
-        <f>(IF(MOD(PARAM!$J$6,180)=0,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2),PARAM!$E$6/2))+IF(IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$37,PARAM!$B$44:$K$49,4,FALSE),0))</f>
+        <f>(IF(MOD(PARAM!$J$6,180)=0,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2),PARAM!$E$6/2))+IF(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,4,FALSE),0))</f>
         <v>15</v>
       </c>
       <c r="H156" s="22">
@@ -8697,7 +8697,7 @@
         <v>0</v>
       </c>
       <c r="G157" s="22">
-        <f>-((IF(MOD(PARAM!$J$6,180)=0,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2),PARAM!$E$6/2))+IF(IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$38,PARAM!$B$44:$K$49,4,FALSE),0)))</f>
+        <f>-((IF(MOD(PARAM!$J$6,180)=0,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2),PARAM!$E$6/2))+IF(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,4,FALSE),0)))</f>
         <v>-15</v>
       </c>
       <c r="H157" s="22">
@@ -8739,7 +8739,7 @@
         <v>7</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="E1" s="24" t="s">
         <v>9</v>
@@ -9132,7 +9132,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="B19" s="28">
         <v>300</v>
@@ -10121,7 +10121,7 @@
         <v>7</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="E1" s="24" t="s">
         <v>9</v>

--- a/plate3d/PLATE3D_COLUMN.xlsx
+++ b/plate3d/PLATE3D_COLUMN.xlsx
@@ -131,13 +131,13 @@
     <t>1</t>
   </si>
   <si>
-    <t>beam top flange</t>
+    <t>upper stiffener</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>beam bottom flange</t>
+    <t>lower stiffener</t>
   </si>
   <si>
     <t>3</t>

--- a/plate3d/PLATE3D_COLUMN.xlsx
+++ b/plate3d/PLATE3D_COLUMN.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="440">
   <si>
     <t>COLUMN</t>
   </si>
@@ -420,9 +420,6 @@
   </si>
   <si>
     <t>ZUP</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>SECT  id  material  length  TYPE  base.pt  v1..v7        an H takes seven values, a tube four — the last three go blank by formula</t>
@@ -3463,19 +3460,14 @@
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>134</v>
-      </c>
-    </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -3483,10 +3475,10 @@
         <v>17</v>
       </c>
       <c r="B6" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="22" t="s">
         <v>137</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>138</v>
       </c>
       <c r="D6" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3501,7 +3493,7 @@
         <v>H</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H6" s="22">
         <f>PARAM!$E$6</f>
@@ -3537,10 +3529,10 @@
         <v>18</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D7" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3555,7 +3547,7 @@
         <v>H</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H7" s="22">
         <f>PARAM!$E$6</f>
@@ -3591,10 +3583,10 @@
         <v>19</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D8" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3609,7 +3601,7 @@
         <v>H</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H8" s="22">
         <f>PARAM!$E$6</f>
@@ -3640,25 +3632,20 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>134</v>
-      </c>
-    </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B11" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="C11" s="22" t="s">
         <v>144</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>145</v>
       </c>
       <c r="D11" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3669,10 +3656,10 @@
         <v>12</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H11" s="22">
         <f>IF(PARAM!$C$6="H",PARAM!$E$28,PARAM!$E$31)</f>
@@ -3685,13 +3672,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="C12" s="22" t="s">
         <v>147</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="C12" s="22" t="s">
-        <v>148</v>
       </c>
       <c r="D12" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3702,10 +3689,10 @@
         <v>10</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H12" s="22">
         <f>PARAM!$E$29</f>
@@ -3718,13 +3705,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" s="22" t="s">
         <v>149</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>150</v>
       </c>
       <c r="D13" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3735,10 +3722,10 @@
         <v>10</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H13" s="22">
         <f>PARAM!$E$30</f>
@@ -3751,13 +3738,13 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="C14" s="22" t="s">
         <v>152</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>153</v>
       </c>
       <c r="D14" s="22" t="str">
         <f>PARAM!$G$37</f>
@@ -3789,13 +3776,13 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="C15" s="22" t="s">
         <v>154</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>155</v>
       </c>
       <c r="D15" s="22" t="str">
         <f>PARAM!$G$37</f>
@@ -3825,30 +3812,25 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>134</v>
-      </c>
-    </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="C19" s="22" t="s">
         <v>158</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>159</v>
       </c>
       <c r="D19" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3859,10 +3841,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H19" s="22">
         <f>MAX(1,PARAM!$G$15)</f>
@@ -3875,10 +3857,10 @@
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D20" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3889,10 +3871,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H20" s="22">
         <f>MAX(1,PARAM!$G$16)</f>
@@ -3905,10 +3887,10 @@
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D21" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3919,10 +3901,10 @@
         <v>1</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H21" s="22">
         <f>MAX(1,PARAM!$G$17)</f>
@@ -3935,10 +3917,10 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D22" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3949,10 +3931,10 @@
         <v>1</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H22" s="22">
         <f>MAX(1,PARAM!$G$18)</f>
@@ -3965,10 +3947,10 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D23" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3979,10 +3961,10 @@
         <v>1</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H23" s="22">
         <f>MAX(1,PARAM!$G$19)</f>
@@ -3995,10 +3977,10 @@
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D24" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -4009,10 +3991,10 @@
         <v>1</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H24" s="22">
         <f>MAX(1,PARAM!$G$20)</f>
@@ -4025,10 +4007,10 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D25" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -4039,10 +4021,10 @@
         <v>1</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G25" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H25" s="22">
         <f>MAX(1,PARAM!$G$21)</f>
@@ -4055,10 +4037,10 @@
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D26" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -4069,10 +4051,10 @@
         <v>1</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H26" s="22">
         <f>MAX(1,PARAM!$G$22)</f>
@@ -4083,30 +4065,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
-        <v>134</v>
-      </c>
-    </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B30" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="C30" s="22" t="s">
         <v>170</v>
-      </c>
-      <c r="C30" s="22" t="s">
-        <v>171</v>
       </c>
       <c r="D30" s="22" t="str">
         <f>IF(PARAM!$E$7&gt;0,"sc.c1","")</f>
@@ -4123,7 +4100,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J30" s="22">
         <v>0</v>
@@ -4137,27 +4114,27 @@
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C31" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="C31" s="22" t="s">
-        <v>171</v>
-      </c>
       <c r="D31" s="22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E31" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31" s="22" t="s">
         <v>138</v>
-      </c>
-      <c r="F31" s="22" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D32" s="22" t="str">
         <f>"sc.c2"</f>
@@ -4174,7 +4151,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J32" s="22">
         <v>0</v>
@@ -4188,27 +4165,27 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D34" s="22" t="str">
         <f>IF(PARAM!$I$7&gt;0,"sc.c3","")</f>
@@ -4225,7 +4202,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J34" s="22">
         <v>0</v>
@@ -4239,47 +4216,42 @@
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C38" s="22" t="s">
         <v>177</v>
-      </c>
-      <c r="B38" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="C38" s="22" t="s">
-        <v>178</v>
       </c>
       <c r="D38" s="22" t="str">
         <f>IF(PARAM!$E$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F38" s="22">
         <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$28/2)),0)</f>
@@ -4299,17 +4271,17 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D39" s="22" t="str">
         <f>IF(PARAM!$E$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F39" s="22">
         <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$28/2)),0)</f>
@@ -4329,20 +4301,20 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D40" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F40" s="22">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -4356,22 +4328,22 @@
         <v>0</v>
       </c>
       <c r="I40" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B41" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D41" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F41" s="22">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -4385,22 +4357,22 @@
         <v>0</v>
       </c>
       <c r="I41" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D42" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F42" s="22">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -4414,22 +4386,22 @@
         <v>0</v>
       </c>
       <c r="I42" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D43" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F43" s="22">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -4443,25 +4415,25 @@
         <v>0</v>
       </c>
       <c r="I43" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D44" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F44" s="22">
         <v>0</v>
@@ -4474,22 +4446,22 @@
         <v>0</v>
       </c>
       <c r="I44" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B45" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D45" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F45" s="22">
         <v>0</v>
@@ -4502,18 +4474,18 @@
         <v>0</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D46" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4533,7 +4505,7 @@
         <v>35</v>
       </c>
       <c r="I46" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J46" s="22">
         <v>0</v>
@@ -4575,10 +4547,10 @@
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B47" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D47" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4598,7 +4570,7 @@
         <v>35</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J47" s="22">
         <v>0</v>
@@ -4640,10 +4612,10 @@
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B48" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D48" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4663,7 +4635,7 @@
         <v>-35</v>
       </c>
       <c r="I48" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J48" s="22">
         <v>0</v>
@@ -4705,10 +4677,10 @@
     </row>
     <row r="49" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B49" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D49" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4728,7 +4700,7 @@
         <v>-35</v>
       </c>
       <c r="I49" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J49" s="22">
         <v>0</v>
@@ -4770,10 +4742,10 @@
     </row>
     <row r="50" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B50" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D50" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4793,7 +4765,7 @@
         <v>35</v>
       </c>
       <c r="I50" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J50" s="22">
         <v>0</v>
@@ -4835,10 +4807,10 @@
     </row>
     <row r="51" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B51" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D51" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4858,7 +4830,7 @@
         <v>35</v>
       </c>
       <c r="I51" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J51" s="22">
         <v>0</v>
@@ -4900,10 +4872,10 @@
     </row>
     <row r="52" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B52" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D52" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4923,7 +4895,7 @@
         <v>-35</v>
       </c>
       <c r="I52" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J52" s="22">
         <v>0</v>
@@ -4965,10 +4937,10 @@
     </row>
     <row r="53" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B53" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D53" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4988,7 +4960,7 @@
         <v>-35</v>
       </c>
       <c r="I53" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J53" s="22">
         <v>0</v>
@@ -5030,13 +5002,13 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D54" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -5056,7 +5028,7 @@
         <v>-10</v>
       </c>
       <c r="I54" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J54" s="22">
         <v>0</v>
@@ -5084,10 +5056,10 @@
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B55" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D55" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -5107,7 +5079,7 @@
         <v>-10</v>
       </c>
       <c r="I55" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J55" s="22">
         <v>0</v>
@@ -5135,13 +5107,13 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D56" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
@@ -5161,7 +5133,7 @@
         <v>-10</v>
       </c>
       <c r="I56" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J56" s="22">
         <v>0</v>
@@ -5189,10 +5161,10 @@
     </row>
     <row r="57" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B57" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D57" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
@@ -5212,7 +5184,7 @@
         <v>-10</v>
       </c>
       <c r="I57" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J57" s="22">
         <v>0</v>
@@ -5240,13 +5212,13 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D58" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -5266,7 +5238,7 @@
         <v>30</v>
       </c>
       <c r="I58" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J58" s="22">
         <v>0</v>
@@ -5308,10 +5280,10 @@
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B59" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D59" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -5331,7 +5303,7 @@
         <v>-30</v>
       </c>
       <c r="I59" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J59" s="22">
         <v>0</v>
@@ -5373,34 +5345,34 @@
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B60" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D60" s="22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E60" s="22" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F60" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B61" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D61" s="22" t="str">
         <f>IF(PARAM!$I$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E61" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F61" s="22">
         <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$28/2)),0)</f>
@@ -5420,17 +5392,17 @@
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B62" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D62" s="22" t="str">
         <f>IF(PARAM!$I$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F62" s="22">
         <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$28/2)),0)</f>
@@ -5450,17 +5422,17 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B63" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D63" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E63" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F63" s="22">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -5474,22 +5446,22 @@
         <v>0</v>
       </c>
       <c r="I63" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B64" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D64" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E64" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F64" s="22">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -5503,22 +5475,22 @@
         <v>0</v>
       </c>
       <c r="I64" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B65" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D65" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E65" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F65" s="22">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -5532,22 +5504,22 @@
         <v>0</v>
       </c>
       <c r="I65" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B66" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C66" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D66" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E66" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F66" s="22">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -5561,22 +5533,22 @@
         <v>0</v>
       </c>
       <c r="I66" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B67" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C67" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D67" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E67" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F67" s="22">
         <v>0</v>
@@ -5589,22 +5561,22 @@
         <v>0</v>
       </c>
       <c r="I67" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B68" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D68" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F68" s="22">
         <v>0</v>
@@ -5617,15 +5589,15 @@
         <v>0</v>
       </c>
       <c r="I68" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B69" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D69" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5645,7 +5617,7 @@
         <v>35</v>
       </c>
       <c r="I69" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J69" s="22">
         <v>0</v>
@@ -5687,10 +5659,10 @@
     </row>
     <row r="70" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B70" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D70" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5710,7 +5682,7 @@
         <v>35</v>
       </c>
       <c r="I70" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J70" s="22">
         <v>0</v>
@@ -5752,10 +5724,10 @@
     </row>
     <row r="71" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B71" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D71" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5775,7 +5747,7 @@
         <v>-35</v>
       </c>
       <c r="I71" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J71" s="22">
         <v>0</v>
@@ -5817,10 +5789,10 @@
     </row>
     <row r="72" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B72" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D72" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5840,7 +5812,7 @@
         <v>-35</v>
       </c>
       <c r="I72" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J72" s="22">
         <v>0</v>
@@ -5882,10 +5854,10 @@
     </row>
     <row r="73" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B73" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D73" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5905,7 +5877,7 @@
         <v>35</v>
       </c>
       <c r="I73" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J73" s="22">
         <v>0</v>
@@ -5947,10 +5919,10 @@
     </row>
     <row r="74" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B74" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C74" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D74" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5970,7 +5942,7 @@
         <v>35</v>
       </c>
       <c r="I74" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J74" s="22">
         <v>0</v>
@@ -6012,10 +5984,10 @@
     </row>
     <row r="75" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B75" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C75" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D75" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -6035,7 +6007,7 @@
         <v>-35</v>
       </c>
       <c r="I75" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J75" s="22">
         <v>0</v>
@@ -6077,10 +6049,10 @@
     </row>
     <row r="76" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B76" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C76" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D76" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -6100,7 +6072,7 @@
         <v>-35</v>
       </c>
       <c r="I76" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J76" s="22">
         <v>0</v>
@@ -6142,10 +6114,10 @@
     </row>
     <row r="77" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B77" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D77" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -6165,7 +6137,7 @@
         <v>-10</v>
       </c>
       <c r="I77" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J77" s="22">
         <v>0</v>
@@ -6193,10 +6165,10 @@
     </row>
     <row r="78" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B78" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C78" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D78" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -6216,7 +6188,7 @@
         <v>-10</v>
       </c>
       <c r="I78" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J78" s="22">
         <v>0</v>
@@ -6244,10 +6216,10 @@
     </row>
     <row r="79" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B79" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C79" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D79" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
@@ -6267,7 +6239,7 @@
         <v>-10</v>
       </c>
       <c r="I79" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J79" s="22">
         <v>0</v>
@@ -6295,10 +6267,10 @@
     </row>
     <row r="80" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B80" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C80" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D80" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
@@ -6318,7 +6290,7 @@
         <v>-10</v>
       </c>
       <c r="I80" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J80" s="22">
         <v>0</v>
@@ -6346,10 +6318,10 @@
     </row>
     <row r="81" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B81" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C81" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D81" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -6369,7 +6341,7 @@
         <v>30</v>
       </c>
       <c r="I81" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J81" s="22">
         <v>0</v>
@@ -6411,10 +6383,10 @@
     </row>
     <row r="82" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B82" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C82" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D82" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -6434,7 +6406,7 @@
         <v>-30</v>
       </c>
       <c r="I82" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J82" s="22">
         <v>0</v>
@@ -6476,52 +6448,47 @@
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B83" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C83" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D83" s="22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E83" s="22" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F83" s="22" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="12" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B87" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C87" s="22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D87" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$15&gt;0),"pl.stf1","")</f>
         <v>pl.stf1</v>
       </c>
       <c r="E87" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F87" s="22">
         <v>0</v>
@@ -6535,7 +6502,7 @@
         <v>845.5</v>
       </c>
       <c r="I87" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J87" s="22">
         <v>0</v>
@@ -6562,17 +6529,17 @@
     </row>
     <row r="88" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B88" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C88" s="22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D88" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$16&gt;0),"pl.stf2","")</f>
         <v>pl.stf2</v>
       </c>
       <c r="E88" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F88" s="22">
         <v>0</v>
@@ -6586,7 +6553,7 @@
         <v>554.5</v>
       </c>
       <c r="I88" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J88" s="22">
         <v>0</v>
@@ -6613,17 +6580,17 @@
     </row>
     <row r="89" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B89" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C89" s="22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D89" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$17&gt;0),"pl.stf3","")</f>
         <v/>
       </c>
       <c r="E89" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F89" s="22">
         <v>0</v>
@@ -6637,7 +6604,7 @@
         <v>700</v>
       </c>
       <c r="I89" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J89" s="22">
         <v>0</v>
@@ -6664,17 +6631,17 @@
     </row>
     <row r="90" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B90" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C90" s="22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D90" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$18&gt;0),"pl.stf4","")</f>
         <v/>
       </c>
       <c r="E90" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F90" s="22">
         <v>0</v>
@@ -6688,7 +6655,7 @@
         <v>700</v>
       </c>
       <c r="I90" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J90" s="22">
         <v>0</v>
@@ -6715,17 +6682,17 @@
     </row>
     <row r="91" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B91" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C91" s="22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D91" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$19&gt;0),"pl.stf5","")</f>
         <v/>
       </c>
       <c r="E91" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F91" s="22">
         <v>0</v>
@@ -6739,7 +6706,7 @@
         <v>700</v>
       </c>
       <c r="I91" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J91" s="22">
         <v>0</v>
@@ -6766,17 +6733,17 @@
     </row>
     <row r="92" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B92" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C92" s="22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D92" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$20&gt;0),"pl.stf6","")</f>
         <v/>
       </c>
       <c r="E92" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F92" s="22">
         <v>0</v>
@@ -6790,7 +6757,7 @@
         <v>700</v>
       </c>
       <c r="I92" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J92" s="22">
         <v>0</v>
@@ -6817,17 +6784,17 @@
     </row>
     <row r="93" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B93" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C93" s="22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D93" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$21&gt;0),"pl.stf7","")</f>
         <v/>
       </c>
       <c r="E93" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F93" s="22">
         <v>0</v>
@@ -6841,7 +6808,7 @@
         <v>700</v>
       </c>
       <c r="I93" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J93" s="22">
         <v>0</v>
@@ -6868,17 +6835,17 @@
     </row>
     <row r="94" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B94" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C94" s="22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D94" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$22&gt;0),"pl.stf8","")</f>
         <v/>
       </c>
       <c r="E94" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F94" s="22">
         <v>0</v>
@@ -6892,7 +6859,7 @@
         <v>700</v>
       </c>
       <c r="I94" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J94" s="22">
         <v>0</v>
@@ -6917,14 +6884,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="12" t="s">
-        <v>134</v>
-      </c>
-    </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -6932,16 +6894,16 @@
         <v>18</v>
       </c>
       <c r="B97" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="C97" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="C97" s="22" t="s">
+      <c r="D97" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="E97" s="22" t="s">
         <v>194</v>
-      </c>
-      <c r="D97" s="22" t="s">
-        <v>174</v>
-      </c>
-      <c r="E97" s="22" t="s">
-        <v>195</v>
       </c>
       <c r="F97" s="22">
         <v>0</v>
@@ -6966,19 +6928,19 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B98" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="C98" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="C98" s="22" t="s">
+      <c r="D98" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="E98" s="22" t="s">
         <v>194</v>
-      </c>
-      <c r="D98" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="E98" s="22" t="s">
-        <v>195</v>
       </c>
       <c r="F98" s="22">
         <v>0</v>
@@ -7006,16 +6968,16 @@
         <v>19</v>
       </c>
       <c r="B99" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="C99" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="C99" s="22" t="s">
+      <c r="D99" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="E99" s="22" t="s">
         <v>194</v>
-      </c>
-      <c r="D99" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="E99" s="22" t="s">
-        <v>195</v>
       </c>
       <c r="F99" s="22">
         <v>0</v>
@@ -7040,19 +7002,19 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B100" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="C100" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="C100" s="22" t="s">
+      <c r="D100" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="E100" s="22" t="s">
         <v>194</v>
-      </c>
-      <c r="D100" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="E100" s="22" t="s">
-        <v>195</v>
       </c>
       <c r="F100" s="22">
         <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$28/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
@@ -7079,16 +7041,16 @@
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="C101" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="C101" s="22" t="s">
+      <c r="D101" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="E101" s="22" t="s">
         <v>194</v>
-      </c>
-      <c r="D101" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="E101" s="22" t="s">
-        <v>195</v>
       </c>
       <c r="F101" s="22">
         <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$28/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
@@ -7113,25 +7075,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="12" t="s">
-        <v>134</v>
-      </c>
-    </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="B104" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="C104" s="22" t="s">
         <v>199</v>
-      </c>
-      <c r="B104" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="C104" s="22" t="s">
-        <v>200</v>
       </c>
       <c r="D104" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7145,7 +7102,7 @@
         <v>14</v>
       </c>
       <c r="G104" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H104" s="22">
         <f>PARAM!$E$59</f>
@@ -7178,10 +7135,10 @@
     </row>
     <row r="105" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B105" s="21" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C105" s="22" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D105" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7195,7 +7152,7 @@
         <v>14</v>
       </c>
       <c r="G105" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H105" s="22">
         <f>PARAM!$E$60</f>
@@ -7228,10 +7185,10 @@
     </row>
     <row r="106" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B106" s="21" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C106" s="22" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D106" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7245,7 +7202,7 @@
         <v>14</v>
       </c>
       <c r="G106" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H106" s="22">
         <f>PARAM!$E$61</f>
@@ -7278,10 +7235,10 @@
     </row>
     <row r="107" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B107" s="21" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C107" s="22" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D107" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7295,7 +7252,7 @@
         <v>14</v>
       </c>
       <c r="G107" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H107" s="22">
         <f>PARAM!$E$62</f>
@@ -7326,25 +7283,20 @@
         <v>13</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" s="12" t="s">
-        <v>134</v>
-      </c>
-    </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B110" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="C110" s="22" t="s">
         <v>205</v>
-      </c>
-      <c r="B110" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="C110" s="22" t="s">
-        <v>206</v>
       </c>
       <c r="D110" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7355,10 +7307,10 @@
         <v>20</v>
       </c>
       <c r="F110" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G110" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H110" s="22">
         <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,5,FALSE),0))</f>
@@ -7371,10 +7323,10 @@
     </row>
     <row r="111" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B111" s="21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C111" s="22" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D111" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7385,10 +7337,10 @@
         <v>10</v>
       </c>
       <c r="F111" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G111" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H111" s="22">
         <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,5,FALSE),0))</f>
@@ -7401,10 +7353,10 @@
     </row>
     <row r="112" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B112" s="21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C112" s="22" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D112" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7415,10 +7367,10 @@
         <v>10</v>
       </c>
       <c r="F112" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G112" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H112" s="22">
         <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,5,FALSE),0))</f>
@@ -7431,10 +7383,10 @@
     </row>
     <row r="113" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B113" s="21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C113" s="22" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D113" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7445,10 +7397,10 @@
         <v>10</v>
       </c>
       <c r="F113" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G113" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H113" s="22">
         <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,5,FALSE),0))</f>
@@ -7461,13 +7413,13 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="B114" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="C114" s="22" t="s">
         <v>210</v>
-      </c>
-      <c r="B114" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="C114" s="22" t="s">
-        <v>211</v>
       </c>
       <c r="D114" s="22" t="str">
         <f>PARAM!$G$37</f>
@@ -7499,10 +7451,10 @@
     </row>
     <row r="115" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B115" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C115" s="22" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D115" s="22" t="str">
         <f>PARAM!$G$37</f>
@@ -7534,10 +7486,10 @@
     </row>
     <row r="116" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B116" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C116" s="22" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D116" s="22" t="str">
         <f>PARAM!$G$37</f>
@@ -7569,10 +7521,10 @@
     </row>
     <row r="117" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B117" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C117" s="22" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D117" s="22" t="str">
         <f>PARAM!$G$37</f>
@@ -7602,42 +7554,32 @@
         <v>4.1</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="12" t="s">
-        <v>134</v>
-      </c>
-    </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="12" t="s">
-        <v>134</v>
+        <v>214</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="B122" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C122" s="22" t="s">
         <v>217</v>
-      </c>
-      <c r="B122" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="C122" s="22" t="s">
-        <v>218</v>
       </c>
       <c r="D122" s="22" t="str">
         <f>IF(AND(PARAM!$J$59&gt;0,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cna","")</f>
         <v>pl.cna</v>
       </c>
       <c r="E122" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F122" s="22">
         <f>-IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)/2</f>
@@ -7651,7 +7593,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J122" s="22">
         <v>0</v>
@@ -7665,20 +7607,20 @@
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B123" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C123" s="22" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D123" s="22" t="str">
         <f>IF(AND(PARAM!$J$59&gt;0,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cna","")</f>
         <v/>
       </c>
       <c r="E123" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F123" s="22">
         <f>-1.5*IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)</f>
@@ -7692,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="I123" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J123" s="22">
         <v>0</v>
@@ -7706,20 +7648,20 @@
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B124" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C124" s="22" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D124" s="22" t="str">
         <f>IF(AND(PARAM!$J$59&gt;0,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cna","")</f>
         <v/>
       </c>
       <c r="E124" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F124" s="22">
         <f>IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,4,FALSE),0)</f>
@@ -7733,7 +7675,7 @@
         <v>0</v>
       </c>
       <c r="I124" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J124" s="22">
         <v>0</v>
@@ -7747,13 +7689,13 @@
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B125" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C125" s="22" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D125" s="22" t="str">
         <f>IF(PARAM!$J$59&gt;0,"sc.bma","")</f>
@@ -7770,7 +7712,7 @@
         <v>0</v>
       </c>
       <c r="I125" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J125" s="22">
         <v>0</v>
@@ -7784,13 +7726,13 @@
     </row>
     <row r="126" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B126" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C126" s="22" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D126" s="22" t="str">
         <f>IF(OR(PARAM!$J$59&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cna")</f>
@@ -7854,44 +7796,39 @@
     </row>
     <row r="127" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B127" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C127" s="22" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D127" s="22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E127" s="22" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F127" s="22" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" s="12" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="130" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B130" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C130" s="22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D130" s="22" t="str">
         <f>IF(AND(PARAM!$J$60&gt;0,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cnb","")</f>
         <v/>
       </c>
       <c r="E130" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F130" s="22">
         <f>-(-IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)/2)</f>
@@ -7905,7 +7842,7 @@
         <v>0</v>
       </c>
       <c r="I130" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J130" s="22">
         <v>0</v>
@@ -7919,17 +7856,17 @@
     </row>
     <row r="131" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B131" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C131" s="22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D131" s="22" t="str">
         <f>IF(AND(PARAM!$J$60&gt;0,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnb","")</f>
         <v/>
       </c>
       <c r="E131" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F131" s="22">
         <f>-(-1.5*IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0))</f>
@@ -7943,7 +7880,7 @@
         <v>0</v>
       </c>
       <c r="I131" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J131" s="22">
         <v>0</v>
@@ -7957,17 +7894,17 @@
     </row>
     <row r="132" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B132" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C132" s="22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D132" s="22" t="str">
         <f>IF(AND(PARAM!$J$60&gt;0,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cnb","")</f>
         <v>pl.cnb</v>
       </c>
       <c r="E132" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F132" s="22">
         <f>-(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,4,FALSE),0))</f>
@@ -7981,7 +7918,7 @@
         <v>0</v>
       </c>
       <c r="I132" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J132" s="22">
         <v>0</v>
@@ -7995,10 +7932,10 @@
     </row>
     <row r="133" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B133" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C133" s="22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D133" s="22" t="str">
         <f>IF(PARAM!$J$60&gt;0,"sc.bmb","")</f>
@@ -8015,7 +7952,7 @@
         <v>0</v>
       </c>
       <c r="I133" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J133" s="22">
         <v>0</v>
@@ -8029,10 +7966,10 @@
     </row>
     <row r="134" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B134" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C134" s="22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D134" s="22" t="str">
         <f>IF(OR(PARAM!$J$60&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cnb")</f>
@@ -8096,44 +8033,39 @@
     </row>
     <row r="135" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B135" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C135" s="22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D135" s="22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E135" s="22" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F135" s="22" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" s="12" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="138" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B138" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C138" s="22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D138" s="22" t="str">
         <f>IF(AND(PARAM!$J$61&gt;0,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cnc","")</f>
         <v/>
       </c>
       <c r="E138" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F138" s="22">
         <f>0</f>
@@ -8147,7 +8079,7 @@
         <v>0</v>
       </c>
       <c r="I138" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J138" s="22">
         <v>0</v>
@@ -8161,17 +8093,17 @@
     </row>
     <row r="139" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B139" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C139" s="22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D139" s="22" t="str">
         <f>IF(AND(PARAM!$J$61&gt;0,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnc","")</f>
         <v/>
       </c>
       <c r="E139" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F139" s="22">
         <f>0</f>
@@ -8185,7 +8117,7 @@
         <v>0</v>
       </c>
       <c r="I139" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J139" s="22">
         <v>0</v>
@@ -8199,17 +8131,17 @@
     </row>
     <row r="140" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B140" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C140" s="22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D140" s="22" t="str">
         <f>IF(AND(PARAM!$J$61&gt;0,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cnc","")</f>
         <v>pl.cnc</v>
       </c>
       <c r="E140" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F140" s="22">
         <f>PARAM!$G$61/2+IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0)/2</f>
@@ -8223,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="I140" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J140" s="22">
         <v>0</v>
@@ -8237,10 +8169,10 @@
     </row>
     <row r="141" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B141" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C141" s="22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D141" s="22" t="str">
         <f>IF(PARAM!$J$61&gt;0,"sc.bmc","")</f>
@@ -8257,7 +8189,7 @@
         <v>0</v>
       </c>
       <c r="I141" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J141" s="22">
         <v>0</v>
@@ -8271,10 +8203,10 @@
     </row>
     <row r="142" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B142" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C142" s="22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D142" s="22" t="str">
         <f>IF(OR(PARAM!$J$61&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cnc")</f>
@@ -8338,44 +8270,39 @@
     </row>
     <row r="143" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B143" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C143" s="22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D143" s="22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E143" s="22" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F143" s="22" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" s="12" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="146" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B146" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C146" s="22" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D146" s="22" t="str">
         <f>IF(AND(PARAM!$J$62&gt;0,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cnd","")</f>
         <v/>
       </c>
       <c r="E146" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F146" s="22">
         <f>0</f>
@@ -8389,7 +8316,7 @@
         <v>0</v>
       </c>
       <c r="I146" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J146" s="22">
         <v>0</v>
@@ -8403,17 +8330,17 @@
     </row>
     <row r="147" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B147" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C147" s="22" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D147" s="22" t="str">
         <f>IF(AND(PARAM!$J$62&gt;0,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnd","")</f>
         <v/>
       </c>
       <c r="E147" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F147" s="22">
         <f>0</f>
@@ -8427,7 +8354,7 @@
         <v>0</v>
       </c>
       <c r="I147" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J147" s="22">
         <v>0</v>
@@ -8441,17 +8368,17 @@
     </row>
     <row r="148" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B148" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C148" s="22" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D148" s="22" t="str">
         <f>IF(AND(PARAM!$J$62&gt;0,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cnd","")</f>
         <v/>
       </c>
       <c r="E148" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F148" s="22">
         <f>-(PARAM!$G$62/2+IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0)/2)</f>
@@ -8465,7 +8392,7 @@
         <v>0</v>
       </c>
       <c r="I148" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J148" s="22">
         <v>0</v>
@@ -8479,10 +8406,10 @@
     </row>
     <row r="149" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B149" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C149" s="22" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D149" s="22" t="str">
         <f>IF(PARAM!$J$62&gt;0,"sc.bmd","")</f>
@@ -8499,7 +8426,7 @@
         <v>0</v>
       </c>
       <c r="I149" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J149" s="22">
         <v>0</v>
@@ -8513,10 +8440,10 @@
     </row>
     <row r="150" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B150" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C150" s="22" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D150" s="22" t="str">
         <f>IF(OR(PARAM!$J$62&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cnd")</f>
@@ -8580,46 +8507,41 @@
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B151" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C151" s="22" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D151" s="22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E151" s="22" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F151" s="22" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" s="12" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B154" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="C154" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="C154" s="22" t="s">
+      <c r="D154" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="E154" s="22" t="s">
         <v>194</v>
-      </c>
-      <c r="D154" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="E154" s="22" t="s">
-        <v>195</v>
       </c>
       <c r="F154" s="22">
         <f>(IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,4,FALSE),0))</f>
@@ -8634,16 +8556,16 @@
     </row>
     <row r="155" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B155" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="C155" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="C155" s="22" t="s">
+      <c r="D155" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="E155" s="22" t="s">
         <v>194</v>
-      </c>
-      <c r="D155" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="E155" s="22" t="s">
-        <v>195</v>
       </c>
       <c r="F155" s="22">
         <f>-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,4,FALSE),0)))</f>
@@ -8658,16 +8580,16 @@
     </row>
     <row r="156" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B156" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="C156" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="C156" s="22" t="s">
+      <c r="D156" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="E156" s="22" t="s">
         <v>194</v>
-      </c>
-      <c r="D156" s="22" t="s">
-        <v>226</v>
-      </c>
-      <c r="E156" s="22" t="s">
-        <v>195</v>
       </c>
       <c r="F156" s="22">
         <v>0</v>
@@ -8682,16 +8604,16 @@
     </row>
     <row r="157" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B157" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="C157" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="C157" s="22" t="s">
+      <c r="D157" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="E157" s="22" t="s">
         <v>194</v>
-      </c>
-      <c r="D157" s="22" t="s">
-        <v>228</v>
-      </c>
-      <c r="E157" s="22" t="s">
-        <v>195</v>
       </c>
       <c r="F157" s="22">
         <v>0</v>
@@ -8704,14 +8626,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" s="12" t="s">
-        <v>134</v>
-      </c>
-    </row>
     <row r="159" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B159" s="21" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -8753,7 +8670,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -8764,7 +8681,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B3" s="28">
         <v>100</v>
@@ -8787,7 +8704,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B4" s="30">
         <v>125</v>
@@ -8810,7 +8727,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B5" s="28">
         <v>150</v>
@@ -8833,7 +8750,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B6" s="30">
         <v>148</v>
@@ -8856,7 +8773,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B7" s="28">
         <v>150</v>
@@ -8879,7 +8796,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B8" s="30">
         <v>198</v>
@@ -8902,7 +8819,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B9" s="28">
         <v>200</v>
@@ -8925,7 +8842,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B10" s="30">
         <v>194</v>
@@ -8948,7 +8865,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B11" s="28">
         <v>200</v>
@@ -8971,7 +8888,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B12" s="30">
         <v>200</v>
@@ -8994,7 +8911,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B13" s="28">
         <v>248</v>
@@ -9017,7 +8934,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B14" s="30">
         <v>250</v>
@@ -9040,7 +8957,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B15" s="28">
         <v>244</v>
@@ -9063,7 +8980,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B16" s="30">
         <v>250</v>
@@ -9086,7 +9003,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B17" s="28">
         <v>250</v>
@@ -9109,7 +9026,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B18" s="30">
         <v>298</v>
@@ -9155,7 +9072,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B20" s="30">
         <v>294</v>
@@ -9178,7 +9095,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B21" s="28">
         <v>294</v>
@@ -9224,7 +9141,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B23" s="28">
         <v>300</v>
@@ -9247,7 +9164,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B24" s="30">
         <v>346</v>
@@ -9270,7 +9187,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B25" s="28">
         <v>350</v>
@@ -9293,7 +9210,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B26" s="30">
         <v>340</v>
@@ -9316,7 +9233,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B27" s="28">
         <v>344</v>
@@ -9339,7 +9256,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B28" s="30">
         <v>350</v>
@@ -9362,7 +9279,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B29" s="28">
         <v>396</v>
@@ -9385,7 +9302,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B30" s="30">
         <v>400</v>
@@ -9408,7 +9325,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B31" s="28">
         <v>390</v>
@@ -9431,7 +9348,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B32" s="30">
         <v>388</v>
@@ -9454,7 +9371,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="27" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B33" s="28">
         <v>394</v>
@@ -9477,7 +9394,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B34" s="30">
         <v>400</v>
@@ -9500,7 +9417,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B35" s="28">
         <v>400</v>
@@ -9523,7 +9440,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B36" s="30">
         <v>414</v>
@@ -9546,7 +9463,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B37" s="28">
         <v>428</v>
@@ -9569,7 +9486,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B38" s="30">
         <v>458</v>
@@ -9592,7 +9509,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B39" s="28">
         <v>498</v>
@@ -9615,7 +9532,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B40" s="30">
         <v>446</v>
@@ -9638,7 +9555,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B41" s="28">
         <v>450</v>
@@ -9661,7 +9578,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B42" s="30">
         <v>440</v>
@@ -9684,7 +9601,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="27" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B43" s="28">
         <v>440</v>
@@ -9707,7 +9624,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B44" s="30">
         <v>496</v>
@@ -9730,7 +9647,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B45" s="28">
         <v>500</v>
@@ -9753,7 +9670,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B46" s="30">
         <v>482</v>
@@ -9776,7 +9693,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="27" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B47" s="28">
         <v>488</v>
@@ -9799,7 +9716,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B48" s="30">
         <v>596</v>
@@ -9822,7 +9739,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B49" s="28">
         <v>600</v>
@@ -9845,7 +9762,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B50" s="30">
         <v>582</v>
@@ -9868,7 +9785,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B51" s="28">
         <v>588</v>
@@ -9891,7 +9808,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B52" s="30">
         <v>594</v>
@@ -9914,7 +9831,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="27" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B53" s="28">
         <v>692</v>
@@ -9937,7 +9854,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B54" s="30">
         <v>700</v>
@@ -9960,7 +9877,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B55" s="28">
         <v>792</v>
@@ -9983,7 +9900,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B56" s="30">
         <v>800</v>
@@ -10006,7 +9923,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="27" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B57" s="28">
         <v>890</v>
@@ -10029,7 +9946,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B58" s="30">
         <v>900</v>
@@ -10052,7 +9969,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B59" s="28">
         <v>912</v>
@@ -10075,7 +9992,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B60" s="30">
         <v>918</v>
@@ -10135,7 +10052,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -10146,7 +10063,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B3" s="28">
         <v>20</v>
@@ -10169,7 +10086,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B4" s="30">
         <v>20</v>
@@ -10192,7 +10109,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B5" s="28">
         <v>25</v>
@@ -10215,7 +10132,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B6" s="30">
         <v>25</v>
@@ -10238,7 +10155,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B7" s="28">
         <v>30</v>
@@ -10261,7 +10178,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B8" s="30">
         <v>30</v>
@@ -10284,7 +10201,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B9" s="28">
         <v>40</v>
@@ -10307,7 +10224,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B10" s="30">
         <v>40</v>
@@ -10330,7 +10247,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B11" s="28">
         <v>50</v>
@@ -10353,7 +10270,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B12" s="30">
         <v>50</v>
@@ -10376,7 +10293,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B13" s="28">
         <v>50</v>
@@ -10399,7 +10316,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B14" s="30">
         <v>60</v>
@@ -10422,7 +10339,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B15" s="28">
         <v>60</v>
@@ -10445,7 +10362,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B16" s="30">
         <v>60</v>
@@ -10468,7 +10385,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B17" s="28">
         <v>75</v>
@@ -10491,7 +10408,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B18" s="30">
         <v>75</v>
@@ -10514,7 +10431,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B19" s="28">
         <v>75</v>
@@ -10537,7 +10454,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B20" s="30">
         <v>75</v>
@@ -10560,7 +10477,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B21" s="28">
         <v>80</v>
@@ -10583,7 +10500,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B22" s="30">
         <v>80</v>
@@ -10606,7 +10523,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B23" s="28">
         <v>80</v>
@@ -10629,7 +10546,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B24" s="30">
         <v>90</v>
@@ -10652,7 +10569,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B25" s="28">
         <v>90</v>
@@ -10675,7 +10592,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B26" s="30">
         <v>100</v>
@@ -10698,7 +10615,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B27" s="28">
         <v>100</v>
@@ -10721,7 +10638,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B28" s="30">
         <v>100</v>
@@ -10744,7 +10661,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B29" s="28">
         <v>100</v>
@@ -10767,7 +10684,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B30" s="30">
         <v>100</v>
@@ -10790,7 +10707,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B31" s="28">
         <v>100</v>
@@ -10813,7 +10730,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B32" s="30">
         <v>100</v>
@@ -10836,7 +10753,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="27" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B33" s="28">
         <v>125</v>
@@ -10859,7 +10776,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B34" s="30">
         <v>125</v>
@@ -10882,7 +10799,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B35" s="28">
         <v>125</v>
@@ -10905,7 +10822,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B36" s="30">
         <v>125</v>
@@ -10928,7 +10845,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B37" s="28">
         <v>125</v>
@@ -10951,7 +10868,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B38" s="30">
         <v>125</v>
@@ -10974,7 +10891,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B39" s="28">
         <v>150</v>
@@ -10997,7 +10914,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B40" s="30">
         <v>150</v>
@@ -11020,7 +10937,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B41" s="28">
         <v>150</v>
@@ -11043,7 +10960,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B42" s="30">
         <v>150</v>
@@ -11066,7 +10983,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="27" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B43" s="28">
         <v>175</v>
@@ -11089,7 +11006,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B44" s="30">
         <v>175</v>
@@ -11112,7 +11029,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B45" s="28">
         <v>175</v>
@@ -11135,7 +11052,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B46" s="30">
         <v>200</v>
@@ -11158,7 +11075,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="27" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B47" s="28">
         <v>200</v>
@@ -11181,7 +11098,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B48" s="30">
         <v>200</v>
@@ -11204,7 +11121,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B49" s="28">
         <v>200</v>
@@ -11227,7 +11144,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B50" s="30">
         <v>200</v>
@@ -11250,7 +11167,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B51" s="28">
         <v>250</v>
@@ -11273,7 +11190,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B52" s="30">
         <v>250</v>
@@ -11296,7 +11213,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="27" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B53" s="28">
         <v>250</v>
@@ -11319,7 +11236,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B54" s="30">
         <v>250</v>
@@ -11342,7 +11259,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B55" s="28">
         <v>250</v>
@@ -11365,7 +11282,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B56" s="30">
         <v>300</v>
@@ -11388,7 +11305,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="27" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B57" s="28">
         <v>300</v>
@@ -11411,7 +11328,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B58" s="30">
         <v>300</v>
@@ -11434,7 +11351,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B59" s="28">
         <v>300</v>
@@ -11457,7 +11374,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B60" s="30">
         <v>200</v>
@@ -11480,7 +11397,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="27" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B61" s="28">
         <v>200</v>
@@ -11503,7 +11420,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="29" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B62" s="30">
         <v>200</v>
@@ -11526,7 +11443,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="27" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B63" s="28">
         <v>200</v>
@@ -11549,7 +11466,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="29" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B64" s="30">
         <v>250</v>
@@ -11572,7 +11489,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="27" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B65" s="28">
         <v>250</v>
@@ -11595,7 +11512,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B66" s="30">
         <v>250</v>
@@ -11618,7 +11535,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="27" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B67" s="28">
         <v>250</v>
@@ -11641,7 +11558,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="29" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B68" s="30">
         <v>250</v>
@@ -11664,7 +11581,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="27" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B69" s="28">
         <v>250</v>
@@ -11687,7 +11604,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="29" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B70" s="30">
         <v>300</v>
@@ -11710,7 +11627,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="27" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B71" s="28">
         <v>300</v>
@@ -11733,7 +11650,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="29" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B72" s="30">
         <v>300</v>
@@ -11756,7 +11673,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="27" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B73" s="28">
         <v>300</v>
@@ -11779,7 +11696,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="29" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B74" s="30">
         <v>300</v>
@@ -11802,7 +11719,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="27" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B75" s="28">
         <v>300</v>
@@ -11825,7 +11742,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="29" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B76" s="30">
         <v>300</v>
@@ -11848,7 +11765,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="27" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B77" s="28">
         <v>350</v>
@@ -11871,7 +11788,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="29" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B78" s="30">
         <v>350</v>
@@ -11894,7 +11811,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="27" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B79" s="28">
         <v>350</v>
@@ -11917,7 +11834,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B80" s="30">
         <v>350</v>
@@ -11940,7 +11857,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="27" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B81" s="28">
         <v>350</v>
@@ -11963,7 +11880,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="29" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B82" s="30">
         <v>350</v>
@@ -11986,7 +11903,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="27" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B83" s="28">
         <v>400</v>
@@ -12009,7 +11926,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="29" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B84" s="30">
         <v>400</v>
@@ -12032,7 +11949,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="27" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B85" s="28">
         <v>400</v>
@@ -12055,7 +11972,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="29" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B86" s="30">
         <v>400</v>
@@ -12078,7 +11995,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="27" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B87" s="28">
         <v>400</v>
@@ -12101,7 +12018,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="29" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B88" s="30">
         <v>400</v>
@@ -12124,7 +12041,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="27" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B89" s="28">
         <v>450</v>
@@ -12147,7 +12064,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="29" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B90" s="30">
         <v>450</v>
@@ -12170,7 +12087,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B91" s="28">
         <v>450</v>
@@ -12193,7 +12110,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="29" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B92" s="30">
         <v>450</v>
@@ -12216,7 +12133,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="27" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B93" s="28">
         <v>450</v>
@@ -12239,7 +12156,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="29" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B94" s="30">
         <v>450</v>
@@ -12262,7 +12179,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="27" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B95" s="28">
         <v>500</v>
@@ -12285,7 +12202,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="29" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B96" s="30">
         <v>500</v>
@@ -12308,7 +12225,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="27" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B97" s="28">
         <v>500</v>
@@ -12331,7 +12248,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B98" s="30">
         <v>500</v>
@@ -12354,7 +12271,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="27" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B99" s="28">
         <v>500</v>
@@ -12377,7 +12294,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="29" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B100" s="30">
         <v>500</v>
@@ -12400,7 +12317,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="27" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B101" s="28">
         <v>550</v>
@@ -12423,7 +12340,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="29" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B102" s="30">
         <v>550</v>
@@ -12446,7 +12363,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="27" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B103" s="28">
         <v>550</v>
@@ -12469,7 +12386,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="29" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B104" s="30">
         <v>550</v>
@@ -12492,7 +12409,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="27" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B105" s="28">
         <v>550</v>
@@ -12515,7 +12432,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="29" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B106" s="30">
         <v>600</v>
@@ -12538,7 +12455,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="27" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B107" s="28">
         <v>600</v>
@@ -12561,7 +12478,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="29" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B108" s="30">
         <v>600</v>
@@ -12584,7 +12501,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="27" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B109" s="28">
         <v>600</v>
@@ -12607,7 +12524,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="29" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B110" s="30">
         <v>600</v>
@@ -12630,7 +12547,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="27" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B111" s="28">
         <v>600</v>
@@ -12653,7 +12570,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="29" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B112" s="30">
         <v>600</v>
@@ -12676,7 +12593,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="27" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B113" s="28">
         <v>600</v>
@@ -12699,7 +12616,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="29" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B114" s="30">
         <v>600</v>
@@ -12722,7 +12639,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="27" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B115" s="28">
         <v>600</v>
@@ -12745,7 +12662,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="29" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B116" s="30">
         <v>600</v>
@@ -12768,7 +12685,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="27" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B117" s="28">
         <v>650</v>
@@ -12791,7 +12708,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="29" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B118" s="30">
         <v>650</v>
@@ -12814,7 +12731,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="27" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B119" s="28">
         <v>650</v>
@@ -12837,7 +12754,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="29" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B120" s="30">
         <v>650</v>
@@ -12860,7 +12777,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="27" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B121" s="28">
         <v>650</v>
@@ -12883,7 +12800,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="29" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B122" s="30">
         <v>650</v>
@@ -12906,7 +12823,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="27" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B123" s="28">
         <v>650</v>
@@ -12929,7 +12846,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="29" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B124" s="30">
         <v>650</v>
@@ -12952,7 +12869,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="27" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B125" s="28">
         <v>650</v>
@@ -12975,7 +12892,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="29" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B126" s="30">
         <v>650</v>
@@ -12998,7 +12915,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="27" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B127" s="28">
         <v>700</v>
@@ -13021,7 +12938,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="29" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B128" s="30">
         <v>700</v>
@@ -13044,7 +12961,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="27" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B129" s="28">
         <v>700</v>
@@ -13067,7 +12984,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="29" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B130" s="30">
         <v>700</v>
@@ -13090,7 +13007,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="27" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B131" s="28">
         <v>700</v>
@@ -13113,7 +13030,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="29" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B132" s="30">
         <v>700</v>
@@ -13136,7 +13053,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="27" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B133" s="28">
         <v>700</v>
@@ -13159,7 +13076,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="29" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B134" s="30">
         <v>700</v>
@@ -13182,7 +13099,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="27" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B135" s="28">
         <v>700</v>
@@ -13205,7 +13122,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="29" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B136" s="30">
         <v>700</v>
@@ -13228,7 +13145,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="27" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B137" s="28">
         <v>750</v>
@@ -13251,7 +13168,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="29" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B138" s="30">
         <v>750</v>
@@ -13274,7 +13191,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="27" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B139" s="28">
         <v>750</v>
@@ -13297,7 +13214,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="29" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B140" s="30">
         <v>750</v>
@@ -13320,7 +13237,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="27" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B141" s="28">
         <v>750</v>
@@ -13343,7 +13260,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="29" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B142" s="30">
         <v>750</v>
@@ -13366,7 +13283,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="27" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B143" s="28">
         <v>750</v>
@@ -13389,7 +13306,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="29" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B144" s="30">
         <v>750</v>
@@ -13412,7 +13329,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="27" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B145" s="28">
         <v>750</v>
@@ -13435,7 +13352,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="29" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B146" s="30">
         <v>800</v>
@@ -13458,7 +13375,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="27" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B147" s="28">
         <v>800</v>
@@ -13481,7 +13398,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="29" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B148" s="30">
         <v>800</v>
@@ -13504,7 +13421,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="27" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B149" s="28">
         <v>800</v>
@@ -13527,7 +13444,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="29" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B150" s="30">
         <v>800</v>
@@ -13550,7 +13467,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="27" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B151" s="28">
         <v>800</v>
@@ -13573,7 +13490,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="29" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B152" s="30">
         <v>800</v>
@@ -13596,7 +13513,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="27" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B153" s="28">
         <v>800</v>
@@ -13619,7 +13536,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="29" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B154" s="30">
         <v>800</v>

--- a/plate3d/PLATE3D_COLUMN.xlsx
+++ b/plate3d/PLATE3D_COLUMN.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="441">
   <si>
     <t>COLUMN</t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t>plates fit</t>
+  </si>
+  <si>
+    <t>joint</t>
   </si>
   <si>
     <t xml:space="preserve">  4.  BOLTS</t>
@@ -2479,7 +2482,7 @@
         <v>21</v>
       </c>
       <c r="J28" s="7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K28" s="17" t="s">
         <v>58</v>
@@ -2574,7 +2577,7 @@
       <c r="K32" s="12"/>
       <c r="L32" s="12"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="11" t="s">
         <v>25</v>
       </c>
@@ -2599,13 +2602,20 @@
         <f>IF(PARAM!$C$6="H",IF(AND(PARAM!$E$28&lt;=PARAM!$F$6,PARAM!$E$30&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6),"ok",IF(PARAM!$E$28&gt;PARAM!$F$6,"flange plate too wide","web plate too deep")),"n/a")</f>
         <v>ok</v>
       </c>
+      <c r="I33" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="J33" s="11" t="str">
+        <f>IF(NOT(PARAM!$C$6="H"),"two end plates, "&amp;2*PARAM!$G$31&amp;" thick",IF(PARAM!$J$28=0,"bearing — the ends meet",PARAM!$J$28&amp;"mm apart — shim or division plate?"))</f>
+        <v>bearing — the ends meet</v>
+      </c>
     </row>
     <row r="35" ht="20" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -2619,27 +2629,27 @@
     </row>
     <row r="36" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E36" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E37" s="7">
         <v>16</v>
@@ -2649,7 +2659,7 @@
         <v>18</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H37" s="19">
         <f>IF(PARAM!$C$6="H",CEILING(PARAM!$G$28+PARAM!$H$6+PARAM!$G$29+1.1*PARAM!$E$37,5),"—")</f>
@@ -2666,30 +2676,30 @@
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G38" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I38" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="J38" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="J38" s="5" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E39" s="7">
         <v>4</v>
@@ -2712,7 +2722,7 @@
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E40" s="7">
         <v>4</v>
@@ -2735,16 +2745,16 @@
     </row>
     <row r="41" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E41" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
@@ -2766,7 +2776,7 @@
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B43" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
@@ -2784,21 +2794,21 @@
         <v>25</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D44" s="11" t="str">
         <f>IF(PARAM!$C$6="H",ROUND((PARAM!$F$28/2-PARAM!$G$39-PARAM!$F$39/2)/(PARAM!$E$39/2-1),1)&amp;" / "&amp;ROUND((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1),1),"n/a")</f>
         <v>85 / 60</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F44" s="11" t="str">
         <f>IF(PARAM!$C$6="H",ROUND((PARAM!$F$30/2-PARAM!$G$40-PARAM!$F$40/2)/(PARAM!$E$40/2-1),1)&amp;" / "&amp;ROUND((PARAM!$E$30-2*PARAM!$J$40-PARAM!$I$40)/(PARAM!$H$40-1),1),"n/a")</f>
         <v>90 / 77</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H44" s="11" t="str">
         <f>IF(PARAM!$C$6="H",2*PARAM!$E$39*PARAM!$H$39+PARAM!$E$40*PARAM!$H$40,2*PARAM!$E$42+2*MAX(0,PARAM!$H$42-2))&amp;" per splice"</f>
@@ -2807,10 +2817,10 @@
     </row>
     <row r="46" ht="20" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B46" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -2827,42 +2837,42 @@
         <v>4</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L47" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B48" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E48" s="8">
         <v>0</v>
@@ -2892,13 +2902,13 @@
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B49" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E49" s="8">
         <v>0</v>
@@ -2928,13 +2938,13 @@
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E50" s="8">
         <v>10</v>
@@ -2964,13 +2974,13 @@
     </row>
     <row r="51" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B51" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E51" s="8">
         <v>10</v>
@@ -3000,13 +3010,13 @@
     </row>
     <row r="52" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B52" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E52" s="8">
         <v>10</v>
@@ -3036,11 +3046,11 @@
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E53" s="8">
         <v>0</v>
@@ -3070,7 +3080,7 @@
     </row>
     <row r="54" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B54" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C54" s="12"/>
       <c r="D54" s="12"/>
@@ -3088,28 +3098,28 @@
         <v>25</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D55" s="11" t="str">
         <f>IF(COUNTIF(PARAM!$B$48:$B$53,PARAM!$C$59)+COUNTIF(PARAM!$B$48:$B$53,PARAM!$C$60)+COUNTIF(PARAM!$B$48:$B$53,PARAM!$C$61)+COUNTIF(PARAM!$B$48:$B$53,PARAM!$C$62)=4,"all 4 beams found theirs","a beam names a mark that is not in the list")</f>
         <v>all 4 beams found theirs</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F55" s="11" t="str">
         <f>IF(NOT(PARAM!$C$6="H"),"n/a",IF(SUMPRODUCT(MAX((PARAM!$C$48:$C$53="end plate")*(PARAM!$F$48:$F$53)))&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"fits between the flanges","hits the flanges on a web face"))</f>
         <v>fits between the flanges</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H55" s="11" t="str">
         <f>"M"&amp;PARAM!$E$37&amp;" L"&amp;MAX(IF(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0))+1.1*PARAM!$E$37,5),IF(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$59+1.1*PARAM!$E$37,5),0)),IF(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0))+1.1*PARAM!$E$37,5),IF(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$60+1.1*PARAM!$E$37,5),0)),IF(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0))+1.1*PARAM!$E$37,5),IF(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$61+1.1*PARAM!$E$37,5),0)),IF(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0))+1.1*PARAM!$E$37,5),IF(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$62+1.1*PARAM!$E$37,5),0)))</f>
         <v>M16 L55</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J55" s="11" t="str">
         <f>IF(NOT(PARAM!$C$6="H"),"n/a",IF(MOD(PARAM!$J$6,180)=0,IF(MAX(PARAM!$F$61,PARAM!$F$62)&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"ok","strip the beam flange"),IF(MAX(PARAM!$F$59,PARAM!$F$60)&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"ok","strip the beam flange")))</f>
@@ -3118,10 +3128,10 @@
     </row>
     <row r="57" ht="20" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B57" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -3135,7 +3145,7 @@
     </row>
     <row r="58" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C58" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>5</v>
@@ -3147,7 +3157,7 @@
         <v>7</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H58" s="5" t="s">
         <v>9</v>
@@ -3164,13 +3174,13 @@
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E59" s="8">
         <f>IFERROR(VLOOKUP($D$59,SECT!$A:$G,2,FALSE),"")</f>
@@ -3202,13 +3212,13 @@
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D60" s="7" t="s">
         <v>124</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>123</v>
       </c>
       <c r="E60" s="8">
         <f>IFERROR(VLOOKUP($D$60,SECT!$A:$G,2,FALSE),"")</f>
@@ -3240,13 +3250,13 @@
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E61" s="8">
         <f>IFERROR(VLOOKUP($D$61,SECT!$A:$G,2,FALSE),"")</f>
@@ -3278,13 +3288,13 @@
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E62" s="8">
         <f>IFERROR(VLOOKUP($D$62,SECT!$A:$G,2,FALSE),"")</f>
@@ -3316,7 +3326,7 @@
     </row>
     <row r="63" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B63" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C63" s="12"/>
       <c r="D63" s="12"/>
@@ -3334,21 +3344,21 @@
         <v>25</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D64" s="11" t="str">
         <f>IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,"flange","web"),"tube wall")</f>
         <v>flange</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F64" s="11" t="str">
         <f>IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,"web","flange"),"tube wall")</f>
         <v>web</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H64" s="11" t="str">
         <f>(IF(PARAM!$J$59&gt;0,1,0)+IF(PARAM!$J$60&gt;0,1,0)+IF(PARAM!$J$61&gt;0,1,0)+IF(PARAM!$J$62&gt;0,1,0))&amp;" of 4"</f>
@@ -3449,25 +3459,25 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -3475,10 +3485,10 @@
         <v>17</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D6" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3493,7 +3503,7 @@
         <v>H</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H6" s="22">
         <f>PARAM!$E$6</f>
@@ -3529,10 +3539,10 @@
         <v>18</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D7" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3547,7 +3557,7 @@
         <v>H</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H7" s="22">
         <f>PARAM!$E$6</f>
@@ -3583,10 +3593,10 @@
         <v>19</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D8" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3601,7 +3611,7 @@
         <v>H</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H8" s="22">
         <f>PARAM!$E$6</f>
@@ -3634,18 +3644,18 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D11" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3656,10 +3666,10 @@
         <v>12</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H11" s="22">
         <f>IF(PARAM!$C$6="H",PARAM!$E$28,PARAM!$E$31)</f>
@@ -3672,13 +3682,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3689,10 +3699,10 @@
         <v>10</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H12" s="22">
         <f>PARAM!$E$29</f>
@@ -3705,13 +3715,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D13" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3722,10 +3732,10 @@
         <v>10</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H13" s="22">
         <f>PARAM!$E$30</f>
@@ -3738,13 +3748,13 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D14" s="22" t="str">
         <f>PARAM!$G$37</f>
@@ -3776,13 +3786,13 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D15" s="22" t="str">
         <f>PARAM!$G$37</f>
@@ -3814,23 +3824,23 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D19" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3841,10 +3851,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H19" s="22">
         <f>MAX(1,PARAM!$G$15)</f>
@@ -3857,10 +3867,10 @@
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D20" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3871,10 +3881,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H20" s="22">
         <f>MAX(1,PARAM!$G$16)</f>
@@ -3887,10 +3897,10 @@
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D21" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3901,10 +3911,10 @@
         <v>1</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H21" s="22">
         <f>MAX(1,PARAM!$G$17)</f>
@@ -3917,10 +3927,10 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D22" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3931,10 +3941,10 @@
         <v>1</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H22" s="22">
         <f>MAX(1,PARAM!$G$18)</f>
@@ -3947,10 +3957,10 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D23" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3961,10 +3971,10 @@
         <v>1</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H23" s="22">
         <f>MAX(1,PARAM!$G$19)</f>
@@ -3977,10 +3987,10 @@
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D24" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3991,10 +4001,10 @@
         <v>1</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H24" s="22">
         <f>MAX(1,PARAM!$G$20)</f>
@@ -4007,10 +4017,10 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D25" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -4021,10 +4031,10 @@
         <v>1</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G25" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H25" s="22">
         <f>MAX(1,PARAM!$G$21)</f>
@@ -4037,10 +4047,10 @@
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D26" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -4051,10 +4061,10 @@
         <v>1</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H26" s="22">
         <f>MAX(1,PARAM!$G$22)</f>
@@ -4067,23 +4077,23 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D30" s="22" t="str">
         <f>IF(PARAM!$E$7&gt;0,"sc.c1","")</f>
@@ -4100,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J30" s="22">
         <v>0</v>
@@ -4114,27 +4124,27 @@
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D32" s="22" t="str">
         <f>"sc.c2"</f>
@@ -4151,7 +4161,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J32" s="22">
         <v>0</v>
@@ -4165,27 +4175,27 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C33" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="D33" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="D33" s="22" t="s">
-        <v>172</v>
-      </c>
       <c r="E33" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F33" s="22" t="s">
         <v>139</v>
-      </c>
-      <c r="F33" s="22" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D34" s="22" t="str">
         <f>IF(PARAM!$I$7&gt;0,"sc.c3","")</f>
@@ -4202,7 +4212,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J34" s="22">
         <v>0</v>
@@ -4216,42 +4226,42 @@
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D38" s="22" t="str">
         <f>IF(PARAM!$E$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F38" s="22">
         <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$28/2)),0)</f>
@@ -4271,17 +4281,17 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D39" s="22" t="str">
         <f>IF(PARAM!$E$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F39" s="22">
         <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$28/2)),0)</f>
@@ -4301,20 +4311,20 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="C40" s="22" t="s">
         <v>178</v>
-      </c>
-      <c r="B40" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="C40" s="22" t="s">
-        <v>177</v>
       </c>
       <c r="D40" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F40" s="22">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -4328,22 +4338,22 @@
         <v>0</v>
       </c>
       <c r="I40" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B41" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D41" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F41" s="22">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -4357,22 +4367,22 @@
         <v>0</v>
       </c>
       <c r="I41" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D42" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F42" s="22">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -4386,22 +4396,22 @@
         <v>0</v>
       </c>
       <c r="I42" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D43" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F43" s="22">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -4415,25 +4425,25 @@
         <v>0</v>
       </c>
       <c r="I43" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D44" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F44" s="22">
         <v>0</v>
@@ -4446,22 +4456,22 @@
         <v>0</v>
       </c>
       <c r="I44" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B45" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D45" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F45" s="22">
         <v>0</v>
@@ -4474,18 +4484,18 @@
         <v>0</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D46" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4505,7 +4515,7 @@
         <v>35</v>
       </c>
       <c r="I46" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J46" s="22">
         <v>0</v>
@@ -4547,10 +4557,10 @@
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B47" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D47" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4570,7 +4580,7 @@
         <v>35</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J47" s="22">
         <v>0</v>
@@ -4612,10 +4622,10 @@
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B48" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D48" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4635,7 +4645,7 @@
         <v>-35</v>
       </c>
       <c r="I48" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J48" s="22">
         <v>0</v>
@@ -4677,10 +4687,10 @@
     </row>
     <row r="49" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B49" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D49" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4700,7 +4710,7 @@
         <v>-35</v>
       </c>
       <c r="I49" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J49" s="22">
         <v>0</v>
@@ -4742,10 +4752,10 @@
     </row>
     <row r="50" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B50" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D50" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4765,7 +4775,7 @@
         <v>35</v>
       </c>
       <c r="I50" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J50" s="22">
         <v>0</v>
@@ -4807,10 +4817,10 @@
     </row>
     <row r="51" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B51" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D51" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4830,7 +4840,7 @@
         <v>35</v>
       </c>
       <c r="I51" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J51" s="22">
         <v>0</v>
@@ -4872,10 +4882,10 @@
     </row>
     <row r="52" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B52" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D52" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4895,7 +4905,7 @@
         <v>-35</v>
       </c>
       <c r="I52" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J52" s="22">
         <v>0</v>
@@ -4937,10 +4947,10 @@
     </row>
     <row r="53" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B53" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D53" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4960,7 +4970,7 @@
         <v>-35</v>
       </c>
       <c r="I53" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J53" s="22">
         <v>0</v>
@@ -5002,13 +5012,13 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D54" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -5028,7 +5038,7 @@
         <v>-10</v>
       </c>
       <c r="I54" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J54" s="22">
         <v>0</v>
@@ -5056,10 +5066,10 @@
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B55" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D55" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -5079,7 +5089,7 @@
         <v>-10</v>
       </c>
       <c r="I55" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J55" s="22">
         <v>0</v>
@@ -5107,13 +5117,13 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D56" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
@@ -5133,7 +5143,7 @@
         <v>-10</v>
       </c>
       <c r="I56" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J56" s="22">
         <v>0</v>
@@ -5161,10 +5171,10 @@
     </row>
     <row r="57" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B57" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D57" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
@@ -5184,7 +5194,7 @@
         <v>-10</v>
       </c>
       <c r="I57" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J57" s="22">
         <v>0</v>
@@ -5212,13 +5222,13 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D58" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -5238,7 +5248,7 @@
         <v>30</v>
       </c>
       <c r="I58" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J58" s="22">
         <v>0</v>
@@ -5280,10 +5290,10 @@
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B59" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D59" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -5303,7 +5313,7 @@
         <v>-30</v>
       </c>
       <c r="I59" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J59" s="22">
         <v>0</v>
@@ -5345,34 +5355,34 @@
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B60" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D60" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E60" s="22" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F60" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B61" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D61" s="22" t="str">
         <f>IF(PARAM!$I$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E61" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F61" s="22">
         <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$28/2)),0)</f>
@@ -5392,17 +5402,17 @@
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B62" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D62" s="22" t="str">
         <f>IF(PARAM!$I$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F62" s="22">
         <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$28/2)),0)</f>
@@ -5422,17 +5432,17 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B63" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D63" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E63" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F63" s="22">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -5446,22 +5456,22 @@
         <v>0</v>
       </c>
       <c r="I63" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B64" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D64" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E64" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F64" s="22">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -5475,22 +5485,22 @@
         <v>0</v>
       </c>
       <c r="I64" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B65" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D65" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E65" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F65" s="22">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -5504,22 +5514,22 @@
         <v>0</v>
       </c>
       <c r="I65" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B66" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C66" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D66" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E66" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F66" s="22">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -5533,22 +5543,22 @@
         <v>0</v>
       </c>
       <c r="I66" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B67" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C67" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D67" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E67" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F67" s="22">
         <v>0</v>
@@ -5561,22 +5571,22 @@
         <v>0</v>
       </c>
       <c r="I67" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B68" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D68" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F68" s="22">
         <v>0</v>
@@ -5589,15 +5599,15 @@
         <v>0</v>
       </c>
       <c r="I68" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B69" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D69" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5617,7 +5627,7 @@
         <v>35</v>
       </c>
       <c r="I69" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J69" s="22">
         <v>0</v>
@@ -5659,10 +5669,10 @@
     </row>
     <row r="70" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B70" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D70" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5682,7 +5692,7 @@
         <v>35</v>
       </c>
       <c r="I70" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J70" s="22">
         <v>0</v>
@@ -5724,10 +5734,10 @@
     </row>
     <row r="71" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B71" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D71" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5747,7 +5757,7 @@
         <v>-35</v>
       </c>
       <c r="I71" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J71" s="22">
         <v>0</v>
@@ -5789,10 +5799,10 @@
     </row>
     <row r="72" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B72" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D72" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5812,7 +5822,7 @@
         <v>-35</v>
       </c>
       <c r="I72" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J72" s="22">
         <v>0</v>
@@ -5854,10 +5864,10 @@
     </row>
     <row r="73" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B73" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D73" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5877,7 +5887,7 @@
         <v>35</v>
       </c>
       <c r="I73" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J73" s="22">
         <v>0</v>
@@ -5919,10 +5929,10 @@
     </row>
     <row r="74" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B74" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C74" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D74" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5942,7 +5952,7 @@
         <v>35</v>
       </c>
       <c r="I74" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J74" s="22">
         <v>0</v>
@@ -5984,10 +5994,10 @@
     </row>
     <row r="75" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B75" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C75" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D75" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -6007,7 +6017,7 @@
         <v>-35</v>
       </c>
       <c r="I75" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J75" s="22">
         <v>0</v>
@@ -6049,10 +6059,10 @@
     </row>
     <row r="76" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B76" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C76" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D76" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -6072,7 +6082,7 @@
         <v>-35</v>
       </c>
       <c r="I76" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J76" s="22">
         <v>0</v>
@@ -6114,10 +6124,10 @@
     </row>
     <row r="77" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B77" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D77" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -6137,7 +6147,7 @@
         <v>-10</v>
       </c>
       <c r="I77" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J77" s="22">
         <v>0</v>
@@ -6165,10 +6175,10 @@
     </row>
     <row r="78" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B78" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C78" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D78" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -6188,7 +6198,7 @@
         <v>-10</v>
       </c>
       <c r="I78" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J78" s="22">
         <v>0</v>
@@ -6216,10 +6226,10 @@
     </row>
     <row r="79" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B79" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C79" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D79" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
@@ -6239,7 +6249,7 @@
         <v>-10</v>
       </c>
       <c r="I79" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J79" s="22">
         <v>0</v>
@@ -6267,10 +6277,10 @@
     </row>
     <row r="80" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B80" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C80" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D80" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
@@ -6290,7 +6300,7 @@
         <v>-10</v>
       </c>
       <c r="I80" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J80" s="22">
         <v>0</v>
@@ -6318,10 +6328,10 @@
     </row>
     <row r="81" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B81" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C81" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D81" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -6341,7 +6351,7 @@
         <v>30</v>
       </c>
       <c r="I81" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J81" s="22">
         <v>0</v>
@@ -6383,10 +6393,10 @@
     </row>
     <row r="82" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B82" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C82" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D82" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -6406,7 +6416,7 @@
         <v>-30</v>
       </c>
       <c r="I82" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J82" s="22">
         <v>0</v>
@@ -6448,47 +6458,47 @@
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B83" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C83" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="D83" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="E83" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="D83" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="E83" s="22" t="s">
-        <v>186</v>
-      </c>
       <c r="F83" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B87" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C87" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D87" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$15&gt;0),"pl.stf1","")</f>
         <v>pl.stf1</v>
       </c>
       <c r="E87" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F87" s="22">
         <v>0</v>
@@ -6502,7 +6512,7 @@
         <v>845.5</v>
       </c>
       <c r="I87" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J87" s="22">
         <v>0</v>
@@ -6529,17 +6539,17 @@
     </row>
     <row r="88" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B88" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C88" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D88" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$16&gt;0),"pl.stf2","")</f>
         <v>pl.stf2</v>
       </c>
       <c r="E88" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F88" s="22">
         <v>0</v>
@@ -6553,7 +6563,7 @@
         <v>554.5</v>
       </c>
       <c r="I88" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J88" s="22">
         <v>0</v>
@@ -6580,17 +6590,17 @@
     </row>
     <row r="89" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B89" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C89" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D89" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$17&gt;0),"pl.stf3","")</f>
         <v/>
       </c>
       <c r="E89" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F89" s="22">
         <v>0</v>
@@ -6604,7 +6614,7 @@
         <v>700</v>
       </c>
       <c r="I89" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J89" s="22">
         <v>0</v>
@@ -6631,17 +6641,17 @@
     </row>
     <row r="90" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B90" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C90" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D90" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$18&gt;0),"pl.stf4","")</f>
         <v/>
       </c>
       <c r="E90" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F90" s="22">
         <v>0</v>
@@ -6655,7 +6665,7 @@
         <v>700</v>
       </c>
       <c r="I90" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J90" s="22">
         <v>0</v>
@@ -6682,17 +6692,17 @@
     </row>
     <row r="91" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B91" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C91" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D91" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$19&gt;0),"pl.stf5","")</f>
         <v/>
       </c>
       <c r="E91" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F91" s="22">
         <v>0</v>
@@ -6706,7 +6716,7 @@
         <v>700</v>
       </c>
       <c r="I91" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J91" s="22">
         <v>0</v>
@@ -6733,17 +6743,17 @@
     </row>
     <row r="92" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B92" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C92" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D92" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$20&gt;0),"pl.stf6","")</f>
         <v/>
       </c>
       <c r="E92" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F92" s="22">
         <v>0</v>
@@ -6757,7 +6767,7 @@
         <v>700</v>
       </c>
       <c r="I92" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J92" s="22">
         <v>0</v>
@@ -6784,17 +6794,17 @@
     </row>
     <row r="93" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B93" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C93" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D93" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$21&gt;0),"pl.stf7","")</f>
         <v/>
       </c>
       <c r="E93" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F93" s="22">
         <v>0</v>
@@ -6808,7 +6818,7 @@
         <v>700</v>
       </c>
       <c r="I93" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J93" s="22">
         <v>0</v>
@@ -6835,17 +6845,17 @@
     </row>
     <row r="94" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B94" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C94" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D94" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$22&gt;0),"pl.stf8","")</f>
         <v/>
       </c>
       <c r="E94" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F94" s="22">
         <v>0</v>
@@ -6859,7 +6869,7 @@
         <v>700</v>
       </c>
       <c r="I94" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J94" s="22">
         <v>0</v>
@@ -6886,7 +6896,7 @@
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -6894,16 +6904,16 @@
         <v>18</v>
       </c>
       <c r="B97" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C97" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D97" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E97" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F97" s="22">
         <v>0</v>
@@ -6928,19 +6938,19 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="B98" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="C98" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="D98" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="E98" s="22" t="s">
         <v>195</v>
-      </c>
-      <c r="B98" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="C98" s="22" t="s">
-        <v>193</v>
-      </c>
-      <c r="D98" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="E98" s="22" t="s">
-        <v>194</v>
       </c>
       <c r="F98" s="22">
         <v>0</v>
@@ -6950,7 +6960,7 @@
       </c>
       <c r="H98" s="22">
         <f>(PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$28,2*PARAM!$G$31))</f>
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="I98" s="22">
         <v>0</v>
@@ -6968,16 +6978,16 @@
         <v>19</v>
       </c>
       <c r="B99" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C99" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D99" s="22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E99" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F99" s="22">
         <v>0</v>
@@ -6987,7 +6997,7 @@
       </c>
       <c r="H99" s="22">
         <f>-((PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$28,2*PARAM!$G$31))+MAX(1,PARAM!$I$7))</f>
-        <v>-1410</v>
+        <v>-1400</v>
       </c>
       <c r="I99" s="22">
         <v>0</v>
@@ -7002,19 +7012,19 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B100" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C100" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D100" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E100" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F100" s="22">
         <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$28/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
@@ -7026,7 +7036,7 @@
       </c>
       <c r="H100" s="22">
         <f>(PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$28/2,PARAM!$G$31))+IF(PARAM!$C$6="H",0,-PARAM!$G$31/2)</f>
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="I100" s="22">
         <v>0</v>
@@ -7041,16 +7051,16 @@
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C101" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D101" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E101" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F101" s="22">
         <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$28/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
@@ -7062,7 +7072,7 @@
       </c>
       <c r="H101" s="22">
         <f>-(PARAM!$G$7/2+IF(PARAM!$C$6="H",PARAM!$J$28/2,PARAM!$G$31))+IF(PARAM!$C$6="H",0,PARAM!$G$31/2)</f>
-        <v>-705</v>
+        <v>-700</v>
       </c>
       <c r="I101" s="22">
         <v>0</v>
@@ -7077,18 +7087,18 @@
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B104" s="21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C104" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D104" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7102,7 +7112,7 @@
         <v>14</v>
       </c>
       <c r="G104" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H104" s="22">
         <f>PARAM!$E$59</f>
@@ -7135,10 +7145,10 @@
     </row>
     <row r="105" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B105" s="21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C105" s="22" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D105" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7152,7 +7162,7 @@
         <v>14</v>
       </c>
       <c r="G105" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H105" s="22">
         <f>PARAM!$E$60</f>
@@ -7185,10 +7195,10 @@
     </row>
     <row r="106" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B106" s="21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C106" s="22" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D106" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7202,7 +7212,7 @@
         <v>14</v>
       </c>
       <c r="G106" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H106" s="22">
         <f>PARAM!$E$61</f>
@@ -7235,10 +7245,10 @@
     </row>
     <row r="107" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B107" s="21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C107" s="22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D107" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7252,7 +7262,7 @@
         <v>14</v>
       </c>
       <c r="G107" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H107" s="22">
         <f>PARAM!$E$62</f>
@@ -7285,18 +7295,18 @@
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B110" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C110" s="22" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D110" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7307,10 +7317,10 @@
         <v>20</v>
       </c>
       <c r="F110" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G110" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H110" s="22">
         <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,5,FALSE),0))</f>
@@ -7323,10 +7333,10 @@
     </row>
     <row r="111" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B111" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C111" s="22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D111" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7337,10 +7347,10 @@
         <v>10</v>
       </c>
       <c r="F111" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G111" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H111" s="22">
         <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,5,FALSE),0))</f>
@@ -7353,10 +7363,10 @@
     </row>
     <row r="112" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B112" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C112" s="22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D112" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7367,10 +7377,10 @@
         <v>10</v>
       </c>
       <c r="F112" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G112" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H112" s="22">
         <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,5,FALSE),0))</f>
@@ -7383,10 +7393,10 @@
     </row>
     <row r="113" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B113" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C113" s="22" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D113" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7397,10 +7407,10 @@
         <v>10</v>
       </c>
       <c r="F113" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G113" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H113" s="22">
         <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,5,FALSE),0))</f>
@@ -7413,13 +7423,13 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B114" s="21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C114" s="22" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D114" s="22" t="str">
         <f>PARAM!$G$37</f>
@@ -7451,10 +7461,10 @@
     </row>
     <row r="115" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B115" s="21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C115" s="22" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D115" s="22" t="str">
         <f>PARAM!$G$37</f>
@@ -7486,10 +7496,10 @@
     </row>
     <row r="116" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B116" s="21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C116" s="22" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D116" s="22" t="str">
         <f>PARAM!$G$37</f>
@@ -7521,10 +7531,10 @@
     </row>
     <row r="117" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B117" s="21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C117" s="22" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D117" s="22" t="str">
         <f>PARAM!$G$37</f>
@@ -7556,30 +7566,30 @@
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B122" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C122" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D122" s="22" t="str">
         <f>IF(AND(PARAM!$J$59&gt;0,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cna","")</f>
         <v>pl.cna</v>
       </c>
       <c r="E122" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F122" s="22">
         <f>-IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)/2</f>
@@ -7593,7 +7603,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J122" s="22">
         <v>0</v>
@@ -7607,20 +7617,20 @@
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="B123" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="C123" s="22" t="s">
         <v>218</v>
-      </c>
-      <c r="B123" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="C123" s="22" t="s">
-        <v>217</v>
       </c>
       <c r="D123" s="22" t="str">
         <f>IF(AND(PARAM!$J$59&gt;0,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cna","")</f>
         <v/>
       </c>
       <c r="E123" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F123" s="22">
         <f>-1.5*IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)</f>
@@ -7634,7 +7644,7 @@
         <v>0</v>
       </c>
       <c r="I123" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J123" s="22">
         <v>0</v>
@@ -7648,20 +7658,20 @@
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B124" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C124" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D124" s="22" t="str">
         <f>IF(AND(PARAM!$J$59&gt;0,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cna","")</f>
         <v/>
       </c>
       <c r="E124" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F124" s="22">
         <f>IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,4,FALSE),0)</f>
@@ -7675,7 +7685,7 @@
         <v>0</v>
       </c>
       <c r="I124" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J124" s="22">
         <v>0</v>
@@ -7689,13 +7699,13 @@
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B125" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C125" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D125" s="22" t="str">
         <f>IF(PARAM!$J$59&gt;0,"sc.bma","")</f>
@@ -7712,7 +7722,7 @@
         <v>0</v>
       </c>
       <c r="I125" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J125" s="22">
         <v>0</v>
@@ -7726,13 +7736,13 @@
     </row>
     <row r="126" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B126" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C126" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D126" s="22" t="str">
         <f>IF(OR(PARAM!$J$59&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cna")</f>
@@ -7796,39 +7806,39 @@
     </row>
     <row r="127" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B127" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C127" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D127" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E127" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F127" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="130" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B130" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C130" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D130" s="22" t="str">
         <f>IF(AND(PARAM!$J$60&gt;0,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cnb","")</f>
         <v/>
       </c>
       <c r="E130" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F130" s="22">
         <f>-(-IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)/2)</f>
@@ -7842,7 +7852,7 @@
         <v>0</v>
       </c>
       <c r="I130" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J130" s="22">
         <v>0</v>
@@ -7856,17 +7866,17 @@
     </row>
     <row r="131" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B131" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C131" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D131" s="22" t="str">
         <f>IF(AND(PARAM!$J$60&gt;0,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnb","")</f>
         <v/>
       </c>
       <c r="E131" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F131" s="22">
         <f>-(-1.5*IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0))</f>
@@ -7880,7 +7890,7 @@
         <v>0</v>
       </c>
       <c r="I131" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J131" s="22">
         <v>0</v>
@@ -7894,17 +7904,17 @@
     </row>
     <row r="132" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B132" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C132" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D132" s="22" t="str">
         <f>IF(AND(PARAM!$J$60&gt;0,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cnb","")</f>
         <v>pl.cnb</v>
       </c>
       <c r="E132" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F132" s="22">
         <f>-(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,4,FALSE),0))</f>
@@ -7918,7 +7928,7 @@
         <v>0</v>
       </c>
       <c r="I132" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J132" s="22">
         <v>0</v>
@@ -7932,10 +7942,10 @@
     </row>
     <row r="133" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B133" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C133" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D133" s="22" t="str">
         <f>IF(PARAM!$J$60&gt;0,"sc.bmb","")</f>
@@ -7952,7 +7962,7 @@
         <v>0</v>
       </c>
       <c r="I133" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J133" s="22">
         <v>0</v>
@@ -7966,10 +7976,10 @@
     </row>
     <row r="134" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B134" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C134" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D134" s="22" t="str">
         <f>IF(OR(PARAM!$J$60&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cnb")</f>
@@ -8033,39 +8043,39 @@
     </row>
     <row r="135" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B135" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C135" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D135" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E135" s="22" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F135" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="138" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B138" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C138" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D138" s="22" t="str">
         <f>IF(AND(PARAM!$J$61&gt;0,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cnc","")</f>
         <v/>
       </c>
       <c r="E138" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F138" s="22">
         <f>0</f>
@@ -8079,7 +8089,7 @@
         <v>0</v>
       </c>
       <c r="I138" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J138" s="22">
         <v>0</v>
@@ -8093,17 +8103,17 @@
     </row>
     <row r="139" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B139" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C139" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D139" s="22" t="str">
         <f>IF(AND(PARAM!$J$61&gt;0,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnc","")</f>
         <v/>
       </c>
       <c r="E139" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F139" s="22">
         <f>0</f>
@@ -8117,7 +8127,7 @@
         <v>0</v>
       </c>
       <c r="I139" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J139" s="22">
         <v>0</v>
@@ -8131,17 +8141,17 @@
     </row>
     <row r="140" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B140" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C140" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D140" s="22" t="str">
         <f>IF(AND(PARAM!$J$61&gt;0,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cnc","")</f>
         <v>pl.cnc</v>
       </c>
       <c r="E140" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F140" s="22">
         <f>PARAM!$G$61/2+IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0)/2</f>
@@ -8155,7 +8165,7 @@
         <v>0</v>
       </c>
       <c r="I140" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J140" s="22">
         <v>0</v>
@@ -8169,10 +8179,10 @@
     </row>
     <row r="141" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B141" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C141" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D141" s="22" t="str">
         <f>IF(PARAM!$J$61&gt;0,"sc.bmc","")</f>
@@ -8189,7 +8199,7 @@
         <v>0</v>
       </c>
       <c r="I141" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J141" s="22">
         <v>0</v>
@@ -8203,10 +8213,10 @@
     </row>
     <row r="142" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B142" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C142" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D142" s="22" t="str">
         <f>IF(OR(PARAM!$J$61&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cnc")</f>
@@ -8270,39 +8280,39 @@
     </row>
     <row r="143" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B143" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C143" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D143" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E143" s="22" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F143" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="146" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B146" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C146" s="22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D146" s="22" t="str">
         <f>IF(AND(PARAM!$J$62&gt;0,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cnd","")</f>
         <v/>
       </c>
       <c r="E146" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F146" s="22">
         <f>0</f>
@@ -8316,7 +8326,7 @@
         <v>0</v>
       </c>
       <c r="I146" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J146" s="22">
         <v>0</v>
@@ -8330,17 +8340,17 @@
     </row>
     <row r="147" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B147" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C147" s="22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D147" s="22" t="str">
         <f>IF(AND(PARAM!$J$62&gt;0,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnd","")</f>
         <v/>
       </c>
       <c r="E147" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F147" s="22">
         <f>0</f>
@@ -8354,7 +8364,7 @@
         <v>0</v>
       </c>
       <c r="I147" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J147" s="22">
         <v>0</v>
@@ -8368,17 +8378,17 @@
     </row>
     <row r="148" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B148" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C148" s="22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D148" s="22" t="str">
         <f>IF(AND(PARAM!$J$62&gt;0,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cnd","")</f>
         <v/>
       </c>
       <c r="E148" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F148" s="22">
         <f>-(PARAM!$G$62/2+IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0)/2)</f>
@@ -8392,7 +8402,7 @@
         <v>0</v>
       </c>
       <c r="I148" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J148" s="22">
         <v>0</v>
@@ -8406,10 +8416,10 @@
     </row>
     <row r="149" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B149" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C149" s="22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D149" s="22" t="str">
         <f>IF(PARAM!$J$62&gt;0,"sc.bmd","")</f>
@@ -8426,7 +8436,7 @@
         <v>0</v>
       </c>
       <c r="I149" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J149" s="22">
         <v>0</v>
@@ -8440,10 +8450,10 @@
     </row>
     <row r="150" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B150" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C150" s="22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D150" s="22" t="str">
         <f>IF(OR(PARAM!$J$62&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cnd")</f>
@@ -8507,41 +8517,41 @@
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B151" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C151" s="22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D151" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E151" s="22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F151" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B154" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C154" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D154" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E154" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F154" s="22">
         <f>(IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,4,FALSE),0))</f>
@@ -8556,16 +8566,16 @@
     </row>
     <row r="155" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B155" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C155" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D155" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E155" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F155" s="22">
         <f>-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,4,FALSE),0)))</f>
@@ -8580,16 +8590,16 @@
     </row>
     <row r="156" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B156" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C156" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D156" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E156" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F156" s="22">
         <v>0</v>
@@ -8604,16 +8614,16 @@
     </row>
     <row r="157" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B157" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C157" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D157" s="22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E157" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F157" s="22">
         <v>0</v>
@@ -8628,7 +8638,7 @@
     </row>
     <row r="159" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B159" s="21" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -8656,7 +8666,7 @@
         <v>7</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E1" s="24" t="s">
         <v>9</v>
@@ -8670,7 +8680,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -8681,7 +8691,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B3" s="28">
         <v>100</v>
@@ -8704,7 +8714,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B4" s="30">
         <v>125</v>
@@ -8727,7 +8737,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B5" s="28">
         <v>150</v>
@@ -8750,7 +8760,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B6" s="30">
         <v>148</v>
@@ -8773,7 +8783,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B7" s="28">
         <v>150</v>
@@ -8796,7 +8806,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B8" s="30">
         <v>198</v>
@@ -8819,7 +8829,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B9" s="28">
         <v>200</v>
@@ -8842,7 +8852,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B10" s="30">
         <v>194</v>
@@ -8865,7 +8875,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B11" s="28">
         <v>200</v>
@@ -8888,7 +8898,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B12" s="30">
         <v>200</v>
@@ -8911,7 +8921,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B13" s="28">
         <v>248</v>
@@ -8934,7 +8944,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B14" s="30">
         <v>250</v>
@@ -8957,7 +8967,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B15" s="28">
         <v>244</v>
@@ -8980,7 +8990,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B16" s="30">
         <v>250</v>
@@ -9003,7 +9013,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B17" s="28">
         <v>250</v>
@@ -9026,7 +9036,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B18" s="30">
         <v>298</v>
@@ -9049,7 +9059,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B19" s="28">
         <v>300</v>
@@ -9072,7 +9082,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B20" s="30">
         <v>294</v>
@@ -9095,7 +9105,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B21" s="28">
         <v>294</v>
@@ -9141,7 +9151,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B23" s="28">
         <v>300</v>
@@ -9164,7 +9174,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B24" s="30">
         <v>346</v>
@@ -9187,7 +9197,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B25" s="28">
         <v>350</v>
@@ -9210,7 +9220,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B26" s="30">
         <v>340</v>
@@ -9233,7 +9243,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B27" s="28">
         <v>344</v>
@@ -9256,7 +9266,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B28" s="30">
         <v>350</v>
@@ -9279,7 +9289,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B29" s="28">
         <v>396</v>
@@ -9302,7 +9312,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B30" s="30">
         <v>400</v>
@@ -9325,7 +9335,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B31" s="28">
         <v>390</v>
@@ -9348,7 +9358,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B32" s="30">
         <v>388</v>
@@ -9371,7 +9381,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="27" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B33" s="28">
         <v>394</v>
@@ -9394,7 +9404,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B34" s="30">
         <v>400</v>
@@ -9417,7 +9427,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B35" s="28">
         <v>400</v>
@@ -9440,7 +9450,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B36" s="30">
         <v>414</v>
@@ -9463,7 +9473,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B37" s="28">
         <v>428</v>
@@ -9486,7 +9496,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B38" s="30">
         <v>458</v>
@@ -9509,7 +9519,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B39" s="28">
         <v>498</v>
@@ -9532,7 +9542,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B40" s="30">
         <v>446</v>
@@ -9555,7 +9565,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B41" s="28">
         <v>450</v>
@@ -9578,7 +9588,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B42" s="30">
         <v>440</v>
@@ -9601,7 +9611,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="27" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B43" s="28">
         <v>440</v>
@@ -9624,7 +9634,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B44" s="30">
         <v>496</v>
@@ -9647,7 +9657,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B45" s="28">
         <v>500</v>
@@ -9670,7 +9680,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B46" s="30">
         <v>482</v>
@@ -9693,7 +9703,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="27" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B47" s="28">
         <v>488</v>
@@ -9716,7 +9726,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B48" s="30">
         <v>596</v>
@@ -9739,7 +9749,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B49" s="28">
         <v>600</v>
@@ -9762,7 +9772,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B50" s="30">
         <v>582</v>
@@ -9785,7 +9795,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B51" s="28">
         <v>588</v>
@@ -9808,7 +9818,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B52" s="30">
         <v>594</v>
@@ -9831,7 +9841,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="27" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B53" s="28">
         <v>692</v>
@@ -9854,7 +9864,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B54" s="30">
         <v>700</v>
@@ -9877,7 +9887,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B55" s="28">
         <v>792</v>
@@ -9900,7 +9910,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B56" s="30">
         <v>800</v>
@@ -9923,7 +9933,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="27" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B57" s="28">
         <v>890</v>
@@ -9946,7 +9956,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B58" s="30">
         <v>900</v>
@@ -9969,7 +9979,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B59" s="28">
         <v>912</v>
@@ -9992,7 +10002,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B60" s="30">
         <v>918</v>
@@ -10038,7 +10048,7 @@
         <v>7</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E1" s="24" t="s">
         <v>9</v>
@@ -10052,7 +10062,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -10063,7 +10073,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B3" s="28">
         <v>20</v>
@@ -10086,7 +10096,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B4" s="30">
         <v>20</v>
@@ -10109,7 +10119,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B5" s="28">
         <v>25</v>
@@ -10132,7 +10142,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B6" s="30">
         <v>25</v>
@@ -10155,7 +10165,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B7" s="28">
         <v>30</v>
@@ -10178,7 +10188,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B8" s="30">
         <v>30</v>
@@ -10201,7 +10211,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B9" s="28">
         <v>40</v>
@@ -10224,7 +10234,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B10" s="30">
         <v>40</v>
@@ -10247,7 +10257,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B11" s="28">
         <v>50</v>
@@ -10270,7 +10280,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B12" s="30">
         <v>50</v>
@@ -10293,7 +10303,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B13" s="28">
         <v>50</v>
@@ -10316,7 +10326,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B14" s="30">
         <v>60</v>
@@ -10339,7 +10349,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B15" s="28">
         <v>60</v>
@@ -10362,7 +10372,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B16" s="30">
         <v>60</v>
@@ -10385,7 +10395,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B17" s="28">
         <v>75</v>
@@ -10408,7 +10418,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B18" s="30">
         <v>75</v>
@@ -10431,7 +10441,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B19" s="28">
         <v>75</v>
@@ -10454,7 +10464,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B20" s="30">
         <v>75</v>
@@ -10477,7 +10487,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B21" s="28">
         <v>80</v>
@@ -10500,7 +10510,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B22" s="30">
         <v>80</v>
@@ -10523,7 +10533,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B23" s="28">
         <v>80</v>
@@ -10546,7 +10556,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B24" s="30">
         <v>90</v>
@@ -10569,7 +10579,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B25" s="28">
         <v>90</v>
@@ -10592,7 +10602,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B26" s="30">
         <v>100</v>
@@ -10615,7 +10625,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B27" s="28">
         <v>100</v>
@@ -10638,7 +10648,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B28" s="30">
         <v>100</v>
@@ -10661,7 +10671,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B29" s="28">
         <v>100</v>
@@ -10684,7 +10694,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B30" s="30">
         <v>100</v>
@@ -10707,7 +10717,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B31" s="28">
         <v>100</v>
@@ -10730,7 +10740,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B32" s="30">
         <v>100</v>
@@ -10753,7 +10763,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="27" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B33" s="28">
         <v>125</v>
@@ -10776,7 +10786,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B34" s="30">
         <v>125</v>
@@ -10799,7 +10809,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B35" s="28">
         <v>125</v>
@@ -10822,7 +10832,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B36" s="30">
         <v>125</v>
@@ -10845,7 +10855,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B37" s="28">
         <v>125</v>
@@ -10868,7 +10878,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B38" s="30">
         <v>125</v>
@@ -10891,7 +10901,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B39" s="28">
         <v>150</v>
@@ -10914,7 +10924,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B40" s="30">
         <v>150</v>
@@ -10937,7 +10947,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B41" s="28">
         <v>150</v>
@@ -10960,7 +10970,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B42" s="30">
         <v>150</v>
@@ -10983,7 +10993,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="27" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B43" s="28">
         <v>175</v>
@@ -11006,7 +11016,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B44" s="30">
         <v>175</v>
@@ -11029,7 +11039,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B45" s="28">
         <v>175</v>
@@ -11052,7 +11062,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B46" s="30">
         <v>200</v>
@@ -11075,7 +11085,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="27" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B47" s="28">
         <v>200</v>
@@ -11098,7 +11108,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B48" s="30">
         <v>200</v>
@@ -11121,7 +11131,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B49" s="28">
         <v>200</v>
@@ -11144,7 +11154,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B50" s="30">
         <v>200</v>
@@ -11167,7 +11177,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B51" s="28">
         <v>250</v>
@@ -11190,7 +11200,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B52" s="30">
         <v>250</v>
@@ -11213,7 +11223,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="27" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B53" s="28">
         <v>250</v>
@@ -11236,7 +11246,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B54" s="30">
         <v>250</v>
@@ -11259,7 +11269,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B55" s="28">
         <v>250</v>
@@ -11282,7 +11292,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B56" s="30">
         <v>300</v>
@@ -11305,7 +11315,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="27" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B57" s="28">
         <v>300</v>
@@ -11328,7 +11338,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B58" s="30">
         <v>300</v>
@@ -11351,7 +11361,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B59" s="28">
         <v>300</v>
@@ -11374,7 +11384,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B60" s="30">
         <v>200</v>
@@ -11397,7 +11407,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="27" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B61" s="28">
         <v>200</v>
@@ -11420,7 +11430,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="29" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B62" s="30">
         <v>200</v>
@@ -11443,7 +11453,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="27" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B63" s="28">
         <v>200</v>
@@ -11466,7 +11476,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="29" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B64" s="30">
         <v>250</v>
@@ -11489,7 +11499,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="27" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B65" s="28">
         <v>250</v>
@@ -11512,7 +11522,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="29" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B66" s="30">
         <v>250</v>
@@ -11535,7 +11545,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="27" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B67" s="28">
         <v>250</v>
@@ -11558,7 +11568,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="29" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B68" s="30">
         <v>250</v>
@@ -11581,7 +11591,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="27" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B69" s="28">
         <v>250</v>
@@ -11604,7 +11614,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="29" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B70" s="30">
         <v>300</v>
@@ -11627,7 +11637,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="27" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B71" s="28">
         <v>300</v>
@@ -11650,7 +11660,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="29" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B72" s="30">
         <v>300</v>
@@ -11673,7 +11683,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="27" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B73" s="28">
         <v>300</v>
@@ -11696,7 +11706,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="29" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B74" s="30">
         <v>300</v>
@@ -11719,7 +11729,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="27" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B75" s="28">
         <v>300</v>
@@ -11742,7 +11752,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="29" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B76" s="30">
         <v>300</v>
@@ -11765,7 +11775,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="27" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B77" s="28">
         <v>350</v>
@@ -11788,7 +11798,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="29" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B78" s="30">
         <v>350</v>
@@ -11811,7 +11821,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="27" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B79" s="28">
         <v>350</v>
@@ -11834,7 +11844,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="29" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B80" s="30">
         <v>350</v>
@@ -11857,7 +11867,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="27" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B81" s="28">
         <v>350</v>
@@ -11880,7 +11890,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="29" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B82" s="30">
         <v>350</v>
@@ -11903,7 +11913,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="27" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B83" s="28">
         <v>400</v>
@@ -11926,7 +11936,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="29" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B84" s="30">
         <v>400</v>
@@ -11949,7 +11959,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="27" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B85" s="28">
         <v>400</v>
@@ -11972,7 +11982,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="29" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B86" s="30">
         <v>400</v>
@@ -11995,7 +12005,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="27" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B87" s="28">
         <v>400</v>
@@ -12018,7 +12028,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="29" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B88" s="30">
         <v>400</v>
@@ -12041,7 +12051,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="27" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B89" s="28">
         <v>450</v>
@@ -12064,7 +12074,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="29" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B90" s="30">
         <v>450</v>
@@ -12087,7 +12097,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="27" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B91" s="28">
         <v>450</v>
@@ -12110,7 +12120,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="29" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B92" s="30">
         <v>450</v>
@@ -12133,7 +12143,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="27" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B93" s="28">
         <v>450</v>
@@ -12156,7 +12166,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="29" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B94" s="30">
         <v>450</v>
@@ -12179,7 +12189,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="27" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B95" s="28">
         <v>500</v>
@@ -12202,7 +12212,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="29" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B96" s="30">
         <v>500</v>
@@ -12225,7 +12235,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="27" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B97" s="28">
         <v>500</v>
@@ -12248,7 +12258,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="29" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B98" s="30">
         <v>500</v>
@@ -12271,7 +12281,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="27" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B99" s="28">
         <v>500</v>
@@ -12294,7 +12304,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="29" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B100" s="30">
         <v>500</v>
@@ -12317,7 +12327,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="27" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B101" s="28">
         <v>550</v>
@@ -12340,7 +12350,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="29" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B102" s="30">
         <v>550</v>
@@ -12363,7 +12373,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="27" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B103" s="28">
         <v>550</v>
@@ -12386,7 +12396,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="29" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B104" s="30">
         <v>550</v>
@@ -12409,7 +12419,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="27" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B105" s="28">
         <v>550</v>
@@ -12432,7 +12442,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="29" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B106" s="30">
         <v>600</v>
@@ -12455,7 +12465,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="27" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B107" s="28">
         <v>600</v>
@@ -12478,7 +12488,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="29" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B108" s="30">
         <v>600</v>
@@ -12501,7 +12511,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="27" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B109" s="28">
         <v>600</v>
@@ -12524,7 +12534,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="29" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B110" s="30">
         <v>600</v>
@@ -12547,7 +12557,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="27" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B111" s="28">
         <v>600</v>
@@ -12570,7 +12580,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="29" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B112" s="30">
         <v>600</v>
@@ -12593,7 +12603,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="27" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B113" s="28">
         <v>600</v>
@@ -12616,7 +12626,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="29" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B114" s="30">
         <v>600</v>
@@ -12639,7 +12649,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="27" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B115" s="28">
         <v>600</v>
@@ -12662,7 +12672,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="29" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B116" s="30">
         <v>600</v>
@@ -12685,7 +12695,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="27" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B117" s="28">
         <v>650</v>
@@ -12708,7 +12718,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="29" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B118" s="30">
         <v>650</v>
@@ -12731,7 +12741,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="27" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B119" s="28">
         <v>650</v>
@@ -12754,7 +12764,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="29" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B120" s="30">
         <v>650</v>
@@ -12777,7 +12787,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="27" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B121" s="28">
         <v>650</v>
@@ -12800,7 +12810,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="29" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B122" s="30">
         <v>650</v>
@@ -12823,7 +12833,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="27" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B123" s="28">
         <v>650</v>
@@ -12846,7 +12856,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="29" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B124" s="30">
         <v>650</v>
@@ -12869,7 +12879,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="27" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B125" s="28">
         <v>650</v>
@@ -12892,7 +12902,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="29" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B126" s="30">
         <v>650</v>
@@ -12915,7 +12925,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="27" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B127" s="28">
         <v>700</v>
@@ -12938,7 +12948,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="29" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B128" s="30">
         <v>700</v>
@@ -12961,7 +12971,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="27" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B129" s="28">
         <v>700</v>
@@ -12984,7 +12994,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="29" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B130" s="30">
         <v>700</v>
@@ -13007,7 +13017,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="27" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B131" s="28">
         <v>700</v>
@@ -13030,7 +13040,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="29" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B132" s="30">
         <v>700</v>
@@ -13053,7 +13063,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="27" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B133" s="28">
         <v>700</v>
@@ -13076,7 +13086,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="29" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B134" s="30">
         <v>700</v>
@@ -13099,7 +13109,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="27" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B135" s="28">
         <v>700</v>
@@ -13122,7 +13132,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="29" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B136" s="30">
         <v>700</v>
@@ -13145,7 +13155,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="27" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B137" s="28">
         <v>750</v>
@@ -13168,7 +13178,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="29" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B138" s="30">
         <v>750</v>
@@ -13191,7 +13201,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="27" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B139" s="28">
         <v>750</v>
@@ -13214,7 +13224,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="29" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B140" s="30">
         <v>750</v>
@@ -13237,7 +13247,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="27" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B141" s="28">
         <v>750</v>
@@ -13260,7 +13270,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="29" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B142" s="30">
         <v>750</v>
@@ -13283,7 +13293,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="27" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B143" s="28">
         <v>750</v>
@@ -13306,7 +13316,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="29" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B144" s="30">
         <v>750</v>
@@ -13329,7 +13339,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="27" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B145" s="28">
         <v>750</v>
@@ -13352,7 +13362,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="29" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B146" s="30">
         <v>800</v>
@@ -13375,7 +13385,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="27" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B147" s="28">
         <v>800</v>
@@ -13398,7 +13408,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="29" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B148" s="30">
         <v>800</v>
@@ -13421,7 +13431,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="27" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B149" s="28">
         <v>800</v>
@@ -13444,7 +13454,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B150" s="30">
         <v>800</v>
@@ -13467,7 +13477,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="27" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B151" s="28">
         <v>800</v>
@@ -13490,7 +13500,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="29" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B152" s="30">
         <v>800</v>
@@ -13513,7 +13523,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="27" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B153" s="28">
         <v>800</v>
@@ -13536,7 +13546,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="29" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B154" s="30">
         <v>800</v>

--- a/plate3d/PLATE3D_COLUMN.xlsx
+++ b/plate3d/PLATE3D_COLUMN.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="449">
   <si>
     <t>COLUMN</t>
   </si>
@@ -711,6 +711,30 @@
   </si>
   <si>
     <t>the beam start: the column face, plus the plate or plates in front of it</t>
+  </si>
+  <si>
+    <t>VIEW</t>
+  </si>
+  <si>
+    <t>ISO</t>
+  </si>
+  <si>
+    <t>COLUMN - ISOMETRIC</t>
+  </si>
+  <si>
+    <t>PLOT</t>
+  </si>
+  <si>
+    <t>PART</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>PLATES</t>
+  </si>
+  <si>
+    <t>SECTIONS</t>
   </si>
   <si>
     <t>END</t>
@@ -3441,13 +3465,13 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T159"/>
+  <dimension ref="A1:T162"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -3457,12 +3481,12 @@
     <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="21" t="s">
         <v>133</v>
       </c>
@@ -3470,12 +3494,13 @@
         <v>134</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>136</v>
       </c>
@@ -3642,7 +3667,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>142</v>
       </c>
@@ -3822,12 +3848,13 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>157</v>
       </c>
@@ -3865,7 +3892,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B20" s="21" t="s">
         <v>144</v>
       </c>
@@ -3895,7 +3922,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B21" s="21" t="s">
         <v>144</v>
       </c>
@@ -3925,7 +3952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B22" s="21" t="s">
         <v>144</v>
       </c>
@@ -3955,7 +3982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B23" s="21" t="s">
         <v>144</v>
       </c>
@@ -3985,7 +4012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B24" s="21" t="s">
         <v>144</v>
       </c>
@@ -4015,7 +4042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B25" s="21" t="s">
         <v>144</v>
       </c>
@@ -4045,7 +4072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B26" s="21" t="s">
         <v>144</v>
       </c>
@@ -4075,12 +4102,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
         <v>168</v>
       </c>
@@ -4122,7 +4150,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B31" s="21" t="s">
         <v>170</v>
       </c>
@@ -4139,7 +4167,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B32" s="21" t="s">
         <v>170</v>
       </c>
@@ -4173,7 +4201,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B33" s="21" t="s">
         <v>170</v>
       </c>
@@ -4190,7 +4218,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B34" s="21" t="s">
         <v>170</v>
       </c>
@@ -4224,7 +4252,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="21" t="s">
         <v>170</v>
       </c>
@@ -4241,7 +4269,8 @@
         <v>139</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>176</v>
       </c>
@@ -4279,7 +4308,7 @@
         <v>YZ</v>
       </c>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B39" s="21" t="s">
         <v>170</v>
       </c>
@@ -4341,7 +4370,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B41" s="21" t="s">
         <v>170</v>
       </c>
@@ -4370,7 +4399,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B42" s="21" t="s">
         <v>170</v>
       </c>
@@ -4399,7 +4428,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B43" s="21" t="s">
         <v>170</v>
       </c>
@@ -4459,7 +4488,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B45" s="21" t="s">
         <v>170</v>
       </c>
@@ -4555,7 +4584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B47" s="21" t="s">
         <v>170</v>
       </c>
@@ -4620,7 +4649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B48" s="21" t="s">
         <v>170</v>
       </c>
@@ -4685,7 +4714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B49" s="21" t="s">
         <v>170</v>
       </c>
@@ -4750,7 +4779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B50" s="21" t="s">
         <v>170</v>
       </c>
@@ -4815,7 +4844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B51" s="21" t="s">
         <v>170</v>
       </c>
@@ -4880,7 +4909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B52" s="21" t="s">
         <v>170</v>
       </c>
@@ -4945,7 +4974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B53" s="21" t="s">
         <v>170</v>
       </c>
@@ -5020,9 +5049,8 @@
       <c r="C54" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="D54" s="22" t="str">
+      <c r="D54" s="22">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
-        <v/>
       </c>
       <c r="E54" s="22"/>
       <c r="F54" s="22">
@@ -5064,16 +5092,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B55" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C55" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="D55" s="22" t="str">
+      <c r="D55" s="22">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
-        <v/>
       </c>
       <c r="E55" s="22"/>
       <c r="F55" s="22">
@@ -5125,9 +5152,8 @@
       <c r="C56" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="D56" s="22" t="str">
+      <c r="D56" s="22">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
-        <v/>
       </c>
       <c r="E56" s="22"/>
       <c r="F56" s="22">
@@ -5169,16 +5195,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B57" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C57" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="D57" s="22" t="str">
+      <c r="D57" s="22">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
-        <v/>
       </c>
       <c r="E57" s="22"/>
       <c r="F57" s="22">
@@ -5288,7 +5313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B59" s="21" t="s">
         <v>170</v>
       </c>
@@ -5353,7 +5378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B60" s="21" t="s">
         <v>170</v>
       </c>
@@ -5370,7 +5395,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B61" s="21" t="s">
         <v>170</v>
       </c>
@@ -5400,7 +5425,7 @@
         <v>YZ</v>
       </c>
     </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B62" s="21" t="s">
         <v>170</v>
       </c>
@@ -5430,7 +5455,7 @@
         <v>YZ</v>
       </c>
     </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B63" s="21" t="s">
         <v>170</v>
       </c>
@@ -5459,7 +5484,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B64" s="21" t="s">
         <v>170</v>
       </c>
@@ -5488,7 +5513,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B65" s="21" t="s">
         <v>170</v>
       </c>
@@ -5517,7 +5542,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B66" s="21" t="s">
         <v>170</v>
       </c>
@@ -5546,7 +5571,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B67" s="21" t="s">
         <v>170</v>
       </c>
@@ -5574,7 +5599,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B68" s="21" t="s">
         <v>170</v>
       </c>
@@ -5602,7 +5627,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B69" s="21" t="s">
         <v>170</v>
       </c>
@@ -5667,7 +5692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B70" s="21" t="s">
         <v>170</v>
       </c>
@@ -5732,7 +5757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B71" s="21" t="s">
         <v>170</v>
       </c>
@@ -5797,7 +5822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B72" s="21" t="s">
         <v>170</v>
       </c>
@@ -5862,7 +5887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B73" s="21" t="s">
         <v>170</v>
       </c>
@@ -5927,7 +5952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B74" s="21" t="s">
         <v>170</v>
       </c>
@@ -5992,7 +6017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B75" s="21" t="s">
         <v>170</v>
       </c>
@@ -6057,7 +6082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B76" s="21" t="s">
         <v>170</v>
       </c>
@@ -6122,16 +6147,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B77" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C77" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="D77" s="22" t="str">
+      <c r="D77" s="22">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
-        <v/>
       </c>
       <c r="E77" s="22"/>
       <c r="F77" s="22">
@@ -6173,16 +6197,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B78" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C78" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="D78" s="22" t="str">
+      <c r="D78" s="22">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
-        <v/>
       </c>
       <c r="E78" s="22"/>
       <c r="F78" s="22">
@@ -6224,16 +6247,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B79" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C79" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="D79" s="22" t="str">
+      <c r="D79" s="22">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
-        <v/>
       </c>
       <c r="E79" s="22"/>
       <c r="F79" s="22">
@@ -6275,16 +6297,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B80" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C80" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="D80" s="22" t="str">
+      <c r="D80" s="22">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
-        <v/>
       </c>
       <c r="E80" s="22"/>
       <c r="F80" s="22">
@@ -6326,7 +6347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B81" s="21" t="s">
         <v>170</v>
       </c>
@@ -6391,7 +6412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B82" s="21" t="s">
         <v>170</v>
       </c>
@@ -6456,7 +6477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B83" s="21" t="s">
         <v>170</v>
       </c>
@@ -6473,12 +6494,13 @@
         <v>139</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
         <v>190</v>
       </c>
@@ -6537,7 +6559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B88" s="21" t="s">
         <v>170</v>
       </c>
@@ -6588,16 +6610,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B89" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C89" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="D89" s="22" t="str">
+      <c r="D89" s="22">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$17&gt;0),"pl.stf3","")</f>
-        <v/>
       </c>
       <c r="E89" s="22" t="s">
         <v>139</v>
@@ -6639,16 +6660,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B90" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C90" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="D90" s="22" t="str">
+      <c r="D90" s="22">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$18&gt;0),"pl.stf4","")</f>
-        <v/>
       </c>
       <c r="E90" s="22" t="s">
         <v>139</v>
@@ -6690,16 +6710,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B91" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C91" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="D91" s="22" t="str">
+      <c r="D91" s="22">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$19&gt;0),"pl.stf5","")</f>
-        <v/>
       </c>
       <c r="E91" s="22" t="s">
         <v>139</v>
@@ -6741,16 +6760,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B92" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C92" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="D92" s="22" t="str">
+      <c r="D92" s="22">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$20&gt;0),"pl.stf6","")</f>
-        <v/>
       </c>
       <c r="E92" s="22" t="s">
         <v>139</v>
@@ -6792,16 +6810,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B93" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C93" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="D93" s="22" t="str">
+      <c r="D93" s="22">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$21&gt;0),"pl.stf7","")</f>
-        <v/>
       </c>
       <c r="E93" s="22" t="s">
         <v>139</v>
@@ -6843,16 +6860,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B94" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C94" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="D94" s="22" t="str">
+      <c r="D94" s="22">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$22&gt;0),"pl.stf8","")</f>
-        <v/>
       </c>
       <c r="E94" s="22" t="s">
         <v>139</v>
@@ -6894,7 +6910,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
         <v>192</v>
       </c>
@@ -7049,7 +7066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B101" s="21" t="s">
         <v>193</v>
       </c>
@@ -7085,7 +7102,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
         <v>198</v>
       </c>
@@ -7143,7 +7161,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B105" s="21" t="s">
         <v>137</v>
       </c>
@@ -7193,7 +7211,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="106" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B106" s="21" t="s">
         <v>137</v>
       </c>
@@ -7243,7 +7261,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="107" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B107" s="21" t="s">
         <v>137</v>
       </c>
@@ -7293,7 +7311,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
         <v>204</v>
       </c>
@@ -7331,7 +7350,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B111" s="21" t="s">
         <v>144</v>
       </c>
@@ -7361,7 +7380,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B112" s="21" t="s">
         <v>144</v>
       </c>
@@ -7391,7 +7410,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B113" s="21" t="s">
         <v>144</v>
       </c>
@@ -7459,7 +7478,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="115" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B115" s="21" t="s">
         <v>152</v>
       </c>
@@ -7494,7 +7513,7 @@
         <v>4.1</v>
       </c>
     </row>
-    <row r="116" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B116" s="21" t="s">
         <v>152</v>
       </c>
@@ -7529,7 +7548,7 @@
         <v>4.1</v>
       </c>
     </row>
-    <row r="117" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B117" s="21" t="s">
         <v>152</v>
       </c>
@@ -7564,12 +7583,14 @@
         <v>4.1</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
         <v>216</v>
       </c>
@@ -7625,9 +7646,8 @@
       <c r="C123" s="22" t="s">
         <v>218</v>
       </c>
-      <c r="D123" s="22" t="str">
+      <c r="D123" s="22">
         <f>IF(AND(PARAM!$J$59&gt;0,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cna","")</f>
-        <v/>
       </c>
       <c r="E123" s="22" t="s">
         <v>139</v>
@@ -7666,9 +7686,8 @@
       <c r="C124" s="22" t="s">
         <v>218</v>
       </c>
-      <c r="D124" s="22" t="str">
+      <c r="D124" s="22">
         <f>IF(AND(PARAM!$J$59&gt;0,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cna","")</f>
-        <v/>
       </c>
       <c r="E124" s="22" t="s">
         <v>139</v>
@@ -7804,7 +7823,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B127" s="21" t="s">
         <v>170</v>
       </c>
@@ -7821,21 +7840,21 @@
         <v>139</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="130" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B130" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C130" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="D130" s="22" t="str">
+      <c r="D130" s="22">
         <f>IF(AND(PARAM!$J$60&gt;0,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cnb","")</f>
-        <v/>
       </c>
       <c r="E130" s="22" t="s">
         <v>139</v>
@@ -7864,16 +7883,15 @@
         <v>180</v>
       </c>
     </row>
-    <row r="131" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B131" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C131" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="D131" s="22" t="str">
+      <c r="D131" s="22">
         <f>IF(AND(PARAM!$J$60&gt;0,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnb","")</f>
-        <v/>
       </c>
       <c r="E131" s="22" t="s">
         <v>139</v>
@@ -7902,7 +7920,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="132" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B132" s="21" t="s">
         <v>170</v>
       </c>
@@ -7940,7 +7958,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="133" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B133" s="21" t="s">
         <v>170</v>
       </c>
@@ -7974,7 +7992,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="134" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B134" s="21" t="s">
         <v>170</v>
       </c>
@@ -8041,7 +8059,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B135" s="21" t="s">
         <v>170</v>
       </c>
@@ -8058,21 +8076,21 @@
         <v>139</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="138" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B138" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C138" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="D138" s="22" t="str">
+      <c r="D138" s="22">
         <f>IF(AND(PARAM!$J$61&gt;0,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cnc","")</f>
-        <v/>
       </c>
       <c r="E138" s="22" t="s">
         <v>139</v>
@@ -8101,16 +8119,15 @@
         <v>180</v>
       </c>
     </row>
-    <row r="139" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B139" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C139" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="D139" s="22" t="str">
+      <c r="D139" s="22">
         <f>IF(AND(PARAM!$J$61&gt;0,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnc","")</f>
-        <v/>
       </c>
       <c r="E139" s="22" t="s">
         <v>139</v>
@@ -8139,7 +8156,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="140" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B140" s="21" t="s">
         <v>170</v>
       </c>
@@ -8177,7 +8194,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="141" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B141" s="21" t="s">
         <v>170</v>
       </c>
@@ -8211,7 +8228,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="142" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B142" s="21" t="s">
         <v>170</v>
       </c>
@@ -8278,7 +8295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B143" s="21" t="s">
         <v>170</v>
       </c>
@@ -8295,21 +8312,21 @@
         <v>139</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="12" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="146" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B146" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C146" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="D146" s="22" t="str">
+      <c r="D146" s="22">
         <f>IF(AND(PARAM!$J$62&gt;0,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cnd","")</f>
-        <v/>
       </c>
       <c r="E146" s="22" t="s">
         <v>139</v>
@@ -8338,16 +8355,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B147" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C147" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="D147" s="22" t="str">
+      <c r="D147" s="22">
         <f>IF(AND(PARAM!$J$62&gt;0,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnd","")</f>
-        <v/>
       </c>
       <c r="E147" s="22" t="s">
         <v>139</v>
@@ -8376,16 +8392,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B148" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C148" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="D148" s="22" t="str">
+      <c r="D148" s="22">
         <f>IF(AND(PARAM!$J$62&gt;0,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cnd","")</f>
-        <v/>
       </c>
       <c r="E148" s="22" t="s">
         <v>139</v>
@@ -8414,16 +8429,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B149" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C149" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="D149" s="22" t="str">
+      <c r="D149" s="22">
         <f>IF(PARAM!$J$62&gt;0,"sc.bmd","")</f>
-        <v/>
       </c>
       <c r="E149" s="22"/>
       <c r="F149" s="22">
@@ -8448,16 +8462,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B150" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C150" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="D150" s="22" t="str">
+      <c r="D150" s="22">
         <f>IF(OR(PARAM!$J$62&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cnd")</f>
-        <v/>
       </c>
       <c r="E150" s="22"/>
       <c r="F150" s="22">
@@ -8515,7 +8528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B151" s="21" t="s">
         <v>170</v>
       </c>
@@ -8532,7 +8545,8 @@
         <v>139</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="12" t="s">
         <v>229</v>
       </c>
@@ -8564,7 +8578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B155" s="21" t="s">
         <v>193</v>
       </c>
@@ -8588,7 +8602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B156" s="21" t="s">
         <v>193</v>
       </c>
@@ -8612,7 +8626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B157" s="21" t="s">
         <v>193</v>
       </c>
@@ -8636,14 +8650,66 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B159" s="21" t="s">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B159" t="s">
         <v>231</v>
+      </c>
+      <c r="C159" t="s">
+        <v>194</v>
+      </c>
+      <c r="D159" t="s">
+        <v>232</v>
+      </c>
+      <c r="G159">
+        <v>50</v>
+      </c>
+      <c r="H159" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B160" t="s">
+        <v>234</v>
+      </c>
+      <c r="C160" t="s">
+        <v>235</v>
+      </c>
+      <c r="D160" t="s">
+        <v>236</v>
+      </c>
+      <c r="E160">
+        <v>10</v>
+      </c>
+      <c r="F160" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="161" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B161" t="s">
+        <v>234</v>
+      </c>
+      <c r="C161" t="s">
+        <v>137</v>
+      </c>
+      <c r="D161" t="s">
+        <v>236</v>
+      </c>
+      <c r="E161">
+        <v>20</v>
+      </c>
+      <c r="F161" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B162" s="21" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -8680,7 +8746,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -8691,7 +8757,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B3" s="28">
         <v>100</v>
@@ -8714,7 +8780,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B4" s="30">
         <v>125</v>
@@ -8737,7 +8803,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B5" s="28">
         <v>150</v>
@@ -8760,7 +8826,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B6" s="30">
         <v>148</v>
@@ -8783,7 +8849,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B7" s="28">
         <v>150</v>
@@ -8806,7 +8872,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="B8" s="30">
         <v>198</v>
@@ -8829,7 +8895,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="B9" s="28">
         <v>200</v>
@@ -8852,7 +8918,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B10" s="30">
         <v>194</v>
@@ -8875,7 +8941,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B11" s="28">
         <v>200</v>
@@ -8898,7 +8964,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B12" s="30">
         <v>200</v>
@@ -8921,7 +8987,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B13" s="28">
         <v>248</v>
@@ -8944,7 +9010,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B14" s="30">
         <v>250</v>
@@ -8967,7 +9033,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B15" s="28">
         <v>244</v>
@@ -8990,7 +9056,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B16" s="30">
         <v>250</v>
@@ -9013,7 +9079,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="B17" s="28">
         <v>250</v>
@@ -9036,7 +9102,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B18" s="30">
         <v>298</v>
@@ -9082,7 +9148,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B20" s="30">
         <v>294</v>
@@ -9105,7 +9171,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B21" s="28">
         <v>294</v>
@@ -9151,7 +9217,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B23" s="28">
         <v>300</v>
@@ -9174,7 +9240,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="B24" s="30">
         <v>346</v>
@@ -9197,7 +9263,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B25" s="28">
         <v>350</v>
@@ -9220,7 +9286,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B26" s="30">
         <v>340</v>
@@ -9243,7 +9309,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="B27" s="28">
         <v>344</v>
@@ -9266,7 +9332,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="B28" s="30">
         <v>350</v>
@@ -9289,7 +9355,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B29" s="28">
         <v>396</v>
@@ -9312,7 +9378,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="B30" s="30">
         <v>400</v>
@@ -9335,7 +9401,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B31" s="28">
         <v>390</v>
@@ -9358,7 +9424,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B32" s="30">
         <v>388</v>
@@ -9381,7 +9447,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="27" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B33" s="28">
         <v>394</v>
@@ -9404,7 +9470,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="B34" s="30">
         <v>400</v>
@@ -9427,7 +9493,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B35" s="28">
         <v>400</v>
@@ -9450,7 +9516,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="B36" s="30">
         <v>414</v>
@@ -9473,7 +9539,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="B37" s="28">
         <v>428</v>
@@ -9496,7 +9562,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="B38" s="30">
         <v>458</v>
@@ -9519,7 +9585,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="B39" s="28">
         <v>498</v>
@@ -9542,7 +9608,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B40" s="30">
         <v>446</v>
@@ -9565,7 +9631,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B41" s="28">
         <v>450</v>
@@ -9588,7 +9654,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B42" s="30">
         <v>440</v>
@@ -9611,7 +9677,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="27" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B43" s="28">
         <v>440</v>
@@ -9634,7 +9700,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B44" s="30">
         <v>496</v>
@@ -9657,7 +9723,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B45" s="28">
         <v>500</v>
@@ -9680,7 +9746,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="B46" s="30">
         <v>482</v>
@@ -9703,7 +9769,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="27" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B47" s="28">
         <v>488</v>
@@ -9726,7 +9792,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="B48" s="30">
         <v>596</v>
@@ -9749,7 +9815,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B49" s="28">
         <v>600</v>
@@ -9772,7 +9838,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B50" s="30">
         <v>582</v>
@@ -9795,7 +9861,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="B51" s="28">
         <v>588</v>
@@ -9818,7 +9884,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="B52" s="30">
         <v>594</v>
@@ -9841,7 +9907,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="27" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B53" s="28">
         <v>692</v>
@@ -9864,7 +9930,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="B54" s="30">
         <v>700</v>
@@ -9887,7 +9953,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B55" s="28">
         <v>792</v>
@@ -9910,7 +9976,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B56" s="30">
         <v>800</v>
@@ -9933,7 +9999,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="27" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="B57" s="28">
         <v>890</v>
@@ -9956,7 +10022,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B58" s="30">
         <v>900</v>
@@ -9979,7 +10045,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="B59" s="28">
         <v>912</v>
@@ -10002,7 +10068,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B60" s="30">
         <v>918</v>
@@ -10025,7 +10091,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -10062,7 +10128,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -10073,7 +10139,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B3" s="28">
         <v>20</v>
@@ -10096,7 +10162,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="B4" s="30">
         <v>20</v>
@@ -10119,7 +10185,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B5" s="28">
         <v>25</v>
@@ -10142,7 +10208,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="B6" s="30">
         <v>25</v>
@@ -10165,7 +10231,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="B7" s="28">
         <v>30</v>
@@ -10188,7 +10254,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="B8" s="30">
         <v>30</v>
@@ -10211,7 +10277,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B9" s="28">
         <v>40</v>
@@ -10234,7 +10300,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="B10" s="30">
         <v>40</v>
@@ -10257,7 +10323,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B11" s="28">
         <v>50</v>
@@ -10280,7 +10346,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B12" s="30">
         <v>50</v>
@@ -10303,7 +10369,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="B13" s="28">
         <v>50</v>
@@ -10326,7 +10392,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="B14" s="30">
         <v>60</v>
@@ -10349,7 +10415,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B15" s="28">
         <v>60</v>
@@ -10372,7 +10438,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B16" s="30">
         <v>60</v>
@@ -10395,7 +10461,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B17" s="28">
         <v>75</v>
@@ -10418,7 +10484,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B18" s="30">
         <v>75</v>
@@ -10441,7 +10507,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B19" s="28">
         <v>75</v>
@@ -10464,7 +10530,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="B20" s="30">
         <v>75</v>
@@ -10487,7 +10553,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="B21" s="28">
         <v>80</v>
@@ -10510,7 +10576,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="B22" s="30">
         <v>80</v>
@@ -10533,7 +10599,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B23" s="28">
         <v>80</v>
@@ -10556,7 +10622,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B24" s="30">
         <v>90</v>
@@ -10579,7 +10645,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B25" s="28">
         <v>90</v>
@@ -10602,7 +10668,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B26" s="30">
         <v>100</v>
@@ -10625,7 +10691,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B27" s="28">
         <v>100</v>
@@ -10648,7 +10714,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B28" s="30">
         <v>100</v>
@@ -10671,7 +10737,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B29" s="28">
         <v>100</v>
@@ -10694,7 +10760,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B30" s="30">
         <v>100</v>
@@ -10717,7 +10783,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B31" s="28">
         <v>100</v>
@@ -10740,7 +10806,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B32" s="30">
         <v>100</v>
@@ -10763,7 +10829,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="27" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B33" s="28">
         <v>125</v>
@@ -10786,7 +10852,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B34" s="30">
         <v>125</v>
@@ -10809,7 +10875,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="B35" s="28">
         <v>125</v>
@@ -10832,7 +10898,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B36" s="30">
         <v>125</v>
@@ -10855,7 +10921,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B37" s="28">
         <v>125</v>
@@ -10878,7 +10944,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B38" s="30">
         <v>125</v>
@@ -10901,7 +10967,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="B39" s="28">
         <v>150</v>
@@ -10924,7 +10990,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B40" s="30">
         <v>150</v>
@@ -10947,7 +11013,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B41" s="28">
         <v>150</v>
@@ -10970,7 +11036,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B42" s="30">
         <v>150</v>
@@ -10993,7 +11059,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="27" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B43" s="28">
         <v>175</v>
@@ -11016,7 +11082,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="B44" s="30">
         <v>175</v>
@@ -11039,7 +11105,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B45" s="28">
         <v>175</v>
@@ -11062,7 +11128,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B46" s="30">
         <v>200</v>
@@ -11085,7 +11151,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="27" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B47" s="28">
         <v>200</v>
@@ -11108,7 +11174,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="B48" s="30">
         <v>200</v>
@@ -11131,7 +11197,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B49" s="28">
         <v>200</v>
@@ -11154,7 +11220,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="B50" s="30">
         <v>200</v>
@@ -11177,7 +11243,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B51" s="28">
         <v>250</v>
@@ -11200,7 +11266,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B52" s="30">
         <v>250</v>
@@ -11223,7 +11289,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="27" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="B53" s="28">
         <v>250</v>
@@ -11246,7 +11312,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B54" s="30">
         <v>250</v>
@@ -11269,7 +11335,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B55" s="28">
         <v>250</v>
@@ -11292,7 +11358,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="B56" s="30">
         <v>300</v>
@@ -11315,7 +11381,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="27" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B57" s="28">
         <v>300</v>
@@ -11338,7 +11404,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="B58" s="30">
         <v>300</v>
@@ -11361,7 +11427,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="B59" s="28">
         <v>300</v>
@@ -11384,7 +11450,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="B60" s="30">
         <v>200</v>
@@ -11407,7 +11473,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="27" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B61" s="28">
         <v>200</v>
@@ -11430,7 +11496,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="29" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="B62" s="30">
         <v>200</v>
@@ -11453,7 +11519,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="27" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B63" s="28">
         <v>200</v>
@@ -11476,7 +11542,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="29" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B64" s="30">
         <v>250</v>
@@ -11499,7 +11565,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="27" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="B65" s="28">
         <v>250</v>
@@ -11522,7 +11588,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="29" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B66" s="30">
         <v>250</v>
@@ -11545,7 +11611,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="27" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B67" s="28">
         <v>250</v>
@@ -11568,7 +11634,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="29" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B68" s="30">
         <v>250</v>
@@ -11591,7 +11657,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="27" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B69" s="28">
         <v>250</v>
@@ -11614,7 +11680,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="29" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B70" s="30">
         <v>300</v>
@@ -11637,7 +11703,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="27" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B71" s="28">
         <v>300</v>
@@ -11660,7 +11726,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="29" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B72" s="30">
         <v>300</v>
@@ -11683,7 +11749,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="27" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="B73" s="28">
         <v>300</v>
@@ -11706,7 +11772,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="29" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="B74" s="30">
         <v>300</v>
@@ -11729,7 +11795,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="27" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="B75" s="28">
         <v>300</v>
@@ -11752,7 +11818,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="29" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="B76" s="30">
         <v>300</v>
@@ -11775,7 +11841,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="27" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B77" s="28">
         <v>350</v>
@@ -11798,7 +11864,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="29" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B78" s="30">
         <v>350</v>
@@ -11821,7 +11887,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="27" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B79" s="28">
         <v>350</v>
@@ -11844,7 +11910,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="29" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B80" s="30">
         <v>350</v>
@@ -11867,7 +11933,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="27" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B81" s="28">
         <v>350</v>
@@ -11890,7 +11956,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="29" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="B82" s="30">
         <v>350</v>
@@ -11913,7 +11979,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="27" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="B83" s="28">
         <v>400</v>
@@ -11936,7 +12002,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="29" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B84" s="30">
         <v>400</v>
@@ -11959,7 +12025,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="27" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="B85" s="28">
         <v>400</v>
@@ -11982,7 +12048,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="29" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="B86" s="30">
         <v>400</v>
@@ -12005,7 +12071,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="27" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="B87" s="28">
         <v>400</v>
@@ -12028,7 +12094,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="29" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B88" s="30">
         <v>400</v>
@@ -12051,7 +12117,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="27" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B89" s="28">
         <v>450</v>
@@ -12074,7 +12140,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="29" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="B90" s="30">
         <v>450</v>
@@ -12097,7 +12163,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="27" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B91" s="28">
         <v>450</v>
@@ -12120,7 +12186,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="29" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="B92" s="30">
         <v>450</v>
@@ -12143,7 +12209,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="27" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="B93" s="28">
         <v>450</v>
@@ -12166,7 +12232,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="29" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="B94" s="30">
         <v>450</v>
@@ -12189,7 +12255,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="27" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="B95" s="28">
         <v>500</v>
@@ -12212,7 +12278,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="29" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B96" s="30">
         <v>500</v>
@@ -12235,7 +12301,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="27" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="B97" s="28">
         <v>500</v>
@@ -12258,7 +12324,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="29" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B98" s="30">
         <v>500</v>
@@ -12281,7 +12347,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="27" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="B99" s="28">
         <v>500</v>
@@ -12304,7 +12370,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="29" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B100" s="30">
         <v>500</v>
@@ -12327,7 +12393,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="27" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="B101" s="28">
         <v>550</v>
@@ -12350,7 +12416,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="29" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="B102" s="30">
         <v>550</v>
@@ -12373,7 +12439,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="27" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="B103" s="28">
         <v>550</v>
@@ -12396,7 +12462,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="29" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B104" s="30">
         <v>550</v>
@@ -12419,7 +12485,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="27" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B105" s="28">
         <v>550</v>
@@ -12442,7 +12508,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="29" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="B106" s="30">
         <v>600</v>
@@ -12465,7 +12531,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="27" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="B107" s="28">
         <v>600</v>
@@ -12488,7 +12554,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="29" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="B108" s="30">
         <v>600</v>
@@ -12511,7 +12577,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="27" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="B109" s="28">
         <v>600</v>
@@ -12534,7 +12600,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="29" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="B110" s="30">
         <v>600</v>
@@ -12557,7 +12623,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="27" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="B111" s="28">
         <v>600</v>
@@ -12580,7 +12646,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="29" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="B112" s="30">
         <v>600</v>
@@ -12603,7 +12669,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="27" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="B113" s="28">
         <v>600</v>
@@ -12626,7 +12692,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="29" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="B114" s="30">
         <v>600</v>
@@ -12649,7 +12715,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="27" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="B115" s="28">
         <v>600</v>
@@ -12672,7 +12738,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="29" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="B116" s="30">
         <v>600</v>
@@ -12695,7 +12761,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="27" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B117" s="28">
         <v>650</v>
@@ -12718,7 +12784,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="29" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="B118" s="30">
         <v>650</v>
@@ -12741,7 +12807,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="27" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="B119" s="28">
         <v>650</v>
@@ -12764,7 +12830,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="29" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="B120" s="30">
         <v>650</v>
@@ -12787,7 +12853,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="27" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="B121" s="28">
         <v>650</v>
@@ -12810,7 +12876,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="29" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B122" s="30">
         <v>650</v>
@@ -12833,7 +12899,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="27" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="B123" s="28">
         <v>650</v>
@@ -12856,7 +12922,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="29" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="B124" s="30">
         <v>650</v>
@@ -12879,7 +12945,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="27" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="B125" s="28">
         <v>650</v>
@@ -12902,7 +12968,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="29" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="B126" s="30">
         <v>650</v>
@@ -12925,7 +12991,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="27" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="B127" s="28">
         <v>700</v>
@@ -12948,7 +13014,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="29" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="B128" s="30">
         <v>700</v>
@@ -12971,7 +13037,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="27" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="B129" s="28">
         <v>700</v>
@@ -12994,7 +13060,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="29" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="B130" s="30">
         <v>700</v>
@@ -13017,7 +13083,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="27" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="B131" s="28">
         <v>700</v>
@@ -13040,7 +13106,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="29" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="B132" s="30">
         <v>700</v>
@@ -13063,7 +13129,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="27" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="B133" s="28">
         <v>700</v>
@@ -13086,7 +13152,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="29" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="B134" s="30">
         <v>700</v>
@@ -13109,7 +13175,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="27" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="B135" s="28">
         <v>700</v>
@@ -13132,7 +13198,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="29" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="B136" s="30">
         <v>700</v>
@@ -13155,7 +13221,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="27" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="B137" s="28">
         <v>750</v>
@@ -13178,7 +13244,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="29" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="B138" s="30">
         <v>750</v>
@@ -13201,7 +13267,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="27" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="B139" s="28">
         <v>750</v>
@@ -13224,7 +13290,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="29" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="B140" s="30">
         <v>750</v>
@@ -13247,7 +13313,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="27" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="B141" s="28">
         <v>750</v>
@@ -13270,7 +13336,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="29" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="B142" s="30">
         <v>750</v>
@@ -13293,7 +13359,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="27" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="B143" s="28">
         <v>750</v>
@@ -13316,7 +13382,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="29" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="B144" s="30">
         <v>750</v>
@@ -13339,7 +13405,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="27" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="B145" s="28">
         <v>750</v>
@@ -13362,7 +13428,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="29" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="B146" s="30">
         <v>800</v>
@@ -13385,7 +13451,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="27" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="B147" s="28">
         <v>800</v>
@@ -13408,7 +13474,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="29" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="B148" s="30">
         <v>800</v>
@@ -13431,7 +13497,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="27" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="B149" s="28">
         <v>800</v>
@@ -13454,7 +13520,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="29" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="B150" s="30">
         <v>800</v>
@@ -13477,7 +13543,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="27" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="B151" s="28">
         <v>800</v>
@@ -13500,7 +13566,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="29" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="B152" s="30">
         <v>800</v>
@@ -13523,7 +13589,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="27" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="B153" s="28">
         <v>800</v>
@@ -13546,7 +13612,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="29" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B154" s="30">
         <v>800</v>
@@ -13569,6 +13635,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/plate3d/PLATE3D_COLUMN.xlsx
+++ b/plate3d/PLATE3D_COLUMN.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="441">
   <si>
     <t>COLUMN</t>
   </si>
@@ -711,30 +711,6 @@
   </si>
   <si>
     <t>the beam start: the column face, plus the plate or plates in front of it</t>
-  </si>
-  <si>
-    <t>VIEW</t>
-  </si>
-  <si>
-    <t>ISO</t>
-  </si>
-  <si>
-    <t>COLUMN - ISOMETRIC</t>
-  </si>
-  <si>
-    <t>PLOT</t>
-  </si>
-  <si>
-    <t>PART</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>PLATES</t>
-  </si>
-  <si>
-    <t>SECTIONS</t>
   </si>
   <si>
     <t>END</t>
@@ -3465,13 +3441,13 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T162"/>
+  <dimension ref="A1:T159"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -3481,12 +3457,12 @@
     <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="21" t="s">
         <v>133</v>
       </c>
@@ -3494,13 +3470,12 @@
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>136</v>
       </c>
@@ -3667,8 +3642,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>142</v>
       </c>
@@ -3848,13 +3822,12 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>157</v>
       </c>
@@ -3892,7 +3865,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="21" t="s">
         <v>144</v>
       </c>
@@ -3922,7 +3895,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="21" t="s">
         <v>144</v>
       </c>
@@ -3952,7 +3925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="21" t="s">
         <v>144</v>
       </c>
@@ -3982,7 +3955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="21" t="s">
         <v>144</v>
       </c>
@@ -4012,7 +3985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="21" t="s">
         <v>144</v>
       </c>
@@ -4042,7 +4015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="21" t="s">
         <v>144</v>
       </c>
@@ -4072,7 +4045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="21" t="s">
         <v>144</v>
       </c>
@@ -4102,13 +4075,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
         <v>168</v>
       </c>
@@ -4150,7 +4122,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="21" t="s">
         <v>170</v>
       </c>
@@ -4167,7 +4139,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="21" t="s">
         <v>170</v>
       </c>
@@ -4201,7 +4173,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="21" t="s">
         <v>170</v>
       </c>
@@ -4218,7 +4190,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="21" t="s">
         <v>170</v>
       </c>
@@ -4252,7 +4224,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="21" t="s">
         <v>170</v>
       </c>
@@ -4269,8 +4241,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>176</v>
       </c>
@@ -4308,7 +4279,7 @@
         <v>YZ</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="21" t="s">
         <v>170</v>
       </c>
@@ -4370,7 +4341,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B41" s="21" t="s">
         <v>170</v>
       </c>
@@ -4399,7 +4370,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" s="21" t="s">
         <v>170</v>
       </c>
@@ -4428,7 +4399,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" s="21" t="s">
         <v>170</v>
       </c>
@@ -4488,7 +4459,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B45" s="21" t="s">
         <v>170</v>
       </c>
@@ -4584,7 +4555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B47" s="21" t="s">
         <v>170</v>
       </c>
@@ -4649,7 +4620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B48" s="21" t="s">
         <v>170</v>
       </c>
@@ -4714,7 +4685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B49" s="21" t="s">
         <v>170</v>
       </c>
@@ -4779,7 +4750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B50" s="21" t="s">
         <v>170</v>
       </c>
@@ -4844,7 +4815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B51" s="21" t="s">
         <v>170</v>
       </c>
@@ -4909,7 +4880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B52" s="21" t="s">
         <v>170</v>
       </c>
@@ -4974,7 +4945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B53" s="21" t="s">
         <v>170</v>
       </c>
@@ -5049,8 +5020,9 @@
       <c r="C54" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="D54" s="22">
+      <c r="D54" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
+        <v/>
       </c>
       <c r="E54" s="22"/>
       <c r="F54" s="22">
@@ -5092,15 +5064,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B55" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C55" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="D55" s="22">
+      <c r="D55" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
+        <v/>
       </c>
       <c r="E55" s="22"/>
       <c r="F55" s="22">
@@ -5152,8 +5125,9 @@
       <c r="C56" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="D56" s="22">
+      <c r="D56" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
+        <v/>
       </c>
       <c r="E56" s="22"/>
       <c r="F56" s="22">
@@ -5195,15 +5169,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B57" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C57" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="D57" s="22">
+      <c r="D57" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
+        <v/>
       </c>
       <c r="E57" s="22"/>
       <c r="F57" s="22">
@@ -5313,7 +5288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B59" s="21" t="s">
         <v>170</v>
       </c>
@@ -5378,7 +5353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B60" s="21" t="s">
         <v>170</v>
       </c>
@@ -5395,7 +5370,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B61" s="21" t="s">
         <v>170</v>
       </c>
@@ -5425,7 +5400,7 @@
         <v>YZ</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B62" s="21" t="s">
         <v>170</v>
       </c>
@@ -5455,7 +5430,7 @@
         <v>YZ</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B63" s="21" t="s">
         <v>170</v>
       </c>
@@ -5484,7 +5459,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B64" s="21" t="s">
         <v>170</v>
       </c>
@@ -5513,7 +5488,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B65" s="21" t="s">
         <v>170</v>
       </c>
@@ -5542,7 +5517,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B66" s="21" t="s">
         <v>170</v>
       </c>
@@ -5571,7 +5546,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B67" s="21" t="s">
         <v>170</v>
       </c>
@@ -5599,7 +5574,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B68" s="21" t="s">
         <v>170</v>
       </c>
@@ -5627,7 +5602,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B69" s="21" t="s">
         <v>170</v>
       </c>
@@ -5692,7 +5667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B70" s="21" t="s">
         <v>170</v>
       </c>
@@ -5757,7 +5732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B71" s="21" t="s">
         <v>170</v>
       </c>
@@ -5822,7 +5797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B72" s="21" t="s">
         <v>170</v>
       </c>
@@ -5887,7 +5862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B73" s="21" t="s">
         <v>170</v>
       </c>
@@ -5952,7 +5927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B74" s="21" t="s">
         <v>170</v>
       </c>
@@ -6017,7 +5992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B75" s="21" t="s">
         <v>170</v>
       </c>
@@ -6082,7 +6057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B76" s="21" t="s">
         <v>170</v>
       </c>
@@ -6147,15 +6122,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B77" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C77" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="D77" s="22">
+      <c r="D77" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
+        <v/>
       </c>
       <c r="E77" s="22"/>
       <c r="F77" s="22">
@@ -6197,15 +6173,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B78" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C78" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="D78" s="22">
+      <c r="D78" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
+        <v/>
       </c>
       <c r="E78" s="22"/>
       <c r="F78" s="22">
@@ -6247,15 +6224,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B79" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C79" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="D79" s="22">
+      <c r="D79" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
+        <v/>
       </c>
       <c r="E79" s="22"/>
       <c r="F79" s="22">
@@ -6297,15 +6275,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B80" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C80" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="D80" s="22">
+      <c r="D80" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
+        <v/>
       </c>
       <c r="E80" s="22"/>
       <c r="F80" s="22">
@@ -6347,7 +6326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B81" s="21" t="s">
         <v>170</v>
       </c>
@@ -6412,7 +6391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B82" s="21" t="s">
         <v>170</v>
       </c>
@@ -6477,7 +6456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B83" s="21" t="s">
         <v>170</v>
       </c>
@@ -6494,13 +6473,12 @@
         <v>139</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
         <v>190</v>
       </c>
@@ -6559,7 +6537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B88" s="21" t="s">
         <v>170</v>
       </c>
@@ -6610,15 +6588,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B89" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C89" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="D89" s="22">
+      <c r="D89" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$17&gt;0),"pl.stf3","")</f>
+        <v/>
       </c>
       <c r="E89" s="22" t="s">
         <v>139</v>
@@ -6660,15 +6639,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B90" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C90" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="D90" s="22">
+      <c r="D90" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$18&gt;0),"pl.stf4","")</f>
+        <v/>
       </c>
       <c r="E90" s="22" t="s">
         <v>139</v>
@@ -6710,15 +6690,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B91" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C91" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="D91" s="22">
+      <c r="D91" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$19&gt;0),"pl.stf5","")</f>
+        <v/>
       </c>
       <c r="E91" s="22" t="s">
         <v>139</v>
@@ -6760,15 +6741,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B92" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C92" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="D92" s="22">
+      <c r="D92" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$20&gt;0),"pl.stf6","")</f>
+        <v/>
       </c>
       <c r="E92" s="22" t="s">
         <v>139</v>
@@ -6810,15 +6792,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B93" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C93" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="D93" s="22">
+      <c r="D93" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$21&gt;0),"pl.stf7","")</f>
+        <v/>
       </c>
       <c r="E93" s="22" t="s">
         <v>139</v>
@@ -6860,15 +6843,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B94" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C94" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="D94" s="22">
+      <c r="D94" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$22&gt;0),"pl.stf8","")</f>
+        <v/>
       </c>
       <c r="E94" s="22" t="s">
         <v>139</v>
@@ -6910,8 +6894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
         <v>192</v>
       </c>
@@ -7066,7 +7049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" s="21" t="s">
         <v>193</v>
       </c>
@@ -7102,8 +7085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
         <v>198</v>
       </c>
@@ -7161,7 +7143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B105" s="21" t="s">
         <v>137</v>
       </c>
@@ -7211,7 +7193,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B106" s="21" t="s">
         <v>137</v>
       </c>
@@ -7261,7 +7243,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B107" s="21" t="s">
         <v>137</v>
       </c>
@@ -7311,8 +7293,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
         <v>204</v>
       </c>
@@ -7350,7 +7331,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B111" s="21" t="s">
         <v>144</v>
       </c>
@@ -7380,7 +7361,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B112" s="21" t="s">
         <v>144</v>
       </c>
@@ -7410,7 +7391,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B113" s="21" t="s">
         <v>144</v>
       </c>
@@ -7478,7 +7459,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B115" s="21" t="s">
         <v>152</v>
       </c>
@@ -7513,7 +7494,7 @@
         <v>4.1</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B116" s="21" t="s">
         <v>152</v>
       </c>
@@ -7548,7 +7529,7 @@
         <v>4.1</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B117" s="21" t="s">
         <v>152</v>
       </c>
@@ -7583,14 +7564,12 @@
         <v>4.1</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
         <v>216</v>
       </c>
@@ -7646,8 +7625,9 @@
       <c r="C123" s="22" t="s">
         <v>218</v>
       </c>
-      <c r="D123" s="22">
+      <c r="D123" s="22" t="str">
         <f>IF(AND(PARAM!$J$59&gt;0,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cna","")</f>
+        <v/>
       </c>
       <c r="E123" s="22" t="s">
         <v>139</v>
@@ -7686,8 +7666,9 @@
       <c r="C124" s="22" t="s">
         <v>218</v>
       </c>
-      <c r="D124" s="22">
+      <c r="D124" s="22" t="str">
         <f>IF(AND(PARAM!$J$59&gt;0,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cna","")</f>
+        <v/>
       </c>
       <c r="E124" s="22" t="s">
         <v>139</v>
@@ -7823,7 +7804,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B127" s="21" t="s">
         <v>170</v>
       </c>
@@ -7840,21 +7821,21 @@
         <v>139</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B130" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C130" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="D130" s="22">
+      <c r="D130" s="22" t="str">
         <f>IF(AND(PARAM!$J$60&gt;0,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cnb","")</f>
+        <v/>
       </c>
       <c r="E130" s="22" t="s">
         <v>139</v>
@@ -7883,15 +7864,16 @@
         <v>180</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B131" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C131" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="D131" s="22">
+      <c r="D131" s="22" t="str">
         <f>IF(AND(PARAM!$J$60&gt;0,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnb","")</f>
+        <v/>
       </c>
       <c r="E131" s="22" t="s">
         <v>139</v>
@@ -7920,7 +7902,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B132" s="21" t="s">
         <v>170</v>
       </c>
@@ -7958,7 +7940,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B133" s="21" t="s">
         <v>170</v>
       </c>
@@ -7992,7 +7974,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B134" s="21" t="s">
         <v>170</v>
       </c>
@@ -8059,7 +8041,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B135" s="21" t="s">
         <v>170</v>
       </c>
@@ -8076,21 +8058,21 @@
         <v>139</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B138" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C138" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="D138" s="22">
+      <c r="D138" s="22" t="str">
         <f>IF(AND(PARAM!$J$61&gt;0,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cnc","")</f>
+        <v/>
       </c>
       <c r="E138" s="22" t="s">
         <v>139</v>
@@ -8119,15 +8101,16 @@
         <v>180</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B139" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C139" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="D139" s="22">
+      <c r="D139" s="22" t="str">
         <f>IF(AND(PARAM!$J$61&gt;0,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnc","")</f>
+        <v/>
       </c>
       <c r="E139" s="22" t="s">
         <v>139</v>
@@ -8156,7 +8139,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B140" s="21" t="s">
         <v>170</v>
       </c>
@@ -8194,7 +8177,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B141" s="21" t="s">
         <v>170</v>
       </c>
@@ -8228,7 +8211,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B142" s="21" t="s">
         <v>170</v>
       </c>
@@ -8295,7 +8278,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B143" s="21" t="s">
         <v>170</v>
       </c>
@@ -8312,21 +8295,21 @@
         <v>139</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="12" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B146" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C146" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="D146" s="22">
+      <c r="D146" s="22" t="str">
         <f>IF(AND(PARAM!$J$62&gt;0,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cnd","")</f>
+        <v/>
       </c>
       <c r="E146" s="22" t="s">
         <v>139</v>
@@ -8355,15 +8338,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B147" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C147" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="D147" s="22">
+      <c r="D147" s="22" t="str">
         <f>IF(AND(PARAM!$J$62&gt;0,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnd","")</f>
+        <v/>
       </c>
       <c r="E147" s="22" t="s">
         <v>139</v>
@@ -8392,15 +8376,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B148" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C148" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="D148" s="22">
+      <c r="D148" s="22" t="str">
         <f>IF(AND(PARAM!$J$62&gt;0,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cnd","")</f>
+        <v/>
       </c>
       <c r="E148" s="22" t="s">
         <v>139</v>
@@ -8429,15 +8414,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B149" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C149" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="D149" s="22">
+      <c r="D149" s="22" t="str">
         <f>IF(PARAM!$J$62&gt;0,"sc.bmd","")</f>
+        <v/>
       </c>
       <c r="E149" s="22"/>
       <c r="F149" s="22">
@@ -8462,15 +8448,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B150" s="21" t="s">
         <v>170</v>
       </c>
       <c r="C150" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="D150" s="22">
+      <c r="D150" s="22" t="str">
         <f>IF(OR(PARAM!$J$62&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cnd")</f>
+        <v/>
       </c>
       <c r="E150" s="22"/>
       <c r="F150" s="22">
@@ -8528,7 +8515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B151" s="21" t="s">
         <v>170</v>
       </c>
@@ -8545,8 +8532,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="12" t="s">
         <v>229</v>
       </c>
@@ -8578,7 +8564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B155" s="21" t="s">
         <v>193</v>
       </c>
@@ -8602,7 +8588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B156" s="21" t="s">
         <v>193</v>
       </c>
@@ -8626,7 +8612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B157" s="21" t="s">
         <v>193</v>
       </c>
@@ -8650,66 +8636,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B159" t="s">
+    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B159" s="21" t="s">
         <v>231</v>
-      </c>
-      <c r="C159" t="s">
-        <v>194</v>
-      </c>
-      <c r="D159" t="s">
-        <v>232</v>
-      </c>
-      <c r="G159">
-        <v>50</v>
-      </c>
-      <c r="H159" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="160" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B160" t="s">
-        <v>234</v>
-      </c>
-      <c r="C160" t="s">
-        <v>235</v>
-      </c>
-      <c r="D160" t="s">
-        <v>236</v>
-      </c>
-      <c r="E160">
-        <v>10</v>
-      </c>
-      <c r="F160" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B161" t="s">
-        <v>234</v>
-      </c>
-      <c r="C161" t="s">
-        <v>137</v>
-      </c>
-      <c r="D161" t="s">
-        <v>236</v>
-      </c>
-      <c r="E161">
-        <v>20</v>
-      </c>
-      <c r="F161" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B162" s="21" t="s">
-        <v>239</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -8746,7 +8680,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -8757,7 +8691,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B3" s="28">
         <v>100</v>
@@ -8780,7 +8714,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="B4" s="30">
         <v>125</v>
@@ -8803,7 +8737,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="B5" s="28">
         <v>150</v>
@@ -8826,7 +8760,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="B6" s="30">
         <v>148</v>
@@ -8849,7 +8783,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="B7" s="28">
         <v>150</v>
@@ -8872,7 +8806,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B8" s="30">
         <v>198</v>
@@ -8895,7 +8829,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="B9" s="28">
         <v>200</v>
@@ -8918,7 +8852,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B10" s="30">
         <v>194</v>
@@ -8941,7 +8875,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="B11" s="28">
         <v>200</v>
@@ -8964,7 +8898,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B12" s="30">
         <v>200</v>
@@ -8987,7 +8921,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B13" s="28">
         <v>248</v>
@@ -9010,7 +8944,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="B14" s="30">
         <v>250</v>
@@ -9033,7 +8967,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="B15" s="28">
         <v>244</v>
@@ -9056,7 +8990,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B16" s="30">
         <v>250</v>
@@ -9079,7 +9013,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B17" s="28">
         <v>250</v>
@@ -9102,7 +9036,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B18" s="30">
         <v>298</v>
@@ -9148,7 +9082,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="B20" s="30">
         <v>294</v>
@@ -9171,7 +9105,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="B21" s="28">
         <v>294</v>
@@ -9217,7 +9151,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B23" s="28">
         <v>300</v>
@@ -9240,7 +9174,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="B24" s="30">
         <v>346</v>
@@ -9263,7 +9197,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B25" s="28">
         <v>350</v>
@@ -9286,7 +9220,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B26" s="30">
         <v>340</v>
@@ -9309,7 +9243,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="B27" s="28">
         <v>344</v>
@@ -9332,7 +9266,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B28" s="30">
         <v>350</v>
@@ -9355,7 +9289,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="B29" s="28">
         <v>396</v>
@@ -9378,7 +9312,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="B30" s="30">
         <v>400</v>
@@ -9401,7 +9335,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B31" s="28">
         <v>390</v>
@@ -9424,7 +9358,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="B32" s="30">
         <v>388</v>
@@ -9447,7 +9381,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="27" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B33" s="28">
         <v>394</v>
@@ -9470,7 +9404,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="B34" s="30">
         <v>400</v>
@@ -9493,7 +9427,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="B35" s="28">
         <v>400</v>
@@ -9516,7 +9450,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B36" s="30">
         <v>414</v>
@@ -9539,7 +9473,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="B37" s="28">
         <v>428</v>
@@ -9562,7 +9496,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="B38" s="30">
         <v>458</v>
@@ -9585,7 +9519,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="B39" s="28">
         <v>498</v>
@@ -9608,7 +9542,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B40" s="30">
         <v>446</v>
@@ -9631,7 +9565,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="B41" s="28">
         <v>450</v>
@@ -9654,7 +9588,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="B42" s="30">
         <v>440</v>
@@ -9677,7 +9611,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="27" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B43" s="28">
         <v>440</v>
@@ -9700,7 +9634,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B44" s="30">
         <v>496</v>
@@ -9723,7 +9657,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="B45" s="28">
         <v>500</v>
@@ -9746,7 +9680,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="B46" s="30">
         <v>482</v>
@@ -9769,7 +9703,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="27" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B47" s="28">
         <v>488</v>
@@ -9792,7 +9726,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="B48" s="30">
         <v>596</v>
@@ -9815,7 +9749,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="B49" s="28">
         <v>600</v>
@@ -9838,7 +9772,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="B50" s="30">
         <v>582</v>
@@ -9861,7 +9795,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="B51" s="28">
         <v>588</v>
@@ -9884,7 +9818,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="B52" s="30">
         <v>594</v>
@@ -9907,7 +9841,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="27" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B53" s="28">
         <v>692</v>
@@ -9930,7 +9864,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="B54" s="30">
         <v>700</v>
@@ -9953,7 +9887,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="B55" s="28">
         <v>792</v>
@@ -9976,7 +9910,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="B56" s="30">
         <v>800</v>
@@ -9999,7 +9933,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="27" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B57" s="28">
         <v>890</v>
@@ -10022,7 +9956,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="B58" s="30">
         <v>900</v>
@@ -10045,7 +9979,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="B59" s="28">
         <v>912</v>
@@ -10068,7 +10002,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="B60" s="30">
         <v>918</v>
@@ -10091,7 +10025,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -10128,7 +10062,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -10139,7 +10073,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B3" s="28">
         <v>20</v>
@@ -10162,7 +10096,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="B4" s="30">
         <v>20</v>
@@ -10185,7 +10119,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="B5" s="28">
         <v>25</v>
@@ -10208,7 +10142,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="B6" s="30">
         <v>25</v>
@@ -10231,7 +10165,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B7" s="28">
         <v>30</v>
@@ -10254,7 +10188,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="B8" s="30">
         <v>30</v>
@@ -10277,7 +10211,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="B9" s="28">
         <v>40</v>
@@ -10300,7 +10234,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="B10" s="30">
         <v>40</v>
@@ -10323,7 +10257,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="B11" s="28">
         <v>50</v>
@@ -10346,7 +10280,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B12" s="30">
         <v>50</v>
@@ -10369,7 +10303,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="B13" s="28">
         <v>50</v>
@@ -10392,7 +10326,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="B14" s="30">
         <v>60</v>
@@ -10415,7 +10349,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B15" s="28">
         <v>60</v>
@@ -10438,7 +10372,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="B16" s="30">
         <v>60</v>
@@ -10461,7 +10395,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="B17" s="28">
         <v>75</v>
@@ -10484,7 +10418,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="B18" s="30">
         <v>75</v>
@@ -10507,7 +10441,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="B19" s="28">
         <v>75</v>
@@ -10530,7 +10464,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B20" s="30">
         <v>75</v>
@@ -10553,7 +10487,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="B21" s="28">
         <v>80</v>
@@ -10576,7 +10510,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="B22" s="30">
         <v>80</v>
@@ -10599,7 +10533,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B23" s="28">
         <v>80</v>
@@ -10622,7 +10556,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B24" s="30">
         <v>90</v>
@@ -10645,7 +10579,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="B25" s="28">
         <v>90</v>
@@ -10668,7 +10602,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="B26" s="30">
         <v>100</v>
@@ -10691,7 +10625,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="B27" s="28">
         <v>100</v>
@@ -10714,7 +10648,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="B28" s="30">
         <v>100</v>
@@ -10737,7 +10671,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="B29" s="28">
         <v>100</v>
@@ -10760,7 +10694,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B30" s="30">
         <v>100</v>
@@ -10783,7 +10717,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="B31" s="28">
         <v>100</v>
@@ -10806,7 +10740,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="B32" s="30">
         <v>100</v>
@@ -10829,7 +10763,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="27" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="B33" s="28">
         <v>125</v>
@@ -10852,7 +10786,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B34" s="30">
         <v>125</v>
@@ -10875,7 +10809,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="B35" s="28">
         <v>125</v>
@@ -10898,7 +10832,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="B36" s="30">
         <v>125</v>
@@ -10921,7 +10855,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B37" s="28">
         <v>125</v>
@@ -10944,7 +10878,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="B38" s="30">
         <v>125</v>
@@ -10967,7 +10901,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="B39" s="28">
         <v>150</v>
@@ -10990,7 +10924,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="B40" s="30">
         <v>150</v>
@@ -11013,7 +10947,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="B41" s="28">
         <v>150</v>
@@ -11036,7 +10970,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B42" s="30">
         <v>150</v>
@@ -11059,7 +10993,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="27" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="B43" s="28">
         <v>175</v>
@@ -11082,7 +11016,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="B44" s="30">
         <v>175</v>
@@ -11105,7 +11039,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="B45" s="28">
         <v>175</v>
@@ -11128,7 +11062,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="B46" s="30">
         <v>200</v>
@@ -11151,7 +11085,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="27" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B47" s="28">
         <v>200</v>
@@ -11174,7 +11108,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B48" s="30">
         <v>200</v>
@@ -11197,7 +11131,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B49" s="28">
         <v>200</v>
@@ -11220,7 +11154,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="B50" s="30">
         <v>200</v>
@@ -11243,7 +11177,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="B51" s="28">
         <v>250</v>
@@ -11266,7 +11200,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B52" s="30">
         <v>250</v>
@@ -11289,7 +11223,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="27" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="B53" s="28">
         <v>250</v>
@@ -11312,7 +11246,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="B54" s="30">
         <v>250</v>
@@ -11335,7 +11269,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="B55" s="28">
         <v>250</v>
@@ -11358,7 +11292,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="B56" s="30">
         <v>300</v>
@@ -11381,7 +11315,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="27" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B57" s="28">
         <v>300</v>
@@ -11404,7 +11338,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="B58" s="30">
         <v>300</v>
@@ -11427,7 +11361,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="B59" s="28">
         <v>300</v>
@@ -11450,7 +11384,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="B60" s="30">
         <v>200</v>
@@ -11473,7 +11407,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="27" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="B61" s="28">
         <v>200</v>
@@ -11496,7 +11430,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="29" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B62" s="30">
         <v>200</v>
@@ -11519,7 +11453,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="27" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="B63" s="28">
         <v>200</v>
@@ -11542,7 +11476,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="29" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="B64" s="30">
         <v>250</v>
@@ -11565,7 +11499,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="27" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="B65" s="28">
         <v>250</v>
@@ -11588,7 +11522,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="29" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="B66" s="30">
         <v>250</v>
@@ -11611,7 +11545,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="27" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="B67" s="28">
         <v>250</v>
@@ -11634,7 +11568,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="29" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B68" s="30">
         <v>250</v>
@@ -11657,7 +11591,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="27" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="B69" s="28">
         <v>250</v>
@@ -11680,7 +11614,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="29" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B70" s="30">
         <v>300</v>
@@ -11703,7 +11637,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="27" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B71" s="28">
         <v>300</v>
@@ -11726,7 +11660,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="29" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="B72" s="30">
         <v>300</v>
@@ -11749,7 +11683,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="27" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B73" s="28">
         <v>300</v>
@@ -11772,7 +11706,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="29" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B74" s="30">
         <v>300</v>
@@ -11795,7 +11729,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="27" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="B75" s="28">
         <v>300</v>
@@ -11818,7 +11752,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="29" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="B76" s="30">
         <v>300</v>
@@ -11841,7 +11775,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="27" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="B77" s="28">
         <v>350</v>
@@ -11864,7 +11798,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="29" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B78" s="30">
         <v>350</v>
@@ -11887,7 +11821,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="27" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="B79" s="28">
         <v>350</v>
@@ -11910,7 +11844,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="29" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B80" s="30">
         <v>350</v>
@@ -11933,7 +11867,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="27" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="B81" s="28">
         <v>350</v>
@@ -11956,7 +11890,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="29" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="B82" s="30">
         <v>350</v>
@@ -11979,7 +11913,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="27" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="B83" s="28">
         <v>400</v>
@@ -12002,7 +11936,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="29" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B84" s="30">
         <v>400</v>
@@ -12025,7 +11959,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="27" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="B85" s="28">
         <v>400</v>
@@ -12048,7 +11982,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="29" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B86" s="30">
         <v>400</v>
@@ -12071,7 +12005,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="27" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="B87" s="28">
         <v>400</v>
@@ -12094,7 +12028,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="29" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B88" s="30">
         <v>400</v>
@@ -12117,7 +12051,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="27" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="B89" s="28">
         <v>450</v>
@@ -12140,7 +12074,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="29" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="B90" s="30">
         <v>450</v>
@@ -12163,7 +12097,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="27" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="B91" s="28">
         <v>450</v>
@@ -12186,7 +12120,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="29" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="B92" s="30">
         <v>450</v>
@@ -12209,7 +12143,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="27" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="B93" s="28">
         <v>450</v>
@@ -12232,7 +12166,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="29" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="B94" s="30">
         <v>450</v>
@@ -12255,7 +12189,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="27" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="B95" s="28">
         <v>500</v>
@@ -12278,7 +12212,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="29" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="B96" s="30">
         <v>500</v>
@@ -12301,7 +12235,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="27" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="B97" s="28">
         <v>500</v>
@@ -12324,7 +12258,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="29" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B98" s="30">
         <v>500</v>
@@ -12347,7 +12281,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="27" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="B99" s="28">
         <v>500</v>
@@ -12370,7 +12304,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="29" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="B100" s="30">
         <v>500</v>
@@ -12393,7 +12327,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="27" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="B101" s="28">
         <v>550</v>
@@ -12416,7 +12350,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="29" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="B102" s="30">
         <v>550</v>
@@ -12439,7 +12373,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="27" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="B103" s="28">
         <v>550</v>
@@ -12462,7 +12396,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="29" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="B104" s="30">
         <v>550</v>
@@ -12485,7 +12419,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="27" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="B105" s="28">
         <v>550</v>
@@ -12508,7 +12442,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="29" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="B106" s="30">
         <v>600</v>
@@ -12531,7 +12465,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="27" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="B107" s="28">
         <v>600</v>
@@ -12554,7 +12488,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="29" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="B108" s="30">
         <v>600</v>
@@ -12577,7 +12511,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="27" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="B109" s="28">
         <v>600</v>
@@ -12600,7 +12534,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="29" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="B110" s="30">
         <v>600</v>
@@ -12623,7 +12557,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="27" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="B111" s="28">
         <v>600</v>
@@ -12646,7 +12580,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="29" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="B112" s="30">
         <v>600</v>
@@ -12669,7 +12603,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="27" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B113" s="28">
         <v>600</v>
@@ -12692,7 +12626,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="29" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="B114" s="30">
         <v>600</v>
@@ -12715,7 +12649,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="27" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="B115" s="28">
         <v>600</v>
@@ -12738,7 +12672,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="29" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="B116" s="30">
         <v>600</v>
@@ -12761,7 +12695,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="27" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="B117" s="28">
         <v>650</v>
@@ -12784,7 +12718,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="29" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="B118" s="30">
         <v>650</v>
@@ -12807,7 +12741,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="27" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="B119" s="28">
         <v>650</v>
@@ -12830,7 +12764,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="29" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="B120" s="30">
         <v>650</v>
@@ -12853,7 +12787,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="27" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="B121" s="28">
         <v>650</v>
@@ -12876,7 +12810,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="29" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="B122" s="30">
         <v>650</v>
@@ -12899,7 +12833,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="27" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="B123" s="28">
         <v>650</v>
@@ -12922,7 +12856,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="29" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="B124" s="30">
         <v>650</v>
@@ -12945,7 +12879,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="27" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="B125" s="28">
         <v>650</v>
@@ -12968,7 +12902,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="29" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="B126" s="30">
         <v>650</v>
@@ -12991,7 +12925,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="27" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="B127" s="28">
         <v>700</v>
@@ -13014,7 +12948,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="29" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B128" s="30">
         <v>700</v>
@@ -13037,7 +12971,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="27" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="B129" s="28">
         <v>700</v>
@@ -13060,7 +12994,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="29" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B130" s="30">
         <v>700</v>
@@ -13083,7 +13017,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="27" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="B131" s="28">
         <v>700</v>
@@ -13106,7 +13040,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="29" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="B132" s="30">
         <v>700</v>
@@ -13129,7 +13063,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="27" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="B133" s="28">
         <v>700</v>
@@ -13152,7 +13086,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="29" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="B134" s="30">
         <v>700</v>
@@ -13175,7 +13109,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="27" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="B135" s="28">
         <v>700</v>
@@ -13198,7 +13132,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="29" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="B136" s="30">
         <v>700</v>
@@ -13221,7 +13155,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="27" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="B137" s="28">
         <v>750</v>
@@ -13244,7 +13178,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="29" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="B138" s="30">
         <v>750</v>
@@ -13267,7 +13201,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="27" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="B139" s="28">
         <v>750</v>
@@ -13290,7 +13224,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="29" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="B140" s="30">
         <v>750</v>
@@ -13313,7 +13247,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="27" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="B141" s="28">
         <v>750</v>
@@ -13336,7 +13270,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="29" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="B142" s="30">
         <v>750</v>
@@ -13359,7 +13293,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="27" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="B143" s="28">
         <v>750</v>
@@ -13382,7 +13316,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="29" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="B144" s="30">
         <v>750</v>
@@ -13405,7 +13339,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="27" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="B145" s="28">
         <v>750</v>
@@ -13428,7 +13362,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="29" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="B146" s="30">
         <v>800</v>
@@ -13451,7 +13385,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="27" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="B147" s="28">
         <v>800</v>
@@ -13474,7 +13408,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="29" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="B148" s="30">
         <v>800</v>
@@ -13497,7 +13431,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="27" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="B149" s="28">
         <v>800</v>
@@ -13520,7 +13454,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="29" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="B150" s="30">
         <v>800</v>
@@ -13543,7 +13477,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="27" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="B151" s="28">
         <v>800</v>
@@ -13566,7 +13500,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="29" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="B152" s="30">
         <v>800</v>
@@ -13589,7 +13523,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="27" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="B153" s="28">
         <v>800</v>
@@ -13612,7 +13546,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="29" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="B154" s="30">
         <v>800</v>
@@ -13635,6 +13569,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/plate3d/PLATE3D_COLUMN.xlsx
+++ b/plate3d/PLATE3D_COLUMN.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="466">
   <si>
     <t>COLUMN</t>
   </si>
@@ -747,6 +747,18 @@
   </si>
   <si>
     <t>the beam start: the column face, plus the plate or plates in front of it</t>
+  </si>
+  <si>
+    <t>the copes. A beam on the web face runs in between the flanges, where the stiffeners already are, so its own flanges come off. BY names the plate and the engine works out the shape.</t>
+  </si>
+  <si>
+    <t>the beams that frame onto the web</t>
+  </si>
+  <si>
+    <t>NOTCH</t>
+  </si>
+  <si>
+    <t>BY</t>
   </si>
   <si>
     <t>the drawings Save DXF makes, named by this sheet</t>
@@ -3522,7 +3534,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T185"/>
+  <dimension ref="A1:T191"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -9195,62 +9207,126 @@
         <v>243</v>
       </c>
     </row>
-    <row r="181" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" s="12" t="s">
+        <v>244</v>
+      </c>
       <c r="B181" s="21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C181" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="D181" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="E181" s="22" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="182" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B182" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="C182" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="D182" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="E182" s="22" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="183" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B183" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="C183" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="D183" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="E183" s="22" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="184" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B184" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="C184" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="D184" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="E184" s="22" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" s="12" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="187" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B187" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="C187" s="22" t="s">
         <v>206</v>
       </c>
-      <c r="D181" s="22" t="s">
-        <v>245</v>
-      </c>
-      <c r="E181" s="22"/>
-      <c r="F181" s="22"/>
-      <c r="G181" s="22">
+      <c r="D187" s="22" t="s">
+        <v>249</v>
+      </c>
+      <c r="E187" s="22"/>
+      <c r="F187" s="22"/>
+      <c r="G187" s="22">
         <v>50</v>
       </c>
-      <c r="H181" s="22" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B182" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="C182" s="22" t="s">
-        <v>248</v>
-      </c>
-      <c r="D182" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="E182" s="22">
+      <c r="H187" s="22" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="188" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B188" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="C188" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="D188" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="E188" s="22">
         <v>10</v>
       </c>
-      <c r="F182" s="22" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="183" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B183" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="C183" s="22" t="s">
+      <c r="F188" s="22" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="189" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B189" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="C189" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="D183" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="E183" s="22">
+      <c r="D189" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="E189" s="22">
         <v>20</v>
       </c>
-      <c r="F183" s="22" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B185" s="21" t="s">
-        <v>252</v>
+      <c r="F189" s="22" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B191" s="21" t="s">
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -9292,7 +9368,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -9303,7 +9379,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B3" s="28">
         <v>100</v>
@@ -9326,7 +9402,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B4" s="30">
         <v>125</v>
@@ -9349,7 +9425,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B5" s="28">
         <v>150</v>
@@ -9372,7 +9448,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B6" s="30">
         <v>148</v>
@@ -9395,7 +9471,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B7" s="28">
         <v>150</v>
@@ -9418,7 +9494,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B8" s="30">
         <v>198</v>
@@ -9441,7 +9517,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B9" s="28">
         <v>200</v>
@@ -9464,7 +9540,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B10" s="30">
         <v>194</v>
@@ -9487,7 +9563,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B11" s="28">
         <v>200</v>
@@ -9510,7 +9586,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B12" s="30">
         <v>200</v>
@@ -9533,7 +9609,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B13" s="28">
         <v>248</v>
@@ -9556,7 +9632,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B14" s="30">
         <v>250</v>
@@ -9579,7 +9655,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B15" s="28">
         <v>244</v>
@@ -9602,7 +9678,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B16" s="30">
         <v>250</v>
@@ -9625,7 +9701,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B17" s="28">
         <v>250</v>
@@ -9648,7 +9724,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B18" s="30">
         <v>298</v>
@@ -9694,7 +9770,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B20" s="30">
         <v>294</v>
@@ -9717,7 +9793,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B21" s="28">
         <v>294</v>
@@ -9763,7 +9839,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B23" s="28">
         <v>300</v>
@@ -9786,7 +9862,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B24" s="30">
         <v>346</v>
@@ -9809,7 +9885,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B25" s="28">
         <v>350</v>
@@ -9832,7 +9908,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B26" s="30">
         <v>340</v>
@@ -9855,7 +9931,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B27" s="28">
         <v>344</v>
@@ -9878,7 +9954,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B28" s="30">
         <v>350</v>
@@ -9901,7 +9977,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B29" s="28">
         <v>396</v>
@@ -9924,7 +10000,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B30" s="30">
         <v>400</v>
@@ -9947,7 +10023,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B31" s="28">
         <v>390</v>
@@ -9970,7 +10046,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B32" s="30">
         <v>388</v>
@@ -9993,7 +10069,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="27" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B33" s="28">
         <v>394</v>
@@ -10016,7 +10092,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B34" s="30">
         <v>400</v>
@@ -10039,7 +10115,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B35" s="28">
         <v>400</v>
@@ -10062,7 +10138,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B36" s="30">
         <v>414</v>
@@ -10085,7 +10161,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B37" s="28">
         <v>428</v>
@@ -10108,7 +10184,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B38" s="30">
         <v>458</v>
@@ -10131,7 +10207,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B39" s="28">
         <v>498</v>
@@ -10154,7 +10230,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B40" s="30">
         <v>446</v>
@@ -10177,7 +10253,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B41" s="28">
         <v>450</v>
@@ -10200,7 +10276,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B42" s="30">
         <v>440</v>
@@ -10223,7 +10299,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="27" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B43" s="28">
         <v>440</v>
@@ -10246,7 +10322,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B44" s="30">
         <v>496</v>
@@ -10269,7 +10345,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B45" s="28">
         <v>500</v>
@@ -10292,7 +10368,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B46" s="30">
         <v>482</v>
@@ -10315,7 +10391,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="27" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B47" s="28">
         <v>488</v>
@@ -10338,7 +10414,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B48" s="30">
         <v>596</v>
@@ -10361,7 +10437,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B49" s="28">
         <v>600</v>
@@ -10384,7 +10460,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B50" s="30">
         <v>582</v>
@@ -10407,7 +10483,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B51" s="28">
         <v>588</v>
@@ -10430,7 +10506,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B52" s="30">
         <v>594</v>
@@ -10453,7 +10529,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="27" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B53" s="28">
         <v>692</v>
@@ -10476,7 +10552,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B54" s="30">
         <v>700</v>
@@ -10499,7 +10575,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B55" s="28">
         <v>792</v>
@@ -10522,7 +10598,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B56" s="30">
         <v>800</v>
@@ -10545,7 +10621,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="27" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B57" s="28">
         <v>890</v>
@@ -10568,7 +10644,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B58" s="30">
         <v>900</v>
@@ -10591,7 +10667,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B59" s="28">
         <v>912</v>
@@ -10614,7 +10690,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B60" s="30">
         <v>918</v>
@@ -10674,7 +10750,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -10685,7 +10761,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B3" s="28">
         <v>20</v>
@@ -10708,7 +10784,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B4" s="30">
         <v>20</v>
@@ -10731,7 +10807,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B5" s="28">
         <v>25</v>
@@ -10754,7 +10830,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B6" s="30">
         <v>25</v>
@@ -10777,7 +10853,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B7" s="28">
         <v>30</v>
@@ -10800,7 +10876,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B8" s="30">
         <v>30</v>
@@ -10823,7 +10899,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B9" s="28">
         <v>40</v>
@@ -10846,7 +10922,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B10" s="30">
         <v>40</v>
@@ -10869,7 +10945,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B11" s="28">
         <v>50</v>
@@ -10892,7 +10968,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B12" s="30">
         <v>50</v>
@@ -10915,7 +10991,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B13" s="28">
         <v>50</v>
@@ -10938,7 +11014,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B14" s="30">
         <v>60</v>
@@ -10961,7 +11037,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B15" s="28">
         <v>60</v>
@@ -10984,7 +11060,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B16" s="30">
         <v>60</v>
@@ -11007,7 +11083,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B17" s="28">
         <v>75</v>
@@ -11030,7 +11106,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B18" s="30">
         <v>75</v>
@@ -11053,7 +11129,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B19" s="28">
         <v>75</v>
@@ -11076,7 +11152,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B20" s="30">
         <v>75</v>
@@ -11099,7 +11175,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B21" s="28">
         <v>80</v>
@@ -11122,7 +11198,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B22" s="30">
         <v>80</v>
@@ -11145,7 +11221,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B23" s="28">
         <v>80</v>
@@ -11168,7 +11244,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B24" s="30">
         <v>90</v>
@@ -11191,7 +11267,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B25" s="28">
         <v>90</v>
@@ -11214,7 +11290,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B26" s="30">
         <v>100</v>
@@ -11237,7 +11313,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B27" s="28">
         <v>100</v>
@@ -11260,7 +11336,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B28" s="30">
         <v>100</v>
@@ -11283,7 +11359,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B29" s="28">
         <v>100</v>
@@ -11306,7 +11382,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B30" s="30">
         <v>100</v>
@@ -11329,7 +11405,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B31" s="28">
         <v>100</v>
@@ -11352,7 +11428,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B32" s="30">
         <v>100</v>
@@ -11375,7 +11451,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="27" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B33" s="28">
         <v>125</v>
@@ -11398,7 +11474,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B34" s="30">
         <v>125</v>
@@ -11421,7 +11497,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B35" s="28">
         <v>125</v>
@@ -11444,7 +11520,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B36" s="30">
         <v>125</v>
@@ -11467,7 +11543,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B37" s="28">
         <v>125</v>
@@ -11490,7 +11566,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B38" s="30">
         <v>125</v>
@@ -11513,7 +11589,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B39" s="28">
         <v>150</v>
@@ -11536,7 +11612,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B40" s="30">
         <v>150</v>
@@ -11559,7 +11635,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B41" s="28">
         <v>150</v>
@@ -11582,7 +11658,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B42" s="30">
         <v>150</v>
@@ -11605,7 +11681,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="27" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B43" s="28">
         <v>175</v>
@@ -11628,7 +11704,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B44" s="30">
         <v>175</v>
@@ -11651,7 +11727,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B45" s="28">
         <v>175</v>
@@ -11674,7 +11750,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B46" s="30">
         <v>200</v>
@@ -11697,7 +11773,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="27" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B47" s="28">
         <v>200</v>
@@ -11720,7 +11796,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B48" s="30">
         <v>200</v>
@@ -11743,7 +11819,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B49" s="28">
         <v>200</v>
@@ -11766,7 +11842,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B50" s="30">
         <v>200</v>
@@ -11789,7 +11865,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B51" s="28">
         <v>250</v>
@@ -11812,7 +11888,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B52" s="30">
         <v>250</v>
@@ -11835,7 +11911,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="27" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B53" s="28">
         <v>250</v>
@@ -11858,7 +11934,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B54" s="30">
         <v>250</v>
@@ -11881,7 +11957,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B55" s="28">
         <v>250</v>
@@ -11904,7 +11980,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B56" s="30">
         <v>300</v>
@@ -11927,7 +12003,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="27" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B57" s="28">
         <v>300</v>
@@ -11950,7 +12026,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B58" s="30">
         <v>300</v>
@@ -11973,7 +12049,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B59" s="28">
         <v>300</v>
@@ -11996,7 +12072,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B60" s="30">
         <v>200</v>
@@ -12019,7 +12095,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="27" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B61" s="28">
         <v>200</v>
@@ -12042,7 +12118,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="29" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B62" s="30">
         <v>200</v>
@@ -12065,7 +12141,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="27" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B63" s="28">
         <v>200</v>
@@ -12088,7 +12164,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="29" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B64" s="30">
         <v>250</v>
@@ -12111,7 +12187,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="27" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B65" s="28">
         <v>250</v>
@@ -12134,7 +12210,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="29" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B66" s="30">
         <v>250</v>
@@ -12157,7 +12233,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="27" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B67" s="28">
         <v>250</v>
@@ -12180,7 +12256,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="29" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B68" s="30">
         <v>250</v>
@@ -12203,7 +12279,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="27" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B69" s="28">
         <v>250</v>
@@ -12226,7 +12302,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="29" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B70" s="30">
         <v>300</v>
@@ -12249,7 +12325,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="27" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B71" s="28">
         <v>300</v>
@@ -12272,7 +12348,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="29" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B72" s="30">
         <v>300</v>
@@ -12295,7 +12371,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="27" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B73" s="28">
         <v>300</v>
@@ -12318,7 +12394,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="29" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B74" s="30">
         <v>300</v>
@@ -12341,7 +12417,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="27" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B75" s="28">
         <v>300</v>
@@ -12364,7 +12440,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="29" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B76" s="30">
         <v>300</v>
@@ -12387,7 +12463,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="27" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B77" s="28">
         <v>350</v>
@@ -12410,7 +12486,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="29" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B78" s="30">
         <v>350</v>
@@ -12433,7 +12509,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="27" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B79" s="28">
         <v>350</v>
@@ -12456,7 +12532,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="29" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B80" s="30">
         <v>350</v>
@@ -12479,7 +12555,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="27" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B81" s="28">
         <v>350</v>
@@ -12502,7 +12578,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="29" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B82" s="30">
         <v>350</v>
@@ -12525,7 +12601,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="27" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B83" s="28">
         <v>400</v>
@@ -12548,7 +12624,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="29" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B84" s="30">
         <v>400</v>
@@ -12571,7 +12647,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="27" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B85" s="28">
         <v>400</v>
@@ -12594,7 +12670,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="29" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B86" s="30">
         <v>400</v>
@@ -12617,7 +12693,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="27" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B87" s="28">
         <v>400</v>
@@ -12640,7 +12716,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="29" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B88" s="30">
         <v>400</v>
@@ -12663,7 +12739,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="27" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B89" s="28">
         <v>450</v>
@@ -12686,7 +12762,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="29" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B90" s="30">
         <v>450</v>
@@ -12709,7 +12785,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="27" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B91" s="28">
         <v>450</v>
@@ -12732,7 +12808,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="29" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B92" s="30">
         <v>450</v>
@@ -12755,7 +12831,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="27" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B93" s="28">
         <v>450</v>
@@ -12778,7 +12854,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="29" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B94" s="30">
         <v>450</v>
@@ -12801,7 +12877,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="27" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B95" s="28">
         <v>500</v>
@@ -12824,7 +12900,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="29" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B96" s="30">
         <v>500</v>
@@ -12847,7 +12923,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="27" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B97" s="28">
         <v>500</v>
@@ -12870,7 +12946,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="29" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B98" s="30">
         <v>500</v>
@@ -12893,7 +12969,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="27" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B99" s="28">
         <v>500</v>
@@ -12916,7 +12992,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="29" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B100" s="30">
         <v>500</v>
@@ -12939,7 +13015,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="27" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B101" s="28">
         <v>550</v>
@@ -12962,7 +13038,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="29" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B102" s="30">
         <v>550</v>
@@ -12985,7 +13061,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="27" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B103" s="28">
         <v>550</v>
@@ -13008,7 +13084,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="29" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B104" s="30">
         <v>550</v>
@@ -13031,7 +13107,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="27" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B105" s="28">
         <v>550</v>
@@ -13054,7 +13130,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="29" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B106" s="30">
         <v>600</v>
@@ -13077,7 +13153,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="27" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B107" s="28">
         <v>600</v>
@@ -13100,7 +13176,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="29" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B108" s="30">
         <v>600</v>
@@ -13123,7 +13199,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="27" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B109" s="28">
         <v>600</v>
@@ -13146,7 +13222,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="29" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B110" s="30">
         <v>600</v>
@@ -13169,7 +13245,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="27" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B111" s="28">
         <v>600</v>
@@ -13192,7 +13268,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="29" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B112" s="30">
         <v>600</v>
@@ -13215,7 +13291,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="27" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B113" s="28">
         <v>600</v>
@@ -13238,7 +13314,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="29" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B114" s="30">
         <v>600</v>
@@ -13261,7 +13337,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="27" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B115" s="28">
         <v>600</v>
@@ -13284,7 +13360,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="29" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B116" s="30">
         <v>600</v>
@@ -13307,7 +13383,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="27" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B117" s="28">
         <v>650</v>
@@ -13330,7 +13406,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="29" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B118" s="30">
         <v>650</v>
@@ -13353,7 +13429,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="27" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B119" s="28">
         <v>650</v>
@@ -13376,7 +13452,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="29" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B120" s="30">
         <v>650</v>
@@ -13399,7 +13475,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="27" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B121" s="28">
         <v>650</v>
@@ -13422,7 +13498,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="29" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B122" s="30">
         <v>650</v>
@@ -13445,7 +13521,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="27" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B123" s="28">
         <v>650</v>
@@ -13468,7 +13544,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="29" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B124" s="30">
         <v>650</v>
@@ -13491,7 +13567,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="27" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B125" s="28">
         <v>650</v>
@@ -13514,7 +13590,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="29" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B126" s="30">
         <v>650</v>
@@ -13537,7 +13613,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="27" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B127" s="28">
         <v>700</v>
@@ -13560,7 +13636,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="29" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B128" s="30">
         <v>700</v>
@@ -13583,7 +13659,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="27" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B129" s="28">
         <v>700</v>
@@ -13606,7 +13682,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="29" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B130" s="30">
         <v>700</v>
@@ -13629,7 +13705,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="27" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B131" s="28">
         <v>700</v>
@@ -13652,7 +13728,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="29" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B132" s="30">
         <v>700</v>
@@ -13675,7 +13751,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="27" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B133" s="28">
         <v>700</v>
@@ -13698,7 +13774,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="29" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B134" s="30">
         <v>700</v>
@@ -13721,7 +13797,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="27" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B135" s="28">
         <v>700</v>
@@ -13744,7 +13820,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="29" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B136" s="30">
         <v>700</v>
@@ -13767,7 +13843,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="27" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B137" s="28">
         <v>750</v>
@@ -13790,7 +13866,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="29" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B138" s="30">
         <v>750</v>
@@ -13813,7 +13889,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="27" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B139" s="28">
         <v>750</v>
@@ -13836,7 +13912,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="29" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B140" s="30">
         <v>750</v>
@@ -13859,7 +13935,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="27" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B141" s="28">
         <v>750</v>
@@ -13882,7 +13958,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="29" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B142" s="30">
         <v>750</v>
@@ -13905,7 +13981,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="27" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B143" s="28">
         <v>750</v>
@@ -13928,7 +14004,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="29" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B144" s="30">
         <v>750</v>
@@ -13951,7 +14027,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="27" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B145" s="28">
         <v>750</v>
@@ -13974,7 +14050,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="29" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B146" s="30">
         <v>800</v>
@@ -13997,7 +14073,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="27" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B147" s="28">
         <v>800</v>
@@ -14020,7 +14096,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="29" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B148" s="30">
         <v>800</v>
@@ -14043,7 +14119,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="27" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B149" s="28">
         <v>800</v>
@@ -14066,7 +14142,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="29" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B150" s="30">
         <v>800</v>
@@ -14089,7 +14165,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="27" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B151" s="28">
         <v>800</v>
@@ -14112,7 +14188,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="29" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B152" s="30">
         <v>800</v>
@@ -14135,7 +14211,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="27" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B153" s="28">
         <v>800</v>
@@ -14158,7 +14234,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="29" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B154" s="30">
         <v>800</v>

--- a/plate3d/PLATE3D_COLUMN.xlsx
+++ b/plate3d/PLATE3D_COLUMN.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="468">
   <si>
     <t>COLUMN</t>
   </si>
@@ -134,6 +134,9 @@
     <t>size</t>
   </si>
   <si>
+    <t>clearance</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -750,6 +753,9 @@
   </si>
   <si>
     <t>the copes. A beam on the web face runs in between the flanges, where the stiffeners already are, so its own flanges come off. BY names the plate and the engine works out the shape.</t>
+  </si>
+  <si>
+    <t>The last cell is the clearance from chapter 2: room at the plate's EDGES, which is where the beam is put in past it. Not through the thickness — on the far side of the plate is the beam's own web.</t>
   </si>
   <si>
     <t>the beams that frame onto the web</t>
@@ -2294,7 +2300,7 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D14" s="5" t="s">
         <v>31</v>
       </c>
@@ -2316,13 +2322,16 @@
       <c r="J14" s="5" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K14" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E15" s="8">
         <v>145.5</v>
@@ -2337,18 +2346,21 @@
         <v>12</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J15" s="8">
         <v>35</v>
       </c>
+      <c r="K15" s="8">
+        <v>20</v>
+      </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E16" s="8">
         <v>-145.5</v>
@@ -2365,7 +2377,7 @@
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="8">
@@ -2383,7 +2395,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="8">
@@ -2401,7 +2413,7 @@
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D19" s="14"/>
       <c r="E19" s="8">
@@ -2419,7 +2431,7 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D20" s="14"/>
       <c r="E20" s="8">
@@ -2437,7 +2449,7 @@
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D21" s="14"/>
       <c r="E21" s="8">
@@ -2455,7 +2467,7 @@
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="8">
@@ -2473,7 +2485,7 @@
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -2491,21 +2503,21 @@
         <v>25</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D24" s="11" t="str">
         <f>IF(PARAM!$C$6="H",IF($H$15&gt;0,2,0)+IF($H$16&gt;0,2,0)+IF($H$17&gt;0,2,0)+IF($H$18&gt;0,2,0)+IF($H$19&gt;0,2,0)+IF($H$20&gt;0,2,0)+IF($H$21&gt;0,2,0)+IF($H$22&gt;0,2,0),0)&amp;" of 16"</f>
         <v>4 of 16</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F24" s="11" t="str">
         <f>IF(NOT(PARAM!$C$6="H"),"n/a",IF(MAX($F$15:$F$22)&gt;(PARAM!$F$6-PARAM!$G$6)/2,"too wide",IF(MAX($G$15:$G$22)&gt;PARAM!$E$6-2*PARAM!$H$6,"too deep","ok")))</f>
         <v>ok</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H24" s="11" t="str">
         <f>ROUND((PARAM!$E$59-PARAM!$H$59)/2,1)&amp;" / "&amp;ROUND((PARAM!$E$60-PARAM!$H$60)/2,1)&amp;" / "&amp;ROUND((PARAM!$E$61-PARAM!$H$61)/2,1)&amp;" / "&amp;ROUND((PARAM!$E$62-PARAM!$H$62)/2,1)</f>
@@ -2514,10 +2526,10 @@
     </row>
     <row r="26" ht="20" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -2531,27 +2543,27 @@
     </row>
     <row r="27" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E27" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E28" s="7">
         <v>300</v>
@@ -2572,12 +2584,12 @@
         <v>0</v>
       </c>
       <c r="K28" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E29" s="7">
         <v>110</v>
@@ -2595,12 +2607,12 @@
         <v>21</v>
       </c>
       <c r="K29" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E30" s="7">
         <v>234</v>
@@ -2618,12 +2630,12 @@
         <v>21</v>
       </c>
       <c r="K30" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E31" s="18">
         <f>PARAM!$E$6+2*PARAM!$J$31</f>
@@ -2646,12 +2658,12 @@
         <v>60</v>
       </c>
       <c r="K31" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
@@ -2669,28 +2681,28 @@
         <v>25</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D33" s="11" t="str">
         <f>IF(PARAM!$C$6="H","cover plates","end plate")</f>
         <v>cover plates</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F33" s="11">
         <f>ROUND(IF(PARAM!$C$6="H",PARAM!$E$28*PARAM!$F$28*PARAM!$G$28*2+PARAM!$E$29*PARAM!$F$29*PARAM!$G$29*4+PARAM!$E$30*PARAM!$F$30*PARAM!$G$30*2,PARAM!$E$31*PARAM!$F$31*PARAM!$G$31*2)*7.85/1000000,1)</f>
         <v>42.2</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H33" s="11" t="str">
         <f>IF(PARAM!$C$6="H",IF(AND(PARAM!$E$28&lt;=PARAM!$F$6,PARAM!$E$30&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6),"ok",IF(PARAM!$E$28&gt;PARAM!$F$6,"flange plate too wide","web plate too deep")),"n/a")</f>
         <v>ok</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J33" s="11" t="str">
         <f>IF(NOT(PARAM!$C$6="H"),"two end plates, "&amp;2*PARAM!$G$31&amp;" thick",IF(PARAM!$J$28=0,"bearing — the ends meet",PARAM!$J$28&amp;"mm apart — shim or division plate?"))</f>
@@ -2699,10 +2711,10 @@
     </row>
     <row r="35" ht="20" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -2716,27 +2728,27 @@
     </row>
     <row r="36" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E36" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E37" s="7">
         <v>16</v>
@@ -2746,7 +2758,7 @@
         <v>18</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H37" s="19">
         <f>IF(PARAM!$C$6="H",CEILING(PARAM!$G$28+PARAM!$H$6+PARAM!$G$29+1.1*PARAM!$E$37,5),"—")</f>
@@ -2763,30 +2775,30 @@
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G38" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I38" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="J38" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="J38" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E39" s="7">
         <v>4</v>
@@ -2809,7 +2821,7 @@
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E40" s="7">
         <v>4</v>
@@ -2832,21 +2844,21 @@
     </row>
     <row r="41" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E41" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E42" s="7">
         <v>3</v>
@@ -2863,7 +2875,7 @@
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B43" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
@@ -2881,21 +2893,21 @@
         <v>25</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D44" s="11" t="str">
         <f>IF(PARAM!$C$6="H",ROUND((PARAM!$F$28/2-PARAM!$G$39-PARAM!$F$39/2)/(PARAM!$E$39/2-1),1)&amp;" / "&amp;ROUND((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1),1),"n/a")</f>
         <v>85 / 60</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F44" s="11" t="str">
         <f>IF(PARAM!$C$6="H",ROUND((PARAM!$F$30/2-PARAM!$G$40-PARAM!$F$40/2)/(PARAM!$E$40/2-1),1)&amp;" / "&amp;ROUND((PARAM!$E$30-2*PARAM!$J$40-PARAM!$I$40)/(PARAM!$H$40-1),1),"n/a")</f>
         <v>90 / 77</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H44" s="11" t="str">
         <f>IF(PARAM!$C$6="H",2*PARAM!$E$39*PARAM!$H$39+PARAM!$E$40*PARAM!$H$40,2*PARAM!$E$42+2*MAX(0,PARAM!$H$42-2))&amp;" per splice"</f>
@@ -2904,10 +2916,10 @@
     </row>
     <row r="46" ht="20" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B46" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -2924,42 +2936,42 @@
         <v>4</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>35</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L47" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B48" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E48" s="8">
         <v>0</v>
@@ -2989,13 +3001,13 @@
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B49" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E49" s="8">
         <v>0</v>
@@ -3025,13 +3037,13 @@
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E50" s="8">
         <v>10</v>
@@ -3061,13 +3073,13 @@
     </row>
     <row r="51" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B51" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E51" s="8">
         <v>10</v>
@@ -3097,13 +3109,13 @@
     </row>
     <row r="52" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B52" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E52" s="8">
         <v>10</v>
@@ -3133,11 +3145,11 @@
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E53" s="8">
         <v>0</v>
@@ -3167,7 +3179,7 @@
     </row>
     <row r="54" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B54" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C54" s="12"/>
       <c r="D54" s="12"/>
@@ -3185,28 +3197,28 @@
         <v>25</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D55" s="11" t="str">
         <f>IF(COUNTIF(PARAM!$B$48:$B$53,PARAM!$C$59)+COUNTIF(PARAM!$B$48:$B$53,PARAM!$C$60)+COUNTIF(PARAM!$B$48:$B$53,PARAM!$C$61)+COUNTIF(PARAM!$B$48:$B$53,PARAM!$C$62)=4,"all 4 beams found theirs","a beam names a mark that is not in the list")</f>
         <v>all 4 beams found theirs</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F55" s="11" t="str">
         <f>IF(NOT(PARAM!$C$6="H"),"n/a",IF(SUMPRODUCT(MAX((PARAM!$C$48:$C$53="end plate")*(PARAM!$F$48:$F$53)))&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"fits between the flanges","hits the flanges on a web face"))</f>
         <v>fits between the flanges</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H55" s="11" t="str">
         <f>"M"&amp;PARAM!$E$37&amp;" L"&amp;MAX(IF(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0))+1.1*PARAM!$E$37,5),IF(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$59+1.1*PARAM!$E$37,5),0)),IF(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$H$6,PARAM!$G$6)+IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0))+1.1*PARAM!$E$37,5),IF(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$60+1.1*PARAM!$E$37,5),0)),IF(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0))+1.1*PARAM!$E$37,5),IF(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$61+1.1*PARAM!$E$37,5),0)),IF(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",CEILING(IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,PARAM!$G$6,PARAM!$H$6)+IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0))+1.1*PARAM!$E$37,5),IF(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate",CEILING(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0)+PARAM!$G$62+1.1*PARAM!$E$37,5),0)))</f>
         <v>M16 L55</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J55" s="11" t="str">
         <f>IF(NOT(PARAM!$C$6="H"),"n/a",IF(MOD(PARAM!$J$6,180)=0,IF(MAX(PARAM!$F$61,PARAM!$F$62)&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"ok","strip the beam flange"),IF(MAX(PARAM!$F$59,PARAM!$F$60)&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"ok","strip the beam flange")))</f>
@@ -3215,10 +3227,10 @@
     </row>
     <row r="57" ht="20" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B57" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -3232,7 +3244,7 @@
     </row>
     <row r="58" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C58" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>5</v>
@@ -3244,7 +3256,7 @@
         <v>7</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H58" s="5" t="s">
         <v>9</v>
@@ -3261,13 +3273,13 @@
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E59" s="8">
         <f>IFERROR(VLOOKUP($D$59,SECT!$A:$G,2,FALSE),"")</f>
@@ -3299,13 +3311,13 @@
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D60" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>127</v>
       </c>
       <c r="E60" s="8">
         <f>IFERROR(VLOOKUP($D$60,SECT!$A:$G,2,FALSE),"")</f>
@@ -3337,13 +3349,13 @@
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E61" s="8">
         <f>IFERROR(VLOOKUP($D$61,SECT!$A:$G,2,FALSE),"")</f>
@@ -3375,13 +3387,13 @@
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E62" s="8">
         <f>IFERROR(VLOOKUP($D$62,SECT!$A:$G,2,FALSE),"")</f>
@@ -3413,7 +3425,7 @@
     </row>
     <row r="63" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B63" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C63" s="12"/>
       <c r="D63" s="12"/>
@@ -3431,21 +3443,21 @@
         <v>25</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D64" s="11" t="str">
         <f>IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,"flange","web"),"tube wall")</f>
         <v>flange</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F64" s="11" t="str">
         <f>IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,"web","flange"),"tube wall")</f>
         <v>web</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H64" s="11" t="str">
         <f>(IF(PARAM!$J$59&gt;0,1,0)+IF(PARAM!$J$60&gt;0,1,0)+IF(PARAM!$J$61&gt;0,1,0)+IF(PARAM!$J$62&gt;0,1,0))&amp;" of 4"</f>
@@ -3534,7 +3546,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T191"/>
+  <dimension ref="A1:T192"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -3546,25 +3558,25 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -3572,10 +3584,10 @@
         <v>17</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D6" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3590,7 +3602,7 @@
         <v>H</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H6" s="22">
         <f>PARAM!$E$6</f>
@@ -3626,10 +3638,10 @@
         <v>18</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D7" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3644,7 +3656,7 @@
         <v>H</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H7" s="22">
         <f>PARAM!$E$6</f>
@@ -3680,10 +3692,10 @@
         <v>19</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D8" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3698,7 +3710,7 @@
         <v>H</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H8" s="22">
         <f>PARAM!$E$6</f>
@@ -3731,18 +3743,18 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3753,10 +3765,10 @@
         <v>12</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H11" s="22">
         <f>IF(PARAM!$C$6="H",PARAM!$E$28,PARAM!$E$31)</f>
@@ -3769,13 +3781,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D12" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3786,10 +3798,10 @@
         <v>10</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H12" s="22">
         <f>PARAM!$E$29</f>
@@ -3802,13 +3814,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D13" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3819,10 +3831,10 @@
         <v>10</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H13" s="22">
         <f>PARAM!$E$30</f>
@@ -3835,13 +3847,13 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D14" s="22" t="str">
         <f>PARAM!$G$37</f>
@@ -3873,13 +3885,13 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D15" s="22" t="str">
         <f>PARAM!$G$37</f>
@@ -3911,23 +3923,23 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D19" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3938,10 +3950,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H19" s="22">
         <f>MAX(1,PARAM!$G$15)</f>
@@ -3954,10 +3966,10 @@
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D20" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3968,10 +3980,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H20" s="22">
         <f>MAX(1,PARAM!$G$16)</f>
@@ -3984,10 +3996,10 @@
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D21" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -3998,10 +4010,10 @@
         <v>1</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H21" s="22">
         <f>MAX(1,PARAM!$G$17)</f>
@@ -4014,10 +4026,10 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D22" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -4028,10 +4040,10 @@
         <v>1</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H22" s="22">
         <f>MAX(1,PARAM!$G$18)</f>
@@ -4044,10 +4056,10 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D23" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -4058,10 +4070,10 @@
         <v>1</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H23" s="22">
         <f>MAX(1,PARAM!$G$19)</f>
@@ -4074,10 +4086,10 @@
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D24" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -4088,10 +4100,10 @@
         <v>1</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H24" s="22">
         <f>MAX(1,PARAM!$G$20)</f>
@@ -4104,10 +4116,10 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D25" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -4118,10 +4130,10 @@
         <v>1</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G25" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H25" s="22">
         <f>MAX(1,PARAM!$G$21)</f>
@@ -4134,10 +4146,10 @@
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D26" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -4148,10 +4160,10 @@
         <v>1</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H26" s="22">
         <f>MAX(1,PARAM!$G$22)</f>
@@ -4164,25 +4176,25 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D29" s="22" t="str">
         <f>IF(PARAM!$I$15="S","RECT","CIRC")</f>
         <v>CIRC</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F29" s="22">
         <f>2*PARAM!$J$15</f>
@@ -4195,23 +4207,23 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D32" s="22">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$15&gt;0),MAX(1,PARAM!$G$15)/2,9999)</f>
@@ -4222,7 +4234,7 @@
         <v>72.5</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G32" s="22">
         <f>-MAX(1,PARAM!$G$15)</f>
@@ -4237,10 +4249,10 @@
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D33" s="22">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$16&gt;0),MAX(1,PARAM!$G$16)/2,9999)</f>
@@ -4251,7 +4263,7 @@
         <v>72.5</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G33" s="22">
         <f>-MAX(1,PARAM!$G$16)</f>
@@ -4266,10 +4278,10 @@
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D34" s="22">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$17&gt;0),MAX(1,PARAM!$G$17)/2,9999)</f>
@@ -4280,7 +4292,7 @@
         <v>0.5</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G34" s="22">
         <f>-MAX(1,PARAM!$G$17)</f>
@@ -4295,10 +4307,10 @@
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D35" s="22">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$18&gt;0),MAX(1,PARAM!$G$18)/2,9999)</f>
@@ -4309,7 +4321,7 @@
         <v>0.5</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G35" s="22">
         <f>-MAX(1,PARAM!$G$18)</f>
@@ -4324,10 +4336,10 @@
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D36" s="22">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$19&gt;0),MAX(1,PARAM!$G$19)/2,9999)</f>
@@ -4338,7 +4350,7 @@
         <v>0.5</v>
       </c>
       <c r="F36" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G36" s="22">
         <f>-MAX(1,PARAM!$G$19)</f>
@@ -4353,10 +4365,10 @@
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B37" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D37" s="22">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$20&gt;0),MAX(1,PARAM!$G$20)/2,9999)</f>
@@ -4367,7 +4379,7 @@
         <v>0.5</v>
       </c>
       <c r="F37" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G37" s="22">
         <f>-MAX(1,PARAM!$G$20)</f>
@@ -4382,10 +4394,10 @@
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B38" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D38" s="22">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$21&gt;0),MAX(1,PARAM!$G$21)/2,9999)</f>
@@ -4396,7 +4408,7 @@
         <v>0.5</v>
       </c>
       <c r="F38" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G38" s="22">
         <f>-MAX(1,PARAM!$G$21)</f>
@@ -4411,10 +4423,10 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D39" s="22">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$22&gt;0),MAX(1,PARAM!$G$22)/2,9999)</f>
@@ -4425,7 +4437,7 @@
         <v>0.5</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G39" s="22">
         <f>-MAX(1,PARAM!$G$22)</f>
@@ -4440,23 +4452,23 @@
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D43" s="22" t="str">
         <f>IF(PARAM!$E$7&gt;0,"sc.c1","")</f>
@@ -4473,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J43" s="22">
         <v>0</v>
@@ -4487,27 +4499,27 @@
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B44" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B45" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D45" s="22" t="str">
         <f>"sc.c2"</f>
@@ -4524,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J45" s="22">
         <v>0</v>
@@ -4538,27 +4550,27 @@
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B46" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C46" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="D46" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="D46" s="22" t="s">
-        <v>184</v>
-      </c>
       <c r="E46" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="F46" s="22" t="s">
         <v>143</v>
-      </c>
-      <c r="F46" s="22" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B47" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D47" s="22" t="str">
         <f>IF(PARAM!$I$7&gt;0,"sc.c3","")</f>
@@ -4575,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J47" s="22">
         <v>0</v>
@@ -4589,42 +4601,42 @@
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B48" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D48" s="22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E48" s="22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F48" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D51" s="22" t="str">
         <f>IF(PARAM!$E$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F51" s="22">
         <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$28/2)),0)</f>
@@ -4644,17 +4656,17 @@
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B52" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D52" s="22" t="str">
         <f>IF(PARAM!$E$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F52" s="22">
         <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$28/2)),0)</f>
@@ -4674,20 +4686,20 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="C53" s="22" t="s">
         <v>190</v>
-      </c>
-      <c r="B53" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="C53" s="22" t="s">
-        <v>189</v>
       </c>
       <c r="D53" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F53" s="22">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -4701,22 +4713,22 @@
         <v>0</v>
       </c>
       <c r="I53" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B54" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D54" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F54" s="22">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -4730,22 +4742,22 @@
         <v>0</v>
       </c>
       <c r="I54" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B55" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D55" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E55" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F55" s="22">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -4759,22 +4771,22 @@
         <v>0</v>
       </c>
       <c r="I55" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B56" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D56" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E56" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F56" s="22">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -4788,25 +4800,25 @@
         <v>0</v>
       </c>
       <c r="I56" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B57" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D57" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E57" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F57" s="22">
         <v>0</v>
@@ -4819,22 +4831,22 @@
         <v>0</v>
       </c>
       <c r="I57" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B58" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D58" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E58" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F58" s="22">
         <v>0</v>
@@ -4847,18 +4859,18 @@
         <v>0</v>
       </c>
       <c r="I58" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D59" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4878,7 +4890,7 @@
         <v>35</v>
       </c>
       <c r="I59" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J59" s="22">
         <v>0</v>
@@ -4920,10 +4932,10 @@
     </row>
     <row r="60" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B60" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D60" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4943,7 +4955,7 @@
         <v>35</v>
       </c>
       <c r="I60" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J60" s="22">
         <v>0</v>
@@ -4985,10 +4997,10 @@
     </row>
     <row r="61" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B61" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D61" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5008,7 +5020,7 @@
         <v>-35</v>
       </c>
       <c r="I61" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J61" s="22">
         <v>0</v>
@@ -5050,10 +5062,10 @@
     </row>
     <row r="62" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B62" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D62" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5073,7 +5085,7 @@
         <v>-35</v>
       </c>
       <c r="I62" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J62" s="22">
         <v>0</v>
@@ -5115,10 +5127,10 @@
     </row>
     <row r="63" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B63" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D63" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5138,7 +5150,7 @@
         <v>35</v>
       </c>
       <c r="I63" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J63" s="22">
         <v>0</v>
@@ -5180,10 +5192,10 @@
     </row>
     <row r="64" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B64" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D64" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5203,7 +5215,7 @@
         <v>35</v>
       </c>
       <c r="I64" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J64" s="22">
         <v>0</v>
@@ -5245,10 +5257,10 @@
     </row>
     <row r="65" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B65" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D65" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5268,7 +5280,7 @@
         <v>-35</v>
       </c>
       <c r="I65" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J65" s="22">
         <v>0</v>
@@ -5310,10 +5322,10 @@
     </row>
     <row r="66" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B66" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C66" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D66" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5333,7 +5345,7 @@
         <v>-35</v>
       </c>
       <c r="I66" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J66" s="22">
         <v>0</v>
@@ -5375,13 +5387,13 @@
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C67" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D67" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -5401,7 +5413,7 @@
         <v>-10</v>
       </c>
       <c r="I67" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J67" s="22">
         <v>0</v>
@@ -5429,10 +5441,10 @@
     </row>
     <row r="68" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B68" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D68" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -5452,7 +5464,7 @@
         <v>-10</v>
       </c>
       <c r="I68" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J68" s="22">
         <v>0</v>
@@ -5480,13 +5492,13 @@
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B69" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D69" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
@@ -5506,7 +5518,7 @@
         <v>-10</v>
       </c>
       <c r="I69" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J69" s="22">
         <v>0</v>
@@ -5534,10 +5546,10 @@
     </row>
     <row r="70" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B70" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D70" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
@@ -5557,7 +5569,7 @@
         <v>-10</v>
       </c>
       <c r="I70" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J70" s="22">
         <v>0</v>
@@ -5585,13 +5597,13 @@
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B71" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D71" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -5611,7 +5623,7 @@
         <v>30</v>
       </c>
       <c r="I71" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J71" s="22">
         <v>0</v>
@@ -5653,10 +5665,10 @@
     </row>
     <row r="72" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B72" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D72" s="22" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -5676,7 +5688,7 @@
         <v>-30</v>
       </c>
       <c r="I72" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J72" s="22">
         <v>0</v>
@@ -5718,34 +5730,34 @@
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B73" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D73" s="22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E73" s="22" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F73" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B74" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C74" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D74" s="22" t="str">
         <f>IF(PARAM!$I$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E74" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F74" s="22">
         <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$28/2)),0)</f>
@@ -5765,17 +5777,17 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B75" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C75" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D75" s="22" t="str">
         <f>IF(PARAM!$I$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E75" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F75" s="22">
         <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$28/2)),0)</f>
@@ -5795,17 +5807,17 @@
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B76" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C76" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D76" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E76" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F76" s="22">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -5819,22 +5831,22 @@
         <v>0</v>
       </c>
       <c r="I76" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B77" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D77" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E77" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F77" s="22">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -5848,22 +5860,22 @@
         <v>0</v>
       </c>
       <c r="I77" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B78" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C78" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D78" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E78" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F78" s="22">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -5877,22 +5889,22 @@
         <v>0</v>
       </c>
       <c r="I78" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B79" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C79" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D79" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E79" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F79" s="22">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -5906,22 +5918,22 @@
         <v>0</v>
       </c>
       <c r="I79" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B80" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C80" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D80" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E80" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F80" s="22">
         <v>0</v>
@@ -5934,22 +5946,22 @@
         <v>0</v>
       </c>
       <c r="I80" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B81" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C81" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D81" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E81" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F81" s="22">
         <v>0</v>
@@ -5962,15 +5974,15 @@
         <v>0</v>
       </c>
       <c r="I81" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="82" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B82" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C82" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D82" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5990,7 +6002,7 @@
         <v>35</v>
       </c>
       <c r="I82" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J82" s="22">
         <v>0</v>
@@ -6032,10 +6044,10 @@
     </row>
     <row r="83" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B83" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C83" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D83" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -6055,7 +6067,7 @@
         <v>35</v>
       </c>
       <c r="I83" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J83" s="22">
         <v>0</v>
@@ -6097,10 +6109,10 @@
     </row>
     <row r="84" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B84" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C84" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D84" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -6120,7 +6132,7 @@
         <v>-35</v>
       </c>
       <c r="I84" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J84" s="22">
         <v>0</v>
@@ -6162,10 +6174,10 @@
     </row>
     <row r="85" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B85" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C85" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D85" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -6185,7 +6197,7 @@
         <v>-35</v>
       </c>
       <c r="I85" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J85" s="22">
         <v>0</v>
@@ -6227,10 +6239,10 @@
     </row>
     <row r="86" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B86" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C86" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D86" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -6250,7 +6262,7 @@
         <v>35</v>
       </c>
       <c r="I86" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J86" s="22">
         <v>0</v>
@@ -6292,10 +6304,10 @@
     </row>
     <row r="87" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B87" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C87" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D87" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -6315,7 +6327,7 @@
         <v>35</v>
       </c>
       <c r="I87" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J87" s="22">
         <v>0</v>
@@ -6357,10 +6369,10 @@
     </row>
     <row r="88" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B88" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C88" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D88" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -6380,7 +6392,7 @@
         <v>-35</v>
       </c>
       <c r="I88" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J88" s="22">
         <v>0</v>
@@ -6422,10 +6434,10 @@
     </row>
     <row r="89" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B89" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C89" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D89" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -6445,7 +6457,7 @@
         <v>-35</v>
       </c>
       <c r="I89" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J89" s="22">
         <v>0</v>
@@ -6487,10 +6499,10 @@
     </row>
     <row r="90" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B90" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C90" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D90" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -6510,7 +6522,7 @@
         <v>-10</v>
       </c>
       <c r="I90" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J90" s="22">
         <v>0</v>
@@ -6538,10 +6550,10 @@
     </row>
     <row r="91" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B91" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C91" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D91" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -6561,7 +6573,7 @@
         <v>-10</v>
       </c>
       <c r="I91" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J91" s="22">
         <v>0</v>
@@ -6589,10 +6601,10 @@
     </row>
     <row r="92" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B92" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C92" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D92" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
@@ -6612,7 +6624,7 @@
         <v>-10</v>
       </c>
       <c r="I92" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J92" s="22">
         <v>0</v>
@@ -6640,10 +6652,10 @@
     </row>
     <row r="93" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B93" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C93" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D93" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
@@ -6663,7 +6675,7 @@
         <v>-10</v>
       </c>
       <c r="I93" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J93" s="22">
         <v>0</v>
@@ -6691,10 +6703,10 @@
     </row>
     <row r="94" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B94" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C94" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D94" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -6714,7 +6726,7 @@
         <v>30</v>
       </c>
       <c r="I94" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J94" s="22">
         <v>0</v>
@@ -6756,10 +6768,10 @@
     </row>
     <row r="95" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B95" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C95" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D95" s="22" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -6779,7 +6791,7 @@
         <v>-30</v>
       </c>
       <c r="I95" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J95" s="22">
         <v>0</v>
@@ -6821,47 +6833,47 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B96" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C96" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="D96" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="E96" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="D96" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="E96" s="22" t="s">
-        <v>198</v>
-      </c>
       <c r="F96" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B100" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C100" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D100" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$15&gt;0),"pl.stf1","")</f>
         <v>pl.stf1</v>
       </c>
       <c r="E100" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F100" s="22">
         <v>0</v>
@@ -6875,7 +6887,7 @@
         <v>845.5</v>
       </c>
       <c r="I100" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J100" s="22">
         <v>0</v>
@@ -6889,20 +6901,20 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B101" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C101" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D101" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$15&gt;0),"pl.stf1","")</f>
         <v>pl.stf1</v>
       </c>
       <c r="E101" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F101" s="22">
         <v>0</v>
@@ -6916,7 +6928,7 @@
         <v>845.5</v>
       </c>
       <c r="I101" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J101" s="22">
         <v>0</v>
@@ -6930,17 +6942,17 @@
     </row>
     <row r="102" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B102" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C102" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D102" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$16&gt;0),"pl.stf2","")</f>
         <v>pl.stf2</v>
       </c>
       <c r="E102" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F102" s="22">
         <v>0</v>
@@ -6954,7 +6966,7 @@
         <v>554.5</v>
       </c>
       <c r="I102" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J102" s="22">
         <v>0</v>
@@ -6968,17 +6980,17 @@
     </row>
     <row r="103" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B103" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C103" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D103" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$16&gt;0),"pl.stf2","")</f>
         <v>pl.stf2</v>
       </c>
       <c r="E103" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F103" s="22">
         <v>0</v>
@@ -6992,7 +7004,7 @@
         <v>554.5</v>
       </c>
       <c r="I103" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J103" s="22">
         <v>0</v>
@@ -7006,17 +7018,17 @@
     </row>
     <row r="104" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B104" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C104" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D104" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$17&gt;0),"pl.stf3","")</f>
         <v/>
       </c>
       <c r="E104" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F104" s="22">
         <v>0</v>
@@ -7030,7 +7042,7 @@
         <v>700</v>
       </c>
       <c r="I104" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J104" s="22">
         <v>0</v>
@@ -7044,17 +7056,17 @@
     </row>
     <row r="105" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B105" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C105" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D105" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$17&gt;0),"pl.stf3","")</f>
         <v/>
       </c>
       <c r="E105" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F105" s="22">
         <v>0</v>
@@ -7068,7 +7080,7 @@
         <v>700</v>
       </c>
       <c r="I105" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J105" s="22">
         <v>0</v>
@@ -7082,17 +7094,17 @@
     </row>
     <row r="106" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B106" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C106" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D106" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$18&gt;0),"pl.stf4","")</f>
         <v/>
       </c>
       <c r="E106" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F106" s="22">
         <v>0</v>
@@ -7106,7 +7118,7 @@
         <v>700</v>
       </c>
       <c r="I106" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J106" s="22">
         <v>0</v>
@@ -7120,17 +7132,17 @@
     </row>
     <row r="107" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B107" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C107" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D107" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$18&gt;0),"pl.stf4","")</f>
         <v/>
       </c>
       <c r="E107" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F107" s="22">
         <v>0</v>
@@ -7144,7 +7156,7 @@
         <v>700</v>
       </c>
       <c r="I107" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J107" s="22">
         <v>0</v>
@@ -7158,17 +7170,17 @@
     </row>
     <row r="108" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B108" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C108" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D108" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$19&gt;0),"pl.stf5","")</f>
         <v/>
       </c>
       <c r="E108" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F108" s="22">
         <v>0</v>
@@ -7182,7 +7194,7 @@
         <v>700</v>
       </c>
       <c r="I108" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J108" s="22">
         <v>0</v>
@@ -7196,17 +7208,17 @@
     </row>
     <row r="109" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B109" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C109" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D109" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$19&gt;0),"pl.stf5","")</f>
         <v/>
       </c>
       <c r="E109" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F109" s="22">
         <v>0</v>
@@ -7220,7 +7232,7 @@
         <v>700</v>
       </c>
       <c r="I109" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J109" s="22">
         <v>0</v>
@@ -7234,17 +7246,17 @@
     </row>
     <row r="110" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B110" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C110" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D110" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$20&gt;0),"pl.stf6","")</f>
         <v/>
       </c>
       <c r="E110" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F110" s="22">
         <v>0</v>
@@ -7258,7 +7270,7 @@
         <v>700</v>
       </c>
       <c r="I110" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J110" s="22">
         <v>0</v>
@@ -7272,17 +7284,17 @@
     </row>
     <row r="111" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B111" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C111" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D111" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$20&gt;0),"pl.stf6","")</f>
         <v/>
       </c>
       <c r="E111" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F111" s="22">
         <v>0</v>
@@ -7296,7 +7308,7 @@
         <v>700</v>
       </c>
       <c r="I111" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J111" s="22">
         <v>0</v>
@@ -7310,17 +7322,17 @@
     </row>
     <row r="112" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B112" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C112" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D112" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$21&gt;0),"pl.stf7","")</f>
         <v/>
       </c>
       <c r="E112" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F112" s="22">
         <v>0</v>
@@ -7334,7 +7346,7 @@
         <v>700</v>
       </c>
       <c r="I112" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J112" s="22">
         <v>0</v>
@@ -7348,17 +7360,17 @@
     </row>
     <row r="113" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B113" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C113" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D113" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$21&gt;0),"pl.stf7","")</f>
         <v/>
       </c>
       <c r="E113" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F113" s="22">
         <v>0</v>
@@ -7372,7 +7384,7 @@
         <v>700</v>
       </c>
       <c r="I113" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J113" s="22">
         <v>0</v>
@@ -7386,17 +7398,17 @@
     </row>
     <row r="114" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B114" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C114" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D114" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$22&gt;0),"pl.stf8","")</f>
         <v/>
       </c>
       <c r="E114" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F114" s="22">
         <v>0</v>
@@ -7410,7 +7422,7 @@
         <v>700</v>
       </c>
       <c r="I114" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J114" s="22">
         <v>0</v>
@@ -7424,17 +7436,17 @@
     </row>
     <row r="115" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B115" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C115" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D115" s="22" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$22&gt;0),"pl.stf8","")</f>
         <v/>
       </c>
       <c r="E115" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F115" s="22">
         <v>0</v>
@@ -7448,7 +7460,7 @@
         <v>700</v>
       </c>
       <c r="I115" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J115" s="22">
         <v>0</v>
@@ -7462,7 +7474,7 @@
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -7470,16 +7482,16 @@
         <v>18</v>
       </c>
       <c r="B118" s="21" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C118" s="22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D118" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E118" s="22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F118" s="22">
         <v>0</v>
@@ -7504,19 +7516,19 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="B119" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="C119" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="D119" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="E119" s="22" t="s">
         <v>208</v>
-      </c>
-      <c r="B119" s="21" t="s">
-        <v>205</v>
-      </c>
-      <c r="C119" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="D119" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="E119" s="22" t="s">
-        <v>207</v>
       </c>
       <c r="F119" s="22">
         <v>0</v>
@@ -7544,16 +7556,16 @@
         <v>19</v>
       </c>
       <c r="B120" s="21" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C120" s="22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D120" s="22" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E120" s="22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F120" s="22">
         <v>0</v>
@@ -7578,19 +7590,19 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B121" s="21" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C121" s="22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D121" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E121" s="22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F121" s="22">
         <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$28/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
@@ -7617,16 +7629,16 @@
     </row>
     <row r="122" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B122" s="21" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C122" s="22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D122" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E122" s="22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F122" s="22">
         <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$28/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
@@ -7653,18 +7665,18 @@
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B125" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C125" s="22" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D125" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7678,7 +7690,7 @@
         <v>14</v>
       </c>
       <c r="G125" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H125" s="22">
         <f>PARAM!$E$59</f>
@@ -7711,10 +7723,10 @@
     </row>
     <row r="126" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B126" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C126" s="22" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D126" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7728,7 +7740,7 @@
         <v>14</v>
       </c>
       <c r="G126" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H126" s="22">
         <f>PARAM!$E$60</f>
@@ -7761,10 +7773,10 @@
     </row>
     <row r="127" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B127" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C127" s="22" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D127" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7778,7 +7790,7 @@
         <v>14</v>
       </c>
       <c r="G127" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H127" s="22">
         <f>PARAM!$E$61</f>
@@ -7811,10 +7823,10 @@
     </row>
     <row r="128" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B128" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C128" s="22" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D128" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7828,7 +7840,7 @@
         <v>14</v>
       </c>
       <c r="G128" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H128" s="22">
         <f>PARAM!$E$62</f>
@@ -7861,18 +7873,18 @@
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B131" s="21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C131" s="22" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D131" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7883,10 +7895,10 @@
         <v>20</v>
       </c>
       <c r="F131" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G131" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H131" s="22">
         <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,5,FALSE),0))</f>
@@ -7899,10 +7911,10 @@
     </row>
     <row r="132" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B132" s="21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C132" s="22" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D132" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7913,10 +7925,10 @@
         <v>10</v>
       </c>
       <c r="F132" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G132" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H132" s="22">
         <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,5,FALSE),0))</f>
@@ -7929,10 +7941,10 @@
     </row>
     <row r="133" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B133" s="21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C133" s="22" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D133" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7943,10 +7955,10 @@
         <v>10</v>
       </c>
       <c r="F133" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G133" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H133" s="22">
         <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,5,FALSE),0))</f>
@@ -7959,10 +7971,10 @@
     </row>
     <row r="134" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B134" s="21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C134" s="22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D134" s="22" t="str">
         <f>PARAM!$C$8</f>
@@ -7973,10 +7985,10 @@
         <v>10</v>
       </c>
       <c r="F134" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G134" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H134" s="22">
         <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,5,FALSE),0))</f>
@@ -7989,13 +8001,13 @@
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B135" s="21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C135" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D135" s="22" t="str">
         <f>PARAM!$G$37</f>
@@ -8027,10 +8039,10 @@
     </row>
     <row r="136" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B136" s="21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C136" s="22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D136" s="22" t="str">
         <f>PARAM!$G$37</f>
@@ -8062,10 +8074,10 @@
     </row>
     <row r="137" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B137" s="21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C137" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D137" s="22" t="str">
         <f>PARAM!$G$37</f>
@@ -8097,10 +8109,10 @@
     </row>
     <row r="138" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B138" s="21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C138" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D138" s="22" t="str">
         <f>PARAM!$G$37</f>
@@ -8132,30 +8144,30 @@
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B143" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C143" s="22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D143" s="22" t="str">
         <f>IF(AND(PARAM!$J$59&gt;0,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cna","")</f>
         <v>pl.cna</v>
       </c>
       <c r="E143" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F143" s="22">
         <f>-IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)/2</f>
@@ -8169,7 +8181,7 @@
         <v>0</v>
       </c>
       <c r="I143" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J143" s="22">
         <v>0</v>
@@ -8183,20 +8195,20 @@
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="B144" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="C144" s="22" t="s">
         <v>231</v>
-      </c>
-      <c r="B144" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="C144" s="22" t="s">
-        <v>230</v>
       </c>
       <c r="D144" s="22" t="str">
         <f>IF(AND(PARAM!$J$59&gt;0,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cna","")</f>
         <v/>
       </c>
       <c r="E144" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F144" s="22">
         <f>-1.5*IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)</f>
@@ -8210,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="I144" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J144" s="22">
         <v>0</v>
@@ -8224,20 +8236,20 @@
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B145" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C145" s="22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D145" s="22" t="str">
         <f>IF(AND(PARAM!$J$59&gt;0,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cna","")</f>
         <v/>
       </c>
       <c r="E145" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F145" s="22">
         <f>IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,4,FALSE),0)</f>
@@ -8251,7 +8263,7 @@
         <v>0</v>
       </c>
       <c r="I145" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J145" s="22">
         <v>0</v>
@@ -8265,13 +8277,13 @@
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B146" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C146" s="22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D146" s="22" t="str">
         <f>IF(PARAM!$J$59&gt;0,"sc.bma","")</f>
@@ -8288,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="I146" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J146" s="22">
         <v>0</v>
@@ -8302,13 +8314,13 @@
     </row>
     <row r="147" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A147" s="12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B147" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C147" s="22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D147" s="22" t="str">
         <f>IF(OR(PARAM!$J$59&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cna")</f>
@@ -8372,39 +8384,39 @@
     </row>
     <row r="148" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B148" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C148" s="22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D148" s="22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E148" s="22" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F148" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="151" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B151" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C151" s="22" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D151" s="22" t="str">
         <f>IF(AND(PARAM!$J$60&gt;0,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cnb","")</f>
         <v/>
       </c>
       <c r="E151" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F151" s="22">
         <f>-(-IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)/2)</f>
@@ -8418,7 +8430,7 @@
         <v>0</v>
       </c>
       <c r="I151" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J151" s="22">
         <v>0</v>
@@ -8432,17 +8444,17 @@
     </row>
     <row r="152" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B152" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C152" s="22" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D152" s="22" t="str">
         <f>IF(AND(PARAM!$J$60&gt;0,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnb","")</f>
         <v/>
       </c>
       <c r="E152" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F152" s="22">
         <f>-(-1.5*IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0))</f>
@@ -8456,7 +8468,7 @@
         <v>0</v>
       </c>
       <c r="I152" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J152" s="22">
         <v>0</v>
@@ -8470,17 +8482,17 @@
     </row>
     <row r="153" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B153" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C153" s="22" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D153" s="22" t="str">
         <f>IF(AND(PARAM!$J$60&gt;0,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cnb","")</f>
         <v>pl.cnb</v>
       </c>
       <c r="E153" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F153" s="22">
         <f>-(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,4,FALSE),0))</f>
@@ -8494,7 +8506,7 @@
         <v>0</v>
       </c>
       <c r="I153" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J153" s="22">
         <v>0</v>
@@ -8508,10 +8520,10 @@
     </row>
     <row r="154" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B154" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C154" s="22" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D154" s="22" t="str">
         <f>IF(PARAM!$J$60&gt;0,"sc.bmb","")</f>
@@ -8528,7 +8540,7 @@
         <v>0</v>
       </c>
       <c r="I154" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J154" s="22">
         <v>0</v>
@@ -8542,10 +8554,10 @@
     </row>
     <row r="155" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B155" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C155" s="22" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D155" s="22" t="str">
         <f>IF(OR(PARAM!$J$60&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cnb")</f>
@@ -8609,39 +8621,39 @@
     </row>
     <row r="156" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B156" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C156" s="22" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D156" s="22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E156" s="22" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F156" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="159" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B159" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C159" s="22" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D159" s="22" t="str">
         <f>IF(AND(PARAM!$J$61&gt;0,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cnc","")</f>
         <v/>
       </c>
       <c r="E159" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F159" s="22">
         <f>0</f>
@@ -8655,7 +8667,7 @@
         <v>0</v>
       </c>
       <c r="I159" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J159" s="22">
         <v>0</v>
@@ -8669,17 +8681,17 @@
     </row>
     <row r="160" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B160" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C160" s="22" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D160" s="22" t="str">
         <f>IF(AND(PARAM!$J$61&gt;0,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnc","")</f>
         <v/>
       </c>
       <c r="E160" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F160" s="22">
         <f>0</f>
@@ -8693,7 +8705,7 @@
         <v>0</v>
       </c>
       <c r="I160" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J160" s="22">
         <v>0</v>
@@ -8707,17 +8719,17 @@
     </row>
     <row r="161" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B161" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C161" s="22" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D161" s="22" t="str">
         <f>IF(AND(PARAM!$J$61&gt;0,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cnc","")</f>
         <v>pl.cnc</v>
       </c>
       <c r="E161" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F161" s="22">
         <f>PARAM!$G$61/2+IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0)/2</f>
@@ -8731,7 +8743,7 @@
         <v>0</v>
       </c>
       <c r="I161" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J161" s="22">
         <v>0</v>
@@ -8745,10 +8757,10 @@
     </row>
     <row r="162" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B162" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C162" s="22" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D162" s="22" t="str">
         <f>IF(PARAM!$J$61&gt;0,"sc.bmc","")</f>
@@ -8765,7 +8777,7 @@
         <v>0</v>
       </c>
       <c r="I162" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J162" s="22">
         <v>0</v>
@@ -8779,10 +8791,10 @@
     </row>
     <row r="163" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B163" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C163" s="22" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D163" s="22" t="str">
         <f>IF(OR(PARAM!$J$61&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cnc")</f>
@@ -8846,39 +8858,39 @@
     </row>
     <row r="164" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B164" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C164" s="22" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D164" s="22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E164" s="22" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F164" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="12" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="167" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B167" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C167" s="22" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D167" s="22" t="str">
         <f>IF(AND(PARAM!$J$62&gt;0,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cnd","")</f>
         <v/>
       </c>
       <c r="E167" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F167" s="22">
         <f>0</f>
@@ -8892,7 +8904,7 @@
         <v>0</v>
       </c>
       <c r="I167" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J167" s="22">
         <v>0</v>
@@ -8906,17 +8918,17 @@
     </row>
     <row r="168" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B168" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C168" s="22" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D168" s="22" t="str">
         <f>IF(AND(PARAM!$J$62&gt;0,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnd","")</f>
         <v/>
       </c>
       <c r="E168" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F168" s="22">
         <f>0</f>
@@ -8930,7 +8942,7 @@
         <v>0</v>
       </c>
       <c r="I168" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J168" s="22">
         <v>0</v>
@@ -8944,17 +8956,17 @@
     </row>
     <row r="169" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B169" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C169" s="22" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D169" s="22" t="str">
         <f>IF(AND(PARAM!$J$62&gt;0,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cnd","")</f>
         <v/>
       </c>
       <c r="E169" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F169" s="22">
         <f>-(PARAM!$G$62/2+IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0)/2)</f>
@@ -8968,7 +8980,7 @@
         <v>0</v>
       </c>
       <c r="I169" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J169" s="22">
         <v>0</v>
@@ -8982,10 +8994,10 @@
     </row>
     <row r="170" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B170" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C170" s="22" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D170" s="22" t="str">
         <f>IF(PARAM!$J$62&gt;0,"sc.bmd","")</f>
@@ -9002,7 +9014,7 @@
         <v>0</v>
       </c>
       <c r="I170" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J170" s="22">
         <v>0</v>
@@ -9016,10 +9028,10 @@
     </row>
     <row r="171" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B171" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C171" s="22" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D171" s="22" t="str">
         <f>IF(OR(PARAM!$J$62&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cnd")</f>
@@ -9083,41 +9095,41 @@
     </row>
     <row r="172" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B172" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C172" s="22" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D172" s="22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E172" s="22" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F172" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B175" s="21" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C175" s="22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D175" s="22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E175" s="22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F175" s="22">
         <f>(IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,4,FALSE),0))</f>
@@ -9132,16 +9144,16 @@
     </row>
     <row r="176" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B176" s="21" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C176" s="22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D176" s="22" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E176" s="22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F176" s="22">
         <f>-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,4,FALSE),0)))</f>
@@ -9156,16 +9168,16 @@
     </row>
     <row r="177" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B177" s="21" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C177" s="22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D177" s="22" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E177" s="22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F177" s="22">
         <v>0</v>
@@ -9180,16 +9192,16 @@
     </row>
     <row r="178" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B178" s="21" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C178" s="22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D178" s="22" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E178" s="22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F178" s="22">
         <v>0</v>
@@ -9204,129 +9216,150 @@
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="12" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="B181" s="21" t="s">
         <v>245</v>
       </c>
-      <c r="C181" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="D181" s="22" t="s">
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="E181" s="22" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="182" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B182" s="21" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C182" s="22" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D182" s="22" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E182" s="22" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="183" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F182" s="22">
+        <f>PARAM!$K$15</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="183" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B183" s="21" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C183" s="22" t="s">
         <v>215</v>
       </c>
       <c r="D183" s="22" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E183" s="22" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="184" spans="2:5" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+      <c r="F183" s="22">
+        <f>PARAM!$K$15</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="184" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B184" s="21" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C184" s="22" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D184" s="22" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E184" s="22" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A186" s="12" t="s">
+      <c r="F184" s="22">
+        <f>PARAM!$K$15</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="185" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B185" s="21" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="187" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B187" s="21" t="s">
+      <c r="C185" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="D185" s="22" t="s">
         <v>248</v>
       </c>
-      <c r="C187" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="D187" s="22" t="s">
+      <c r="E185" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="F185" s="22">
+        <f>PARAM!$K$15</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="E187" s="22"/>
-      <c r="F187" s="22"/>
-      <c r="G187" s="22">
+    </row>
+    <row r="188" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B188" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="C188" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="D188" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="E188" s="22"/>
+      <c r="F188" s="22"/>
+      <c r="G188" s="22">
         <v>50</v>
       </c>
-      <c r="H187" s="22" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="188" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B188" s="21" t="s">
-        <v>251</v>
-      </c>
-      <c r="C188" s="22" t="s">
+      <c r="H188" s="22" t="s">
         <v>252</v>
-      </c>
-      <c r="D188" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="E188" s="22">
-        <v>10</v>
-      </c>
-      <c r="F188" s="22" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="189" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B189" s="21" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C189" s="22" t="s">
-        <v>140</v>
+        <v>254</v>
       </c>
       <c r="D189" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="E189" s="22">
+        <v>10</v>
+      </c>
+      <c r="F189" s="22" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="190" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B190" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="E189" s="22">
+      <c r="C190" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="D190" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="E190" s="22">
         <v>20</v>
       </c>
-      <c r="F189" s="22" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B191" s="21" t="s">
-        <v>256</v>
+      <c r="F190" s="22" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B192" s="21" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -9354,7 +9387,7 @@
         <v>7</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E1" s="24" t="s">
         <v>9</v>
@@ -9368,7 +9401,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -9379,7 +9412,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B3" s="28">
         <v>100</v>
@@ -9402,7 +9435,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B4" s="30">
         <v>125</v>
@@ -9425,7 +9458,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B5" s="28">
         <v>150</v>
@@ -9448,7 +9481,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B6" s="30">
         <v>148</v>
@@ -9471,7 +9504,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B7" s="28">
         <v>150</v>
@@ -9494,7 +9527,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B8" s="30">
         <v>198</v>
@@ -9517,7 +9550,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B9" s="28">
         <v>200</v>
@@ -9540,7 +9573,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B10" s="30">
         <v>194</v>
@@ -9563,7 +9596,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B11" s="28">
         <v>200</v>
@@ -9586,7 +9619,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B12" s="30">
         <v>200</v>
@@ -9609,7 +9642,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B13" s="28">
         <v>248</v>
@@ -9632,7 +9665,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B14" s="30">
         <v>250</v>
@@ -9655,7 +9688,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B15" s="28">
         <v>244</v>
@@ -9678,7 +9711,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B16" s="30">
         <v>250</v>
@@ -9701,7 +9734,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B17" s="28">
         <v>250</v>
@@ -9724,7 +9757,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B18" s="30">
         <v>298</v>
@@ -9747,7 +9780,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B19" s="28">
         <v>300</v>
@@ -9770,7 +9803,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B20" s="30">
         <v>294</v>
@@ -9793,7 +9826,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B21" s="28">
         <v>294</v>
@@ -9839,7 +9872,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B23" s="28">
         <v>300</v>
@@ -9862,7 +9895,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B24" s="30">
         <v>346</v>
@@ -9885,7 +9918,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B25" s="28">
         <v>350</v>
@@ -9908,7 +9941,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B26" s="30">
         <v>340</v>
@@ -9931,7 +9964,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B27" s="28">
         <v>344</v>
@@ -9954,7 +9987,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B28" s="30">
         <v>350</v>
@@ -9977,7 +10010,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B29" s="28">
         <v>396</v>
@@ -10000,7 +10033,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B30" s="30">
         <v>400</v>
@@ -10023,7 +10056,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B31" s="28">
         <v>390</v>
@@ -10046,7 +10079,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B32" s="30">
         <v>388</v>
@@ -10069,7 +10102,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="27" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B33" s="28">
         <v>394</v>
@@ -10092,7 +10125,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B34" s="30">
         <v>400</v>
@@ -10115,7 +10148,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B35" s="28">
         <v>400</v>
@@ -10138,7 +10171,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B36" s="30">
         <v>414</v>
@@ -10161,7 +10194,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B37" s="28">
         <v>428</v>
@@ -10184,7 +10217,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B38" s="30">
         <v>458</v>
@@ -10207,7 +10240,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B39" s="28">
         <v>498</v>
@@ -10230,7 +10263,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B40" s="30">
         <v>446</v>
@@ -10253,7 +10286,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B41" s="28">
         <v>450</v>
@@ -10276,7 +10309,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B42" s="30">
         <v>440</v>
@@ -10299,7 +10332,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="27" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B43" s="28">
         <v>440</v>
@@ -10322,7 +10355,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B44" s="30">
         <v>496</v>
@@ -10345,7 +10378,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B45" s="28">
         <v>500</v>
@@ -10368,7 +10401,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B46" s="30">
         <v>482</v>
@@ -10391,7 +10424,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="27" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B47" s="28">
         <v>488</v>
@@ -10414,7 +10447,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B48" s="30">
         <v>596</v>
@@ -10437,7 +10470,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B49" s="28">
         <v>600</v>
@@ -10460,7 +10493,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B50" s="30">
         <v>582</v>
@@ -10483,7 +10516,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B51" s="28">
         <v>588</v>
@@ -10506,7 +10539,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B52" s="30">
         <v>594</v>
@@ -10529,7 +10562,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="27" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B53" s="28">
         <v>692</v>
@@ -10552,7 +10585,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B54" s="30">
         <v>700</v>
@@ -10575,7 +10608,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B55" s="28">
         <v>792</v>
@@ -10598,7 +10631,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B56" s="30">
         <v>800</v>
@@ -10621,7 +10654,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="27" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B57" s="28">
         <v>890</v>
@@ -10644,7 +10677,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B58" s="30">
         <v>900</v>
@@ -10667,7 +10700,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B59" s="28">
         <v>912</v>
@@ -10690,7 +10723,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B60" s="30">
         <v>918</v>
@@ -10736,7 +10769,7 @@
         <v>7</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E1" s="24" t="s">
         <v>9</v>
@@ -10750,7 +10783,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -10761,7 +10794,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B3" s="28">
         <v>20</v>
@@ -10784,7 +10817,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B4" s="30">
         <v>20</v>
@@ -10807,7 +10840,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B5" s="28">
         <v>25</v>
@@ -10830,7 +10863,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B6" s="30">
         <v>25</v>
@@ -10853,7 +10886,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B7" s="28">
         <v>30</v>
@@ -10876,7 +10909,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B8" s="30">
         <v>30</v>
@@ -10899,7 +10932,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B9" s="28">
         <v>40</v>
@@ -10922,7 +10955,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B10" s="30">
         <v>40</v>
@@ -10945,7 +10978,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B11" s="28">
         <v>50</v>
@@ -10968,7 +11001,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B12" s="30">
         <v>50</v>
@@ -10991,7 +11024,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B13" s="28">
         <v>50</v>
@@ -11014,7 +11047,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B14" s="30">
         <v>60</v>
@@ -11037,7 +11070,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B15" s="28">
         <v>60</v>
@@ -11060,7 +11093,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B16" s="30">
         <v>60</v>
@@ -11083,7 +11116,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B17" s="28">
         <v>75</v>
@@ -11106,7 +11139,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B18" s="30">
         <v>75</v>
@@ -11129,7 +11162,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B19" s="28">
         <v>75</v>
@@ -11152,7 +11185,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B20" s="30">
         <v>75</v>
@@ -11175,7 +11208,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B21" s="28">
         <v>80</v>
@@ -11198,7 +11231,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B22" s="30">
         <v>80</v>
@@ -11221,7 +11254,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B23" s="28">
         <v>80</v>
@@ -11244,7 +11277,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B24" s="30">
         <v>90</v>
@@ -11267,7 +11300,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B25" s="28">
         <v>90</v>
@@ -11290,7 +11323,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B26" s="30">
         <v>100</v>
@@ -11313,7 +11346,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B27" s="28">
         <v>100</v>
@@ -11336,7 +11369,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B28" s="30">
         <v>100</v>
@@ -11359,7 +11392,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B29" s="28">
         <v>100</v>
@@ -11382,7 +11415,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B30" s="30">
         <v>100</v>
@@ -11405,7 +11438,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B31" s="28">
         <v>100</v>
@@ -11428,7 +11461,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B32" s="30">
         <v>100</v>
@@ -11451,7 +11484,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="27" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B33" s="28">
         <v>125</v>
@@ -11474,7 +11507,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B34" s="30">
         <v>125</v>
@@ -11497,7 +11530,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B35" s="28">
         <v>125</v>
@@ -11520,7 +11553,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B36" s="30">
         <v>125</v>
@@ -11543,7 +11576,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B37" s="28">
         <v>125</v>
@@ -11566,7 +11599,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B38" s="30">
         <v>125</v>
@@ -11589,7 +11622,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B39" s="28">
         <v>150</v>
@@ -11612,7 +11645,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B40" s="30">
         <v>150</v>
@@ -11635,7 +11668,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B41" s="28">
         <v>150</v>
@@ -11658,7 +11691,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B42" s="30">
         <v>150</v>
@@ -11681,7 +11714,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="27" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B43" s="28">
         <v>175</v>
@@ -11704,7 +11737,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B44" s="30">
         <v>175</v>
@@ -11727,7 +11760,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B45" s="28">
         <v>175</v>
@@ -11750,7 +11783,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B46" s="30">
         <v>200</v>
@@ -11773,7 +11806,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="27" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B47" s="28">
         <v>200</v>
@@ -11796,7 +11829,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B48" s="30">
         <v>200</v>
@@ -11819,7 +11852,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B49" s="28">
         <v>200</v>
@@ -11842,7 +11875,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B50" s="30">
         <v>200</v>
@@ -11865,7 +11898,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B51" s="28">
         <v>250</v>
@@ -11888,7 +11921,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B52" s="30">
         <v>250</v>
@@ -11911,7 +11944,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="27" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B53" s="28">
         <v>250</v>
@@ -11934,7 +11967,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B54" s="30">
         <v>250</v>
@@ -11957,7 +11990,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B55" s="28">
         <v>250</v>
@@ -11980,7 +12013,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B56" s="30">
         <v>300</v>
@@ -12003,7 +12036,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="27" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B57" s="28">
         <v>300</v>
@@ -12026,7 +12059,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B58" s="30">
         <v>300</v>
@@ -12049,7 +12082,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B59" s="28">
         <v>300</v>
@@ -12072,7 +12105,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B60" s="30">
         <v>200</v>
@@ -12095,7 +12128,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="27" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B61" s="28">
         <v>200</v>
@@ -12118,7 +12151,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="29" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B62" s="30">
         <v>200</v>
@@ -12141,7 +12174,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="27" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B63" s="28">
         <v>200</v>
@@ -12164,7 +12197,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="29" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B64" s="30">
         <v>250</v>
@@ -12187,7 +12220,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="27" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B65" s="28">
         <v>250</v>
@@ -12210,7 +12243,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="29" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B66" s="30">
         <v>250</v>
@@ -12233,7 +12266,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="27" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B67" s="28">
         <v>250</v>
@@ -12256,7 +12289,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="29" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B68" s="30">
         <v>250</v>
@@ -12279,7 +12312,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="27" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B69" s="28">
         <v>250</v>
@@ -12302,7 +12335,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="29" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B70" s="30">
         <v>300</v>
@@ -12325,7 +12358,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="27" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B71" s="28">
         <v>300</v>
@@ -12348,7 +12381,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="29" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B72" s="30">
         <v>300</v>
@@ -12371,7 +12404,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="27" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B73" s="28">
         <v>300</v>
@@ -12394,7 +12427,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="29" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B74" s="30">
         <v>300</v>
@@ -12417,7 +12450,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="27" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B75" s="28">
         <v>300</v>
@@ -12440,7 +12473,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="29" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B76" s="30">
         <v>300</v>
@@ -12463,7 +12496,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="27" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B77" s="28">
         <v>350</v>
@@ -12486,7 +12519,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="29" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B78" s="30">
         <v>350</v>
@@ -12509,7 +12542,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="27" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B79" s="28">
         <v>350</v>
@@ -12532,7 +12565,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="29" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B80" s="30">
         <v>350</v>
@@ -12555,7 +12588,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="27" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B81" s="28">
         <v>350</v>
@@ -12578,7 +12611,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="29" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B82" s="30">
         <v>350</v>
@@ -12601,7 +12634,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="27" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B83" s="28">
         <v>400</v>
@@ -12624,7 +12657,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="29" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B84" s="30">
         <v>400</v>
@@ -12647,7 +12680,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="27" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B85" s="28">
         <v>400</v>
@@ -12670,7 +12703,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="29" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B86" s="30">
         <v>400</v>
@@ -12693,7 +12726,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="27" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B87" s="28">
         <v>400</v>
@@ -12716,7 +12749,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="29" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B88" s="30">
         <v>400</v>
@@ -12739,7 +12772,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="27" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B89" s="28">
         <v>450</v>
@@ -12762,7 +12795,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="29" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B90" s="30">
         <v>450</v>
@@ -12785,7 +12818,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="27" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B91" s="28">
         <v>450</v>
@@ -12808,7 +12841,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="29" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B92" s="30">
         <v>450</v>
@@ -12831,7 +12864,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="27" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B93" s="28">
         <v>450</v>
@@ -12854,7 +12887,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="29" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B94" s="30">
         <v>450</v>
@@ -12877,7 +12910,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="27" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B95" s="28">
         <v>500</v>
@@ -12900,7 +12933,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="29" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B96" s="30">
         <v>500</v>
@@ -12923,7 +12956,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="27" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B97" s="28">
         <v>500</v>
@@ -12946,7 +12979,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="29" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B98" s="30">
         <v>500</v>
@@ -12969,7 +13002,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="27" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B99" s="28">
         <v>500</v>
@@ -12992,7 +13025,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="29" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B100" s="30">
         <v>500</v>
@@ -13015,7 +13048,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="27" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B101" s="28">
         <v>550</v>
@@ -13038,7 +13071,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="29" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B102" s="30">
         <v>550</v>
@@ -13061,7 +13094,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="27" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B103" s="28">
         <v>550</v>
@@ -13084,7 +13117,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="29" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B104" s="30">
         <v>550</v>
@@ -13107,7 +13140,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="27" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B105" s="28">
         <v>550</v>
@@ -13130,7 +13163,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="29" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B106" s="30">
         <v>600</v>
@@ -13153,7 +13186,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="27" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B107" s="28">
         <v>600</v>
@@ -13176,7 +13209,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="29" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B108" s="30">
         <v>600</v>
@@ -13199,7 +13232,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="27" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B109" s="28">
         <v>600</v>
@@ -13222,7 +13255,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="29" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B110" s="30">
         <v>600</v>
@@ -13245,7 +13278,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="27" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B111" s="28">
         <v>600</v>
@@ -13268,7 +13301,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="29" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B112" s="30">
         <v>600</v>
@@ -13291,7 +13324,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="27" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B113" s="28">
         <v>600</v>
@@ -13314,7 +13347,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="29" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B114" s="30">
         <v>600</v>
@@ -13337,7 +13370,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="27" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B115" s="28">
         <v>600</v>
@@ -13360,7 +13393,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="29" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B116" s="30">
         <v>600</v>
@@ -13383,7 +13416,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="27" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B117" s="28">
         <v>650</v>
@@ -13406,7 +13439,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="29" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B118" s="30">
         <v>650</v>
@@ -13429,7 +13462,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="27" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B119" s="28">
         <v>650</v>
@@ -13452,7 +13485,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="29" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B120" s="30">
         <v>650</v>
@@ -13475,7 +13508,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="27" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B121" s="28">
         <v>650</v>
@@ -13498,7 +13531,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="29" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B122" s="30">
         <v>650</v>
@@ -13521,7 +13554,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="27" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B123" s="28">
         <v>650</v>
@@ -13544,7 +13577,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="29" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B124" s="30">
         <v>650</v>
@@ -13567,7 +13600,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="27" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B125" s="28">
         <v>650</v>
@@ -13590,7 +13623,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="29" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B126" s="30">
         <v>650</v>
@@ -13613,7 +13646,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="27" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B127" s="28">
         <v>700</v>
@@ -13636,7 +13669,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="29" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B128" s="30">
         <v>700</v>
@@ -13659,7 +13692,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="27" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B129" s="28">
         <v>700</v>
@@ -13682,7 +13715,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="29" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B130" s="30">
         <v>700</v>
@@ -13705,7 +13738,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="27" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B131" s="28">
         <v>700</v>
@@ -13728,7 +13761,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="29" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B132" s="30">
         <v>700</v>
@@ -13751,7 +13784,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="27" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B133" s="28">
         <v>700</v>
@@ -13774,7 +13807,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="29" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B134" s="30">
         <v>700</v>
@@ -13797,7 +13830,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="27" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B135" s="28">
         <v>700</v>
@@ -13820,7 +13853,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="29" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B136" s="30">
         <v>700</v>
@@ -13843,7 +13876,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="27" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B137" s="28">
         <v>750</v>
@@ -13866,7 +13899,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="29" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B138" s="30">
         <v>750</v>
@@ -13889,7 +13922,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="27" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B139" s="28">
         <v>750</v>
@@ -13912,7 +13945,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="29" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B140" s="30">
         <v>750</v>
@@ -13935,7 +13968,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="27" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B141" s="28">
         <v>750</v>
@@ -13958,7 +13991,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="29" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B142" s="30">
         <v>750</v>
@@ -13981,7 +14014,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="27" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B143" s="28">
         <v>750</v>
@@ -14004,7 +14037,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="29" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B144" s="30">
         <v>750</v>
@@ -14027,7 +14060,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="27" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B145" s="28">
         <v>750</v>
@@ -14050,7 +14083,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="29" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B146" s="30">
         <v>800</v>
@@ -14073,7 +14106,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="27" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B147" s="28">
         <v>800</v>
@@ -14096,7 +14129,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="29" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B148" s="30">
         <v>800</v>
@@ -14119,7 +14152,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="27" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B149" s="28">
         <v>800</v>
@@ -14142,7 +14175,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="29" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B150" s="30">
         <v>800</v>
@@ -14165,7 +14198,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="27" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B151" s="28">
         <v>800</v>
@@ -14188,7 +14221,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="29" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B152" s="30">
         <v>800</v>
@@ -14211,7 +14244,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="27" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B153" s="28">
         <v>800</v>
@@ -14234,7 +14267,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="29" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B154" s="30">
         <v>800</v>

--- a/plate3d/PLATE3D_COLUMN.xlsx
+++ b/plate3d/PLATE3D_COLUMN.xlsx
@@ -2301,7 +2301,7 @@
         <v>109</v>
       </c>
       <c r="G15" s="8">
-        <v>234</v>
+        <v>270</v>
       </c>
       <c r="H15" s="8">
         <v>12</v>
@@ -2324,7 +2324,7 @@
         <v>109</v>
       </c>
       <c r="G16" s="8">
-        <v>234</v>
+        <v>270</v>
       </c>
       <c r="H16" s="8">
         <v>12</v>
@@ -2468,7 +2468,7 @@
         <v>49</v>
       </c>
       <c r="F24" s="11" t="str">
-        <f>IF(NOT(PARAM!$C$6="H"),"n/a",IF(MAX($F$15:$F$22)&gt;(PARAM!$F$6-PARAM!$G$6)/2-2*PARAM!$I$6,"too wide",IF(MAX($G$15:$G$22)&gt;PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"too deep","ok")))</f>
+        <f>IF(NOT(PARAM!$C$6="H"),"n/a",IF(MAX($F$15:$F$22)&gt;(PARAM!$F$6-PARAM!$G$6)/2-2*PARAM!$I$6,"too wide",IF(MAX($G$15:$G$22)&gt;PARAM!$E$6-2*PARAM!$H$6,"too deep","ok")))</f>
         <v>ok</v>
       </c>
       <c r="G24" s="13" t="s">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="H19" s="22">
         <f>MAX(1,PARAM!$G$15)</f>
-        <v>234</v>
+        <v>270</v>
       </c>
       <c r="I19" s="22">
         <f>MAX(1,PARAM!$F$15)</f>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="H20" s="22">
         <f>MAX(1,PARAM!$G$16)</f>
-        <v>234</v>
+        <v>270</v>
       </c>
       <c r="I20" s="22">
         <f>MAX(1,PARAM!$F$16)</f>

--- a/plate3d/PLATE3D_COLUMN.xlsx
+++ b/plate3d/PLATE3D_COLUMN.xlsx
@@ -7271,7 +7271,7 @@
         <v>0</v>
       </c>
       <c r="H108" s="21">
-        <f>(PARAM!$G$7/2+IF(PARAM!$C$6="H",0,PARAM!$G$31))+IF(PARAM!$C$6="H",0,-PARAM!$G$31/2)</f>
+        <f>(PARAM!$G$7/2+IF(PARAM!$C$6="H",0,PARAM!$G$31))+IF(PARAM!$C$6="H",0,PARAM!$G$31/2)</f>
         <v>700</v>
       </c>
       <c r="I108" s="21">

--- a/plate3d/PLATE3D_COLUMN.xlsx
+++ b/plate3d/PLATE3D_COLUMN.xlsx
@@ -2632,7 +2632,7 @@
         <v>65</v>
       </c>
       <c r="H33" s="11" t="str">
-        <f>IF(PARAM!$C$6="H",IF(AND(PARAM!$E$28&lt;=PARAM!$F$6,PARAM!$E$30&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6),"ok",IF(PARAM!$E$28&gt;PARAM!$F$6,"flange plate too wide","web plate too deep")),"n/a")</f>
+        <f>IF(PARAM!$C$6="H",IF(AND(PARAM!$E$28&lt;=PARAM!$F$6,PARAM!$E$30&lt;=PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,PARAM!$E$29/2&lt;=(PARAM!$I$39/2+((PARAM!$E$28/2-PARAM!$J$39-PARAM!$I$39/2)/(PARAM!$H$39/2-1))/2)-(PARAM!$G$6/2+PARAM!$I$6)),"ok",IF(PARAM!$E$28&gt;PARAM!$F$6,"flange plate too wide",IF(PARAM!$E$30&gt;PARAM!$E$6-2*PARAM!$H$6-2*PARAM!$I$6,"web plate too deep","inner plate hits the fillet"))),"n/a")</f>
         <v>ok</v>
       </c>
       <c r="I33" s="13" t="s">

--- a/plate3d/PLATE3D_COLUMN.xlsx
+++ b/plate3d/PLATE3D_COLUMN.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="456">
   <si>
     <t>COLUMN</t>
   </si>
@@ -386,6 +386,9 @@
     <t>tw</t>
   </si>
   <si>
+    <t>level</t>
+  </si>
+  <si>
     <t>X+</t>
   </si>
   <si>
@@ -710,7 +713,7 @@
     <t>The beams go on last. No spin: they belong to the grid, not to the column.</t>
   </si>
   <si>
-    <t>the beam start: the column face, plus the plate or plates in front of it</t>
+    <t>the beam start: the column face, plus the plate or plates in front of it. The last cell is how high it sits.</t>
   </si>
   <si>
     <t>the copes. A beam on the web face runs in between the flanges, where the stiffeners already are, so its own flanges come off. BY names the plate and the engine works out the shape.</t>
@@ -3176,7 +3179,7 @@
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C58" s="5" t="s">
         <v>120</v>
       </c>
@@ -3204,16 +3207,19 @@
       <c r="K58" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L58" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B59" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>99</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E59" s="8">
         <f>IFERROR(VLOOKUP($D$59,SECT!$A:$G,2,FALSE),"")</f>
@@ -3242,16 +3248,19 @@
         <f>IFERROR(VLOOKUP($D$59,SECT!$A:$G,7,FALSE),"")</f>
         <v>36.7</v>
       </c>
-    </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L59" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B60" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>104</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E60" s="8">
         <f>IFERROR(VLOOKUP($D$60,SECT!$A:$G,2,FALSE),"")</f>
@@ -3280,16 +3289,19 @@
         <f>IFERROR(VLOOKUP($D$60,SECT!$A:$G,7,FALSE),"")</f>
         <v>36.7</v>
       </c>
-    </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L60" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B61" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>104</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E61" s="8">
         <f>IFERROR(VLOOKUP($D$61,SECT!$A:$G,2,FALSE),"")</f>
@@ -3318,16 +3330,19 @@
         <f>IFERROR(VLOOKUP($D$61,SECT!$A:$G,7,FALSE),"")</f>
         <v>36.7</v>
       </c>
-    </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L61" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>104</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E62" s="8">
         <f>IFERROR(VLOOKUP($D$62,SECT!$A:$G,2,FALSE),"")</f>
@@ -3356,10 +3371,13 @@
         <f>IFERROR(VLOOKUP($D$62,SECT!$A:$G,7,FALSE),"")</f>
         <v>36.7</v>
       </c>
+      <c r="L62" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="63" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B63" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C63" s="12"/>
       <c r="D63" s="12"/>
@@ -3377,21 +3395,21 @@
         <v>25</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D64" s="11" t="str">
         <f>IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,"flange","web"),"tube wall")</f>
         <v>flange</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F64" s="11" t="str">
         <f>IF(PARAM!$C$6="H",IF(MOD(PARAM!$J$6,180)=0,"web","flange"),"tube wall")</f>
         <v>web</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H64" s="11" t="str">
         <f>(IF(PARAM!$J$59&gt;0,1,0)+IF(PARAM!$J$60&gt;0,1,0)+IF(PARAM!$J$61&gt;0,1,0)+IF(PARAM!$J$62&gt;0,1,0))&amp;" of 4"</f>
@@ -3492,25 +3510,25 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -3518,10 +3536,10 @@
         <v>17</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D6" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -3536,7 +3554,7 @@
         <v>H</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H6" s="21">
         <f>PARAM!$E$6</f>
@@ -3572,10 +3590,10 @@
         <v>18</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D7" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -3590,7 +3608,7 @@
         <v>H</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H7" s="21">
         <f>PARAM!$E$6</f>
@@ -3626,10 +3644,10 @@
         <v>19</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D8" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -3644,7 +3662,7 @@
         <v>H</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H8" s="21">
         <f>PARAM!$E$6</f>
@@ -3677,18 +3695,18 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D11" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -3699,10 +3717,10 @@
         <v>12</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H11" s="21">
         <f>IF(PARAM!$C$6="H",PARAM!$E$28,PARAM!$E$31)</f>
@@ -3715,13 +3733,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -3732,10 +3750,10 @@
         <v>10</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H12" s="21">
         <f>PARAM!$E$29</f>
@@ -3748,13 +3766,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D13" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -3765,10 +3783,10 @@
         <v>10</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H13" s="21">
         <f>PARAM!$E$30</f>
@@ -3781,13 +3799,13 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D14" s="21" t="str">
         <f>PARAM!$G$37</f>
@@ -3819,13 +3837,13 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D15" s="21" t="str">
         <f>PARAM!$G$37</f>
@@ -3857,23 +3875,23 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D19" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -3884,10 +3902,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G19" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H19" s="21">
         <f>MAX(1,PARAM!$G$15)</f>
@@ -3900,10 +3918,10 @@
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D20" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -3914,10 +3932,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G20" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H20" s="21">
         <f>MAX(1,PARAM!$G$16)</f>
@@ -3930,10 +3948,10 @@
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D21" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -3944,10 +3962,10 @@
         <v>1</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H21" s="21">
         <f>MAX(1,PARAM!$G$17)</f>
@@ -3960,10 +3978,10 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D22" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -3974,10 +3992,10 @@
         <v>1</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H22" s="21">
         <f>MAX(1,PARAM!$G$18)</f>
@@ -3990,10 +4008,10 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D23" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -4004,10 +4022,10 @@
         <v>1</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H23" s="21">
         <f>MAX(1,PARAM!$G$19)</f>
@@ -4020,10 +4038,10 @@
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D24" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -4034,10 +4052,10 @@
         <v>1</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H24" s="21">
         <f>MAX(1,PARAM!$G$20)</f>
@@ -4050,10 +4068,10 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D25" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -4064,10 +4082,10 @@
         <v>1</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H25" s="21">
         <f>MAX(1,PARAM!$G$21)</f>
@@ -4080,10 +4098,10 @@
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D26" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -4094,10 +4112,10 @@
         <v>1</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H26" s="21">
         <f>MAX(1,PARAM!$G$22)</f>
@@ -4110,23 +4128,23 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D30" s="21" t="str">
         <f>IF(PARAM!$E$7&gt;0,"sc.c1","")</f>
@@ -4143,7 +4161,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J30" s="21">
         <v>0</v>
@@ -4157,27 +4175,27 @@
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D32" s="21" t="str">
         <f>"sc.c2"</f>
@@ -4194,7 +4212,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J32" s="21">
         <v>0</v>
@@ -4208,27 +4226,27 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C33" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="D33" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="D33" s="21" t="s">
-        <v>172</v>
-      </c>
       <c r="E33" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="F33" s="21" t="s">
         <v>139</v>
-      </c>
-      <c r="F33" s="21" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D34" s="21" t="str">
         <f>IF(PARAM!$I$7&gt;0,"sc.c3","")</f>
@@ -4245,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J34" s="21">
         <v>0</v>
@@ -4259,42 +4277,42 @@
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E35" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F35" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D38" s="21" t="str">
         <f>IF(PARAM!$E$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F38" s="21">
         <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$28/2)),0)</f>
@@ -4314,17 +4332,17 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D39" s="21" t="str">
         <f>IF(PARAM!$E$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F39" s="21">
         <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$28/2)),0)</f>
@@ -4344,20 +4362,20 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="C40" s="21" t="s">
         <v>178</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>177</v>
       </c>
       <c r="D40" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E40" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F40" s="21">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -4371,22 +4389,22 @@
         <v>0</v>
       </c>
       <c r="I40" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B41" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D41" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E41" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F41" s="21">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -4400,22 +4418,22 @@
         <v>0</v>
       </c>
       <c r="I41" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D42" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E42" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F42" s="21">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -4429,22 +4447,22 @@
         <v>0</v>
       </c>
       <c r="I42" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D43" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E43" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F43" s="21">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -4458,25 +4476,25 @@
         <v>0</v>
       </c>
       <c r="I43" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D44" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E44" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F44" s="21">
         <v>0</v>
@@ -4489,22 +4507,22 @@
         <v>0</v>
       </c>
       <c r="I44" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B45" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D45" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E45" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F45" s="21">
         <v>0</v>
@@ -4517,18 +4535,18 @@
         <v>0</v>
       </c>
       <c r="I45" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D46" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4548,7 +4566,7 @@
         <v>35</v>
       </c>
       <c r="I46" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J46" s="21">
         <v>0</v>
@@ -4590,10 +4608,10 @@
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B47" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D47" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4613,7 +4631,7 @@
         <v>35</v>
       </c>
       <c r="I47" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J47" s="21">
         <v>0</v>
@@ -4655,10 +4673,10 @@
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B48" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D48" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4678,7 +4696,7 @@
         <v>-35</v>
       </c>
       <c r="I48" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J48" s="21">
         <v>0</v>
@@ -4720,10 +4738,10 @@
     </row>
     <row r="49" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B49" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D49" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4743,7 +4761,7 @@
         <v>-35</v>
       </c>
       <c r="I49" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J49" s="21">
         <v>0</v>
@@ -4785,10 +4803,10 @@
     </row>
     <row r="50" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B50" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D50" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4808,7 +4826,7 @@
         <v>35</v>
       </c>
       <c r="I50" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J50" s="21">
         <v>0</v>
@@ -4850,10 +4868,10 @@
     </row>
     <row r="51" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B51" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D51" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4873,7 +4891,7 @@
         <v>35</v>
       </c>
       <c r="I51" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J51" s="21">
         <v>0</v>
@@ -4915,10 +4933,10 @@
     </row>
     <row r="52" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B52" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D52" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -4938,7 +4956,7 @@
         <v>-35</v>
       </c>
       <c r="I52" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J52" s="21">
         <v>0</v>
@@ -4980,10 +4998,10 @@
     </row>
     <row r="53" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B53" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D53" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5003,7 +5021,7 @@
         <v>-35</v>
       </c>
       <c r="I53" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J53" s="21">
         <v>0</v>
@@ -5045,13 +5063,13 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D54" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -5071,7 +5089,7 @@
         <v>-10</v>
       </c>
       <c r="I54" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J54" s="21">
         <v>0</v>
@@ -5099,10 +5117,10 @@
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B55" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D55" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -5122,7 +5140,7 @@
         <v>-10</v>
       </c>
       <c r="I55" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J55" s="21">
         <v>0</v>
@@ -5150,13 +5168,13 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D56" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
@@ -5176,7 +5194,7 @@
         <v>-10</v>
       </c>
       <c r="I56" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J56" s="21">
         <v>0</v>
@@ -5204,10 +5222,10 @@
     </row>
     <row r="57" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B57" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D57" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
@@ -5227,7 +5245,7 @@
         <v>-10</v>
       </c>
       <c r="I57" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J57" s="21">
         <v>0</v>
@@ -5255,13 +5273,13 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D58" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -5281,7 +5299,7 @@
         <v>30</v>
       </c>
       <c r="I58" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J58" s="21">
         <v>0</v>
@@ -5323,10 +5341,10 @@
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B59" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D59" s="21" t="str">
         <f>IF(AND(PARAM!$E$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -5346,7 +5364,7 @@
         <v>-30</v>
       </c>
       <c r="I59" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J59" s="21">
         <v>0</v>
@@ -5388,34 +5406,34 @@
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B60" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E60" s="21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F60" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B61" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D61" s="21" t="str">
         <f>IF(PARAM!$I$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E61" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F61" s="21">
         <f>IF(PARAM!$C$6="H",((PARAM!$E$6/2+PARAM!$G$28/2)),0)</f>
@@ -5435,17 +5453,17 @@
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B62" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D62" s="21" t="str">
         <f>IF(PARAM!$I$7&gt;0,"pl.fo","")</f>
         <v>pl.fo</v>
       </c>
       <c r="E62" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F62" s="21">
         <f>IF(PARAM!$C$6="H",-((PARAM!$E$6/2+PARAM!$G$28/2)),0)</f>
@@ -5465,17 +5483,17 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B63" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D63" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E63" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F63" s="21">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -5489,22 +5507,22 @@
         <v>0</v>
       </c>
       <c r="I63" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B64" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D64" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E64" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F64" s="21">
         <f>((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -5518,22 +5536,22 @@
         <v>0</v>
       </c>
       <c r="I64" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B65" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D65" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E65" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F65" s="21">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -5547,22 +5565,22 @@
         <v>0</v>
       </c>
       <c r="I65" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B66" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D66" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.fi","")</f>
         <v>pl.fi</v>
       </c>
       <c r="E66" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F66" s="21">
         <f>-((PARAM!$E$6/2-PARAM!$H$6-PARAM!$G$29/2))</f>
@@ -5576,22 +5594,22 @@
         <v>0</v>
       </c>
       <c r="I66" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B67" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D67" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E67" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F67" s="21">
         <v>0</v>
@@ -5604,22 +5622,22 @@
         <v>0</v>
       </c>
       <c r="I67" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B68" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D68" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"pl.wp","")</f>
         <v>pl.wp</v>
       </c>
       <c r="E68" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F68" s="21">
         <v>0</v>
@@ -5632,15 +5650,15 @@
         <v>0</v>
       </c>
       <c r="I68" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B69" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D69" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5660,7 +5678,7 @@
         <v>35</v>
       </c>
       <c r="I69" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J69" s="21">
         <v>0</v>
@@ -5702,10 +5720,10 @@
     </row>
     <row r="70" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B70" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D70" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5725,7 +5743,7 @@
         <v>35</v>
       </c>
       <c r="I70" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J70" s="21">
         <v>0</v>
@@ -5767,10 +5785,10 @@
     </row>
     <row r="71" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B71" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D71" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5790,7 +5808,7 @@
         <v>-35</v>
       </c>
       <c r="I71" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J71" s="21">
         <v>0</v>
@@ -5832,10 +5850,10 @@
     </row>
     <row r="72" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B72" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D72" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5855,7 +5873,7 @@
         <v>-35</v>
       </c>
       <c r="I72" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J72" s="21">
         <v>0</v>
@@ -5897,10 +5915,10 @@
     </row>
     <row r="73" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B73" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C73" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D73" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5920,7 +5938,7 @@
         <v>35</v>
       </c>
       <c r="I73" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J73" s="21">
         <v>0</v>
@@ -5962,10 +5980,10 @@
     </row>
     <row r="74" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B74" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C74" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D74" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -5985,7 +6003,7 @@
         <v>35</v>
       </c>
       <c r="I74" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J74" s="21">
         <v>0</v>
@@ -6027,10 +6045,10 @@
     </row>
     <row r="75" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B75" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C75" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D75" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -6050,7 +6068,7 @@
         <v>-35</v>
       </c>
       <c r="I75" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J75" s="21">
         <v>0</v>
@@ -6092,10 +6110,10 @@
     </row>
     <row r="76" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B76" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D76" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.f","")</f>
@@ -6115,7 +6133,7 @@
         <v>-35</v>
       </c>
       <c r="I76" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J76" s="21">
         <v>0</v>
@@ -6157,10 +6175,10 @@
     </row>
     <row r="77" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B77" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D77" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -6180,7 +6198,7 @@
         <v>-10</v>
       </c>
       <c r="I77" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J77" s="21">
         <v>0</v>
@@ -6208,10 +6226,10 @@
     </row>
     <row r="78" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B78" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D78" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H")),"bo.f","")</f>
@@ -6231,7 +6249,7 @@
         <v>-10</v>
       </c>
       <c r="I78" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J78" s="21">
         <v>0</v>
@@ -6259,10 +6277,10 @@
     </row>
     <row r="79" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B79" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D79" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
@@ -6282,7 +6300,7 @@
         <v>-10</v>
       </c>
       <c r="I79" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J79" s="21">
         <v>0</v>
@@ -6310,10 +6328,10 @@
     </row>
     <row r="80" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B80" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D80" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,NOT(PARAM!$C$6="H"),PARAM!$H$42&gt;2),"bo.f","")</f>
@@ -6333,7 +6351,7 @@
         <v>-10</v>
       </c>
       <c r="I80" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J80" s="21">
         <v>0</v>
@@ -6361,10 +6379,10 @@
     </row>
     <row r="81" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B81" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D81" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -6384,7 +6402,7 @@
         <v>30</v>
       </c>
       <c r="I81" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J81" s="21">
         <v>0</v>
@@ -6426,10 +6444,10 @@
     </row>
     <row r="82" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B82" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D82" s="21" t="str">
         <f>IF(AND(PARAM!$I$7&gt;0,PARAM!$C$6="H"),"bo.w","")</f>
@@ -6449,7 +6467,7 @@
         <v>-30</v>
       </c>
       <c r="I82" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J82" s="21">
         <v>0</v>
@@ -6491,47 +6509,47 @@
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B83" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C83" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="D83" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E83" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="D83" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="E83" s="21" t="s">
-        <v>186</v>
-      </c>
       <c r="F83" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B87" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C87" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D87" s="21" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$15&gt;0),"pl.stf1","")</f>
         <v>pl.stf1</v>
       </c>
       <c r="E87" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F87" s="21">
         <v>0</v>
@@ -6545,7 +6563,7 @@
         <v>845.5</v>
       </c>
       <c r="I87" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J87" s="21">
         <v>0</v>
@@ -6559,20 +6577,20 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B88" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C88" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D88" s="21" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$15&gt;0),"pl.stf1","")</f>
         <v>pl.stf1</v>
       </c>
       <c r="E88" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F88" s="21">
         <v>0</v>
@@ -6586,7 +6604,7 @@
         <v>845.5</v>
       </c>
       <c r="I88" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J88" s="21">
         <v>0</v>
@@ -6600,17 +6618,17 @@
     </row>
     <row r="89" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B89" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C89" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D89" s="21" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$16&gt;0),"pl.stf2","")</f>
         <v>pl.stf2</v>
       </c>
       <c r="E89" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F89" s="21">
         <v>0</v>
@@ -6624,7 +6642,7 @@
         <v>554.5</v>
       </c>
       <c r="I89" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J89" s="21">
         <v>0</v>
@@ -6638,17 +6656,17 @@
     </row>
     <row r="90" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B90" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D90" s="21" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$16&gt;0),"pl.stf2","")</f>
         <v>pl.stf2</v>
       </c>
       <c r="E90" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F90" s="21">
         <v>0</v>
@@ -6662,7 +6680,7 @@
         <v>554.5</v>
       </c>
       <c r="I90" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J90" s="21">
         <v>0</v>
@@ -6676,17 +6694,17 @@
     </row>
     <row r="91" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B91" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C91" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D91" s="21" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$17&gt;0),"pl.stf3","")</f>
         <v/>
       </c>
       <c r="E91" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F91" s="21">
         <v>0</v>
@@ -6700,7 +6718,7 @@
         <v>700</v>
       </c>
       <c r="I91" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J91" s="21">
         <v>0</v>
@@ -6714,17 +6732,17 @@
     </row>
     <row r="92" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B92" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C92" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D92" s="21" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$17&gt;0),"pl.stf3","")</f>
         <v/>
       </c>
       <c r="E92" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F92" s="21">
         <v>0</v>
@@ -6738,7 +6756,7 @@
         <v>700</v>
       </c>
       <c r="I92" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J92" s="21">
         <v>0</v>
@@ -6752,17 +6770,17 @@
     </row>
     <row r="93" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B93" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C93" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D93" s="21" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$18&gt;0),"pl.stf4","")</f>
         <v/>
       </c>
       <c r="E93" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F93" s="21">
         <v>0</v>
@@ -6776,7 +6794,7 @@
         <v>700</v>
       </c>
       <c r="I93" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J93" s="21">
         <v>0</v>
@@ -6790,17 +6808,17 @@
     </row>
     <row r="94" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B94" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D94" s="21" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$18&gt;0),"pl.stf4","")</f>
         <v/>
       </c>
       <c r="E94" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F94" s="21">
         <v>0</v>
@@ -6814,7 +6832,7 @@
         <v>700</v>
       </c>
       <c r="I94" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J94" s="21">
         <v>0</v>
@@ -6828,17 +6846,17 @@
     </row>
     <row r="95" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B95" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C95" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D95" s="21" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$19&gt;0),"pl.stf5","")</f>
         <v/>
       </c>
       <c r="E95" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F95" s="21">
         <v>0</v>
@@ -6852,7 +6870,7 @@
         <v>700</v>
       </c>
       <c r="I95" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J95" s="21">
         <v>0</v>
@@ -6866,17 +6884,17 @@
     </row>
     <row r="96" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B96" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D96" s="21" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$19&gt;0),"pl.stf5","")</f>
         <v/>
       </c>
       <c r="E96" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F96" s="21">
         <v>0</v>
@@ -6890,7 +6908,7 @@
         <v>700</v>
       </c>
       <c r="I96" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J96" s="21">
         <v>0</v>
@@ -6904,17 +6922,17 @@
     </row>
     <row r="97" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B97" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C97" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D97" s="21" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$20&gt;0),"pl.stf6","")</f>
         <v/>
       </c>
       <c r="E97" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F97" s="21">
         <v>0</v>
@@ -6928,7 +6946,7 @@
         <v>700</v>
       </c>
       <c r="I97" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J97" s="21">
         <v>0</v>
@@ -6942,17 +6960,17 @@
     </row>
     <row r="98" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B98" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D98" s="21" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$20&gt;0),"pl.stf6","")</f>
         <v/>
       </c>
       <c r="E98" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F98" s="21">
         <v>0</v>
@@ -6966,7 +6984,7 @@
         <v>700</v>
       </c>
       <c r="I98" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J98" s="21">
         <v>0</v>
@@ -6980,17 +6998,17 @@
     </row>
     <row r="99" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B99" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C99" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D99" s="21" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$21&gt;0),"pl.stf7","")</f>
         <v/>
       </c>
       <c r="E99" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F99" s="21">
         <v>0</v>
@@ -7004,7 +7022,7 @@
         <v>700</v>
       </c>
       <c r="I99" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J99" s="21">
         <v>0</v>
@@ -7018,17 +7036,17 @@
     </row>
     <row r="100" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B100" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D100" s="21" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$21&gt;0),"pl.stf7","")</f>
         <v/>
       </c>
       <c r="E100" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F100" s="21">
         <v>0</v>
@@ -7042,7 +7060,7 @@
         <v>700</v>
       </c>
       <c r="I100" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J100" s="21">
         <v>0</v>
@@ -7056,17 +7074,17 @@
     </row>
     <row r="101" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B101" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C101" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D101" s="21" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$22&gt;0),"pl.stf8","")</f>
         <v/>
       </c>
       <c r="E101" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F101" s="21">
         <v>0</v>
@@ -7080,7 +7098,7 @@
         <v>700</v>
       </c>
       <c r="I101" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J101" s="21">
         <v>0</v>
@@ -7094,17 +7112,17 @@
     </row>
     <row r="102" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B102" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D102" s="21" t="str">
         <f>IF(AND(PARAM!$C$6="H",PARAM!$H$22&gt;0),"pl.stf8","")</f>
         <v/>
       </c>
       <c r="E102" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F102" s="21">
         <v>0</v>
@@ -7118,7 +7136,7 @@
         <v>700</v>
       </c>
       <c r="I102" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J102" s="21">
         <v>0</v>
@@ -7132,7 +7150,7 @@
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -7140,16 +7158,16 @@
         <v>18</v>
       </c>
       <c r="B105" s="20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C105" s="21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D105" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E105" s="21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F105" s="21">
         <v>0</v>
@@ -7174,19 +7192,19 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B106" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="C106" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="D106" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="E106" s="21" t="s">
         <v>196</v>
-      </c>
-      <c r="B106" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="C106" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="D106" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="E106" s="21" t="s">
-        <v>195</v>
       </c>
       <c r="F106" s="21">
         <v>0</v>
@@ -7214,16 +7232,16 @@
         <v>19</v>
       </c>
       <c r="B107" s="20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C107" s="21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D107" s="21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E107" s="21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F107" s="21">
         <v>0</v>
@@ -7248,19 +7266,19 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B108" s="20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C108" s="21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D108" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E108" s="21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F108" s="21">
         <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$28/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
@@ -7287,16 +7305,16 @@
     </row>
     <row r="109" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B109" s="20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C109" s="21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D109" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E109" s="21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F109" s="21">
         <f>ROUND((IF(PARAM!$C$6="H",(PARAM!$E$6/2+PARAM!$G$28/2),0))*COS(RADIANS(PARAM!$J$6)),6)</f>
@@ -7323,18 +7341,18 @@
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B112" s="20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C112" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D112" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -7348,7 +7366,7 @@
         <v>14</v>
       </c>
       <c r="G112" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H112" s="21">
         <f>PARAM!$E$59</f>
@@ -7381,10 +7399,10 @@
     </row>
     <row r="113" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B113" s="20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C113" s="21" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D113" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -7398,7 +7416,7 @@
         <v>14</v>
       </c>
       <c r="G113" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H113" s="21">
         <f>PARAM!$E$60</f>
@@ -7431,10 +7449,10 @@
     </row>
     <row r="114" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B114" s="20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C114" s="21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D114" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -7448,7 +7466,7 @@
         <v>14</v>
       </c>
       <c r="G114" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H114" s="21">
         <f>PARAM!$E$61</f>
@@ -7481,10 +7499,10 @@
     </row>
     <row r="115" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B115" s="20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C115" s="21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D115" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -7498,7 +7516,7 @@
         <v>14</v>
       </c>
       <c r="G115" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H115" s="21">
         <f>PARAM!$E$62</f>
@@ -7531,18 +7549,18 @@
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B118" s="20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C118" s="21" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D118" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -7553,10 +7571,10 @@
         <v>20</v>
       </c>
       <c r="F118" s="21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G118" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H118" s="21">
         <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,5,FALSE),0))</f>
@@ -7569,10 +7587,10 @@
     </row>
     <row r="119" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B119" s="20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C119" s="21" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D119" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -7583,10 +7601,10 @@
         <v>10</v>
       </c>
       <c r="F119" s="21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G119" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H119" s="21">
         <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,5,FALSE),0))</f>
@@ -7599,10 +7617,10 @@
     </row>
     <row r="120" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B120" s="20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C120" s="21" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D120" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -7613,10 +7631,10 @@
         <v>10</v>
       </c>
       <c r="F120" s="21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G120" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H120" s="21">
         <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,5,FALSE),0))</f>
@@ -7629,10 +7647,10 @@
     </row>
     <row r="121" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B121" s="20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C121" s="21" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D121" s="21" t="str">
         <f>PARAM!$C$8</f>
@@ -7643,10 +7661,10 @@
         <v>10</v>
       </c>
       <c r="F121" s="21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G121" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H121" s="21">
         <f>MAX(1,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,5,FALSE),0))</f>
@@ -7659,13 +7677,13 @@
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B122" s="20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C122" s="21" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D122" s="21" t="str">
         <f>PARAM!$G$37</f>
@@ -7697,10 +7715,10 @@
     </row>
     <row r="123" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B123" s="20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C123" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D123" s="21" t="str">
         <f>PARAM!$G$37</f>
@@ -7732,10 +7750,10 @@
     </row>
     <row r="124" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B124" s="20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C124" s="21" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D124" s="21" t="str">
         <f>PARAM!$G$37</f>
@@ -7767,10 +7785,10 @@
     </row>
     <row r="125" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B125" s="20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C125" s="21" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D125" s="21" t="str">
         <f>PARAM!$G$37</f>
@@ -7802,30 +7820,30 @@
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B130" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C130" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D130" s="21" t="str">
         <f>IF(AND(PARAM!$J$59&gt;0,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cna","")</f>
         <v>pl.cna</v>
       </c>
       <c r="E130" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F130" s="21">
         <f>-IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)/2</f>
@@ -7839,7 +7857,7 @@
         <v>0</v>
       </c>
       <c r="I130" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J130" s="21">
         <v>0</v>
@@ -7853,20 +7871,20 @@
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="B131" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="C131" s="21" t="s">
         <v>219</v>
-      </c>
-      <c r="B131" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="C131" s="21" t="s">
-        <v>218</v>
       </c>
       <c r="D131" s="21" t="str">
         <f>IF(AND(PARAM!$J$59&gt;0,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cna","")</f>
         <v/>
       </c>
       <c r="E131" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F131" s="21">
         <f>-1.5*IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)</f>
@@ -7880,7 +7898,7 @@
         <v>0</v>
       </c>
       <c r="I131" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J131" s="21">
         <v>0</v>
@@ -7894,20 +7912,20 @@
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B132" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C132" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D132" s="21" t="str">
         <f>IF(AND(PARAM!$J$59&gt;0,IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cna","")</f>
         <v/>
       </c>
       <c r="E132" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F132" s="21">
         <f>IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,4,FALSE),0)</f>
@@ -7921,7 +7939,7 @@
         <v>0</v>
       </c>
       <c r="I132" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J132" s="21">
         <v>0</v>
@@ -7935,13 +7953,13 @@
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B133" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C133" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D133" s="21" t="str">
         <f>IF(PARAM!$J$59&gt;0,"sc.bma","")</f>
@@ -7958,7 +7976,7 @@
         <v>0</v>
       </c>
       <c r="I133" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J133" s="21">
         <v>0</v>
@@ -7972,13 +7990,13 @@
     </row>
     <row r="134" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B134" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C134" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D134" s="21" t="str">
         <f>IF(OR(PARAM!$J$59&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cna")</f>
@@ -8042,39 +8060,39 @@
     </row>
     <row r="135" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B135" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C135" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D135" s="21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E135" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F135" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="138" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B138" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C138" s="21" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D138" s="21" t="str">
         <f>IF(AND(PARAM!$J$60&gt;0,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cnb","")</f>
         <v/>
       </c>
       <c r="E138" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F138" s="21">
         <f>-(-IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)/2)</f>
@@ -8088,7 +8106,7 @@
         <v>0</v>
       </c>
       <c r="I138" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J138" s="21">
         <v>0</v>
@@ -8102,17 +8120,17 @@
     </row>
     <row r="139" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B139" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C139" s="21" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D139" s="21" t="str">
         <f>IF(AND(PARAM!$J$60&gt;0,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnb","")</f>
         <v/>
       </c>
       <c r="E139" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F139" s="21">
         <f>-(-1.5*IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0))</f>
@@ -8126,7 +8144,7 @@
         <v>0</v>
       </c>
       <c r="I139" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J139" s="21">
         <v>0</v>
@@ -8140,17 +8158,17 @@
     </row>
     <row r="140" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B140" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C140" s="21" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D140" s="21" t="str">
         <f>IF(AND(PARAM!$J$60&gt;0,IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cnb","")</f>
         <v>pl.cnb</v>
       </c>
       <c r="E140" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F140" s="21">
         <f>-(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,5,FALSE),0)/2-IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,4,FALSE),0))</f>
@@ -8164,7 +8182,7 @@
         <v>0</v>
       </c>
       <c r="I140" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J140" s="21">
         <v>0</v>
@@ -8178,10 +8196,10 @@
     </row>
     <row r="141" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B141" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C141" s="21" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D141" s="21" t="str">
         <f>IF(PARAM!$J$60&gt;0,"sc.bmb","")</f>
@@ -8198,7 +8216,7 @@
         <v>0</v>
       </c>
       <c r="I141" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J141" s="21">
         <v>0</v>
@@ -8212,10 +8230,10 @@
     </row>
     <row r="142" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B142" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C142" s="21" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D142" s="21" t="str">
         <f>IF(OR(PARAM!$J$60&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cnb")</f>
@@ -8279,39 +8297,39 @@
     </row>
     <row r="143" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B143" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C143" s="21" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D143" s="21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E143" s="21" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F143" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="146" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B146" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C146" s="21" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D146" s="21" t="str">
         <f>IF(AND(PARAM!$J$61&gt;0,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cnc","")</f>
         <v/>
       </c>
       <c r="E146" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F146" s="21">
         <f>0</f>
@@ -8325,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="I146" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J146" s="21">
         <v>0</v>
@@ -8339,17 +8357,17 @@
     </row>
     <row r="147" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B147" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C147" s="21" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D147" s="21" t="str">
         <f>IF(AND(PARAM!$J$61&gt;0,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnc","")</f>
         <v/>
       </c>
       <c r="E147" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F147" s="21">
         <f>0</f>
@@ -8363,7 +8381,7 @@
         <v>0</v>
       </c>
       <c r="I147" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J147" s="21">
         <v>0</v>
@@ -8377,17 +8395,17 @@
     </row>
     <row r="148" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B148" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C148" s="21" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D148" s="21" t="str">
         <f>IF(AND(PARAM!$J$61&gt;0,IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cnc","")</f>
         <v>pl.cnc</v>
       </c>
       <c r="E148" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F148" s="21">
         <f>PARAM!$G$61/2+IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,7,FALSE),0)/2</f>
@@ -8401,7 +8419,7 @@
         <v>0</v>
       </c>
       <c r="I148" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J148" s="21">
         <v>0</v>
@@ -8415,10 +8433,10 @@
     </row>
     <row r="149" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B149" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C149" s="21" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D149" s="21" t="str">
         <f>IF(PARAM!$J$61&gt;0,"sc.bmc","")</f>
@@ -8435,7 +8453,7 @@
         <v>0</v>
       </c>
       <c r="I149" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J149" s="21">
         <v>0</v>
@@ -8449,10 +8467,10 @@
     </row>
     <row r="150" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B150" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C150" s="21" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D150" s="21" t="str">
         <f>IF(OR(PARAM!$J$61&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$61,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cnc")</f>
@@ -8516,39 +8534,39 @@
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B151" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C151" s="21" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D151" s="21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E151" s="21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F151" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="154" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B154" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C154" s="21" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D154" s="21" t="str">
         <f>IF(AND(PARAM!$J$62&gt;0,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),"pl.cnd","")</f>
         <v/>
       </c>
       <c r="E154" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F154" s="21">
         <f>0</f>
@@ -8562,7 +8580,7 @@
         <v>0</v>
       </c>
       <c r="I154" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J154" s="21">
         <v>0</v>
@@ -8576,17 +8594,17 @@
     </row>
     <row r="155" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B155" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C155" s="21" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D155" s="21" t="str">
         <f>IF(AND(PARAM!$J$62&gt;0,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",NOT(PARAM!$C$6="H")),"pl.cnd","")</f>
         <v/>
       </c>
       <c r="E155" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F155" s="21">
         <f>0</f>
@@ -8600,7 +8618,7 @@
         <v>0</v>
       </c>
       <c r="I155" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J155" s="21">
         <v>0</v>
@@ -8614,17 +8632,17 @@
     </row>
     <row r="156" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B156" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C156" s="21" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D156" s="21" t="str">
         <f>IF(AND(PARAM!$J$62&gt;0,IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"),"pl.cnd","")</f>
         <v/>
       </c>
       <c r="E156" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F156" s="21">
         <f>-(PARAM!$G$62/2+IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,7,FALSE),0)/2)</f>
@@ -8638,7 +8656,7 @@
         <v>0</v>
       </c>
       <c r="I156" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J156" s="21">
         <v>0</v>
@@ -8652,10 +8670,10 @@
     </row>
     <row r="157" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B157" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C157" s="21" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D157" s="21" t="str">
         <f>IF(PARAM!$J$62&gt;0,"sc.bmd","")</f>
@@ -8672,7 +8690,7 @@
         <v>0</v>
       </c>
       <c r="I157" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J157" s="21">
         <v>0</v>
@@ -8686,10 +8704,10 @@
     </row>
     <row r="158" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B158" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C158" s="21" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D158" s="21" t="str">
         <f>IF(OR(PARAM!$J$62&lt;=0,AND(NOT(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="end plate"),NOT(IFERROR(VLOOKUP(PARAM!$C$62,PARAM!$B$48:$K$53,2,FALSE),"")="fin plate"))),"","bo.cnd")</f>
@@ -8753,41 +8771,41 @@
     </row>
     <row r="159" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B159" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C159" s="21" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D159" s="21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E159" s="21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F159" s="21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B162" s="20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C162" s="21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D162" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E162" s="21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F162" s="21">
         <f>(IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$59,PARAM!$B$48:$K$53,4,FALSE),0))</f>
@@ -8797,21 +8815,22 @@
         <v>0</v>
       </c>
       <c r="H162" s="21">
+        <f>PARAM!$L$59</f>
         <v>0</v>
       </c>
     </row>
     <row r="163" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B163" s="20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C163" s="21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D163" s="21" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E163" s="21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F163" s="21">
         <f>-((IF(MOD(PARAM!$J$6,180)=0,PARAM!$E$6/2,IF(PARAM!$C$6="H",PARAM!$G$6/2,PARAM!$F$6/2)))+IF(IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,2,FALSE),"")="end plate",IF(PARAM!$C$6="H",IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0),2*IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,7,FALSE),0)),IFERROR(VLOOKUP(PARAM!$C$60,PARAM!$B$48:$K$53,4,FALSE),0)))</f>
@@ -8821,21 +8840,22 @@
         <v>0</v>
       </c>
       <c r="H163" s="21">
+        <f>PARAM!$L$60</f>
         <v>0</v>
       </c>
     </row>
     <row r="164" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B164" s="20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C164" s="21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D164" s="21" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E164" s="21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F164" s="21">
         <v>0</v>
@@ -8845,21 +8865,22 @@
         <v>15</v>
       </c>
       <c r="H164" s="21">
+        <f>PARAM!$L$61</f>
         <v>0</v>
       </c>
     </row>
     <row r="165" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B165" s="20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C165" s="21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D165" s="21" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E165" s="21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F165" s="21">
         <v>0</v>
@@ -8869,34 +8890,35 @@
         <v>-15</v>
       </c>
       <c r="H165" s="21">
+        <f>PARAM!$L$62</f>
         <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B169" s="20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C169" s="21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D169" s="21" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E169" s="21" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F169" s="21">
         <f>PARAM!$I$15</f>
@@ -8905,16 +8927,16 @@
     </row>
     <row r="170" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B170" s="20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C170" s="21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D170" s="21" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E170" s="21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F170" s="21">
         <f>PARAM!$I$16</f>
@@ -8923,16 +8945,16 @@
     </row>
     <row r="171" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B171" s="20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C171" s="21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D171" s="21" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E171" s="21" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F171" s="21">
         <f>PARAM!$I$15</f>
@@ -8941,16 +8963,16 @@
     </row>
     <row r="172" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B172" s="20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C172" s="21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D172" s="21" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E172" s="21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F172" s="21">
         <f>PARAM!$I$16</f>
@@ -8959,18 +8981,18 @@
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="175" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B175" s="20" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C175" s="21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D175" s="21" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E175" s="21"/>
       <c r="F175" s="21"/>
@@ -8978,46 +9000,46 @@
         <v>50</v>
       </c>
       <c r="H175" s="21" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="176" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B176" s="20" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C176" s="21" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D176" s="21" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E176" s="21">
         <v>10</v>
       </c>
       <c r="F176" s="21" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B177" s="20" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C177" s="21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D177" s="21" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E177" s="21">
         <v>20</v>
       </c>
       <c r="F177" s="21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="179" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B179" s="20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -9059,7 +9081,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
@@ -9070,7 +9092,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B3" s="27">
         <v>100</v>
@@ -9093,7 +9115,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B4" s="29">
         <v>125</v>
@@ -9116,7 +9138,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B5" s="27">
         <v>150</v>
@@ -9139,7 +9161,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B6" s="29">
         <v>148</v>
@@ -9162,7 +9184,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B7" s="27">
         <v>150</v>
@@ -9185,7 +9207,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B8" s="29">
         <v>198</v>
@@ -9208,7 +9230,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B9" s="27">
         <v>200</v>
@@ -9231,7 +9253,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B10" s="29">
         <v>194</v>
@@ -9254,7 +9276,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B11" s="27">
         <v>200</v>
@@ -9277,7 +9299,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B12" s="29">
         <v>200</v>
@@ -9300,7 +9322,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B13" s="27">
         <v>248</v>
@@ -9323,7 +9345,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B14" s="29">
         <v>250</v>
@@ -9346,7 +9368,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B15" s="27">
         <v>244</v>
@@ -9369,7 +9391,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B16" s="29">
         <v>250</v>
@@ -9392,7 +9414,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B17" s="27">
         <v>250</v>
@@ -9415,7 +9437,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B18" s="29">
         <v>298</v>
@@ -9438,7 +9460,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B19" s="27">
         <v>300</v>
@@ -9461,7 +9483,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B20" s="29">
         <v>294</v>
@@ -9484,7 +9506,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B21" s="27">
         <v>294</v>
@@ -9530,7 +9552,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B23" s="27">
         <v>300</v>
@@ -9553,7 +9575,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B24" s="29">
         <v>346</v>
@@ -9576,7 +9598,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B25" s="27">
         <v>350</v>
@@ -9599,7 +9621,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B26" s="29">
         <v>340</v>
@@ -9622,7 +9644,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B27" s="27">
         <v>344</v>
@@ -9645,7 +9667,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B28" s="29">
         <v>350</v>
@@ -9668,7 +9690,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B29" s="27">
         <v>396</v>
@@ -9691,7 +9713,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B30" s="29">
         <v>400</v>
@@ -9714,7 +9736,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B31" s="27">
         <v>390</v>
@@ -9737,7 +9759,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="28" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B32" s="29">
         <v>388</v>
@@ -9760,7 +9782,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B33" s="27">
         <v>394</v>
@@ -9783,7 +9805,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="28" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B34" s="29">
         <v>400</v>
@@ -9806,7 +9828,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B35" s="27">
         <v>400</v>
@@ -9829,7 +9851,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B36" s="29">
         <v>414</v>
@@ -9852,7 +9874,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="26" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B37" s="27">
         <v>428</v>
@@ -9875,7 +9897,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B38" s="29">
         <v>458</v>
@@ -9898,7 +9920,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B39" s="27">
         <v>498</v>
@@ -9921,7 +9943,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="28" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B40" s="29">
         <v>446</v>
@@ -9944,7 +9966,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B41" s="27">
         <v>450</v>
@@ -9967,7 +9989,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="28" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B42" s="29">
         <v>440</v>
@@ -9990,7 +10012,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B43" s="27">
         <v>440</v>
@@ -10013,7 +10035,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="28" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B44" s="29">
         <v>496</v>
@@ -10036,7 +10058,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="26" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B45" s="27">
         <v>500</v>
@@ -10059,7 +10081,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="28" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B46" s="29">
         <v>482</v>
@@ -10082,7 +10104,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B47" s="27">
         <v>488</v>
@@ -10105,7 +10127,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B48" s="29">
         <v>596</v>
@@ -10128,7 +10150,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B49" s="27">
         <v>600</v>
@@ -10151,7 +10173,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="28" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B50" s="29">
         <v>582</v>
@@ -10174,7 +10196,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="26" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B51" s="27">
         <v>588</v>
@@ -10197,7 +10219,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="28" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B52" s="29">
         <v>594</v>
@@ -10220,7 +10242,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="26" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B53" s="27">
         <v>692</v>
@@ -10243,7 +10265,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="28" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B54" s="29">
         <v>700</v>
@@ -10266,7 +10288,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B55" s="27">
         <v>792</v>
@@ -10289,7 +10311,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="28" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B56" s="29">
         <v>800</v>
@@ -10312,7 +10334,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B57" s="27">
         <v>890</v>
@@ -10335,7 +10357,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="28" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B58" s="29">
         <v>900</v>
@@ -10358,7 +10380,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B59" s="27">
         <v>912</v>
@@ -10381,7 +10403,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="28" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B60" s="29">
         <v>918</v>
@@ -10441,7 +10463,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
@@ -10452,7 +10474,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B3" s="27">
         <v>20</v>
@@ -10475,7 +10497,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B4" s="29">
         <v>20</v>
@@ -10498,7 +10520,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B5" s="27">
         <v>25</v>
@@ -10521,7 +10543,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B6" s="29">
         <v>25</v>
@@ -10544,7 +10566,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B7" s="27">
         <v>30</v>
@@ -10567,7 +10589,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B8" s="29">
         <v>30</v>
@@ -10590,7 +10612,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B9" s="27">
         <v>40</v>
@@ -10613,7 +10635,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B10" s="29">
         <v>40</v>
@@ -10636,7 +10658,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B11" s="27">
         <v>50</v>
@@ -10659,7 +10681,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B12" s="29">
         <v>50</v>
@@ -10682,7 +10704,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B13" s="27">
         <v>50</v>
@@ -10705,7 +10727,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B14" s="29">
         <v>60</v>
@@ -10728,7 +10750,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B15" s="27">
         <v>60</v>
@@ -10751,7 +10773,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B16" s="29">
         <v>60</v>
@@ -10774,7 +10796,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B17" s="27">
         <v>75</v>
@@ -10797,7 +10819,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B18" s="29">
         <v>75</v>
@@ -10820,7 +10842,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B19" s="27">
         <v>75</v>
@@ -10843,7 +10865,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B20" s="29">
         <v>75</v>
@@ -10866,7 +10888,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B21" s="27">
         <v>80</v>
@@ -10889,7 +10911,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B22" s="29">
         <v>80</v>
@@ -10912,7 +10934,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B23" s="27">
         <v>80</v>
@@ -10935,7 +10957,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B24" s="29">
         <v>90</v>
@@ -10958,7 +10980,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B25" s="27">
         <v>90</v>
@@ -10981,7 +11003,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B26" s="29">
         <v>100</v>
@@ -11004,7 +11026,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B27" s="27">
         <v>100</v>
@@ -11027,7 +11049,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B28" s="29">
         <v>100</v>
@@ -11050,7 +11072,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B29" s="27">
         <v>100</v>
@@ -11073,7 +11095,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B30" s="29">
         <v>100</v>
@@ -11096,7 +11118,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B31" s="27">
         <v>100</v>
@@ -11119,7 +11141,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="28" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B32" s="29">
         <v>100</v>
@@ -11142,7 +11164,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B33" s="27">
         <v>125</v>
@@ -11165,7 +11187,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="28" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B34" s="29">
         <v>125</v>
@@ -11188,7 +11210,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B35" s="27">
         <v>125</v>
@@ -11211,7 +11233,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B36" s="29">
         <v>125</v>
@@ -11234,7 +11256,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="26" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B37" s="27">
         <v>125</v>
@@ -11257,7 +11279,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="28" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B38" s="29">
         <v>125</v>
@@ -11280,7 +11302,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B39" s="27">
         <v>150</v>
@@ -11303,7 +11325,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="28" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B40" s="29">
         <v>150</v>
@@ -11326,7 +11348,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B41" s="27">
         <v>150</v>
@@ -11349,7 +11371,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="28" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B42" s="29">
         <v>150</v>
@@ -11372,7 +11394,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B43" s="27">
         <v>175</v>
@@ -11395,7 +11417,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="28" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B44" s="29">
         <v>175</v>
@@ -11418,7 +11440,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="26" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B45" s="27">
         <v>175</v>
@@ -11441,7 +11463,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="28" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B46" s="29">
         <v>200</v>
@@ -11464,7 +11486,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="26" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B47" s="27">
         <v>200</v>
@@ -11487,7 +11509,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="28" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B48" s="29">
         <v>200</v>
@@ -11510,7 +11532,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B49" s="27">
         <v>200</v>
@@ -11533,7 +11555,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="28" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B50" s="29">
         <v>200</v>
@@ -11556,7 +11578,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="26" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B51" s="27">
         <v>250</v>
@@ -11579,7 +11601,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="28" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B52" s="29">
         <v>250</v>
@@ -11602,7 +11624,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="26" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B53" s="27">
         <v>250</v>
@@ -11625,7 +11647,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="28" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B54" s="29">
         <v>250</v>
@@ -11648,7 +11670,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B55" s="27">
         <v>250</v>
@@ -11671,7 +11693,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="28" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B56" s="29">
         <v>300</v>
@@ -11694,7 +11716,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B57" s="27">
         <v>300</v>
@@ -11717,7 +11739,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="28" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B58" s="29">
         <v>300</v>
@@ -11740,7 +11762,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B59" s="27">
         <v>300</v>
@@ -11763,7 +11785,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="28" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B60" s="29">
         <v>200</v>
@@ -11786,7 +11808,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B61" s="27">
         <v>200</v>
@@ -11809,7 +11831,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="28" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B62" s="29">
         <v>200</v>
@@ -11832,7 +11854,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="26" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B63" s="27">
         <v>200</v>
@@ -11855,7 +11877,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="28" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B64" s="29">
         <v>250</v>
@@ -11878,7 +11900,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="26" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B65" s="27">
         <v>250</v>
@@ -11901,7 +11923,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="28" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B66" s="29">
         <v>250</v>
@@ -11924,7 +11946,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="26" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B67" s="27">
         <v>250</v>
@@ -11947,7 +11969,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="28" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B68" s="29">
         <v>250</v>
@@ -11970,7 +11992,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="26" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B69" s="27">
         <v>250</v>
@@ -11993,7 +12015,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="28" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B70" s="29">
         <v>300</v>
@@ -12016,7 +12038,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="26" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B71" s="27">
         <v>300</v>
@@ -12039,7 +12061,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="28" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B72" s="29">
         <v>300</v>
@@ -12062,7 +12084,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="26" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B73" s="27">
         <v>300</v>
@@ -12085,7 +12107,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="28" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B74" s="29">
         <v>300</v>
@@ -12108,7 +12130,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="26" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B75" s="27">
         <v>300</v>
@@ -12131,7 +12153,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="28" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B76" s="29">
         <v>300</v>
@@ -12154,7 +12176,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="26" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B77" s="27">
         <v>350</v>
@@ -12177,7 +12199,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="28" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B78" s="29">
         <v>350</v>
@@ -12200,7 +12222,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="26" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B79" s="27">
         <v>350</v>
@@ -12223,7 +12245,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="28" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B80" s="29">
         <v>350</v>
@@ -12246,7 +12268,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="26" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B81" s="27">
         <v>350</v>
@@ -12269,7 +12291,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="28" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B82" s="29">
         <v>350</v>
@@ -12292,7 +12314,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="26" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B83" s="27">
         <v>400</v>
@@ -12315,7 +12337,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="28" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B84" s="29">
         <v>400</v>
@@ -12338,7 +12360,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="26" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B85" s="27">
         <v>400</v>
@@ -12361,7 +12383,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="28" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B86" s="29">
         <v>400</v>
@@ -12384,7 +12406,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="26" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B87" s="27">
         <v>400</v>
@@ -12407,7 +12429,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="28" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B88" s="29">
         <v>400</v>
@@ -12430,7 +12452,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="26" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B89" s="27">
         <v>450</v>
@@ -12453,7 +12475,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="28" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B90" s="29">
         <v>450</v>
@@ -12476,7 +12498,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="26" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B91" s="27">
         <v>450</v>
@@ -12499,7 +12521,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="28" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B92" s="29">
         <v>450</v>
@@ -12522,7 +12544,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="26" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B93" s="27">
         <v>450</v>
@@ -12545,7 +12567,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="28" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B94" s="29">
         <v>450</v>
@@ -12568,7 +12590,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="26" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B95" s="27">
         <v>500</v>
@@ -12591,7 +12613,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="28" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B96" s="29">
         <v>500</v>
@@ -12614,7 +12636,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="26" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B97" s="27">
         <v>500</v>
@@ -12637,7 +12659,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="28" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B98" s="29">
         <v>500</v>
@@ -12660,7 +12682,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="26" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B99" s="27">
         <v>500</v>
@@ -12683,7 +12705,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="28" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B100" s="29">
         <v>500</v>
@@ -12706,7 +12728,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="26" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B101" s="27">
         <v>550</v>
@@ -12729,7 +12751,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="28" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B102" s="29">
         <v>550</v>
@@ -12752,7 +12774,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="26" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B103" s="27">
         <v>550</v>
@@ -12775,7 +12797,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="28" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B104" s="29">
         <v>550</v>
@@ -12798,7 +12820,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="26" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B105" s="27">
         <v>550</v>
@@ -12821,7 +12843,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="28" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B106" s="29">
         <v>600</v>
@@ -12844,7 +12866,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="26" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B107" s="27">
         <v>600</v>
@@ -12867,7 +12889,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="28" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B108" s="29">
         <v>600</v>
@@ -12890,7 +12912,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="26" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B109" s="27">
         <v>600</v>
@@ -12913,7 +12935,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="28" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B110" s="29">
         <v>600</v>
@@ -12936,7 +12958,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="26" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B111" s="27">
         <v>600</v>
@@ -12959,7 +12981,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="28" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B112" s="29">
         <v>600</v>
@@ -12982,7 +13004,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="26" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B113" s="27">
         <v>600</v>
@@ -13005,7 +13027,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="28" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B114" s="29">
         <v>600</v>
@@ -13028,7 +13050,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="26" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B115" s="27">
         <v>600</v>
@@ -13051,7 +13073,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="28" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B116" s="29">
         <v>600</v>
@@ -13074,7 +13096,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="26" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B117" s="27">
         <v>650</v>
@@ -13097,7 +13119,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="28" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B118" s="29">
         <v>650</v>
@@ -13120,7 +13142,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="26" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B119" s="27">
         <v>650</v>
@@ -13143,7 +13165,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="28" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B120" s="29">
         <v>650</v>
@@ -13166,7 +13188,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="26" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B121" s="27">
         <v>650</v>
@@ -13189,7 +13211,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="28" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B122" s="29">
         <v>650</v>
@@ -13212,7 +13234,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="26" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B123" s="27">
         <v>650</v>
@@ -13235,7 +13257,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="28" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B124" s="29">
         <v>650</v>
@@ -13258,7 +13280,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="26" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B125" s="27">
         <v>650</v>
@@ -13281,7 +13303,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="28" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B126" s="29">
         <v>650</v>
@@ -13304,7 +13326,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="26" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B127" s="27">
         <v>700</v>
@@ -13327,7 +13349,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="28" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B128" s="29">
         <v>700</v>
@@ -13350,7 +13372,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="26" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B129" s="27">
         <v>700</v>
@@ -13373,7 +13395,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="28" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B130" s="29">
         <v>700</v>
@@ -13396,7 +13418,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="26" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B131" s="27">
         <v>700</v>
@@ -13419,7 +13441,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="28" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B132" s="29">
         <v>700</v>
@@ -13442,7 +13464,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="26" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B133" s="27">
         <v>700</v>
@@ -13465,7 +13487,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="28" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B134" s="29">
         <v>700</v>
@@ -13488,7 +13510,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="26" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B135" s="27">
         <v>700</v>
@@ -13511,7 +13533,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="28" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B136" s="29">
         <v>700</v>
@@ -13534,7 +13556,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="26" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B137" s="27">
         <v>750</v>
@@ -13557,7 +13579,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="28" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B138" s="29">
         <v>750</v>
@@ -13580,7 +13602,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="26" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B139" s="27">
         <v>750</v>
@@ -13603,7 +13625,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="28" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B140" s="29">
         <v>750</v>
@@ -13626,7 +13648,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="26" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B141" s="27">
         <v>750</v>
@@ -13649,7 +13671,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="28" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B142" s="29">
         <v>750</v>
@@ -13672,7 +13694,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="26" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B143" s="27">
         <v>750</v>
@@ -13695,7 +13717,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="28" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B144" s="29">
         <v>750</v>
@@ -13718,7 +13740,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="26" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B145" s="27">
         <v>750</v>
@@ -13741,7 +13763,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="28" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B146" s="29">
         <v>800</v>
@@ -13764,7 +13786,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="26" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B147" s="27">
         <v>800</v>
@@ -13787,7 +13809,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="28" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B148" s="29">
         <v>800</v>
@@ -13810,7 +13832,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="26" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B149" s="27">
         <v>800</v>
@@ -13833,7 +13855,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="28" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B150" s="29">
         <v>800</v>
@@ -13856,7 +13878,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="26" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B151" s="27">
         <v>800</v>
@@ -13879,7 +13901,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="28" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B152" s="29">
         <v>800</v>
@@ -13902,7 +13924,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="26" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B153" s="27">
         <v>800</v>
@@ -13925,7 +13947,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="28" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B154" s="29">
         <v>800</v>
